--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\ASV-Manager\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ABF277-B30D-4A19-8E5B-FDB337491C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77969F03-6AA4-4E79-BCBF-E9C146641129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="159">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -474,6 +474,54 @@
   </si>
   <si>
     <t>U12_2</t>
+  </si>
+  <si>
+    <t>MÄDCHENCAMP</t>
+  </si>
+  <si>
+    <t>Neudörfl</t>
+  </si>
+  <si>
+    <t>Neudöfl</t>
+  </si>
+  <si>
+    <t>Kittsee</t>
+  </si>
+  <si>
+    <t>Deutsch Jahrndorf</t>
+  </si>
+  <si>
+    <t>Tadten</t>
+  </si>
+  <si>
+    <t>Mönchhof</t>
+  </si>
+  <si>
+    <t>Winden</t>
+  </si>
+  <si>
+    <t>Gattendorf</t>
+  </si>
+  <si>
+    <t>Wallern</t>
+  </si>
+  <si>
+    <t>Siegendorf</t>
+  </si>
+  <si>
+    <t>Hornstein</t>
+  </si>
+  <si>
+    <t>Gols</t>
+  </si>
+  <si>
+    <t>Illmitz</t>
+  </si>
+  <si>
+    <t>Andau</t>
+  </si>
+  <si>
+    <t>BFV-CUP</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1590,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1674,475 +1722,756 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="D6" s="13">
+        <v>46213</v>
+      </c>
+      <c r="E6" s="111">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6">
-        <v>2</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="D7" s="13">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="111">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6">
-        <v>3</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="D8" s="13">
+        <v>46213</v>
+      </c>
+      <c r="E8" s="111">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B9" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="D9" s="14">
+        <v>46249</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B10" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="D10" s="14">
+        <v>46256</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B11" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="D11" s="14">
+        <v>46263</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B12" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="D12" s="14">
+        <v>46270</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B13" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="D13" s="14">
+        <v>46277</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="D14" s="14">
+        <v>46284</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B15" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="D15" s="14">
+        <v>46291</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="D16" s="14">
+        <v>46297</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B17" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="D17" s="14">
+        <v>46305</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B18" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="D18" s="14">
+        <v>46312</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B19" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="D19" s="14">
+        <v>46319</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B20" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="D20" s="14">
+        <v>46326</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B21" s="6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="D21" s="14">
+        <v>46333</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B22" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
+      <c r="D22" s="14">
+        <v>46249</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B23" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+      <c r="D23" s="14">
+        <v>46256</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B24" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+      <c r="D24" s="14">
+        <v>46263</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B25" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+      <c r="D25" s="14">
+        <v>46270</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B26" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
+      <c r="D26" s="14">
+        <v>46277</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B27" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
+      <c r="D27" s="14">
+        <v>46284</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B28" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
+      <c r="D28" s="14">
+        <v>46291</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B29" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+      <c r="D29" s="14">
+        <v>46297</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B30" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
+      <c r="D30" s="14">
+        <v>46305</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B31" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+      <c r="D31" s="14">
+        <v>46312</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="29">
-        <v>14</v>
-      </c>
-      <c r="B32" s="29">
-        <v>1</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
+      <c r="A32" s="6">
+        <v>11</v>
+      </c>
+      <c r="B32" s="6">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="14">
+        <v>46319</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="29">
-        <v>15</v>
-      </c>
-      <c r="B33" s="29">
+      <c r="A33" s="6">
+        <v>12</v>
+      </c>
+      <c r="B33" s="6">
+        <v>12</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="14">
+        <v>46326</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <v>13</v>
+      </c>
+      <c r="B34" s="6">
+        <v>13</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="14">
+        <v>46333</v>
+      </c>
+      <c r="E34" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="29">
-        <v>16</v>
-      </c>
-      <c r="B34" s="29">
-        <v>3</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
+      <c r="G34" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="29">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B35" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35" s="29" t="s">
         <v>39</v>
@@ -2155,10 +2484,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="29">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B36" s="29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C36" s="29" t="s">
         <v>39</v>
@@ -2171,10 +2500,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="29">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B37" s="29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C37" s="29" t="s">
         <v>39</v>
@@ -2187,10 +2516,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="29">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B38" s="29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C38" s="29" t="s">
         <v>39</v>
@@ -2203,10 +2532,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="29">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B39" s="29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C39" s="29" t="s">
         <v>39</v>
@@ -2219,10 +2548,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="29">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B40" s="29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>39</v>
@@ -2235,10 +2564,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="29">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B41" s="29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C41" s="29" t="s">
         <v>39</v>
@@ -2250,59 +2579,59 @@
       <c r="H41" s="29"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="8">
-        <v>25</v>
-      </c>
-      <c r="B42" s="8">
-        <v>2</v>
-      </c>
-      <c r="C42" s="8" t="s">
+      <c r="A42" s="29">
+        <v>21</v>
+      </c>
+      <c r="B42" s="29">
+        <v>8</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="36"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="29">
+        <v>22</v>
+      </c>
+      <c r="B43" s="29">
+        <v>9</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="36"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="29">
         <v>23</v>
       </c>
-      <c r="D42" s="15"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
-        <v>26</v>
-      </c>
-      <c r="B43" s="8">
-        <v>3</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43" s="15"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
-        <v>27</v>
-      </c>
-      <c r="B44" s="8">
-        <v>4</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
+      <c r="B44" s="29">
+        <v>10</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="36"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B45" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>23</v>
@@ -2315,10 +2644,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B46" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>23</v>
@@ -2331,10 +2660,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B47" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>23</v>
@@ -2347,10 +2676,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B48" s="8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>23</v>
@@ -2363,10 +2692,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B49" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>23</v>
@@ -2377,65 +2706,60 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:10" s="17" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="26">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>31</v>
+      </c>
+      <c r="B50" s="8">
+        <v>8</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="15"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>32</v>
+      </c>
+      <c r="B51" s="8">
+        <v>9</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="15"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>33</v>
+      </c>
+      <c r="B52" s="8">
+        <v>10</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="15"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" s="17" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="26">
         <v>34</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B53" s="20">
         <v>1</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="21"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="24"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="26">
-        <v>35</v>
-      </c>
-      <c r="B51" s="20">
-        <v>2</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="21"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="25"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="26">
-        <v>36</v>
-      </c>
-      <c r="B52" s="20">
-        <v>3</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="21"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="25"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="26">
-        <v>37</v>
-      </c>
-      <c r="B53" s="20">
-        <v>4</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>13</v>
@@ -2445,15 +2769,14 @@
       <c r="F53" s="20"/>
       <c r="G53" s="20"/>
       <c r="H53" s="20"/>
-      <c r="I53" s="23"/>
-      <c r="J53" s="25"/>
+      <c r="I53" s="24"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="26">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B54" s="20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>13</v>
@@ -2468,10 +2791,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="26">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B55" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>13</v>
@@ -2486,10 +2809,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="26">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B56" s="20">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>13</v>
@@ -2504,10 +2827,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="26">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B57" s="20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C57" s="20" t="s">
         <v>13</v>
@@ -2520,60 +2843,66 @@
       <c r="I57" s="23"/>
       <c r="J57" s="25"/>
     </row>
-    <row r="58" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="26">
+        <v>40</v>
+      </c>
+      <c r="B58" s="20">
+        <v>7</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="21"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="25"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="26">
+        <v>41</v>
+      </c>
+      <c r="B59" s="20">
+        <v>8</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="21"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="25"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="26">
+        <v>42</v>
+      </c>
+      <c r="B60" s="20">
+        <v>9</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="21"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="23"/>
+      <c r="J60" s="25"/>
+    </row>
+    <row r="61" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="10">
         <v>44</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B61" s="10">
         <v>1</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D58" s="31"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="10">
-        <v>46</v>
-      </c>
-      <c r="B59" s="10">
-        <v>3</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D59" s="31"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="10">
-        <v>47</v>
-      </c>
-      <c r="B60" s="10">
-        <v>4</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D60" s="31"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="10">
-        <v>48</v>
-      </c>
-      <c r="B61" s="10">
-        <v>5</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>141</v>
@@ -2586,10 +2915,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B62" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>141</v>
@@ -2602,10 +2931,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B63" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>141</v>
@@ -2618,10 +2947,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B64" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>141</v>
@@ -2634,10 +2963,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B65" s="10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>141</v>
@@ -2649,59 +2978,59 @@
       <c r="H65" s="10"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="27">
-        <v>54</v>
-      </c>
-      <c r="B66" s="27">
-        <v>1</v>
-      </c>
-      <c r="C66" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="D66" s="32"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
+      <c r="A66" s="10">
+        <v>51</v>
+      </c>
+      <c r="B66" s="10">
+        <v>8</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="31"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="27">
-        <v>55</v>
-      </c>
-      <c r="B67" s="27">
-        <v>2</v>
-      </c>
-      <c r="C67" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="D67" s="32"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
+      <c r="A67" s="10">
+        <v>52</v>
+      </c>
+      <c r="B67" s="10">
+        <v>9</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="31"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="27">
-        <v>56</v>
-      </c>
-      <c r="B68" s="27">
-        <v>3</v>
-      </c>
-      <c r="C68" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="D68" s="32"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
+      <c r="A68" s="10">
+        <v>53</v>
+      </c>
+      <c r="B68" s="10">
+        <v>10</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="31"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="27">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B69" s="27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C69" s="27" t="s">
         <v>142</v>
@@ -2714,10 +3043,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="27">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B70" s="27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C70" s="27" t="s">
         <v>142</v>
@@ -2730,10 +3059,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="27">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B71" s="27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C71" s="27" t="s">
         <v>142</v>
@@ -2746,10 +3075,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="27">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B72" s="27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C72" s="27" t="s">
         <v>142</v>
@@ -2762,10 +3091,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="27">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B73" s="27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C73" s="27" t="s">
         <v>142</v>
@@ -2777,59 +3106,59 @@
       <c r="H73" s="27"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="12">
-        <v>64</v>
-      </c>
-      <c r="B74" s="12">
-        <v>1</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" s="37"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
+      <c r="A74" s="27">
+        <v>60</v>
+      </c>
+      <c r="B74" s="27">
+        <v>7</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" s="32"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="H74" s="27"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="12">
-        <v>65</v>
-      </c>
-      <c r="B75" s="12">
-        <v>2</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D75" s="37"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
+      <c r="A75" s="27">
+        <v>61</v>
+      </c>
+      <c r="B75" s="27">
+        <v>8</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" s="32"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="12">
-        <v>66</v>
-      </c>
-      <c r="B76" s="12">
-        <v>3</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D76" s="37"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
+      <c r="A76" s="27">
+        <v>62</v>
+      </c>
+      <c r="B76" s="27">
+        <v>9</v>
+      </c>
+      <c r="C76" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" s="32"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="12">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B77" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>38</v>
@@ -2841,9 +3170,11 @@
       <c r="H77" s="12"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="12"/>
+      <c r="A78" s="12">
+        <v>65</v>
+      </c>
       <c r="B78" s="12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>38</v>
@@ -2855,9 +3186,11 @@
       <c r="H78" s="12"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="12"/>
+      <c r="A79" s="12">
+        <v>66</v>
+      </c>
       <c r="B79" s="12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>38</v>
@@ -2869,9 +3202,11 @@
       <c r="H79" s="12"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="12"/>
+      <c r="A80" s="12">
+        <v>67</v>
+      </c>
       <c r="B80" s="12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>38</v>
@@ -2885,7 +3220,7 @@
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="12"/>
       <c r="B81" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>38</v>
@@ -2899,7 +3234,7 @@
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="12"/>
       <c r="B82" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>38</v>
@@ -2911,11 +3246,9 @@
       <c r="H82" s="12"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="12">
-        <v>68</v>
-      </c>
+      <c r="A83" s="12"/>
       <c r="B83" s="12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>38</v>
@@ -2927,57 +3260,55 @@
       <c r="H83" s="12"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="33">
+      <c r="A84" s="12"/>
+      <c r="B84" s="12">
+        <v>8</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D84" s="37"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="12"/>
+      <c r="B85" s="12">
+        <v>9</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" s="37"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="12">
+        <v>68</v>
+      </c>
+      <c r="B86" s="12">
+        <v>10</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" s="37"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="33">
         <v>69</v>
       </c>
-      <c r="B84" s="33">
+      <c r="B87" s="33">
         <v>1</v>
-      </c>
-      <c r="C84" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="D84" s="34"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="33"/>
-      <c r="H84" s="33"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="33">
-        <v>70</v>
-      </c>
-      <c r="B85" s="33">
-        <v>2</v>
-      </c>
-      <c r="C85" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="D85" s="34"/>
-      <c r="E85" s="35"/>
-      <c r="F85" s="33"/>
-      <c r="G85" s="33"/>
-      <c r="H85" s="33"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="33">
-        <v>71</v>
-      </c>
-      <c r="B86" s="33">
-        <v>3</v>
-      </c>
-      <c r="C86" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="D86" s="34"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="33"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="33"/>
-      <c r="B87" s="33">
-        <v>4</v>
       </c>
       <c r="C87" s="33" t="s">
         <v>136</v>
@@ -2989,9 +3320,11 @@
       <c r="H87" s="33"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="33"/>
+      <c r="A88" s="33">
+        <v>70</v>
+      </c>
       <c r="B88" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C88" s="33" t="s">
         <v>136</v>
@@ -3003,9 +3336,11 @@
       <c r="H88" s="33"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="33"/>
+      <c r="A89" s="33">
+        <v>71</v>
+      </c>
       <c r="B89" s="33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C89" s="33" t="s">
         <v>136</v>
@@ -3019,7 +3354,7 @@
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="33"/>
       <c r="B90" s="33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C90" s="33" t="s">
         <v>136</v>
@@ -3033,7 +3368,7 @@
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="33"/>
       <c r="B91" s="33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C91" s="33" t="s">
         <v>136</v>
@@ -3045,11 +3380,9 @@
       <c r="H91" s="33"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="33">
-        <v>72</v>
-      </c>
+      <c r="A92" s="33"/>
       <c r="B92" s="33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C92" s="33" t="s">
         <v>136</v>
@@ -3061,11 +3394,9 @@
       <c r="H92" s="33"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="33">
-        <v>73</v>
-      </c>
+      <c r="A93" s="33"/>
       <c r="B93" s="33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C93" s="33" t="s">
         <v>136</v>
@@ -3077,55 +3408,57 @@
       <c r="H93" s="33"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="53">
+      <c r="A94" s="33"/>
+      <c r="B94" s="33">
+        <v>8</v>
+      </c>
+      <c r="C94" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D94" s="34"/>
+      <c r="E94" s="35"/>
+      <c r="F94" s="33"/>
+      <c r="G94" s="33"/>
+      <c r="H94" s="33"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="33">
+        <v>72</v>
+      </c>
+      <c r="B95" s="33">
+        <v>9</v>
+      </c>
+      <c r="C95" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D95" s="34"/>
+      <c r="E95" s="35"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="33"/>
+      <c r="H95" s="33"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="33">
+        <v>73</v>
+      </c>
+      <c r="B96" s="33">
+        <v>10</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D96" s="34"/>
+      <c r="E96" s="35"/>
+      <c r="F96" s="33"/>
+      <c r="G96" s="33"/>
+      <c r="H96" s="33"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="53">
         <v>74</v>
       </c>
-      <c r="B94" s="53">
+      <c r="B97" s="53">
         <v>1</v>
-      </c>
-      <c r="C94" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="D94" s="54"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
-      <c r="H94" s="53"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="53">
-        <v>75</v>
-      </c>
-      <c r="B95" s="53">
-        <v>2</v>
-      </c>
-      <c r="C95" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="D95" s="54"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
-      <c r="H95" s="53"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="53"/>
-      <c r="B96" s="53">
-        <v>3</v>
-      </c>
-      <c r="C96" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="D96" s="54"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="53"/>
-      <c r="H96" s="53"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="53"/>
-      <c r="B97" s="53">
-        <v>4</v>
       </c>
       <c r="C97" s="53" t="s">
         <v>24</v>
@@ -3137,9 +3470,11 @@
       <c r="H97" s="53"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="53"/>
+      <c r="A98" s="53">
+        <v>75</v>
+      </c>
       <c r="B98" s="53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C98" s="53" t="s">
         <v>24</v>
@@ -3153,7 +3488,7 @@
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="53"/>
       <c r="B99" s="53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C99" s="53" t="s">
         <v>24</v>
@@ -3167,7 +3502,7 @@
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="53"/>
       <c r="B100" s="53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C100" s="53" t="s">
         <v>24</v>
@@ -3179,11 +3514,9 @@
       <c r="H100" s="53"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="53">
-        <v>76</v>
-      </c>
+      <c r="A101" s="53"/>
       <c r="B101" s="53">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C101" s="53" t="s">
         <v>24</v>
@@ -3195,11 +3528,9 @@
       <c r="H101" s="53"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="53">
-        <v>77</v>
-      </c>
+      <c r="A102" s="53"/>
       <c r="B102" s="53">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C102" s="53" t="s">
         <v>24</v>
@@ -3211,11 +3542,9 @@
       <c r="H102" s="53"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="53">
-        <v>78</v>
-      </c>
+      <c r="A103" s="53"/>
       <c r="B103" s="53">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C103" s="53" t="s">
         <v>24</v>
@@ -3227,53 +3556,59 @@
       <c r="H103" s="53"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="116">
+      <c r="A104" s="53">
+        <v>76</v>
+      </c>
+      <c r="B104" s="53">
+        <v>8</v>
+      </c>
+      <c r="C104" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" s="54"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="53"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="53">
+        <v>77</v>
+      </c>
+      <c r="B105" s="53">
+        <v>9</v>
+      </c>
+      <c r="C105" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" s="54"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
+      <c r="H105" s="53"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="53">
+        <v>78</v>
+      </c>
+      <c r="B106" s="53">
+        <v>10</v>
+      </c>
+      <c r="C106" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" s="54"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="53"/>
+      <c r="G106" s="53"/>
+      <c r="H106" s="53"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="116">
         <v>79</v>
       </c>
-      <c r="B104" s="116">
+      <c r="B107" s="116">
         <v>1</v>
-      </c>
-      <c r="C104" s="116" t="s">
-        <v>20</v>
-      </c>
-      <c r="D104" s="117"/>
-      <c r="E104" s="118"/>
-      <c r="F104" s="119"/>
-      <c r="G104" s="119"/>
-      <c r="H104" s="119"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="116"/>
-      <c r="B105" s="116">
-        <v>2</v>
-      </c>
-      <c r="C105" s="116" t="s">
-        <v>20</v>
-      </c>
-      <c r="D105" s="117"/>
-      <c r="E105" s="118"/>
-      <c r="F105" s="119"/>
-      <c r="G105" s="119"/>
-      <c r="H105" s="119"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="116"/>
-      <c r="B106" s="116">
-        <v>3</v>
-      </c>
-      <c r="C106" s="116" t="s">
-        <v>20</v>
-      </c>
-      <c r="D106" s="117"/>
-      <c r="E106" s="118"/>
-      <c r="F106" s="119"/>
-      <c r="G106" s="119"/>
-      <c r="H106" s="119"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="116"/>
-      <c r="B107" s="116">
-        <v>4</v>
       </c>
       <c r="C107" s="116" t="s">
         <v>20</v>
@@ -3287,7 +3622,7 @@
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="116"/>
       <c r="B108" s="116">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C108" s="116" t="s">
         <v>20</v>
@@ -3299,53 +3634,51 @@
       <c r="H108" s="119"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="112"/>
-      <c r="B109" s="112">
+      <c r="A109" s="116"/>
+      <c r="B109" s="116">
+        <v>3</v>
+      </c>
+      <c r="C109" s="116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D109" s="117"/>
+      <c r="E109" s="118"/>
+      <c r="F109" s="119"/>
+      <c r="G109" s="119"/>
+      <c r="H109" s="119"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="116"/>
+      <c r="B110" s="116">
+        <v>4</v>
+      </c>
+      <c r="C110" s="116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" s="117"/>
+      <c r="E110" s="118"/>
+      <c r="F110" s="119"/>
+      <c r="G110" s="119"/>
+      <c r="H110" s="119"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="116"/>
+      <c r="B111" s="116">
+        <v>5</v>
+      </c>
+      <c r="C111" s="116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="117"/>
+      <c r="E111" s="118"/>
+      <c r="F111" s="119"/>
+      <c r="G111" s="119"/>
+      <c r="H111" s="119"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="112"/>
+      <c r="B112" s="112">
         <v>1</v>
-      </c>
-      <c r="C109" s="112" t="s">
-        <v>62</v>
-      </c>
-      <c r="D109" s="113"/>
-      <c r="E109" s="114"/>
-      <c r="F109" s="115"/>
-      <c r="G109" s="115"/>
-      <c r="H109" s="115"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="112"/>
-      <c r="B110" s="112">
-        <v>2</v>
-      </c>
-      <c r="C110" s="112" t="s">
-        <v>62</v>
-      </c>
-      <c r="D110" s="113"/>
-      <c r="E110" s="114"/>
-      <c r="F110" s="115"/>
-      <c r="G110" s="115"/>
-      <c r="H110" s="115"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="112"/>
-      <c r="B111" s="112">
-        <v>3</v>
-      </c>
-      <c r="C111" s="112" t="s">
-        <v>62</v>
-      </c>
-      <c r="D111" s="113"/>
-      <c r="E111" s="114"/>
-      <c r="F111" s="115"/>
-      <c r="G111" s="115"/>
-      <c r="H111" s="115"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="112">
-        <v>80</v>
-      </c>
-      <c r="B112" s="112">
-        <v>4</v>
       </c>
       <c r="C112" s="112" t="s">
         <v>62</v>
@@ -3357,11 +3690,9 @@
       <c r="H112" s="115"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="112">
-        <v>81</v>
-      </c>
+      <c r="A113" s="112"/>
       <c r="B113" s="112">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C113" s="112" t="s">
         <v>62</v>
@@ -3373,87 +3704,61 @@
       <c r="H113" s="115"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="40"/>
-      <c r="B114" s="40">
-        <v>1</v>
-      </c>
-      <c r="C114" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="D114" s="83">
-        <v>46321</v>
-      </c>
-      <c r="E114" s="106">
-        <v>0.375</v>
-      </c>
-      <c r="F114" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="G114" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="H114" s="41" t="s">
-        <v>10</v>
-      </c>
+      <c r="A114" s="112"/>
+      <c r="B114" s="112">
+        <v>3</v>
+      </c>
+      <c r="C114" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="D114" s="113"/>
+      <c r="E114" s="114"/>
+      <c r="F114" s="115"/>
+      <c r="G114" s="115"/>
+      <c r="H114" s="115"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="40"/>
-      <c r="B115" s="40">
-        <v>2</v>
-      </c>
-      <c r="C115" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="D115" s="83">
-        <v>46322</v>
-      </c>
-      <c r="E115" s="106">
-        <v>0.375</v>
-      </c>
-      <c r="F115" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="G115" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="H115" s="41" t="s">
-        <v>10</v>
-      </c>
+      <c r="A115" s="112">
+        <v>80</v>
+      </c>
+      <c r="B115" s="112">
+        <v>4</v>
+      </c>
+      <c r="C115" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="D115" s="113"/>
+      <c r="E115" s="114"/>
+      <c r="F115" s="115"/>
+      <c r="G115" s="115"/>
+      <c r="H115" s="115"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="40"/>
-      <c r="B116" s="40">
-        <v>3</v>
-      </c>
-      <c r="C116" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="D116" s="83">
-        <v>46323</v>
-      </c>
-      <c r="E116" s="106">
-        <v>0.375</v>
-      </c>
-      <c r="F116" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="G116" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="H116" s="41" t="s">
-        <v>10</v>
-      </c>
+      <c r="A116" s="112">
+        <v>81</v>
+      </c>
+      <c r="B116" s="112">
+        <v>5</v>
+      </c>
+      <c r="C116" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="D116" s="113"/>
+      <c r="E116" s="114"/>
+      <c r="F116" s="115"/>
+      <c r="G116" s="115"/>
+      <c r="H116" s="115"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="40"/>
       <c r="B117" s="40">
         <v>1</v>
       </c>
-      <c r="C117" s="83" t="s">
-        <v>137</v>
+      <c r="C117" s="40" t="s">
+        <v>139</v>
       </c>
       <c r="D117" s="83">
-        <v>46230</v>
+        <v>46321</v>
       </c>
       <c r="E117" s="106">
         <v>0.375</v>
@@ -3473,11 +3778,11 @@
       <c r="B118" s="40">
         <v>2</v>
       </c>
-      <c r="C118" s="83" t="s">
-        <v>137</v>
+      <c r="C118" s="40" t="s">
+        <v>139</v>
       </c>
       <c r="D118" s="83">
-        <v>46231</v>
+        <v>46322</v>
       </c>
       <c r="E118" s="106">
         <v>0.375</v>
@@ -3497,11 +3802,11 @@
       <c r="B119" s="40">
         <v>3</v>
       </c>
-      <c r="C119" s="83" t="s">
-        <v>137</v>
+      <c r="C119" s="40" t="s">
+        <v>139</v>
       </c>
       <c r="D119" s="83">
-        <v>46232</v>
+        <v>46323</v>
       </c>
       <c r="E119" s="106">
         <v>0.375</v>
@@ -3519,13 +3824,13 @@
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="40"/>
       <c r="B120" s="40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C120" s="83" t="s">
         <v>137</v>
       </c>
       <c r="D120" s="83">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="E120" s="106">
         <v>0.375</v>
@@ -3543,13 +3848,13 @@
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="40"/>
       <c r="B121" s="40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C121" s="83" t="s">
         <v>137</v>
       </c>
       <c r="D121" s="83">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="E121" s="106">
         <v>0.375</v>
@@ -3565,50 +3870,194 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="51">
+      <c r="A122" s="40"/>
+      <c r="B122" s="40">
+        <v>3</v>
+      </c>
+      <c r="C122" s="83" t="s">
+        <v>137</v>
+      </c>
+      <c r="D122" s="83">
+        <v>46232</v>
+      </c>
+      <c r="E122" s="106">
+        <v>0.375</v>
+      </c>
+      <c r="F122" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G122" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H122" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="40"/>
+      <c r="B123" s="40">
+        <v>4</v>
+      </c>
+      <c r="C123" s="83" t="s">
+        <v>137</v>
+      </c>
+      <c r="D123" s="83">
+        <v>46233</v>
+      </c>
+      <c r="E123" s="106">
+        <v>0.375</v>
+      </c>
+      <c r="F123" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G123" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H123" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="40"/>
+      <c r="B124" s="40">
+        <v>5</v>
+      </c>
+      <c r="C124" s="83" t="s">
+        <v>137</v>
+      </c>
+      <c r="D124" s="83">
+        <v>46234</v>
+      </c>
+      <c r="E124" s="106">
+        <v>0.375</v>
+      </c>
+      <c r="F124" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G124" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H124" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="40"/>
+      <c r="B125" s="40">
+        <v>1</v>
+      </c>
+      <c r="C125" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="D125" s="83">
+        <v>46237</v>
+      </c>
+      <c r="E125" s="106">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F125" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G125" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H125" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="40"/>
+      <c r="B126" s="40">
+        <v>2</v>
+      </c>
+      <c r="C126" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="D126" s="83">
+        <v>46238</v>
+      </c>
+      <c r="E126" s="106">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F126" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G126" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H126" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="40"/>
+      <c r="B127" s="40">
+        <v>3</v>
+      </c>
+      <c r="C127" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="D127" s="83">
+        <v>46239</v>
+      </c>
+      <c r="E127" s="106">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F127" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="G127" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H127" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="51">
         <v>83</v>
       </c>
-      <c r="B122" s="51">
+      <c r="B128" s="51">
         <v>2</v>
       </c>
-      <c r="C122" s="51" t="s">
+      <c r="C128" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D122" s="84">
+      <c r="D128" s="84">
         <v>46256</v>
       </c>
-      <c r="E122" s="107">
+      <c r="E128" s="107">
         <v>0.375</v>
       </c>
-      <c r="F122" s="52" t="s">
+      <c r="F128" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="G122" s="12" t="s">
+      <c r="G128" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="H122" s="52" t="s">
+      <c r="H128" s="52" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H93" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H93">
-      <sortCondition ref="A1:A93"/>
+  <autoFilter ref="A1:H96" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H96">
+      <sortCondition ref="A1:A96"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="49" max="16383" man="1"/>
-    <brk id="57" max="16383" man="1"/>
+    <brk id="52" max="16383" man="1"/>
+    <brk id="60" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="108"/>
@@ -3703,7 +4152,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D3" s="39">
-        <f t="shared" ref="D3:D66" si="0">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
+        <f t="shared" ref="D3:D8" si="0">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
         <v>0.86458333333333326</v>
       </c>
       <c r="E3" s="39" t="str">
@@ -3804,27 +4253,27 @@
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="105">
         <f>'Nach Mannschaften sortiert'!D6</f>
-        <v>0</v>
+        <v>46213</v>
       </c>
       <c r="C6" s="39">
         <f>'Nach Mannschaften sortiert'!E6</f>
-        <v>0</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D6" s="39">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E6" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="120">
+        <v>NEUDÖRFL</v>
+      </c>
+      <c r="G6" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H6</f>
-        <v>0</v>
-      </c>
-      <c r="H6">
+        <v>Auswärts</v>
+      </c>
+      <c r="H6" t="str">
         <f>'Nach Mannschaften sortiert'!G6</f>
-        <v>0</v>
+        <v>Neudöfl</v>
       </c>
       <c r="I6" t="str">
         <f>'Nach Mannschaften sortiert'!C6</f>
@@ -3834,33 +4283,33 @@
         <v>96</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="105">
         <f>'Nach Mannschaften sortiert'!D7</f>
-        <v>0</v>
+        <v>46235</v>
       </c>
       <c r="C7" s="39">
         <f>'Nach Mannschaften sortiert'!E7</f>
-        <v>0</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D7" s="39">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E7" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="120">
+        <v>KITTSEE</v>
+      </c>
+      <c r="G7" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
-        <v>0</v>
-      </c>
-      <c r="H7">
+        <v>Auswärts</v>
+      </c>
+      <c r="H7" t="str">
         <f>'Nach Mannschaften sortiert'!G7</f>
-        <v>0</v>
+        <v>Kittsee</v>
       </c>
       <c r="I7" t="str">
         <f>'Nach Mannschaften sortiert'!C7</f>
@@ -3870,33 +4319,33 @@
         <v>96</v>
       </c>
       <c r="K7" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="105">
         <f>'Nach Mannschaften sortiert'!D8</f>
-        <v>0</v>
+        <v>46213</v>
       </c>
       <c r="C8" s="39">
         <f>'Nach Mannschaften sortiert'!E8</f>
-        <v>0</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D8" s="39">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E8" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="120">
+        <v>NEUDÖRFL</v>
+      </c>
+      <c r="G8" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
-        <v>0</v>
-      </c>
-      <c r="H8">
+        <v>Auswärts</v>
+      </c>
+      <c r="H8" t="str">
         <f>'Nach Mannschaften sortiert'!G8</f>
-        <v>0</v>
+        <v>Neudöfl</v>
       </c>
       <c r="I8" t="str">
         <f>'Nach Mannschaften sortiert'!C8</f>
@@ -3906,33 +4355,33 @@
         <v>96</v>
       </c>
       <c r="K8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="105">
         <f>'Nach Mannschaften sortiert'!D9</f>
-        <v>0</v>
+        <v>46249</v>
       </c>
       <c r="C9" s="39">
         <f>'Nach Mannschaften sortiert'!E9</f>
-        <v>0</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D9" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" ref="D3:D69" si="1">IF(I9 = "KM",C9+"1:45",IF(I9="U23",C9+"1:45",IF(I9 = "U16",C9+"1:45",IF(I9 = "U15",C9+"1:30",IF(I9 = "U14",C9+"1:30",IF(I9 = "U13",C9+"1:35",IF(I9 = "U12",C9+"1:10",IF(I9 = "U11",C9+"1:10",IF(I9 = "U10",C9+"1:03",C9+"3:00")))))))))</f>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E9" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="120">
+        <v>KITTSEE</v>
+      </c>
+      <c r="G9" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
-        <v>0</v>
-      </c>
-      <c r="H9">
+        <v>Auswärts</v>
+      </c>
+      <c r="H9" t="str">
         <f>'Nach Mannschaften sortiert'!G9</f>
-        <v>0</v>
+        <v>Kittsee</v>
       </c>
       <c r="I9" t="str">
         <f>'Nach Mannschaften sortiert'!C9</f>
@@ -3948,27 +4397,27 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="105">
         <f>'Nach Mannschaften sortiert'!D10</f>
-        <v>0</v>
+        <v>46256</v>
       </c>
       <c r="C10" s="39">
         <f>'Nach Mannschaften sortiert'!E10</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D10" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.78125</v>
       </c>
       <c r="E10" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="120">
+        <v>DEUTSCH JAHRNDORF</v>
+      </c>
+      <c r="G10" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
-        <v>0</v>
-      </c>
-      <c r="H10">
+        <v>Auswärts</v>
+      </c>
+      <c r="H10" t="str">
         <f>'Nach Mannschaften sortiert'!G10</f>
-        <v>0</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I10" t="str">
         <f>'Nach Mannschaften sortiert'!C10</f>
@@ -3984,27 +4433,27 @@
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="105">
         <f>'Nach Mannschaften sortiert'!D11</f>
-        <v>0</v>
+        <v>46263</v>
       </c>
       <c r="C11" s="39">
         <f>'Nach Mannschaften sortiert'!E11</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D11" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.78125</v>
       </c>
       <c r="E11" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G11" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
-        <v>0</v>
-      </c>
-      <c r="H11">
+        <v>Heim</v>
+      </c>
+      <c r="H11" t="str">
         <f>'Nach Mannschaften sortiert'!G11</f>
-        <v>0</v>
+        <v>Tadten</v>
       </c>
       <c r="I11" t="str">
         <f>'Nach Mannschaften sortiert'!C11</f>
@@ -4020,27 +4469,27 @@
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="105">
         <f>'Nach Mannschaften sortiert'!D12</f>
-        <v>0</v>
+        <v>46270</v>
       </c>
       <c r="C12" s="39">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="D12" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E12" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="120">
+        <v>MÖNCHHOF</v>
+      </c>
+      <c r="G12" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
-        <v>0</v>
-      </c>
-      <c r="H12">
+        <v>Auswärts</v>
+      </c>
+      <c r="H12" t="str">
         <f>'Nach Mannschaften sortiert'!G12</f>
-        <v>0</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I12" t="str">
         <f>'Nach Mannschaften sortiert'!C12</f>
@@ -4056,27 +4505,27 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="105">
         <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>0</v>
+        <v>46277</v>
       </c>
       <c r="C13" s="39">
         <f>'Nach Mannschaften sortiert'!E13</f>
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="D13" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E13" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G13" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
-        <v>0</v>
-      </c>
-      <c r="H13">
+        <v>Heim</v>
+      </c>
+      <c r="H13" t="str">
         <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>0</v>
+        <v>Winden</v>
       </c>
       <c r="I13" t="str">
         <f>'Nach Mannschaften sortiert'!C13</f>
@@ -4092,27 +4541,27 @@
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="105">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>0</v>
+        <v>46284</v>
       </c>
       <c r="C14" s="39">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D14" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E14" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="120">
+        <v>GATTENDORF</v>
+      </c>
+      <c r="G14" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>0</v>
-      </c>
-      <c r="H14">
+        <v>Auswärts</v>
+      </c>
+      <c r="H14" t="str">
         <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>0</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I14" t="str">
         <f>'Nach Mannschaften sortiert'!C14</f>
@@ -4128,27 +4577,27 @@
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="105">
         <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>0</v>
+        <v>46291</v>
       </c>
       <c r="C15" s="39">
         <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D15" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E15" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G15" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
-        <v>0</v>
-      </c>
-      <c r="H15">
+        <v>Heim</v>
+      </c>
+      <c r="H15" t="str">
         <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>0</v>
+        <v>Wallern</v>
       </c>
       <c r="I15" t="str">
         <f>'Nach Mannschaften sortiert'!C15</f>
@@ -4164,27 +4613,27 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="105">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>0</v>
+        <v>46297</v>
       </c>
       <c r="C16" s="39">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D16" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E16" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="120">
+        <v>SIEGENDORF</v>
+      </c>
+      <c r="G16" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>0</v>
-      </c>
-      <c r="H16">
+        <v>Auswärts</v>
+      </c>
+      <c r="H16" t="str">
         <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>0</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I16" t="str">
         <f>'Nach Mannschaften sortiert'!C16</f>
@@ -4200,27 +4649,27 @@
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="105">
         <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>0</v>
+        <v>46305</v>
       </c>
       <c r="C17" s="39">
         <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D17" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.71875</v>
       </c>
       <c r="E17" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G17" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>0</v>
-      </c>
-      <c r="H17">
+        <v>Heim</v>
+      </c>
+      <c r="H17" t="str">
         <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>0</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I17" t="str">
         <f>'Nach Mannschaften sortiert'!C17</f>
@@ -4236,27 +4685,27 @@
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="105">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>0</v>
+        <v>46312</v>
       </c>
       <c r="C18" s="39">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D18" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.71875</v>
       </c>
       <c r="E18" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="120">
+        <v>HORNSTEIN</v>
+      </c>
+      <c r="G18" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>0</v>
-      </c>
-      <c r="H18">
+        <v>Auswärts</v>
+      </c>
+      <c r="H18" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>0</v>
+        <v>Hornstein</v>
       </c>
       <c r="I18" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
@@ -4272,31 +4721,31 @@
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="105">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>0</v>
+        <v>46319</v>
       </c>
       <c r="C19" s="39">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D19" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E19" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G19" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>0</v>
-      </c>
-      <c r="H19">
+        <v>Heim</v>
+      </c>
+      <c r="H19" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>0</v>
+        <v>Gols</v>
       </c>
       <c r="I19" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J19" s="108" t="s">
         <v>96</v>
@@ -4308,31 +4757,31 @@
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="105">
         <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>0</v>
+        <v>46326</v>
       </c>
       <c r="C20" s="39">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D20" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.65625</v>
       </c>
       <c r="E20" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="120">
+        <v>ILLMITZ</v>
+      </c>
+      <c r="G20" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>0</v>
-      </c>
-      <c r="H20">
+        <v>Auswärts</v>
+      </c>
+      <c r="H20" t="str">
         <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>0</v>
+        <v>Illmitz</v>
       </c>
       <c r="I20" t="str">
         <f>'Nach Mannschaften sortiert'!C20</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J20" s="108" t="s">
         <v>96</v>
@@ -4344,31 +4793,31 @@
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="105">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>0</v>
+        <v>46333</v>
       </c>
       <c r="C21" s="39">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D21" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.65625</v>
       </c>
       <c r="E21" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G21" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>0</v>
-      </c>
-      <c r="H21">
+        <v>Heim</v>
+      </c>
+      <c r="H21" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I21" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J21" s="108" t="s">
         <v>96</v>
@@ -4380,27 +4829,27 @@
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="105">
         <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>0</v>
+        <v>46249</v>
       </c>
       <c r="C22" s="39">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D22" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.71875</v>
       </c>
       <c r="E22" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="120">
+        <v>KITTSEE</v>
+      </c>
+      <c r="G22" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>0</v>
-      </c>
-      <c r="H22">
+        <v>Auswärts</v>
+      </c>
+      <c r="H22" t="str">
         <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>0</v>
+        <v>Kittsee</v>
       </c>
       <c r="I22" t="str">
         <f>'Nach Mannschaften sortiert'!C22</f>
@@ -4416,27 +4865,27 @@
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="105">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>0</v>
+        <v>46256</v>
       </c>
       <c r="C23" s="39">
         <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D23" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E23" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
-        <v/>
-      </c>
-      <c r="G23" s="120">
+        <v>DEUTSCH JAHRNDORF</v>
+      </c>
+      <c r="G23" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>0</v>
-      </c>
-      <c r="H23">
+        <v>Auswärts</v>
+      </c>
+      <c r="H23" t="str">
         <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>0</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I23" t="str">
         <f>'Nach Mannschaften sortiert'!C23</f>
@@ -4452,27 +4901,27 @@
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="105">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>0</v>
+        <v>46263</v>
       </c>
       <c r="C24" s="39">
         <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D24" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E24" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
-        <v/>
-      </c>
-      <c r="G24" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G24" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
-        <v>0</v>
-      </c>
-      <c r="H24">
+        <v>Heim</v>
+      </c>
+      <c r="H24" t="str">
         <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>0</v>
+        <v>Tadten</v>
       </c>
       <c r="I24" t="str">
         <f>'Nach Mannschaften sortiert'!C24</f>
@@ -4488,27 +4937,27 @@
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="105">
         <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>0</v>
+        <v>46270</v>
       </c>
       <c r="C25" s="39">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D25" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E25" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
-        <v/>
-      </c>
-      <c r="G25" s="120">
+        <v>MÖNCHHOF</v>
+      </c>
+      <c r="G25" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>0</v>
-      </c>
-      <c r="H25">
+        <v>Auswärts</v>
+      </c>
+      <c r="H25" t="str">
         <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>0</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I25" t="str">
         <f>'Nach Mannschaften sortiert'!C25</f>
@@ -4524,27 +4973,27 @@
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="105">
         <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>0</v>
+        <v>46277</v>
       </c>
       <c r="C26" s="39">
         <f>'Nach Mannschaften sortiert'!E26</f>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D26" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E26" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G26" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
-        <v>0</v>
-      </c>
-      <c r="H26">
+        <v>Heim</v>
+      </c>
+      <c r="H26" t="str">
         <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>0</v>
+        <v>Winden</v>
       </c>
       <c r="I26" t="str">
         <f>'Nach Mannschaften sortiert'!C26</f>
@@ -4560,27 +5009,27 @@
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="105">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>0</v>
+        <v>46284</v>
       </c>
       <c r="C27" s="39">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D27" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.65625</v>
       </c>
       <c r="E27" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="120">
+        <v>GATTENDORF</v>
+      </c>
+      <c r="G27" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>0</v>
-      </c>
-      <c r="H27">
+        <v>Auswärts</v>
+      </c>
+      <c r="H27" t="str">
         <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>0</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I27" t="str">
         <f>'Nach Mannschaften sortiert'!C27</f>
@@ -4596,27 +5045,27 @@
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="105">
         <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>0</v>
+        <v>46291</v>
       </c>
       <c r="C28" s="39">
         <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D28" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.65625</v>
       </c>
       <c r="E28" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G28" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
-        <v>0</v>
-      </c>
-      <c r="H28">
+        <v>Heim</v>
+      </c>
+      <c r="H28" t="str">
         <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>0</v>
+        <v>Wallern</v>
       </c>
       <c r="I28" t="str">
         <f>'Nach Mannschaften sortiert'!C28</f>
@@ -4632,27 +5081,27 @@
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="105">
         <f>'Nach Mannschaften sortiert'!D29</f>
-        <v>0</v>
+        <v>46297</v>
       </c>
       <c r="C29" s="39">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.78125</v>
       </c>
       <c r="E29" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="120">
+        <v>SIEGENDORF</v>
+      </c>
+      <c r="G29" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
-        <v>0</v>
-      </c>
-      <c r="H29">
+        <v>Auswärts</v>
+      </c>
+      <c r="H29" t="str">
         <f>'Nach Mannschaften sortiert'!G29</f>
-        <v>0</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I29" t="str">
         <f>'Nach Mannschaften sortiert'!C29</f>
@@ -4668,27 +5117,27 @@
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="105">
         <f>'Nach Mannschaften sortiert'!D30</f>
-        <v>0</v>
+        <v>46305</v>
       </c>
       <c r="C30" s="39">
         <f>'Nach Mannschaften sortiert'!E30</f>
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="D30" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.63541666666666663</v>
       </c>
       <c r="E30" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G30" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
-        <v>0</v>
-      </c>
-      <c r="H30">
+        <v>Heim</v>
+      </c>
+      <c r="H30" t="str">
         <f>'Nach Mannschaften sortiert'!G30</f>
-        <v>0</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I30" t="str">
         <f>'Nach Mannschaften sortiert'!C30</f>
@@ -4704,27 +5153,27 @@
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="105">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>0</v>
+        <v>46312</v>
       </c>
       <c r="C31" s="39">
         <f>'Nach Mannschaften sortiert'!E31</f>
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="D31" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.63541666666666663</v>
       </c>
       <c r="E31" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="120">
+        <v>HORNSTEIN</v>
+      </c>
+      <c r="G31" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
-        <v>0</v>
-      </c>
-      <c r="H31">
+        <v>Auswärts</v>
+      </c>
+      <c r="H31" t="str">
         <f>'Nach Mannschaften sortiert'!G31</f>
-        <v>0</v>
+        <v>Hornstein</v>
       </c>
       <c r="I31" t="str">
         <f>'Nach Mannschaften sortiert'!C31</f>
@@ -4740,31 +5189,31 @@
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="105">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>0</v>
+        <v>46319</v>
       </c>
       <c r="C32" s="39">
         <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D32" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.61458333333333326</v>
       </c>
       <c r="E32" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G32" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>0</v>
-      </c>
-      <c r="H32">
+        <v>Heim</v>
+      </c>
+      <c r="H32" t="str">
         <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>0</v>
+        <v>Gols</v>
       </c>
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J32" s="108" t="s">
         <v>96</v>
@@ -4776,31 +5225,31 @@
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="105">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>0</v>
+        <v>46326</v>
       </c>
       <c r="C33" s="39">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D33" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.57291666666666663</v>
       </c>
       <c r="E33" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="120">
+        <v>ILLMITZ</v>
+      </c>
+      <c r="G33" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>0</v>
-      </c>
-      <c r="H33">
+        <v>Auswärts</v>
+      </c>
+      <c r="H33" t="str">
         <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>0</v>
+        <v>Illmitz</v>
       </c>
       <c r="I33" t="str">
         <f>'Nach Mannschaften sortiert'!C33</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J33" s="108" t="s">
         <v>96</v>
@@ -4812,31 +5261,31 @@
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="105">
         <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>0</v>
+        <v>46333</v>
       </c>
       <c r="C34" s="39">
         <f>'Nach Mannschaften sortiert'!E34</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D34" s="39">
-        <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.57291666666666663</v>
       </c>
       <c r="E34" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="120">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G34" s="120" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>0</v>
-      </c>
-      <c r="H34">
+        <v>Heim</v>
+      </c>
+      <c r="H34" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I34" t="str">
         <f>'Nach Mannschaften sortiert'!C34</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J34" s="108" t="s">
         <v>96</v>
@@ -4855,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E35" s="39" t="str">
@@ -4891,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E36" s="39" t="str">
@@ -4927,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E37" s="39" t="str">
@@ -4963,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E38" s="39" t="str">
@@ -4999,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E39" s="39" t="str">
@@ -5035,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E40" s="39" t="str">
@@ -5071,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E41" s="39" t="str">
@@ -5107,8 +5556,8 @@
         <v>0</v>
       </c>
       <c r="D42" s="39">
-        <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E42" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
@@ -5124,7 +5573,7 @@
       </c>
       <c r="I42" t="str">
         <f>'Nach Mannschaften sortiert'!C42</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J42" s="108" t="s">
         <v>96</v>
@@ -5143,8 +5592,8 @@
         <v>0</v>
       </c>
       <c r="D43" s="39">
-        <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E43" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F43)</f>
@@ -5160,7 +5609,7 @@
       </c>
       <c r="I43" t="str">
         <f>'Nach Mannschaften sortiert'!C43</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J43" s="108" t="s">
         <v>96</v>
@@ -5179,8 +5628,8 @@
         <v>0</v>
       </c>
       <c r="D44" s="39">
-        <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E44" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F44)</f>
@@ -5196,7 +5645,7 @@
       </c>
       <c r="I44" t="str">
         <f>'Nach Mannschaften sortiert'!C44</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J44" s="108" t="s">
         <v>96</v>
@@ -5215,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="E45" s="39" t="str">
@@ -5251,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="E46" s="39" t="str">
@@ -5287,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="E47" s="39" t="str">
@@ -5323,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="E48" s="39" t="str">
@@ -5359,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="E49" s="39" t="str">
@@ -5395,8 +5844,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="39">
-        <f t="shared" si="0"/>
-        <v>6.5972222222222224E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
       </c>
       <c r="E50" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
@@ -5412,7 +5861,7 @@
       </c>
       <c r="I50" t="str">
         <f>'Nach Mannschaften sortiert'!C50</f>
-        <v>U13</v>
+        <v>U14</v>
       </c>
       <c r="J50" s="108" t="s">
         <v>96</v>
@@ -5431,8 +5880,8 @@
         <v>0</v>
       </c>
       <c r="D51" s="39">
-        <f t="shared" si="0"/>
-        <v>6.5972222222222224E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
       </c>
       <c r="E51" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
@@ -5448,7 +5897,7 @@
       </c>
       <c r="I51" t="str">
         <f>'Nach Mannschaften sortiert'!C51</f>
-        <v>U13</v>
+        <v>U14</v>
       </c>
       <c r="J51" s="108" t="s">
         <v>96</v>
@@ -5467,8 +5916,8 @@
         <v>0</v>
       </c>
       <c r="D52" s="39">
-        <f t="shared" si="0"/>
-        <v>6.5972222222222224E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
       </c>
       <c r="E52" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F52)</f>
@@ -5484,7 +5933,7 @@
       </c>
       <c r="I52" t="str">
         <f>'Nach Mannschaften sortiert'!C52</f>
-        <v>U13</v>
+        <v>U14</v>
       </c>
       <c r="J52" s="108" t="s">
         <v>96</v>
@@ -5503,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5972222222222224E-2</v>
       </c>
       <c r="E53" s="39" t="str">
@@ -5539,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="D54" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5972222222222224E-2</v>
       </c>
       <c r="E54" s="39" t="str">
@@ -5575,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="D55" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5972222222222224E-2</v>
       </c>
       <c r="E55" s="39" t="str">
@@ -5611,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5972222222222224E-2</v>
       </c>
       <c r="E56" s="39" t="str">
@@ -5647,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5972222222222224E-2</v>
       </c>
       <c r="E57" s="39" t="str">
@@ -5683,8 +6132,8 @@
         <v>0</v>
       </c>
       <c r="D58" s="39">
-        <f t="shared" si="0"/>
-        <v>0.125</v>
+        <f t="shared" si="1"/>
+        <v>6.5972222222222224E-2</v>
       </c>
       <c r="E58" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F58)</f>
@@ -5700,7 +6149,7 @@
       </c>
       <c r="I58" t="str">
         <f>'Nach Mannschaften sortiert'!C58</f>
-        <v>U12_1</v>
+        <v>U13</v>
       </c>
       <c r="J58" s="108" t="s">
         <v>96</v>
@@ -5719,8 +6168,8 @@
         <v>0</v>
       </c>
       <c r="D59" s="39">
-        <f t="shared" si="0"/>
-        <v>0.125</v>
+        <f t="shared" si="1"/>
+        <v>6.5972222222222224E-2</v>
       </c>
       <c r="E59" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F59)</f>
@@ -5736,7 +6185,7 @@
       </c>
       <c r="I59" t="str">
         <f>'Nach Mannschaften sortiert'!C59</f>
-        <v>U12_1</v>
+        <v>U13</v>
       </c>
       <c r="J59" s="108" t="s">
         <v>96</v>
@@ -5755,8 +6204,8 @@
         <v>0</v>
       </c>
       <c r="D60" s="39">
-        <f t="shared" si="0"/>
-        <v>0.125</v>
+        <f t="shared" si="1"/>
+        <v>6.5972222222222224E-2</v>
       </c>
       <c r="E60" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
@@ -5772,7 +6221,7 @@
       </c>
       <c r="I60" t="str">
         <f>'Nach Mannschaften sortiert'!C60</f>
-        <v>U12_1</v>
+        <v>U13</v>
       </c>
       <c r="J60" s="108" t="s">
         <v>96</v>
@@ -5791,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E61" s="39" t="str">
@@ -5827,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E62" s="39" t="str">
@@ -5863,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E63" s="39" t="str">
@@ -5899,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E64" s="39" t="str">
@@ -5935,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E65" s="39" t="str">
@@ -5971,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E66" s="39" t="str">
@@ -5988,7 +6437,7 @@
       </c>
       <c r="I66" t="str">
         <f>'Nach Mannschaften sortiert'!C66</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J66" s="108" t="s">
         <v>96</v>
@@ -6007,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="D67" s="39">
-        <f t="shared" ref="D67:D107" si="1">IF(I67 = "KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67 = "U16",C67+"1:45",IF(I67 = "U15",C67+"1:30",IF(I67 = "U14",C67+"1:30",IF(I67 = "U13",C67+"1:35",IF(I67 = "U12",C67+"1:10",IF(I67 = "U11",C67+"1:10",IF(I67 = "U10",C67+"1:03",C67+"3:00")))))))))</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E67" s="39" t="str">
@@ -6024,7 +6473,7 @@
       </c>
       <c r="I67" t="str">
         <f>'Nach Mannschaften sortiert'!C67</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J67" s="108" t="s">
         <v>96</v>
@@ -6060,7 +6509,7 @@
       </c>
       <c r="I68" t="str">
         <f>'Nach Mannschaften sortiert'!C68</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J68" s="108" t="s">
         <v>96</v>
@@ -6115,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D70:D110" si="2">IF(I70 = "KM",C70+"1:45",IF(I70="U23",C70+"1:45",IF(I70 = "U16",C70+"1:45",IF(I70 = "U15",C70+"1:30",IF(I70 = "U14",C70+"1:30",IF(I70 = "U13",C70+"1:35",IF(I70 = "U12",C70+"1:10",IF(I70 = "U11",C70+"1:10",IF(I70 = "U10",C70+"1:03",C70+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E70" s="39" t="str">
@@ -6151,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E71" s="39" t="str">
@@ -6187,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E72" s="39" t="str">
@@ -6223,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E73" s="39" t="str">
@@ -6259,8 +6708,8 @@
         <v>0</v>
       </c>
       <c r="D74" s="39">
-        <f t="shared" si="1"/>
-        <v>4.8611111111111112E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.125</v>
       </c>
       <c r="E74" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F74)</f>
@@ -6276,7 +6725,7 @@
       </c>
       <c r="I74" t="str">
         <f>'Nach Mannschaften sortiert'!C74</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J74" s="108" t="s">
         <v>96</v>
@@ -6295,8 +6744,8 @@
         <v>0</v>
       </c>
       <c r="D75" s="39">
-        <f t="shared" si="1"/>
-        <v>4.8611111111111112E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.125</v>
       </c>
       <c r="E75" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F75)</f>
@@ -6312,7 +6761,7 @@
       </c>
       <c r="I75" t="str">
         <f>'Nach Mannschaften sortiert'!C75</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J75" s="108" t="s">
         <v>96</v>
@@ -6331,8 +6780,8 @@
         <v>0</v>
       </c>
       <c r="D76" s="39">
-        <f t="shared" si="1"/>
-        <v>4.8611111111111112E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.125</v>
       </c>
       <c r="E76" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F76)</f>
@@ -6348,7 +6797,7 @@
       </c>
       <c r="I76" t="str">
         <f>'Nach Mannschaften sortiert'!C76</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J76" s="108" t="s">
         <v>96</v>
@@ -6367,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E77" s="39" t="str">
@@ -6403,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E78" s="39" t="str">
@@ -6439,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E79" s="39" t="str">
@@ -6475,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="D80" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E80" s="39" t="str">
@@ -6511,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="D81" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E81" s="39" t="str">
@@ -6547,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E82" s="39" t="str">
@@ -6583,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E83" s="39" t="str">
@@ -6619,8 +7068,8 @@
         <v>0</v>
       </c>
       <c r="D84" s="39">
-        <f t="shared" si="1"/>
-        <v>4.3750000000000004E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E84" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F84)</f>
@@ -6636,7 +7085,7 @@
       </c>
       <c r="I84" t="str">
         <f>'Nach Mannschaften sortiert'!C84</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J84" s="108" t="s">
         <v>96</v>
@@ -6655,8 +7104,8 @@
         <v>0</v>
       </c>
       <c r="D85" s="39">
-        <f t="shared" si="1"/>
-        <v>4.3750000000000004E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E85" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F85)</f>
@@ -6672,7 +7121,7 @@
       </c>
       <c r="I85" t="str">
         <f>'Nach Mannschaften sortiert'!C85</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J85" s="108" t="s">
         <v>96</v>
@@ -6691,8 +7140,8 @@
         <v>0</v>
       </c>
       <c r="D86" s="39">
-        <f t="shared" si="1"/>
-        <v>4.3750000000000004E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E86" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F86)</f>
@@ -6708,7 +7157,7 @@
       </c>
       <c r="I86" t="str">
         <f>'Nach Mannschaften sortiert'!C86</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J86" s="108" t="s">
         <v>96</v>
@@ -6727,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E87" s="39" t="str">
@@ -6763,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="D88" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E88" s="39" t="str">
@@ -6799,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E89" s="39" t="str">
@@ -6835,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="D90" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E90" s="39" t="str">
@@ -6871,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="D91" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E91" s="39" t="str">
@@ -6907,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E92" s="39" t="str">
@@ -6943,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E93" s="39" t="str">
@@ -6979,8 +7428,8 @@
         <v>0</v>
       </c>
       <c r="D94" s="39">
-        <f t="shared" si="1"/>
-        <v>0.125</v>
+        <f t="shared" si="2"/>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E94" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F94)</f>
@@ -6996,7 +7445,7 @@
       </c>
       <c r="I94" t="str">
         <f>'Nach Mannschaften sortiert'!C94</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J94" s="108" t="s">
         <v>96</v>
@@ -7015,8 +7464,8 @@
         <v>0</v>
       </c>
       <c r="D95" s="39">
-        <f t="shared" si="1"/>
-        <v>0.125</v>
+        <f t="shared" si="2"/>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E95" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F95)</f>
@@ -7032,7 +7481,7 @@
       </c>
       <c r="I95" t="str">
         <f>'Nach Mannschaften sortiert'!C95</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J95" s="108" t="s">
         <v>96</v>
@@ -7051,8 +7500,8 @@
         <v>0</v>
       </c>
       <c r="D96" s="39">
-        <f t="shared" si="1"/>
-        <v>0.125</v>
+        <f t="shared" si="2"/>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E96" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F96)</f>
@@ -7068,7 +7517,7 @@
       </c>
       <c r="I96" t="str">
         <f>'Nach Mannschaften sortiert'!C96</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J96" s="108" t="s">
         <v>96</v>
@@ -7087,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="D97" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E97" s="39" t="str">
@@ -7123,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="D98" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E98" s="39" t="str">
@@ -7159,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="D99" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E99" s="39" t="str">
@@ -7195,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E100" s="39" t="str">
@@ -7231,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E101" s="39" t="str">
@@ -7267,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="D102" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E102" s="39" t="str">
@@ -7303,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E103" s="39" t="str">
@@ -7339,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="D104" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E104" s="39" t="str">
@@ -7356,7 +7805,7 @@
       </c>
       <c r="I104" t="str">
         <f>'Nach Mannschaften sortiert'!C104</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J104" s="108" t="s">
         <v>96</v>
@@ -7375,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E105" s="39" t="str">
@@ -7392,7 +7841,7 @@
       </c>
       <c r="I105" t="str">
         <f>'Nach Mannschaften sortiert'!C105</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J105" s="108" t="s">
         <v>96</v>
@@ -7411,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="D106" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E106" s="39" t="str">
@@ -7428,7 +7877,7 @@
       </c>
       <c r="I106" t="str">
         <f>'Nach Mannschaften sortiert'!C106</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J106" s="108" t="s">
         <v>96</v>
@@ -7447,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E107" s="39" t="str">
@@ -7483,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="39">
-        <f>IF(I108 = "KM",C108+"1:45",IF(I108="U23",C108+"1:45",IF(I108 = "U16",C108+"1:45",IF(I108 = "U15",C108+"1:30",IF(I108 = "U14",C108+"1:30",IF(I108 = "U13",C108+"1:35",IF(I108 = "U12",C108+"1:10",IF(I108 = "U11",C108+"1:10",IF(I108 = "U10",C108+"1:03",C108+"3:00")))))))))</f>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E108" s="39" t="str">
@@ -7519,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="39">
-        <f t="shared" ref="D109:D116" si="2">IF(I109 = "KM",C109+"1:45",IF(I109="U23",C109+"1:45",IF(I109 = "U16",C109+"1:45",IF(I109 = "U15",C109+"1:30",IF(I109 = "U14",C109+"1:30",IF(I109 = "U13",C109+"1:35",IF(I109 = "U12",C109+"1:10",IF(I109 = "U11",C109+"1:10",IF(I109 = "U10",C109+"1:03",C109+"3:00")))))))))</f>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E109" s="39" t="str">
@@ -7536,7 +7985,7 @@
       </c>
       <c r="I109" t="str">
         <f>'Nach Mannschaften sortiert'!C109</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J109" s="108" t="s">
         <v>96</v>
@@ -7572,7 +8021,7 @@
       </c>
       <c r="I110" t="str">
         <f>'Nach Mannschaften sortiert'!C110</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J110" s="108" t="s">
         <v>96</v>
@@ -7591,7 +8040,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="39">
-        <f t="shared" si="2"/>
+        <f>IF(I111 = "KM",C111+"1:45",IF(I111="U23",C111+"1:45",IF(I111 = "U16",C111+"1:45",IF(I111 = "U15",C111+"1:30",IF(I111 = "U14",C111+"1:30",IF(I111 = "U13",C111+"1:35",IF(I111 = "U12",C111+"1:10",IF(I111 = "U11",C111+"1:10",IF(I111 = "U10",C111+"1:03",C111+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E111" s="39" t="str">
@@ -7608,7 +8057,7 @@
       </c>
       <c r="I111" t="str">
         <f>'Nach Mannschaften sortiert'!C111</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J111" s="108" t="s">
         <v>96</v>
@@ -7627,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D112:D119" si="3">IF(I112 = "KM",C112+"1:45",IF(I112="U23",C112+"1:45",IF(I112 = "U16",C112+"1:45",IF(I112 = "U15",C112+"1:30",IF(I112 = "U14",C112+"1:30",IF(I112 = "U13",C112+"1:35",IF(I112 = "U12",C112+"1:10",IF(I112 = "U11",C112+"1:10",IF(I112 = "U10",C112+"1:03",C112+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E112" s="39" t="str">
@@ -7663,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E113" s="39" t="str">
@@ -7692,123 +8141,122 @@
     <row r="114" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B114" s="105">
         <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46321</v>
+        <v>0</v>
       </c>
       <c r="C114" s="39">
         <f>'Nach Mannschaften sortiert'!E114</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D114" s="39">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.125</v>
       </c>
       <c r="E114" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F114)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G114" s="120" t="str">
+        <v/>
+      </c>
+      <c r="G114" s="120">
         <f>'Nach Mannschaften sortiert'!H114</f>
-        <v>Heim</v>
-      </c>
-      <c r="H114" t="str">
+        <v>0</v>
+      </c>
+      <c r="H114">
         <f>'Nach Mannschaften sortiert'!G114</f>
-        <v>CAMP</v>
+        <v>0</v>
       </c>
       <c r="I114" t="str">
         <f>'Nach Mannschaften sortiert'!C114</f>
-        <v>TECO 7 CAMP</v>
+        <v>U7</v>
       </c>
       <c r="J114" s="108" t="s">
         <v>96</v>
       </c>
       <c r="K114" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="105">
         <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46322</v>
+        <v>0</v>
       </c>
       <c r="C115" s="39">
         <f>'Nach Mannschaften sortiert'!E115</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D115" s="39">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.125</v>
       </c>
       <c r="E115" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F115)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G115" s="120" t="str">
+        <v/>
+      </c>
+      <c r="G115" s="120">
         <f>'Nach Mannschaften sortiert'!H115</f>
-        <v>Heim</v>
-      </c>
-      <c r="H115" t="str">
+        <v>0</v>
+      </c>
+      <c r="H115">
         <f>'Nach Mannschaften sortiert'!G115</f>
-        <v>CAMP</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>'Nach Mannschaften sortiert'!C115</f>
-        <v>TECO 7 CAMP</v>
+        <v>U7</v>
       </c>
       <c r="J115" s="108" t="s">
         <v>96</v>
       </c>
       <c r="K115" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" s="105">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46323</v>
+        <v>0</v>
       </c>
       <c r="C116" s="39">
         <f>'Nach Mannschaften sortiert'!E116</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D116" s="39">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.125</v>
       </c>
       <c r="E116" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F116)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G116" s="120" t="str">
+        <v/>
+      </c>
+      <c r="G116" s="120">
         <f>'Nach Mannschaften sortiert'!H116</f>
-        <v>Heim</v>
-      </c>
-      <c r="H116" t="str">
+        <v>0</v>
+      </c>
+      <c r="H116">
         <f>'Nach Mannschaften sortiert'!G116</f>
-        <v>CAMP</v>
+        <v>0</v>
       </c>
       <c r="I116" t="str">
         <f>'Nach Mannschaften sortiert'!C116</f>
-        <v>TECO 7 CAMP</v>
+        <v>U7</v>
       </c>
       <c r="J116" s="108" t="s">
         <v>96</v>
       </c>
       <c r="K116" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="105">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46230</v>
+        <v>46321</v>
       </c>
       <c r="C117" s="39">
         <f>'Nach Mannschaften sortiert'!E117</f>
         <v>0.375</v>
       </c>
       <c r="D117" s="39">
-        <f>IF(I117 = "KM",C117+"1:45",IF(I117="U23",C117+"1:45",IF(I117 = "U16",C117+"1:45",IF(I117 = "U15",C117+"1:30",IF(I117 = "U14",C117+"1:30",IF(I117 = "U13",C117+"1:35",IF(I117 = "U12",C117+"1:10",IF(I117 = "U11",C117+"1:10",IF(I117 = "U10",C117+"1:03",C117+"3:00")))))))))</f>
-        <v>0.5</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="E117" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F117)</f>
@@ -7824,7 +8272,7 @@
       </c>
       <c r="I117" t="str">
         <f>'Nach Mannschaften sortiert'!C117</f>
-        <v>REAL MADRID CAMP</v>
+        <v>TECO 7 CAMP</v>
       </c>
       <c r="J117" s="108" t="s">
         <v>96</v>
@@ -7836,15 +8284,14 @@
     <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="105">
         <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46231</v>
+        <v>46322</v>
       </c>
       <c r="C118" s="39">
         <f>'Nach Mannschaften sortiert'!E118</f>
         <v>0.375</v>
       </c>
       <c r="D118" s="39">
-        <f t="shared" ref="D118:D121" si="3">IF(I118 = "KM",C118+"1:45",IF(I118="U23",C118+"1:45",IF(I118 = "U16",C118+"1:45",IF(I118 = "U15",C118+"1:30",IF(I118 = "U14",C118+"1:30",IF(I118 = "U13",C118+"1:35",IF(I118 = "U12",C118+"1:10",IF(I118 = "U11",C118+"1:10",IF(I118 = "U10",C118+"1:03",C118+"3:00")))))))))</f>
-        <v>0.5</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="E118" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F118)</f>
@@ -7860,7 +8307,7 @@
       </c>
       <c r="I118" t="str">
         <f>'Nach Mannschaften sortiert'!C118</f>
-        <v>REAL MADRID CAMP</v>
+        <v>TECO 7 CAMP</v>
       </c>
       <c r="J118" s="108" t="s">
         <v>96</v>
@@ -7872,15 +8319,14 @@
     <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" s="105">
         <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46232</v>
+        <v>46323</v>
       </c>
       <c r="C119" s="39">
         <f>'Nach Mannschaften sortiert'!E119</f>
         <v>0.375</v>
       </c>
       <c r="D119" s="39">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="E119" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F119)</f>
@@ -7896,7 +8342,7 @@
       </c>
       <c r="I119" t="str">
         <f>'Nach Mannschaften sortiert'!C119</f>
-        <v>REAL MADRID CAMP</v>
+        <v>TECO 7 CAMP</v>
       </c>
       <c r="J119" s="108" t="s">
         <v>96</v>
@@ -7908,15 +8354,14 @@
     <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" s="105">
         <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="C120" s="39">
         <f>'Nach Mannschaften sortiert'!E120</f>
         <v>0.375</v>
       </c>
       <c r="D120" s="39">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E120" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F120)</f>
@@ -7944,15 +8389,14 @@
     <row r="121" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B121" s="105">
         <f>'Nach Mannschaften sortiert'!D121</f>
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="C121" s="39">
         <f>'Nach Mannschaften sortiert'!E121</f>
         <v>0.375</v>
       </c>
       <c r="D121" s="39">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E121" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F121)</f>
@@ -7980,15 +8424,14 @@
     <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" s="105">
         <f>'Nach Mannschaften sortiert'!D122</f>
-        <v>46256</v>
+        <v>46232</v>
       </c>
       <c r="C122" s="39">
         <f>'Nach Mannschaften sortiert'!E122</f>
         <v>0.375</v>
       </c>
       <c r="D122" s="39">
-        <f t="shared" ref="D122" si="4">IF(I122 = "KM",C122+"1:45",IF(I122="U23",C122+"1:45",IF(I122 = "U16",C122+"1:45",IF(I122 = "U15",C122+"1:30",IF(I122 = "U14",C122+"1:30",IF(I122 = "U13",C122+"1:35",IF(I122 = "U12",C122+"1:10",IF(I122 = "U11",C122+"1:10",IF(I122 = "U10",C122+"1:03",C122+"3:00")))))))))</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E122" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F122)</f>
@@ -8000,16 +8443,227 @@
       </c>
       <c r="H122" t="str">
         <f>'Nach Mannschaften sortiert'!G122</f>
-        <v>viele Gegner</v>
+        <v>CAMP</v>
       </c>
       <c r="I122" t="str">
         <f>'Nach Mannschaften sortiert'!C122</f>
-        <v>GGG</v>
+        <v>REAL MADRID CAMP</v>
       </c>
       <c r="J122" s="108" t="s">
         <v>96</v>
       </c>
       <c r="K122" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B123" s="105">
+        <f>'Nach Mannschaften sortiert'!D123</f>
+        <v>46233</v>
+      </c>
+      <c r="C123" s="39">
+        <f>'Nach Mannschaften sortiert'!E123</f>
+        <v>0.375</v>
+      </c>
+      <c r="D123" s="39">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E123" s="39" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F123)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G123" s="120" t="str">
+        <f>'Nach Mannschaften sortiert'!H123</f>
+        <v>Heim</v>
+      </c>
+      <c r="H123" t="str">
+        <f>'Nach Mannschaften sortiert'!G123</f>
+        <v>CAMP</v>
+      </c>
+      <c r="I123" t="str">
+        <f>'Nach Mannschaften sortiert'!C123</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="J123" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="K123" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B124" s="105">
+        <f>'Nach Mannschaften sortiert'!D124</f>
+        <v>46234</v>
+      </c>
+      <c r="C124" s="39">
+        <f>'Nach Mannschaften sortiert'!E124</f>
+        <v>0.375</v>
+      </c>
+      <c r="D124" s="39">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E124" s="39" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F124)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G124" s="120" t="str">
+        <f>'Nach Mannschaften sortiert'!H124</f>
+        <v>Heim</v>
+      </c>
+      <c r="H124" t="str">
+        <f>'Nach Mannschaften sortiert'!G124</f>
+        <v>CAMP</v>
+      </c>
+      <c r="I124" t="str">
+        <f>'Nach Mannschaften sortiert'!C124</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="J124" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="K124" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B125" s="105">
+        <f>'Nach Mannschaften sortiert'!D125</f>
+        <v>46237</v>
+      </c>
+      <c r="C125" s="39">
+        <f>'Nach Mannschaften sortiert'!E128</f>
+        <v>0.375</v>
+      </c>
+      <c r="D125" s="39">
+        <v>0.625</v>
+      </c>
+      <c r="E125" s="39" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F125)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G125" s="120" t="str">
+        <f>'Nach Mannschaften sortiert'!H125</f>
+        <v>Heim</v>
+      </c>
+      <c r="H125" t="str">
+        <f>'Nach Mannschaften sortiert'!G125</f>
+        <v>CAMP</v>
+      </c>
+      <c r="I125" t="str">
+        <f>'Nach Mannschaften sortiert'!C125</f>
+        <v>MÄDCHENCAMP</v>
+      </c>
+      <c r="J125" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="K125" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B126" s="105">
+        <f>'Nach Mannschaften sortiert'!D126</f>
+        <v>46238</v>
+      </c>
+      <c r="C126" s="39">
+        <f>'Nach Mannschaften sortiert'!E129</f>
+        <v>0</v>
+      </c>
+      <c r="D126" s="39">
+        <v>0.625</v>
+      </c>
+      <c r="E126" s="39" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F126)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G126" s="120" t="str">
+        <f>'Nach Mannschaften sortiert'!H126</f>
+        <v>Heim</v>
+      </c>
+      <c r="H126" t="str">
+        <f>'Nach Mannschaften sortiert'!G126</f>
+        <v>CAMP</v>
+      </c>
+      <c r="I126" t="str">
+        <f>'Nach Mannschaften sortiert'!C126</f>
+        <v>MÄDCHENCAMP</v>
+      </c>
+      <c r="J126" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="K126" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B127" s="105">
+        <f>'Nach Mannschaften sortiert'!D127</f>
+        <v>46239</v>
+      </c>
+      <c r="C127" s="39">
+        <f>'Nach Mannschaften sortiert'!E130</f>
+        <v>0</v>
+      </c>
+      <c r="D127" s="39">
+        <v>0.625</v>
+      </c>
+      <c r="E127" s="39" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F127)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G127" s="120" t="str">
+        <f>'Nach Mannschaften sortiert'!H127</f>
+        <v>Heim</v>
+      </c>
+      <c r="H127" t="str">
+        <f>'Nach Mannschaften sortiert'!G127</f>
+        <v>CAMP</v>
+      </c>
+      <c r="I127" t="str">
+        <f>'Nach Mannschaften sortiert'!C127</f>
+        <v>MÄDCHENCAMP</v>
+      </c>
+      <c r="J127" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="K127" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B128" s="105">
+        <f>'Nach Mannschaften sortiert'!D128</f>
+        <v>46256</v>
+      </c>
+      <c r="C128" s="39">
+        <f>'Nach Mannschaften sortiert'!E128</f>
+        <v>0.375</v>
+      </c>
+      <c r="D128" s="39">
+        <f t="shared" ref="D128" si="4">IF(I128 = "KM",C128+"1:45",IF(I128="U23",C128+"1:45",IF(I128 = "U16",C128+"1:45",IF(I128 = "U15",C128+"1:30",IF(I128 = "U14",C128+"1:30",IF(I128 = "U13",C128+"1:35",IF(I128 = "U12",C128+"1:10",IF(I128 = "U11",C128+"1:10",IF(I128 = "U10",C128+"1:03",C128+"3:00")))))))))</f>
+        <v>0.5</v>
+      </c>
+      <c r="E128" s="39" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F128)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G128" s="120" t="str">
+        <f>'Nach Mannschaften sortiert'!H128</f>
+        <v>Heim</v>
+      </c>
+      <c r="H128" t="str">
+        <f>'Nach Mannschaften sortiert'!G128</f>
+        <v>viele Gegner</v>
+      </c>
+      <c r="I128" t="str">
+        <f>'Nach Mannschaften sortiert'!C128</f>
+        <v>GGG</v>
+      </c>
+      <c r="J128" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="K128" t="s">
         <v>69</v>
       </c>
     </row>
@@ -8660,783 +9314,783 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <f>'Nach Mannschaften sortiert'!A6</f>
+        <f>'Nach Mannschaften sortiert'!A9</f>
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <f>'Nach Mannschaften sortiert'!B6</f>
+        <f>'Nach Mannschaften sortiert'!B9</f>
         <v>1</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C6</f>
+        <f>'Nach Mannschaften sortiert'!C9</f>
         <v>KM</v>
       </c>
       <c r="D2" s="16">
-        <f>'Nach Mannschaften sortiert'!D6</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D9</f>
+        <v>46249</v>
       </c>
       <c r="E2" s="38">
-        <f>'Nach Mannschaften sortiert'!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <f>'Nach Mannschaften sortiert'!F6</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <f>'Nach Mannschaften sortiert'!G6</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <f>'Nach Mannschaften sortiert'!H6</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E9</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F9</f>
+        <v>Kittsee</v>
+      </c>
+      <c r="G2" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G9</f>
+        <v>Kittsee</v>
+      </c>
+      <c r="H2" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H9</f>
+        <v>Auswärts</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <f>'Nach Mannschaften sortiert'!A7</f>
+        <f>'Nach Mannschaften sortiert'!A10</f>
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <f>'Nach Mannschaften sortiert'!B7</f>
+        <f>'Nach Mannschaften sortiert'!B10</f>
         <v>2</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C7</f>
+        <f>'Nach Mannschaften sortiert'!C10</f>
         <v>KM</v>
       </c>
       <c r="D3" s="16">
-        <f>'Nach Mannschaften sortiert'!D7</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D10</f>
+        <v>46256</v>
       </c>
       <c r="E3" s="38">
-        <f>'Nach Mannschaften sortiert'!E7</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <f>'Nach Mannschaften sortiert'!F7</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <f>'Nach Mannschaften sortiert'!G7</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <f>'Nach Mannschaften sortiert'!H7</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E10</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F10</f>
+        <v>Deutsch Jahrndorf</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G10</f>
+        <v>Deutsch Jahrndorf</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H10</f>
+        <v>Auswärts</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <f>'Nach Mannschaften sortiert'!A8</f>
+        <f>'Nach Mannschaften sortiert'!A11</f>
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <f>'Nach Mannschaften sortiert'!B8</f>
+        <f>'Nach Mannschaften sortiert'!B11</f>
         <v>3</v>
       </c>
       <c r="C4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C8</f>
+        <f>'Nach Mannschaften sortiert'!C11</f>
         <v>KM</v>
       </c>
       <c r="D4" s="16">
-        <f>'Nach Mannschaften sortiert'!D8</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D11</f>
+        <v>46263</v>
       </c>
       <c r="E4" s="38">
-        <f>'Nach Mannschaften sortiert'!E8</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <f>'Nach Mannschaften sortiert'!F8</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <f>'Nach Mannschaften sortiert'!G8</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <f>'Nach Mannschaften sortiert'!H8</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E11</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F11</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G11</f>
+        <v>Tadten</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H11</f>
+        <v>Heim</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <f>'Nach Mannschaften sortiert'!A50</f>
+        <f>'Nach Mannschaften sortiert'!A53</f>
         <v>34</v>
       </c>
       <c r="B5" s="2">
-        <f>'Nach Mannschaften sortiert'!B50</f>
+        <f>'Nach Mannschaften sortiert'!B53</f>
         <v>1</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C50</f>
+        <f>'Nach Mannschaften sortiert'!C53</f>
         <v>U13</v>
       </c>
       <c r="D5" s="16">
-        <f>'Nach Mannschaften sortiert'!D50</f>
+        <f>'Nach Mannschaften sortiert'!D53</f>
         <v>0</v>
       </c>
       <c r="E5" s="38">
-        <f>'Nach Mannschaften sortiert'!E50</f>
+        <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <f>'Nach Mannschaften sortiert'!F50</f>
+        <f>'Nach Mannschaften sortiert'!F53</f>
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <f>'Nach Mannschaften sortiert'!G50</f>
+        <f>'Nach Mannschaften sortiert'!G53</f>
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f>'Nach Mannschaften sortiert'!H50</f>
+        <f>'Nach Mannschaften sortiert'!H53</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <f>'Nach Mannschaften sortiert'!A10</f>
+        <f>'Nach Mannschaften sortiert'!A13</f>
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <f>'Nach Mannschaften sortiert'!B10</f>
+        <f>'Nach Mannschaften sortiert'!B13</f>
         <v>5</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C10</f>
+        <f>'Nach Mannschaften sortiert'!C13</f>
         <v>KM</v>
       </c>
       <c r="D6" s="16">
-        <f>'Nach Mannschaften sortiert'!D10</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D13</f>
+        <v>46277</v>
       </c>
       <c r="E6" s="38">
-        <f>'Nach Mannschaften sortiert'!E10</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <f>'Nach Mannschaften sortiert'!F10</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <f>'Nach Mannschaften sortiert'!G10</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <f>'Nach Mannschaften sortiert'!H10</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E13</f>
+        <v>0.6875</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F13</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G13</f>
+        <v>Winden</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H13</f>
+        <v>Heim</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <f>'Nach Mannschaften sortiert'!A58</f>
+        <f>'Nach Mannschaften sortiert'!A61</f>
         <v>44</v>
       </c>
       <c r="B7" s="2">
-        <f>'Nach Mannschaften sortiert'!B58</f>
+        <f>'Nach Mannschaften sortiert'!B61</f>
         <v>1</v>
       </c>
       <c r="C7" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C58</f>
+        <f>'Nach Mannschaften sortiert'!C61</f>
         <v>U12_1</v>
       </c>
       <c r="D7" s="16">
-        <f>'Nach Mannschaften sortiert'!D58</f>
+        <f>'Nach Mannschaften sortiert'!D61</f>
         <v>0</v>
       </c>
       <c r="E7" s="38">
-        <f>'Nach Mannschaften sortiert'!E58</f>
+        <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <f>'Nach Mannschaften sortiert'!F58</f>
+        <f>'Nach Mannschaften sortiert'!F61</f>
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <f>'Nach Mannschaften sortiert'!G58</f>
+        <f>'Nach Mannschaften sortiert'!G61</f>
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <f>'Nach Mannschaften sortiert'!H58</f>
+        <f>'Nach Mannschaften sortiert'!H61</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
+        <f>'Nach Mannschaften sortiert'!A15</f>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <f>'Nach Mannschaften sortiert'!B15</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C15</f>
+        <v>KM</v>
+      </c>
+      <c r="D8" s="16">
+        <f>'Nach Mannschaften sortiert'!D15</f>
+        <v>46291</v>
+      </c>
+      <c r="E8" s="38">
+        <f>'Nach Mannschaften sortiert'!E15</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F15</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G15</f>
+        <v>Wallern</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H15</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="66">
+        <f>'Nach Mannschaften sortiert'!A107</f>
+        <v>79</v>
+      </c>
+      <c r="B9" s="66">
+        <f>'Nach Mannschaften sortiert'!B107</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="66" t="str">
+        <f>'Nach Mannschaften sortiert'!C107</f>
+        <v>U8</v>
+      </c>
+      <c r="D9" s="67">
+        <f>'Nach Mannschaften sortiert'!D107</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="68">
+        <f>'Nach Mannschaften sortiert'!E107</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="66">
+        <f>'Nach Mannschaften sortiert'!F107</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="66">
+        <f>'Nach Mannschaften sortiert'!G107</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="66">
+        <f>'Nach Mannschaften sortiert'!H107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <f>'Nach Mannschaften sortiert'!A17</f>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <f>'Nach Mannschaften sortiert'!B17</f>
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C17</f>
+        <v>KM</v>
+      </c>
+      <c r="D10" s="16">
+        <f>'Nach Mannschaften sortiert'!D17</f>
+        <v>46305</v>
+      </c>
+      <c r="E10" s="38">
+        <f>'Nach Mannschaften sortiert'!E17</f>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F17</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G17</f>
+        <v>Wimpassing</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H17</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="66">
+        <f>'Nach Mannschaften sortiert'!A115</f>
+        <v>80</v>
+      </c>
+      <c r="B11" s="66">
+        <f>'Nach Mannschaften sortiert'!B115</f>
+        <v>4</v>
+      </c>
+      <c r="C11" s="66" t="str">
+        <f>'Nach Mannschaften sortiert'!C115</f>
+        <v>U7</v>
+      </c>
+      <c r="D11" s="67">
+        <f>'Nach Mannschaften sortiert'!D115</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="68">
+        <f>'Nach Mannschaften sortiert'!E115</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="66">
+        <f>'Nach Mannschaften sortiert'!F115</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="66">
+        <f>'Nach Mannschaften sortiert'!G115</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="66">
+        <f>'Nach Mannschaften sortiert'!H115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <f>'Nach Mannschaften sortiert'!A19</f>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <f>'Nach Mannschaften sortiert'!B19</f>
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C19</f>
+        <v>KM</v>
+      </c>
+      <c r="D12" s="16">
+        <f>'Nach Mannschaften sortiert'!D19</f>
+        <v>46319</v>
+      </c>
+      <c r="E12" s="38">
+        <f>'Nach Mannschaften sortiert'!E19</f>
+        <v>0.625</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F19</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G19</f>
+        <v>Gols</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H19</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <f>'Nach Mannschaften sortiert'!A20</f>
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <f>'Nach Mannschaften sortiert'!B20</f>
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C20</f>
+        <v>KM</v>
+      </c>
+      <c r="D13" s="16">
+        <f>'Nach Mannschaften sortiert'!D20</f>
+        <v>46326</v>
+      </c>
+      <c r="E13" s="38">
+        <f>'Nach Mannschaften sortiert'!E20</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F20</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G20</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="H13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H20</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="66">
+        <f>'Nach Mannschaften sortiert'!A116</f>
+        <v>81</v>
+      </c>
+      <c r="B14" s="66">
+        <f>'Nach Mannschaften sortiert'!B116</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="66" t="str">
+        <f>'Nach Mannschaften sortiert'!C116</f>
+        <v>U7</v>
+      </c>
+      <c r="D14" s="67">
+        <f>'Nach Mannschaften sortiert'!D116</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="68">
+        <f>'Nach Mannschaften sortiert'!E116</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="66">
+        <f>'Nach Mannschaften sortiert'!F116</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="66">
+        <f>'Nach Mannschaften sortiert'!G116</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="66">
+        <f>'Nach Mannschaften sortiert'!H116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <f>'Nach Mannschaften sortiert'!A35</f>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <f>'Nach Mannschaften sortiert'!B35</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C35</f>
+        <v>U16</v>
+      </c>
+      <c r="D15" s="16">
+        <f>'Nach Mannschaften sortiert'!D35</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="38">
+        <f>'Nach Mannschaften sortiert'!E35</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <f>'Nach Mannschaften sortiert'!F35</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <f>'Nach Mannschaften sortiert'!G35</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <f>'Nach Mannschaften sortiert'!H35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="60">
+        <f>'Nach Mannschaften sortiert'!A36</f>
+        <v>15</v>
+      </c>
+      <c r="B16" s="60">
+        <f>'Nach Mannschaften sortiert'!B36</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!C36</f>
+        <v>U16</v>
+      </c>
+      <c r="D16" s="61">
+        <f>'Nach Mannschaften sortiert'!D36</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="62">
+        <f>'Nach Mannschaften sortiert'!E36</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="60">
+        <f>'Nach Mannschaften sortiert'!F36</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="60">
+        <f>'Nach Mannschaften sortiert'!G36</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="60">
+        <f>'Nach Mannschaften sortiert'!H36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <f>'Nach Mannschaften sortiert'!A37</f>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <f>'Nach Mannschaften sortiert'!B37</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C37</f>
+        <v>U16</v>
+      </c>
+      <c r="D17" s="16">
+        <f>'Nach Mannschaften sortiert'!D37</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="38">
+        <f>'Nach Mannschaften sortiert'!E37</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f>'Nach Mannschaften sortiert'!F37</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <f>'Nach Mannschaften sortiert'!G37</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <f>'Nach Mannschaften sortiert'!H37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <f>'Nach Mannschaften sortiert'!A12</f>
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2">
         <f>'Nach Mannschaften sortiert'!B12</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!C12</f>
         <v>KM</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D18" s="16">
         <f>'Nach Mannschaften sortiert'!D12</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="38">
+        <v>46270</v>
+      </c>
+      <c r="E18" s="38">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="F18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F12</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
+        <v>Mönchhof</v>
+      </c>
+      <c r="G18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!G12</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
+        <v>Mönchhof</v>
+      </c>
+      <c r="H18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="66">
-        <f>'Nach Mannschaften sortiert'!A104</f>
-        <v>79</v>
-      </c>
-      <c r="B9" s="66">
-        <f>'Nach Mannschaften sortiert'!B104</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="66" t="str">
-        <f>'Nach Mannschaften sortiert'!C104</f>
-        <v>U8</v>
-      </c>
-      <c r="D9" s="67">
-        <f>'Nach Mannschaften sortiert'!D104</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="68">
-        <f>'Nach Mannschaften sortiert'!E104</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="66">
-        <f>'Nach Mannschaften sortiert'!F104</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="66">
-        <f>'Nach Mannschaften sortiert'!G104</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="66">
-        <f>'Nach Mannschaften sortiert'!H104</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <f>'Nach Mannschaften sortiert'!A14</f>
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <f>'Nach Mannschaften sortiert'!B14</f>
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C14</f>
-        <v>KM</v>
-      </c>
-      <c r="D10" s="16">
-        <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="38">
-        <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <f>'Nach Mannschaften sortiert'!F14</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="66">
-        <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>80</v>
-      </c>
-      <c r="B11" s="66">
-        <f>'Nach Mannschaften sortiert'!B112</f>
-        <v>4</v>
-      </c>
-      <c r="C11" s="66" t="str">
-        <f>'Nach Mannschaften sortiert'!C112</f>
-        <v>U7</v>
-      </c>
-      <c r="D11" s="67">
-        <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="68">
-        <f>'Nach Mannschaften sortiert'!E112</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="66">
-        <f>'Nach Mannschaften sortiert'!F112</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="66">
-        <f>'Nach Mannschaften sortiert'!G112</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="66">
-        <f>'Nach Mannschaften sortiert'!H112</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <f>'Nach Mannschaften sortiert'!A16</f>
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <f>'Nach Mannschaften sortiert'!B16</f>
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C16</f>
-        <v>KM</v>
-      </c>
-      <c r="D12" s="16">
-        <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <f>'Nach Mannschaften sortiert'!F16</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <f>'Nach Mannschaften sortiert'!A17</f>
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
-        <f>'Nach Mannschaften sortiert'!B17</f>
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
-        <v>KM</v>
-      </c>
-      <c r="D13" s="16">
-        <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="38">
-        <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <f>'Nach Mannschaften sortiert'!F17</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
-        <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="66">
-        <f>'Nach Mannschaften sortiert'!A113</f>
-        <v>81</v>
-      </c>
-      <c r="B14" s="66">
-        <f>'Nach Mannschaften sortiert'!B113</f>
-        <v>5</v>
-      </c>
-      <c r="C14" s="66" t="str">
-        <f>'Nach Mannschaften sortiert'!C113</f>
-        <v>U7</v>
-      </c>
-      <c r="D14" s="67">
-        <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="68">
-        <f>'Nach Mannschaften sortiert'!E113</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="66">
-        <f>'Nach Mannschaften sortiert'!F113</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="66">
-        <f>'Nach Mannschaften sortiert'!G113</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="66">
-        <f>'Nach Mannschaften sortiert'!H113</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <f>'Nach Mannschaften sortiert'!A32</f>
-        <v>14</v>
-      </c>
-      <c r="B15" s="2">
-        <f>'Nach Mannschaften sortiert'!B32</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C32</f>
-        <v>U16</v>
-      </c>
-      <c r="D15" s="16">
-        <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="38">
-        <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f>'Nach Mannschaften sortiert'!F32</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60">
-        <f>'Nach Mannschaften sortiert'!A33</f>
-        <v>15</v>
-      </c>
-      <c r="B16" s="60">
-        <f>'Nach Mannschaften sortiert'!B33</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C33</f>
-        <v>U16</v>
-      </c>
-      <c r="D16" s="61">
-        <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="62">
-        <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="60">
-        <f>'Nach Mannschaften sortiert'!F33</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="60">
-        <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="60">
-        <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <f>'Nach Mannschaften sortiert'!A34</f>
-        <v>16</v>
-      </c>
-      <c r="B17" s="2">
-        <f>'Nach Mannschaften sortiert'!B34</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C34</f>
-        <v>U16</v>
-      </c>
-      <c r="D17" s="16">
-        <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="38">
-        <f>'Nach Mannschaften sortiert'!E34</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f>'Nach Mannschaften sortiert'!F34</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <f>'Nach Mannschaften sortiert'!A9</f>
-        <v>4</v>
-      </c>
-      <c r="B18" s="2">
-        <f>'Nach Mannschaften sortiert'!B9</f>
-        <v>4</v>
-      </c>
-      <c r="C18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C9</f>
-        <v>KM</v>
-      </c>
-      <c r="D18" s="16">
-        <f>'Nach Mannschaften sortiert'!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="38">
-        <f>'Nach Mannschaften sortiert'!E9</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f>'Nach Mannschaften sortiert'!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="2">
-        <f>'Nach Mannschaften sortiert'!G9</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <f>'Nach Mannschaften sortiert'!H9</f>
-        <v>0</v>
+        <v>Auswärts</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <f>'Nach Mannschaften sortiert'!A36</f>
+        <f>'Nach Mannschaften sortiert'!A39</f>
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <f>'Nach Mannschaften sortiert'!B36</f>
+        <f>'Nach Mannschaften sortiert'!B39</f>
         <v>5</v>
       </c>
       <c r="C19" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C36</f>
+        <f>'Nach Mannschaften sortiert'!C39</f>
         <v>U16</v>
       </c>
       <c r="D19" s="16">
-        <f>'Nach Mannschaften sortiert'!D36</f>
+        <f>'Nach Mannschaften sortiert'!D39</f>
         <v>0</v>
       </c>
       <c r="E19" s="38">
-        <f>'Nach Mannschaften sortiert'!E36</f>
+        <f>'Nach Mannschaften sortiert'!E39</f>
         <v>0</v>
       </c>
       <c r="F19" s="2">
-        <f>'Nach Mannschaften sortiert'!F36</f>
+        <f>'Nach Mannschaften sortiert'!F39</f>
         <v>0</v>
       </c>
       <c r="G19" s="2">
-        <f>'Nach Mannschaften sortiert'!G36</f>
+        <f>'Nach Mannschaften sortiert'!G39</f>
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <f>'Nach Mannschaften sortiert'!H36</f>
+        <f>'Nach Mannschaften sortiert'!H39</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="57">
-        <f>'Nach Mannschaften sortiert'!A37</f>
+        <f>'Nach Mannschaften sortiert'!A40</f>
         <v>19</v>
       </c>
       <c r="B20" s="57">
-        <f>'Nach Mannschaften sortiert'!B37</f>
+        <f>'Nach Mannschaften sortiert'!B40</f>
         <v>6</v>
       </c>
       <c r="C20" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C37</f>
+        <f>'Nach Mannschaften sortiert'!C40</f>
         <v>U16</v>
       </c>
       <c r="D20" s="58">
-        <f>'Nach Mannschaften sortiert'!D37</f>
+        <f>'Nach Mannschaften sortiert'!D40</f>
         <v>0</v>
       </c>
       <c r="E20" s="59">
-        <f>'Nach Mannschaften sortiert'!E37</f>
+        <f>'Nach Mannschaften sortiert'!E40</f>
         <v>0</v>
       </c>
       <c r="F20" s="57">
-        <f>'Nach Mannschaften sortiert'!F37</f>
+        <f>'Nach Mannschaften sortiert'!F40</f>
         <v>0</v>
       </c>
       <c r="G20" s="57">
-        <f>'Nach Mannschaften sortiert'!G37</f>
+        <f>'Nach Mannschaften sortiert'!G40</f>
         <v>0</v>
       </c>
       <c r="H20" s="57">
-        <f>'Nach Mannschaften sortiert'!H37</f>
+        <f>'Nach Mannschaften sortiert'!H40</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <f>'Nach Mannschaften sortiert'!A38</f>
+        <f>'Nach Mannschaften sortiert'!A41</f>
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <f>'Nach Mannschaften sortiert'!B38</f>
+        <f>'Nach Mannschaften sortiert'!B41</f>
         <v>7</v>
       </c>
       <c r="C21" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C38</f>
+        <f>'Nach Mannschaften sortiert'!C41</f>
         <v>U16</v>
       </c>
       <c r="D21" s="16">
-        <f>'Nach Mannschaften sortiert'!D38</f>
+        <f>'Nach Mannschaften sortiert'!D41</f>
         <v>0</v>
       </c>
       <c r="E21" s="38">
-        <f>'Nach Mannschaften sortiert'!E38</f>
+        <f>'Nach Mannschaften sortiert'!E41</f>
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <f>'Nach Mannschaften sortiert'!F38</f>
+        <f>'Nach Mannschaften sortiert'!F41</f>
         <v>0</v>
       </c>
       <c r="G21" s="2">
-        <f>'Nach Mannschaften sortiert'!G38</f>
+        <f>'Nach Mannschaften sortiert'!G41</f>
         <v>0</v>
       </c>
       <c r="H21" s="2">
-        <f>'Nach Mannschaften sortiert'!H38</f>
+        <f>'Nach Mannschaften sortiert'!H41</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="60">
-        <f>'Nach Mannschaften sortiert'!A39</f>
+        <f>'Nach Mannschaften sortiert'!A42</f>
         <v>21</v>
       </c>
       <c r="B22" s="60">
-        <f>'Nach Mannschaften sortiert'!B39</f>
+        <f>'Nach Mannschaften sortiert'!B42</f>
         <v>8</v>
       </c>
       <c r="C22" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C39</f>
+        <f>'Nach Mannschaften sortiert'!C42</f>
         <v>U16</v>
       </c>
       <c r="D22" s="61">
-        <f>'Nach Mannschaften sortiert'!D39</f>
+        <f>'Nach Mannschaften sortiert'!D42</f>
         <v>0</v>
       </c>
       <c r="E22" s="62">
-        <f>'Nach Mannschaften sortiert'!E39</f>
+        <f>'Nach Mannschaften sortiert'!E42</f>
         <v>0</v>
       </c>
       <c r="F22" s="60">
-        <f>'Nach Mannschaften sortiert'!F39</f>
+        <f>'Nach Mannschaften sortiert'!F42</f>
         <v>0</v>
       </c>
       <c r="G22" s="60">
-        <f>'Nach Mannschaften sortiert'!G39</f>
+        <f>'Nach Mannschaften sortiert'!G42</f>
         <v>0</v>
       </c>
       <c r="H22" s="60">
-        <f>'Nach Mannschaften sortiert'!H39</f>
+        <f>'Nach Mannschaften sortiert'!H42</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <f>'Nach Mannschaften sortiert'!A40</f>
+        <f>'Nach Mannschaften sortiert'!A43</f>
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <f>'Nach Mannschaften sortiert'!B40</f>
+        <f>'Nach Mannschaften sortiert'!B43</f>
         <v>9</v>
       </c>
       <c r="C23" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C40</f>
+        <f>'Nach Mannschaften sortiert'!C43</f>
         <v>U16</v>
       </c>
       <c r="D23" s="16">
-        <f>'Nach Mannschaften sortiert'!D40</f>
+        <f>'Nach Mannschaften sortiert'!D43</f>
         <v>0</v>
       </c>
       <c r="E23" s="38">
-        <f>'Nach Mannschaften sortiert'!E40</f>
+        <f>'Nach Mannschaften sortiert'!E43</f>
         <v>0</v>
       </c>
       <c r="F23" s="2">
-        <f>'Nach Mannschaften sortiert'!F40</f>
+        <f>'Nach Mannschaften sortiert'!F43</f>
         <v>0</v>
       </c>
       <c r="G23" s="2">
-        <f>'Nach Mannschaften sortiert'!G40</f>
+        <f>'Nach Mannschaften sortiert'!G43</f>
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <f>'Nach Mannschaften sortiert'!H40</f>
+        <f>'Nach Mannschaften sortiert'!H43</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="63">
-        <f>'Nach Mannschaften sortiert'!A74</f>
+        <f>'Nach Mannschaften sortiert'!A77</f>
         <v>64</v>
       </c>
       <c r="B24" s="63">
-        <f>'Nach Mannschaften sortiert'!B74</f>
+        <f>'Nach Mannschaften sortiert'!B77</f>
         <v>1</v>
       </c>
       <c r="C24" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C74</f>
+        <f>'Nach Mannschaften sortiert'!C77</f>
         <v>U11</v>
       </c>
       <c r="D24" s="64">
-        <f>'Nach Mannschaften sortiert'!D74</f>
+        <f>'Nach Mannschaften sortiert'!D77</f>
         <v>0</v>
       </c>
       <c r="E24" s="65">
-        <f>'Nach Mannschaften sortiert'!E74</f>
+        <f>'Nach Mannschaften sortiert'!E77</f>
         <v>0</v>
       </c>
       <c r="F24" s="63">
-        <f>'Nach Mannschaften sortiert'!F74</f>
+        <f>'Nach Mannschaften sortiert'!F77</f>
         <v>0</v>
       </c>
       <c r="G24" s="63">
-        <f>'Nach Mannschaften sortiert'!G74</f>
+        <f>'Nach Mannschaften sortiert'!G77</f>
         <v>0</v>
       </c>
       <c r="H24" s="63">
-        <f>'Nach Mannschaften sortiert'!H74</f>
+        <f>'Nach Mannschaften sortiert'!H77</f>
         <v>0</v>
       </c>
     </row>
@@ -9476,137 +10130,137 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="63">
-        <f>'Nach Mannschaften sortiert'!A84</f>
+        <f>'Nach Mannschaften sortiert'!A87</f>
         <v>69</v>
       </c>
       <c r="B26" s="63">
-        <f>'Nach Mannschaften sortiert'!B84</f>
+        <f>'Nach Mannschaften sortiert'!B87</f>
         <v>1</v>
       </c>
       <c r="C26" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C84</f>
+        <f>'Nach Mannschaften sortiert'!C87</f>
         <v>U10</v>
       </c>
       <c r="D26" s="64">
-        <f>'Nach Mannschaften sortiert'!D84</f>
+        <f>'Nach Mannschaften sortiert'!D87</f>
         <v>0</v>
       </c>
       <c r="E26" s="65">
-        <f>'Nach Mannschaften sortiert'!E84</f>
+        <f>'Nach Mannschaften sortiert'!E87</f>
         <v>0</v>
       </c>
       <c r="F26" s="63">
-        <f>'Nach Mannschaften sortiert'!F84</f>
+        <f>'Nach Mannschaften sortiert'!F87</f>
         <v>0</v>
       </c>
       <c r="G26" s="63">
-        <f>'Nach Mannschaften sortiert'!G84</f>
+        <f>'Nach Mannschaften sortiert'!G87</f>
         <v>0</v>
       </c>
       <c r="H26" s="63">
-        <f>'Nach Mannschaften sortiert'!H84</f>
+        <f>'Nach Mannschaften sortiert'!H87</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="60">
-        <f>'Nach Mannschaften sortiert'!A43</f>
+        <f>'Nach Mannschaften sortiert'!A46</f>
         <v>26</v>
       </c>
       <c r="B27" s="60">
-        <f>'Nach Mannschaften sortiert'!B43</f>
+        <f>'Nach Mannschaften sortiert'!B46</f>
         <v>3</v>
       </c>
       <c r="C27" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C43</f>
+        <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U14</v>
       </c>
       <c r="D27" s="61">
-        <f>'Nach Mannschaften sortiert'!D43</f>
+        <f>'Nach Mannschaften sortiert'!D46</f>
         <v>0</v>
       </c>
       <c r="E27" s="62">
-        <f>'Nach Mannschaften sortiert'!E43</f>
+        <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="F27" s="60">
-        <f>'Nach Mannschaften sortiert'!F43</f>
+        <f>'Nach Mannschaften sortiert'!F46</f>
         <v>0</v>
       </c>
       <c r="G27" s="60">
-        <f>'Nach Mannschaften sortiert'!G43</f>
+        <f>'Nach Mannschaften sortiert'!G46</f>
         <v>0</v>
       </c>
       <c r="H27" s="60">
-        <f>'Nach Mannschaften sortiert'!H43</f>
+        <f>'Nach Mannschaften sortiert'!H46</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <f>'Nach Mannschaften sortiert'!A44</f>
+        <f>'Nach Mannschaften sortiert'!A47</f>
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <f>'Nach Mannschaften sortiert'!B44</f>
+        <f>'Nach Mannschaften sortiert'!B47</f>
         <v>4</v>
       </c>
       <c r="C28" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C44</f>
+        <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U14</v>
       </c>
       <c r="D28" s="16">
-        <f>'Nach Mannschaften sortiert'!D44</f>
+        <f>'Nach Mannschaften sortiert'!D47</f>
         <v>0</v>
       </c>
       <c r="E28" s="38">
-        <f>'Nach Mannschaften sortiert'!E44</f>
+        <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="F28" s="2">
-        <f>'Nach Mannschaften sortiert'!F44</f>
+        <f>'Nach Mannschaften sortiert'!F47</f>
         <v>0</v>
       </c>
       <c r="G28" s="2">
-        <f>'Nach Mannschaften sortiert'!G44</f>
+        <f>'Nach Mannschaften sortiert'!G47</f>
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <f>'Nach Mannschaften sortiert'!H44</f>
+        <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="63">
-        <f>'Nach Mannschaften sortiert'!A94</f>
+        <f>'Nach Mannschaften sortiert'!A97</f>
         <v>74</v>
       </c>
       <c r="B29" s="63">
-        <f>'Nach Mannschaften sortiert'!B94</f>
+        <f>'Nach Mannschaften sortiert'!B97</f>
         <v>1</v>
       </c>
       <c r="C29" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C94</f>
+        <f>'Nach Mannschaften sortiert'!C97</f>
         <v>U9</v>
       </c>
       <c r="D29" s="64">
-        <f>'Nach Mannschaften sortiert'!D94</f>
+        <f>'Nach Mannschaften sortiert'!D97</f>
         <v>0</v>
       </c>
       <c r="E29" s="65">
-        <f>'Nach Mannschaften sortiert'!E94</f>
+        <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="F29" s="63">
-        <f>'Nach Mannschaften sortiert'!F94</f>
+        <f>'Nach Mannschaften sortiert'!F97</f>
         <v>0</v>
       </c>
       <c r="G29" s="63">
-        <f>'Nach Mannschaften sortiert'!G94</f>
+        <f>'Nach Mannschaften sortiert'!G97</f>
         <v>0</v>
       </c>
       <c r="H29" s="63">
-        <f>'Nach Mannschaften sortiert'!H94</f>
+        <f>'Nach Mannschaften sortiert'!H97</f>
         <v>0</v>
       </c>
     </row>
@@ -9646,273 +10300,273 @@
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <f>'Nach Mannschaften sortiert'!A46</f>
+        <f>'Nach Mannschaften sortiert'!A49</f>
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <f>'Nach Mannschaften sortiert'!B46</f>
+        <f>'Nach Mannschaften sortiert'!B49</f>
         <v>7</v>
       </c>
       <c r="C31" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C46</f>
+        <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U14</v>
       </c>
       <c r="D31" s="16">
-        <f>'Nach Mannschaften sortiert'!D46</f>
+        <f>'Nach Mannschaften sortiert'!D49</f>
         <v>0</v>
       </c>
       <c r="E31" s="38">
-        <f>'Nach Mannschaften sortiert'!E46</f>
+        <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="F31" s="2">
-        <f>'Nach Mannschaften sortiert'!F46</f>
+        <f>'Nach Mannschaften sortiert'!F49</f>
         <v>0</v>
       </c>
       <c r="G31" s="2">
-        <f>'Nach Mannschaften sortiert'!G46</f>
+        <f>'Nach Mannschaften sortiert'!G49</f>
         <v>0</v>
       </c>
       <c r="H31" s="2">
-        <f>'Nach Mannschaften sortiert'!H46</f>
+        <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <f>'Nach Mannschaften sortiert'!A47</f>
+        <f>'Nach Mannschaften sortiert'!A50</f>
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <f>'Nach Mannschaften sortiert'!B47</f>
+        <f>'Nach Mannschaften sortiert'!B50</f>
         <v>8</v>
       </c>
       <c r="C32" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C47</f>
+        <f>'Nach Mannschaften sortiert'!C50</f>
         <v>U14</v>
       </c>
       <c r="D32" s="16">
-        <f>'Nach Mannschaften sortiert'!D47</f>
+        <f>'Nach Mannschaften sortiert'!D50</f>
         <v>0</v>
       </c>
       <c r="E32" s="38">
-        <f>'Nach Mannschaften sortiert'!E47</f>
+        <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="F32" s="2">
-        <f>'Nach Mannschaften sortiert'!F47</f>
+        <f>'Nach Mannschaften sortiert'!F50</f>
         <v>0</v>
       </c>
       <c r="G32" s="2">
-        <f>'Nach Mannschaften sortiert'!G47</f>
+        <f>'Nach Mannschaften sortiert'!G50</f>
         <v>0</v>
       </c>
       <c r="H32" s="2">
-        <f>'Nach Mannschaften sortiert'!H47</f>
+        <f>'Nach Mannschaften sortiert'!H50</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="60">
-        <f>'Nach Mannschaften sortiert'!A48</f>
+        <f>'Nach Mannschaften sortiert'!A51</f>
         <v>32</v>
       </c>
       <c r="B33" s="60">
-        <f>'Nach Mannschaften sortiert'!B48</f>
+        <f>'Nach Mannschaften sortiert'!B51</f>
         <v>9</v>
       </c>
       <c r="C33" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C48</f>
+        <f>'Nach Mannschaften sortiert'!C51</f>
         <v>U14</v>
       </c>
       <c r="D33" s="61">
-        <f>'Nach Mannschaften sortiert'!D48</f>
+        <f>'Nach Mannschaften sortiert'!D51</f>
         <v>0</v>
       </c>
       <c r="E33" s="62">
-        <f>'Nach Mannschaften sortiert'!E48</f>
+        <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="F33" s="60">
-        <f>'Nach Mannschaften sortiert'!F48</f>
+        <f>'Nach Mannschaften sortiert'!F51</f>
         <v>0</v>
       </c>
       <c r="G33" s="60">
-        <f>'Nach Mannschaften sortiert'!G48</f>
+        <f>'Nach Mannschaften sortiert'!G51</f>
         <v>0</v>
       </c>
       <c r="H33" s="60">
-        <f>'Nach Mannschaften sortiert'!H48</f>
+        <f>'Nach Mannschaften sortiert'!H51</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <f>'Nach Mannschaften sortiert'!A49</f>
+        <f>'Nach Mannschaften sortiert'!A52</f>
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <f>'Nach Mannschaften sortiert'!B49</f>
+        <f>'Nach Mannschaften sortiert'!B52</f>
         <v>10</v>
       </c>
       <c r="C34" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C49</f>
+        <f>'Nach Mannschaften sortiert'!C52</f>
         <v>U14</v>
       </c>
       <c r="D34" s="16">
-        <f>'Nach Mannschaften sortiert'!D49</f>
+        <f>'Nach Mannschaften sortiert'!D52</f>
         <v>0</v>
       </c>
       <c r="E34" s="38">
-        <f>'Nach Mannschaften sortiert'!E49</f>
+        <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <f>'Nach Mannschaften sortiert'!F49</f>
+        <f>'Nach Mannschaften sortiert'!F52</f>
         <v>0</v>
       </c>
       <c r="G34" s="2">
-        <f>'Nach Mannschaften sortiert'!G49</f>
+        <f>'Nach Mannschaften sortiert'!G52</f>
         <v>0</v>
       </c>
       <c r="H34" s="2">
-        <f>'Nach Mannschaften sortiert'!H49</f>
+        <f>'Nach Mannschaften sortiert'!H52</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="63">
-        <f>'Nach Mannschaften sortiert'!A67</f>
+        <f>'Nach Mannschaften sortiert'!A70</f>
         <v>55</v>
       </c>
       <c r="B35" s="63">
-        <f>'Nach Mannschaften sortiert'!B67</f>
+        <f>'Nach Mannschaften sortiert'!B70</f>
         <v>2</v>
       </c>
       <c r="C35" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C67</f>
+        <f>'Nach Mannschaften sortiert'!C70</f>
         <v>U12_2</v>
       </c>
       <c r="D35" s="64">
-        <f>'Nach Mannschaften sortiert'!D67</f>
+        <f>'Nach Mannschaften sortiert'!D70</f>
         <v>0</v>
       </c>
       <c r="E35" s="65">
-        <f>'Nach Mannschaften sortiert'!E67</f>
+        <f>'Nach Mannschaften sortiert'!E70</f>
         <v>0</v>
       </c>
       <c r="F35" s="63">
-        <f>'Nach Mannschaften sortiert'!F67</f>
+        <f>'Nach Mannschaften sortiert'!F70</f>
         <v>0</v>
       </c>
       <c r="G35" s="63">
-        <f>'Nach Mannschaften sortiert'!G67</f>
+        <f>'Nach Mannschaften sortiert'!G70</f>
         <v>0</v>
       </c>
       <c r="H35" s="63">
-        <f>'Nach Mannschaften sortiert'!H67</f>
+        <f>'Nach Mannschaften sortiert'!H70</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <f>'Nach Mannschaften sortiert'!A51</f>
+        <f>'Nach Mannschaften sortiert'!A54</f>
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <f>'Nach Mannschaften sortiert'!B51</f>
+        <f>'Nach Mannschaften sortiert'!B54</f>
         <v>2</v>
       </c>
       <c r="C36" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C51</f>
+        <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U13</v>
       </c>
       <c r="D36" s="16">
-        <f>'Nach Mannschaften sortiert'!D51</f>
+        <f>'Nach Mannschaften sortiert'!D54</f>
         <v>0</v>
       </c>
       <c r="E36" s="38">
-        <f>'Nach Mannschaften sortiert'!E51</f>
+        <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <f>'Nach Mannschaften sortiert'!F51</f>
+        <f>'Nach Mannschaften sortiert'!F54</f>
         <v>0</v>
       </c>
       <c r="G36" s="2">
-        <f>'Nach Mannschaften sortiert'!G51</f>
+        <f>'Nach Mannschaften sortiert'!G54</f>
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <f>'Nach Mannschaften sortiert'!H51</f>
+        <f>'Nach Mannschaften sortiert'!H54</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <f>'Nach Mannschaften sortiert'!A52</f>
+        <f>'Nach Mannschaften sortiert'!A55</f>
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <f>'Nach Mannschaften sortiert'!B52</f>
+        <f>'Nach Mannschaften sortiert'!B55</f>
         <v>3</v>
       </c>
       <c r="C37" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C52</f>
+        <f>'Nach Mannschaften sortiert'!C55</f>
         <v>U13</v>
       </c>
       <c r="D37" s="16">
-        <f>'Nach Mannschaften sortiert'!D52</f>
+        <f>'Nach Mannschaften sortiert'!D55</f>
         <v>0</v>
       </c>
       <c r="E37" s="38">
-        <f>'Nach Mannschaften sortiert'!E52</f>
+        <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <f>'Nach Mannschaften sortiert'!F52</f>
+        <f>'Nach Mannschaften sortiert'!F55</f>
         <v>0</v>
       </c>
       <c r="G37" s="2">
-        <f>'Nach Mannschaften sortiert'!G52</f>
+        <f>'Nach Mannschaften sortiert'!G55</f>
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <f>'Nach Mannschaften sortiert'!H52</f>
+        <f>'Nach Mannschaften sortiert'!H55</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="60">
-        <f>'Nach Mannschaften sortiert'!A42</f>
+        <f>'Nach Mannschaften sortiert'!A45</f>
         <v>25</v>
       </c>
       <c r="B38" s="60">
-        <f>'Nach Mannschaften sortiert'!B42</f>
+        <f>'Nach Mannschaften sortiert'!B45</f>
         <v>2</v>
       </c>
       <c r="C38" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C42</f>
+        <f>'Nach Mannschaften sortiert'!C45</f>
         <v>U14</v>
       </c>
       <c r="D38" s="61">
-        <f>'Nach Mannschaften sortiert'!D42</f>
+        <f>'Nach Mannschaften sortiert'!D45</f>
         <v>0</v>
       </c>
       <c r="E38" s="62">
-        <f>'Nach Mannschaften sortiert'!E42</f>
+        <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="F38" s="60">
-        <f>'Nach Mannschaften sortiert'!F42</f>
+        <f>'Nach Mannschaften sortiert'!F45</f>
         <v>0</v>
       </c>
       <c r="G38" s="60">
-        <f>'Nach Mannschaften sortiert'!G42</f>
+        <f>'Nach Mannschaften sortiert'!G45</f>
         <v>0</v>
       </c>
       <c r="H38" s="60">
-        <f>'Nach Mannschaften sortiert'!H42</f>
+        <f>'Nach Mannschaften sortiert'!H45</f>
         <v>0</v>
       </c>
     </row>
@@ -9952,205 +10606,205 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <f>'Nach Mannschaften sortiert'!A54</f>
+        <f>'Nach Mannschaften sortiert'!A57</f>
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <f>'Nach Mannschaften sortiert'!B54</f>
+        <f>'Nach Mannschaften sortiert'!B57</f>
         <v>6</v>
       </c>
       <c r="C40" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C54</f>
+        <f>'Nach Mannschaften sortiert'!C57</f>
         <v>U13</v>
       </c>
       <c r="D40" s="16">
-        <f>'Nach Mannschaften sortiert'!D54</f>
+        <f>'Nach Mannschaften sortiert'!D57</f>
         <v>0</v>
       </c>
       <c r="E40" s="38">
-        <f>'Nach Mannschaften sortiert'!E54</f>
+        <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
       <c r="F40" s="2">
-        <f>'Nach Mannschaften sortiert'!F54</f>
+        <f>'Nach Mannschaften sortiert'!F57</f>
         <v>0</v>
       </c>
       <c r="G40" s="2">
-        <f>'Nach Mannschaften sortiert'!G54</f>
+        <f>'Nach Mannschaften sortiert'!G57</f>
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <f>'Nach Mannschaften sortiert'!H54</f>
+        <f>'Nach Mannschaften sortiert'!H57</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="60">
-        <f>'Nach Mannschaften sortiert'!A11</f>
+        <f>'Nach Mannschaften sortiert'!A14</f>
         <v>6</v>
       </c>
       <c r="B41" s="60">
-        <f>'Nach Mannschaften sortiert'!B11</f>
+        <f>'Nach Mannschaften sortiert'!B14</f>
         <v>6</v>
       </c>
       <c r="C41" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C11</f>
+        <f>'Nach Mannschaften sortiert'!C14</f>
         <v>KM</v>
       </c>
       <c r="D41" s="61">
-        <f>'Nach Mannschaften sortiert'!D11</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D14</f>
+        <v>46284</v>
       </c>
       <c r="E41" s="62">
-        <f>'Nach Mannschaften sortiert'!E11</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="60">
-        <f>'Nach Mannschaften sortiert'!F11</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="60">
-        <f>'Nach Mannschaften sortiert'!G11</f>
-        <v>0</v>
-      </c>
-      <c r="H41" s="60">
-        <f>'Nach Mannschaften sortiert'!H11</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E14</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!F14</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="G41" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!G14</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="H41" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!H14</f>
+        <v>Auswärts</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="69">
-        <f>'Nach Mannschaften sortiert'!A69</f>
+        <f>'Nach Mannschaften sortiert'!A72</f>
         <v>57</v>
       </c>
       <c r="B42" s="69">
-        <f>'Nach Mannschaften sortiert'!B69</f>
+        <f>'Nach Mannschaften sortiert'!B72</f>
         <v>4</v>
       </c>
       <c r="C42" s="69" t="str">
-        <f>'Nach Mannschaften sortiert'!C69</f>
+        <f>'Nach Mannschaften sortiert'!C72</f>
         <v>U12_2</v>
       </c>
       <c r="D42" s="70">
-        <f>'Nach Mannschaften sortiert'!D69</f>
+        <f>'Nach Mannschaften sortiert'!D72</f>
         <v>0</v>
       </c>
       <c r="E42" s="71">
-        <f>'Nach Mannschaften sortiert'!E69</f>
+        <f>'Nach Mannschaften sortiert'!E72</f>
         <v>0</v>
       </c>
       <c r="F42" s="69">
-        <f>'Nach Mannschaften sortiert'!F69</f>
+        <f>'Nach Mannschaften sortiert'!F72</f>
         <v>0</v>
       </c>
       <c r="G42" s="69">
-        <f>'Nach Mannschaften sortiert'!G69</f>
+        <f>'Nach Mannschaften sortiert'!G72</f>
         <v>0</v>
       </c>
       <c r="H42" s="69">
-        <f>'Nach Mannschaften sortiert'!H69</f>
+        <f>'Nach Mannschaften sortiert'!H72</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <f>'Nach Mannschaften sortiert'!A57</f>
+        <f>'Nach Mannschaften sortiert'!A60</f>
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <f>'Nach Mannschaften sortiert'!B57</f>
+        <f>'Nach Mannschaften sortiert'!B60</f>
         <v>9</v>
       </c>
       <c r="C43" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C57</f>
+        <f>'Nach Mannschaften sortiert'!C60</f>
         <v>U13</v>
       </c>
       <c r="D43" s="16">
-        <f>'Nach Mannschaften sortiert'!D57</f>
+        <f>'Nach Mannschaften sortiert'!D60</f>
         <v>0</v>
       </c>
       <c r="E43" s="38">
-        <f>'Nach Mannschaften sortiert'!E57</f>
+        <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="F43" s="2">
-        <f>'Nach Mannschaften sortiert'!F57</f>
+        <f>'Nach Mannschaften sortiert'!F60</f>
         <v>0</v>
       </c>
       <c r="G43" s="2">
-        <f>'Nach Mannschaften sortiert'!G57</f>
+        <f>'Nach Mannschaften sortiert'!G60</f>
         <v>0</v>
       </c>
       <c r="H43" s="2">
-        <f>'Nach Mannschaften sortiert'!H57</f>
+        <f>'Nach Mannschaften sortiert'!H60</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="63">
-        <f>'Nach Mannschaften sortiert'!A60</f>
+        <f>'Nach Mannschaften sortiert'!A63</f>
         <v>47</v>
       </c>
       <c r="B44" s="63">
-        <f>'Nach Mannschaften sortiert'!B60</f>
+        <f>'Nach Mannschaften sortiert'!B63</f>
         <v>4</v>
       </c>
       <c r="C44" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C60</f>
+        <f>'Nach Mannschaften sortiert'!C63</f>
         <v>U12_1</v>
       </c>
       <c r="D44" s="64">
-        <f>'Nach Mannschaften sortiert'!D60</f>
+        <f>'Nach Mannschaften sortiert'!D63</f>
         <v>0</v>
       </c>
       <c r="E44" s="65">
-        <f>'Nach Mannschaften sortiert'!E60</f>
+        <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="F44" s="63">
-        <f>'Nach Mannschaften sortiert'!F60</f>
+        <f>'Nach Mannschaften sortiert'!F63</f>
         <v>0</v>
       </c>
       <c r="G44" s="63">
-        <f>'Nach Mannschaften sortiert'!G60</f>
+        <f>'Nach Mannschaften sortiert'!G63</f>
         <v>0</v>
       </c>
       <c r="H44" s="63">
-        <f>'Nach Mannschaften sortiert'!H60</f>
+        <f>'Nach Mannschaften sortiert'!H63</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="63">
-        <f>'Nach Mannschaften sortiert'!A53</f>
+        <f>'Nach Mannschaften sortiert'!A56</f>
         <v>37</v>
       </c>
       <c r="B45" s="63">
-        <f>'Nach Mannschaften sortiert'!B53</f>
+        <f>'Nach Mannschaften sortiert'!B56</f>
         <v>4</v>
       </c>
       <c r="C45" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C53</f>
+        <f>'Nach Mannschaften sortiert'!C56</f>
         <v>U13</v>
       </c>
       <c r="D45" s="64">
-        <f>'Nach Mannschaften sortiert'!D53</f>
+        <f>'Nach Mannschaften sortiert'!D56</f>
         <v>0</v>
       </c>
       <c r="E45" s="65">
-        <f>'Nach Mannschaften sortiert'!E53</f>
+        <f>'Nach Mannschaften sortiert'!E56</f>
         <v>0</v>
       </c>
       <c r="F45" s="63">
-        <f>'Nach Mannschaften sortiert'!F53</f>
+        <f>'Nach Mannschaften sortiert'!F56</f>
         <v>0</v>
       </c>
       <c r="G45" s="63">
-        <f>'Nach Mannschaften sortiert'!G53</f>
+        <f>'Nach Mannschaften sortiert'!G56</f>
         <v>0</v>
       </c>
       <c r="H45" s="63">
-        <f>'Nach Mannschaften sortiert'!H53</f>
+        <f>'Nach Mannschaften sortiert'!H56</f>
         <v>0</v>
       </c>
     </row>
@@ -10190,137 +10844,137 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <f>'Nach Mannschaften sortiert'!A59</f>
+        <f>'Nach Mannschaften sortiert'!A62</f>
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <f>'Nach Mannschaften sortiert'!B59</f>
+        <f>'Nach Mannschaften sortiert'!B62</f>
         <v>3</v>
       </c>
       <c r="C47" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C59</f>
+        <f>'Nach Mannschaften sortiert'!C62</f>
         <v>U12_1</v>
       </c>
       <c r="D47" s="16">
-        <f>'Nach Mannschaften sortiert'!D59</f>
+        <f>'Nach Mannschaften sortiert'!D62</f>
         <v>0</v>
       </c>
       <c r="E47" s="38">
-        <f>'Nach Mannschaften sortiert'!E59</f>
+        <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="F47" s="2">
-        <f>'Nach Mannschaften sortiert'!F59</f>
+        <f>'Nach Mannschaften sortiert'!F62</f>
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <f>'Nach Mannschaften sortiert'!G59</f>
+        <f>'Nach Mannschaften sortiert'!G62</f>
         <v>0</v>
       </c>
       <c r="H47" s="2">
-        <f>'Nach Mannschaften sortiert'!H59</f>
+        <f>'Nach Mannschaften sortiert'!H62</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="60">
-        <f>'Nach Mannschaften sortiert'!A35</f>
+        <f>'Nach Mannschaften sortiert'!A38</f>
         <v>17</v>
       </c>
       <c r="B48" s="60">
-        <f>'Nach Mannschaften sortiert'!B35</f>
+        <f>'Nach Mannschaften sortiert'!B38</f>
         <v>4</v>
       </c>
       <c r="C48" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C35</f>
+        <f>'Nach Mannschaften sortiert'!C38</f>
         <v>U16</v>
       </c>
       <c r="D48" s="61">
-        <f>'Nach Mannschaften sortiert'!D35</f>
+        <f>'Nach Mannschaften sortiert'!D38</f>
         <v>0</v>
       </c>
       <c r="E48" s="62">
-        <f>'Nach Mannschaften sortiert'!E35</f>
+        <f>'Nach Mannschaften sortiert'!E38</f>
         <v>0</v>
       </c>
       <c r="F48" s="60">
-        <f>'Nach Mannschaften sortiert'!F35</f>
+        <f>'Nach Mannschaften sortiert'!F38</f>
         <v>0</v>
       </c>
       <c r="G48" s="60">
-        <f>'Nach Mannschaften sortiert'!G35</f>
+        <f>'Nach Mannschaften sortiert'!G38</f>
         <v>0</v>
       </c>
       <c r="H48" s="60">
-        <f>'Nach Mannschaften sortiert'!H35</f>
+        <f>'Nach Mannschaften sortiert'!H38</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <f>'Nach Mannschaften sortiert'!A61</f>
+        <f>'Nach Mannschaften sortiert'!A64</f>
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <f>'Nach Mannschaften sortiert'!B61</f>
+        <f>'Nach Mannschaften sortiert'!B64</f>
         <v>5</v>
       </c>
       <c r="C49" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C61</f>
+        <f>'Nach Mannschaften sortiert'!C64</f>
         <v>U12_1</v>
       </c>
       <c r="D49" s="16">
-        <f>'Nach Mannschaften sortiert'!D61</f>
+        <f>'Nach Mannschaften sortiert'!D64</f>
         <v>0</v>
       </c>
       <c r="E49" s="38">
-        <f>'Nach Mannschaften sortiert'!E61</f>
+        <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="F49" s="2">
-        <f>'Nach Mannschaften sortiert'!F61</f>
+        <f>'Nach Mannschaften sortiert'!F64</f>
         <v>0</v>
       </c>
       <c r="G49" s="2">
-        <f>'Nach Mannschaften sortiert'!G61</f>
+        <f>'Nach Mannschaften sortiert'!G64</f>
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <f>'Nach Mannschaften sortiert'!H61</f>
+        <f>'Nach Mannschaften sortiert'!H64</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <f>'Nach Mannschaften sortiert'!A62</f>
+        <f>'Nach Mannschaften sortiert'!A65</f>
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <f>'Nach Mannschaften sortiert'!B62</f>
+        <f>'Nach Mannschaften sortiert'!B65</f>
         <v>6</v>
       </c>
       <c r="C50" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C62</f>
+        <f>'Nach Mannschaften sortiert'!C65</f>
         <v>U12_1</v>
       </c>
       <c r="D50" s="16">
-        <f>'Nach Mannschaften sortiert'!D62</f>
+        <f>'Nach Mannschaften sortiert'!D65</f>
         <v>0</v>
       </c>
       <c r="E50" s="38">
-        <f>'Nach Mannschaften sortiert'!E62</f>
+        <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="F50" s="2">
-        <f>'Nach Mannschaften sortiert'!F62</f>
+        <f>'Nach Mannschaften sortiert'!F65</f>
         <v>0</v>
       </c>
       <c r="G50" s="2">
-        <f>'Nach Mannschaften sortiert'!G62</f>
+        <f>'Nach Mannschaften sortiert'!G65</f>
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <f>'Nach Mannschaften sortiert'!H62</f>
+        <f>'Nach Mannschaften sortiert'!H65</f>
         <v>0</v>
       </c>
     </row>
@@ -10360,240 +11014,240 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="60">
-        <f>'Nach Mannschaften sortiert'!A13</f>
+        <f>'Nach Mannschaften sortiert'!A16</f>
         <v>8</v>
       </c>
       <c r="B52" s="60">
-        <f>'Nach Mannschaften sortiert'!B13</f>
+        <f>'Nach Mannschaften sortiert'!B16</f>
         <v>8</v>
       </c>
       <c r="C52" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C13</f>
+        <f>'Nach Mannschaften sortiert'!C16</f>
         <v>KM</v>
       </c>
       <c r="D52" s="61">
-        <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D16</f>
+        <v>46297</v>
       </c>
       <c r="E52" s="62">
-        <f>'Nach Mannschaften sortiert'!E13</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="60">
-        <f>'Nach Mannschaften sortiert'!F13</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="60">
-        <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>0</v>
-      </c>
-      <c r="H52" s="60">
-        <f>'Nach Mannschaften sortiert'!H13</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E16</f>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F52" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!F16</f>
+        <v>Siegendorf</v>
+      </c>
+      <c r="G52" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!G16</f>
+        <v>Siegendorf</v>
+      </c>
+      <c r="H52" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!H16</f>
+        <v>Auswärts</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <f>'Nach Mannschaften sortiert'!A64</f>
+        <f>'Nach Mannschaften sortiert'!A67</f>
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <f>'Nach Mannschaften sortiert'!B64</f>
+        <f>'Nach Mannschaften sortiert'!B67</f>
         <v>9</v>
       </c>
       <c r="C53" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C64</f>
+        <f>'Nach Mannschaften sortiert'!C67</f>
         <v>U12_1</v>
       </c>
       <c r="D53" s="16">
-        <f>'Nach Mannschaften sortiert'!D64</f>
+        <f>'Nach Mannschaften sortiert'!D67</f>
         <v>0</v>
       </c>
       <c r="E53" s="38">
-        <f>'Nach Mannschaften sortiert'!E64</f>
+        <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="F53" s="2">
-        <f>'Nach Mannschaften sortiert'!F64</f>
+        <f>'Nach Mannschaften sortiert'!F67</f>
         <v>0</v>
       </c>
       <c r="G53" s="2">
-        <f>'Nach Mannschaften sortiert'!G64</f>
+        <f>'Nach Mannschaften sortiert'!G67</f>
         <v>0</v>
       </c>
       <c r="H53" s="2">
-        <f>'Nach Mannschaften sortiert'!H64</f>
+        <f>'Nach Mannschaften sortiert'!H67</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="60">
-        <f>'Nach Mannschaften sortiert'!A45</f>
+        <f>'Nach Mannschaften sortiert'!A48</f>
         <v>28</v>
       </c>
       <c r="B54" s="60">
-        <f>'Nach Mannschaften sortiert'!B45</f>
+        <f>'Nach Mannschaften sortiert'!B48</f>
         <v>5</v>
       </c>
       <c r="C54" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C45</f>
+        <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U14</v>
       </c>
       <c r="D54" s="61">
-        <f>'Nach Mannschaften sortiert'!D45</f>
+        <f>'Nach Mannschaften sortiert'!D48</f>
         <v>0</v>
       </c>
       <c r="E54" s="62">
-        <f>'Nach Mannschaften sortiert'!E45</f>
+        <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="F54" s="60">
-        <f>'Nach Mannschaften sortiert'!F45</f>
+        <f>'Nach Mannschaften sortiert'!F48</f>
         <v>0</v>
       </c>
       <c r="G54" s="60">
-        <f>'Nach Mannschaften sortiert'!G45</f>
+        <f>'Nach Mannschaften sortiert'!G48</f>
         <v>0</v>
       </c>
       <c r="H54" s="60">
-        <f>'Nach Mannschaften sortiert'!H45</f>
+        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <f>'Nach Mannschaften sortiert'!A66</f>
+        <f>'Nach Mannschaften sortiert'!A69</f>
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <f>'Nach Mannschaften sortiert'!B66</f>
+        <f>'Nach Mannschaften sortiert'!B69</f>
         <v>1</v>
       </c>
       <c r="C55" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C66</f>
+        <f>'Nach Mannschaften sortiert'!C69</f>
         <v>U12_2</v>
       </c>
       <c r="D55" s="16">
-        <f>'Nach Mannschaften sortiert'!D66</f>
+        <f>'Nach Mannschaften sortiert'!D69</f>
         <v>0</v>
       </c>
       <c r="E55" s="38">
-        <f>'Nach Mannschaften sortiert'!E66</f>
+        <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="F55" s="2">
-        <f>'Nach Mannschaften sortiert'!F66</f>
+        <f>'Nach Mannschaften sortiert'!F69</f>
         <v>0</v>
       </c>
       <c r="G55" s="2">
-        <f>'Nach Mannschaften sortiert'!G66</f>
+        <f>'Nach Mannschaften sortiert'!G69</f>
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <f>'Nach Mannschaften sortiert'!H66</f>
+        <f>'Nach Mannschaften sortiert'!H69</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="60">
-        <f>'Nach Mannschaften sortiert'!A70</f>
+        <f>'Nach Mannschaften sortiert'!A73</f>
         <v>59</v>
       </c>
       <c r="B56" s="60">
-        <f>'Nach Mannschaften sortiert'!B70</f>
+        <f>'Nach Mannschaften sortiert'!B73</f>
         <v>6</v>
       </c>
       <c r="C56" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C70</f>
+        <f>'Nach Mannschaften sortiert'!C73</f>
         <v>U12_2</v>
       </c>
       <c r="D56" s="61">
-        <f>'Nach Mannschaften sortiert'!D70</f>
+        <f>'Nach Mannschaften sortiert'!D73</f>
         <v>0</v>
       </c>
       <c r="E56" s="62">
-        <f>'Nach Mannschaften sortiert'!E70</f>
+        <f>'Nach Mannschaften sortiert'!E73</f>
         <v>0</v>
       </c>
       <c r="F56" s="60">
-        <f>'Nach Mannschaften sortiert'!F70</f>
+        <f>'Nach Mannschaften sortiert'!F73</f>
         <v>0</v>
       </c>
       <c r="G56" s="60">
-        <f>'Nach Mannschaften sortiert'!G70</f>
+        <f>'Nach Mannschaften sortiert'!G73</f>
         <v>0</v>
       </c>
       <c r="H56" s="60">
-        <f>'Nach Mannschaften sortiert'!H70</f>
+        <f>'Nach Mannschaften sortiert'!H73</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <f>'Nach Mannschaften sortiert'!A68</f>
+        <f>'Nach Mannschaften sortiert'!A71</f>
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <f>'Nach Mannschaften sortiert'!B68</f>
+        <f>'Nach Mannschaften sortiert'!B71</f>
         <v>3</v>
       </c>
       <c r="C57" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C68</f>
+        <f>'Nach Mannschaften sortiert'!C71</f>
         <v>U12_2</v>
       </c>
       <c r="D57" s="16">
-        <f>'Nach Mannschaften sortiert'!D68</f>
+        <f>'Nach Mannschaften sortiert'!D71</f>
         <v>0</v>
       </c>
       <c r="E57" s="38">
-        <f>'Nach Mannschaften sortiert'!E68</f>
+        <f>'Nach Mannschaften sortiert'!E71</f>
         <v>0</v>
       </c>
       <c r="F57" s="2">
-        <f>'Nach Mannschaften sortiert'!F68</f>
+        <f>'Nach Mannschaften sortiert'!F71</f>
         <v>0</v>
       </c>
       <c r="G57" s="2">
-        <f>'Nach Mannschaften sortiert'!G68</f>
+        <f>'Nach Mannschaften sortiert'!G71</f>
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <f>'Nach Mannschaften sortiert'!H68</f>
+        <f>'Nach Mannschaften sortiert'!H71</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="60">
-        <f>'Nach Mannschaften sortiert'!A15</f>
+        <f>'Nach Mannschaften sortiert'!A18</f>
         <v>10</v>
       </c>
       <c r="B58" s="60">
-        <f>'Nach Mannschaften sortiert'!B15</f>
+        <f>'Nach Mannschaften sortiert'!B18</f>
         <v>10</v>
       </c>
       <c r="C58" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C15</f>
+        <f>'Nach Mannschaften sortiert'!C18</f>
         <v>KM</v>
       </c>
       <c r="D58" s="61">
-        <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D18</f>
+        <v>46312</v>
       </c>
       <c r="E58" s="62">
-        <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="60">
-        <f>'Nach Mannschaften sortiert'!F15</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="60">
-        <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="60">
-        <f>'Nach Mannschaften sortiert'!H15</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E18</f>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F58" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!F18</f>
+        <v>Hornstein</v>
+      </c>
+      <c r="G58" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!G18</f>
+        <v>Hornstein</v>
+      </c>
+      <c r="H58" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!H18</f>
+        <v>Auswärts</v>
       </c>
     </row>
     <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -10632,137 +11286,137 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="60">
-        <f>'Nach Mannschaften sortiert'!A55</f>
+        <f>'Nach Mannschaften sortiert'!A58</f>
         <v>40</v>
       </c>
       <c r="B60" s="60">
-        <f>'Nach Mannschaften sortiert'!B55</f>
+        <f>'Nach Mannschaften sortiert'!B58</f>
         <v>7</v>
       </c>
       <c r="C60" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C55</f>
+        <f>'Nach Mannschaften sortiert'!C58</f>
         <v>U13</v>
       </c>
       <c r="D60" s="61">
-        <f>'Nach Mannschaften sortiert'!D55</f>
+        <f>'Nach Mannschaften sortiert'!D58</f>
         <v>0</v>
       </c>
       <c r="E60" s="62">
-        <f>'Nach Mannschaften sortiert'!E55</f>
+        <f>'Nach Mannschaften sortiert'!E58</f>
         <v>0</v>
       </c>
       <c r="F60" s="60">
-        <f>'Nach Mannschaften sortiert'!F55</f>
+        <f>'Nach Mannschaften sortiert'!F58</f>
         <v>0</v>
       </c>
       <c r="G60" s="60">
-        <f>'Nach Mannschaften sortiert'!G55</f>
+        <f>'Nach Mannschaften sortiert'!G58</f>
         <v>0</v>
       </c>
       <c r="H60" s="60">
-        <f>'Nach Mannschaften sortiert'!H55</f>
+        <f>'Nach Mannschaften sortiert'!H58</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <f>'Nach Mannschaften sortiert'!A71</f>
+        <f>'Nach Mannschaften sortiert'!A74</f>
         <v>60</v>
       </c>
       <c r="B61" s="2">
-        <f>'Nach Mannschaften sortiert'!B71</f>
+        <f>'Nach Mannschaften sortiert'!B74</f>
         <v>7</v>
       </c>
       <c r="C61" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C71</f>
+        <f>'Nach Mannschaften sortiert'!C74</f>
         <v>U12_2</v>
       </c>
       <c r="D61" s="16">
-        <f>'Nach Mannschaften sortiert'!D71</f>
+        <f>'Nach Mannschaften sortiert'!D74</f>
         <v>0</v>
       </c>
       <c r="E61" s="38">
-        <f>'Nach Mannschaften sortiert'!E71</f>
+        <f>'Nach Mannschaften sortiert'!E74</f>
         <v>0</v>
       </c>
       <c r="F61" s="2">
-        <f>'Nach Mannschaften sortiert'!F71</f>
+        <f>'Nach Mannschaften sortiert'!F74</f>
         <v>0</v>
       </c>
       <c r="G61" s="2">
-        <f>'Nach Mannschaften sortiert'!G71</f>
+        <f>'Nach Mannschaften sortiert'!G74</f>
         <v>0</v>
       </c>
       <c r="H61" s="2">
-        <f>'Nach Mannschaften sortiert'!H71</f>
+        <f>'Nach Mannschaften sortiert'!H74</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="57">
-        <f>'Nach Mannschaften sortiert'!A56</f>
+        <f>'Nach Mannschaften sortiert'!A59</f>
         <v>41</v>
       </c>
       <c r="B62" s="57">
-        <f>'Nach Mannschaften sortiert'!B56</f>
+        <f>'Nach Mannschaften sortiert'!B59</f>
         <v>8</v>
       </c>
       <c r="C62" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C56</f>
+        <f>'Nach Mannschaften sortiert'!C59</f>
         <v>U13</v>
       </c>
       <c r="D62" s="58">
-        <f>'Nach Mannschaften sortiert'!D56</f>
+        <f>'Nach Mannschaften sortiert'!D59</f>
         <v>0</v>
       </c>
       <c r="E62" s="59">
-        <f>'Nach Mannschaften sortiert'!E56</f>
+        <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="F62" s="57">
-        <f>'Nach Mannschaften sortiert'!F56</f>
+        <f>'Nach Mannschaften sortiert'!F59</f>
         <v>0</v>
       </c>
       <c r="G62" s="57">
-        <f>'Nach Mannschaften sortiert'!G56</f>
+        <f>'Nach Mannschaften sortiert'!G59</f>
         <v>0</v>
       </c>
       <c r="H62" s="57">
-        <f>'Nach Mannschaften sortiert'!H56</f>
+        <f>'Nach Mannschaften sortiert'!H59</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <f>'Nach Mannschaften sortiert'!A73</f>
+        <f>'Nach Mannschaften sortiert'!A76</f>
         <v>62</v>
       </c>
       <c r="B63" s="2">
-        <f>'Nach Mannschaften sortiert'!B73</f>
+        <f>'Nach Mannschaften sortiert'!B76</f>
         <v>9</v>
       </c>
       <c r="C63" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C73</f>
+        <f>'Nach Mannschaften sortiert'!C76</f>
         <v>U12_2</v>
       </c>
       <c r="D63" s="16">
-        <f>'Nach Mannschaften sortiert'!D73</f>
+        <f>'Nach Mannschaften sortiert'!D76</f>
         <v>0</v>
       </c>
       <c r="E63" s="38">
-        <f>'Nach Mannschaften sortiert'!E73</f>
+        <f>'Nach Mannschaften sortiert'!E76</f>
         <v>0</v>
       </c>
       <c r="F63" s="2">
-        <f>'Nach Mannschaften sortiert'!F73</f>
+        <f>'Nach Mannschaften sortiert'!F76</f>
         <v>0</v>
       </c>
       <c r="G63" s="2">
-        <f>'Nach Mannschaften sortiert'!G73</f>
+        <f>'Nach Mannschaften sortiert'!G76</f>
         <v>0</v>
       </c>
       <c r="H63" s="2">
-        <f>'Nach Mannschaften sortiert'!H73</f>
+        <f>'Nach Mannschaften sortiert'!H76</f>
         <v>0</v>
       </c>
     </row>
@@ -10802,15 +11456,15 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="60">
-        <f>'Nach Mannschaften sortiert'!A72</f>
+        <f>'Nach Mannschaften sortiert'!A75</f>
         <v>61</v>
       </c>
       <c r="B65" s="60">
-        <f>'Nach Mannschaften sortiert'!B72</f>
+        <f>'Nach Mannschaften sortiert'!B75</f>
         <v>8</v>
       </c>
       <c r="C65" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C72</f>
+        <f>'Nach Mannschaften sortiert'!C75</f>
         <v>U12_2</v>
       </c>
       <c r="D65" s="61">
@@ -10820,525 +11474,525 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F65" s="60">
-        <f>'Nach Mannschaften sortiert'!F72</f>
+        <f>'Nach Mannschaften sortiert'!F75</f>
         <v>0</v>
       </c>
       <c r="G65" s="60">
-        <f>'Nach Mannschaften sortiert'!G72</f>
+        <f>'Nach Mannschaften sortiert'!G75</f>
         <v>0</v>
       </c>
       <c r="H65" s="60">
-        <f>'Nach Mannschaften sortiert'!H72</f>
+        <f>'Nach Mannschaften sortiert'!H75</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <f>'Nach Mannschaften sortiert'!A75</f>
+        <f>'Nach Mannschaften sortiert'!A78</f>
         <v>65</v>
       </c>
       <c r="B66" s="2">
-        <f>'Nach Mannschaften sortiert'!B75</f>
+        <f>'Nach Mannschaften sortiert'!B78</f>
         <v>2</v>
       </c>
       <c r="C66" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C75</f>
+        <f>'Nach Mannschaften sortiert'!C78</f>
         <v>U11</v>
       </c>
       <c r="D66" s="16">
-        <f>'Nach Mannschaften sortiert'!D75</f>
+        <f>'Nach Mannschaften sortiert'!D78</f>
         <v>0</v>
       </c>
       <c r="E66" s="38">
-        <f>'Nach Mannschaften sortiert'!E75</f>
+        <f>'Nach Mannschaften sortiert'!E78</f>
         <v>0</v>
       </c>
       <c r="F66" s="2">
-        <f>'Nach Mannschaften sortiert'!F75</f>
+        <f>'Nach Mannschaften sortiert'!F78</f>
         <v>0</v>
       </c>
       <c r="G66" s="2">
-        <f>'Nach Mannschaften sortiert'!G75</f>
+        <f>'Nach Mannschaften sortiert'!G78</f>
         <v>0</v>
       </c>
       <c r="H66" s="2">
-        <f>'Nach Mannschaften sortiert'!H75</f>
+        <f>'Nach Mannschaften sortiert'!H78</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <f>'Nach Mannschaften sortiert'!A76</f>
+        <f>'Nach Mannschaften sortiert'!A79</f>
         <v>66</v>
       </c>
       <c r="B67" s="2">
-        <f>'Nach Mannschaften sortiert'!B76</f>
+        <f>'Nach Mannschaften sortiert'!B79</f>
         <v>3</v>
       </c>
       <c r="C67" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C76</f>
+        <f>'Nach Mannschaften sortiert'!C79</f>
         <v>U11</v>
       </c>
       <c r="D67" s="16">
-        <f>'Nach Mannschaften sortiert'!D76</f>
+        <f>'Nach Mannschaften sortiert'!D79</f>
         <v>0</v>
       </c>
       <c r="E67" s="38">
-        <f>'Nach Mannschaften sortiert'!E76</f>
+        <f>'Nach Mannschaften sortiert'!E79</f>
         <v>0</v>
       </c>
       <c r="F67" s="2">
-        <f>'Nach Mannschaften sortiert'!F76</f>
+        <f>'Nach Mannschaften sortiert'!F79</f>
         <v>0</v>
       </c>
       <c r="G67" s="2">
-        <f>'Nach Mannschaften sortiert'!G76</f>
+        <f>'Nach Mannschaften sortiert'!G79</f>
         <v>0</v>
       </c>
       <c r="H67" s="2">
-        <f>'Nach Mannschaften sortiert'!H76</f>
+        <f>'Nach Mannschaften sortiert'!H79</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <f>'Nach Mannschaften sortiert'!A77</f>
+        <f>'Nach Mannschaften sortiert'!A80</f>
         <v>67</v>
       </c>
       <c r="B68" s="2">
-        <f>'Nach Mannschaften sortiert'!B77</f>
+        <f>'Nach Mannschaften sortiert'!B80</f>
         <v>4</v>
       </c>
       <c r="C68" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C77</f>
+        <f>'Nach Mannschaften sortiert'!C80</f>
         <v>U11</v>
       </c>
       <c r="D68" s="16">
-        <f>'Nach Mannschaften sortiert'!D77</f>
+        <f>'Nach Mannschaften sortiert'!D80</f>
         <v>0</v>
       </c>
       <c r="E68" s="38">
-        <f>'Nach Mannschaften sortiert'!E77</f>
+        <f>'Nach Mannschaften sortiert'!E80</f>
         <v>0</v>
       </c>
       <c r="F68" s="2">
-        <f>'Nach Mannschaften sortiert'!F77</f>
+        <f>'Nach Mannschaften sortiert'!F80</f>
         <v>0</v>
       </c>
       <c r="G68" s="2">
-        <f>'Nach Mannschaften sortiert'!G77</f>
+        <f>'Nach Mannschaften sortiert'!G80</f>
         <v>0</v>
       </c>
       <c r="H68" s="2">
-        <f>'Nach Mannschaften sortiert'!H77</f>
+        <f>'Nach Mannschaften sortiert'!H80</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <f>'Nach Mannschaften sortiert'!A83</f>
+        <f>'Nach Mannschaften sortiert'!A86</f>
         <v>68</v>
       </c>
       <c r="B69" s="2">
-        <f>'Nach Mannschaften sortiert'!B83</f>
+        <f>'Nach Mannschaften sortiert'!B86</f>
         <v>10</v>
       </c>
       <c r="C69" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C83</f>
+        <f>'Nach Mannschaften sortiert'!C86</f>
         <v>U11</v>
       </c>
       <c r="D69" s="16">
-        <f>'Nach Mannschaften sortiert'!D83</f>
+        <f>'Nach Mannschaften sortiert'!D86</f>
         <v>0</v>
       </c>
       <c r="E69" s="38">
-        <f>'Nach Mannschaften sortiert'!E83</f>
+        <f>'Nach Mannschaften sortiert'!E86</f>
         <v>0</v>
       </c>
       <c r="F69" s="2">
-        <f>'Nach Mannschaften sortiert'!F83</f>
+        <f>'Nach Mannschaften sortiert'!F86</f>
         <v>0</v>
       </c>
       <c r="G69" s="2">
-        <f>'Nach Mannschaften sortiert'!G83</f>
+        <f>'Nach Mannschaften sortiert'!G86</f>
         <v>0</v>
       </c>
       <c r="H69" s="2">
-        <f>'Nach Mannschaften sortiert'!H83</f>
+        <f>'Nach Mannschaften sortiert'!H86</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="60">
-        <f>'Nach Mannschaften sortiert'!A63</f>
+        <f>'Nach Mannschaften sortiert'!A66</f>
         <v>51</v>
       </c>
       <c r="B70" s="60">
-        <f>'Nach Mannschaften sortiert'!B63</f>
+        <f>'Nach Mannschaften sortiert'!B66</f>
         <v>8</v>
       </c>
       <c r="C70" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C63</f>
+        <f>'Nach Mannschaften sortiert'!C66</f>
         <v>U12_1</v>
       </c>
       <c r="D70" s="61">
-        <f>'Nach Mannschaften sortiert'!D63</f>
+        <f>'Nach Mannschaften sortiert'!D66</f>
         <v>0</v>
       </c>
       <c r="E70" s="62">
-        <f>'Nach Mannschaften sortiert'!E63</f>
+        <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="F70" s="60">
-        <f>'Nach Mannschaften sortiert'!F63</f>
+        <f>'Nach Mannschaften sortiert'!F66</f>
         <v>0</v>
       </c>
       <c r="G70" s="60">
-        <f>'Nach Mannschaften sortiert'!G63</f>
+        <f>'Nach Mannschaften sortiert'!G66</f>
         <v>0</v>
       </c>
       <c r="H70" s="60">
-        <f>'Nach Mannschaften sortiert'!H63</f>
+        <f>'Nach Mannschaften sortiert'!H66</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <f>'Nach Mannschaften sortiert'!A85</f>
+        <f>'Nach Mannschaften sortiert'!A88</f>
         <v>70</v>
       </c>
       <c r="B71" s="2">
-        <f>'Nach Mannschaften sortiert'!B85</f>
+        <f>'Nach Mannschaften sortiert'!B88</f>
         <v>2</v>
       </c>
       <c r="C71" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C85</f>
+        <f>'Nach Mannschaften sortiert'!C88</f>
         <v>U10</v>
       </c>
       <c r="D71" s="16">
-        <f>'Nach Mannschaften sortiert'!D85</f>
+        <f>'Nach Mannschaften sortiert'!D88</f>
         <v>0</v>
       </c>
       <c r="E71" s="38">
-        <f>'Nach Mannschaften sortiert'!E85</f>
+        <f>'Nach Mannschaften sortiert'!E88</f>
         <v>0</v>
       </c>
       <c r="F71" s="2">
-        <f>'Nach Mannschaften sortiert'!F85</f>
+        <f>'Nach Mannschaften sortiert'!F88</f>
         <v>0</v>
       </c>
       <c r="G71" s="2">
-        <f>'Nach Mannschaften sortiert'!G85</f>
+        <f>'Nach Mannschaften sortiert'!G88</f>
         <v>0</v>
       </c>
       <c r="H71" s="2">
-        <f>'Nach Mannschaften sortiert'!H85</f>
+        <f>'Nach Mannschaften sortiert'!H88</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <f>'Nach Mannschaften sortiert'!A86</f>
+        <f>'Nach Mannschaften sortiert'!A89</f>
         <v>71</v>
       </c>
       <c r="B72" s="2">
-        <f>'Nach Mannschaften sortiert'!B86</f>
+        <f>'Nach Mannschaften sortiert'!B89</f>
         <v>3</v>
       </c>
       <c r="C72" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C86</f>
+        <f>'Nach Mannschaften sortiert'!C89</f>
         <v>U10</v>
       </c>
       <c r="D72" s="16">
-        <f>'Nach Mannschaften sortiert'!D86</f>
+        <f>'Nach Mannschaften sortiert'!D89</f>
         <v>0</v>
       </c>
       <c r="E72" s="38">
-        <f>'Nach Mannschaften sortiert'!E86</f>
+        <f>'Nach Mannschaften sortiert'!E89</f>
         <v>0</v>
       </c>
       <c r="F72" s="2">
-        <f>'Nach Mannschaften sortiert'!F86</f>
+        <f>'Nach Mannschaften sortiert'!F89</f>
         <v>0</v>
       </c>
       <c r="G72" s="2">
-        <f>'Nach Mannschaften sortiert'!G86</f>
+        <f>'Nach Mannschaften sortiert'!G89</f>
         <v>0</v>
       </c>
       <c r="H72" s="2">
-        <f>'Nach Mannschaften sortiert'!H86</f>
+        <f>'Nach Mannschaften sortiert'!H89</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <f>'Nach Mannschaften sortiert'!A92</f>
+        <f>'Nach Mannschaften sortiert'!A95</f>
         <v>72</v>
       </c>
       <c r="B73" s="2">
-        <f>'Nach Mannschaften sortiert'!B92</f>
+        <f>'Nach Mannschaften sortiert'!B95</f>
         <v>9</v>
       </c>
       <c r="C73" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C92</f>
+        <f>'Nach Mannschaften sortiert'!C95</f>
         <v>U10</v>
       </c>
       <c r="D73" s="16">
-        <f>'Nach Mannschaften sortiert'!D92</f>
+        <f>'Nach Mannschaften sortiert'!D95</f>
         <v>0</v>
       </c>
       <c r="E73" s="38">
-        <f>'Nach Mannschaften sortiert'!E92</f>
+        <f>'Nach Mannschaften sortiert'!E95</f>
         <v>0</v>
       </c>
       <c r="F73" s="2">
-        <f>'Nach Mannschaften sortiert'!F92</f>
+        <f>'Nach Mannschaften sortiert'!F95</f>
         <v>0</v>
       </c>
       <c r="G73" s="2">
-        <f>'Nach Mannschaften sortiert'!G92</f>
+        <f>'Nach Mannschaften sortiert'!G95</f>
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <f>'Nach Mannschaften sortiert'!H92</f>
+        <f>'Nach Mannschaften sortiert'!H95</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <f>'Nach Mannschaften sortiert'!A93</f>
+        <f>'Nach Mannschaften sortiert'!A96</f>
         <v>73</v>
       </c>
       <c r="B74" s="2">
-        <f>'Nach Mannschaften sortiert'!B93</f>
+        <f>'Nach Mannschaften sortiert'!B96</f>
         <v>10</v>
       </c>
       <c r="C74" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C93</f>
+        <f>'Nach Mannschaften sortiert'!C96</f>
         <v>U10</v>
       </c>
       <c r="D74" s="16">
-        <f>'Nach Mannschaften sortiert'!D93</f>
+        <f>'Nach Mannschaften sortiert'!D96</f>
         <v>0</v>
       </c>
       <c r="E74" s="38">
-        <f>'Nach Mannschaften sortiert'!E93</f>
+        <f>'Nach Mannschaften sortiert'!E96</f>
         <v>0</v>
       </c>
       <c r="F74" s="2">
-        <f>'Nach Mannschaften sortiert'!F93</f>
+        <f>'Nach Mannschaften sortiert'!F96</f>
         <v>0</v>
       </c>
       <c r="G74" s="2">
-        <f>'Nach Mannschaften sortiert'!G93</f>
+        <f>'Nach Mannschaften sortiert'!G96</f>
         <v>0</v>
       </c>
       <c r="H74" s="2">
-        <f>'Nach Mannschaften sortiert'!H93</f>
+        <f>'Nach Mannschaften sortiert'!H96</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="60">
-        <f>'Nach Mannschaften sortiert'!A18</f>
+        <f>'Nach Mannschaften sortiert'!A21</f>
         <v>13</v>
       </c>
       <c r="B75" s="60">
-        <f>'Nach Mannschaften sortiert'!B18</f>
+        <f>'Nach Mannschaften sortiert'!B21</f>
         <v>13</v>
       </c>
       <c r="C75" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C18</f>
+        <f>'Nach Mannschaften sortiert'!C21</f>
         <v>KM</v>
       </c>
       <c r="D75" s="61">
-        <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!D21</f>
+        <v>46333</v>
       </c>
       <c r="E75" s="62">
-        <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0</v>
-      </c>
-      <c r="F75" s="60">
-        <f>'Nach Mannschaften sortiert'!F18</f>
-        <v>0</v>
-      </c>
-      <c r="G75" s="60">
-        <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="60">
-        <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>0</v>
+        <f>'Nach Mannschaften sortiert'!E21</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F75" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!F21</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G75" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!G21</f>
+        <v>Andau</v>
+      </c>
+      <c r="H75" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!H21</f>
+        <v>Heim</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <f>'Nach Mannschaften sortiert'!A95</f>
+        <f>'Nach Mannschaften sortiert'!A98</f>
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <f>'Nach Mannschaften sortiert'!B95</f>
+        <f>'Nach Mannschaften sortiert'!B98</f>
         <v>2</v>
       </c>
       <c r="C76" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C95</f>
+        <f>'Nach Mannschaften sortiert'!C98</f>
         <v>U9</v>
       </c>
       <c r="D76" s="16">
-        <f>'Nach Mannschaften sortiert'!D95</f>
+        <f>'Nach Mannschaften sortiert'!D98</f>
         <v>0</v>
       </c>
       <c r="E76" s="38">
-        <f>'Nach Mannschaften sortiert'!E95</f>
+        <f>'Nach Mannschaften sortiert'!E98</f>
         <v>0</v>
       </c>
       <c r="F76" s="2">
-        <f>'Nach Mannschaften sortiert'!F95</f>
+        <f>'Nach Mannschaften sortiert'!F98</f>
         <v>0</v>
       </c>
       <c r="G76" s="2">
-        <f>'Nach Mannschaften sortiert'!G95</f>
+        <f>'Nach Mannschaften sortiert'!G98</f>
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <f>'Nach Mannschaften sortiert'!H95</f>
+        <f>'Nach Mannschaften sortiert'!H98</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <f>'Nach Mannschaften sortiert'!A101</f>
+        <f>'Nach Mannschaften sortiert'!A104</f>
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <f>'Nach Mannschaften sortiert'!B101</f>
+        <f>'Nach Mannschaften sortiert'!B104</f>
         <v>8</v>
       </c>
       <c r="C77" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C101</f>
+        <f>'Nach Mannschaften sortiert'!C104</f>
         <v>U9</v>
       </c>
       <c r="D77" s="16">
-        <f>'Nach Mannschaften sortiert'!D101</f>
+        <f>'Nach Mannschaften sortiert'!D104</f>
         <v>0</v>
       </c>
       <c r="E77" s="38">
-        <f>'Nach Mannschaften sortiert'!E101</f>
+        <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0</v>
       </c>
       <c r="F77" s="2">
-        <f>'Nach Mannschaften sortiert'!F101</f>
+        <f>'Nach Mannschaften sortiert'!F104</f>
         <v>0</v>
       </c>
       <c r="G77" s="2">
-        <f>'Nach Mannschaften sortiert'!G101</f>
+        <f>'Nach Mannschaften sortiert'!G104</f>
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <f>'Nach Mannschaften sortiert'!H101</f>
+        <f>'Nach Mannschaften sortiert'!H104</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <f>'Nach Mannschaften sortiert'!A102</f>
+        <f>'Nach Mannschaften sortiert'!A105</f>
         <v>77</v>
       </c>
       <c r="B78" s="2">
-        <f>'Nach Mannschaften sortiert'!B102</f>
+        <f>'Nach Mannschaften sortiert'!B105</f>
         <v>9</v>
       </c>
       <c r="C78" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C102</f>
+        <f>'Nach Mannschaften sortiert'!C105</f>
         <v>U9</v>
       </c>
       <c r="D78" s="16">
-        <f>'Nach Mannschaften sortiert'!D102</f>
+        <f>'Nach Mannschaften sortiert'!D105</f>
         <v>0</v>
       </c>
       <c r="E78" s="38">
-        <f>'Nach Mannschaften sortiert'!E102</f>
+        <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="F78" s="2">
-        <f>'Nach Mannschaften sortiert'!F102</f>
+        <f>'Nach Mannschaften sortiert'!F105</f>
         <v>0</v>
       </c>
       <c r="G78" s="2">
-        <f>'Nach Mannschaften sortiert'!G102</f>
+        <f>'Nach Mannschaften sortiert'!G105</f>
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <f>'Nach Mannschaften sortiert'!H102</f>
+        <f>'Nach Mannschaften sortiert'!H105</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <f>'Nach Mannschaften sortiert'!A103</f>
+        <f>'Nach Mannschaften sortiert'!A106</f>
         <v>78</v>
       </c>
       <c r="B79" s="2">
-        <f>'Nach Mannschaften sortiert'!B103</f>
+        <f>'Nach Mannschaften sortiert'!B106</f>
         <v>10</v>
       </c>
       <c r="C79" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C103</f>
+        <f>'Nach Mannschaften sortiert'!C106</f>
         <v>U9</v>
       </c>
       <c r="D79" s="16">
-        <f>'Nach Mannschaften sortiert'!D103</f>
+        <f>'Nach Mannschaften sortiert'!D106</f>
         <v>0</v>
       </c>
       <c r="E79" s="38">
-        <f>'Nach Mannschaften sortiert'!E103</f>
+        <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="F79" s="2">
-        <f>'Nach Mannschaften sortiert'!F103</f>
+        <f>'Nach Mannschaften sortiert'!F106</f>
         <v>0</v>
       </c>
       <c r="G79" s="2">
-        <f>'Nach Mannschaften sortiert'!G103</f>
+        <f>'Nach Mannschaften sortiert'!G106</f>
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <f>'Nach Mannschaften sortiert'!H103</f>
+        <f>'Nach Mannschaften sortiert'!H106</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="60">
-        <f>'Nach Mannschaften sortiert'!A65</f>
+        <f>'Nach Mannschaften sortiert'!A68</f>
         <v>53</v>
       </c>
       <c r="B80" s="60">
-        <f>'Nach Mannschaften sortiert'!B65</f>
+        <f>'Nach Mannschaften sortiert'!B68</f>
         <v>10</v>
       </c>
       <c r="C80" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C65</f>
+        <f>'Nach Mannschaften sortiert'!C68</f>
         <v>U12_1</v>
       </c>
       <c r="D80" s="61">
-        <f>'Nach Mannschaften sortiert'!D65</f>
+        <f>'Nach Mannschaften sortiert'!D68</f>
         <v>0</v>
       </c>
       <c r="E80" s="62">
-        <f>'Nach Mannschaften sortiert'!E65</f>
+        <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="F80" s="60">
-        <f>'Nach Mannschaften sortiert'!F65</f>
+        <f>'Nach Mannschaften sortiert'!F68</f>
         <v>0</v>
       </c>
       <c r="G80" s="60">
-        <f>'Nach Mannschaften sortiert'!G65</f>
+        <f>'Nach Mannschaften sortiert'!G68</f>
         <v>0</v>
       </c>
       <c r="H80" s="60">
-        <f>'Nach Mannschaften sortiert'!H65</f>
+        <f>'Nach Mannschaften sortiert'!H68</f>
         <v>0</v>
       </c>
     </row>
@@ -11378,35 +12032,35 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="60">
-        <f>'Nach Mannschaften sortiert'!A41</f>
+        <f>'Nach Mannschaften sortiert'!A44</f>
         <v>23</v>
       </c>
       <c r="B82" s="60">
-        <f>'Nach Mannschaften sortiert'!B41</f>
+        <f>'Nach Mannschaften sortiert'!B44</f>
         <v>10</v>
       </c>
       <c r="C82" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C41</f>
+        <f>'Nach Mannschaften sortiert'!C44</f>
         <v>U16</v>
       </c>
       <c r="D82" s="61">
-        <f>'Nach Mannschaften sortiert'!D41</f>
+        <f>'Nach Mannschaften sortiert'!D44</f>
         <v>0</v>
       </c>
       <c r="E82" s="62">
-        <f>'Nach Mannschaften sortiert'!E41</f>
+        <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="F82" s="60">
-        <f>'Nach Mannschaften sortiert'!F41</f>
+        <f>'Nach Mannschaften sortiert'!F44</f>
         <v>0</v>
       </c>
       <c r="G82" s="60">
-        <f>'Nach Mannschaften sortiert'!G41</f>
+        <f>'Nach Mannschaften sortiert'!G44</f>
         <v>0</v>
       </c>
       <c r="H82" s="60">
-        <f>'Nach Mannschaften sortiert'!H41</f>
+        <f>'Nach Mannschaften sortiert'!H44</f>
         <v>0</v>
       </c>
     </row>
@@ -11446,35 +12100,35 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <f>'Nach Mannschaften sortiert'!A122</f>
+        <f>'Nach Mannschaften sortiert'!A128</f>
         <v>83</v>
       </c>
       <c r="B84" s="2">
-        <f>'Nach Mannschaften sortiert'!B122</f>
+        <f>'Nach Mannschaften sortiert'!B128</f>
         <v>2</v>
       </c>
       <c r="C84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C122</f>
+        <f>'Nach Mannschaften sortiert'!C128</f>
         <v>GGG</v>
       </c>
       <c r="D84" s="16">
-        <f>'Nach Mannschaften sortiert'!D122</f>
+        <f>'Nach Mannschaften sortiert'!D128</f>
         <v>46256</v>
       </c>
       <c r="E84" s="38">
-        <f>'Nach Mannschaften sortiert'!E122</f>
+        <f>'Nach Mannschaften sortiert'!E128</f>
         <v>0.375</v>
       </c>
       <c r="F84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F122</f>
+        <f>'Nach Mannschaften sortiert'!F128</f>
         <v>Neufeld</v>
       </c>
       <c r="G84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G122</f>
+        <f>'Nach Mannschaften sortiert'!G128</f>
         <v>viele Gegner</v>
       </c>
       <c r="H84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H122</f>
+        <f>'Nach Mannschaften sortiert'!H128</f>
         <v>Heim</v>
       </c>
     </row>
@@ -11634,16 +12288,16 @@
       </c>
       <c r="B3" s="72">
         <f>Heimspiele!D4</f>
-        <v>0</v>
+        <v>46263</v>
       </c>
       <c r="C3" s="72"/>
-      <c r="D3">
+      <c r="D3" t="str">
         <f>Heimspiele!F4</f>
-        <v>0</v>
-      </c>
-      <c r="E3">
+        <v>Neufeld</v>
+      </c>
+      <c r="E3" t="str">
         <f>Heimspiele!G4</f>
-        <v>0</v>
+        <v>Tadten</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -11716,16 +12370,16 @@
       </c>
       <c r="B5" s="72">
         <f>Heimspiele!D6</f>
-        <v>0</v>
+        <v>46277</v>
       </c>
       <c r="C5" s="72"/>
-      <c r="D5">
+      <c r="D5" t="str">
         <f>Heimspiele!F6</f>
-        <v>0</v>
-      </c>
-      <c r="E5">
+        <v>Neufeld</v>
+      </c>
+      <c r="E5" t="str">
         <f>Heimspiele!G6</f>
-        <v>0</v>
+        <v>Winden</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -11798,16 +12452,16 @@
       </c>
       <c r="B7" s="72">
         <f>Heimspiele!D8</f>
-        <v>0</v>
+        <v>46291</v>
       </c>
       <c r="C7" s="72"/>
-      <c r="D7">
+      <c r="D7" t="str">
         <f>Heimspiele!F8</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
+        <v>Neufeld</v>
+      </c>
+      <c r="E7" t="str">
         <f>Heimspiele!G8</f>
-        <v>0</v>
+        <v>Wallern</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -11880,16 +12534,16 @@
       </c>
       <c r="B9" s="72">
         <f>Heimspiele!D10</f>
-        <v>0</v>
+        <v>46305</v>
       </c>
       <c r="C9" s="72"/>
-      <c r="D9">
+      <c r="D9" t="str">
         <f>Heimspiele!F10</f>
-        <v>0</v>
-      </c>
-      <c r="E9">
+        <v>Neufeld</v>
+      </c>
+      <c r="E9" t="str">
         <f>Heimspiele!G10</f>
-        <v>0</v>
+        <v>Wimpassing</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
@@ -11922,19 +12576,19 @@
       </c>
       <c r="B10" s="81">
         <f>Heimspiele!D3</f>
-        <v>0</v>
+        <v>46256</v>
       </c>
       <c r="C10" s="82">
         <f>Heimspiele!E3</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="80">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D10" s="80" t="str">
         <f>Heimspiele!F3</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="80">
+        <v>Deutsch Jahrndorf</v>
+      </c>
+      <c r="E10" s="80" t="str">
         <f>Heimspiele!G3</f>
-        <v>0</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="F10" s="80" t="s">
         <v>17</v>
@@ -11967,16 +12621,16 @@
       </c>
       <c r="B11" s="72">
         <f>Heimspiele!D12</f>
-        <v>0</v>
+        <v>46319</v>
       </c>
       <c r="C11" s="72"/>
-      <c r="D11">
+      <c r="D11" t="str">
         <f>Heimspiele!F12</f>
-        <v>0</v>
-      </c>
-      <c r="E11">
+        <v>Neufeld</v>
+      </c>
+      <c r="E11" t="str">
         <f>Heimspiele!G12</f>
-        <v>0</v>
+        <v>Gols</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
@@ -12009,16 +12663,16 @@
       </c>
       <c r="B12" s="72">
         <f>Heimspiele!D13</f>
-        <v>0</v>
+        <v>46326</v>
       </c>
       <c r="C12" s="72"/>
-      <c r="D12">
+      <c r="D12" t="str">
         <f>Heimspiele!F13</f>
-        <v>0</v>
-      </c>
-      <c r="E12">
+        <v>Illmitz</v>
+      </c>
+      <c r="E12" t="str">
         <f>Heimspiele!G13</f>
-        <v>0</v>
+        <v>Illmitz</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
@@ -12942,19 +13596,19 @@
       </c>
       <c r="B34" s="81">
         <f>Heimspiele!D18</f>
-        <v>0</v>
+        <v>46270</v>
       </c>
       <c r="C34" s="82">
         <f>Heimspiele!E18</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="80">
+        <v>0.6875</v>
+      </c>
+      <c r="D34" s="80" t="str">
         <f>Heimspiele!F18</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="80">
+        <v>Mönchhof</v>
+      </c>
+      <c r="E34" s="80" t="str">
         <f>Heimspiele!G18</f>
-        <v>0</v>
+        <v>Mönchhof</v>
       </c>
       <c r="F34" s="80" t="s">
         <v>17</v>
@@ -13506,19 +14160,19 @@
       </c>
       <c r="B47" s="81">
         <f>Heimspiele!D41</f>
-        <v>0</v>
+        <v>46284</v>
       </c>
       <c r="C47" s="82">
         <f>Heimspiele!E41</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="80">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D47" s="80" t="str">
         <f>Heimspiele!F41</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="80">
+        <v>Gattendorf</v>
+      </c>
+      <c r="E47" s="80" t="str">
         <f>Heimspiele!G41</f>
-        <v>0</v>
+        <v>Gattendorf</v>
       </c>
       <c r="F47" s="80" t="s">
         <v>17</v>
@@ -14025,19 +14679,19 @@
       </c>
       <c r="B59" s="81">
         <f>Heimspiele!D52</f>
-        <v>0</v>
+        <v>46297</v>
       </c>
       <c r="C59" s="82">
         <f>Heimspiele!E52</f>
-        <v>0</v>
-      </c>
-      <c r="D59" s="80">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D59" s="80" t="str">
         <f>Heimspiele!F52</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="80">
+        <v>Siegendorf</v>
+      </c>
+      <c r="E59" s="80" t="str">
         <f>Heimspiele!G52</f>
-        <v>0</v>
+        <v>Siegendorf</v>
       </c>
       <c r="F59" s="80" t="s">
         <v>17</v>
@@ -14454,19 +15108,19 @@
       </c>
       <c r="B69" s="81">
         <f>Heimspiele!D58</f>
-        <v>0</v>
+        <v>46312</v>
       </c>
       <c r="C69" s="82">
         <f>Heimspiele!E58</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="80">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D69" s="80" t="str">
         <f>Heimspiele!F58</f>
-        <v>0</v>
-      </c>
-      <c r="E69" s="80">
+        <v>Hornstein</v>
+      </c>
+      <c r="E69" s="80" t="str">
         <f>Heimspiele!G58</f>
-        <v>0</v>
+        <v>Hornstein</v>
       </c>
       <c r="F69" s="80" t="s">
         <v>17</v>
@@ -15015,19 +15669,19 @@
       </c>
       <c r="B82" s="81">
         <f>Heimspiele!D75</f>
-        <v>0</v>
+        <v>46333</v>
       </c>
       <c r="C82" s="82">
         <f>Heimspiele!E75</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="80">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D82" s="80" t="str">
         <f>Heimspiele!F75</f>
-        <v>0</v>
-      </c>
-      <c r="E82" s="80">
+        <v>Neufeld</v>
+      </c>
+      <c r="E82" s="80" t="str">
         <f>Heimspiele!G75</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="F82" s="80" t="s">
         <v>17</v>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77969F03-6AA4-4E79-BCBF-E9C146641129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF514FF-0229-47FE-8DFB-080876E0302A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4368,7 +4368,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="D9" s="39">
-        <f t="shared" ref="D3:D69" si="1">IF(I9 = "KM",C9+"1:45",IF(I9="U23",C9+"1:45",IF(I9 = "U16",C9+"1:45",IF(I9 = "U15",C9+"1:30",IF(I9 = "U14",C9+"1:30",IF(I9 = "U13",C9+"1:35",IF(I9 = "U12",C9+"1:10",IF(I9 = "U11",C9+"1:10",IF(I9 = "U10",C9+"1:03",C9+"3:00")))))))))</f>
+        <f t="shared" ref="D9:D69" si="1">IF(I9 = "KM",C9+"1:45",IF(I9="U23",C9+"1:45",IF(I9 = "U16",C9+"1:45",IF(I9 = "U15",C9+"1:30",IF(I9 = "U14",C9+"1:30",IF(I9 = "U13",C9+"1:35",IF(I9 = "U12",C9+"1:10",IF(I9 = "U11",C9+"1:10",IF(I9 = "U10",C9+"1:03",C9+"3:00")))))))))</f>
         <v>0.80208333333333326</v>
       </c>
       <c r="E9" s="39" t="str">
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="39">
-        <f t="shared" ref="D112:D119" si="3">IF(I112 = "KM",C112+"1:45",IF(I112="U23",C112+"1:45",IF(I112 = "U16",C112+"1:45",IF(I112 = "U15",C112+"1:30",IF(I112 = "U14",C112+"1:30",IF(I112 = "U13",C112+"1:35",IF(I112 = "U12",C112+"1:10",IF(I112 = "U11",C112+"1:10",IF(I112 = "U10",C112+"1:03",C112+"3:00")))))))))</f>
+        <f t="shared" ref="D112:D116" si="3">IF(I112 = "KM",C112+"1:45",IF(I112="U23",C112+"1:45",IF(I112 = "U16",C112+"1:45",IF(I112 = "U15",C112+"1:30",IF(I112 = "U14",C112+"1:30",IF(I112 = "U13",C112+"1:35",IF(I112 = "U12",C112+"1:10",IF(I112 = "U11",C112+"1:10",IF(I112 = "U10",C112+"1:03",C112+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E112" s="39" t="str">

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F4B0E0-21F3-4770-AB8A-F3979B272611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADBAE9D-CFCE-45C5-9ECC-E489754D8D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="163">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -522,6 +522,18 @@
   </si>
   <si>
     <t>U12_2</t>
+  </si>
+  <si>
+    <t>Pöttsching</t>
+  </si>
+  <si>
+    <t>Freundschaftsspiel</t>
+  </si>
+  <si>
+    <t>BFV-Cup</t>
+  </si>
+  <si>
+    <t>BFV-Cupspiel</t>
   </si>
 </sst>
 </file>
@@ -1300,6 +1312,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1327,28 +1361,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1581,7 +1593,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1633,7 +1645,7 @@
       <c r="D2" s="11">
         <v>46199</v>
       </c>
-      <c r="E2" s="131">
+      <c r="E2" s="114">
         <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -1660,7 +1672,7 @@
       <c r="D3" s="11">
         <v>46199</v>
       </c>
-      <c r="E3" s="131">
+      <c r="E3" s="114">
         <v>0.75</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -1675,7 +1687,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <f t="shared" ref="A4:A65" si="0">A3+1</f>
+        <f t="shared" ref="A4:A66" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="4">
@@ -1687,7 +1699,7 @@
       <c r="D4" s="11">
         <v>46213</v>
       </c>
-      <c r="E4" s="131">
+      <c r="E4" s="114">
         <v>0.79166666666666663</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -1714,7 +1726,7 @@
       <c r="D5" s="11">
         <v>46220</v>
       </c>
-      <c r="E5" s="131">
+      <c r="E5" s="114">
         <v>0.79166666666666663</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1741,7 +1753,7 @@
       <c r="D6" s="11">
         <v>46235</v>
       </c>
-      <c r="E6" s="131">
+      <c r="E6" s="114">
         <v>0.72916666666666663</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1768,7 +1780,7 @@
       <c r="D7" s="11">
         <v>46241</v>
       </c>
-      <c r="E7" s="131">
+      <c r="E7" s="114">
         <v>0.79166666666666663</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -1795,7 +1807,7 @@
       <c r="D8" s="11">
         <v>46243</v>
       </c>
-      <c r="E8" s="131">
+      <c r="E8" s="114">
         <v>0.45833333333333331</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -1809,54 +1821,50 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="4">
+        <v>0</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="12">
-        <v>46249</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="D9" s="11">
+        <v>46217</v>
+      </c>
+      <c r="E9" s="114">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>A8+1</f>
+        <v>8</v>
       </c>
       <c r="B10" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="12">
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="E10" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>10</v>
@@ -1865,349 +1873,349 @@
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="12">
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="E11" s="5">
         <v>0.70833333333333337</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="12">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E12" s="5">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="12">
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="E13" s="5">
         <v>0.6875</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D14" s="12">
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="E14" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="12">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E15" s="5">
         <v>0.66666666666666663</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="12">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="E16" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="12">
-        <v>46305</v>
+        <v>46297</v>
       </c>
       <c r="E17" s="5">
-        <v>0.64583333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="12">
-        <v>46312</v>
+        <v>46305</v>
       </c>
       <c r="E18" s="5">
         <v>0.64583333333333337</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="12">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="E19" s="5">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="12">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E20" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="12">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E21" s="5">
         <v>0.58333333333333337</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D22" s="12">
-        <v>46249</v>
+        <v>46333</v>
       </c>
       <c r="E22" s="5">
-        <v>0.64583333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D23" s="12">
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="E23" s="5">
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>10</v>
@@ -2216,332 +2224,340 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D24" s="12">
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="E24" s="5">
         <v>0.625</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D25" s="12">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E25" s="5">
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D26" s="12">
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="E26" s="5">
         <v>0.60416666666666663</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D27" s="12">
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="E27" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D28" s="12">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E28" s="5">
         <v>0.58333333333333337</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="12">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="E29" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="12">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="E30" s="5">
-        <v>0.5625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D31" s="12">
-        <v>46312</v>
+        <v>46305</v>
       </c>
       <c r="E31" s="5">
         <v>0.5625</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="12">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="E32" s="5">
-        <v>0.54166666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D33" s="12">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E33" s="5">
-        <v>0.5</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D34" s="12">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E34" s="5">
         <v>0.5</v>
       </c>
       <c r="F34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B35" s="6">
+        <v>13</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="12">
+        <v>46333</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G35" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="26">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B35" s="26">
-        <v>1</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="33">
-        <v>46023</v>
-      </c>
-      <c r="E35" s="27"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="26">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D36" s="33">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="26"/>
@@ -2551,16 +2567,16 @@
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D37" s="33">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="26"/>
@@ -2570,16 +2586,16 @@
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="26">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D38" s="33">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="26"/>
@@ -2589,16 +2605,16 @@
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="26">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D39" s="33">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="26"/>
@@ -2608,16 +2624,16 @@
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="26">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D40" s="33">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="26"/>
@@ -2627,16 +2643,16 @@
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="26">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D41" s="33">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="E41" s="27"/>
       <c r="F41" s="26"/>
@@ -2646,16 +2662,16 @@
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="26">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D42" s="33">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="E42" s="27"/>
       <c r="F42" s="26"/>
@@ -2665,16 +2681,16 @@
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="26">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D43" s="33">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="E43" s="27"/>
       <c r="F43" s="26"/>
@@ -2684,76 +2700,74 @@
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="26">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D44" s="33">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="E44" s="27"/>
       <c r="F44" s="26"/>
       <c r="G44" s="26"/>
       <c r="H44" s="26"/>
     </row>
-    <row r="45" spans="1:10" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="23">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="26">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B45" s="26">
+        <v>10</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="33">
+        <v>46032</v>
+      </c>
+      <c r="E45" s="27"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+    </row>
+    <row r="46" spans="1:10" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="23">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B46" s="17">
         <v>1</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D45" s="18">
-        <v>46033</v>
-      </c>
-      <c r="E45" s="19"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="21"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="23">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B46" s="17">
-        <v>2</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D46" s="18">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="E46" s="19"/>
       <c r="F46" s="17"/>
       <c r="G46" s="17"/>
       <c r="H46" s="17"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="22"/>
+      <c r="I46" s="21"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="23">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D47" s="18">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="E47" s="19"/>
       <c r="F47" s="17"/>
@@ -2765,16 +2779,16 @@
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="23">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="18">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E48" s="19"/>
       <c r="F48" s="17"/>
@@ -2786,16 +2800,16 @@
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="23">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D49" s="18">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="E49" s="19"/>
       <c r="F49" s="17"/>
@@ -2807,16 +2821,16 @@
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="23">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D50" s="18">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="E50" s="19"/>
       <c r="F50" s="17"/>
@@ -2828,16 +2842,16 @@
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="23">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D51" s="18">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="E51" s="19"/>
       <c r="F51" s="17"/>
@@ -2849,16 +2863,16 @@
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="23">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D52" s="18">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="E52" s="19"/>
       <c r="F52" s="17"/>
@@ -2870,16 +2884,16 @@
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="23">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D53" s="18">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="E53" s="19"/>
       <c r="F53" s="17"/>
@@ -2891,16 +2905,16 @@
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="23">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="18">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="E54" s="19"/>
       <c r="F54" s="17"/>
@@ -2909,38 +2923,40 @@
       <c r="I54" s="20"/>
       <c r="J54" s="22"/>
     </row>
-    <row r="55" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="8">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="23">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B55" s="17">
+        <v>10</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" s="18">
+        <v>46042</v>
+      </c>
+      <c r="E55" s="19"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="22"/>
+    </row>
+    <row r="56" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B56" s="8">
         <v>1</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D55" s="28">
-        <v>46043</v>
-      </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="8">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="B56" s="8">
-        <v>2</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D56" s="28">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="8"/>
@@ -2950,16 +2966,16 @@
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D57" s="28">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="E57" s="9"/>
       <c r="F57" s="8"/>
@@ -2969,16 +2985,16 @@
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D58" s="28">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="E58" s="9"/>
       <c r="F58" s="8"/>
@@ -2988,16 +3004,16 @@
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D59" s="28">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="E59" s="9"/>
       <c r="F59" s="8"/>
@@ -3007,16 +3023,16 @@
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D60" s="28">
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="E60" s="9"/>
       <c r="F60" s="8"/>
@@ -3026,16 +3042,16 @@
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D61" s="28">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="E61" s="9"/>
       <c r="F61" s="8"/>
@@ -3045,16 +3061,16 @@
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D62" s="28">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="E62" s="9"/>
       <c r="F62" s="8"/>
@@ -3064,16 +3080,16 @@
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D63" s="28">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="E63" s="9"/>
       <c r="F63" s="8"/>
@@ -3083,16 +3099,16 @@
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D64" s="28">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="E64" s="9"/>
       <c r="F64" s="8"/>
@@ -3100,227 +3116,227 @@
       <c r="H64" s="8"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="128">
+      <c r="A65" s="8">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B65" s="8">
+        <v>10</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D65" s="28">
+        <v>46052</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="111">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B65" s="128">
+      <c r="B66" s="111">
         <v>1</v>
       </c>
-      <c r="C65" s="128" t="s">
+      <c r="C66" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D65" s="129">
+      <c r="D66" s="112">
         <v>46053</v>
       </c>
-      <c r="E65" s="130"/>
-      <c r="F65" s="128"/>
-      <c r="G65" s="128"/>
-      <c r="H65" s="128"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="128">
-        <f t="shared" ref="A66:A121" si="1">A65+1</f>
+      <c r="E66" s="113"/>
+      <c r="F66" s="111"/>
+      <c r="G66" s="111"/>
+      <c r="H66" s="111"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="111">
+        <f t="shared" ref="A67:A122" si="1">A66+1</f>
         <v>65</v>
       </c>
-      <c r="B66" s="128">
+      <c r="B67" s="111">
         <v>2</v>
       </c>
-      <c r="C66" s="128" t="s">
+      <c r="C67" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D66" s="129">
+      <c r="D67" s="112">
         <v>46054</v>
       </c>
-      <c r="E66" s="130"/>
-      <c r="F66" s="128"/>
-      <c r="G66" s="128"/>
-      <c r="H66" s="128"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="128">
+      <c r="E67" s="113"/>
+      <c r="F67" s="111"/>
+      <c r="G67" s="111"/>
+      <c r="H67" s="111"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="111">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="B67" s="128">
+      <c r="B68" s="111">
         <v>3</v>
       </c>
-      <c r="C67" s="128" t="s">
+      <c r="C68" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D67" s="129">
+      <c r="D68" s="112">
         <v>46055</v>
       </c>
-      <c r="E67" s="130"/>
-      <c r="F67" s="128"/>
-      <c r="G67" s="128"/>
-      <c r="H67" s="128"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="128">
+      <c r="E68" s="113"/>
+      <c r="F68" s="111"/>
+      <c r="G68" s="111"/>
+      <c r="H68" s="111"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="111">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="B68" s="128">
+      <c r="B69" s="111">
         <v>4</v>
       </c>
-      <c r="C68" s="128" t="s">
+      <c r="C69" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D68" s="129">
+      <c r="D69" s="112">
         <v>46056</v>
       </c>
-      <c r="E68" s="130"/>
-      <c r="F68" s="128"/>
-      <c r="G68" s="128"/>
-      <c r="H68" s="128"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="128">
+      <c r="E69" s="113"/>
+      <c r="F69" s="111"/>
+      <c r="G69" s="111"/>
+      <c r="H69" s="111"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="111">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="B69" s="128">
+      <c r="B70" s="111">
         <v>5</v>
       </c>
-      <c r="C69" s="128" t="s">
+      <c r="C70" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D69" s="129">
+      <c r="D70" s="112">
         <v>46057</v>
       </c>
-      <c r="E69" s="130"/>
-      <c r="F69" s="128"/>
-      <c r="G69" s="128"/>
-      <c r="H69" s="128"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="128">
+      <c r="E70" s="113"/>
+      <c r="F70" s="111"/>
+      <c r="G70" s="111"/>
+      <c r="H70" s="111"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="111">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B70" s="128">
+      <c r="B71" s="111">
         <v>6</v>
       </c>
-      <c r="C70" s="128" t="s">
+      <c r="C71" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D70" s="129">
+      <c r="D71" s="112">
         <v>46058</v>
       </c>
-      <c r="E70" s="130"/>
-      <c r="F70" s="128"/>
-      <c r="G70" s="128"/>
-      <c r="H70" s="128"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="128">
+      <c r="E71" s="113"/>
+      <c r="F71" s="111"/>
+      <c r="G71" s="111"/>
+      <c r="H71" s="111"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="111">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="B71" s="128">
+      <c r="B72" s="111">
         <v>7</v>
       </c>
-      <c r="C71" s="128" t="s">
+      <c r="C72" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D71" s="129">
+      <c r="D72" s="112">
         <v>46059</v>
       </c>
-      <c r="E71" s="130"/>
-      <c r="F71" s="128"/>
-      <c r="G71" s="128"/>
-      <c r="H71" s="128"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="128">
+      <c r="E72" s="113"/>
+      <c r="F72" s="111"/>
+      <c r="G72" s="111"/>
+      <c r="H72" s="111"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="111">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B72" s="128">
+      <c r="B73" s="111">
         <v>8</v>
       </c>
-      <c r="C72" s="128" t="s">
+      <c r="C73" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D72" s="129">
+      <c r="D73" s="112">
         <v>46060</v>
       </c>
-      <c r="E72" s="130"/>
-      <c r="F72" s="128"/>
-      <c r="G72" s="128"/>
-      <c r="H72" s="128"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="128">
+      <c r="E73" s="113"/>
+      <c r="F73" s="111"/>
+      <c r="G73" s="111"/>
+      <c r="H73" s="111"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="111">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B73" s="128">
+      <c r="B74" s="111">
         <v>9</v>
       </c>
-      <c r="C73" s="128" t="s">
+      <c r="C74" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D73" s="129">
+      <c r="D74" s="112">
         <v>46061</v>
       </c>
-      <c r="E73" s="130"/>
-      <c r="F73" s="128"/>
-      <c r="G73" s="128"/>
-      <c r="H73" s="128"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="128">
+      <c r="E74" s="113"/>
+      <c r="F74" s="111"/>
+      <c r="G74" s="111"/>
+      <c r="H74" s="111"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="111">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="B74" s="128">
+      <c r="B75" s="111">
         <v>10</v>
       </c>
-      <c r="C74" s="128" t="s">
+      <c r="C75" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="D74" s="129">
+      <c r="D75" s="112">
         <v>46062</v>
       </c>
-      <c r="E74" s="130"/>
-      <c r="F74" s="128"/>
-      <c r="G74" s="128"/>
-      <c r="H74" s="128"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="24">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-      <c r="B75" s="24">
-        <v>1</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D75" s="29">
-        <v>46063</v>
-      </c>
-      <c r="E75" s="25"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
-      <c r="H75" s="24"/>
+      <c r="E75" s="113"/>
+      <c r="F75" s="111"/>
+      <c r="G75" s="111"/>
+      <c r="H75" s="111"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="24">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D76" s="29">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="E76" s="25"/>
       <c r="F76" s="24"/>
@@ -3330,16 +3346,16 @@
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="24">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D77" s="29">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="E77" s="25"/>
       <c r="F77" s="24"/>
@@ -3349,16 +3365,16 @@
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="24">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" s="24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C78" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D78" s="29">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="E78" s="25"/>
       <c r="F78" s="24"/>
@@ -3368,16 +3384,16 @@
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="24">
         <f t="shared" si="1"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" s="24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D79" s="29">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="E79" s="25"/>
       <c r="F79" s="24"/>
@@ -3387,16 +3403,16 @@
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="24">
         <f t="shared" si="1"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" s="24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D80" s="29">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="E80" s="25"/>
       <c r="F80" s="24"/>
@@ -3406,16 +3422,16 @@
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="24">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" s="24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C81" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D81" s="29">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="E81" s="25"/>
       <c r="F81" s="24"/>
@@ -3425,16 +3441,16 @@
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="24">
         <f t="shared" si="1"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" s="24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D82" s="29">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="E82" s="25"/>
       <c r="F82" s="24"/>
@@ -3444,16 +3460,16 @@
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="24">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C83" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D83" s="29">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E83" s="25"/>
       <c r="F83" s="24"/>
@@ -3463,16 +3479,16 @@
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="24">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C84" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D84" s="29">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E84" s="25"/>
       <c r="F84" s="24"/>
@@ -3480,132 +3496,132 @@
       <c r="H84" s="24"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="125">
+      <c r="A85" s="24">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B85" s="24">
+        <v>10</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D85" s="29">
+        <v>46072</v>
+      </c>
+      <c r="E85" s="25"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
+      <c r="H85" s="24"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="108">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B85" s="125">
+      <c r="B86" s="108">
         <v>1</v>
       </c>
-      <c r="C85" s="125" t="s">
+      <c r="C86" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="D85" s="126">
+      <c r="D86" s="109">
         <v>46073</v>
       </c>
-      <c r="E85" s="127"/>
-      <c r="F85" s="125"/>
-      <c r="G85" s="125"/>
-      <c r="H85" s="125"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="125">
+      <c r="E86" s="110"/>
+      <c r="F86" s="108"/>
+      <c r="G86" s="108"/>
+      <c r="H86" s="108"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="108">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B86" s="125">
+      <c r="B87" s="108">
         <v>2</v>
       </c>
-      <c r="C86" s="125" t="s">
+      <c r="C87" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="126">
+      <c r="D87" s="109">
         <v>46074</v>
       </c>
-      <c r="E86" s="127"/>
-      <c r="F86" s="125"/>
-      <c r="G86" s="125"/>
-      <c r="H86" s="125"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="125">
+      <c r="E87" s="110"/>
+      <c r="F87" s="108"/>
+      <c r="G87" s="108"/>
+      <c r="H87" s="108"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="108">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B87" s="125">
+      <c r="B88" s="108">
         <v>3</v>
       </c>
-      <c r="C87" s="125" t="s">
+      <c r="C88" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="D87" s="126">
+      <c r="D88" s="109">
         <v>46075</v>
       </c>
-      <c r="E87" s="127"/>
-      <c r="F87" s="125"/>
-      <c r="G87" s="125"/>
-      <c r="H87" s="125"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="125">
+      <c r="E88" s="110"/>
+      <c r="F88" s="108"/>
+      <c r="G88" s="108"/>
+      <c r="H88" s="108"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="108">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B88" s="125">
+      <c r="B89" s="108">
         <v>4</v>
       </c>
-      <c r="C88" s="125" t="s">
+      <c r="C89" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="D88" s="126">
+      <c r="D89" s="109">
         <v>46076</v>
       </c>
-      <c r="E88" s="127"/>
-      <c r="F88" s="125"/>
-      <c r="G88" s="125"/>
-      <c r="H88" s="125"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="125">
+      <c r="E89" s="110"/>
+      <c r="F89" s="108"/>
+      <c r="G89" s="108"/>
+      <c r="H89" s="108"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="108">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B89" s="125">
+      <c r="B90" s="108">
         <v>5</v>
       </c>
-      <c r="C89" s="125" t="s">
+      <c r="C90" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="D89" s="126">
+      <c r="D90" s="109">
         <v>46077</v>
       </c>
-      <c r="E89" s="127"/>
-      <c r="F89" s="125"/>
-      <c r="G89" s="125"/>
-      <c r="H89" s="125"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="10">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B90" s="10">
-        <v>1</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="34">
-        <v>46078</v>
-      </c>
-      <c r="E90" s="16"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
+      <c r="E90" s="110"/>
+      <c r="F90" s="108"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="108"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="10">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="34">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E91" s="16"/>
       <c r="F91" s="10"/>
@@ -3615,16 +3631,16 @@
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B92" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="34">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E92" s="16"/>
       <c r="F92" s="10"/>
@@ -3634,16 +3650,16 @@
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <f t="shared" si="1"/>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D93" s="34">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="E93" s="16"/>
       <c r="F93" s="10"/>
@@ -3653,16 +3669,16 @@
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <f t="shared" si="1"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D94" s="34">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E94" s="16"/>
       <c r="F94" s="10"/>
@@ -3672,16 +3688,16 @@
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D95" s="34">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="E95" s="16"/>
       <c r="F95" s="10"/>
@@ -3691,16 +3707,16 @@
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B96" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="34">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E96" s="16"/>
       <c r="F96" s="10"/>
@@ -3710,16 +3726,16 @@
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D97" s="34">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E97" s="16"/>
       <c r="F97" s="10"/>
@@ -3729,16 +3745,16 @@
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="34">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E98" s="16"/>
       <c r="F98" s="10"/>
@@ -3748,16 +3764,16 @@
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="34">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E99" s="16"/>
       <c r="F99" s="10"/>
@@ -3765,37 +3781,37 @@
       <c r="H99" s="10"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="30">
+      <c r="A100" s="10">
         <f t="shared" si="1"/>
-        <v>99</v>
-      </c>
-      <c r="B100" s="30">
-        <v>1</v>
-      </c>
-      <c r="C100" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D100" s="31">
-        <v>46088</v>
-      </c>
-      <c r="E100" s="32"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
+        <v>98</v>
+      </c>
+      <c r="B100" s="10">
+        <v>10</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="34">
+        <v>46087</v>
+      </c>
+      <c r="E100" s="16"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="10"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="30">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D101" s="31">
-        <v>46089</v>
+        <v>46088</v>
       </c>
       <c r="E101" s="32"/>
       <c r="F101" s="30"/>
@@ -3805,16 +3821,16 @@
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="30">
         <f t="shared" si="1"/>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="31">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E102" s="32"/>
       <c r="F102" s="30"/>
@@ -3824,16 +3840,16 @@
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="30">
         <f t="shared" si="1"/>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C103" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D103" s="31">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="E103" s="32"/>
       <c r="F103" s="30"/>
@@ -3843,16 +3859,16 @@
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="30">
         <f t="shared" si="1"/>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B104" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="31">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E104" s="32"/>
       <c r="F104" s="30"/>
@@ -3860,37 +3876,37 @@
       <c r="H104" s="30"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="50">
+      <c r="A105" s="30">
         <f t="shared" si="1"/>
-        <v>104</v>
-      </c>
-      <c r="B105" s="50">
-        <v>1</v>
-      </c>
-      <c r="C105" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="D105" s="51">
-        <v>46093</v>
-      </c>
-      <c r="E105" s="52"/>
-      <c r="F105" s="50"/>
-      <c r="G105" s="50"/>
-      <c r="H105" s="50"/>
+        <v>103</v>
+      </c>
+      <c r="B105" s="30">
+        <v>5</v>
+      </c>
+      <c r="C105" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" s="31">
+        <v>46092</v>
+      </c>
+      <c r="E105" s="32"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="50">
         <f t="shared" si="1"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D106" s="51">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="E106" s="52"/>
       <c r="F106" s="50"/>
@@ -3900,16 +3916,16 @@
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="50">
         <f t="shared" si="1"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B107" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C107" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D107" s="51">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="E107" s="52"/>
       <c r="F107" s="50"/>
@@ -3919,16 +3935,16 @@
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="50">
         <f t="shared" si="1"/>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B108" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D108" s="51">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="E108" s="52"/>
       <c r="F108" s="50"/>
@@ -3938,16 +3954,16 @@
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="50">
         <f t="shared" si="1"/>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D109" s="51">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="E109" s="52"/>
       <c r="F109" s="50"/>
@@ -3955,45 +3971,37 @@
       <c r="H109" s="50"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="37">
+      <c r="A110" s="50">
         <f t="shared" si="1"/>
-        <v>109</v>
-      </c>
-      <c r="B110" s="37">
-        <v>1</v>
-      </c>
-      <c r="C110" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D110" s="80">
-        <v>46230</v>
-      </c>
-      <c r="E110" s="103">
-        <v>0.375</v>
-      </c>
-      <c r="F110" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="G110" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="H110" s="38" t="s">
-        <v>11</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B110" s="50">
+        <v>5</v>
+      </c>
+      <c r="C110" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="D110" s="51">
+        <v>46097</v>
+      </c>
+      <c r="E110" s="52"/>
+      <c r="F110" s="50"/>
+      <c r="G110" s="50"/>
+      <c r="H110" s="50"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="37">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B111" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D111" s="80">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="E111" s="103">
         <v>0.375</v>
@@ -4011,16 +4019,16 @@
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="37">
         <f t="shared" si="1"/>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D112" s="80">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="E112" s="103">
         <v>0.375</v>
@@ -4038,16 +4046,16 @@
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="37">
         <f t="shared" si="1"/>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B113" s="37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C113" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D113" s="80">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E113" s="103">
         <v>0.375</v>
@@ -4065,16 +4073,16 @@
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="37">
         <f t="shared" si="1"/>
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D114" s="80">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="E114" s="103">
         <v>0.375</v>
@@ -4092,16 +4100,16 @@
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="37">
         <f t="shared" si="1"/>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B115" s="37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C115" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D115" s="80">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="E115" s="103">
         <v>0.375</v>
@@ -4110,7 +4118,7 @@
         <v>2</v>
       </c>
       <c r="G115" s="38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H115" s="38" t="s">
         <v>11</v>
@@ -4119,16 +4127,16 @@
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="37">
         <f t="shared" si="1"/>
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B116" s="37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C116" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D116" s="80">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E116" s="103">
         <v>0.375</v>
@@ -4146,16 +4154,16 @@
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="37">
         <f t="shared" si="1"/>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B117" s="37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D117" s="80">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E117" s="103">
         <v>0.375</v>
@@ -4173,16 +4181,16 @@
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="37">
         <f t="shared" si="1"/>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B118" s="37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C118" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D118" s="80">
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="E118" s="103">
         <v>0.375</v>
@@ -4191,7 +4199,7 @@
         <v>2</v>
       </c>
       <c r="G118" s="38" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="H118" s="38" t="s">
         <v>11</v>
@@ -4200,16 +4208,16 @@
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="37">
         <f t="shared" si="1"/>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B119" s="37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C119" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D119" s="80">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="E119" s="103">
         <v>0.375</v>
@@ -4227,16 +4235,16 @@
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="37">
         <f t="shared" si="1"/>
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B120" s="37">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C120" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D120" s="80">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E120" s="103">
         <v>0.375</v>
@@ -4252,51 +4260,78 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="48">
+      <c r="A121" s="37">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="B121" s="37">
+        <v>11</v>
+      </c>
+      <c r="C121" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D121" s="80">
+        <v>46323</v>
+      </c>
+      <c r="E121" s="103">
+        <v>0.375</v>
+      </c>
+      <c r="F121" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="G121" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H121" s="38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="48">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="B121" s="48">
+      <c r="B122" s="48">
         <v>2</v>
       </c>
-      <c r="C121" s="48" t="s">
+      <c r="C122" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="D121" s="81">
+      <c r="D122" s="81">
         <v>46256</v>
       </c>
-      <c r="E121" s="104">
+      <c r="E122" s="104">
         <v>0.375</v>
       </c>
-      <c r="F121" s="49" t="s">
+      <c r="F122" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="G121" s="10" t="s">
+      <c r="G122" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H121" s="49" t="s">
+      <c r="H122" s="49" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H104" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H104">
-      <sortCondition ref="A1:A104"/>
+  <autoFilter ref="A1:H105" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H105">
+      <sortCondition ref="A1:A105"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="44" max="16383" man="1"/>
-    <brk id="54" max="16383" man="1"/>
+    <brk id="45" max="16383" man="1"/>
+    <brk id="55" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="105"/>
@@ -4305,7 +4340,7 @@
     <col min="4" max="4" width="8.33203125" style="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" style="36" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.109375" style="105" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="132"/>
+    <col min="7" max="7" width="11.5546875" style="115"/>
     <col min="10" max="10" width="11.5546875" style="105"/>
   </cols>
   <sheetData>
@@ -4328,7 +4363,7 @@
       <c r="F1" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="132" t="s">
+      <c r="G1" s="115" t="s">
         <v>97</v>
       </c>
       <c r="H1" t="s">
@@ -4364,7 +4399,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F2)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G2" s="132" t="str">
+      <c r="G2" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H2</f>
         <v>Heim</v>
       </c>
@@ -4380,7 +4415,7 @@
         <v>107</v>
       </c>
       <c r="K2" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L2" t="s">
         <v>145</v>
@@ -4396,14 +4431,14 @@
         <v>0.75</v>
       </c>
       <c r="D3" s="36">
-        <f t="shared" ref="D3:D66" si="0">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
+        <f t="shared" ref="D3:D67" si="0">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
         <v>0.82291666666666663</v>
       </c>
       <c r="E3" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F3)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G3" s="132" t="str">
+      <c r="G3" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H3</f>
         <v>Heim</v>
       </c>
@@ -4419,7 +4454,7 @@
         <v>107</v>
       </c>
       <c r="K3" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L3" t="s">
         <v>145</v>
@@ -4442,7 +4477,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F4)</f>
         <v>NEUDÖRFL</v>
       </c>
-      <c r="G4" s="132" t="str">
+      <c r="G4" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H4</f>
         <v>Auswärts</v>
       </c>
@@ -4458,7 +4493,7 @@
         <v>107</v>
       </c>
       <c r="K4" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L4" t="s">
         <v>145</v>
@@ -4481,7 +4516,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F5)</f>
         <v>ROHBACH</v>
       </c>
-      <c r="G5" s="132" t="str">
+      <c r="G5" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H5</f>
         <v>Auswärts</v>
       </c>
@@ -4497,7 +4532,7 @@
         <v>107</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L5" t="s">
         <v>145</v>
@@ -4520,7 +4555,10 @@
         <f>UPPER('Nach Mannschaften sortiert'!F6)</f>
         <v>KITTSEE</v>
       </c>
-      <c r="G6" s="132" t="str">
+      <c r="F6" s="105" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H6</f>
         <v>Auswärts</v>
       </c>
@@ -4536,7 +4574,7 @@
         <v>107</v>
       </c>
       <c r="K6" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="L6" t="s">
         <v>145</v>
@@ -4559,7 +4597,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F7)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G7" s="132" t="str">
+      <c r="G7" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
         <v>Heim</v>
       </c>
@@ -4575,7 +4613,7 @@
         <v>107</v>
       </c>
       <c r="K7" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L7" t="s">
         <v>145</v>
@@ -4598,7 +4636,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F8)</f>
         <v>WIENER NEUDORF</v>
       </c>
-      <c r="G8" s="132" t="str">
+      <c r="G8" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
         <v>Auswärts</v>
       </c>
@@ -4614,7 +4652,7 @@
         <v>107</v>
       </c>
       <c r="K8" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L8" t="s">
         <v>145</v>
@@ -4623,27 +4661,27 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="102">
         <f>'Nach Mannschaften sortiert'!D9</f>
-        <v>46249</v>
+        <v>46217</v>
       </c>
       <c r="C9" s="36">
         <f>'Nach Mannschaften sortiert'!E9</f>
-        <v>0.72916666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D9" s="36">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.90625</v>
       </c>
       <c r="E9" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
-        <v>KITTSEE</v>
-      </c>
-      <c r="G9" s="132" t="str">
+        <v>PÖTTSCHING</v>
+      </c>
+      <c r="G9" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
         <v>Auswärts</v>
       </c>
       <c r="H9" t="str">
         <f>'Nach Mannschaften sortiert'!G9</f>
-        <v>Kittsee</v>
+        <v>Pöttsching</v>
       </c>
       <c r="I9" t="str">
         <f>'Nach Mannschaften sortiert'!C9</f>
@@ -4653,7 +4691,7 @@
         <v>107</v>
       </c>
       <c r="K9" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L9" t="s">
         <v>145</v>
@@ -4662,27 +4700,27 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="102">
         <f>'Nach Mannschaften sortiert'!D10</f>
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="C10" s="36">
         <f>'Nach Mannschaften sortiert'!E10</f>
-        <v>0.70833333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D10" s="36">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E10" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F10)</f>
-        <v>DEUTSCH JAHRNDORF</v>
-      </c>
-      <c r="G10" s="132" t="str">
+        <v>KITTSEE</v>
+      </c>
+      <c r="G10" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
         <v>Auswärts</v>
       </c>
       <c r="H10" t="str">
         <f>'Nach Mannschaften sortiert'!G10</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I10" t="str">
         <f>'Nach Mannschaften sortiert'!C10</f>
@@ -4701,7 +4739,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="102">
         <f>'Nach Mannschaften sortiert'!D11</f>
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="C11" s="36">
         <f>'Nach Mannschaften sortiert'!E11</f>
@@ -4713,15 +4751,15 @@
       </c>
       <c r="E11" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G11" s="132" t="str">
+        <v>DEUTSCH JAHRNDORF</v>
+      </c>
+      <c r="G11" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H11" t="str">
         <f>'Nach Mannschaften sortiert'!G11</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I11" t="str">
         <f>'Nach Mannschaften sortiert'!C11</f>
@@ -4740,27 +4778,27 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="102">
         <f>'Nach Mannschaften sortiert'!D12</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C12" s="36">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="36">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E12" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
-        <v>MÖNCHHOF</v>
-      </c>
-      <c r="G12" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G12" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H12" t="str">
         <f>'Nach Mannschaften sortiert'!G12</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I12" t="str">
         <f>'Nach Mannschaften sortiert'!C12</f>
@@ -4779,7 +4817,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" s="102">
         <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="C13" s="36">
         <f>'Nach Mannschaften sortiert'!E13</f>
@@ -4791,15 +4829,15 @@
       </c>
       <c r="E13" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G13" s="132" t="str">
+        <v>MÖNCHHOF</v>
+      </c>
+      <c r="G13" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H13" t="str">
         <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I13" t="str">
         <f>'Nach Mannschaften sortiert'!C13</f>
@@ -4818,27 +4856,27 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="102">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="C14" s="36">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="D14" s="36">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E14" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
-        <v>GATTENDORF</v>
-      </c>
-      <c r="G14" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G14" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H14" t="str">
         <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I14" t="str">
         <f>'Nach Mannschaften sortiert'!C14</f>
@@ -4857,7 +4895,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" s="102">
         <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C15" s="36">
         <f>'Nach Mannschaften sortiert'!E15</f>
@@ -4869,15 +4907,15 @@
       </c>
       <c r="E15" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G15" s="132" t="str">
+        <v>GATTENDORF</v>
+      </c>
+      <c r="G15" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H15" t="str">
         <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I15" t="str">
         <f>'Nach Mannschaften sortiert'!C15</f>
@@ -4896,27 +4934,27 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" s="102">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C16" s="36">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.79166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" si="0"/>
-        <v>0.86458333333333326</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E16" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
-        <v>SIEGENDORF</v>
-      </c>
-      <c r="G16" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G16" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H16" t="str">
         <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I16" t="str">
         <f>'Nach Mannschaften sortiert'!C16</f>
@@ -4935,27 +4973,27 @@
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="102">
         <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46305</v>
+        <v>46297</v>
       </c>
       <c r="C17" s="36">
         <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.64583333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E17" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G17" s="132" t="str">
+        <v>SIEGENDORF</v>
+      </c>
+      <c r="G17" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H17" t="str">
         <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I17" t="str">
         <f>'Nach Mannschaften sortiert'!C17</f>
@@ -4974,7 +5012,7 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="102">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46312</v>
+        <v>46305</v>
       </c>
       <c r="C18" s="36">
         <f>'Nach Mannschaften sortiert'!E18</f>
@@ -4986,15 +5024,15 @@
       </c>
       <c r="E18" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
-        <v>HORNSTEIN</v>
-      </c>
-      <c r="G18" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G18" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H18" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I18" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
@@ -5013,27 +5051,27 @@
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="102">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="C19" s="36">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D19" s="36">
         <f t="shared" si="0"/>
-        <v>0.69791666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="E19" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G19" s="132" t="str">
+        <v>HORNSTEIN</v>
+      </c>
+      <c r="G19" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H19" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I19" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
@@ -5052,27 +5090,27 @@
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="102">
         <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C20" s="36">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.58333333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="D20" s="36">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E20" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
-        <v>ILLMITZ</v>
-      </c>
-      <c r="G20" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G20" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H20" t="str">
         <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I20" t="str">
         <f>'Nach Mannschaften sortiert'!C20</f>
@@ -5091,7 +5129,7 @@
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="102">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C21" s="36">
         <f>'Nach Mannschaften sortiert'!E21</f>
@@ -5103,15 +5141,15 @@
       </c>
       <c r="E21" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G21" s="132" t="str">
+        <v>ILLMITZ</v>
+      </c>
+      <c r="G21" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H21" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I21" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
@@ -5130,31 +5168,31 @@
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="102">
         <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46249</v>
+        <v>46333</v>
       </c>
       <c r="C22" s="36">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.64583333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D22" s="36">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.65625</v>
       </c>
       <c r="E22" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
-        <v>KITTSEE</v>
-      </c>
-      <c r="G22" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G22" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H22" t="str">
         <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Kittsee</v>
+        <v>Andau</v>
       </c>
       <c r="I22" t="str">
         <f>'Nach Mannschaften sortiert'!C22</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J22" s="105" t="s">
         <v>107</v>
@@ -5169,27 +5207,27 @@
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="102">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46256</v>
+        <v>46249</v>
       </c>
       <c r="C23" s="36">
         <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.625</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D23" s="36">
         <f t="shared" si="0"/>
-        <v>0.69791666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="E23" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
-        <v>DEUTSCH JAHRNDORF</v>
-      </c>
-      <c r="G23" s="132" t="str">
+        <v>KITTSEE</v>
+      </c>
+      <c r="G23" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
         <v>Auswärts</v>
       </c>
       <c r="H23" t="str">
         <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I23" t="str">
         <f>'Nach Mannschaften sortiert'!C23</f>
@@ -5208,7 +5246,7 @@
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="102">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="C24" s="36">
         <f>'Nach Mannschaften sortiert'!E24</f>
@@ -5220,15 +5258,15 @@
       </c>
       <c r="E24" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G24" s="132" t="str">
+        <v>DEUTSCH JAHRNDORF</v>
+      </c>
+      <c r="G24" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H24" t="str">
         <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I24" t="str">
         <f>'Nach Mannschaften sortiert'!C24</f>
@@ -5247,27 +5285,27 @@
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="102">
         <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C25" s="36">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.60416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D25" s="36">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E25" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
-        <v>MÖNCHHOF</v>
-      </c>
-      <c r="G25" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G25" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H25" t="str">
         <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I25" t="str">
         <f>'Nach Mannschaften sortiert'!C25</f>
@@ -5286,7 +5324,7 @@
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="102">
         <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="C26" s="36">
         <f>'Nach Mannschaften sortiert'!E26</f>
@@ -5298,15 +5336,15 @@
       </c>
       <c r="E26" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G26" s="132" t="str">
+        <v>MÖNCHHOF</v>
+      </c>
+      <c r="G26" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H26" t="str">
         <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I26" t="str">
         <f>'Nach Mannschaften sortiert'!C26</f>
@@ -5325,27 +5363,27 @@
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="102">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="C27" s="36">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D27" s="36">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E27" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
-        <v>GATTENDORF</v>
-      </c>
-      <c r="G27" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G27" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H27" t="str">
         <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I27" t="str">
         <f>'Nach Mannschaften sortiert'!C27</f>
@@ -5364,7 +5402,7 @@
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="102">
         <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C28" s="36">
         <f>'Nach Mannschaften sortiert'!E28</f>
@@ -5376,15 +5414,15 @@
       </c>
       <c r="E28" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G28" s="132" t="str">
+        <v>GATTENDORF</v>
+      </c>
+      <c r="G28" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H28" t="str">
         <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I28" t="str">
         <f>'Nach Mannschaften sortiert'!C28</f>
@@ -5403,27 +5441,27 @@
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="102">
         <f>'Nach Mannschaften sortiert'!D29</f>
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C29" s="36">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.70833333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D29" s="36">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.65625</v>
       </c>
       <c r="E29" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
-        <v>SIEGENDORF</v>
-      </c>
-      <c r="G29" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G29" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H29" t="str">
         <f>'Nach Mannschaften sortiert'!G29</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I29" t="str">
         <f>'Nach Mannschaften sortiert'!C29</f>
@@ -5442,27 +5480,27 @@
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="102">
         <f>'Nach Mannschaften sortiert'!D30</f>
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="C30" s="36">
         <f>'Nach Mannschaften sortiert'!E30</f>
-        <v>0.5625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D30" s="36">
         <f t="shared" si="0"/>
-        <v>0.63541666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E30" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G30" s="132" t="str">
+        <v>SIEGENDORF</v>
+      </c>
+      <c r="G30" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H30" t="str">
         <f>'Nach Mannschaften sortiert'!G30</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I30" t="str">
         <f>'Nach Mannschaften sortiert'!C30</f>
@@ -5481,7 +5519,7 @@
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="102">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>46312</v>
+        <v>46305</v>
       </c>
       <c r="C31" s="36">
         <f>'Nach Mannschaften sortiert'!E31</f>
@@ -5493,15 +5531,15 @@
       </c>
       <c r="E31" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
-        <v>HORNSTEIN</v>
-      </c>
-      <c r="G31" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G31" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H31" t="str">
         <f>'Nach Mannschaften sortiert'!G31</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I31" t="str">
         <f>'Nach Mannschaften sortiert'!C31</f>
@@ -5520,27 +5558,27 @@
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="102">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="C32" s="36">
         <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0.54166666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D32" s="36">
         <f t="shared" si="0"/>
-        <v>0.61458333333333326</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="E32" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G32" s="132" t="str">
+        <v>HORNSTEIN</v>
+      </c>
+      <c r="G32" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H32" t="str">
         <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
@@ -5559,27 +5597,27 @@
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="102">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C33" s="36">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.5</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D33" s="36">
         <f t="shared" si="0"/>
-        <v>0.57291666666666663</v>
+        <v>0.61458333333333326</v>
       </c>
       <c r="E33" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
-        <v>ILLMITZ</v>
-      </c>
-      <c r="G33" s="132" t="str">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G33" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H33" t="str">
         <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I33" t="str">
         <f>'Nach Mannschaften sortiert'!C33</f>
@@ -5598,7 +5636,7 @@
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="102">
         <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C34" s="36">
         <f>'Nach Mannschaften sortiert'!E34</f>
@@ -5610,15 +5648,15 @@
       </c>
       <c r="E34" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G34" s="132" t="str">
+        <v>ILLMITZ</v>
+      </c>
+      <c r="G34" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H34" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I34" t="str">
         <f>'Nach Mannschaften sortiert'!C34</f>
@@ -5637,31 +5675,31 @@
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="102">
         <f>'Nach Mannschaften sortiert'!D35</f>
-        <v>46023</v>
+        <v>46333</v>
       </c>
       <c r="C35" s="36">
         <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D35" s="36">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="E35" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="132">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G35" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
-        <v>0</v>
-      </c>
-      <c r="H35">
+        <v>Heim</v>
+      </c>
+      <c r="H35" t="str">
         <f>'Nach Mannschaften sortiert'!G35</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I35" t="str">
         <f>'Nach Mannschaften sortiert'!C35</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J35" s="105" t="s">
         <v>107</v>
@@ -5676,7 +5714,7 @@
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="102">
         <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C36" s="36">
         <f>'Nach Mannschaften sortiert'!E36</f>
@@ -5690,7 +5728,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
         <v/>
       </c>
-      <c r="G36" s="132">
+      <c r="G36" s="115">
         <f>'Nach Mannschaften sortiert'!H36</f>
         <v>0</v>
       </c>
@@ -5715,7 +5753,7 @@
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="102">
         <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C37" s="36">
         <f>'Nach Mannschaften sortiert'!E37</f>
@@ -5729,7 +5767,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
         <v/>
       </c>
-      <c r="G37" s="132">
+      <c r="G37" s="115">
         <f>'Nach Mannschaften sortiert'!H37</f>
         <v>0</v>
       </c>
@@ -5754,7 +5792,7 @@
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="102">
         <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C38" s="36">
         <f>'Nach Mannschaften sortiert'!E38</f>
@@ -5768,7 +5806,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
         <v/>
       </c>
-      <c r="G38" s="132">
+      <c r="G38" s="115">
         <f>'Nach Mannschaften sortiert'!H38</f>
         <v>0</v>
       </c>
@@ -5793,7 +5831,7 @@
     <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="102">
         <f>'Nach Mannschaften sortiert'!D39</f>
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C39" s="36">
         <f>'Nach Mannschaften sortiert'!E39</f>
@@ -5807,7 +5845,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
         <v/>
       </c>
-      <c r="G39" s="132">
+      <c r="G39" s="115">
         <f>'Nach Mannschaften sortiert'!H39</f>
         <v>0</v>
       </c>
@@ -5832,7 +5870,7 @@
     <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="102">
         <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C40" s="36">
         <f>'Nach Mannschaften sortiert'!E40</f>
@@ -5846,7 +5884,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
         <v/>
       </c>
-      <c r="G40" s="132">
+      <c r="G40" s="115">
         <f>'Nach Mannschaften sortiert'!H40</f>
         <v>0</v>
       </c>
@@ -5871,7 +5909,7 @@
     <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="102">
         <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C41" s="36">
         <f>'Nach Mannschaften sortiert'!E41</f>
@@ -5885,7 +5923,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F41)</f>
         <v/>
       </c>
-      <c r="G41" s="132">
+      <c r="G41" s="115">
         <f>'Nach Mannschaften sortiert'!H41</f>
         <v>0</v>
       </c>
@@ -5910,7 +5948,7 @@
     <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="102">
         <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C42" s="36">
         <f>'Nach Mannschaften sortiert'!E42</f>
@@ -5924,7 +5962,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
         <v/>
       </c>
-      <c r="G42" s="132">
+      <c r="G42" s="115">
         <f>'Nach Mannschaften sortiert'!H42</f>
         <v>0</v>
       </c>
@@ -5949,7 +5987,7 @@
     <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="102">
         <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C43" s="36">
         <f>'Nach Mannschaften sortiert'!E43</f>
@@ -5963,7 +6001,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F43)</f>
         <v/>
       </c>
-      <c r="G43" s="132">
+      <c r="G43" s="115">
         <f>'Nach Mannschaften sortiert'!H43</f>
         <v>0</v>
       </c>
@@ -5988,7 +6026,7 @@
     <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="102">
         <f>'Nach Mannschaften sortiert'!D44</f>
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C44" s="36">
         <f>'Nach Mannschaften sortiert'!E44</f>
@@ -6002,7 +6040,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F44)</f>
         <v/>
       </c>
-      <c r="G44" s="132">
+      <c r="G44" s="115">
         <f>'Nach Mannschaften sortiert'!H44</f>
         <v>0</v>
       </c>
@@ -6027,7 +6065,7 @@
     <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="102">
         <f>'Nach Mannschaften sortiert'!D45</f>
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C45" s="36">
         <f>'Nach Mannschaften sortiert'!E45</f>
@@ -6035,13 +6073,13 @@
       </c>
       <c r="D45" s="36">
         <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E45" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F45)</f>
         <v/>
       </c>
-      <c r="G45" s="132">
+      <c r="G45" s="115">
         <f>'Nach Mannschaften sortiert'!H45</f>
         <v>0</v>
       </c>
@@ -6051,7 +6089,7 @@
       </c>
       <c r="I45" t="str">
         <f>'Nach Mannschaften sortiert'!C45</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J45" s="105" t="s">
         <v>107</v>
@@ -6066,7 +6104,7 @@
     <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="102">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C46" s="36">
         <f>'Nach Mannschaften sortiert'!E46</f>
@@ -6080,7 +6118,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F46)</f>
         <v/>
       </c>
-      <c r="G46" s="132">
+      <c r="G46" s="115">
         <f>'Nach Mannschaften sortiert'!H46</f>
         <v>0</v>
       </c>
@@ -6105,7 +6143,7 @@
     <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="102">
         <f>'Nach Mannschaften sortiert'!D47</f>
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C47" s="36">
         <f>'Nach Mannschaften sortiert'!E47</f>
@@ -6119,7 +6157,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F47)</f>
         <v/>
       </c>
-      <c r="G47" s="132">
+      <c r="G47" s="115">
         <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
@@ -6144,7 +6182,7 @@
     <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="102">
         <f>'Nach Mannschaften sortiert'!D48</f>
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C48" s="36">
         <f>'Nach Mannschaften sortiert'!E48</f>
@@ -6158,7 +6196,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F48)</f>
         <v/>
       </c>
-      <c r="G48" s="132">
+      <c r="G48" s="115">
         <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
@@ -6183,7 +6221,7 @@
     <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="102">
         <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="C49" s="36">
         <f>'Nach Mannschaften sortiert'!E49</f>
@@ -6197,7 +6235,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F49)</f>
         <v/>
       </c>
-      <c r="G49" s="132">
+      <c r="G49" s="115">
         <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
@@ -6222,7 +6260,7 @@
     <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="102">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="C50" s="36">
         <f>'Nach Mannschaften sortiert'!E50</f>
@@ -6236,7 +6274,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
         <v/>
       </c>
-      <c r="G50" s="132">
+      <c r="G50" s="115">
         <f>'Nach Mannschaften sortiert'!H50</f>
         <v>0</v>
       </c>
@@ -6261,7 +6299,7 @@
     <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="102">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C51" s="36">
         <f>'Nach Mannschaften sortiert'!E51</f>
@@ -6275,7 +6313,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
         <v/>
       </c>
-      <c r="G51" s="132">
+      <c r="G51" s="115">
         <f>'Nach Mannschaften sortiert'!H51</f>
         <v>0</v>
       </c>
@@ -6300,7 +6338,7 @@
     <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="102">
         <f>'Nach Mannschaften sortiert'!D52</f>
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C52" s="36">
         <f>'Nach Mannschaften sortiert'!E52</f>
@@ -6314,7 +6352,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F52)</f>
         <v/>
       </c>
-      <c r="G52" s="132">
+      <c r="G52" s="115">
         <f>'Nach Mannschaften sortiert'!H52</f>
         <v>0</v>
       </c>
@@ -6339,7 +6377,7 @@
     <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="102">
         <f>'Nach Mannschaften sortiert'!D53</f>
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C53" s="36">
         <f>'Nach Mannschaften sortiert'!E53</f>
@@ -6353,7 +6391,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F53)</f>
         <v/>
       </c>
-      <c r="G53" s="132">
+      <c r="G53" s="115">
         <f>'Nach Mannschaften sortiert'!H53</f>
         <v>0</v>
       </c>
@@ -6378,7 +6416,7 @@
     <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="102">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C54" s="36">
         <f>'Nach Mannschaften sortiert'!E54</f>
@@ -6392,7 +6430,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
         <v/>
       </c>
-      <c r="G54" s="132">
+      <c r="G54" s="115">
         <f>'Nach Mannschaften sortiert'!H54</f>
         <v>0</v>
       </c>
@@ -6417,7 +6455,7 @@
     <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="102">
         <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C55" s="36">
         <f>'Nach Mannschaften sortiert'!E55</f>
@@ -6425,13 +6463,13 @@
       </c>
       <c r="D55" s="36">
         <f t="shared" si="0"/>
-        <v>0.125</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E55" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F55)</f>
         <v/>
       </c>
-      <c r="G55" s="132">
+      <c r="G55" s="115">
         <f>'Nach Mannschaften sortiert'!H55</f>
         <v>0</v>
       </c>
@@ -6441,7 +6479,7 @@
       </c>
       <c r="I55" t="str">
         <f>'Nach Mannschaften sortiert'!C55</f>
-        <v>U12_1</v>
+        <v>U14</v>
       </c>
       <c r="J55" s="105" t="s">
         <v>107</v>
@@ -6456,7 +6494,7 @@
     <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="102">
         <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C56" s="36">
         <f>'Nach Mannschaften sortiert'!E56</f>
@@ -6470,7 +6508,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F56)</f>
         <v/>
       </c>
-      <c r="G56" s="132">
+      <c r="G56" s="115">
         <f>'Nach Mannschaften sortiert'!H56</f>
         <v>0</v>
       </c>
@@ -6495,7 +6533,7 @@
     <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="102">
         <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C57" s="36">
         <f>'Nach Mannschaften sortiert'!E57</f>
@@ -6509,7 +6547,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F57)</f>
         <v/>
       </c>
-      <c r="G57" s="132">
+      <c r="G57" s="115">
         <f>'Nach Mannschaften sortiert'!H57</f>
         <v>0</v>
       </c>
@@ -6534,7 +6572,7 @@
     <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="102">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C58" s="36">
         <f>'Nach Mannschaften sortiert'!E58</f>
@@ -6548,7 +6586,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F58)</f>
         <v/>
       </c>
-      <c r="G58" s="132">
+      <c r="G58" s="115">
         <f>'Nach Mannschaften sortiert'!H58</f>
         <v>0</v>
       </c>
@@ -6573,7 +6611,7 @@
     <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="102">
         <f>'Nach Mannschaften sortiert'!D59</f>
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C59" s="36">
         <f>'Nach Mannschaften sortiert'!E59</f>
@@ -6587,7 +6625,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F59)</f>
         <v/>
       </c>
-      <c r="G59" s="132">
+      <c r="G59" s="115">
         <f>'Nach Mannschaften sortiert'!H59</f>
         <v>0</v>
       </c>
@@ -6612,7 +6650,7 @@
     <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="102">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="C60" s="36">
         <f>'Nach Mannschaften sortiert'!E60</f>
@@ -6626,7 +6664,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
         <v/>
       </c>
-      <c r="G60" s="132">
+      <c r="G60" s="115">
         <f>'Nach Mannschaften sortiert'!H60</f>
         <v>0</v>
       </c>
@@ -6651,7 +6689,7 @@
     <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="102">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="C61" s="36">
         <f>'Nach Mannschaften sortiert'!E61</f>
@@ -6665,7 +6703,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F61)</f>
         <v/>
       </c>
-      <c r="G61" s="132">
+      <c r="G61" s="115">
         <f>'Nach Mannschaften sortiert'!H61</f>
         <v>0</v>
       </c>
@@ -6690,7 +6728,7 @@
     <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="102">
         <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C62" s="36">
         <f>'Nach Mannschaften sortiert'!E62</f>
@@ -6704,7 +6742,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
         <v/>
       </c>
-      <c r="G62" s="132">
+      <c r="G62" s="115">
         <f>'Nach Mannschaften sortiert'!H62</f>
         <v>0</v>
       </c>
@@ -6729,7 +6767,7 @@
     <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="102">
         <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C63" s="36">
         <f>'Nach Mannschaften sortiert'!E63</f>
@@ -6743,7 +6781,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
         <v/>
       </c>
-      <c r="G63" s="132">
+      <c r="G63" s="115">
         <f>'Nach Mannschaften sortiert'!H63</f>
         <v>0</v>
       </c>
@@ -6768,7 +6806,7 @@
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="102">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="C64" s="36">
         <f>'Nach Mannschaften sortiert'!E64</f>
@@ -6782,7 +6820,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F64)</f>
         <v/>
       </c>
-      <c r="G64" s="132">
+      <c r="G64" s="115">
         <f>'Nach Mannschaften sortiert'!H64</f>
         <v>0</v>
       </c>
@@ -6807,7 +6845,7 @@
     <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="102">
         <f>'Nach Mannschaften sortiert'!D65</f>
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C65" s="36">
         <f>'Nach Mannschaften sortiert'!E65</f>
@@ -6821,7 +6859,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F65)</f>
         <v/>
       </c>
-      <c r="G65" s="132">
+      <c r="G65" s="115">
         <f>'Nach Mannschaften sortiert'!H65</f>
         <v>0</v>
       </c>
@@ -6831,7 +6869,7 @@
       </c>
       <c r="I65" t="str">
         <f>'Nach Mannschaften sortiert'!C65</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J65" s="105" t="s">
         <v>107</v>
@@ -6846,7 +6884,7 @@
     <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="102">
         <f>'Nach Mannschaften sortiert'!D66</f>
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="C66" s="36">
         <f>'Nach Mannschaften sortiert'!E66</f>
@@ -6860,7 +6898,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F66)</f>
         <v/>
       </c>
-      <c r="G66" s="132">
+      <c r="G66" s="115">
         <f>'Nach Mannschaften sortiert'!H66</f>
         <v>0</v>
       </c>
@@ -6885,21 +6923,21 @@
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="102">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C67" s="36">
         <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="D67" s="36">
-        <f t="shared" ref="D67:D103" si="1">IF(I67 = "KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67 = "U16",C67+"1:45",IF(I67 = "U15",C67+"1:30",IF(I67 = "U14",C67+"1:30",IF(I67 = "U13",C67+"1:35",IF(I67 = "U12",C67+"1:10",IF(I67 = "U11",C67+"1:10",IF(I67 = "U10",C67+"1:03",C67+"3:00")))))))))</f>
+        <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
       <c r="E67" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F67)</f>
         <v/>
       </c>
-      <c r="G67" s="132">
+      <c r="G67" s="115">
         <f>'Nach Mannschaften sortiert'!H67</f>
         <v>0</v>
       </c>
@@ -6924,21 +6962,21 @@
     <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="102">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C68" s="36">
         <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="D68" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D68:D104" si="1">IF(I68 = "KM",C68+"1:45",IF(I68="U23",C68+"1:45",IF(I68 = "U16",C68+"1:45",IF(I68 = "U15",C68+"1:30",IF(I68 = "U14",C68+"1:30",IF(I68 = "U13",C68+"1:35",IF(I68 = "U12",C68+"1:10",IF(I68 = "U11",C68+"1:10",IF(I68 = "U10",C68+"1:03",C68+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E68" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F68)</f>
         <v/>
       </c>
-      <c r="G68" s="132">
+      <c r="G68" s="115">
         <f>'Nach Mannschaften sortiert'!H68</f>
         <v>0</v>
       </c>
@@ -6963,7 +7001,7 @@
     <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="102">
         <f>'Nach Mannschaften sortiert'!D69</f>
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="C69" s="36">
         <f>'Nach Mannschaften sortiert'!E69</f>
@@ -6977,7 +7015,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F69)</f>
         <v/>
       </c>
-      <c r="G69" s="132">
+      <c r="G69" s="115">
         <f>'Nach Mannschaften sortiert'!H69</f>
         <v>0</v>
       </c>
@@ -7002,7 +7040,7 @@
     <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="102">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C70" s="36">
         <f>'Nach Mannschaften sortiert'!E70</f>
@@ -7016,7 +7054,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F70)</f>
         <v/>
       </c>
-      <c r="G70" s="132">
+      <c r="G70" s="115">
         <f>'Nach Mannschaften sortiert'!H70</f>
         <v>0</v>
       </c>
@@ -7041,7 +7079,7 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="102">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="C71" s="36">
         <f>'Nach Mannschaften sortiert'!E71</f>
@@ -7055,7 +7093,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F71)</f>
         <v/>
       </c>
-      <c r="G71" s="132">
+      <c r="G71" s="115">
         <f>'Nach Mannschaften sortiert'!H71</f>
         <v>0</v>
       </c>
@@ -7080,7 +7118,7 @@
     <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="102">
         <f>'Nach Mannschaften sortiert'!D72</f>
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="C72" s="36">
         <f>'Nach Mannschaften sortiert'!E72</f>
@@ -7094,7 +7132,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F72)</f>
         <v/>
       </c>
-      <c r="G72" s="132">
+      <c r="G72" s="115">
         <f>'Nach Mannschaften sortiert'!H72</f>
         <v>0</v>
       </c>
@@ -7119,7 +7157,7 @@
     <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="102">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C73" s="36">
         <f>'Nach Mannschaften sortiert'!E73</f>
@@ -7133,7 +7171,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F73)</f>
         <v/>
       </c>
-      <c r="G73" s="132">
+      <c r="G73" s="115">
         <f>'Nach Mannschaften sortiert'!H73</f>
         <v>0</v>
       </c>
@@ -7158,7 +7196,7 @@
     <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="102">
         <f>'Nach Mannschaften sortiert'!D74</f>
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C74" s="36">
         <f>'Nach Mannschaften sortiert'!E74</f>
@@ -7172,7 +7210,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F74)</f>
         <v/>
       </c>
-      <c r="G74" s="132">
+      <c r="G74" s="115">
         <f>'Nach Mannschaften sortiert'!H74</f>
         <v>0</v>
       </c>
@@ -7197,7 +7235,7 @@
     <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="102">
         <f>'Nach Mannschaften sortiert'!D75</f>
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="C75" s="36">
         <f>'Nach Mannschaften sortiert'!E75</f>
@@ -7205,13 +7243,13 @@
       </c>
       <c r="D75" s="36">
         <f t="shared" si="1"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.125</v>
       </c>
       <c r="E75" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F75)</f>
         <v/>
       </c>
-      <c r="G75" s="132">
+      <c r="G75" s="115">
         <f>'Nach Mannschaften sortiert'!H75</f>
         <v>0</v>
       </c>
@@ -7221,7 +7259,7 @@
       </c>
       <c r="I75" t="str">
         <f>'Nach Mannschaften sortiert'!C75</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J75" s="105" t="s">
         <v>107</v>
@@ -7236,7 +7274,7 @@
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="102">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C76" s="36">
         <f>'Nach Mannschaften sortiert'!E76</f>
@@ -7250,7 +7288,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F76)</f>
         <v/>
       </c>
-      <c r="G76" s="132">
+      <c r="G76" s="115">
         <f>'Nach Mannschaften sortiert'!H76</f>
         <v>0</v>
       </c>
@@ -7275,7 +7313,7 @@
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="102">
         <f>'Nach Mannschaften sortiert'!D77</f>
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C77" s="36">
         <f>'Nach Mannschaften sortiert'!E77</f>
@@ -7289,7 +7327,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F77)</f>
         <v/>
       </c>
-      <c r="G77" s="132">
+      <c r="G77" s="115">
         <f>'Nach Mannschaften sortiert'!H77</f>
         <v>0</v>
       </c>
@@ -7314,7 +7352,7 @@
     <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="102">
         <f>'Nach Mannschaften sortiert'!D78</f>
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C78" s="36">
         <f>'Nach Mannschaften sortiert'!E78</f>
@@ -7328,7 +7366,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F78)</f>
         <v/>
       </c>
-      <c r="G78" s="132">
+      <c r="G78" s="115">
         <f>'Nach Mannschaften sortiert'!H78</f>
         <v>0</v>
       </c>
@@ -7353,7 +7391,7 @@
     <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="102">
         <f>'Nach Mannschaften sortiert'!D79</f>
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="C79" s="36">
         <f>'Nach Mannschaften sortiert'!E79</f>
@@ -7367,7 +7405,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F79)</f>
         <v/>
       </c>
-      <c r="G79" s="132">
+      <c r="G79" s="115">
         <f>'Nach Mannschaften sortiert'!H79</f>
         <v>0</v>
       </c>
@@ -7392,7 +7430,7 @@
     <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="102">
         <f>'Nach Mannschaften sortiert'!D80</f>
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="C80" s="36">
         <f>'Nach Mannschaften sortiert'!E80</f>
@@ -7406,7 +7444,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F80)</f>
         <v/>
       </c>
-      <c r="G80" s="132">
+      <c r="G80" s="115">
         <f>'Nach Mannschaften sortiert'!H80</f>
         <v>0</v>
       </c>
@@ -7431,7 +7469,7 @@
     <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="102">
         <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="C81" s="36">
         <f>'Nach Mannschaften sortiert'!E81</f>
@@ -7445,7 +7483,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F81)</f>
         <v/>
       </c>
-      <c r="G81" s="132">
+      <c r="G81" s="115">
         <f>'Nach Mannschaften sortiert'!H81</f>
         <v>0</v>
       </c>
@@ -7470,7 +7508,7 @@
     <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="102">
         <f>'Nach Mannschaften sortiert'!D82</f>
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="C82" s="36">
         <f>'Nach Mannschaften sortiert'!E82</f>
@@ -7484,7 +7522,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F82)</f>
         <v/>
       </c>
-      <c r="G82" s="132">
+      <c r="G82" s="115">
         <f>'Nach Mannschaften sortiert'!H82</f>
         <v>0</v>
       </c>
@@ -7509,7 +7547,7 @@
     <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="102">
         <f>'Nach Mannschaften sortiert'!D83</f>
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="C83" s="36">
         <f>'Nach Mannschaften sortiert'!E83</f>
@@ -7523,7 +7561,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F83)</f>
         <v/>
       </c>
-      <c r="G83" s="132">
+      <c r="G83" s="115">
         <f>'Nach Mannschaften sortiert'!H83</f>
         <v>0</v>
       </c>
@@ -7548,7 +7586,7 @@
     <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="102">
         <f>'Nach Mannschaften sortiert'!D84</f>
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C84" s="36">
         <f>'Nach Mannschaften sortiert'!E84</f>
@@ -7562,7 +7600,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F84)</f>
         <v/>
       </c>
-      <c r="G84" s="132">
+      <c r="G84" s="115">
         <f>'Nach Mannschaften sortiert'!H84</f>
         <v>0</v>
       </c>
@@ -7587,7 +7625,7 @@
     <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="102">
         <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="C85" s="36">
         <f>'Nach Mannschaften sortiert'!E85</f>
@@ -7595,13 +7633,13 @@
       </c>
       <c r="D85" s="36">
         <f t="shared" si="1"/>
-        <v>4.3750000000000004E-2</v>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E85" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F85)</f>
         <v/>
       </c>
-      <c r="G85" s="132">
+      <c r="G85" s="115">
         <f>'Nach Mannschaften sortiert'!H85</f>
         <v>0</v>
       </c>
@@ -7611,7 +7649,7 @@
       </c>
       <c r="I85" t="str">
         <f>'Nach Mannschaften sortiert'!C85</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J85" s="105" t="s">
         <v>107</v>
@@ -7626,7 +7664,7 @@
     <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="102">
         <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="C86" s="36">
         <f>'Nach Mannschaften sortiert'!E86</f>
@@ -7640,7 +7678,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F86)</f>
         <v/>
       </c>
-      <c r="G86" s="132">
+      <c r="G86" s="115">
         <f>'Nach Mannschaften sortiert'!H86</f>
         <v>0</v>
       </c>
@@ -7665,7 +7703,7 @@
     <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="102">
         <f>'Nach Mannschaften sortiert'!D87</f>
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="C87" s="36">
         <f>'Nach Mannschaften sortiert'!E87</f>
@@ -7679,7 +7717,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F87)</f>
         <v/>
       </c>
-      <c r="G87" s="132">
+      <c r="G87" s="115">
         <f>'Nach Mannschaften sortiert'!H87</f>
         <v>0</v>
       </c>
@@ -7704,7 +7742,7 @@
     <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="102">
         <f>'Nach Mannschaften sortiert'!D88</f>
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="C88" s="36">
         <f>'Nach Mannschaften sortiert'!E88</f>
@@ -7718,7 +7756,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F88)</f>
         <v/>
       </c>
-      <c r="G88" s="132">
+      <c r="G88" s="115">
         <f>'Nach Mannschaften sortiert'!H88</f>
         <v>0</v>
       </c>
@@ -7743,7 +7781,7 @@
     <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="102">
         <f>'Nach Mannschaften sortiert'!D89</f>
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C89" s="36">
         <f>'Nach Mannschaften sortiert'!E89</f>
@@ -7757,7 +7795,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F89)</f>
         <v/>
       </c>
-      <c r="G89" s="132">
+      <c r="G89" s="115">
         <f>'Nach Mannschaften sortiert'!H89</f>
         <v>0</v>
       </c>
@@ -7782,7 +7820,7 @@
     <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="102">
         <f>'Nach Mannschaften sortiert'!D90</f>
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C90" s="36">
         <f>'Nach Mannschaften sortiert'!E90</f>
@@ -7790,13 +7828,13 @@
       </c>
       <c r="D90" s="36">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E90" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F90)</f>
         <v/>
       </c>
-      <c r="G90" s="132">
+      <c r="G90" s="115">
         <f>'Nach Mannschaften sortiert'!H90</f>
         <v>0</v>
       </c>
@@ -7806,7 +7844,7 @@
       </c>
       <c r="I90" t="str">
         <f>'Nach Mannschaften sortiert'!C90</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J90" s="105" t="s">
         <v>107</v>
@@ -7821,7 +7859,7 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="102">
         <f>'Nach Mannschaften sortiert'!D91</f>
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="C91" s="36">
         <f>'Nach Mannschaften sortiert'!E91</f>
@@ -7835,7 +7873,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F91)</f>
         <v/>
       </c>
-      <c r="G91" s="132">
+      <c r="G91" s="115">
         <f>'Nach Mannschaften sortiert'!H91</f>
         <v>0</v>
       </c>
@@ -7860,7 +7898,7 @@
     <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="102">
         <f>'Nach Mannschaften sortiert'!D92</f>
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C92" s="36">
         <f>'Nach Mannschaften sortiert'!E92</f>
@@ -7874,7 +7912,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F92)</f>
         <v/>
       </c>
-      <c r="G92" s="132">
+      <c r="G92" s="115">
         <f>'Nach Mannschaften sortiert'!H92</f>
         <v>0</v>
       </c>
@@ -7899,7 +7937,7 @@
     <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="102">
         <f>'Nach Mannschaften sortiert'!D93</f>
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C93" s="36">
         <f>'Nach Mannschaften sortiert'!E93</f>
@@ -7913,7 +7951,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F93)</f>
         <v/>
       </c>
-      <c r="G93" s="132">
+      <c r="G93" s="115">
         <f>'Nach Mannschaften sortiert'!H93</f>
         <v>0</v>
       </c>
@@ -7938,7 +7976,7 @@
     <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="102">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C94" s="36">
         <f>'Nach Mannschaften sortiert'!E94</f>
@@ -7952,7 +7990,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F94)</f>
         <v/>
       </c>
-      <c r="G94" s="132">
+      <c r="G94" s="115">
         <f>'Nach Mannschaften sortiert'!H94</f>
         <v>0</v>
       </c>
@@ -7977,7 +8015,7 @@
     <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95" s="102">
         <f>'Nach Mannschaften sortiert'!D95</f>
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C95" s="36">
         <f>'Nach Mannschaften sortiert'!E95</f>
@@ -7991,7 +8029,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F95)</f>
         <v/>
       </c>
-      <c r="G95" s="132">
+      <c r="G95" s="115">
         <f>'Nach Mannschaften sortiert'!H95</f>
         <v>0</v>
       </c>
@@ -8016,7 +8054,7 @@
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="102">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C96" s="36">
         <f>'Nach Mannschaften sortiert'!E96</f>
@@ -8030,7 +8068,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F96)</f>
         <v/>
       </c>
-      <c r="G96" s="132">
+      <c r="G96" s="115">
         <f>'Nach Mannschaften sortiert'!H96</f>
         <v>0</v>
       </c>
@@ -8055,7 +8093,7 @@
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="102">
         <f>'Nach Mannschaften sortiert'!D97</f>
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C97" s="36">
         <f>'Nach Mannschaften sortiert'!E97</f>
@@ -8069,7 +8107,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F97)</f>
         <v/>
       </c>
-      <c r="G97" s="132">
+      <c r="G97" s="115">
         <f>'Nach Mannschaften sortiert'!H97</f>
         <v>0</v>
       </c>
@@ -8094,7 +8132,7 @@
     <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B98" s="102">
         <f>'Nach Mannschaften sortiert'!D98</f>
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C98" s="36">
         <f>'Nach Mannschaften sortiert'!E98</f>
@@ -8108,7 +8146,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F98)</f>
         <v/>
       </c>
-      <c r="G98" s="132">
+      <c r="G98" s="115">
         <f>'Nach Mannschaften sortiert'!H98</f>
         <v>0</v>
       </c>
@@ -8133,7 +8171,7 @@
     <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B99" s="102">
         <f>'Nach Mannschaften sortiert'!D99</f>
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="C99" s="36">
         <f>'Nach Mannschaften sortiert'!E99</f>
@@ -8147,7 +8185,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F99)</f>
         <v/>
       </c>
-      <c r="G99" s="132">
+      <c r="G99" s="115">
         <f>'Nach Mannschaften sortiert'!H99</f>
         <v>0</v>
       </c>
@@ -8172,7 +8210,7 @@
     <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100" s="102">
         <f>'Nach Mannschaften sortiert'!D100</f>
-        <v>46088</v>
+        <v>46087</v>
       </c>
       <c r="C100" s="36">
         <f>'Nach Mannschaften sortiert'!E100</f>
@@ -8186,7 +8224,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F100)</f>
         <v/>
       </c>
-      <c r="G100" s="132">
+      <c r="G100" s="115">
         <f>'Nach Mannschaften sortiert'!H100</f>
         <v>0</v>
       </c>
@@ -8196,7 +8234,7 @@
       </c>
       <c r="I100" t="str">
         <f>'Nach Mannschaften sortiert'!C100</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J100" s="105" t="s">
         <v>107</v>
@@ -8211,7 +8249,7 @@
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101" s="102">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46089</v>
+        <v>46088</v>
       </c>
       <c r="C101" s="36">
         <f>'Nach Mannschaften sortiert'!E101</f>
@@ -8225,7 +8263,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F101)</f>
         <v/>
       </c>
-      <c r="G101" s="132">
+      <c r="G101" s="115">
         <f>'Nach Mannschaften sortiert'!H101</f>
         <v>0</v>
       </c>
@@ -8250,7 +8288,7 @@
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102" s="102">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="C102" s="36">
         <f>'Nach Mannschaften sortiert'!E102</f>
@@ -8264,7 +8302,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F102)</f>
         <v/>
       </c>
-      <c r="G102" s="132">
+      <c r="G102" s="115">
         <f>'Nach Mannschaften sortiert'!H102</f>
         <v>0</v>
       </c>
@@ -8289,7 +8327,7 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="102">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C103" s="36">
         <f>'Nach Mannschaften sortiert'!E103</f>
@@ -8303,7 +8341,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F103)</f>
         <v/>
       </c>
-      <c r="G103" s="132">
+      <c r="G103" s="115">
         <f>'Nach Mannschaften sortiert'!H103</f>
         <v>0</v>
       </c>
@@ -8328,21 +8366,21 @@
     <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B104" s="102">
         <f>'Nach Mannschaften sortiert'!D104</f>
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C104" s="36">
         <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0</v>
       </c>
       <c r="D104" s="36">
-        <f>IF(I104 = "KM",C104+"1:45",IF(I104="U23",C104+"1:45",IF(I104 = "U16",C104+"1:45",IF(I104 = "U15",C104+"1:30",IF(I104 = "U14",C104+"1:30",IF(I104 = "U13",C104+"1:35",IF(I104 = "U12",C104+"1:10",IF(I104 = "U11",C104+"1:10",IF(I104 = "U10",C104+"1:03",C104+"3:00")))))))))</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E104" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F104)</f>
         <v/>
       </c>
-      <c r="G104" s="132">
+      <c r="G104" s="115">
         <f>'Nach Mannschaften sortiert'!H104</f>
         <v>0</v>
       </c>
@@ -8367,21 +8405,21 @@
     <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105" s="102">
         <f>'Nach Mannschaften sortiert'!D105</f>
-        <v>46093</v>
+        <v>46092</v>
       </c>
       <c r="C105" s="36">
         <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="D105" s="36">
-        <f t="shared" ref="D105:D126" si="2">IF(I105 = "KM",C105+"1:45",IF(I105="U23",C105+"1:45",IF(I105 = "U16",C105+"1:45",IF(I105 = "U15",C105+"1:30",IF(I105 = "U14",C105+"1:30",IF(I105 = "U13",C105+"1:35",IF(I105 = "U12",C105+"1:10",IF(I105 = "U11",C105+"1:10",IF(I105 = "U10",C105+"1:03",C105+"3:00")))))))))</f>
+        <f>IF(I105 = "KM",C105+"1:45",IF(I105="U23",C105+"1:45",IF(I105 = "U16",C105+"1:45",IF(I105 = "U15",C105+"1:30",IF(I105 = "U14",C105+"1:30",IF(I105 = "U13",C105+"1:35",IF(I105 = "U12",C105+"1:10",IF(I105 = "U11",C105+"1:10",IF(I105 = "U10",C105+"1:03",C105+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E105" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F105)</f>
         <v/>
       </c>
-      <c r="G105" s="132">
+      <c r="G105" s="115">
         <f>'Nach Mannschaften sortiert'!H105</f>
         <v>0</v>
       </c>
@@ -8391,7 +8429,7 @@
       </c>
       <c r="I105" t="str">
         <f>'Nach Mannschaften sortiert'!C105</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J105" s="105" t="s">
         <v>107</v>
@@ -8406,21 +8444,21 @@
     <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106" s="102">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="C106" s="36">
         <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="D106" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D106:D122" si="2">IF(I106 = "KM",C106+"1:45",IF(I106="U23",C106+"1:45",IF(I106 = "U16",C106+"1:45",IF(I106 = "U15",C106+"1:30",IF(I106 = "U14",C106+"1:30",IF(I106 = "U13",C106+"1:35",IF(I106 = "U12",C106+"1:10",IF(I106 = "U11",C106+"1:10",IF(I106 = "U10",C106+"1:03",C106+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E106" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F106)</f>
         <v/>
       </c>
-      <c r="G106" s="132">
+      <c r="G106" s="115">
         <f>'Nach Mannschaften sortiert'!H106</f>
         <v>0</v>
       </c>
@@ -8445,7 +8483,7 @@
     <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B107" s="102">
         <f>'Nach Mannschaften sortiert'!D107</f>
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="C107" s="36">
         <f>'Nach Mannschaften sortiert'!E107</f>
@@ -8459,7 +8497,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F107)</f>
         <v/>
       </c>
-      <c r="G107" s="132">
+      <c r="G107" s="115">
         <f>'Nach Mannschaften sortiert'!H107</f>
         <v>0</v>
       </c>
@@ -8484,7 +8522,7 @@
     <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B108" s="102">
         <f>'Nach Mannschaften sortiert'!D108</f>
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="C108" s="36">
         <f>'Nach Mannschaften sortiert'!E108</f>
@@ -8498,7 +8536,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F108)</f>
         <v/>
       </c>
-      <c r="G108" s="132">
+      <c r="G108" s="115">
         <f>'Nach Mannschaften sortiert'!H108</f>
         <v>0</v>
       </c>
@@ -8523,7 +8561,7 @@
     <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109" s="102">
         <f>'Nach Mannschaften sortiert'!D109</f>
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="C109" s="36">
         <f>'Nach Mannschaften sortiert'!E109</f>
@@ -8537,7 +8575,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F109)</f>
         <v/>
       </c>
-      <c r="G109" s="132">
+      <c r="G109" s="115">
         <f>'Nach Mannschaften sortiert'!H109</f>
         <v>0</v>
       </c>
@@ -8562,31 +8600,31 @@
     <row r="110" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B110" s="102">
         <f>'Nach Mannschaften sortiert'!D110</f>
-        <v>46230</v>
+        <v>46097</v>
       </c>
       <c r="C110" s="36">
         <f>'Nach Mannschaften sortiert'!E110</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D110" s="36">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="E110" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F110)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G110" s="132" t="str">
+        <v/>
+      </c>
+      <c r="G110" s="115">
         <f>'Nach Mannschaften sortiert'!H110</f>
-        <v>Heim</v>
-      </c>
-      <c r="H110" t="str">
+        <v>0</v>
+      </c>
+      <c r="H110">
         <f>'Nach Mannschaften sortiert'!G110</f>
-        <v>REAL MADRID CAMP</v>
+        <v>0</v>
       </c>
       <c r="I110" t="str">
         <f>'Nach Mannschaften sortiert'!C110</f>
-        <v>Camp</v>
+        <v>U7</v>
       </c>
       <c r="J110" s="105" t="s">
         <v>107</v>
@@ -8601,7 +8639,7 @@
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="102">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C111" s="36">
         <f>'Nach Mannschaften sortiert'!E111</f>
@@ -8615,7 +8653,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F111)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G111" s="132" t="str">
+      <c r="G111" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H111</f>
         <v>Heim</v>
       </c>
@@ -8640,7 +8678,7 @@
     <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112" s="102">
         <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C112" s="36">
         <f>'Nach Mannschaften sortiert'!E112</f>
@@ -8654,7 +8692,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F112)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G112" s="132" t="str">
+      <c r="G112" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H112</f>
         <v>Heim</v>
       </c>
@@ -8679,7 +8717,7 @@
     <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113" s="102">
         <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C113" s="36">
         <f>'Nach Mannschaften sortiert'!E113</f>
@@ -8693,7 +8731,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F113)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G113" s="132" t="str">
+      <c r="G113" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H113</f>
         <v>Heim</v>
       </c>
@@ -8718,7 +8756,7 @@
     <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114" s="102">
         <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="C114" s="36">
         <f>'Nach Mannschaften sortiert'!E114</f>
@@ -8732,7 +8770,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F114)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G114" s="132" t="str">
+      <c r="G114" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H114</f>
         <v>Heim</v>
       </c>
@@ -8757,7 +8795,7 @@
     <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115" s="102">
         <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="C115" s="36">
         <f>'Nach Mannschaften sortiert'!E115</f>
@@ -8771,13 +8809,13 @@
         <f>UPPER('Nach Mannschaften sortiert'!F115)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G115" s="132" t="str">
+      <c r="G115" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H115</f>
         <v>Heim</v>
       </c>
       <c r="H115" t="str">
         <f>'Nach Mannschaften sortiert'!G115</f>
-        <v>MÄDCHENCAMP</v>
+        <v>REAL MADRID CAMP</v>
       </c>
       <c r="I115" t="str">
         <f>'Nach Mannschaften sortiert'!C115</f>
@@ -8796,7 +8834,7 @@
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116" s="102">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C116" s="36">
         <f>'Nach Mannschaften sortiert'!E116</f>
@@ -8810,7 +8848,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F116)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G116" s="132" t="str">
+      <c r="G116" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H116</f>
         <v>Heim</v>
       </c>
@@ -8835,7 +8873,7 @@
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117" s="102">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="C117" s="36">
         <f>'Nach Mannschaften sortiert'!E117</f>
@@ -8849,7 +8887,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F117)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G117" s="132" t="str">
+      <c r="G117" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H117</f>
         <v>Heim</v>
       </c>
@@ -8874,7 +8912,7 @@
     <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B118" s="102">
         <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="C118" s="36">
         <f>'Nach Mannschaften sortiert'!E118</f>
@@ -8888,13 +8926,13 @@
         <f>UPPER('Nach Mannschaften sortiert'!F118)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G118" s="132" t="str">
+      <c r="G118" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H118</f>
         <v>Heim</v>
       </c>
       <c r="H118" t="str">
         <f>'Nach Mannschaften sortiert'!G118</f>
-        <v>Teco 7 Camp</v>
+        <v>MÄDCHENCAMP</v>
       </c>
       <c r="I118" t="str">
         <f>'Nach Mannschaften sortiert'!C118</f>
@@ -8913,7 +8951,7 @@
     <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B119" s="102">
         <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C119" s="36">
         <f>'Nach Mannschaften sortiert'!E119</f>
@@ -8927,7 +8965,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F119)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G119" s="132" t="str">
+      <c r="G119" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H119</f>
         <v>Heim</v>
       </c>
@@ -8952,7 +8990,7 @@
     <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B120" s="102">
         <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C120" s="36">
         <f>'Nach Mannschaften sortiert'!E120</f>
@@ -8966,7 +9004,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F120)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G120" s="132" t="str">
+      <c r="G120" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H120</f>
         <v>Heim</v>
       </c>
@@ -8991,7 +9029,7 @@
     <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B121" s="102">
         <f>'Nach Mannschaften sortiert'!D121</f>
-        <v>46256</v>
+        <v>46323</v>
       </c>
       <c r="C121" s="36">
         <f>'Nach Mannschaften sortiert'!E121</f>
@@ -9005,17 +9043,17 @@
         <f>UPPER('Nach Mannschaften sortiert'!F121)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G121" s="132" t="str">
+      <c r="G121" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H121</f>
         <v>Heim</v>
       </c>
       <c r="H121" t="str">
         <f>'Nach Mannschaften sortiert'!G121</f>
-        <v>viele Gegner</v>
+        <v>Teco 7 Camp</v>
       </c>
       <c r="I121" t="str">
         <f>'Nach Mannschaften sortiert'!C121</f>
-        <v>GGG</v>
+        <v>Camp</v>
       </c>
       <c r="J121" s="105" t="s">
         <v>107</v>
@@ -9024,6 +9062,45 @@
         <v>109</v>
       </c>
       <c r="L121" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B122" s="102">
+        <f>'Nach Mannschaften sortiert'!D122</f>
+        <v>46256</v>
+      </c>
+      <c r="C122" s="36">
+        <f>'Nach Mannschaften sortiert'!E122</f>
+        <v>0.375</v>
+      </c>
+      <c r="D122" s="36">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E122" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F122)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G122" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H122</f>
+        <v>Heim</v>
+      </c>
+      <c r="H122" t="str">
+        <f>'Nach Mannschaften sortiert'!G122</f>
+        <v>viele Gegner</v>
+      </c>
+      <c r="I122" t="str">
+        <f>'Nach Mannschaften sortiert'!C122</f>
+        <v>GGG</v>
+      </c>
+      <c r="J122" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K122" t="s">
+        <v>109</v>
+      </c>
+      <c r="L122" t="s">
         <v>145</v>
       </c>
     </row>
@@ -9274,16 +9351,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
@@ -9310,7 +9387,7 @@
       <c r="H2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="111" t="s">
+      <c r="I2" s="119" t="s">
         <v>66</v>
       </c>
       <c r="J2" s="47"/>
@@ -9330,7 +9407,7 @@
       <c r="F3" s="82"/>
       <c r="G3" s="82"/>
       <c r="H3" s="84"/>
-      <c r="I3" s="112"/>
+      <c r="I3" s="120"/>
       <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9350,7 +9427,7 @@
       </c>
       <c r="G4" s="82"/>
       <c r="H4" s="84"/>
-      <c r="I4" s="112"/>
+      <c r="I4" s="120"/>
       <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9370,7 +9447,7 @@
       </c>
       <c r="G5" s="82"/>
       <c r="H5" s="84"/>
-      <c r="I5" s="112"/>
+      <c r="I5" s="120"/>
       <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9390,7 +9467,7 @@
       </c>
       <c r="G6" s="86"/>
       <c r="H6" s="84"/>
-      <c r="I6" s="112"/>
+      <c r="I6" s="120"/>
       <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9412,7 +9489,7 @@
         <v>56</v>
       </c>
       <c r="H7" s="84"/>
-      <c r="I7" s="112"/>
+      <c r="I7" s="120"/>
       <c r="J7" s="47"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9434,7 +9511,7 @@
         <v>56</v>
       </c>
       <c r="H8" s="84"/>
-      <c r="I8" s="112"/>
+      <c r="I8" s="120"/>
       <c r="J8" s="47"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -9458,7 +9535,7 @@
       <c r="H9" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="112"/>
+      <c r="I9" s="120"/>
       <c r="J9" s="47"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9480,7 +9557,7 @@
         <v>94</v>
       </c>
       <c r="H10" s="84"/>
-      <c r="I10" s="112"/>
+      <c r="I10" s="120"/>
       <c r="J10" s="47"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" thickBot="1" x14ac:dyDescent="0.4">
@@ -9500,7 +9577,7 @@
         <v>65</v>
       </c>
       <c r="H11" s="93"/>
-      <c r="I11" s="113"/>
+      <c r="I11" s="121"/>
       <c r="J11" s="47"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
@@ -9558,52 +9635,52 @@
       <c r="H14" s="100"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="126"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="119" t="s">
+      <c r="A16" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="121"/>
+      <c r="B16" s="128"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="129"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="122" t="s">
+      <c r="A17" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="123"/>
-      <c r="E17" s="123"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="123"/>
-      <c r="H17" s="124"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="132"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="108" t="s">
+      <c r="A18" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="110"/>
+      <c r="B18" s="117"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="118"/>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -9673,783 +9750,783 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <f>'Nach Mannschaften sortiert'!A9</f>
+        <f>'Nach Mannschaften sortiert'!A10</f>
         <v>8</v>
       </c>
       <c r="B2" s="2">
-        <f>'Nach Mannschaften sortiert'!B9</f>
+        <f>'Nach Mannschaften sortiert'!B10</f>
         <v>1</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C9</f>
+        <f>'Nach Mannschaften sortiert'!C10</f>
         <v>KM</v>
       </c>
       <c r="D2" s="13">
-        <f>'Nach Mannschaften sortiert'!D9</f>
+        <f>'Nach Mannschaften sortiert'!D10</f>
         <v>46249</v>
       </c>
       <c r="E2" s="35">
-        <f>'Nach Mannschaften sortiert'!E9</f>
+        <f>'Nach Mannschaften sortiert'!E10</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="F2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F9</f>
+        <f>'Nach Mannschaften sortiert'!F10</f>
         <v>Kittsee</v>
       </c>
       <c r="G2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G9</f>
+        <f>'Nach Mannschaften sortiert'!G10</f>
         <v>Kittsee</v>
       </c>
       <c r="H2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H9</f>
+        <f>'Nach Mannschaften sortiert'!H10</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <f>'Nach Mannschaften sortiert'!A10</f>
+        <f>'Nach Mannschaften sortiert'!A11</f>
         <v>9</v>
       </c>
       <c r="B3" s="2">
-        <f>'Nach Mannschaften sortiert'!B10</f>
+        <f>'Nach Mannschaften sortiert'!B11</f>
         <v>2</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C10</f>
+        <f>'Nach Mannschaften sortiert'!C11</f>
         <v>KM</v>
       </c>
       <c r="D3" s="13">
-        <f>'Nach Mannschaften sortiert'!D10</f>
+        <f>'Nach Mannschaften sortiert'!D11</f>
         <v>46256</v>
       </c>
       <c r="E3" s="35">
-        <f>'Nach Mannschaften sortiert'!E10</f>
+        <f>'Nach Mannschaften sortiert'!E11</f>
         <v>0.70833333333333337</v>
       </c>
       <c r="F3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F10</f>
+        <f>'Nach Mannschaften sortiert'!F11</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="G3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G10</f>
+        <f>'Nach Mannschaften sortiert'!G11</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="H3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H10</f>
+        <f>'Nach Mannschaften sortiert'!H11</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <f>'Nach Mannschaften sortiert'!A11</f>
+        <f>'Nach Mannschaften sortiert'!A12</f>
         <v>10</v>
       </c>
       <c r="B4" s="2">
-        <f>'Nach Mannschaften sortiert'!B11</f>
+        <f>'Nach Mannschaften sortiert'!B12</f>
         <v>3</v>
       </c>
       <c r="C4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C11</f>
+        <f>'Nach Mannschaften sortiert'!C12</f>
         <v>KM</v>
       </c>
       <c r="D4" s="13">
-        <f>'Nach Mannschaften sortiert'!D11</f>
+        <f>'Nach Mannschaften sortiert'!D12</f>
         <v>46263</v>
       </c>
       <c r="E4" s="35">
-        <f>'Nach Mannschaften sortiert'!E11</f>
+        <f>'Nach Mannschaften sortiert'!E12</f>
         <v>0.70833333333333337</v>
       </c>
       <c r="F4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F11</f>
+        <f>'Nach Mannschaften sortiert'!F12</f>
         <v>Neufeld</v>
       </c>
       <c r="G4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G11</f>
+        <f>'Nach Mannschaften sortiert'!G12</f>
         <v>Tadten</v>
       </c>
       <c r="H4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H11</f>
+        <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <f>'Nach Mannschaften sortiert'!A45</f>
+        <f>'Nach Mannschaften sortiert'!A46</f>
         <v>44</v>
       </c>
       <c r="B5" s="2">
-        <f>'Nach Mannschaften sortiert'!B45</f>
+        <f>'Nach Mannschaften sortiert'!B46</f>
         <v>1</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C45</f>
+        <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U14</v>
       </c>
       <c r="D5" s="13">
-        <f>'Nach Mannschaften sortiert'!D45</f>
+        <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46033</v>
       </c>
       <c r="E5" s="35">
-        <f>'Nach Mannschaften sortiert'!E45</f>
+        <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <f>'Nach Mannschaften sortiert'!F45</f>
+        <f>'Nach Mannschaften sortiert'!F46</f>
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <f>'Nach Mannschaften sortiert'!G45</f>
+        <f>'Nach Mannschaften sortiert'!G46</f>
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f>'Nach Mannschaften sortiert'!H45</f>
+        <f>'Nach Mannschaften sortiert'!H46</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
+        <f>'Nach Mannschaften sortiert'!A14</f>
+        <v>12</v>
+      </c>
+      <c r="B6" s="2">
+        <f>'Nach Mannschaften sortiert'!B14</f>
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C14</f>
+        <v>KM</v>
+      </c>
+      <c r="D6" s="13">
+        <f>'Nach Mannschaften sortiert'!D14</f>
+        <v>46277</v>
+      </c>
+      <c r="E6" s="35">
+        <f>'Nach Mannschaften sortiert'!E14</f>
+        <v>0.6875</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F14</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G14</f>
+        <v>Winden</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H14</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <f>'Nach Mannschaften sortiert'!A56</f>
+        <v>54</v>
+      </c>
+      <c r="B7" s="2">
+        <f>'Nach Mannschaften sortiert'!B56</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C56</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D7" s="13">
+        <f>'Nach Mannschaften sortiert'!D56</f>
+        <v>46043</v>
+      </c>
+      <c r="E7" s="35">
+        <f>'Nach Mannschaften sortiert'!E56</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <f>'Nach Mannschaften sortiert'!F56</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <f>'Nach Mannschaften sortiert'!G56</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <f>'Nach Mannschaften sortiert'!H56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <f>'Nach Mannschaften sortiert'!A16</f>
+        <v>14</v>
+      </c>
+      <c r="B8" s="2">
+        <f>'Nach Mannschaften sortiert'!B16</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C16</f>
+        <v>KM</v>
+      </c>
+      <c r="D8" s="13">
+        <f>'Nach Mannschaften sortiert'!D16</f>
+        <v>46291</v>
+      </c>
+      <c r="E8" s="35">
+        <f>'Nach Mannschaften sortiert'!E16</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F16</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G16</f>
+        <v>Wallern</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H16</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="63">
+        <f>'Nach Mannschaften sortiert'!A111</f>
+        <v>109</v>
+      </c>
+      <c r="B9" s="63">
+        <f>'Nach Mannschaften sortiert'!B111</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!C111</f>
+        <v>Camp</v>
+      </c>
+      <c r="D9" s="64">
+        <f>'Nach Mannschaften sortiert'!D111</f>
+        <v>46230</v>
+      </c>
+      <c r="E9" s="65">
+        <f>'Nach Mannschaften sortiert'!E111</f>
+        <v>0.375</v>
+      </c>
+      <c r="F9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!F111</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!G111</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!H111</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <f>'Nach Mannschaften sortiert'!A18</f>
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <f>'Nach Mannschaften sortiert'!B18</f>
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C18</f>
+        <v>KM</v>
+      </c>
+      <c r="D10" s="13">
+        <f>'Nach Mannschaften sortiert'!D18</f>
+        <v>46305</v>
+      </c>
+      <c r="E10" s="35">
+        <f>'Nach Mannschaften sortiert'!E18</f>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F18</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G18</f>
+        <v>Wimpassing</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H18</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="63">
+        <f>'Nach Mannschaften sortiert'!A112</f>
+        <v>110</v>
+      </c>
+      <c r="B11" s="63">
+        <f>'Nach Mannschaften sortiert'!B112</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!C112</f>
+        <v>Camp</v>
+      </c>
+      <c r="D11" s="64">
+        <f>'Nach Mannschaften sortiert'!D112</f>
+        <v>46231</v>
+      </c>
+      <c r="E11" s="65">
+        <f>'Nach Mannschaften sortiert'!E112</f>
+        <v>0.375</v>
+      </c>
+      <c r="F11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!F112</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!G112</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!H112</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <f>'Nach Mannschaften sortiert'!A20</f>
+        <v>18</v>
+      </c>
+      <c r="B12" s="2">
+        <f>'Nach Mannschaften sortiert'!B20</f>
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C20</f>
+        <v>KM</v>
+      </c>
+      <c r="D12" s="13">
+        <f>'Nach Mannschaften sortiert'!D20</f>
+        <v>46319</v>
+      </c>
+      <c r="E12" s="35">
+        <f>'Nach Mannschaften sortiert'!E20</f>
+        <v>0.625</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F20</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G20</f>
+        <v>Gols</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H20</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <f>'Nach Mannschaften sortiert'!A21</f>
+        <v>19</v>
+      </c>
+      <c r="B13" s="2">
+        <f>'Nach Mannschaften sortiert'!B21</f>
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C21</f>
+        <v>KM</v>
+      </c>
+      <c r="D13" s="13">
+        <f>'Nach Mannschaften sortiert'!D21</f>
+        <v>46326</v>
+      </c>
+      <c r="E13" s="35">
+        <f>'Nach Mannschaften sortiert'!E21</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F21</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G21</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="H13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H21</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="63">
+        <f>'Nach Mannschaften sortiert'!A113</f>
+        <v>111</v>
+      </c>
+      <c r="B14" s="63">
+        <f>'Nach Mannschaften sortiert'!B113</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!C113</f>
+        <v>Camp</v>
+      </c>
+      <c r="D14" s="64">
+        <f>'Nach Mannschaften sortiert'!D113</f>
+        <v>46232</v>
+      </c>
+      <c r="E14" s="65">
+        <f>'Nach Mannschaften sortiert'!E113</f>
+        <v>0.375</v>
+      </c>
+      <c r="F14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!F113</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!G113</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!H113</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <f>'Nach Mannschaften sortiert'!A36</f>
+        <v>34</v>
+      </c>
+      <c r="B15" s="2">
+        <f>'Nach Mannschaften sortiert'!B36</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C36</f>
+        <v>U16</v>
+      </c>
+      <c r="D15" s="13">
+        <f>'Nach Mannschaften sortiert'!D36</f>
+        <v>46023</v>
+      </c>
+      <c r="E15" s="35">
+        <f>'Nach Mannschaften sortiert'!E36</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <f>'Nach Mannschaften sortiert'!F36</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <f>'Nach Mannschaften sortiert'!G36</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <f>'Nach Mannschaften sortiert'!H36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="57">
+        <f>'Nach Mannschaften sortiert'!A37</f>
+        <v>35</v>
+      </c>
+      <c r="B16" s="57">
+        <f>'Nach Mannschaften sortiert'!B37</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!C37</f>
+        <v>U16</v>
+      </c>
+      <c r="D16" s="58">
+        <f>'Nach Mannschaften sortiert'!D37</f>
+        <v>46024</v>
+      </c>
+      <c r="E16" s="59">
+        <f>'Nach Mannschaften sortiert'!E37</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="57">
+        <f>'Nach Mannschaften sortiert'!F37</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="57">
+        <f>'Nach Mannschaften sortiert'!G37</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="57">
+        <f>'Nach Mannschaften sortiert'!H37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <f>'Nach Mannschaften sortiert'!A38</f>
+        <v>36</v>
+      </c>
+      <c r="B17" s="2">
+        <f>'Nach Mannschaften sortiert'!B38</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C38</f>
+        <v>U16</v>
+      </c>
+      <c r="D17" s="13">
+        <f>'Nach Mannschaften sortiert'!D38</f>
+        <v>46025</v>
+      </c>
+      <c r="E17" s="35">
+        <f>'Nach Mannschaften sortiert'!E38</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f>'Nach Mannschaften sortiert'!F38</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <f>'Nach Mannschaften sortiert'!G38</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <f>'Nach Mannschaften sortiert'!H38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <f>'Nach Mannschaften sortiert'!A13</f>
-        <v>12</v>
-      </c>
-      <c r="B6" s="2">
+        <v>11</v>
+      </c>
+      <c r="B18" s="2">
         <f>'Nach Mannschaften sortiert'!B13</f>
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!C13</f>
         <v>KM</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D18" s="13">
         <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>46277</v>
-      </c>
-      <c r="E6" s="35">
+        <v>46270</v>
+      </c>
+      <c r="E18" s="35">
         <f>'Nach Mannschaften sortiert'!E13</f>
         <v>0.6875</v>
       </c>
-      <c r="F6" s="2" t="str">
+      <c r="F18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F13</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G6" s="2" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="G18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>Winden</v>
-      </c>
-      <c r="H6" s="2" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="H18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <f>'Nach Mannschaften sortiert'!A55</f>
-        <v>54</v>
-      </c>
-      <c r="B7" s="2">
-        <f>'Nach Mannschaften sortiert'!B55</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C55</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D7" s="13">
-        <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46043</v>
-      </c>
-      <c r="E7" s="35">
-        <f>'Nach Mannschaften sortiert'!E55</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <f>'Nach Mannschaften sortiert'!F55</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <f>'Nach Mannschaften sortiert'!G55</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <f>'Nach Mannschaften sortiert'!H55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <f>'Nach Mannschaften sortiert'!A15</f>
-        <v>14</v>
-      </c>
-      <c r="B8" s="2">
-        <f>'Nach Mannschaften sortiert'!B15</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C15</f>
-        <v>KM</v>
-      </c>
-      <c r="D8" s="13">
-        <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46291</v>
-      </c>
-      <c r="E8" s="35">
-        <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F15</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Wallern</v>
-      </c>
-      <c r="H8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H15</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="63">
-        <f>'Nach Mannschaften sortiert'!A110</f>
-        <v>109</v>
-      </c>
-      <c r="B9" s="63">
-        <f>'Nach Mannschaften sortiert'!B110</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C110</f>
-        <v>Camp</v>
-      </c>
-      <c r="D9" s="64">
-        <f>'Nach Mannschaften sortiert'!D110</f>
-        <v>46230</v>
-      </c>
-      <c r="E9" s="65">
-        <f>'Nach Mannschaften sortiert'!E110</f>
-        <v>0.375</v>
-      </c>
-      <c r="F9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!F110</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!G110</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!H110</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <f>'Nach Mannschaften sortiert'!A17</f>
-        <v>16</v>
-      </c>
-      <c r="B10" s="2">
-        <f>'Nach Mannschaften sortiert'!B17</f>
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
-        <v>KM</v>
-      </c>
-      <c r="D10" s="13">
-        <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46305</v>
-      </c>
-      <c r="E10" s="35">
-        <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="F10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F17</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Wimpassing</v>
-      </c>
-      <c r="H10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="63">
-        <f>'Nach Mannschaften sortiert'!A111</f>
-        <v>110</v>
-      </c>
-      <c r="B11" s="63">
-        <f>'Nach Mannschaften sortiert'!B111</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C111</f>
-        <v>Camp</v>
-      </c>
-      <c r="D11" s="64">
-        <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46231</v>
-      </c>
-      <c r="E11" s="65">
-        <f>'Nach Mannschaften sortiert'!E111</f>
-        <v>0.375</v>
-      </c>
-      <c r="F11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!F111</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!G111</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!H111</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <f>'Nach Mannschaften sortiert'!A19</f>
-        <v>18</v>
-      </c>
-      <c r="B12" s="2">
-        <f>'Nach Mannschaften sortiert'!B19</f>
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C19</f>
-        <v>KM</v>
-      </c>
-      <c r="D12" s="13">
-        <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46319</v>
-      </c>
-      <c r="E12" s="35">
-        <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.625</v>
-      </c>
-      <c r="F12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F19</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Gols</v>
-      </c>
-      <c r="H12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <f>'Nach Mannschaften sortiert'!A20</f>
-        <v>19</v>
-      </c>
-      <c r="B13" s="2">
-        <f>'Nach Mannschaften sortiert'!B20</f>
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C20</f>
-        <v>KM</v>
-      </c>
-      <c r="D13" s="13">
-        <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46326</v>
-      </c>
-      <c r="E13" s="35">
-        <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F20</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="G13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="H13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="63">
-        <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>111</v>
-      </c>
-      <c r="B14" s="63">
-        <f>'Nach Mannschaften sortiert'!B112</f>
-        <v>3</v>
-      </c>
-      <c r="C14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C112</f>
-        <v>Camp</v>
-      </c>
-      <c r="D14" s="64">
-        <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46232</v>
-      </c>
-      <c r="E14" s="65">
-        <f>'Nach Mannschaften sortiert'!E112</f>
-        <v>0.375</v>
-      </c>
-      <c r="F14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!F112</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!G112</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!H112</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <f>'Nach Mannschaften sortiert'!A35</f>
-        <v>34</v>
-      </c>
-      <c r="B15" s="2">
-        <f>'Nach Mannschaften sortiert'!B35</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C35</f>
-        <v>U16</v>
-      </c>
-      <c r="D15" s="13">
-        <f>'Nach Mannschaften sortiert'!D35</f>
-        <v>46023</v>
-      </c>
-      <c r="E15" s="35">
-        <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f>'Nach Mannschaften sortiert'!F35</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <f>'Nach Mannschaften sortiert'!G35</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <f>'Nach Mannschaften sortiert'!H35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57">
-        <f>'Nach Mannschaften sortiert'!A36</f>
-        <v>35</v>
-      </c>
-      <c r="B16" s="57">
-        <f>'Nach Mannschaften sortiert'!B36</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C36</f>
-        <v>U16</v>
-      </c>
-      <c r="D16" s="58">
-        <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46024</v>
-      </c>
-      <c r="E16" s="59">
-        <f>'Nach Mannschaften sortiert'!E36</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="57">
-        <f>'Nach Mannschaften sortiert'!F36</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="57">
-        <f>'Nach Mannschaften sortiert'!G36</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="57">
-        <f>'Nach Mannschaften sortiert'!H36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <f>'Nach Mannschaften sortiert'!A37</f>
-        <v>36</v>
-      </c>
-      <c r="B17" s="2">
-        <f>'Nach Mannschaften sortiert'!B37</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C37</f>
-        <v>U16</v>
-      </c>
-      <c r="D17" s="13">
-        <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46025</v>
-      </c>
-      <c r="E17" s="35">
-        <f>'Nach Mannschaften sortiert'!E37</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f>'Nach Mannschaften sortiert'!F37</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <f>'Nach Mannschaften sortiert'!G37</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <f>'Nach Mannschaften sortiert'!H37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <f>'Nach Mannschaften sortiert'!A12</f>
-        <v>11</v>
-      </c>
-      <c r="B18" s="2">
-        <f>'Nach Mannschaften sortiert'!B12</f>
-        <v>4</v>
-      </c>
-      <c r="C18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C12</f>
-        <v>KM</v>
-      </c>
-      <c r="D18" s="13">
-        <f>'Nach Mannschaften sortiert'!D12</f>
-        <v>46270</v>
-      </c>
-      <c r="E18" s="35">
-        <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0.6875</v>
-      </c>
-      <c r="F18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F12</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="G18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G12</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="H18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <f>'Nach Mannschaften sortiert'!A39</f>
+        <f>'Nach Mannschaften sortiert'!A40</f>
         <v>38</v>
       </c>
       <c r="B19" s="2">
-        <f>'Nach Mannschaften sortiert'!B39</f>
+        <f>'Nach Mannschaften sortiert'!B40</f>
         <v>5</v>
       </c>
       <c r="C19" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C39</f>
+        <f>'Nach Mannschaften sortiert'!C40</f>
         <v>U16</v>
       </c>
       <c r="D19" s="13">
-        <f>'Nach Mannschaften sortiert'!D39</f>
+        <f>'Nach Mannschaften sortiert'!D40</f>
         <v>46027</v>
       </c>
       <c r="E19" s="35">
-        <f>'Nach Mannschaften sortiert'!E39</f>
+        <f>'Nach Mannschaften sortiert'!E40</f>
         <v>0</v>
       </c>
       <c r="F19" s="2">
-        <f>'Nach Mannschaften sortiert'!F39</f>
+        <f>'Nach Mannschaften sortiert'!F40</f>
         <v>0</v>
       </c>
       <c r="G19" s="2">
-        <f>'Nach Mannschaften sortiert'!G39</f>
+        <f>'Nach Mannschaften sortiert'!G40</f>
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <f>'Nach Mannschaften sortiert'!H39</f>
+        <f>'Nach Mannschaften sortiert'!H40</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="54">
-        <f>'Nach Mannschaften sortiert'!A40</f>
+        <f>'Nach Mannschaften sortiert'!A41</f>
         <v>39</v>
       </c>
       <c r="B20" s="54">
-        <f>'Nach Mannschaften sortiert'!B40</f>
+        <f>'Nach Mannschaften sortiert'!B41</f>
         <v>6</v>
       </c>
       <c r="C20" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C40</f>
+        <f>'Nach Mannschaften sortiert'!C41</f>
         <v>U16</v>
       </c>
       <c r="D20" s="55">
-        <f>'Nach Mannschaften sortiert'!D40</f>
+        <f>'Nach Mannschaften sortiert'!D41</f>
         <v>46028</v>
       </c>
       <c r="E20" s="56">
-        <f>'Nach Mannschaften sortiert'!E40</f>
+        <f>'Nach Mannschaften sortiert'!E41</f>
         <v>0</v>
       </c>
       <c r="F20" s="54">
-        <f>'Nach Mannschaften sortiert'!F40</f>
+        <f>'Nach Mannschaften sortiert'!F41</f>
         <v>0</v>
       </c>
       <c r="G20" s="54">
-        <f>'Nach Mannschaften sortiert'!G40</f>
+        <f>'Nach Mannschaften sortiert'!G41</f>
         <v>0</v>
       </c>
       <c r="H20" s="54">
-        <f>'Nach Mannschaften sortiert'!H40</f>
+        <f>'Nach Mannschaften sortiert'!H41</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <f>'Nach Mannschaften sortiert'!A41</f>
+        <f>'Nach Mannschaften sortiert'!A42</f>
         <v>40</v>
       </c>
       <c r="B21" s="2">
-        <f>'Nach Mannschaften sortiert'!B41</f>
+        <f>'Nach Mannschaften sortiert'!B42</f>
         <v>7</v>
       </c>
       <c r="C21" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C41</f>
+        <f>'Nach Mannschaften sortiert'!C42</f>
         <v>U16</v>
       </c>
       <c r="D21" s="13">
-        <f>'Nach Mannschaften sortiert'!D41</f>
+        <f>'Nach Mannschaften sortiert'!D42</f>
         <v>46029</v>
       </c>
       <c r="E21" s="35">
-        <f>'Nach Mannschaften sortiert'!E41</f>
+        <f>'Nach Mannschaften sortiert'!E42</f>
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <f>'Nach Mannschaften sortiert'!F41</f>
+        <f>'Nach Mannschaften sortiert'!F42</f>
         <v>0</v>
       </c>
       <c r="G21" s="2">
-        <f>'Nach Mannschaften sortiert'!G41</f>
+        <f>'Nach Mannschaften sortiert'!G42</f>
         <v>0</v>
       </c>
       <c r="H21" s="2">
-        <f>'Nach Mannschaften sortiert'!H41</f>
+        <f>'Nach Mannschaften sortiert'!H42</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="57">
-        <f>'Nach Mannschaften sortiert'!A42</f>
+        <f>'Nach Mannschaften sortiert'!A43</f>
         <v>41</v>
       </c>
       <c r="B22" s="57">
-        <f>'Nach Mannschaften sortiert'!B42</f>
+        <f>'Nach Mannschaften sortiert'!B43</f>
         <v>8</v>
       </c>
       <c r="C22" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C42</f>
+        <f>'Nach Mannschaften sortiert'!C43</f>
         <v>U16</v>
       </c>
       <c r="D22" s="58">
-        <f>'Nach Mannschaften sortiert'!D42</f>
+        <f>'Nach Mannschaften sortiert'!D43</f>
         <v>46030</v>
       </c>
       <c r="E22" s="59">
-        <f>'Nach Mannschaften sortiert'!E42</f>
+        <f>'Nach Mannschaften sortiert'!E43</f>
         <v>0</v>
       </c>
       <c r="F22" s="57">
-        <f>'Nach Mannschaften sortiert'!F42</f>
+        <f>'Nach Mannschaften sortiert'!F43</f>
         <v>0</v>
       </c>
       <c r="G22" s="57">
-        <f>'Nach Mannschaften sortiert'!G42</f>
+        <f>'Nach Mannschaften sortiert'!G43</f>
         <v>0</v>
       </c>
       <c r="H22" s="57">
-        <f>'Nach Mannschaften sortiert'!H42</f>
+        <f>'Nach Mannschaften sortiert'!H43</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <f>'Nach Mannschaften sortiert'!A43</f>
+        <f>'Nach Mannschaften sortiert'!A44</f>
         <v>42</v>
       </c>
       <c r="B23" s="2">
-        <f>'Nach Mannschaften sortiert'!B43</f>
+        <f>'Nach Mannschaften sortiert'!B44</f>
         <v>9</v>
       </c>
       <c r="C23" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C43</f>
+        <f>'Nach Mannschaften sortiert'!C44</f>
         <v>U16</v>
       </c>
       <c r="D23" s="13">
-        <f>'Nach Mannschaften sortiert'!D43</f>
+        <f>'Nach Mannschaften sortiert'!D44</f>
         <v>46031</v>
       </c>
       <c r="E23" s="35">
-        <f>'Nach Mannschaften sortiert'!E43</f>
+        <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="F23" s="2">
-        <f>'Nach Mannschaften sortiert'!F43</f>
+        <f>'Nach Mannschaften sortiert'!F44</f>
         <v>0</v>
       </c>
       <c r="G23" s="2">
-        <f>'Nach Mannschaften sortiert'!G43</f>
+        <f>'Nach Mannschaften sortiert'!G44</f>
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <f>'Nach Mannschaften sortiert'!H43</f>
+        <f>'Nach Mannschaften sortiert'!H44</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="60">
-        <f>'Nach Mannschaften sortiert'!A90</f>
+        <f>'Nach Mannschaften sortiert'!A91</f>
         <v>89</v>
       </c>
       <c r="B24" s="60">
-        <f>'Nach Mannschaften sortiert'!B90</f>
+        <f>'Nach Mannschaften sortiert'!B91</f>
         <v>1</v>
       </c>
       <c r="C24" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C90</f>
+        <f>'Nach Mannschaften sortiert'!C91</f>
         <v>U9</v>
       </c>
       <c r="D24" s="61">
-        <f>'Nach Mannschaften sortiert'!D90</f>
+        <f>'Nach Mannschaften sortiert'!D91</f>
         <v>46078</v>
       </c>
       <c r="E24" s="62">
-        <f>'Nach Mannschaften sortiert'!E90</f>
+        <f>'Nach Mannschaften sortiert'!E91</f>
         <v>0</v>
       </c>
       <c r="F24" s="60">
-        <f>'Nach Mannschaften sortiert'!F90</f>
+        <f>'Nach Mannschaften sortiert'!F91</f>
         <v>0</v>
       </c>
       <c r="G24" s="60">
-        <f>'Nach Mannschaften sortiert'!G90</f>
+        <f>'Nach Mannschaften sortiert'!G91</f>
         <v>0</v>
       </c>
       <c r="H24" s="60">
-        <f>'Nach Mannschaften sortiert'!H90</f>
+        <f>'Nach Mannschaften sortiert'!H91</f>
         <v>0</v>
       </c>
     </row>
@@ -10489,35 +10566,35 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="60">
-        <f>'Nach Mannschaften sortiert'!A100</f>
+        <f>'Nach Mannschaften sortiert'!A101</f>
         <v>99</v>
       </c>
       <c r="B26" s="60">
-        <f>'Nach Mannschaften sortiert'!B100</f>
+        <f>'Nach Mannschaften sortiert'!B101</f>
         <v>1</v>
       </c>
       <c r="C26" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C100</f>
+        <f>'Nach Mannschaften sortiert'!C101</f>
         <v>U8</v>
       </c>
       <c r="D26" s="61">
-        <f>'Nach Mannschaften sortiert'!D100</f>
+        <f>'Nach Mannschaften sortiert'!D101</f>
         <v>46088</v>
       </c>
       <c r="E26" s="62">
-        <f>'Nach Mannschaften sortiert'!E100</f>
+        <f>'Nach Mannschaften sortiert'!E101</f>
         <v>0</v>
       </c>
       <c r="F26" s="60">
-        <f>'Nach Mannschaften sortiert'!F100</f>
+        <f>'Nach Mannschaften sortiert'!F101</f>
         <v>0</v>
       </c>
       <c r="G26" s="60">
-        <f>'Nach Mannschaften sortiert'!G100</f>
+        <f>'Nach Mannschaften sortiert'!G101</f>
         <v>0</v>
       </c>
       <c r="H26" s="60">
-        <f>'Nach Mannschaften sortiert'!H100</f>
+        <f>'Nach Mannschaften sortiert'!H101</f>
         <v>0</v>
       </c>
     </row>
@@ -10591,35 +10668,35 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="60">
-        <f>'Nach Mannschaften sortiert'!A105</f>
+        <f>'Nach Mannschaften sortiert'!A106</f>
         <v>104</v>
       </c>
       <c r="B29" s="60">
-        <f>'Nach Mannschaften sortiert'!B105</f>
+        <f>'Nach Mannschaften sortiert'!B106</f>
         <v>1</v>
       </c>
       <c r="C29" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C105</f>
+        <f>'Nach Mannschaften sortiert'!C106</f>
         <v>U7</v>
       </c>
       <c r="D29" s="61">
-        <f>'Nach Mannschaften sortiert'!D105</f>
+        <f>'Nach Mannschaften sortiert'!D106</f>
         <v>46093</v>
       </c>
       <c r="E29" s="62">
-        <f>'Nach Mannschaften sortiert'!E105</f>
+        <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="F29" s="60">
-        <f>'Nach Mannschaften sortiert'!F105</f>
+        <f>'Nach Mannschaften sortiert'!F106</f>
         <v>0</v>
       </c>
       <c r="G29" s="60">
-        <f>'Nach Mannschaften sortiert'!G105</f>
+        <f>'Nach Mannschaften sortiert'!G106</f>
         <v>0</v>
       </c>
       <c r="H29" s="60">
-        <f>'Nach Mannschaften sortiert'!H105</f>
+        <f>'Nach Mannschaften sortiert'!H106</f>
         <v>0</v>
       </c>
     </row>
@@ -10795,103 +10872,103 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="60">
-        <f>'Nach Mannschaften sortiert'!A76</f>
+        <f>'Nach Mannschaften sortiert'!A77</f>
         <v>75</v>
       </c>
       <c r="B35" s="60">
-        <f>'Nach Mannschaften sortiert'!B76</f>
+        <f>'Nach Mannschaften sortiert'!B77</f>
         <v>2</v>
       </c>
       <c r="C35" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C76</f>
+        <f>'Nach Mannschaften sortiert'!C77</f>
         <v>U11</v>
       </c>
       <c r="D35" s="61">
-        <f>'Nach Mannschaften sortiert'!D76</f>
+        <f>'Nach Mannschaften sortiert'!D77</f>
         <v>46064</v>
       </c>
       <c r="E35" s="62">
-        <f>'Nach Mannschaften sortiert'!E76</f>
+        <f>'Nach Mannschaften sortiert'!E77</f>
         <v>0</v>
       </c>
       <c r="F35" s="60">
-        <f>'Nach Mannschaften sortiert'!F76</f>
+        <f>'Nach Mannschaften sortiert'!F77</f>
         <v>0</v>
       </c>
       <c r="G35" s="60">
-        <f>'Nach Mannschaften sortiert'!G76</f>
+        <f>'Nach Mannschaften sortiert'!G77</f>
         <v>0</v>
       </c>
       <c r="H35" s="60">
-        <f>'Nach Mannschaften sortiert'!H76</f>
+        <f>'Nach Mannschaften sortiert'!H77</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <f>'Nach Mannschaften sortiert'!A46</f>
+        <f>'Nach Mannschaften sortiert'!A47</f>
         <v>45</v>
       </c>
       <c r="B36" s="2">
-        <f>'Nach Mannschaften sortiert'!B46</f>
+        <f>'Nach Mannschaften sortiert'!B47</f>
         <v>2</v>
       </c>
       <c r="C36" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C46</f>
+        <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U14</v>
       </c>
       <c r="D36" s="13">
-        <f>'Nach Mannschaften sortiert'!D46</f>
+        <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46034</v>
       </c>
       <c r="E36" s="35">
-        <f>'Nach Mannschaften sortiert'!E46</f>
+        <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <f>'Nach Mannschaften sortiert'!F46</f>
+        <f>'Nach Mannschaften sortiert'!F47</f>
         <v>0</v>
       </c>
       <c r="G36" s="2">
-        <f>'Nach Mannschaften sortiert'!G46</f>
+        <f>'Nach Mannschaften sortiert'!G47</f>
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <f>'Nach Mannschaften sortiert'!H46</f>
+        <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <f>'Nach Mannschaften sortiert'!A47</f>
+        <f>'Nach Mannschaften sortiert'!A48</f>
         <v>46</v>
       </c>
       <c r="B37" s="2">
-        <f>'Nach Mannschaften sortiert'!B47</f>
+        <f>'Nach Mannschaften sortiert'!B48</f>
         <v>3</v>
       </c>
       <c r="C37" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C47</f>
+        <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U14</v>
       </c>
       <c r="D37" s="13">
-        <f>'Nach Mannschaften sortiert'!D47</f>
+        <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46035</v>
       </c>
       <c r="E37" s="35">
-        <f>'Nach Mannschaften sortiert'!E47</f>
+        <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <f>'Nach Mannschaften sortiert'!F47</f>
+        <f>'Nach Mannschaften sortiert'!F48</f>
         <v>0</v>
       </c>
       <c r="G37" s="2">
-        <f>'Nach Mannschaften sortiert'!G47</f>
+        <f>'Nach Mannschaften sortiert'!G48</f>
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <f>'Nach Mannschaften sortiert'!H47</f>
+        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
@@ -10965,205 +11042,205 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
+        <f>'Nach Mannschaften sortiert'!A50</f>
+        <v>48</v>
+      </c>
+      <c r="B40" s="2">
+        <f>'Nach Mannschaften sortiert'!B50</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C50</f>
+        <v>U14</v>
+      </c>
+      <c r="D40" s="13">
+        <f>'Nach Mannschaften sortiert'!D50</f>
+        <v>46037</v>
+      </c>
+      <c r="E40" s="35">
+        <f>'Nach Mannschaften sortiert'!E50</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <f>'Nach Mannschaften sortiert'!F50</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
+        <f>'Nach Mannschaften sortiert'!G50</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <f>'Nach Mannschaften sortiert'!H50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="57">
+        <f>'Nach Mannschaften sortiert'!A15</f>
+        <v>13</v>
+      </c>
+      <c r="B41" s="57">
+        <f>'Nach Mannschaften sortiert'!B15</f>
+        <v>6</v>
+      </c>
+      <c r="C41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!C15</f>
+        <v>KM</v>
+      </c>
+      <c r="D41" s="58">
+        <f>'Nach Mannschaften sortiert'!D15</f>
+        <v>46284</v>
+      </c>
+      <c r="E41" s="59">
+        <f>'Nach Mannschaften sortiert'!E15</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!F15</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="G41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!G15</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="H41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!H15</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="66">
+        <f>'Nach Mannschaften sortiert'!A81</f>
+        <v>79</v>
+      </c>
+      <c r="B42" s="66">
+        <f>'Nach Mannschaften sortiert'!B81</f>
+        <v>6</v>
+      </c>
+      <c r="C42" s="66" t="str">
+        <f>'Nach Mannschaften sortiert'!C81</f>
+        <v>U11</v>
+      </c>
+      <c r="D42" s="67">
+        <f>'Nach Mannschaften sortiert'!D81</f>
+        <v>46068</v>
+      </c>
+      <c r="E42" s="68">
+        <f>'Nach Mannschaften sortiert'!E81</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="66">
+        <f>'Nach Mannschaften sortiert'!F81</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="66">
+        <f>'Nach Mannschaften sortiert'!G81</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="66">
+        <f>'Nach Mannschaften sortiert'!H81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <f>'Nach Mannschaften sortiert'!A55</f>
+        <v>53</v>
+      </c>
+      <c r="B43" s="2">
+        <f>'Nach Mannschaften sortiert'!B55</f>
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C55</f>
+        <v>U14</v>
+      </c>
+      <c r="D43" s="13">
+        <f>'Nach Mannschaften sortiert'!D55</f>
+        <v>46042</v>
+      </c>
+      <c r="E43" s="35">
+        <f>'Nach Mannschaften sortiert'!E55</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <f>'Nach Mannschaften sortiert'!F55</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
+        <f>'Nach Mannschaften sortiert'!G55</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="2">
+        <f>'Nach Mannschaften sortiert'!H55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="60">
+        <f>'Nach Mannschaften sortiert'!A58</f>
+        <v>56</v>
+      </c>
+      <c r="B44" s="60">
+        <f>'Nach Mannschaften sortiert'!B58</f>
+        <v>3</v>
+      </c>
+      <c r="C44" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!C58</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D44" s="61">
+        <f>'Nach Mannschaften sortiert'!D58</f>
+        <v>46045</v>
+      </c>
+      <c r="E44" s="62">
+        <f>'Nach Mannschaften sortiert'!E58</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="60">
+        <f>'Nach Mannschaften sortiert'!F58</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="60">
+        <f>'Nach Mannschaften sortiert'!G58</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="60">
+        <f>'Nach Mannschaften sortiert'!H58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="60">
         <f>'Nach Mannschaften sortiert'!A49</f>
-        <v>48</v>
-      </c>
-      <c r="B40" s="2">
+        <v>47</v>
+      </c>
+      <c r="B45" s="60">
         <f>'Nach Mannschaften sortiert'!B49</f>
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="C45" s="60" t="str">
         <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U14</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D45" s="61">
         <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46037</v>
-      </c>
-      <c r="E40" s="35">
+        <v>46036</v>
+      </c>
+      <c r="E45" s="62">
         <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F45" s="60">
         <f>'Nach Mannschaften sortiert'!F49</f>
         <v>0</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G45" s="60">
         <f>'Nach Mannschaften sortiert'!G49</f>
         <v>0</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H45" s="60">
         <f>'Nach Mannschaften sortiert'!H49</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="57">
-        <f>'Nach Mannschaften sortiert'!A14</f>
-        <v>13</v>
-      </c>
-      <c r="B41" s="57">
-        <f>'Nach Mannschaften sortiert'!B14</f>
-        <v>6</v>
-      </c>
-      <c r="C41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C14</f>
-        <v>KM</v>
-      </c>
-      <c r="D41" s="58">
-        <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46284</v>
-      </c>
-      <c r="E41" s="59">
-        <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F14</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="G41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="H41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="66">
-        <f>'Nach Mannschaften sortiert'!A80</f>
-        <v>79</v>
-      </c>
-      <c r="B42" s="66">
-        <f>'Nach Mannschaften sortiert'!B80</f>
-        <v>6</v>
-      </c>
-      <c r="C42" s="66" t="str">
-        <f>'Nach Mannschaften sortiert'!C80</f>
-        <v>U11</v>
-      </c>
-      <c r="D42" s="67">
-        <f>'Nach Mannschaften sortiert'!D80</f>
-        <v>46068</v>
-      </c>
-      <c r="E42" s="68">
-        <f>'Nach Mannschaften sortiert'!E80</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="66">
-        <f>'Nach Mannschaften sortiert'!F80</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="66">
-        <f>'Nach Mannschaften sortiert'!G80</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="66">
-        <f>'Nach Mannschaften sortiert'!H80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <f>'Nach Mannschaften sortiert'!A54</f>
-        <v>53</v>
-      </c>
-      <c r="B43" s="2">
-        <f>'Nach Mannschaften sortiert'!B54</f>
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C54</f>
-        <v>U14</v>
-      </c>
-      <c r="D43" s="13">
-        <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46042</v>
-      </c>
-      <c r="E43" s="35">
-        <f>'Nach Mannschaften sortiert'!E54</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <f>'Nach Mannschaften sortiert'!F54</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="2">
-        <f>'Nach Mannschaften sortiert'!G54</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <f>'Nach Mannschaften sortiert'!H54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="60">
-        <f>'Nach Mannschaften sortiert'!A57</f>
-        <v>56</v>
-      </c>
-      <c r="B44" s="60">
-        <f>'Nach Mannschaften sortiert'!B57</f>
-        <v>3</v>
-      </c>
-      <c r="C44" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C57</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D44" s="61">
-        <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46045</v>
-      </c>
-      <c r="E44" s="62">
-        <f>'Nach Mannschaften sortiert'!E57</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="60">
-        <f>'Nach Mannschaften sortiert'!F57</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="60">
-        <f>'Nach Mannschaften sortiert'!G57</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="60">
-        <f>'Nach Mannschaften sortiert'!H57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="60">
-        <f>'Nach Mannschaften sortiert'!A48</f>
-        <v>47</v>
-      </c>
-      <c r="B45" s="60">
-        <f>'Nach Mannschaften sortiert'!B48</f>
-        <v>4</v>
-      </c>
-      <c r="C45" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C48</f>
-        <v>U14</v>
-      </c>
-      <c r="D45" s="61">
-        <f>'Nach Mannschaften sortiert'!D48</f>
-        <v>46036</v>
-      </c>
-      <c r="E45" s="62">
-        <f>'Nach Mannschaften sortiert'!E48</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="60">
-        <f>'Nach Mannschaften sortiert'!F48</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="60">
-        <f>'Nach Mannschaften sortiert'!G48</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="60">
-        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
@@ -11203,137 +11280,137 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <f>'Nach Mannschaften sortiert'!A56</f>
+        <f>'Nach Mannschaften sortiert'!A57</f>
         <v>55</v>
       </c>
       <c r="B47" s="2">
-        <f>'Nach Mannschaften sortiert'!B56</f>
+        <f>'Nach Mannschaften sortiert'!B57</f>
         <v>2</v>
       </c>
       <c r="C47" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C56</f>
+        <f>'Nach Mannschaften sortiert'!C57</f>
         <v>U12_1</v>
       </c>
       <c r="D47" s="13">
-        <f>'Nach Mannschaften sortiert'!D56</f>
+        <f>'Nach Mannschaften sortiert'!D57</f>
         <v>46044</v>
       </c>
       <c r="E47" s="35">
-        <f>'Nach Mannschaften sortiert'!E56</f>
+        <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
       <c r="F47" s="2">
-        <f>'Nach Mannschaften sortiert'!F56</f>
+        <f>'Nach Mannschaften sortiert'!F57</f>
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <f>'Nach Mannschaften sortiert'!G56</f>
+        <f>'Nach Mannschaften sortiert'!G57</f>
         <v>0</v>
       </c>
       <c r="H47" s="2">
-        <f>'Nach Mannschaften sortiert'!H56</f>
+        <f>'Nach Mannschaften sortiert'!H57</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="57">
-        <f>'Nach Mannschaften sortiert'!A38</f>
+        <f>'Nach Mannschaften sortiert'!A39</f>
         <v>37</v>
       </c>
       <c r="B48" s="57">
-        <f>'Nach Mannschaften sortiert'!B38</f>
+        <f>'Nach Mannschaften sortiert'!B39</f>
         <v>4</v>
       </c>
       <c r="C48" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C38</f>
+        <f>'Nach Mannschaften sortiert'!C39</f>
         <v>U16</v>
       </c>
       <c r="D48" s="58">
-        <f>'Nach Mannschaften sortiert'!D38</f>
+        <f>'Nach Mannschaften sortiert'!D39</f>
         <v>46026</v>
       </c>
       <c r="E48" s="59">
-        <f>'Nach Mannschaften sortiert'!E38</f>
+        <f>'Nach Mannschaften sortiert'!E39</f>
         <v>0</v>
       </c>
       <c r="F48" s="57">
-        <f>'Nach Mannschaften sortiert'!F38</f>
+        <f>'Nach Mannschaften sortiert'!F39</f>
         <v>0</v>
       </c>
       <c r="G48" s="57">
-        <f>'Nach Mannschaften sortiert'!G38</f>
+        <f>'Nach Mannschaften sortiert'!G39</f>
         <v>0</v>
       </c>
       <c r="H48" s="57">
-        <f>'Nach Mannschaften sortiert'!H38</f>
+        <f>'Nach Mannschaften sortiert'!H39</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <f>'Nach Mannschaften sortiert'!A58</f>
+        <f>'Nach Mannschaften sortiert'!A59</f>
         <v>57</v>
       </c>
       <c r="B49" s="2">
-        <f>'Nach Mannschaften sortiert'!B58</f>
+        <f>'Nach Mannschaften sortiert'!B59</f>
         <v>4</v>
       </c>
       <c r="C49" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C58</f>
+        <f>'Nach Mannschaften sortiert'!C59</f>
         <v>U12_1</v>
       </c>
       <c r="D49" s="13">
-        <f>'Nach Mannschaften sortiert'!D58</f>
+        <f>'Nach Mannschaften sortiert'!D59</f>
         <v>46046</v>
       </c>
       <c r="E49" s="35">
-        <f>'Nach Mannschaften sortiert'!E58</f>
+        <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="F49" s="2">
-        <f>'Nach Mannschaften sortiert'!F58</f>
+        <f>'Nach Mannschaften sortiert'!F59</f>
         <v>0</v>
       </c>
       <c r="G49" s="2">
-        <f>'Nach Mannschaften sortiert'!G58</f>
+        <f>'Nach Mannschaften sortiert'!G59</f>
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <f>'Nach Mannschaften sortiert'!H58</f>
+        <f>'Nach Mannschaften sortiert'!H59</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <f>'Nach Mannschaften sortiert'!A59</f>
+        <f>'Nach Mannschaften sortiert'!A60</f>
         <v>58</v>
       </c>
       <c r="B50" s="2">
-        <f>'Nach Mannschaften sortiert'!B59</f>
+        <f>'Nach Mannschaften sortiert'!B60</f>
         <v>5</v>
       </c>
       <c r="C50" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C59</f>
+        <f>'Nach Mannschaften sortiert'!C60</f>
         <v>U12_1</v>
       </c>
       <c r="D50" s="13">
-        <f>'Nach Mannschaften sortiert'!D59</f>
+        <f>'Nach Mannschaften sortiert'!D60</f>
         <v>46047</v>
       </c>
       <c r="E50" s="35">
-        <f>'Nach Mannschaften sortiert'!E59</f>
+        <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="F50" s="2">
-        <f>'Nach Mannschaften sortiert'!F59</f>
+        <f>'Nach Mannschaften sortiert'!F60</f>
         <v>0</v>
       </c>
       <c r="G50" s="2">
-        <f>'Nach Mannschaften sortiert'!G59</f>
+        <f>'Nach Mannschaften sortiert'!G60</f>
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <f>'Nach Mannschaften sortiert'!H59</f>
+        <f>'Nach Mannschaften sortiert'!H60</f>
         <v>0</v>
       </c>
     </row>
@@ -11373,69 +11450,69 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="57">
-        <f>'Nach Mannschaften sortiert'!A16</f>
+        <f>'Nach Mannschaften sortiert'!A17</f>
         <v>15</v>
       </c>
       <c r="B52" s="57">
-        <f>'Nach Mannschaften sortiert'!B16</f>
+        <f>'Nach Mannschaften sortiert'!B17</f>
         <v>8</v>
       </c>
       <c r="C52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C16</f>
+        <f>'Nach Mannschaften sortiert'!C17</f>
         <v>KM</v>
       </c>
       <c r="D52" s="58">
-        <f>'Nach Mannschaften sortiert'!D16</f>
+        <f>'Nach Mannschaften sortiert'!D17</f>
         <v>46297</v>
       </c>
       <c r="E52" s="59">
-        <f>'Nach Mannschaften sortiert'!E16</f>
+        <f>'Nach Mannschaften sortiert'!E17</f>
         <v>0.79166666666666663</v>
       </c>
       <c r="F52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F16</f>
+        <f>'Nach Mannschaften sortiert'!F17</f>
         <v>Siegendorf</v>
       </c>
       <c r="G52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G16</f>
+        <f>'Nach Mannschaften sortiert'!G17</f>
         <v>Siegendorf</v>
       </c>
       <c r="H52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H16</f>
+        <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <f>'Nach Mannschaften sortiert'!A61</f>
+        <f>'Nach Mannschaften sortiert'!A62</f>
         <v>60</v>
       </c>
       <c r="B53" s="2">
-        <f>'Nach Mannschaften sortiert'!B61</f>
+        <f>'Nach Mannschaften sortiert'!B62</f>
         <v>7</v>
       </c>
       <c r="C53" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C61</f>
+        <f>'Nach Mannschaften sortiert'!C62</f>
         <v>U12_1</v>
       </c>
       <c r="D53" s="13">
-        <f>'Nach Mannschaften sortiert'!D61</f>
+        <f>'Nach Mannschaften sortiert'!D62</f>
         <v>46049</v>
       </c>
       <c r="E53" s="35">
-        <f>'Nach Mannschaften sortiert'!E61</f>
+        <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="F53" s="2">
-        <f>'Nach Mannschaften sortiert'!F61</f>
+        <f>'Nach Mannschaften sortiert'!F62</f>
         <v>0</v>
       </c>
       <c r="G53" s="2">
-        <f>'Nach Mannschaften sortiert'!G61</f>
+        <f>'Nach Mannschaften sortiert'!G62</f>
         <v>0</v>
       </c>
       <c r="H53" s="2">
-        <f>'Nach Mannschaften sortiert'!H61</f>
+        <f>'Nach Mannschaften sortiert'!H62</f>
         <v>0</v>
       </c>
     </row>
@@ -11475,137 +11552,137 @@
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <f>'Nach Mannschaften sortiert'!A75</f>
+        <f>'Nach Mannschaften sortiert'!A76</f>
         <v>74</v>
       </c>
       <c r="B55" s="2">
-        <f>'Nach Mannschaften sortiert'!B75</f>
+        <f>'Nach Mannschaften sortiert'!B76</f>
         <v>1</v>
       </c>
       <c r="C55" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C75</f>
+        <f>'Nach Mannschaften sortiert'!C76</f>
         <v>U11</v>
       </c>
       <c r="D55" s="13">
-        <f>'Nach Mannschaften sortiert'!D75</f>
+        <f>'Nach Mannschaften sortiert'!D76</f>
         <v>46063</v>
       </c>
       <c r="E55" s="35">
-        <f>'Nach Mannschaften sortiert'!E75</f>
+        <f>'Nach Mannschaften sortiert'!E76</f>
         <v>0</v>
       </c>
       <c r="F55" s="2">
-        <f>'Nach Mannschaften sortiert'!F75</f>
+        <f>'Nach Mannschaften sortiert'!F76</f>
         <v>0</v>
       </c>
       <c r="G55" s="2">
-        <f>'Nach Mannschaften sortiert'!G75</f>
+        <f>'Nach Mannschaften sortiert'!G76</f>
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <f>'Nach Mannschaften sortiert'!H75</f>
+        <f>'Nach Mannschaften sortiert'!H76</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="57">
-        <f>'Nach Mannschaften sortiert'!A81</f>
+        <f>'Nach Mannschaften sortiert'!A82</f>
         <v>80</v>
       </c>
       <c r="B56" s="57">
-        <f>'Nach Mannschaften sortiert'!B81</f>
+        <f>'Nach Mannschaften sortiert'!B82</f>
         <v>7</v>
       </c>
       <c r="C56" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C81</f>
+        <f>'Nach Mannschaften sortiert'!C82</f>
         <v>U11</v>
       </c>
       <c r="D56" s="58">
-        <f>'Nach Mannschaften sortiert'!D81</f>
+        <f>'Nach Mannschaften sortiert'!D82</f>
         <v>46069</v>
       </c>
       <c r="E56" s="59">
-        <f>'Nach Mannschaften sortiert'!E81</f>
+        <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="F56" s="57">
-        <f>'Nach Mannschaften sortiert'!F81</f>
+        <f>'Nach Mannschaften sortiert'!F82</f>
         <v>0</v>
       </c>
       <c r="G56" s="57">
-        <f>'Nach Mannschaften sortiert'!G81</f>
+        <f>'Nach Mannschaften sortiert'!G82</f>
         <v>0</v>
       </c>
       <c r="H56" s="57">
-        <f>'Nach Mannschaften sortiert'!H81</f>
+        <f>'Nach Mannschaften sortiert'!H82</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <f>'Nach Mannschaften sortiert'!A78</f>
+        <f>'Nach Mannschaften sortiert'!A79</f>
         <v>77</v>
       </c>
       <c r="B57" s="2">
-        <f>'Nach Mannschaften sortiert'!B78</f>
+        <f>'Nach Mannschaften sortiert'!B79</f>
         <v>4</v>
       </c>
       <c r="C57" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C78</f>
+        <f>'Nach Mannschaften sortiert'!C79</f>
         <v>U11</v>
       </c>
       <c r="D57" s="13">
-        <f>'Nach Mannschaften sortiert'!D78</f>
+        <f>'Nach Mannschaften sortiert'!D79</f>
         <v>46066</v>
       </c>
       <c r="E57" s="35">
-        <f>'Nach Mannschaften sortiert'!E78</f>
+        <f>'Nach Mannschaften sortiert'!E79</f>
         <v>0</v>
       </c>
       <c r="F57" s="2">
-        <f>'Nach Mannschaften sortiert'!F78</f>
+        <f>'Nach Mannschaften sortiert'!F79</f>
         <v>0</v>
       </c>
       <c r="G57" s="2">
-        <f>'Nach Mannschaften sortiert'!G78</f>
+        <f>'Nach Mannschaften sortiert'!G79</f>
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <f>'Nach Mannschaften sortiert'!H78</f>
+        <f>'Nach Mannschaften sortiert'!H79</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="57">
-        <f>'Nach Mannschaften sortiert'!A18</f>
+        <f>'Nach Mannschaften sortiert'!A19</f>
         <v>17</v>
       </c>
       <c r="B58" s="57">
-        <f>'Nach Mannschaften sortiert'!B18</f>
+        <f>'Nach Mannschaften sortiert'!B19</f>
         <v>10</v>
       </c>
       <c r="C58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C18</f>
+        <f>'Nach Mannschaften sortiert'!C19</f>
         <v>KM</v>
       </c>
       <c r="D58" s="58">
-        <f>'Nach Mannschaften sortiert'!D18</f>
+        <f>'Nach Mannschaften sortiert'!D19</f>
         <v>46312</v>
       </c>
       <c r="E58" s="59">
-        <f>'Nach Mannschaften sortiert'!E18</f>
+        <f>'Nach Mannschaften sortiert'!E19</f>
         <v>0.64583333333333337</v>
       </c>
       <c r="F58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F18</f>
+        <f>'Nach Mannschaften sortiert'!F19</f>
         <v>Hornstein</v>
       </c>
       <c r="G58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G18</f>
+        <f>'Nach Mannschaften sortiert'!G19</f>
         <v>Hornstein</v>
       </c>
       <c r="H58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H18</f>
+        <f>'Nach Mannschaften sortiert'!H19</f>
         <v>Auswärts</v>
       </c>
     </row>
@@ -11645,137 +11722,137 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="57">
-        <f>'Nach Mannschaften sortiert'!A52</f>
+        <f>'Nach Mannschaften sortiert'!A53</f>
         <v>51</v>
       </c>
       <c r="B60" s="57">
-        <f>'Nach Mannschaften sortiert'!B52</f>
+        <f>'Nach Mannschaften sortiert'!B53</f>
         <v>8</v>
       </c>
       <c r="C60" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C52</f>
+        <f>'Nach Mannschaften sortiert'!C53</f>
         <v>U14</v>
       </c>
       <c r="D60" s="58">
-        <f>'Nach Mannschaften sortiert'!D52</f>
+        <f>'Nach Mannschaften sortiert'!D53</f>
         <v>46040</v>
       </c>
       <c r="E60" s="59">
-        <f>'Nach Mannschaften sortiert'!E52</f>
+        <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="F60" s="57">
-        <f>'Nach Mannschaften sortiert'!F52</f>
+        <f>'Nach Mannschaften sortiert'!F53</f>
         <v>0</v>
       </c>
       <c r="G60" s="57">
-        <f>'Nach Mannschaften sortiert'!G52</f>
+        <f>'Nach Mannschaften sortiert'!G53</f>
         <v>0</v>
       </c>
       <c r="H60" s="57">
-        <f>'Nach Mannschaften sortiert'!H52</f>
+        <f>'Nach Mannschaften sortiert'!H53</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <f>'Nach Mannschaften sortiert'!A82</f>
+        <f>'Nach Mannschaften sortiert'!A83</f>
         <v>81</v>
       </c>
       <c r="B61" s="2">
-        <f>'Nach Mannschaften sortiert'!B82</f>
+        <f>'Nach Mannschaften sortiert'!B83</f>
         <v>8</v>
       </c>
       <c r="C61" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C82</f>
+        <f>'Nach Mannschaften sortiert'!C83</f>
         <v>U11</v>
       </c>
       <c r="D61" s="13">
-        <f>'Nach Mannschaften sortiert'!D82</f>
+        <f>'Nach Mannschaften sortiert'!D83</f>
         <v>46070</v>
       </c>
       <c r="E61" s="35">
-        <f>'Nach Mannschaften sortiert'!E82</f>
+        <f>'Nach Mannschaften sortiert'!E83</f>
         <v>0</v>
       </c>
       <c r="F61" s="2">
-        <f>'Nach Mannschaften sortiert'!F82</f>
+        <f>'Nach Mannschaften sortiert'!F83</f>
         <v>0</v>
       </c>
       <c r="G61" s="2">
-        <f>'Nach Mannschaften sortiert'!G82</f>
+        <f>'Nach Mannschaften sortiert'!G83</f>
         <v>0</v>
       </c>
       <c r="H61" s="2">
-        <f>'Nach Mannschaften sortiert'!H82</f>
+        <f>'Nach Mannschaften sortiert'!H83</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="54">
-        <f>'Nach Mannschaften sortiert'!A53</f>
+        <f>'Nach Mannschaften sortiert'!A54</f>
         <v>52</v>
       </c>
       <c r="B62" s="54">
-        <f>'Nach Mannschaften sortiert'!B53</f>
+        <f>'Nach Mannschaften sortiert'!B54</f>
         <v>9</v>
       </c>
       <c r="C62" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C53</f>
+        <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U14</v>
       </c>
       <c r="D62" s="55">
-        <f>'Nach Mannschaften sortiert'!D53</f>
+        <f>'Nach Mannschaften sortiert'!D54</f>
         <v>46041</v>
       </c>
       <c r="E62" s="56">
-        <f>'Nach Mannschaften sortiert'!E53</f>
+        <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="F62" s="54">
-        <f>'Nach Mannschaften sortiert'!F53</f>
+        <f>'Nach Mannschaften sortiert'!F54</f>
         <v>0</v>
       </c>
       <c r="G62" s="54">
-        <f>'Nach Mannschaften sortiert'!G53</f>
+        <f>'Nach Mannschaften sortiert'!G54</f>
         <v>0</v>
       </c>
       <c r="H62" s="54">
-        <f>'Nach Mannschaften sortiert'!H53</f>
+        <f>'Nach Mannschaften sortiert'!H54</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <f>'Nach Mannschaften sortiert'!A84</f>
+        <f>'Nach Mannschaften sortiert'!A85</f>
         <v>83</v>
       </c>
       <c r="B63" s="2">
-        <f>'Nach Mannschaften sortiert'!B84</f>
+        <f>'Nach Mannschaften sortiert'!B85</f>
         <v>10</v>
       </c>
       <c r="C63" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C84</f>
+        <f>'Nach Mannschaften sortiert'!C85</f>
         <v>U11</v>
       </c>
       <c r="D63" s="13">
-        <f>'Nach Mannschaften sortiert'!D84</f>
+        <f>'Nach Mannschaften sortiert'!D85</f>
         <v>46072</v>
       </c>
       <c r="E63" s="35">
-        <f>'Nach Mannschaften sortiert'!E84</f>
+        <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="F63" s="2">
-        <f>'Nach Mannschaften sortiert'!F84</f>
+        <f>'Nach Mannschaften sortiert'!F85</f>
         <v>0</v>
       </c>
       <c r="G63" s="2">
-        <f>'Nach Mannschaften sortiert'!G84</f>
+        <f>'Nach Mannschaften sortiert'!G85</f>
         <v>0</v>
       </c>
       <c r="H63" s="2">
-        <f>'Nach Mannschaften sortiert'!H84</f>
+        <f>'Nach Mannschaften sortiert'!H85</f>
         <v>0</v>
       </c>
     </row>
@@ -11815,15 +11892,15 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="57">
-        <f>'Nach Mannschaften sortiert'!A83</f>
+        <f>'Nach Mannschaften sortiert'!A84</f>
         <v>82</v>
       </c>
       <c r="B65" s="57">
-        <f>'Nach Mannschaften sortiert'!B83</f>
+        <f>'Nach Mannschaften sortiert'!B84</f>
         <v>9</v>
       </c>
       <c r="C65" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C83</f>
+        <f>'Nach Mannschaften sortiert'!C84</f>
         <v>U11</v>
       </c>
       <c r="D65" s="58">
@@ -11833,525 +11910,525 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F65" s="57">
-        <f>'Nach Mannschaften sortiert'!F83</f>
+        <f>'Nach Mannschaften sortiert'!F84</f>
         <v>0</v>
       </c>
       <c r="G65" s="57">
-        <f>'Nach Mannschaften sortiert'!G83</f>
+        <f>'Nach Mannschaften sortiert'!G84</f>
         <v>0</v>
       </c>
       <c r="H65" s="57">
-        <f>'Nach Mannschaften sortiert'!H83</f>
+        <f>'Nach Mannschaften sortiert'!H84</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <f>'Nach Mannschaften sortiert'!A91</f>
+        <f>'Nach Mannschaften sortiert'!A92</f>
         <v>90</v>
       </c>
       <c r="B66" s="2">
-        <f>'Nach Mannschaften sortiert'!B91</f>
+        <f>'Nach Mannschaften sortiert'!B92</f>
         <v>2</v>
       </c>
       <c r="C66" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C91</f>
+        <f>'Nach Mannschaften sortiert'!C92</f>
         <v>U9</v>
       </c>
       <c r="D66" s="13">
-        <f>'Nach Mannschaften sortiert'!D91</f>
+        <f>'Nach Mannschaften sortiert'!D92</f>
         <v>46079</v>
       </c>
       <c r="E66" s="35">
-        <f>'Nach Mannschaften sortiert'!E91</f>
+        <f>'Nach Mannschaften sortiert'!E92</f>
         <v>0</v>
       </c>
       <c r="F66" s="2">
-        <f>'Nach Mannschaften sortiert'!F91</f>
+        <f>'Nach Mannschaften sortiert'!F92</f>
         <v>0</v>
       </c>
       <c r="G66" s="2">
-        <f>'Nach Mannschaften sortiert'!G91</f>
+        <f>'Nach Mannschaften sortiert'!G92</f>
         <v>0</v>
       </c>
       <c r="H66" s="2">
-        <f>'Nach Mannschaften sortiert'!H91</f>
+        <f>'Nach Mannschaften sortiert'!H92</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <f>'Nach Mannschaften sortiert'!A92</f>
+        <f>'Nach Mannschaften sortiert'!A93</f>
         <v>91</v>
       </c>
       <c r="B67" s="2">
-        <f>'Nach Mannschaften sortiert'!B92</f>
+        <f>'Nach Mannschaften sortiert'!B93</f>
         <v>3</v>
       </c>
       <c r="C67" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C92</f>
+        <f>'Nach Mannschaften sortiert'!C93</f>
         <v>U9</v>
       </c>
       <c r="D67" s="13">
-        <f>'Nach Mannschaften sortiert'!D92</f>
+        <f>'Nach Mannschaften sortiert'!D93</f>
         <v>46080</v>
       </c>
       <c r="E67" s="35">
-        <f>'Nach Mannschaften sortiert'!E92</f>
+        <f>'Nach Mannschaften sortiert'!E93</f>
         <v>0</v>
       </c>
       <c r="F67" s="2">
-        <f>'Nach Mannschaften sortiert'!F92</f>
+        <f>'Nach Mannschaften sortiert'!F93</f>
         <v>0</v>
       </c>
       <c r="G67" s="2">
-        <f>'Nach Mannschaften sortiert'!G92</f>
+        <f>'Nach Mannschaften sortiert'!G93</f>
         <v>0</v>
       </c>
       <c r="H67" s="2">
-        <f>'Nach Mannschaften sortiert'!H92</f>
+        <f>'Nach Mannschaften sortiert'!H93</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <f>'Nach Mannschaften sortiert'!A93</f>
+        <f>'Nach Mannschaften sortiert'!A94</f>
         <v>92</v>
       </c>
       <c r="B68" s="2">
-        <f>'Nach Mannschaften sortiert'!B93</f>
+        <f>'Nach Mannschaften sortiert'!B94</f>
         <v>4</v>
       </c>
       <c r="C68" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C93</f>
+        <f>'Nach Mannschaften sortiert'!C94</f>
         <v>U9</v>
       </c>
       <c r="D68" s="13">
-        <f>'Nach Mannschaften sortiert'!D93</f>
+        <f>'Nach Mannschaften sortiert'!D94</f>
         <v>46081</v>
       </c>
       <c r="E68" s="35">
-        <f>'Nach Mannschaften sortiert'!E93</f>
+        <f>'Nach Mannschaften sortiert'!E94</f>
         <v>0</v>
       </c>
       <c r="F68" s="2">
-        <f>'Nach Mannschaften sortiert'!F93</f>
+        <f>'Nach Mannschaften sortiert'!F94</f>
         <v>0</v>
       </c>
       <c r="G68" s="2">
-        <f>'Nach Mannschaften sortiert'!G93</f>
+        <f>'Nach Mannschaften sortiert'!G94</f>
         <v>0</v>
       </c>
       <c r="H68" s="2">
-        <f>'Nach Mannschaften sortiert'!H93</f>
+        <f>'Nach Mannschaften sortiert'!H94</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <f>'Nach Mannschaften sortiert'!A99</f>
+        <f>'Nach Mannschaften sortiert'!A100</f>
         <v>98</v>
       </c>
       <c r="B69" s="2">
-        <f>'Nach Mannschaften sortiert'!B99</f>
+        <f>'Nach Mannschaften sortiert'!B100</f>
         <v>10</v>
       </c>
       <c r="C69" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C99</f>
+        <f>'Nach Mannschaften sortiert'!C100</f>
         <v>U9</v>
       </c>
       <c r="D69" s="13">
-        <f>'Nach Mannschaften sortiert'!D99</f>
+        <f>'Nach Mannschaften sortiert'!D100</f>
         <v>46087</v>
       </c>
       <c r="E69" s="35">
-        <f>'Nach Mannschaften sortiert'!E99</f>
+        <f>'Nach Mannschaften sortiert'!E100</f>
         <v>0</v>
       </c>
       <c r="F69" s="2">
-        <f>'Nach Mannschaften sortiert'!F99</f>
+        <f>'Nach Mannschaften sortiert'!F100</f>
         <v>0</v>
       </c>
       <c r="G69" s="2">
-        <f>'Nach Mannschaften sortiert'!G99</f>
+        <f>'Nach Mannschaften sortiert'!G100</f>
         <v>0</v>
       </c>
       <c r="H69" s="2">
-        <f>'Nach Mannschaften sortiert'!H99</f>
+        <f>'Nach Mannschaften sortiert'!H100</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="57">
-        <f>'Nach Mannschaften sortiert'!A60</f>
+        <f>'Nach Mannschaften sortiert'!A61</f>
         <v>59</v>
       </c>
       <c r="B70" s="57">
-        <f>'Nach Mannschaften sortiert'!B60</f>
+        <f>'Nach Mannschaften sortiert'!B61</f>
         <v>6</v>
       </c>
       <c r="C70" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C60</f>
+        <f>'Nach Mannschaften sortiert'!C61</f>
         <v>U12_1</v>
       </c>
       <c r="D70" s="58">
-        <f>'Nach Mannschaften sortiert'!D60</f>
+        <f>'Nach Mannschaften sortiert'!D61</f>
         <v>46048</v>
       </c>
       <c r="E70" s="59">
-        <f>'Nach Mannschaften sortiert'!E60</f>
+        <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="F70" s="57">
-        <f>'Nach Mannschaften sortiert'!F60</f>
+        <f>'Nach Mannschaften sortiert'!F61</f>
         <v>0</v>
       </c>
       <c r="G70" s="57">
-        <f>'Nach Mannschaften sortiert'!G60</f>
+        <f>'Nach Mannschaften sortiert'!G61</f>
         <v>0</v>
       </c>
       <c r="H70" s="57">
-        <f>'Nach Mannschaften sortiert'!H60</f>
+        <f>'Nach Mannschaften sortiert'!H61</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <f>'Nach Mannschaften sortiert'!A101</f>
+        <f>'Nach Mannschaften sortiert'!A102</f>
         <v>100</v>
       </c>
       <c r="B71" s="2">
-        <f>'Nach Mannschaften sortiert'!B101</f>
+        <f>'Nach Mannschaften sortiert'!B102</f>
         <v>2</v>
       </c>
       <c r="C71" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C101</f>
+        <f>'Nach Mannschaften sortiert'!C102</f>
         <v>U8</v>
       </c>
       <c r="D71" s="13">
-        <f>'Nach Mannschaften sortiert'!D101</f>
+        <f>'Nach Mannschaften sortiert'!D102</f>
         <v>46089</v>
       </c>
       <c r="E71" s="35">
-        <f>'Nach Mannschaften sortiert'!E101</f>
+        <f>'Nach Mannschaften sortiert'!E102</f>
         <v>0</v>
       </c>
       <c r="F71" s="2">
-        <f>'Nach Mannschaften sortiert'!F101</f>
+        <f>'Nach Mannschaften sortiert'!F102</f>
         <v>0</v>
       </c>
       <c r="G71" s="2">
-        <f>'Nach Mannschaften sortiert'!G101</f>
+        <f>'Nach Mannschaften sortiert'!G102</f>
         <v>0</v>
       </c>
       <c r="H71" s="2">
-        <f>'Nach Mannschaften sortiert'!H101</f>
+        <f>'Nach Mannschaften sortiert'!H102</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <f>'Nach Mannschaften sortiert'!A102</f>
+        <f>'Nach Mannschaften sortiert'!A103</f>
         <v>101</v>
       </c>
       <c r="B72" s="2">
-        <f>'Nach Mannschaften sortiert'!B102</f>
+        <f>'Nach Mannschaften sortiert'!B103</f>
         <v>3</v>
       </c>
       <c r="C72" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C102</f>
+        <f>'Nach Mannschaften sortiert'!C103</f>
         <v>U8</v>
       </c>
       <c r="D72" s="13">
-        <f>'Nach Mannschaften sortiert'!D102</f>
+        <f>'Nach Mannschaften sortiert'!D103</f>
         <v>46090</v>
       </c>
       <c r="E72" s="35">
-        <f>'Nach Mannschaften sortiert'!E102</f>
+        <f>'Nach Mannschaften sortiert'!E103</f>
         <v>0</v>
       </c>
       <c r="F72" s="2">
-        <f>'Nach Mannschaften sortiert'!F102</f>
+        <f>'Nach Mannschaften sortiert'!F103</f>
         <v>0</v>
       </c>
       <c r="G72" s="2">
-        <f>'Nach Mannschaften sortiert'!G102</f>
+        <f>'Nach Mannschaften sortiert'!G103</f>
         <v>0</v>
       </c>
       <c r="H72" s="2">
-        <f>'Nach Mannschaften sortiert'!H102</f>
+        <f>'Nach Mannschaften sortiert'!H103</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <f>'Nach Mannschaften sortiert'!A103</f>
+        <f>'Nach Mannschaften sortiert'!A104</f>
         <v>102</v>
       </c>
       <c r="B73" s="2">
-        <f>'Nach Mannschaften sortiert'!B103</f>
+        <f>'Nach Mannschaften sortiert'!B104</f>
         <v>4</v>
       </c>
       <c r="C73" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C103</f>
+        <f>'Nach Mannschaften sortiert'!C104</f>
         <v>U8</v>
       </c>
       <c r="D73" s="13">
-        <f>'Nach Mannschaften sortiert'!D103</f>
+        <f>'Nach Mannschaften sortiert'!D104</f>
         <v>46091</v>
       </c>
       <c r="E73" s="35">
-        <f>'Nach Mannschaften sortiert'!E103</f>
+        <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0</v>
       </c>
       <c r="F73" s="2">
-        <f>'Nach Mannschaften sortiert'!F103</f>
+        <f>'Nach Mannschaften sortiert'!F104</f>
         <v>0</v>
       </c>
       <c r="G73" s="2">
-        <f>'Nach Mannschaften sortiert'!G103</f>
+        <f>'Nach Mannschaften sortiert'!G104</f>
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <f>'Nach Mannschaften sortiert'!H103</f>
+        <f>'Nach Mannschaften sortiert'!H104</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <f>'Nach Mannschaften sortiert'!A104</f>
+        <f>'Nach Mannschaften sortiert'!A105</f>
         <v>103</v>
       </c>
       <c r="B74" s="2">
-        <f>'Nach Mannschaften sortiert'!B104</f>
+        <f>'Nach Mannschaften sortiert'!B105</f>
         <v>5</v>
       </c>
       <c r="C74" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C104</f>
+        <f>'Nach Mannschaften sortiert'!C105</f>
         <v>U8</v>
       </c>
       <c r="D74" s="13">
-        <f>'Nach Mannschaften sortiert'!D104</f>
+        <f>'Nach Mannschaften sortiert'!D105</f>
         <v>46092</v>
       </c>
       <c r="E74" s="35">
-        <f>'Nach Mannschaften sortiert'!E104</f>
+        <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="F74" s="2">
-        <f>'Nach Mannschaften sortiert'!F104</f>
+        <f>'Nach Mannschaften sortiert'!F105</f>
         <v>0</v>
       </c>
       <c r="G74" s="2">
-        <f>'Nach Mannschaften sortiert'!G104</f>
+        <f>'Nach Mannschaften sortiert'!G105</f>
         <v>0</v>
       </c>
       <c r="H74" s="2">
-        <f>'Nach Mannschaften sortiert'!H104</f>
+        <f>'Nach Mannschaften sortiert'!H105</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="57">
-        <f>'Nach Mannschaften sortiert'!A21</f>
+        <f>'Nach Mannschaften sortiert'!A22</f>
         <v>20</v>
       </c>
       <c r="B75" s="57">
-        <f>'Nach Mannschaften sortiert'!B21</f>
+        <f>'Nach Mannschaften sortiert'!B22</f>
         <v>13</v>
       </c>
       <c r="C75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C21</f>
+        <f>'Nach Mannschaften sortiert'!C22</f>
         <v>KM</v>
       </c>
       <c r="D75" s="58">
-        <f>'Nach Mannschaften sortiert'!D21</f>
+        <f>'Nach Mannschaften sortiert'!D22</f>
         <v>46333</v>
       </c>
       <c r="E75" s="59">
-        <f>'Nach Mannschaften sortiert'!E21</f>
+        <f>'Nach Mannschaften sortiert'!E22</f>
         <v>0.58333333333333337</v>
       </c>
       <c r="F75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F21</f>
+        <f>'Nach Mannschaften sortiert'!F22</f>
         <v>Neufeld</v>
       </c>
       <c r="G75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G21</f>
+        <f>'Nach Mannschaften sortiert'!G22</f>
         <v>Andau</v>
       </c>
       <c r="H75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H21</f>
+        <f>'Nach Mannschaften sortiert'!H22</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <f>'Nach Mannschaften sortiert'!A106</f>
+        <f>'Nach Mannschaften sortiert'!A107</f>
         <v>105</v>
       </c>
       <c r="B76" s="2">
-        <f>'Nach Mannschaften sortiert'!B106</f>
+        <f>'Nach Mannschaften sortiert'!B107</f>
         <v>2</v>
       </c>
       <c r="C76" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C106</f>
+        <f>'Nach Mannschaften sortiert'!C107</f>
         <v>U7</v>
       </c>
       <c r="D76" s="13">
-        <f>'Nach Mannschaften sortiert'!D106</f>
+        <f>'Nach Mannschaften sortiert'!D107</f>
         <v>46094</v>
       </c>
       <c r="E76" s="35">
-        <f>'Nach Mannschaften sortiert'!E106</f>
+        <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="F76" s="2">
-        <f>'Nach Mannschaften sortiert'!F106</f>
+        <f>'Nach Mannschaften sortiert'!F107</f>
         <v>0</v>
       </c>
       <c r="G76" s="2">
-        <f>'Nach Mannschaften sortiert'!G106</f>
+        <f>'Nach Mannschaften sortiert'!G107</f>
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <f>'Nach Mannschaften sortiert'!H106</f>
+        <f>'Nach Mannschaften sortiert'!H107</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <f>'Nach Mannschaften sortiert'!A107</f>
+        <f>'Nach Mannschaften sortiert'!A108</f>
         <v>106</v>
       </c>
       <c r="B77" s="2">
-        <f>'Nach Mannschaften sortiert'!B107</f>
+        <f>'Nach Mannschaften sortiert'!B108</f>
         <v>3</v>
       </c>
       <c r="C77" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C107</f>
+        <f>'Nach Mannschaften sortiert'!C108</f>
         <v>U7</v>
       </c>
       <c r="D77" s="13">
-        <f>'Nach Mannschaften sortiert'!D107</f>
+        <f>'Nach Mannschaften sortiert'!D108</f>
         <v>46095</v>
       </c>
       <c r="E77" s="35">
-        <f>'Nach Mannschaften sortiert'!E107</f>
+        <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="F77" s="2">
-        <f>'Nach Mannschaften sortiert'!F107</f>
+        <f>'Nach Mannschaften sortiert'!F108</f>
         <v>0</v>
       </c>
       <c r="G77" s="2">
-        <f>'Nach Mannschaften sortiert'!G107</f>
+        <f>'Nach Mannschaften sortiert'!G108</f>
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <f>'Nach Mannschaften sortiert'!H107</f>
+        <f>'Nach Mannschaften sortiert'!H108</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <f>'Nach Mannschaften sortiert'!A108</f>
+        <f>'Nach Mannschaften sortiert'!A109</f>
         <v>107</v>
       </c>
       <c r="B78" s="2">
-        <f>'Nach Mannschaften sortiert'!B108</f>
+        <f>'Nach Mannschaften sortiert'!B109</f>
         <v>4</v>
       </c>
       <c r="C78" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C108</f>
+        <f>'Nach Mannschaften sortiert'!C109</f>
         <v>U7</v>
       </c>
       <c r="D78" s="13">
-        <f>'Nach Mannschaften sortiert'!D108</f>
+        <f>'Nach Mannschaften sortiert'!D109</f>
         <v>46096</v>
       </c>
       <c r="E78" s="35">
-        <f>'Nach Mannschaften sortiert'!E108</f>
+        <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="F78" s="2">
-        <f>'Nach Mannschaften sortiert'!F108</f>
+        <f>'Nach Mannschaften sortiert'!F109</f>
         <v>0</v>
       </c>
       <c r="G78" s="2">
-        <f>'Nach Mannschaften sortiert'!G108</f>
+        <f>'Nach Mannschaften sortiert'!G109</f>
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <f>'Nach Mannschaften sortiert'!H108</f>
+        <f>'Nach Mannschaften sortiert'!H109</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <f>'Nach Mannschaften sortiert'!A109</f>
+        <f>'Nach Mannschaften sortiert'!A110</f>
         <v>108</v>
       </c>
       <c r="B79" s="2">
-        <f>'Nach Mannschaften sortiert'!B109</f>
+        <f>'Nach Mannschaften sortiert'!B110</f>
         <v>5</v>
       </c>
       <c r="C79" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C109</f>
+        <f>'Nach Mannschaften sortiert'!C110</f>
         <v>U7</v>
       </c>
       <c r="D79" s="13">
-        <f>'Nach Mannschaften sortiert'!D109</f>
+        <f>'Nach Mannschaften sortiert'!D110</f>
         <v>46097</v>
       </c>
       <c r="E79" s="35">
-        <f>'Nach Mannschaften sortiert'!E109</f>
+        <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="F79" s="2">
-        <f>'Nach Mannschaften sortiert'!F109</f>
+        <f>'Nach Mannschaften sortiert'!F110</f>
         <v>0</v>
       </c>
       <c r="G79" s="2">
-        <f>'Nach Mannschaften sortiert'!G109</f>
+        <f>'Nach Mannschaften sortiert'!G110</f>
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <f>'Nach Mannschaften sortiert'!H109</f>
+        <f>'Nach Mannschaften sortiert'!H110</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="57">
-        <f>'Nach Mannschaften sortiert'!A62</f>
+        <f>'Nach Mannschaften sortiert'!A63</f>
         <v>61</v>
       </c>
       <c r="B80" s="57">
-        <f>'Nach Mannschaften sortiert'!B62</f>
+        <f>'Nach Mannschaften sortiert'!B63</f>
         <v>8</v>
       </c>
       <c r="C80" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C62</f>
+        <f>'Nach Mannschaften sortiert'!C63</f>
         <v>U12_1</v>
       </c>
       <c r="D80" s="58">
-        <f>'Nach Mannschaften sortiert'!D62</f>
+        <f>'Nach Mannschaften sortiert'!D63</f>
         <v>46050</v>
       </c>
       <c r="E80" s="59">
-        <f>'Nach Mannschaften sortiert'!E62</f>
+        <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="F80" s="57">
-        <f>'Nach Mannschaften sortiert'!F62</f>
+        <f>'Nach Mannschaften sortiert'!F63</f>
         <v>0</v>
       </c>
       <c r="G80" s="57">
-        <f>'Nach Mannschaften sortiert'!G62</f>
+        <f>'Nach Mannschaften sortiert'!G63</f>
         <v>0</v>
       </c>
       <c r="H80" s="57">
-        <f>'Nach Mannschaften sortiert'!H62</f>
+        <f>'Nach Mannschaften sortiert'!H63</f>
         <v>0</v>
       </c>
     </row>
@@ -12391,35 +12468,35 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="57">
-        <f>'Nach Mannschaften sortiert'!A44</f>
+        <f>'Nach Mannschaften sortiert'!A45</f>
         <v>43</v>
       </c>
       <c r="B82" s="57">
-        <f>'Nach Mannschaften sortiert'!B44</f>
+        <f>'Nach Mannschaften sortiert'!B45</f>
         <v>10</v>
       </c>
       <c r="C82" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C44</f>
+        <f>'Nach Mannschaften sortiert'!C45</f>
         <v>U16</v>
       </c>
       <c r="D82" s="58">
-        <f>'Nach Mannschaften sortiert'!D44</f>
+        <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46032</v>
       </c>
       <c r="E82" s="59">
-        <f>'Nach Mannschaften sortiert'!E44</f>
+        <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="F82" s="57">
-        <f>'Nach Mannschaften sortiert'!F44</f>
+        <f>'Nach Mannschaften sortiert'!F45</f>
         <v>0</v>
       </c>
       <c r="G82" s="57">
-        <f>'Nach Mannschaften sortiert'!G44</f>
+        <f>'Nach Mannschaften sortiert'!G45</f>
         <v>0</v>
       </c>
       <c r="H82" s="57">
-        <f>'Nach Mannschaften sortiert'!H44</f>
+        <f>'Nach Mannschaften sortiert'!H45</f>
         <v>0</v>
       </c>
     </row>
@@ -12459,35 +12536,35 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <f>'Nach Mannschaften sortiert'!A121</f>
+        <f>'Nach Mannschaften sortiert'!A122</f>
         <v>120</v>
       </c>
       <c r="B84" s="2">
-        <f>'Nach Mannschaften sortiert'!B121</f>
+        <f>'Nach Mannschaften sortiert'!B122</f>
         <v>2</v>
       </c>
       <c r="C84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C121</f>
+        <f>'Nach Mannschaften sortiert'!C122</f>
         <v>GGG</v>
       </c>
       <c r="D84" s="13">
-        <f>'Nach Mannschaften sortiert'!D121</f>
+        <f>'Nach Mannschaften sortiert'!D122</f>
         <v>46256</v>
       </c>
       <c r="E84" s="35">
-        <f>'Nach Mannschaften sortiert'!E121</f>
+        <f>'Nach Mannschaften sortiert'!E122</f>
         <v>0.375</v>
       </c>
       <c r="F84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F121</f>
+        <f>'Nach Mannschaften sortiert'!F122</f>
         <v>Neufeld</v>
       </c>
       <c r="G84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G121</f>
+        <f>'Nach Mannschaften sortiert'!G122</f>
         <v>viele Gegner</v>
       </c>
       <c r="H84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H121</f>
+        <f>'Nach Mannschaften sortiert'!H122</f>
         <v>Heim</v>
       </c>
     </row>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADBAE9D-CFCE-45C5-9ECC-E489754D8D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390F61E3-78E2-4D15-856A-AFD607A7AE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="164">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -534,6 +534,9 @@
   </si>
   <si>
     <t>BFV-Cupspiel</t>
+  </si>
+  <si>
+    <t>Heimturnier</t>
   </si>
 </sst>
 </file>
@@ -1831,7 +1834,7 @@
         <v>46217</v>
       </c>
       <c r="E9" s="114">
-        <v>0.83333333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>159</v>
@@ -3526,12 +3529,20 @@
         <v>146</v>
       </c>
       <c r="D86" s="109">
-        <v>46073</v>
-      </c>
-      <c r="E86" s="110"/>
-      <c r="F86" s="108"/>
-      <c r="G86" s="108"/>
-      <c r="H86" s="108"/>
+        <v>46312</v>
+      </c>
+      <c r="E86" s="110">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F86" s="110" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="108" t="s">
+        <v>163</v>
+      </c>
+      <c r="H86" s="108" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="108">
@@ -3811,12 +3822,20 @@
         <v>21</v>
       </c>
       <c r="D101" s="31">
-        <v>46088</v>
-      </c>
-      <c r="E101" s="32"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
-      <c r="H101" s="30"/>
+        <v>46312</v>
+      </c>
+      <c r="E101" s="32">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="G101" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="H101" s="30" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="30">
@@ -3906,7 +3925,7 @@
         <v>72</v>
       </c>
       <c r="D106" s="51">
-        <v>46093</v>
+        <v>46312</v>
       </c>
       <c r="E106" s="52"/>
       <c r="F106" s="50"/>
@@ -4665,11 +4684,11 @@
       </c>
       <c r="C9" s="36">
         <f>'Nach Mannschaften sortiert'!E9</f>
-        <v>0.83333333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D9" s="36">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E9" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
@@ -7664,27 +7683,26 @@
     <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="102">
         <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46073</v>
+        <v>46312</v>
       </c>
       <c r="C86" s="36">
         <f>'Nach Mannschaften sortiert'!E86</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D86" s="36">
-        <f t="shared" si="1"/>
-        <v>4.3750000000000004E-2</v>
+        <v>0.5</v>
       </c>
       <c r="E86" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F86)</f>
-        <v/>
-      </c>
-      <c r="G86" s="115">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G86" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H86</f>
-        <v>0</v>
-      </c>
-      <c r="H86">
+        <v>Heim</v>
+      </c>
+      <c r="H86" t="str">
         <f>'Nach Mannschaften sortiert'!G86</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I86" t="str">
         <f>'Nach Mannschaften sortiert'!C86</f>
@@ -8249,27 +8267,26 @@
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101" s="102">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46088</v>
+        <v>46312</v>
       </c>
       <c r="C101" s="36">
         <f>'Nach Mannschaften sortiert'!E101</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D101" s="36">
-        <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E101" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F101)</f>
-        <v/>
-      </c>
-      <c r="G101" s="115">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G101" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H101</f>
-        <v>0</v>
-      </c>
-      <c r="H101">
+        <v>Heim</v>
+      </c>
+      <c r="H101" t="str">
         <f>'Nach Mannschaften sortiert'!G101</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I101" t="str">
         <f>'Nach Mannschaften sortiert'!C101</f>
@@ -8444,7 +8461,7 @@
     <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106" s="102">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46093</v>
+        <v>46312</v>
       </c>
       <c r="C106" s="36">
         <f>'Nach Mannschaften sortiert'!E106</f>
@@ -10579,23 +10596,23 @@
       </c>
       <c r="D26" s="61">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46088</v>
+        <v>46312</v>
       </c>
       <c r="E26" s="62">
         <f>'Nach Mannschaften sortiert'!E101</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="60">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F26" s="60" t="str">
         <f>'Nach Mannschaften sortiert'!F101</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="60">
+        <v>Neufeld</v>
+      </c>
+      <c r="G26" s="60" t="str">
         <f>'Nach Mannschaften sortiert'!G101</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="60">
+        <v>Heimturnier</v>
+      </c>
+      <c r="H26" s="60" t="str">
         <f>'Nach Mannschaften sortiert'!H101</f>
-        <v>0</v>
+        <v>Heim</v>
       </c>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -10681,7 +10698,7 @@
       </c>
       <c r="D29" s="61">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46093</v>
+        <v>46312</v>
       </c>
       <c r="E29" s="62">
         <f>'Nach Mannschaften sortiert'!E106</f>
@@ -14290,19 +14307,19 @@
       </c>
       <c r="B40" s="78">
         <f>Heimspiele!D26</f>
-        <v>46088</v>
+        <v>46312</v>
       </c>
       <c r="C40" s="79">
         <f>Heimspiele!E26</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="77">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D40" s="77" t="str">
         <f>Heimspiele!F26</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="77">
+        <v>Neufeld</v>
+      </c>
+      <c r="E40" s="77" t="str">
         <f>Heimspiele!G26</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="F40" s="77" t="s">
         <v>21</v>
@@ -14335,7 +14352,7 @@
       </c>
       <c r="B41" s="78">
         <f>Heimspiele!D29</f>
-        <v>46093</v>
+        <v>46312</v>
       </c>
       <c r="C41" s="79">
         <f>Heimspiele!E29</f>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390F61E3-78E2-4D15-856A-AFD607A7AE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398CDBBD-B32B-4631-802E-7B598DD9C558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -1885,10 +1885,10 @@
         <v>30</v>
       </c>
       <c r="D11" s="12">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="E11" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>71</v>
@@ -2236,10 +2236,10 @@
         <v>58</v>
       </c>
       <c r="D24" s="12">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="E24" s="5">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>71</v>
@@ -4758,15 +4758,15 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="102">
         <f>'Nach Mannschaften sortiert'!D11</f>
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="C11" s="36">
         <f>'Nach Mannschaften sortiert'!E11</f>
-        <v>0.70833333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D11" s="36">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.90625</v>
       </c>
       <c r="E11" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
@@ -5265,15 +5265,15 @@
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="102">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="C24" s="36">
         <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="D24" s="36">
         <f t="shared" si="0"/>
-        <v>0.69791666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E24" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
@@ -9814,11 +9814,11 @@
       </c>
       <c r="D3" s="13">
         <f>'Nach Mannschaften sortiert'!D11</f>
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="E3" s="35">
         <f>'Nach Mannschaften sortiert'!E11</f>
-        <v>0.70833333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F3" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F11</f>
@@ -13029,11 +13029,11 @@
       </c>
       <c r="B10" s="78">
         <f>Heimspiele!D3</f>
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="C10" s="79">
         <f>Heimspiele!E3</f>
-        <v>0.70833333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D10" s="77" t="str">
         <f>Heimspiele!F3</f>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398CDBBD-B32B-4631-802E-7B598DD9C558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67768253-A06A-492C-AE9B-3F56E3C79E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="171">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -537,6 +537,27 @@
   </si>
   <si>
     <t>Heimturnier</t>
+  </si>
+  <si>
+    <t>Hallenturnie</t>
+  </si>
+  <si>
+    <t>Steinbrunn</t>
+  </si>
+  <si>
+    <t>Hallencup 2026_27</t>
+  </si>
+  <si>
+    <t>Weihnachtsfeier</t>
+  </si>
+  <si>
+    <t>Weihnachtsfeier 2026</t>
+  </si>
+  <si>
+    <t>Party</t>
+  </si>
+  <si>
+    <t>Weihnachtsfeier Nachwuchs ASV</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1081,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1364,6 +1385,9 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1596,7 +1620,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" bestFit="1" customWidth="1"/>
@@ -3158,7 +3182,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="111">
-        <f t="shared" ref="A67:A122" si="1">A66+1</f>
+        <f t="shared" ref="A67:A129" si="1">A66+1</f>
         <v>65</v>
       </c>
       <c r="B67" s="111">
@@ -4329,6 +4353,195 @@
         <v>104</v>
       </c>
       <c r="H122" s="49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="B123" s="2">
+        <v>1</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D123" s="13">
+        <v>46367</v>
+      </c>
+      <c r="E123" s="133">
+        <v>0.6875</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="B124" s="2">
+        <v>2</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D124" s="13">
+        <v>46368</v>
+      </c>
+      <c r="E124" s="133">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="B125" s="2">
+        <v>3</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D125" s="13">
+        <v>46369</v>
+      </c>
+      <c r="E125" s="133">
+        <v>0.375</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+      <c r="B126" s="2">
+        <v>0</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D126" s="13">
+        <v>46359</v>
+      </c>
+      <c r="E126" s="133">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="B127" s="2">
+        <v>4</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D127" s="13">
+        <v>46402</v>
+      </c>
+      <c r="E127" s="133">
+        <v>0.6875</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="B128" s="2">
+        <v>5</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D128" s="13">
+        <v>46403</v>
+      </c>
+      <c r="E128" s="133">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="B129" s="2">
+        <v>6</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D129" s="13">
+        <v>46404</v>
+      </c>
+      <c r="E129" s="133">
+        <v>0.375</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4350,7 +4563,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="105"/>
@@ -4360,6 +4573,7 @@
     <col min="5" max="5" width="21.6640625" style="36" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.109375" style="105" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="115"/>
+    <col min="8" max="8" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" style="105"/>
   </cols>
   <sheetData>
@@ -9118,6 +9332,275 @@
         <v>109</v>
       </c>
       <c r="L122" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B123" s="102">
+        <f>'Nach Mannschaften sortiert'!D123</f>
+        <v>46367</v>
+      </c>
+      <c r="C123" s="36">
+        <f>'Nach Mannschaften sortiert'!E123</f>
+        <v>0.6875</v>
+      </c>
+      <c r="D123" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E123" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F123)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G123" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H123</f>
+        <v>Heim</v>
+      </c>
+      <c r="H123" t="str">
+        <f>'Nach Mannschaften sortiert'!G123</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I123" t="str">
+        <f>'Nach Mannschaften sortiert'!C123</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J123" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K123" t="s">
+        <v>109</v>
+      </c>
+      <c r="L123" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B124" s="102">
+        <f>'Nach Mannschaften sortiert'!D124</f>
+        <v>46368</v>
+      </c>
+      <c r="C124" s="36">
+        <f>'Nach Mannschaften sortiert'!E124</f>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D124" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E124" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F124)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G124" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H124</f>
+        <v>Heim</v>
+      </c>
+      <c r="H124" t="str">
+        <f>'Nach Mannschaften sortiert'!G124</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I124" t="str">
+        <f>'Nach Mannschaften sortiert'!C124</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J124" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K124" t="s">
+        <v>109</v>
+      </c>
+      <c r="L124" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="125" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B125" s="102">
+        <f>'Nach Mannschaften sortiert'!D125</f>
+        <v>46369</v>
+      </c>
+      <c r="C125" s="36">
+        <f>'Nach Mannschaften sortiert'!E125</f>
+        <v>0.375</v>
+      </c>
+      <c r="D125" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E125" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F125)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G125" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H125</f>
+        <v>Heim</v>
+      </c>
+      <c r="H125" t="str">
+        <f>'Nach Mannschaften sortiert'!G125</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I125" t="str">
+        <f>'Nach Mannschaften sortiert'!C125</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J125" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K125" t="s">
+        <v>109</v>
+      </c>
+      <c r="L125" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B126" s="102">
+        <f>'Nach Mannschaften sortiert'!D126</f>
+        <v>46359</v>
+      </c>
+      <c r="C126" s="36">
+        <f>'Nach Mannschaften sortiert'!E126</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D126" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E126" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F126)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="F126" s="105" t="s">
+        <v>170</v>
+      </c>
+      <c r="G126" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H126</f>
+        <v>Heim</v>
+      </c>
+      <c r="H126" t="str">
+        <f>'Nach Mannschaften sortiert'!G126</f>
+        <v>Weihnachtsfeier 2026</v>
+      </c>
+      <c r="I126" t="str">
+        <f>'Nach Mannschaften sortiert'!C126</f>
+        <v>Weihnachtsfeier</v>
+      </c>
+      <c r="J126" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K126" t="s">
+        <v>109</v>
+      </c>
+      <c r="L126" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B127" s="102">
+        <f>'Nach Mannschaften sortiert'!D127</f>
+        <v>46402</v>
+      </c>
+      <c r="C127" s="36">
+        <f>'Nach Mannschaften sortiert'!E127</f>
+        <v>0.6875</v>
+      </c>
+      <c r="D127" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E127" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F127)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G127" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H127</f>
+        <v>Heim</v>
+      </c>
+      <c r="H127" t="str">
+        <f>'Nach Mannschaften sortiert'!G127</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I127" t="str">
+        <f>'Nach Mannschaften sortiert'!C127</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J127" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K127" t="s">
+        <v>109</v>
+      </c>
+      <c r="L127" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B128" s="102">
+        <f>'Nach Mannschaften sortiert'!D128</f>
+        <v>46403</v>
+      </c>
+      <c r="C128" s="36">
+        <f>'Nach Mannschaften sortiert'!E128</f>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D128" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E128" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F128)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G128" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H128</f>
+        <v>Heim</v>
+      </c>
+      <c r="H128" t="str">
+        <f>'Nach Mannschaften sortiert'!G128</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I128" t="str">
+        <f>'Nach Mannschaften sortiert'!C128</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J128" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K128" t="s">
+        <v>109</v>
+      </c>
+      <c r="L128" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B129" s="102">
+        <f>'Nach Mannschaften sortiert'!D129</f>
+        <v>46404</v>
+      </c>
+      <c r="C129" s="36">
+        <f>'Nach Mannschaften sortiert'!E129</f>
+        <v>0.375</v>
+      </c>
+      <c r="D129" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E129" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F129)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G129" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H129</f>
+        <v>Heim</v>
+      </c>
+      <c r="H129" t="str">
+        <f>'Nach Mannschaften sortiert'!G129</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I129" t="str">
+        <f>'Nach Mannschaften sortiert'!C129</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J129" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K129" t="s">
+        <v>109</v>
+      </c>
+      <c r="L129" t="s">
         <v>145</v>
       </c>
     </row>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67768253-A06A-492C-AE9B-3F56E3C79E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4BBBF7-B3FE-4D3B-A771-5E3A4644A26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -1358,6 +1358,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1385,9 +1388,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1882,7 +1882,7 @@
         <v>30</v>
       </c>
       <c r="D10" s="12">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E10" s="5">
         <v>0.72916666666666663</v>
@@ -1939,7 +1939,7 @@
         <v>46263</v>
       </c>
       <c r="E12" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>2</v>
@@ -1990,10 +1990,10 @@
         <v>30</v>
       </c>
       <c r="D14" s="12">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="E14" s="5">
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>2</v>
@@ -2047,7 +2047,7 @@
         <v>46291</v>
       </c>
       <c r="E16" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>2</v>
@@ -2098,10 +2098,10 @@
         <v>30</v>
       </c>
       <c r="D18" s="12">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="E18" s="5">
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>2</v>
@@ -2125,10 +2125,10 @@
         <v>30</v>
       </c>
       <c r="D19" s="12">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="E19" s="5">
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>3</v>
@@ -2155,7 +2155,7 @@
         <v>46319</v>
       </c>
       <c r="E20" s="5">
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>2</v>
@@ -2182,7 +2182,7 @@
         <v>46326</v>
       </c>
       <c r="E21" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>29</v>
@@ -2209,7 +2209,7 @@
         <v>46333</v>
       </c>
       <c r="E22" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>2</v>
@@ -2233,7 +2233,7 @@
         <v>58</v>
       </c>
       <c r="D23" s="12">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E23" s="5">
         <v>0.64583333333333337</v>
@@ -2290,7 +2290,7 @@
         <v>46263</v>
       </c>
       <c r="E25" s="5">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>2</v>
@@ -2341,10 +2341,10 @@
         <v>58</v>
       </c>
       <c r="D27" s="12">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="E27" s="5">
-        <v>0.60416666666666663</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>2</v>
@@ -2398,7 +2398,7 @@
         <v>46291</v>
       </c>
       <c r="E29" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>2</v>
@@ -2449,10 +2449,10 @@
         <v>58</v>
       </c>
       <c r="D31" s="12">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="E31" s="5">
-        <v>0.5625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>2</v>
@@ -2476,10 +2476,10 @@
         <v>58</v>
       </c>
       <c r="D32" s="12">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="E32" s="5">
-        <v>0.5625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>3</v>
@@ -2506,7 +2506,7 @@
         <v>46319</v>
       </c>
       <c r="E33" s="5">
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>2</v>
@@ -2533,7 +2533,7 @@
         <v>46326</v>
       </c>
       <c r="E34" s="5">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>29</v>
@@ -2560,7 +2560,7 @@
         <v>46333</v>
       </c>
       <c r="E35" s="5">
-        <v>0.5</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>2</v>
@@ -4370,7 +4370,7 @@
       <c r="D123" s="13">
         <v>46367</v>
       </c>
-      <c r="E123" s="133">
+      <c r="E123" s="116">
         <v>0.6875</v>
       </c>
       <c r="F123" s="2" t="s">
@@ -4397,7 +4397,7 @@
       <c r="D124" s="13">
         <v>46368</v>
       </c>
-      <c r="E124" s="133">
+      <c r="E124" s="116">
         <v>0.35416666666666669</v>
       </c>
       <c r="F124" s="2" t="s">
@@ -4424,7 +4424,7 @@
       <c r="D125" s="13">
         <v>46369</v>
       </c>
-      <c r="E125" s="133">
+      <c r="E125" s="116">
         <v>0.375</v>
       </c>
       <c r="F125" s="2" t="s">
@@ -4451,7 +4451,7 @@
       <c r="D126" s="13">
         <v>46359</v>
       </c>
-      <c r="E126" s="133">
+      <c r="E126" s="116">
         <v>0.70833333333333337</v>
       </c>
       <c r="F126" s="2" t="s">
@@ -4478,7 +4478,7 @@
       <c r="D127" s="13">
         <v>46402</v>
       </c>
-      <c r="E127" s="133">
+      <c r="E127" s="116">
         <v>0.6875</v>
       </c>
       <c r="F127" s="2" t="s">
@@ -4505,7 +4505,7 @@
       <c r="D128" s="13">
         <v>46403</v>
       </c>
-      <c r="E128" s="133">
+      <c r="E128" s="116">
         <v>0.35416666666666669</v>
       </c>
       <c r="F128" s="2" t="s">
@@ -4532,7 +4532,7 @@
       <c r="D129" s="13">
         <v>46404</v>
       </c>
-      <c r="E129" s="133">
+      <c r="E129" s="116">
         <v>0.375</v>
       </c>
       <c r="F129" s="2" t="s">
@@ -4933,7 +4933,7 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="102">
         <f>'Nach Mannschaften sortiert'!D10</f>
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="C10" s="36">
         <f>'Nach Mannschaften sortiert'!E10</f>
@@ -5015,11 +5015,11 @@
       </c>
       <c r="C12" s="36">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D12" s="36">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E12" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
@@ -5089,15 +5089,15 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="102">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="C14" s="36">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="D14" s="36">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E14" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
@@ -5171,11 +5171,11 @@
       </c>
       <c r="C16" s="36">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E16" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
@@ -5245,15 +5245,15 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="102">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="C18" s="36">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D18" s="36">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E18" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
@@ -5284,15 +5284,15 @@
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="102">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="C19" s="36">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D19" s="36">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E19" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
@@ -5327,11 +5327,11 @@
       </c>
       <c r="C20" s="36">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D20" s="36">
         <f t="shared" si="0"/>
-        <v>0.69791666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E20" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
@@ -5366,11 +5366,11 @@
       </c>
       <c r="C21" s="36">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D21" s="36">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E21" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
@@ -5405,11 +5405,11 @@
       </c>
       <c r="C22" s="36">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.58333333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D22" s="36">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E22" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
@@ -5440,7 +5440,7 @@
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="102">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="C23" s="36">
         <f>'Nach Mannschaften sortiert'!E23</f>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="C25" s="36">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D25" s="36">
         <f t="shared" si="0"/>
-        <v>0.69791666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E25" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
@@ -5596,15 +5596,15 @@
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="102">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="C27" s="36">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.60416666666666663</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D27" s="36">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E27" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
@@ -5678,11 +5678,11 @@
       </c>
       <c r="C29" s="36">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D29" s="36">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E29" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
@@ -5752,15 +5752,15 @@
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="102">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="C31" s="36">
         <f>'Nach Mannschaften sortiert'!E31</f>
-        <v>0.5625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D31" s="36">
         <f t="shared" si="0"/>
-        <v>0.63541666666666663</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E31" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
@@ -5791,15 +5791,15 @@
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="102">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="C32" s="36">
         <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0.5625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D32" s="36">
         <f t="shared" si="0"/>
-        <v>0.63541666666666663</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E32" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
@@ -5834,11 +5834,11 @@
       </c>
       <c r="C33" s="36">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D33" s="36">
         <f t="shared" si="0"/>
-        <v>0.61458333333333326</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E33" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
@@ -5873,11 +5873,11 @@
       </c>
       <c r="C34" s="36">
         <f>'Nach Mannschaften sortiert'!E34</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D34" s="36">
         <f t="shared" si="0"/>
-        <v>0.57291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E34" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
@@ -5912,11 +5912,11 @@
       </c>
       <c r="C35" s="36">
         <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0.5</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D35" s="36">
         <f t="shared" si="0"/>
-        <v>0.57291666666666663</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E35" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
@@ -9851,16 +9851,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
@@ -9887,7 +9887,7 @@
       <c r="H2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="119" t="s">
+      <c r="I2" s="120" t="s">
         <v>66</v>
       </c>
       <c r="J2" s="47"/>
@@ -9907,7 +9907,7 @@
       <c r="F3" s="82"/>
       <c r="G3" s="82"/>
       <c r="H3" s="84"/>
-      <c r="I3" s="120"/>
+      <c r="I3" s="121"/>
       <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G4" s="82"/>
       <c r="H4" s="84"/>
-      <c r="I4" s="120"/>
+      <c r="I4" s="121"/>
       <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G5" s="82"/>
       <c r="H5" s="84"/>
-      <c r="I5" s="120"/>
+      <c r="I5" s="121"/>
       <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="G6" s="86"/>
       <c r="H6" s="84"/>
-      <c r="I6" s="120"/>
+      <c r="I6" s="121"/>
       <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -9989,7 +9989,7 @@
         <v>56</v>
       </c>
       <c r="H7" s="84"/>
-      <c r="I7" s="120"/>
+      <c r="I7" s="121"/>
       <c r="J7" s="47"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -10011,7 +10011,7 @@
         <v>56</v>
       </c>
       <c r="H8" s="84"/>
-      <c r="I8" s="120"/>
+      <c r="I8" s="121"/>
       <c r="J8" s="47"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10035,7 +10035,7 @@
       <c r="H9" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="120"/>
+      <c r="I9" s="121"/>
       <c r="J9" s="47"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -10057,7 +10057,7 @@
         <v>94</v>
       </c>
       <c r="H10" s="84"/>
-      <c r="I10" s="120"/>
+      <c r="I10" s="121"/>
       <c r="J10" s="47"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" thickBot="1" x14ac:dyDescent="0.4">
@@ -10077,7 +10077,7 @@
         <v>65</v>
       </c>
       <c r="H11" s="93"/>
-      <c r="I11" s="121"/>
+      <c r="I11" s="122"/>
       <c r="J11" s="47"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
@@ -10135,52 +10135,52 @@
       <c r="H14" s="100"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="126"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="127"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="127" t="s">
+      <c r="A16" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="128"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="129"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="130" t="s">
+      <c r="A17" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="132"/>
+      <c r="B17" s="132"/>
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="133"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="116" t="s">
+      <c r="A18" s="117" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="118"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="119"/>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="D2" s="13">
         <f>'Nach Mannschaften sortiert'!D10</f>
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E2" s="35">
         <f>'Nach Mannschaften sortiert'!E10</f>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="E4" s="35">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F4" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F12</f>
@@ -10399,11 +10399,11 @@
       </c>
       <c r="D6" s="13">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="E6" s="35">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="F6" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F14</f>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="E8" s="35">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F8" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F16</f>
@@ -10535,11 +10535,11 @@
       </c>
       <c r="D10" s="13">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="E10" s="35">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F10" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F18</f>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="E12" s="35">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F12" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F20</f>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="E13" s="35">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F13" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F21</f>
@@ -12167,11 +12167,11 @@
       </c>
       <c r="D58" s="58">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="E58" s="59">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F58" s="57" t="str">
         <f>'Nach Mannschaften sortiert'!F19</f>
@@ -12747,7 +12747,7 @@
       </c>
       <c r="E75" s="59">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.58333333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F75" s="57" t="str">
         <f>'Nach Mannschaften sortiert'!F22</f>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="B5" s="69">
         <f>Heimspiele!D6</f>
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" t="str">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="B9" s="69">
         <f>Heimspiele!D10</f>
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" t="str">
@@ -16044,11 +16044,11 @@
       </c>
       <c r="B69" s="78">
         <f>Heimspiele!D58</f>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="C69" s="79">
         <f>Heimspiele!E58</f>
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D69" s="77" t="str">
         <f>Heimspiele!F58</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="C82" s="79">
         <f>Heimspiele!E75</f>
-        <v>0.58333333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D82" s="77" t="str">
         <f>Heimspiele!F75</f>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4BBBF7-B3FE-4D3B-A771-5E3A4644A26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0DEF98-B697-4A92-BF02-F117D6A5D4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="172">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -558,6 +558,9 @@
   </si>
   <si>
     <t>Weihnachtsfeier Nachwuchs ASV</t>
+  </si>
+  <si>
+    <t>Theresienfeld</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1623,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1714,7 +1717,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <f t="shared" ref="A4:A66" si="0">A3+1</f>
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="4">
@@ -1848,6 +1851,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="B9" s="4">
         <v>0</v>
       </c>
@@ -1871,54 +1878,54 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
-        <f>A8+1</f>
-        <v>8</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="12">
-        <v>46250</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>10</v>
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="11">
+        <v>46236</v>
+      </c>
+      <c r="E10" s="114">
+        <v>0.4375</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="12">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E11" s="5">
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>10</v>
@@ -1927,349 +1934,349 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="12">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E12" s="5">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="12">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E13" s="5">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D14" s="12">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E14" s="5">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="12">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E15" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="12">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E16" s="5">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="12">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="E17" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="12">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="E18" s="5">
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="12">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E19" s="5">
         <v>0.8125</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="12">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E20" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="12">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E21" s="5">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="12">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E22" s="5">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D23" s="12">
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="E23" s="5">
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D24" s="12">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E24" s="5">
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>10</v>
@@ -2278,332 +2285,340 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D25" s="12">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E25" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D26" s="12">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E26" s="5">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D27" s="12">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E27" s="5">
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D28" s="12">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E28" s="5">
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="12">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E29" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="12">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="E30" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D31" s="12">
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="E31" s="5">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="12">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E32" s="5">
         <v>0.72916666666666663</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D33" s="12">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E33" s="5">
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D34" s="12">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E34" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D35" s="12">
+        <v>46326</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="6">
+        <v>13</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="12">
         <v>46333</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E36" s="5">
         <v>0.60416666666666663</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G36" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="26">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B36" s="26">
-        <v>1</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="33">
-        <v>46023</v>
-      </c>
-      <c r="E36" s="27"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D37" s="33">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="26"/>
@@ -2613,16 +2628,16 @@
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="26">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D38" s="33">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="26"/>
@@ -2632,16 +2647,16 @@
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="26">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D39" s="33">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="E39" s="27"/>
       <c r="F39" s="26"/>
@@ -2651,16 +2666,16 @@
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="26">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D40" s="33">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="26"/>
@@ -2670,16 +2685,16 @@
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="26">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D41" s="33">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="E41" s="27"/>
       <c r="F41" s="26"/>
@@ -2689,16 +2704,16 @@
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="26">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D42" s="33">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="E42" s="27"/>
       <c r="F42" s="26"/>
@@ -2708,16 +2723,16 @@
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="26">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D43" s="33">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="E43" s="27"/>
       <c r="F43" s="26"/>
@@ -2727,16 +2742,16 @@
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="26">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D44" s="33">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="E44" s="27"/>
       <c r="F44" s="26"/>
@@ -2746,76 +2761,74 @@
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="26">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D45" s="33">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="E45" s="27"/>
       <c r="F45" s="26"/>
       <c r="G45" s="26"/>
       <c r="H45" s="26"/>
     </row>
-    <row r="46" spans="1:10" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B46" s="17">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="26">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="26">
+        <v>10</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="33">
+        <v>46032</v>
+      </c>
+      <c r="E46" s="27"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+    </row>
+    <row r="47" spans="1:10" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="23">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B47" s="17">
         <v>1</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D46" s="18">
-        <v>46033</v>
-      </c>
-      <c r="E46" s="19"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="21"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="23">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B47" s="17">
-        <v>2</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D47" s="18">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="E47" s="19"/>
       <c r="F47" s="17"/>
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="22"/>
+      <c r="I47" s="21"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="23">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="18">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="E48" s="19"/>
       <c r="F48" s="17"/>
@@ -2827,16 +2840,16 @@
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="23">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D49" s="18">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E49" s="19"/>
       <c r="F49" s="17"/>
@@ -2848,16 +2861,16 @@
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="23">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D50" s="18">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="E50" s="19"/>
       <c r="F50" s="17"/>
@@ -2869,16 +2882,16 @@
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="23">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D51" s="18">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="E51" s="19"/>
       <c r="F51" s="17"/>
@@ -2890,16 +2903,16 @@
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="23">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D52" s="18">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="E52" s="19"/>
       <c r="F52" s="17"/>
@@ -2911,16 +2924,16 @@
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="23">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D53" s="18">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="E53" s="19"/>
       <c r="F53" s="17"/>
@@ -2932,16 +2945,16 @@
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="23">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="18">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="E54" s="19"/>
       <c r="F54" s="17"/>
@@ -2953,16 +2966,16 @@
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="23">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D55" s="18">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="E55" s="19"/>
       <c r="F55" s="17"/>
@@ -2971,38 +2984,40 @@
       <c r="I55" s="20"/>
       <c r="J55" s="22"/>
     </row>
-    <row r="56" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="8">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="B56" s="8">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="23">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B56" s="17">
+        <v>10</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" s="18">
+        <v>46042</v>
+      </c>
+      <c r="E56" s="19"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="22"/>
+    </row>
+    <row r="57" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B57" s="8">
         <v>1</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D56" s="28">
-        <v>46043</v>
-      </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="8">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="B57" s="8">
-        <v>2</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D57" s="28">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E57" s="9"/>
       <c r="F57" s="8"/>
@@ -3012,16 +3027,16 @@
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D58" s="28">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="E58" s="9"/>
       <c r="F58" s="8"/>
@@ -3031,16 +3046,16 @@
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D59" s="28">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="E59" s="9"/>
       <c r="F59" s="8"/>
@@ -3050,16 +3065,16 @@
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D60" s="28">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="E60" s="9"/>
       <c r="F60" s="8"/>
@@ -3069,16 +3084,16 @@
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D61" s="28">
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="E61" s="9"/>
       <c r="F61" s="8"/>
@@ -3088,16 +3103,16 @@
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D62" s="28">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="E62" s="9"/>
       <c r="F62" s="8"/>
@@ -3107,16 +3122,16 @@
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D63" s="28">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="E63" s="9"/>
       <c r="F63" s="8"/>
@@ -3126,16 +3141,16 @@
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B64" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D64" s="28">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="E64" s="9"/>
       <c r="F64" s="8"/>
@@ -3145,16 +3160,16 @@
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D65" s="28">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="E65" s="9"/>
       <c r="F65" s="8"/>
@@ -3162,37 +3177,37 @@
       <c r="H65" s="8"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="111">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B66" s="111">
-        <v>1</v>
-      </c>
-      <c r="C66" s="111" t="s">
-        <v>158</v>
-      </c>
-      <c r="D66" s="112">
-        <v>46053</v>
-      </c>
-      <c r="E66" s="113"/>
-      <c r="F66" s="111"/>
-      <c r="G66" s="111"/>
-      <c r="H66" s="111"/>
+      <c r="A66" s="8">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B66" s="8">
+        <v>10</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D66" s="28">
+        <v>46052</v>
+      </c>
+      <c r="E66" s="9"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="111">
-        <f t="shared" ref="A67:A129" si="1">A66+1</f>
-        <v>65</v>
+        <f t="shared" si="0"/>
+        <v>66</v>
       </c>
       <c r="B67" s="111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D67" s="112">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="E67" s="113"/>
       <c r="F67" s="111"/>
@@ -3201,17 +3216,17 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="111">
-        <f t="shared" si="1"/>
-        <v>66</v>
+        <f t="shared" ref="A68:A130" si="1">A67+1</f>
+        <v>67</v>
       </c>
       <c r="B68" s="111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D68" s="112">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="E68" s="113"/>
       <c r="F68" s="111"/>
@@ -3221,16 +3236,16 @@
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="111">
         <f t="shared" si="1"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" s="111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D69" s="112">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="E69" s="113"/>
       <c r="F69" s="111"/>
@@ -3240,16 +3255,16 @@
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="111">
         <f t="shared" si="1"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B70" s="111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D70" s="112">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="E70" s="113"/>
       <c r="F70" s="111"/>
@@ -3259,16 +3274,16 @@
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="111">
         <f t="shared" si="1"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" s="111">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D71" s="112">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="E71" s="113"/>
       <c r="F71" s="111"/>
@@ -3278,16 +3293,16 @@
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="111">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B72" s="111">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C72" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D72" s="112">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="E72" s="113"/>
       <c r="F72" s="111"/>
@@ -3297,16 +3312,16 @@
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="111">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B73" s="111">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C73" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D73" s="112">
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="E73" s="113"/>
       <c r="F73" s="111"/>
@@ -3316,16 +3331,16 @@
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="111">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B74" s="111">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C74" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D74" s="112">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="E74" s="113"/>
       <c r="F74" s="111"/>
@@ -3335,16 +3350,16 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="111">
         <f t="shared" si="1"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" s="111">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C75" s="111" t="s">
         <v>158</v>
       </c>
       <c r="D75" s="112">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="E75" s="113"/>
       <c r="F75" s="111"/>
@@ -3352,37 +3367,37 @@
       <c r="H75" s="111"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="24">
+      <c r="A76" s="111">
         <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-      <c r="B76" s="24">
-        <v>1</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D76" s="29">
-        <v>46063</v>
-      </c>
-      <c r="E76" s="25"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
+        <v>75</v>
+      </c>
+      <c r="B76" s="111">
+        <v>10</v>
+      </c>
+      <c r="C76" s="111" t="s">
+        <v>158</v>
+      </c>
+      <c r="D76" s="112">
+        <v>46062</v>
+      </c>
+      <c r="E76" s="113"/>
+      <c r="F76" s="111"/>
+      <c r="G76" s="111"/>
+      <c r="H76" s="111"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="24">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D77" s="29">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="E77" s="25"/>
       <c r="F77" s="24"/>
@@ -3392,16 +3407,16 @@
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="24">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B78" s="24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D78" s="29">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="E78" s="25"/>
       <c r="F78" s="24"/>
@@ -3411,16 +3426,16 @@
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="24">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" s="24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C79" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D79" s="29">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="E79" s="25"/>
       <c r="F79" s="24"/>
@@ -3430,16 +3445,16 @@
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="24">
         <f t="shared" si="1"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B80" s="24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D80" s="29">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="E80" s="25"/>
       <c r="F80" s="24"/>
@@ -3449,16 +3464,16 @@
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="24">
         <f t="shared" si="1"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" s="24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D81" s="29">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="E81" s="25"/>
       <c r="F81" s="24"/>
@@ -3468,16 +3483,16 @@
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="24">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B82" s="24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D82" s="29">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="E82" s="25"/>
       <c r="F82" s="24"/>
@@ -3487,16 +3502,16 @@
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="24">
         <f t="shared" si="1"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B83" s="24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D83" s="29">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="E83" s="25"/>
       <c r="F83" s="24"/>
@@ -3506,16 +3521,16 @@
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="24">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B84" s="24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C84" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D84" s="29">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E84" s="25"/>
       <c r="F84" s="24"/>
@@ -3525,16 +3540,16 @@
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="24">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B85" s="24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C85" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D85" s="29">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E85" s="25"/>
       <c r="F85" s="24"/>
@@ -3542,64 +3557,64 @@
       <c r="H85" s="24"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="108">
+      <c r="A86" s="24">
         <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-      <c r="B86" s="108">
-        <v>1</v>
-      </c>
-      <c r="C86" s="108" t="s">
-        <v>146</v>
-      </c>
-      <c r="D86" s="109">
-        <v>46312</v>
-      </c>
-      <c r="E86" s="110">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F86" s="110" t="s">
-        <v>2</v>
-      </c>
-      <c r="G86" s="108" t="s">
-        <v>163</v>
-      </c>
-      <c r="H86" s="108" t="s">
-        <v>11</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B86" s="24">
+        <v>10</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D86" s="29">
+        <v>46072</v>
+      </c>
+      <c r="E86" s="25"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="24"/>
+      <c r="H86" s="24"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="108">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" s="108" t="s">
         <v>146</v>
       </c>
       <c r="D87" s="109">
-        <v>46074</v>
-      </c>
-      <c r="E87" s="110"/>
-      <c r="F87" s="108"/>
-      <c r="G87" s="108"/>
-      <c r="H87" s="108"/>
+        <v>46312</v>
+      </c>
+      <c r="E87" s="110">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F87" s="110" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="108" t="s">
+        <v>163</v>
+      </c>
+      <c r="H87" s="108" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="108">
         <f t="shared" si="1"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B88" s="108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88" s="108" t="s">
         <v>146</v>
       </c>
       <c r="D88" s="109">
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="E88" s="110"/>
       <c r="F88" s="108"/>
@@ -3609,16 +3624,16 @@
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="108">
         <f t="shared" si="1"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89" s="108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C89" s="108" t="s">
         <v>146</v>
       </c>
       <c r="D89" s="109">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="E89" s="110"/>
       <c r="F89" s="108"/>
@@ -3628,16 +3643,16 @@
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="108">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B90" s="108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C90" s="108" t="s">
         <v>146</v>
       </c>
       <c r="D90" s="109">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="E90" s="110"/>
       <c r="F90" s="108"/>
@@ -3645,37 +3660,37 @@
       <c r="H90" s="108"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="10">
+      <c r="A91" s="108">
         <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B91" s="10">
-        <v>1</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D91" s="34">
-        <v>46078</v>
-      </c>
-      <c r="E91" s="16"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
+        <v>90</v>
+      </c>
+      <c r="B91" s="108">
+        <v>5</v>
+      </c>
+      <c r="C91" s="108" t="s">
+        <v>146</v>
+      </c>
+      <c r="D91" s="109">
+        <v>46077</v>
+      </c>
+      <c r="E91" s="110"/>
+      <c r="F91" s="108"/>
+      <c r="G91" s="108"/>
+      <c r="H91" s="108"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B92" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="34">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E92" s="16"/>
       <c r="F92" s="10"/>
@@ -3685,16 +3700,16 @@
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <f t="shared" si="1"/>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D93" s="34">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E93" s="16"/>
       <c r="F93" s="10"/>
@@ -3704,16 +3719,16 @@
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <f t="shared" si="1"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B94" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D94" s="34">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="E94" s="16"/>
       <c r="F94" s="10"/>
@@ -3723,16 +3738,16 @@
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <f t="shared" si="1"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D95" s="34">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E95" s="16"/>
       <c r="F95" s="10"/>
@@ -3742,16 +3757,16 @@
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B96" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="34">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="E96" s="16"/>
       <c r="F96" s="10"/>
@@ -3761,16 +3776,16 @@
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B97" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D97" s="34">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E97" s="16"/>
       <c r="F97" s="10"/>
@@ -3780,16 +3795,16 @@
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B98" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="34">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E98" s="16"/>
       <c r="F98" s="10"/>
@@ -3799,16 +3814,16 @@
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="34">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E99" s="16"/>
       <c r="F99" s="10"/>
@@ -3818,16 +3833,16 @@
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="34">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E100" s="16"/>
       <c r="F100" s="10"/>
@@ -3835,64 +3850,64 @@
       <c r="H100" s="10"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="30">
+      <c r="A101" s="10">
         <f t="shared" si="1"/>
-        <v>99</v>
-      </c>
-      <c r="B101" s="30">
-        <v>1</v>
-      </c>
-      <c r="C101" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D101" s="31">
-        <v>46312</v>
-      </c>
-      <c r="E101" s="32">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F101" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="G101" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="H101" s="30" t="s">
-        <v>11</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B101" s="10">
+        <v>10</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" s="34">
+        <v>46087</v>
+      </c>
+      <c r="E101" s="16"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="10"/>
+      <c r="H101" s="10"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="30">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B102" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="31">
-        <v>46089</v>
-      </c>
-      <c r="E102" s="32"/>
-      <c r="F102" s="30"/>
-      <c r="G102" s="30"/>
-      <c r="H102" s="30"/>
+        <v>46312</v>
+      </c>
+      <c r="E102" s="32">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F102" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="G102" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="H102" s="30" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="30">
         <f t="shared" si="1"/>
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B103" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D103" s="31">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E103" s="32"/>
       <c r="F103" s="30"/>
@@ -3902,16 +3917,16 @@
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="30">
         <f t="shared" si="1"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B104" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C104" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="31">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="E104" s="32"/>
       <c r="F104" s="30"/>
@@ -3921,16 +3936,16 @@
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="30">
         <f t="shared" si="1"/>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B105" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D105" s="31">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E105" s="32"/>
       <c r="F105" s="30"/>
@@ -3938,37 +3953,37 @@
       <c r="H105" s="30"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="50">
+      <c r="A106" s="30">
         <f t="shared" si="1"/>
-        <v>104</v>
-      </c>
-      <c r="B106" s="50">
-        <v>1</v>
-      </c>
-      <c r="C106" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="D106" s="51">
-        <v>46312</v>
-      </c>
-      <c r="E106" s="52"/>
-      <c r="F106" s="50"/>
-      <c r="G106" s="50"/>
-      <c r="H106" s="50"/>
+        <v>105</v>
+      </c>
+      <c r="B106" s="30">
+        <v>5</v>
+      </c>
+      <c r="C106" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="31">
+        <v>46092</v>
+      </c>
+      <c r="E106" s="32"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+      <c r="H106" s="30"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="50">
         <f t="shared" si="1"/>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B107" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D107" s="51">
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="E107" s="52"/>
       <c r="F107" s="50"/>
@@ -3978,16 +3993,16 @@
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="50">
         <f t="shared" si="1"/>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B108" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D108" s="51">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="E108" s="52"/>
       <c r="F108" s="50"/>
@@ -3997,16 +4012,16 @@
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="50">
         <f t="shared" si="1"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B109" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D109" s="51">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="E109" s="52"/>
       <c r="F109" s="50"/>
@@ -4016,16 +4031,16 @@
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="50">
         <f t="shared" si="1"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B110" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" s="50" t="s">
         <v>72</v>
       </c>
       <c r="D110" s="51">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="E110" s="52"/>
       <c r="F110" s="50"/>
@@ -4033,45 +4048,37 @@
       <c r="H110" s="50"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="37">
+      <c r="A111" s="50">
         <f t="shared" si="1"/>
-        <v>109</v>
-      </c>
-      <c r="B111" s="37">
-        <v>1</v>
-      </c>
-      <c r="C111" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D111" s="80">
-        <v>46230</v>
-      </c>
-      <c r="E111" s="103">
-        <v>0.375</v>
-      </c>
-      <c r="F111" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="G111" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="H111" s="38" t="s">
-        <v>11</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B111" s="50">
+        <v>5</v>
+      </c>
+      <c r="C111" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="D111" s="51">
+        <v>46097</v>
+      </c>
+      <c r="E111" s="52"/>
+      <c r="F111" s="50"/>
+      <c r="G111" s="50"/>
+      <c r="H111" s="50"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="37">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B112" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D112" s="80">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="E112" s="103">
         <v>0.375</v>
@@ -4089,16 +4096,16 @@
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="37">
         <f t="shared" si="1"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B113" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D113" s="80">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="E113" s="103">
         <v>0.375</v>
@@ -4116,16 +4123,16 @@
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="37">
         <f t="shared" si="1"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B114" s="37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C114" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D114" s="80">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E114" s="103">
         <v>0.375</v>
@@ -4143,16 +4150,16 @@
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="37">
         <f t="shared" si="1"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B115" s="37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D115" s="80">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="E115" s="103">
         <v>0.375</v>
@@ -4170,16 +4177,16 @@
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="37">
         <f t="shared" si="1"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B116" s="37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C116" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D116" s="80">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="E116" s="103">
         <v>0.375</v>
@@ -4188,7 +4195,7 @@
         <v>2</v>
       </c>
       <c r="G116" s="38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H116" s="38" t="s">
         <v>11</v>
@@ -4197,16 +4204,16 @@
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="37">
         <f t="shared" si="1"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B117" s="37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C117" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D117" s="80">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E117" s="103">
         <v>0.375</v>
@@ -4224,16 +4231,16 @@
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="37">
         <f t="shared" si="1"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B118" s="37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D118" s="80">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E118" s="103">
         <v>0.375</v>
@@ -4251,16 +4258,16 @@
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="37">
         <f t="shared" si="1"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B119" s="37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C119" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D119" s="80">
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="E119" s="103">
         <v>0.375</v>
@@ -4269,7 +4276,7 @@
         <v>2</v>
       </c>
       <c r="G119" s="38" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="H119" s="38" t="s">
         <v>11</v>
@@ -4278,16 +4285,16 @@
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="37">
         <f t="shared" si="1"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B120" s="37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C120" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D120" s="80">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="E120" s="103">
         <v>0.375</v>
@@ -4305,16 +4312,16 @@
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="37">
         <f t="shared" si="1"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B121" s="37">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C121" s="37" t="s">
         <v>35</v>
       </c>
       <c r="D121" s="80">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E121" s="103">
         <v>0.375</v>
@@ -4330,75 +4337,75 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="48">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="B122" s="48">
-        <v>2</v>
-      </c>
-      <c r="C122" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D122" s="81">
-        <v>46256</v>
-      </c>
-      <c r="E122" s="104">
-        <v>0.375</v>
-      </c>
-      <c r="F122" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="G122" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H122" s="49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="2">
+      <c r="A122" s="37">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
-      <c r="B123" s="2">
-        <v>1</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D123" s="13">
-        <v>46367</v>
-      </c>
-      <c r="E123" s="116">
-        <v>0.6875</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H123" s="2" t="s">
+      <c r="B122" s="37">
+        <v>11</v>
+      </c>
+      <c r="C122" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D122" s="80">
+        <v>46323</v>
+      </c>
+      <c r="E122" s="103">
+        <v>0.375</v>
+      </c>
+      <c r="F122" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="G122" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H122" s="38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="48">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="B123" s="48">
+        <v>2</v>
+      </c>
+      <c r="C123" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D123" s="81">
+        <v>46256</v>
+      </c>
+      <c r="E123" s="104">
+        <v>0.375</v>
+      </c>
+      <c r="F123" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H123" s="49" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <f t="shared" si="1"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B124" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D124" s="13">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="E124" s="116">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>165</v>
@@ -4413,19 +4420,19 @@
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <f t="shared" si="1"/>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B125" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D125" s="13">
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="E125" s="116">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>165</v>
@@ -4440,25 +4447,25 @@
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <f t="shared" si="1"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B126" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D126" s="13">
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="E126" s="116">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>165</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>11</v>
@@ -4467,25 +4474,25 @@
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <f t="shared" si="1"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B127" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D127" s="13">
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="E127" s="116">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>165</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>11</v>
@@ -4494,19 +4501,19 @@
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <f t="shared" si="1"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B128" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D128" s="13">
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="E128" s="116">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>165</v>
@@ -4521,19 +4528,19 @@
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <f t="shared" si="1"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B129" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D129" s="13">
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="E129" s="116">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>165</v>
@@ -4545,25 +4552,52 @@
         <v>11</v>
       </c>
     </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="B130" s="2">
+        <v>6</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D130" s="13">
+        <v>46404</v>
+      </c>
+      <c r="E130" s="116">
+        <v>0.375</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H105" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H105">
-      <sortCondition ref="A1:A105"/>
+  <autoFilter ref="A1:H106" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H106">
+      <sortCondition ref="A1:A106"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="45" max="16383" man="1"/>
-    <brk id="55" max="16383" man="1"/>
+    <brk id="46" max="16383" man="1"/>
+    <brk id="56" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="105"/>
@@ -4664,7 +4698,7 @@
         <v>0.75</v>
       </c>
       <c r="D3" s="36">
-        <f t="shared" ref="D3:D67" si="0">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
+        <f t="shared" ref="D3:D68" si="0">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
         <v>0.82291666666666663</v>
       </c>
       <c r="E3" s="36" t="str">
@@ -4933,37 +4967,37 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="102">
         <f>'Nach Mannschaften sortiert'!D10</f>
-        <v>46250</v>
+        <v>46236</v>
       </c>
       <c r="C10" s="36">
         <f>'Nach Mannschaften sortiert'!E10</f>
-        <v>0.72916666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="D10" s="36">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="E10" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F10)</f>
-        <v>KITTSEE</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G10" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H10" t="str">
         <f>'Nach Mannschaften sortiert'!G10</f>
-        <v>Kittsee</v>
+        <v>Theresienfeld</v>
       </c>
       <c r="I10" t="str">
         <f>'Nach Mannschaften sortiert'!C10</f>
-        <v>KM</v>
+        <v>U16</v>
       </c>
       <c r="J10" s="105" t="s">
         <v>107</v>
       </c>
       <c r="K10" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="L10" t="s">
         <v>145</v>
@@ -4972,19 +5006,19 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="102">
         <f>'Nach Mannschaften sortiert'!D11</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C11" s="36">
         <f>'Nach Mannschaften sortiert'!E11</f>
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D11" s="36">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E11" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G11" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
@@ -4992,7 +5026,7 @@
       </c>
       <c r="H11" t="str">
         <f>'Nach Mannschaften sortiert'!G11</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I11" t="str">
         <f>'Nach Mannschaften sortiert'!C11</f>
@@ -5011,27 +5045,27 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="102">
         <f>'Nach Mannschaften sortiert'!D12</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C12" s="36">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D12" s="36">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.90625</v>
       </c>
       <c r="E12" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G12" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H12" t="str">
         <f>'Nach Mannschaften sortiert'!G12</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I12" t="str">
         <f>'Nach Mannschaften sortiert'!C12</f>
@@ -5050,27 +5084,27 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" s="102">
         <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C13" s="36">
         <f>'Nach Mannschaften sortiert'!E13</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D13" s="36">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E13" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G13" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H13" t="str">
         <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I13" t="str">
         <f>'Nach Mannschaften sortiert'!C13</f>
@@ -5089,27 +5123,27 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="102">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C14" s="36">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="D14" s="36">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E14" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G14" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H14" t="str">
         <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I14" t="str">
         <f>'Nach Mannschaften sortiert'!C14</f>
@@ -5128,27 +5162,27 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" s="102">
         <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C15" s="36">
         <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D15" s="36">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E15" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G15" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H15" t="str">
         <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I15" t="str">
         <f>'Nach Mannschaften sortiert'!C15</f>
@@ -5167,27 +5201,27 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" s="102">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C16" s="36">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E16" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G16" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H16" t="str">
         <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I16" t="str">
         <f>'Nach Mannschaften sortiert'!C16</f>
@@ -5206,27 +5240,27 @@
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="102">
         <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C17" s="36">
         <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" si="0"/>
-        <v>0.86458333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E17" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G17" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H17" t="str">
         <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I17" t="str">
         <f>'Nach Mannschaften sortiert'!C17</f>
@@ -5245,27 +5279,27 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="102">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="C18" s="36">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D18" s="36">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E18" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G18" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H18" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I18" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
@@ -5284,7 +5318,7 @@
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="102">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C19" s="36">
         <f>'Nach Mannschaften sortiert'!E19</f>
@@ -5296,15 +5330,15 @@
       </c>
       <c r="E19" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G19" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H19" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I19" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
@@ -5323,27 +5357,27 @@
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="102">
         <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C20" s="36">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D20" s="36">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E20" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G20" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H20" t="str">
         <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I20" t="str">
         <f>'Nach Mannschaften sortiert'!C20</f>
@@ -5362,27 +5396,27 @@
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="102">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C21" s="36">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D21" s="36">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E21" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G21" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H21" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I21" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
@@ -5401,27 +5435,27 @@
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="102">
         <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C22" s="36">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D22" s="36">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E22" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G22" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H22" t="str">
         <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I22" t="str">
         <f>'Nach Mannschaften sortiert'!C22</f>
@@ -5440,31 +5474,31 @@
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="102">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="C23" s="36">
         <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D23" s="36">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E23" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
-        <v>KITTSEE</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G23" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H23" t="str">
         <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Kittsee</v>
+        <v>Andau</v>
       </c>
       <c r="I23" t="str">
         <f>'Nach Mannschaften sortiert'!C23</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J23" s="105" t="s">
         <v>107</v>
@@ -5479,19 +5513,19 @@
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="102">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C24" s="36">
         <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D24" s="36">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="E24" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G24" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
@@ -5499,7 +5533,7 @@
       </c>
       <c r="H24" t="str">
         <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I24" t="str">
         <f>'Nach Mannschaften sortiert'!C24</f>
@@ -5518,27 +5552,27 @@
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="102">
         <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C25" s="36">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D25" s="36">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E25" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G25" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H25" t="str">
         <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I25" t="str">
         <f>'Nach Mannschaften sortiert'!C25</f>
@@ -5557,27 +5591,27 @@
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="102">
         <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C26" s="36">
         <f>'Nach Mannschaften sortiert'!E26</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D26" s="36">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E26" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G26" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H26" t="str">
         <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I26" t="str">
         <f>'Nach Mannschaften sortiert'!C26</f>
@@ -5596,27 +5630,27 @@
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="102">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C27" s="36">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D27" s="36">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E27" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G27" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H27" t="str">
         <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I27" t="str">
         <f>'Nach Mannschaften sortiert'!C27</f>
@@ -5635,27 +5669,27 @@
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="102">
         <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C28" s="36">
         <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D28" s="36">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E28" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G28" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H28" t="str">
         <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I28" t="str">
         <f>'Nach Mannschaften sortiert'!C28</f>
@@ -5674,27 +5708,27 @@
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="102">
         <f>'Nach Mannschaften sortiert'!D29</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C29" s="36">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D29" s="36">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.65625</v>
       </c>
       <c r="E29" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G29" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H29" t="str">
         <f>'Nach Mannschaften sortiert'!G29</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I29" t="str">
         <f>'Nach Mannschaften sortiert'!C29</f>
@@ -5713,27 +5747,27 @@
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="102">
         <f>'Nach Mannschaften sortiert'!D30</f>
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C30" s="36">
         <f>'Nach Mannschaften sortiert'!E30</f>
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D30" s="36">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E30" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G30" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H30" t="str">
         <f>'Nach Mannschaften sortiert'!G30</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I30" t="str">
         <f>'Nach Mannschaften sortiert'!C30</f>
@@ -5752,27 +5786,27 @@
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="102">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="C31" s="36">
         <f>'Nach Mannschaften sortiert'!E31</f>
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D31" s="36">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.78125</v>
       </c>
       <c r="E31" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G31" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H31" t="str">
         <f>'Nach Mannschaften sortiert'!G31</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I31" t="str">
         <f>'Nach Mannschaften sortiert'!C31</f>
@@ -5791,7 +5825,7 @@
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="102">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C32" s="36">
         <f>'Nach Mannschaften sortiert'!E32</f>
@@ -5803,15 +5837,15 @@
       </c>
       <c r="E32" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G32" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H32" t="str">
         <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
@@ -5830,27 +5864,27 @@
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="102">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C33" s="36">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D33" s="36">
         <f t="shared" si="0"/>
-        <v>0.69791666666666663</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E33" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G33" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H33" t="str">
         <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I33" t="str">
         <f>'Nach Mannschaften sortiert'!C33</f>
@@ -5869,27 +5903,27 @@
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="102">
         <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C34" s="36">
         <f>'Nach Mannschaften sortiert'!E34</f>
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D34" s="36">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E34" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G34" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H34" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I34" t="str">
         <f>'Nach Mannschaften sortiert'!C34</f>
@@ -5908,27 +5942,27 @@
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="102">
         <f>'Nach Mannschaften sortiert'!D35</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C35" s="36">
         <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D35" s="36">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E35" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G35" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H35" t="str">
         <f>'Nach Mannschaften sortiert'!G35</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I35" t="str">
         <f>'Nach Mannschaften sortiert'!C35</f>
@@ -5947,31 +5981,31 @@
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="102">
         <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46023</v>
+        <v>46333</v>
       </c>
       <c r="C36" s="36">
         <f>'Nach Mannschaften sortiert'!E36</f>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D36" s="36">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E36" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="115">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G36" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
-        <v>0</v>
-      </c>
-      <c r="H36">
+        <v>Heim</v>
+      </c>
+      <c r="H36" t="str">
         <f>'Nach Mannschaften sortiert'!G36</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I36" t="str">
         <f>'Nach Mannschaften sortiert'!C36</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J36" s="105" t="s">
         <v>107</v>
@@ -5986,7 +6020,7 @@
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="102">
         <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C37" s="36">
         <f>'Nach Mannschaften sortiert'!E37</f>
@@ -6025,7 +6059,7 @@
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="102">
         <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C38" s="36">
         <f>'Nach Mannschaften sortiert'!E38</f>
@@ -6064,7 +6098,7 @@
     <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="102">
         <f>'Nach Mannschaften sortiert'!D39</f>
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C39" s="36">
         <f>'Nach Mannschaften sortiert'!E39</f>
@@ -6103,7 +6137,7 @@
     <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="102">
         <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C40" s="36">
         <f>'Nach Mannschaften sortiert'!E40</f>
@@ -6142,7 +6176,7 @@
     <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="102">
         <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C41" s="36">
         <f>'Nach Mannschaften sortiert'!E41</f>
@@ -6181,7 +6215,7 @@
     <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="102">
         <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C42" s="36">
         <f>'Nach Mannschaften sortiert'!E42</f>
@@ -6220,7 +6254,7 @@
     <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="102">
         <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C43" s="36">
         <f>'Nach Mannschaften sortiert'!E43</f>
@@ -6259,7 +6293,7 @@
     <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="102">
         <f>'Nach Mannschaften sortiert'!D44</f>
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C44" s="36">
         <f>'Nach Mannschaften sortiert'!E44</f>
@@ -6298,7 +6332,7 @@
     <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="102">
         <f>'Nach Mannschaften sortiert'!D45</f>
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C45" s="36">
         <f>'Nach Mannschaften sortiert'!E45</f>
@@ -6337,7 +6371,7 @@
     <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="102">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C46" s="36">
         <f>'Nach Mannschaften sortiert'!E46</f>
@@ -6345,7 +6379,7 @@
       </c>
       <c r="D46" s="36">
         <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E46" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F46)</f>
@@ -6361,7 +6395,7 @@
       </c>
       <c r="I46" t="str">
         <f>'Nach Mannschaften sortiert'!C46</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J46" s="105" t="s">
         <v>107</v>
@@ -6376,7 +6410,7 @@
     <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="102">
         <f>'Nach Mannschaften sortiert'!D47</f>
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C47" s="36">
         <f>'Nach Mannschaften sortiert'!E47</f>
@@ -6415,7 +6449,7 @@
     <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="102">
         <f>'Nach Mannschaften sortiert'!D48</f>
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C48" s="36">
         <f>'Nach Mannschaften sortiert'!E48</f>
@@ -6454,7 +6488,7 @@
     <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="102">
         <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C49" s="36">
         <f>'Nach Mannschaften sortiert'!E49</f>
@@ -6493,7 +6527,7 @@
     <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="102">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="C50" s="36">
         <f>'Nach Mannschaften sortiert'!E50</f>
@@ -6532,7 +6566,7 @@
     <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="102">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="C51" s="36">
         <f>'Nach Mannschaften sortiert'!E51</f>
@@ -6571,7 +6605,7 @@
     <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="102">
         <f>'Nach Mannschaften sortiert'!D52</f>
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C52" s="36">
         <f>'Nach Mannschaften sortiert'!E52</f>
@@ -6610,7 +6644,7 @@
     <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="102">
         <f>'Nach Mannschaften sortiert'!D53</f>
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C53" s="36">
         <f>'Nach Mannschaften sortiert'!E53</f>
@@ -6649,7 +6683,7 @@
     <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="102">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C54" s="36">
         <f>'Nach Mannschaften sortiert'!E54</f>
@@ -6688,7 +6722,7 @@
     <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="102">
         <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C55" s="36">
         <f>'Nach Mannschaften sortiert'!E55</f>
@@ -6727,7 +6761,7 @@
     <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="102">
         <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C56" s="36">
         <f>'Nach Mannschaften sortiert'!E56</f>
@@ -6735,7 +6769,7 @@
       </c>
       <c r="D56" s="36">
         <f t="shared" si="0"/>
-        <v>0.125</v>
+        <v>6.25E-2</v>
       </c>
       <c r="E56" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F56)</f>
@@ -6751,7 +6785,7 @@
       </c>
       <c r="I56" t="str">
         <f>'Nach Mannschaften sortiert'!C56</f>
-        <v>U12_1</v>
+        <v>U14</v>
       </c>
       <c r="J56" s="105" t="s">
         <v>107</v>
@@ -6766,7 +6800,7 @@
     <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="102">
         <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C57" s="36">
         <f>'Nach Mannschaften sortiert'!E57</f>
@@ -6805,7 +6839,7 @@
     <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="102">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C58" s="36">
         <f>'Nach Mannschaften sortiert'!E58</f>
@@ -6844,7 +6878,7 @@
     <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="102">
         <f>'Nach Mannschaften sortiert'!D59</f>
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C59" s="36">
         <f>'Nach Mannschaften sortiert'!E59</f>
@@ -6883,7 +6917,7 @@
     <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="102">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C60" s="36">
         <f>'Nach Mannschaften sortiert'!E60</f>
@@ -6922,7 +6956,7 @@
     <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="102">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="C61" s="36">
         <f>'Nach Mannschaften sortiert'!E61</f>
@@ -6961,7 +6995,7 @@
     <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="102">
         <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="C62" s="36">
         <f>'Nach Mannschaften sortiert'!E62</f>
@@ -7000,7 +7034,7 @@
     <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="102">
         <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C63" s="36">
         <f>'Nach Mannschaften sortiert'!E63</f>
@@ -7039,7 +7073,7 @@
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="102">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C64" s="36">
         <f>'Nach Mannschaften sortiert'!E64</f>
@@ -7078,7 +7112,7 @@
     <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="102">
         <f>'Nach Mannschaften sortiert'!D65</f>
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="C65" s="36">
         <f>'Nach Mannschaften sortiert'!E65</f>
@@ -7117,7 +7151,7 @@
     <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="102">
         <f>'Nach Mannschaften sortiert'!D66</f>
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C66" s="36">
         <f>'Nach Mannschaften sortiert'!E66</f>
@@ -7141,7 +7175,7 @@
       </c>
       <c r="I66" t="str">
         <f>'Nach Mannschaften sortiert'!C66</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J66" s="105" t="s">
         <v>107</v>
@@ -7156,7 +7190,7 @@
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="102">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="C67" s="36">
         <f>'Nach Mannschaften sortiert'!E67</f>
@@ -7195,14 +7229,14 @@
     <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="102">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C68" s="36">
         <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="D68" s="36">
-        <f t="shared" ref="D68:D104" si="1">IF(I68 = "KM",C68+"1:45",IF(I68="U23",C68+"1:45",IF(I68 = "U16",C68+"1:45",IF(I68 = "U15",C68+"1:30",IF(I68 = "U14",C68+"1:30",IF(I68 = "U13",C68+"1:35",IF(I68 = "U12",C68+"1:10",IF(I68 = "U11",C68+"1:10",IF(I68 = "U10",C68+"1:03",C68+"3:00")))))))))</f>
+        <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
       <c r="E68" s="36" t="str">
@@ -7234,14 +7268,14 @@
     <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="102">
         <f>'Nach Mannschaften sortiert'!D69</f>
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C69" s="36">
         <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="D69" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D69:D105" si="1">IF(I69 = "KM",C69+"1:45",IF(I69="U23",C69+"1:45",IF(I69 = "U16",C69+"1:45",IF(I69 = "U15",C69+"1:30",IF(I69 = "U14",C69+"1:30",IF(I69 = "U13",C69+"1:35",IF(I69 = "U12",C69+"1:10",IF(I69 = "U11",C69+"1:10",IF(I69 = "U10",C69+"1:03",C69+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E69" s="36" t="str">
@@ -7273,7 +7307,7 @@
     <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="102">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="C70" s="36">
         <f>'Nach Mannschaften sortiert'!E70</f>
@@ -7312,7 +7346,7 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="102">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C71" s="36">
         <f>'Nach Mannschaften sortiert'!E71</f>
@@ -7351,7 +7385,7 @@
     <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="102">
         <f>'Nach Mannschaften sortiert'!D72</f>
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="C72" s="36">
         <f>'Nach Mannschaften sortiert'!E72</f>
@@ -7390,7 +7424,7 @@
     <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="102">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="C73" s="36">
         <f>'Nach Mannschaften sortiert'!E73</f>
@@ -7429,7 +7463,7 @@
     <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="102">
         <f>'Nach Mannschaften sortiert'!D74</f>
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C74" s="36">
         <f>'Nach Mannschaften sortiert'!E74</f>
@@ -7468,7 +7502,7 @@
     <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="102">
         <f>'Nach Mannschaften sortiert'!D75</f>
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C75" s="36">
         <f>'Nach Mannschaften sortiert'!E75</f>
@@ -7507,7 +7541,7 @@
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="102">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="C76" s="36">
         <f>'Nach Mannschaften sortiert'!E76</f>
@@ -7515,7 +7549,7 @@
       </c>
       <c r="D76" s="36">
         <f t="shared" si="1"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.125</v>
       </c>
       <c r="E76" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F76)</f>
@@ -7531,7 +7565,7 @@
       </c>
       <c r="I76" t="str">
         <f>'Nach Mannschaften sortiert'!C76</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J76" s="105" t="s">
         <v>107</v>
@@ -7546,7 +7580,7 @@
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="102">
         <f>'Nach Mannschaften sortiert'!D77</f>
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C77" s="36">
         <f>'Nach Mannschaften sortiert'!E77</f>
@@ -7585,7 +7619,7 @@
     <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="102">
         <f>'Nach Mannschaften sortiert'!D78</f>
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C78" s="36">
         <f>'Nach Mannschaften sortiert'!E78</f>
@@ -7624,7 +7658,7 @@
     <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="102">
         <f>'Nach Mannschaften sortiert'!D79</f>
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C79" s="36">
         <f>'Nach Mannschaften sortiert'!E79</f>
@@ -7663,7 +7697,7 @@
     <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="102">
         <f>'Nach Mannschaften sortiert'!D80</f>
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="C80" s="36">
         <f>'Nach Mannschaften sortiert'!E80</f>
@@ -7702,7 +7736,7 @@
     <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="102">
         <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="C81" s="36">
         <f>'Nach Mannschaften sortiert'!E81</f>
@@ -7741,7 +7775,7 @@
     <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="102">
         <f>'Nach Mannschaften sortiert'!D82</f>
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="C82" s="36">
         <f>'Nach Mannschaften sortiert'!E82</f>
@@ -7780,7 +7814,7 @@
     <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="102">
         <f>'Nach Mannschaften sortiert'!D83</f>
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="C83" s="36">
         <f>'Nach Mannschaften sortiert'!E83</f>
@@ -7819,7 +7853,7 @@
     <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="102">
         <f>'Nach Mannschaften sortiert'!D84</f>
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="C84" s="36">
         <f>'Nach Mannschaften sortiert'!E84</f>
@@ -7858,7 +7892,7 @@
     <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="102">
         <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C85" s="36">
         <f>'Nach Mannschaften sortiert'!E85</f>
@@ -7897,30 +7931,31 @@
     <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="102">
         <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46312</v>
+        <v>46072</v>
       </c>
       <c r="C86" s="36">
         <f>'Nach Mannschaften sortiert'!E86</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D86" s="36">
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E86" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F86)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G86" s="115" t="str">
+        <v/>
+      </c>
+      <c r="G86" s="115">
         <f>'Nach Mannschaften sortiert'!H86</f>
-        <v>Heim</v>
-      </c>
-      <c r="H86" t="str">
+        <v>0</v>
+      </c>
+      <c r="H86">
         <f>'Nach Mannschaften sortiert'!G86</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I86" t="str">
         <f>'Nach Mannschaften sortiert'!C86</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J86" s="105" t="s">
         <v>107</v>
@@ -7935,27 +7970,26 @@
     <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="102">
         <f>'Nach Mannschaften sortiert'!D87</f>
-        <v>46074</v>
+        <v>46312</v>
       </c>
       <c r="C87" s="36">
         <f>'Nach Mannschaften sortiert'!E87</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D87" s="36">
-        <f t="shared" si="1"/>
-        <v>4.3750000000000004E-2</v>
+        <v>0.5</v>
       </c>
       <c r="E87" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F87)</f>
-        <v/>
-      </c>
-      <c r="G87" s="115">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G87" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H87</f>
-        <v>0</v>
-      </c>
-      <c r="H87">
+        <v>Heim</v>
+      </c>
+      <c r="H87" t="str">
         <f>'Nach Mannschaften sortiert'!G87</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I87" t="str">
         <f>'Nach Mannschaften sortiert'!C87</f>
@@ -7974,7 +8008,7 @@
     <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="102">
         <f>'Nach Mannschaften sortiert'!D88</f>
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="C88" s="36">
         <f>'Nach Mannschaften sortiert'!E88</f>
@@ -8013,7 +8047,7 @@
     <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="102">
         <f>'Nach Mannschaften sortiert'!D89</f>
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="C89" s="36">
         <f>'Nach Mannschaften sortiert'!E89</f>
@@ -8052,7 +8086,7 @@
     <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="102">
         <f>'Nach Mannschaften sortiert'!D90</f>
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C90" s="36">
         <f>'Nach Mannschaften sortiert'!E90</f>
@@ -8091,7 +8125,7 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="102">
         <f>'Nach Mannschaften sortiert'!D91</f>
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C91" s="36">
         <f>'Nach Mannschaften sortiert'!E91</f>
@@ -8099,7 +8133,7 @@
       </c>
       <c r="D91" s="36">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E91" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F91)</f>
@@ -8115,7 +8149,7 @@
       </c>
       <c r="I91" t="str">
         <f>'Nach Mannschaften sortiert'!C91</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J91" s="105" t="s">
         <v>107</v>
@@ -8130,7 +8164,7 @@
     <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="102">
         <f>'Nach Mannschaften sortiert'!D92</f>
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="C92" s="36">
         <f>'Nach Mannschaften sortiert'!E92</f>
@@ -8169,7 +8203,7 @@
     <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="102">
         <f>'Nach Mannschaften sortiert'!D93</f>
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C93" s="36">
         <f>'Nach Mannschaften sortiert'!E93</f>
@@ -8208,7 +8242,7 @@
     <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="102">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C94" s="36">
         <f>'Nach Mannschaften sortiert'!E94</f>
@@ -8247,7 +8281,7 @@
     <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95" s="102">
         <f>'Nach Mannschaften sortiert'!D95</f>
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C95" s="36">
         <f>'Nach Mannschaften sortiert'!E95</f>
@@ -8286,7 +8320,7 @@
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="102">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C96" s="36">
         <f>'Nach Mannschaften sortiert'!E96</f>
@@ -8325,7 +8359,7 @@
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="102">
         <f>'Nach Mannschaften sortiert'!D97</f>
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C97" s="36">
         <f>'Nach Mannschaften sortiert'!E97</f>
@@ -8364,7 +8398,7 @@
     <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B98" s="102">
         <f>'Nach Mannschaften sortiert'!D98</f>
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C98" s="36">
         <f>'Nach Mannschaften sortiert'!E98</f>
@@ -8403,7 +8437,7 @@
     <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B99" s="102">
         <f>'Nach Mannschaften sortiert'!D99</f>
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C99" s="36">
         <f>'Nach Mannschaften sortiert'!E99</f>
@@ -8442,7 +8476,7 @@
     <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100" s="102">
         <f>'Nach Mannschaften sortiert'!D100</f>
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="C100" s="36">
         <f>'Nach Mannschaften sortiert'!E100</f>
@@ -8481,30 +8515,31 @@
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101" s="102">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46312</v>
+        <v>46087</v>
       </c>
       <c r="C101" s="36">
         <f>'Nach Mannschaften sortiert'!E101</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D101" s="36">
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.125</v>
       </c>
       <c r="E101" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F101)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G101" s="115" t="str">
+        <v/>
+      </c>
+      <c r="G101" s="115">
         <f>'Nach Mannschaften sortiert'!H101</f>
-        <v>Heim</v>
-      </c>
-      <c r="H101" t="str">
+        <v>0</v>
+      </c>
+      <c r="H101">
         <f>'Nach Mannschaften sortiert'!G101</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>'Nach Mannschaften sortiert'!C101</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J101" s="105" t="s">
         <v>107</v>
@@ -8519,27 +8554,26 @@
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102" s="102">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>46089</v>
+        <v>46312</v>
       </c>
       <c r="C102" s="36">
         <f>'Nach Mannschaften sortiert'!E102</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D102" s="36">
-        <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E102" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F102)</f>
-        <v/>
-      </c>
-      <c r="G102" s="115">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G102" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H102</f>
-        <v>0</v>
-      </c>
-      <c r="H102">
+        <v>Heim</v>
+      </c>
+      <c r="H102" t="str">
         <f>'Nach Mannschaften sortiert'!G102</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I102" t="str">
         <f>'Nach Mannschaften sortiert'!C102</f>
@@ -8558,7 +8592,7 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="102">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="C103" s="36">
         <f>'Nach Mannschaften sortiert'!E103</f>
@@ -8597,7 +8631,7 @@
     <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B104" s="102">
         <f>'Nach Mannschaften sortiert'!D104</f>
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C104" s="36">
         <f>'Nach Mannschaften sortiert'!E104</f>
@@ -8636,14 +8670,14 @@
     <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105" s="102">
         <f>'Nach Mannschaften sortiert'!D105</f>
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C105" s="36">
         <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="D105" s="36">
-        <f>IF(I105 = "KM",C105+"1:45",IF(I105="U23",C105+"1:45",IF(I105 = "U16",C105+"1:45",IF(I105 = "U15",C105+"1:30",IF(I105 = "U14",C105+"1:30",IF(I105 = "U13",C105+"1:35",IF(I105 = "U12",C105+"1:10",IF(I105 = "U11",C105+"1:10",IF(I105 = "U10",C105+"1:03",C105+"3:00")))))))))</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="E105" s="36" t="str">
@@ -8675,14 +8709,14 @@
     <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106" s="102">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46312</v>
+        <v>46092</v>
       </c>
       <c r="C106" s="36">
         <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="D106" s="36">
-        <f t="shared" ref="D106:D122" si="2">IF(I106 = "KM",C106+"1:45",IF(I106="U23",C106+"1:45",IF(I106 = "U16",C106+"1:45",IF(I106 = "U15",C106+"1:30",IF(I106 = "U14",C106+"1:30",IF(I106 = "U13",C106+"1:35",IF(I106 = "U12",C106+"1:10",IF(I106 = "U11",C106+"1:10",IF(I106 = "U10",C106+"1:03",C106+"3:00")))))))))</f>
+        <f>IF(I106 = "KM",C106+"1:45",IF(I106="U23",C106+"1:45",IF(I106 = "U16",C106+"1:45",IF(I106 = "U15",C106+"1:30",IF(I106 = "U14",C106+"1:30",IF(I106 = "U13",C106+"1:35",IF(I106 = "U12",C106+"1:10",IF(I106 = "U11",C106+"1:10",IF(I106 = "U10",C106+"1:03",C106+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E106" s="36" t="str">
@@ -8699,7 +8733,7 @@
       </c>
       <c r="I106" t="str">
         <f>'Nach Mannschaften sortiert'!C106</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J106" s="105" t="s">
         <v>107</v>
@@ -8714,14 +8748,14 @@
     <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B107" s="102">
         <f>'Nach Mannschaften sortiert'!D107</f>
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="C107" s="36">
         <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="D107" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D107:D123" si="2">IF(I107 = "KM",C107+"1:45",IF(I107="U23",C107+"1:45",IF(I107 = "U16",C107+"1:45",IF(I107 = "U15",C107+"1:30",IF(I107 = "U14",C107+"1:30",IF(I107 = "U13",C107+"1:35",IF(I107 = "U12",C107+"1:10",IF(I107 = "U11",C107+"1:10",IF(I107 = "U10",C107+"1:03",C107+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E107" s="36" t="str">
@@ -8753,7 +8787,7 @@
     <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B108" s="102">
         <f>'Nach Mannschaften sortiert'!D108</f>
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="C108" s="36">
         <f>'Nach Mannschaften sortiert'!E108</f>
@@ -8792,7 +8826,7 @@
     <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109" s="102">
         <f>'Nach Mannschaften sortiert'!D109</f>
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="C109" s="36">
         <f>'Nach Mannschaften sortiert'!E109</f>
@@ -8831,7 +8865,7 @@
     <row r="110" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B110" s="102">
         <f>'Nach Mannschaften sortiert'!D110</f>
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="C110" s="36">
         <f>'Nach Mannschaften sortiert'!E110</f>
@@ -8870,31 +8904,31 @@
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="102">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46230</v>
+        <v>46097</v>
       </c>
       <c r="C111" s="36">
         <f>'Nach Mannschaften sortiert'!E111</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D111" s="36">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="E111" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F111)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G111" s="115" t="str">
+        <v/>
+      </c>
+      <c r="G111" s="115">
         <f>'Nach Mannschaften sortiert'!H111</f>
-        <v>Heim</v>
-      </c>
-      <c r="H111" t="str">
+        <v>0</v>
+      </c>
+      <c r="H111">
         <f>'Nach Mannschaften sortiert'!G111</f>
-        <v>REAL MADRID CAMP</v>
+        <v>0</v>
       </c>
       <c r="I111" t="str">
         <f>'Nach Mannschaften sortiert'!C111</f>
-        <v>Camp</v>
+        <v>U7</v>
       </c>
       <c r="J111" s="105" t="s">
         <v>107</v>
@@ -8909,7 +8943,7 @@
     <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112" s="102">
         <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C112" s="36">
         <f>'Nach Mannschaften sortiert'!E112</f>
@@ -8948,7 +8982,7 @@
     <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113" s="102">
         <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C113" s="36">
         <f>'Nach Mannschaften sortiert'!E113</f>
@@ -8987,7 +9021,7 @@
     <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114" s="102">
         <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C114" s="36">
         <f>'Nach Mannschaften sortiert'!E114</f>
@@ -9026,7 +9060,7 @@
     <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115" s="102">
         <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="C115" s="36">
         <f>'Nach Mannschaften sortiert'!E115</f>
@@ -9065,7 +9099,7 @@
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116" s="102">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="C116" s="36">
         <f>'Nach Mannschaften sortiert'!E116</f>
@@ -9085,7 +9119,7 @@
       </c>
       <c r="H116" t="str">
         <f>'Nach Mannschaften sortiert'!G116</f>
-        <v>MÄDCHENCAMP</v>
+        <v>REAL MADRID CAMP</v>
       </c>
       <c r="I116" t="str">
         <f>'Nach Mannschaften sortiert'!C116</f>
@@ -9104,7 +9138,7 @@
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117" s="102">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C117" s="36">
         <f>'Nach Mannschaften sortiert'!E117</f>
@@ -9143,7 +9177,7 @@
     <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B118" s="102">
         <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="C118" s="36">
         <f>'Nach Mannschaften sortiert'!E118</f>
@@ -9182,7 +9216,7 @@
     <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B119" s="102">
         <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="C119" s="36">
         <f>'Nach Mannschaften sortiert'!E119</f>
@@ -9202,7 +9236,7 @@
       </c>
       <c r="H119" t="str">
         <f>'Nach Mannschaften sortiert'!G119</f>
-        <v>Teco 7 Camp</v>
+        <v>MÄDCHENCAMP</v>
       </c>
       <c r="I119" t="str">
         <f>'Nach Mannschaften sortiert'!C119</f>
@@ -9221,7 +9255,7 @@
     <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B120" s="102">
         <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C120" s="36">
         <f>'Nach Mannschaften sortiert'!E120</f>
@@ -9260,7 +9294,7 @@
     <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B121" s="102">
         <f>'Nach Mannschaften sortiert'!D121</f>
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C121" s="36">
         <f>'Nach Mannschaften sortiert'!E121</f>
@@ -9299,7 +9333,7 @@
     <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B122" s="102">
         <f>'Nach Mannschaften sortiert'!D122</f>
-        <v>46256</v>
+        <v>46323</v>
       </c>
       <c r="C122" s="36">
         <f>'Nach Mannschaften sortiert'!E122</f>
@@ -9319,11 +9353,11 @@
       </c>
       <c r="H122" t="str">
         <f>'Nach Mannschaften sortiert'!G122</f>
-        <v>viele Gegner</v>
+        <v>Teco 7 Camp</v>
       </c>
       <c r="I122" t="str">
         <f>'Nach Mannschaften sortiert'!C122</f>
-        <v>GGG</v>
+        <v>Camp</v>
       </c>
       <c r="J122" s="105" t="s">
         <v>107</v>
@@ -9338,18 +9372,19 @@
     <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B123" s="102">
         <f>'Nach Mannschaften sortiert'!D123</f>
-        <v>46367</v>
+        <v>46256</v>
       </c>
       <c r="C123" s="36">
         <f>'Nach Mannschaften sortiert'!E123</f>
-        <v>0.6875</v>
+        <v>0.375</v>
       </c>
       <c r="D123" s="36">
-        <v>0.875</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="E123" s="36" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F123)</f>
-        <v>STEINBRUNN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G123" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H123</f>
@@ -9357,11 +9392,11 @@
       </c>
       <c r="H123" t="str">
         <f>'Nach Mannschaften sortiert'!G123</f>
-        <v>Hallencup 2026_27</v>
+        <v>viele Gegner</v>
       </c>
       <c r="I123" t="str">
         <f>'Nach Mannschaften sortiert'!C123</f>
-        <v>Hallenturnie</v>
+        <v>GGG</v>
       </c>
       <c r="J123" s="105" t="s">
         <v>107</v>
@@ -9376,11 +9411,11 @@
     <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B124" s="102">
         <f>'Nach Mannschaften sortiert'!D124</f>
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="C124" s="36">
         <f>'Nach Mannschaften sortiert'!E124</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D124" s="36">
         <v>0.875</v>
@@ -9414,11 +9449,11 @@
     <row r="125" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B125" s="102">
         <f>'Nach Mannschaften sortiert'!D125</f>
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="C125" s="36">
         <f>'Nach Mannschaften sortiert'!E125</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D125" s="36">
         <v>0.875</v>
@@ -9452,11 +9487,11 @@
     <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B126" s="102">
         <f>'Nach Mannschaften sortiert'!D126</f>
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="C126" s="36">
         <f>'Nach Mannschaften sortiert'!E126</f>
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D126" s="36">
         <v>0.875</v>
@@ -9465,20 +9500,17 @@
         <f>UPPER('Nach Mannschaften sortiert'!F126)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="F126" s="105" t="s">
-        <v>170</v>
-      </c>
       <c r="G126" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H126</f>
         <v>Heim</v>
       </c>
       <c r="H126" t="str">
         <f>'Nach Mannschaften sortiert'!G126</f>
-        <v>Weihnachtsfeier 2026</v>
+        <v>Hallencup 2026_27</v>
       </c>
       <c r="I126" t="str">
         <f>'Nach Mannschaften sortiert'!C126</f>
-        <v>Weihnachtsfeier</v>
+        <v>Hallenturnie</v>
       </c>
       <c r="J126" s="105" t="s">
         <v>107</v>
@@ -9487,17 +9519,17 @@
         <v>109</v>
       </c>
       <c r="L126" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B127" s="102">
         <f>'Nach Mannschaften sortiert'!D127</f>
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="C127" s="36">
         <f>'Nach Mannschaften sortiert'!E127</f>
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D127" s="36">
         <v>0.875</v>
@@ -9506,17 +9538,20 @@
         <f>UPPER('Nach Mannschaften sortiert'!F127)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F127" s="105" t="s">
+        <v>170</v>
+      </c>
       <c r="G127" s="115" t="str">
         <f>'Nach Mannschaften sortiert'!H127</f>
         <v>Heim</v>
       </c>
       <c r="H127" t="str">
         <f>'Nach Mannschaften sortiert'!G127</f>
-        <v>Hallencup 2026_27</v>
+        <v>Weihnachtsfeier 2026</v>
       </c>
       <c r="I127" t="str">
         <f>'Nach Mannschaften sortiert'!C127</f>
-        <v>Hallenturnie</v>
+        <v>Weihnachtsfeier</v>
       </c>
       <c r="J127" s="105" t="s">
         <v>107</v>
@@ -9525,17 +9560,17 @@
         <v>109</v>
       </c>
       <c r="L127" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
     </row>
     <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B128" s="102">
         <f>'Nach Mannschaften sortiert'!D128</f>
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="C128" s="36">
         <f>'Nach Mannschaften sortiert'!E128</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D128" s="36">
         <v>0.875</v>
@@ -9569,11 +9604,11 @@
     <row r="129" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B129" s="102">
         <f>'Nach Mannschaften sortiert'!D129</f>
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="C129" s="36">
         <f>'Nach Mannschaften sortiert'!E129</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D129" s="36">
         <v>0.875</v>
@@ -9601,6 +9636,44 @@
         <v>109</v>
       </c>
       <c r="L129" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B130" s="102">
+        <f>'Nach Mannschaften sortiert'!D130</f>
+        <v>46404</v>
+      </c>
+      <c r="C130" s="36">
+        <f>'Nach Mannschaften sortiert'!E130</f>
+        <v>0.375</v>
+      </c>
+      <c r="D130" s="36">
+        <v>0.875</v>
+      </c>
+      <c r="E130" s="36" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F130)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G130" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H130</f>
+        <v>Heim</v>
+      </c>
+      <c r="H130" t="str">
+        <f>'Nach Mannschaften sortiert'!G130</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I130" t="str">
+        <f>'Nach Mannschaften sortiert'!C130</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J130" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="K130" t="s">
+        <v>109</v>
+      </c>
+      <c r="L130" t="s">
         <v>145</v>
       </c>
     </row>
@@ -10250,783 +10323,783 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <f>'Nach Mannschaften sortiert'!A10</f>
-        <v>8</v>
+        <f>'Nach Mannschaften sortiert'!A11</f>
+        <v>10</v>
       </c>
       <c r="B2" s="2">
-        <f>'Nach Mannschaften sortiert'!B10</f>
+        <f>'Nach Mannschaften sortiert'!B11</f>
         <v>1</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C10</f>
+        <f>'Nach Mannschaften sortiert'!C11</f>
         <v>KM</v>
       </c>
       <c r="D2" s="13">
-        <f>'Nach Mannschaften sortiert'!D10</f>
+        <f>'Nach Mannschaften sortiert'!D11</f>
         <v>46250</v>
       </c>
       <c r="E2" s="35">
-        <f>'Nach Mannschaften sortiert'!E10</f>
+        <f>'Nach Mannschaften sortiert'!E11</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="F2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F10</f>
+        <f>'Nach Mannschaften sortiert'!F11</f>
         <v>Kittsee</v>
       </c>
       <c r="G2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G10</f>
+        <f>'Nach Mannschaften sortiert'!G11</f>
         <v>Kittsee</v>
       </c>
       <c r="H2" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H10</f>
+        <f>'Nach Mannschaften sortiert'!H11</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <f>'Nach Mannschaften sortiert'!A11</f>
-        <v>9</v>
+        <f>'Nach Mannschaften sortiert'!A12</f>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
-        <f>'Nach Mannschaften sortiert'!B11</f>
+        <f>'Nach Mannschaften sortiert'!B12</f>
         <v>2</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C11</f>
+        <f>'Nach Mannschaften sortiert'!C12</f>
         <v>KM</v>
       </c>
       <c r="D3" s="13">
-        <f>'Nach Mannschaften sortiert'!D11</f>
+        <f>'Nach Mannschaften sortiert'!D12</f>
         <v>46255</v>
       </c>
       <c r="E3" s="35">
-        <f>'Nach Mannschaften sortiert'!E11</f>
+        <f>'Nach Mannschaften sortiert'!E12</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="F3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F11</f>
+        <f>'Nach Mannschaften sortiert'!F12</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="G3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G11</f>
+        <f>'Nach Mannschaften sortiert'!G12</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="H3" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H11</f>
+        <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <f>'Nach Mannschaften sortiert'!A12</f>
-        <v>10</v>
+        <f>'Nach Mannschaften sortiert'!A13</f>
+        <v>12</v>
       </c>
       <c r="B4" s="2">
-        <f>'Nach Mannschaften sortiert'!B12</f>
+        <f>'Nach Mannschaften sortiert'!B13</f>
         <v>3</v>
       </c>
       <c r="C4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C12</f>
+        <f>'Nach Mannschaften sortiert'!C13</f>
         <v>KM</v>
       </c>
       <c r="D4" s="13">
-        <f>'Nach Mannschaften sortiert'!D12</f>
+        <f>'Nach Mannschaften sortiert'!D13</f>
         <v>46263</v>
       </c>
       <c r="E4" s="35">
-        <f>'Nach Mannschaften sortiert'!E12</f>
+        <f>'Nach Mannschaften sortiert'!E13</f>
         <v>0.75</v>
       </c>
       <c r="F4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F12</f>
+        <f>'Nach Mannschaften sortiert'!F13</f>
         <v>Neufeld</v>
       </c>
       <c r="G4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G12</f>
+        <f>'Nach Mannschaften sortiert'!G13</f>
         <v>Tadten</v>
       </c>
       <c r="H4" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H12</f>
+        <f>'Nach Mannschaften sortiert'!H13</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <f>'Nach Mannschaften sortiert'!A46</f>
-        <v>44</v>
+        <f>'Nach Mannschaften sortiert'!A47</f>
+        <v>46</v>
       </c>
       <c r="B5" s="2">
-        <f>'Nach Mannschaften sortiert'!B46</f>
+        <f>'Nach Mannschaften sortiert'!B47</f>
         <v>1</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C46</f>
+        <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U14</v>
       </c>
       <c r="D5" s="13">
-        <f>'Nach Mannschaften sortiert'!D46</f>
+        <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46033</v>
       </c>
       <c r="E5" s="35">
-        <f>'Nach Mannschaften sortiert'!E46</f>
+        <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <f>'Nach Mannschaften sortiert'!F46</f>
+        <f>'Nach Mannschaften sortiert'!F47</f>
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <f>'Nach Mannschaften sortiert'!G46</f>
+        <f>'Nach Mannschaften sortiert'!G47</f>
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f>'Nach Mannschaften sortiert'!H46</f>
+        <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
+        <f>'Nach Mannschaften sortiert'!A15</f>
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <f>'Nach Mannschaften sortiert'!B15</f>
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C15</f>
+        <v>KM</v>
+      </c>
+      <c r="D6" s="13">
+        <f>'Nach Mannschaften sortiert'!D15</f>
+        <v>46276</v>
+      </c>
+      <c r="E6" s="35">
+        <f>'Nach Mannschaften sortiert'!E15</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F15</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G15</f>
+        <v>Winden</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H15</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <f>'Nach Mannschaften sortiert'!A57</f>
+        <v>56</v>
+      </c>
+      <c r="B7" s="2">
+        <f>'Nach Mannschaften sortiert'!B57</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C57</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D7" s="13">
+        <f>'Nach Mannschaften sortiert'!D57</f>
+        <v>46043</v>
+      </c>
+      <c r="E7" s="35">
+        <f>'Nach Mannschaften sortiert'!E57</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <f>'Nach Mannschaften sortiert'!F57</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <f>'Nach Mannschaften sortiert'!G57</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <f>'Nach Mannschaften sortiert'!H57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <f>'Nach Mannschaften sortiert'!A17</f>
+        <v>16</v>
+      </c>
+      <c r="B8" s="2">
+        <f>'Nach Mannschaften sortiert'!B17</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C17</f>
+        <v>KM</v>
+      </c>
+      <c r="D8" s="13">
+        <f>'Nach Mannschaften sortiert'!D17</f>
+        <v>46291</v>
+      </c>
+      <c r="E8" s="35">
+        <f>'Nach Mannschaften sortiert'!E17</f>
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F17</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G17</f>
+        <v>Wallern</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H17</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="63">
+        <f>'Nach Mannschaften sortiert'!A112</f>
+        <v>111</v>
+      </c>
+      <c r="B9" s="63">
+        <f>'Nach Mannschaften sortiert'!B112</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!C112</f>
+        <v>Camp</v>
+      </c>
+      <c r="D9" s="64">
+        <f>'Nach Mannschaften sortiert'!D112</f>
+        <v>46230</v>
+      </c>
+      <c r="E9" s="65">
+        <f>'Nach Mannschaften sortiert'!E112</f>
+        <v>0.375</v>
+      </c>
+      <c r="F9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!F112</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!G112</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H9" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!H112</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <f>'Nach Mannschaften sortiert'!A19</f>
+        <v>18</v>
+      </c>
+      <c r="B10" s="2">
+        <f>'Nach Mannschaften sortiert'!B19</f>
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C19</f>
+        <v>KM</v>
+      </c>
+      <c r="D10" s="13">
+        <f>'Nach Mannschaften sortiert'!D19</f>
+        <v>46304</v>
+      </c>
+      <c r="E10" s="35">
+        <f>'Nach Mannschaften sortiert'!E19</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F19</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G19</f>
+        <v>Wimpassing</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H19</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="63">
+        <f>'Nach Mannschaften sortiert'!A113</f>
+        <v>112</v>
+      </c>
+      <c r="B11" s="63">
+        <f>'Nach Mannschaften sortiert'!B113</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!C113</f>
+        <v>Camp</v>
+      </c>
+      <c r="D11" s="64">
+        <f>'Nach Mannschaften sortiert'!D113</f>
+        <v>46231</v>
+      </c>
+      <c r="E11" s="65">
+        <f>'Nach Mannschaften sortiert'!E113</f>
+        <v>0.375</v>
+      </c>
+      <c r="F11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!F113</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!G113</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H11" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!H113</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <f>'Nach Mannschaften sortiert'!A21</f>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2">
+        <f>'Nach Mannschaften sortiert'!B21</f>
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C21</f>
+        <v>KM</v>
+      </c>
+      <c r="D12" s="13">
+        <f>'Nach Mannschaften sortiert'!D21</f>
+        <v>46319</v>
+      </c>
+      <c r="E12" s="35">
+        <f>'Nach Mannschaften sortiert'!E21</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F21</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G21</f>
+        <v>Gols</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H21</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <f>'Nach Mannschaften sortiert'!A22</f>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2">
+        <f>'Nach Mannschaften sortiert'!B22</f>
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C22</f>
+        <v>KM</v>
+      </c>
+      <c r="D13" s="13">
+        <f>'Nach Mannschaften sortiert'!D22</f>
+        <v>46326</v>
+      </c>
+      <c r="E13" s="35">
+        <f>'Nach Mannschaften sortiert'!E22</f>
+        <v>0.75</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!F22</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!G22</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="H13" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!H22</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="63">
+        <f>'Nach Mannschaften sortiert'!A114</f>
+        <v>113</v>
+      </c>
+      <c r="B14" s="63">
+        <f>'Nach Mannschaften sortiert'!B114</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!C114</f>
+        <v>Camp</v>
+      </c>
+      <c r="D14" s="64">
+        <f>'Nach Mannschaften sortiert'!D114</f>
+        <v>46232</v>
+      </c>
+      <c r="E14" s="65">
+        <f>'Nach Mannschaften sortiert'!E114</f>
+        <v>0.375</v>
+      </c>
+      <c r="F14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!F114</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!G114</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H14" s="63" t="str">
+        <f>'Nach Mannschaften sortiert'!H114</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <f>'Nach Mannschaften sortiert'!A37</f>
+        <v>36</v>
+      </c>
+      <c r="B15" s="2">
+        <f>'Nach Mannschaften sortiert'!B37</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C37</f>
+        <v>U16</v>
+      </c>
+      <c r="D15" s="13">
+        <f>'Nach Mannschaften sortiert'!D37</f>
+        <v>46023</v>
+      </c>
+      <c r="E15" s="35">
+        <f>'Nach Mannschaften sortiert'!E37</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <f>'Nach Mannschaften sortiert'!F37</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <f>'Nach Mannschaften sortiert'!G37</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <f>'Nach Mannschaften sortiert'!H37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="57">
+        <f>'Nach Mannschaften sortiert'!A38</f>
+        <v>37</v>
+      </c>
+      <c r="B16" s="57">
+        <f>'Nach Mannschaften sortiert'!B38</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!C38</f>
+        <v>U16</v>
+      </c>
+      <c r="D16" s="58">
+        <f>'Nach Mannschaften sortiert'!D38</f>
+        <v>46024</v>
+      </c>
+      <c r="E16" s="59">
+        <f>'Nach Mannschaften sortiert'!E38</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="57">
+        <f>'Nach Mannschaften sortiert'!F38</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="57">
+        <f>'Nach Mannschaften sortiert'!G38</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="57">
+        <f>'Nach Mannschaften sortiert'!H38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <f>'Nach Mannschaften sortiert'!A39</f>
+        <v>38</v>
+      </c>
+      <c r="B17" s="2">
+        <f>'Nach Mannschaften sortiert'!B39</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C39</f>
+        <v>U16</v>
+      </c>
+      <c r="D17" s="13">
+        <f>'Nach Mannschaften sortiert'!D39</f>
+        <v>46025</v>
+      </c>
+      <c r="E17" s="35">
+        <f>'Nach Mannschaften sortiert'!E39</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f>'Nach Mannschaften sortiert'!F39</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <f>'Nach Mannschaften sortiert'!G39</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <f>'Nach Mannschaften sortiert'!H39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <f>'Nach Mannschaften sortiert'!A14</f>
-        <v>12</v>
-      </c>
-      <c r="B6" s="2">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2">
         <f>'Nach Mannschaften sortiert'!B14</f>
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!C14</f>
         <v>KM</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D18" s="13">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46276</v>
-      </c>
-      <c r="E6" s="35">
+        <v>46270</v>
+      </c>
+      <c r="E18" s="35">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F6" s="2" t="str">
+        <v>0.6875</v>
+      </c>
+      <c r="F18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F14</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G6" s="2" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="G18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>Winden</v>
-      </c>
-      <c r="H6" s="2" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="H18" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <f>'Nach Mannschaften sortiert'!A56</f>
-        <v>54</v>
-      </c>
-      <c r="B7" s="2">
-        <f>'Nach Mannschaften sortiert'!B56</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C56</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D7" s="13">
-        <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46043</v>
-      </c>
-      <c r="E7" s="35">
-        <f>'Nach Mannschaften sortiert'!E56</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <f>'Nach Mannschaften sortiert'!F56</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <f>'Nach Mannschaften sortiert'!G56</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <f>'Nach Mannschaften sortiert'!H56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <f>'Nach Mannschaften sortiert'!A16</f>
-        <v>14</v>
-      </c>
-      <c r="B8" s="2">
-        <f>'Nach Mannschaften sortiert'!B16</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C16</f>
-        <v>KM</v>
-      </c>
-      <c r="D8" s="13">
-        <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46291</v>
-      </c>
-      <c r="E8" s="35">
-        <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.75</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F16</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>Wallern</v>
-      </c>
-      <c r="H8" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="63">
-        <f>'Nach Mannschaften sortiert'!A111</f>
-        <v>109</v>
-      </c>
-      <c r="B9" s="63">
-        <f>'Nach Mannschaften sortiert'!B111</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C111</f>
-        <v>Camp</v>
-      </c>
-      <c r="D9" s="64">
-        <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46230</v>
-      </c>
-      <c r="E9" s="65">
-        <f>'Nach Mannschaften sortiert'!E111</f>
-        <v>0.375</v>
-      </c>
-      <c r="F9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!F111</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!G111</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H9" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!H111</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <f>'Nach Mannschaften sortiert'!A18</f>
-        <v>16</v>
-      </c>
-      <c r="B10" s="2">
-        <f>'Nach Mannschaften sortiert'!B18</f>
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C18</f>
-        <v>KM</v>
-      </c>
-      <c r="D10" s="13">
-        <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46304</v>
-      </c>
-      <c r="E10" s="35">
-        <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F18</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Wimpassing</v>
-      </c>
-      <c r="H10" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="63">
-        <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>110</v>
-      </c>
-      <c r="B11" s="63">
-        <f>'Nach Mannschaften sortiert'!B112</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C112</f>
-        <v>Camp</v>
-      </c>
-      <c r="D11" s="64">
-        <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46231</v>
-      </c>
-      <c r="E11" s="65">
-        <f>'Nach Mannschaften sortiert'!E112</f>
-        <v>0.375</v>
-      </c>
-      <c r="F11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!F112</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!G112</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H11" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!H112</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <f>'Nach Mannschaften sortiert'!A20</f>
-        <v>18</v>
-      </c>
-      <c r="B12" s="2">
-        <f>'Nach Mannschaften sortiert'!B20</f>
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C20</f>
-        <v>KM</v>
-      </c>
-      <c r="D12" s="13">
-        <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46319</v>
-      </c>
-      <c r="E12" s="35">
-        <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F20</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Gols</v>
-      </c>
-      <c r="H12" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <f>'Nach Mannschaften sortiert'!A21</f>
-        <v>19</v>
-      </c>
-      <c r="B13" s="2">
-        <f>'Nach Mannschaften sortiert'!B21</f>
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C21</f>
-        <v>KM</v>
-      </c>
-      <c r="D13" s="13">
-        <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46326</v>
-      </c>
-      <c r="E13" s="35">
-        <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.75</v>
-      </c>
-      <c r="F13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F21</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="G13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="H13" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="63">
-        <f>'Nach Mannschaften sortiert'!A113</f>
-        <v>111</v>
-      </c>
-      <c r="B14" s="63">
-        <f>'Nach Mannschaften sortiert'!B113</f>
-        <v>3</v>
-      </c>
-      <c r="C14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!C113</f>
-        <v>Camp</v>
-      </c>
-      <c r="D14" s="64">
-        <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46232</v>
-      </c>
-      <c r="E14" s="65">
-        <f>'Nach Mannschaften sortiert'!E113</f>
-        <v>0.375</v>
-      </c>
-      <c r="F14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!F113</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!G113</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H14" s="63" t="str">
-        <f>'Nach Mannschaften sortiert'!H113</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <f>'Nach Mannschaften sortiert'!A36</f>
-        <v>34</v>
-      </c>
-      <c r="B15" s="2">
-        <f>'Nach Mannschaften sortiert'!B36</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C36</f>
-        <v>U16</v>
-      </c>
-      <c r="D15" s="13">
-        <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46023</v>
-      </c>
-      <c r="E15" s="35">
-        <f>'Nach Mannschaften sortiert'!E36</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f>'Nach Mannschaften sortiert'!F36</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <f>'Nach Mannschaften sortiert'!G36</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <f>'Nach Mannschaften sortiert'!H36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57">
-        <f>'Nach Mannschaften sortiert'!A37</f>
-        <v>35</v>
-      </c>
-      <c r="B16" s="57">
-        <f>'Nach Mannschaften sortiert'!B37</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C37</f>
-        <v>U16</v>
-      </c>
-      <c r="D16" s="58">
-        <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46024</v>
-      </c>
-      <c r="E16" s="59">
-        <f>'Nach Mannschaften sortiert'!E37</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="57">
-        <f>'Nach Mannschaften sortiert'!F37</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="57">
-        <f>'Nach Mannschaften sortiert'!G37</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="57">
-        <f>'Nach Mannschaften sortiert'!H37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <f>'Nach Mannschaften sortiert'!A38</f>
-        <v>36</v>
-      </c>
-      <c r="B17" s="2">
-        <f>'Nach Mannschaften sortiert'!B38</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C38</f>
-        <v>U16</v>
-      </c>
-      <c r="D17" s="13">
-        <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46025</v>
-      </c>
-      <c r="E17" s="35">
-        <f>'Nach Mannschaften sortiert'!E38</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f>'Nach Mannschaften sortiert'!F38</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <f>'Nach Mannschaften sortiert'!G38</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <f>'Nach Mannschaften sortiert'!H38</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <f>'Nach Mannschaften sortiert'!A13</f>
-        <v>11</v>
-      </c>
-      <c r="B18" s="2">
-        <f>'Nach Mannschaften sortiert'!B13</f>
-        <v>4</v>
-      </c>
-      <c r="C18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C13</f>
-        <v>KM</v>
-      </c>
-      <c r="D18" s="13">
-        <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>46270</v>
-      </c>
-      <c r="E18" s="35">
-        <f>'Nach Mannschaften sortiert'!E13</f>
-        <v>0.6875</v>
-      </c>
-      <c r="F18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F13</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="G18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="H18" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H13</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <f>'Nach Mannschaften sortiert'!A40</f>
-        <v>38</v>
+        <f>'Nach Mannschaften sortiert'!A41</f>
+        <v>40</v>
       </c>
       <c r="B19" s="2">
-        <f>'Nach Mannschaften sortiert'!B40</f>
+        <f>'Nach Mannschaften sortiert'!B41</f>
         <v>5</v>
       </c>
       <c r="C19" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C40</f>
+        <f>'Nach Mannschaften sortiert'!C41</f>
         <v>U16</v>
       </c>
       <c r="D19" s="13">
-        <f>'Nach Mannschaften sortiert'!D40</f>
+        <f>'Nach Mannschaften sortiert'!D41</f>
         <v>46027</v>
       </c>
       <c r="E19" s="35">
-        <f>'Nach Mannschaften sortiert'!E40</f>
+        <f>'Nach Mannschaften sortiert'!E41</f>
         <v>0</v>
       </c>
       <c r="F19" s="2">
-        <f>'Nach Mannschaften sortiert'!F40</f>
+        <f>'Nach Mannschaften sortiert'!F41</f>
         <v>0</v>
       </c>
       <c r="G19" s="2">
-        <f>'Nach Mannschaften sortiert'!G40</f>
+        <f>'Nach Mannschaften sortiert'!G41</f>
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <f>'Nach Mannschaften sortiert'!H40</f>
+        <f>'Nach Mannschaften sortiert'!H41</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="54">
-        <f>'Nach Mannschaften sortiert'!A41</f>
-        <v>39</v>
+        <f>'Nach Mannschaften sortiert'!A42</f>
+        <v>41</v>
       </c>
       <c r="B20" s="54">
-        <f>'Nach Mannschaften sortiert'!B41</f>
+        <f>'Nach Mannschaften sortiert'!B42</f>
         <v>6</v>
       </c>
       <c r="C20" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C41</f>
+        <f>'Nach Mannschaften sortiert'!C42</f>
         <v>U16</v>
       </c>
       <c r="D20" s="55">
-        <f>'Nach Mannschaften sortiert'!D41</f>
+        <f>'Nach Mannschaften sortiert'!D42</f>
         <v>46028</v>
       </c>
       <c r="E20" s="56">
-        <f>'Nach Mannschaften sortiert'!E41</f>
+        <f>'Nach Mannschaften sortiert'!E42</f>
         <v>0</v>
       </c>
       <c r="F20" s="54">
-        <f>'Nach Mannschaften sortiert'!F41</f>
+        <f>'Nach Mannschaften sortiert'!F42</f>
         <v>0</v>
       </c>
       <c r="G20" s="54">
-        <f>'Nach Mannschaften sortiert'!G41</f>
+        <f>'Nach Mannschaften sortiert'!G42</f>
         <v>0</v>
       </c>
       <c r="H20" s="54">
-        <f>'Nach Mannschaften sortiert'!H41</f>
+        <f>'Nach Mannschaften sortiert'!H42</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <f>'Nach Mannschaften sortiert'!A42</f>
-        <v>40</v>
+        <f>'Nach Mannschaften sortiert'!A43</f>
+        <v>42</v>
       </c>
       <c r="B21" s="2">
-        <f>'Nach Mannschaften sortiert'!B42</f>
+        <f>'Nach Mannschaften sortiert'!B43</f>
         <v>7</v>
       </c>
       <c r="C21" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C42</f>
+        <f>'Nach Mannschaften sortiert'!C43</f>
         <v>U16</v>
       </c>
       <c r="D21" s="13">
-        <f>'Nach Mannschaften sortiert'!D42</f>
+        <f>'Nach Mannschaften sortiert'!D43</f>
         <v>46029</v>
       </c>
       <c r="E21" s="35">
-        <f>'Nach Mannschaften sortiert'!E42</f>
+        <f>'Nach Mannschaften sortiert'!E43</f>
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <f>'Nach Mannschaften sortiert'!F42</f>
+        <f>'Nach Mannschaften sortiert'!F43</f>
         <v>0</v>
       </c>
       <c r="G21" s="2">
-        <f>'Nach Mannschaften sortiert'!G42</f>
+        <f>'Nach Mannschaften sortiert'!G43</f>
         <v>0</v>
       </c>
       <c r="H21" s="2">
-        <f>'Nach Mannschaften sortiert'!H42</f>
+        <f>'Nach Mannschaften sortiert'!H43</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="57">
-        <f>'Nach Mannschaften sortiert'!A43</f>
-        <v>41</v>
+        <f>'Nach Mannschaften sortiert'!A44</f>
+        <v>43</v>
       </c>
       <c r="B22" s="57">
-        <f>'Nach Mannschaften sortiert'!B43</f>
+        <f>'Nach Mannschaften sortiert'!B44</f>
         <v>8</v>
       </c>
       <c r="C22" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C43</f>
+        <f>'Nach Mannschaften sortiert'!C44</f>
         <v>U16</v>
       </c>
       <c r="D22" s="58">
-        <f>'Nach Mannschaften sortiert'!D43</f>
+        <f>'Nach Mannschaften sortiert'!D44</f>
         <v>46030</v>
       </c>
       <c r="E22" s="59">
-        <f>'Nach Mannschaften sortiert'!E43</f>
+        <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="F22" s="57">
-        <f>'Nach Mannschaften sortiert'!F43</f>
+        <f>'Nach Mannschaften sortiert'!F44</f>
         <v>0</v>
       </c>
       <c r="G22" s="57">
-        <f>'Nach Mannschaften sortiert'!G43</f>
+        <f>'Nach Mannschaften sortiert'!G44</f>
         <v>0</v>
       </c>
       <c r="H22" s="57">
-        <f>'Nach Mannschaften sortiert'!H43</f>
+        <f>'Nach Mannschaften sortiert'!H44</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <f>'Nach Mannschaften sortiert'!A44</f>
-        <v>42</v>
+        <f>'Nach Mannschaften sortiert'!A45</f>
+        <v>44</v>
       </c>
       <c r="B23" s="2">
-        <f>'Nach Mannschaften sortiert'!B44</f>
+        <f>'Nach Mannschaften sortiert'!B45</f>
         <v>9</v>
       </c>
       <c r="C23" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C44</f>
+        <f>'Nach Mannschaften sortiert'!C45</f>
         <v>U16</v>
       </c>
       <c r="D23" s="13">
-        <f>'Nach Mannschaften sortiert'!D44</f>
+        <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46031</v>
       </c>
       <c r="E23" s="35">
-        <f>'Nach Mannschaften sortiert'!E44</f>
+        <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="F23" s="2">
-        <f>'Nach Mannschaften sortiert'!F44</f>
+        <f>'Nach Mannschaften sortiert'!F45</f>
         <v>0</v>
       </c>
       <c r="G23" s="2">
-        <f>'Nach Mannschaften sortiert'!G44</f>
+        <f>'Nach Mannschaften sortiert'!G45</f>
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <f>'Nach Mannschaften sortiert'!H44</f>
+        <f>'Nach Mannschaften sortiert'!H45</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="60">
-        <f>'Nach Mannschaften sortiert'!A91</f>
-        <v>89</v>
+        <f>'Nach Mannschaften sortiert'!A92</f>
+        <v>91</v>
       </c>
       <c r="B24" s="60">
-        <f>'Nach Mannschaften sortiert'!B91</f>
+        <f>'Nach Mannschaften sortiert'!B92</f>
         <v>1</v>
       </c>
       <c r="C24" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C91</f>
+        <f>'Nach Mannschaften sortiert'!C92</f>
         <v>U9</v>
       </c>
       <c r="D24" s="61">
-        <f>'Nach Mannschaften sortiert'!D91</f>
+        <f>'Nach Mannschaften sortiert'!D92</f>
         <v>46078</v>
       </c>
       <c r="E24" s="62">
-        <f>'Nach Mannschaften sortiert'!E91</f>
+        <f>'Nach Mannschaften sortiert'!E92</f>
         <v>0</v>
       </c>
       <c r="F24" s="60">
-        <f>'Nach Mannschaften sortiert'!F91</f>
+        <f>'Nach Mannschaften sortiert'!F92</f>
         <v>0</v>
       </c>
       <c r="G24" s="60">
-        <f>'Nach Mannschaften sortiert'!G91</f>
+        <f>'Nach Mannschaften sortiert'!G92</f>
         <v>0</v>
       </c>
       <c r="H24" s="60">
-        <f>'Nach Mannschaften sortiert'!H91</f>
+        <f>'Nach Mannschaften sortiert'!H92</f>
         <v>0</v>
       </c>
     </row>
@@ -11066,35 +11139,35 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="60">
-        <f>'Nach Mannschaften sortiert'!A101</f>
-        <v>99</v>
+        <f>'Nach Mannschaften sortiert'!A102</f>
+        <v>101</v>
       </c>
       <c r="B26" s="60">
-        <f>'Nach Mannschaften sortiert'!B101</f>
+        <f>'Nach Mannschaften sortiert'!B102</f>
         <v>1</v>
       </c>
       <c r="C26" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C101</f>
+        <f>'Nach Mannschaften sortiert'!C102</f>
         <v>U8</v>
       </c>
       <c r="D26" s="61">
-        <f>'Nach Mannschaften sortiert'!D101</f>
+        <f>'Nach Mannschaften sortiert'!D102</f>
         <v>46312</v>
       </c>
       <c r="E26" s="62">
-        <f>'Nach Mannschaften sortiert'!E101</f>
+        <f>'Nach Mannschaften sortiert'!E102</f>
         <v>0.39583333333333331</v>
       </c>
       <c r="F26" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!F101</f>
+        <f>'Nach Mannschaften sortiert'!F102</f>
         <v>Neufeld</v>
       </c>
       <c r="G26" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!G101</f>
+        <f>'Nach Mannschaften sortiert'!G102</f>
         <v>Heimturnier</v>
       </c>
       <c r="H26" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!H101</f>
+        <f>'Nach Mannschaften sortiert'!H102</f>
         <v>Heim</v>
       </c>
     </row>
@@ -11168,35 +11241,35 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="60">
-        <f>'Nach Mannschaften sortiert'!A106</f>
-        <v>104</v>
+        <f>'Nach Mannschaften sortiert'!A107</f>
+        <v>106</v>
       </c>
       <c r="B29" s="60">
-        <f>'Nach Mannschaften sortiert'!B106</f>
+        <f>'Nach Mannschaften sortiert'!B107</f>
         <v>1</v>
       </c>
       <c r="C29" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C106</f>
+        <f>'Nach Mannschaften sortiert'!C107</f>
         <v>U7</v>
       </c>
       <c r="D29" s="61">
-        <f>'Nach Mannschaften sortiert'!D106</f>
+        <f>'Nach Mannschaften sortiert'!D107</f>
         <v>46312</v>
       </c>
       <c r="E29" s="62">
-        <f>'Nach Mannschaften sortiert'!E106</f>
+        <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="F29" s="60">
-        <f>'Nach Mannschaften sortiert'!F106</f>
+        <f>'Nach Mannschaften sortiert'!F107</f>
         <v>0</v>
       </c>
       <c r="G29" s="60">
-        <f>'Nach Mannschaften sortiert'!G106</f>
+        <f>'Nach Mannschaften sortiert'!G107</f>
         <v>0</v>
       </c>
       <c r="H29" s="60">
-        <f>'Nach Mannschaften sortiert'!H106</f>
+        <f>'Nach Mannschaften sortiert'!H107</f>
         <v>0</v>
       </c>
     </row>
@@ -11372,103 +11445,103 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="60">
-        <f>'Nach Mannschaften sortiert'!A77</f>
-        <v>75</v>
+        <f>'Nach Mannschaften sortiert'!A78</f>
+        <v>77</v>
       </c>
       <c r="B35" s="60">
-        <f>'Nach Mannschaften sortiert'!B77</f>
+        <f>'Nach Mannschaften sortiert'!B78</f>
         <v>2</v>
       </c>
       <c r="C35" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C77</f>
+        <f>'Nach Mannschaften sortiert'!C78</f>
         <v>U11</v>
       </c>
       <c r="D35" s="61">
-        <f>'Nach Mannschaften sortiert'!D77</f>
+        <f>'Nach Mannschaften sortiert'!D78</f>
         <v>46064</v>
       </c>
       <c r="E35" s="62">
-        <f>'Nach Mannschaften sortiert'!E77</f>
+        <f>'Nach Mannschaften sortiert'!E78</f>
         <v>0</v>
       </c>
       <c r="F35" s="60">
-        <f>'Nach Mannschaften sortiert'!F77</f>
+        <f>'Nach Mannschaften sortiert'!F78</f>
         <v>0</v>
       </c>
       <c r="G35" s="60">
-        <f>'Nach Mannschaften sortiert'!G77</f>
+        <f>'Nach Mannschaften sortiert'!G78</f>
         <v>0</v>
       </c>
       <c r="H35" s="60">
-        <f>'Nach Mannschaften sortiert'!H77</f>
+        <f>'Nach Mannschaften sortiert'!H78</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <f>'Nach Mannschaften sortiert'!A47</f>
-        <v>45</v>
+        <f>'Nach Mannschaften sortiert'!A48</f>
+        <v>47</v>
       </c>
       <c r="B36" s="2">
-        <f>'Nach Mannschaften sortiert'!B47</f>
+        <f>'Nach Mannschaften sortiert'!B48</f>
         <v>2</v>
       </c>
       <c r="C36" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C47</f>
+        <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U14</v>
       </c>
       <c r="D36" s="13">
-        <f>'Nach Mannschaften sortiert'!D47</f>
+        <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46034</v>
       </c>
       <c r="E36" s="35">
-        <f>'Nach Mannschaften sortiert'!E47</f>
+        <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <f>'Nach Mannschaften sortiert'!F47</f>
+        <f>'Nach Mannschaften sortiert'!F48</f>
         <v>0</v>
       </c>
       <c r="G36" s="2">
-        <f>'Nach Mannschaften sortiert'!G47</f>
+        <f>'Nach Mannschaften sortiert'!G48</f>
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <f>'Nach Mannschaften sortiert'!H47</f>
+        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <f>'Nach Mannschaften sortiert'!A48</f>
-        <v>46</v>
+        <f>'Nach Mannschaften sortiert'!A49</f>
+        <v>48</v>
       </c>
       <c r="B37" s="2">
-        <f>'Nach Mannschaften sortiert'!B48</f>
+        <f>'Nach Mannschaften sortiert'!B49</f>
         <v>3</v>
       </c>
       <c r="C37" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C48</f>
+        <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U14</v>
       </c>
       <c r="D37" s="13">
-        <f>'Nach Mannschaften sortiert'!D48</f>
+        <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46035</v>
       </c>
       <c r="E37" s="35">
-        <f>'Nach Mannschaften sortiert'!E48</f>
+        <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <f>'Nach Mannschaften sortiert'!F48</f>
+        <f>'Nach Mannschaften sortiert'!F49</f>
         <v>0</v>
       </c>
       <c r="G37" s="2">
-        <f>'Nach Mannschaften sortiert'!G48</f>
+        <f>'Nach Mannschaften sortiert'!G49</f>
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <f>'Nach Mannschaften sortiert'!H48</f>
+        <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
     </row>
@@ -11542,205 +11615,205 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
+        <f>'Nach Mannschaften sortiert'!A51</f>
+        <v>50</v>
+      </c>
+      <c r="B40" s="2">
+        <f>'Nach Mannschaften sortiert'!B51</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C51</f>
+        <v>U14</v>
+      </c>
+      <c r="D40" s="13">
+        <f>'Nach Mannschaften sortiert'!D51</f>
+        <v>46037</v>
+      </c>
+      <c r="E40" s="35">
+        <f>'Nach Mannschaften sortiert'!E51</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <f>'Nach Mannschaften sortiert'!F51</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
+        <f>'Nach Mannschaften sortiert'!G51</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <f>'Nach Mannschaften sortiert'!H51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="57">
+        <f>'Nach Mannschaften sortiert'!A16</f>
+        <v>15</v>
+      </c>
+      <c r="B41" s="57">
+        <f>'Nach Mannschaften sortiert'!B16</f>
+        <v>6</v>
+      </c>
+      <c r="C41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!C16</f>
+        <v>KM</v>
+      </c>
+      <c r="D41" s="58">
+        <f>'Nach Mannschaften sortiert'!D16</f>
+        <v>46284</v>
+      </c>
+      <c r="E41" s="59">
+        <f>'Nach Mannschaften sortiert'!E16</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!F16</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="G41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!G16</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="H41" s="57" t="str">
+        <f>'Nach Mannschaften sortiert'!H16</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="66">
+        <f>'Nach Mannschaften sortiert'!A82</f>
+        <v>81</v>
+      </c>
+      <c r="B42" s="66">
+        <f>'Nach Mannschaften sortiert'!B82</f>
+        <v>6</v>
+      </c>
+      <c r="C42" s="66" t="str">
+        <f>'Nach Mannschaften sortiert'!C82</f>
+        <v>U11</v>
+      </c>
+      <c r="D42" s="67">
+        <f>'Nach Mannschaften sortiert'!D82</f>
+        <v>46068</v>
+      </c>
+      <c r="E42" s="68">
+        <f>'Nach Mannschaften sortiert'!E82</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="66">
+        <f>'Nach Mannschaften sortiert'!F82</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="66">
+        <f>'Nach Mannschaften sortiert'!G82</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="66">
+        <f>'Nach Mannschaften sortiert'!H82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <f>'Nach Mannschaften sortiert'!A56</f>
+        <v>55</v>
+      </c>
+      <c r="B43" s="2">
+        <f>'Nach Mannschaften sortiert'!B56</f>
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="str">
+        <f>'Nach Mannschaften sortiert'!C56</f>
+        <v>U14</v>
+      </c>
+      <c r="D43" s="13">
+        <f>'Nach Mannschaften sortiert'!D56</f>
+        <v>46042</v>
+      </c>
+      <c r="E43" s="35">
+        <f>'Nach Mannschaften sortiert'!E56</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <f>'Nach Mannschaften sortiert'!F56</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
+        <f>'Nach Mannschaften sortiert'!G56</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="2">
+        <f>'Nach Mannschaften sortiert'!H56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="60">
+        <f>'Nach Mannschaften sortiert'!A59</f>
+        <v>58</v>
+      </c>
+      <c r="B44" s="60">
+        <f>'Nach Mannschaften sortiert'!B59</f>
+        <v>3</v>
+      </c>
+      <c r="C44" s="60" t="str">
+        <f>'Nach Mannschaften sortiert'!C59</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D44" s="61">
+        <f>'Nach Mannschaften sortiert'!D59</f>
+        <v>46045</v>
+      </c>
+      <c r="E44" s="62">
+        <f>'Nach Mannschaften sortiert'!E59</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="60">
+        <f>'Nach Mannschaften sortiert'!F59</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="60">
+        <f>'Nach Mannschaften sortiert'!G59</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="60">
+        <f>'Nach Mannschaften sortiert'!H59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="60">
         <f>'Nach Mannschaften sortiert'!A50</f>
-        <v>48</v>
-      </c>
-      <c r="B40" s="2">
+        <v>49</v>
+      </c>
+      <c r="B45" s="60">
         <f>'Nach Mannschaften sortiert'!B50</f>
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="C45" s="60" t="str">
         <f>'Nach Mannschaften sortiert'!C50</f>
         <v>U14</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D45" s="61">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46037</v>
-      </c>
-      <c r="E40" s="35">
+        <v>46036</v>
+      </c>
+      <c r="E45" s="62">
         <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F45" s="60">
         <f>'Nach Mannschaften sortiert'!F50</f>
         <v>0</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G45" s="60">
         <f>'Nach Mannschaften sortiert'!G50</f>
         <v>0</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H45" s="60">
         <f>'Nach Mannschaften sortiert'!H50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="57">
-        <f>'Nach Mannschaften sortiert'!A15</f>
-        <v>13</v>
-      </c>
-      <c r="B41" s="57">
-        <f>'Nach Mannschaften sortiert'!B15</f>
-        <v>6</v>
-      </c>
-      <c r="C41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C15</f>
-        <v>KM</v>
-      </c>
-      <c r="D41" s="58">
-        <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46284</v>
-      </c>
-      <c r="E41" s="59">
-        <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F15</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="G41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="H41" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H15</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="66">
-        <f>'Nach Mannschaften sortiert'!A81</f>
-        <v>79</v>
-      </c>
-      <c r="B42" s="66">
-        <f>'Nach Mannschaften sortiert'!B81</f>
-        <v>6</v>
-      </c>
-      <c r="C42" s="66" t="str">
-        <f>'Nach Mannschaften sortiert'!C81</f>
-        <v>U11</v>
-      </c>
-      <c r="D42" s="67">
-        <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46068</v>
-      </c>
-      <c r="E42" s="68">
-        <f>'Nach Mannschaften sortiert'!E81</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="66">
-        <f>'Nach Mannschaften sortiert'!F81</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="66">
-        <f>'Nach Mannschaften sortiert'!G81</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="66">
-        <f>'Nach Mannschaften sortiert'!H81</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <f>'Nach Mannschaften sortiert'!A55</f>
-        <v>53</v>
-      </c>
-      <c r="B43" s="2">
-        <f>'Nach Mannschaften sortiert'!B55</f>
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C55</f>
-        <v>U14</v>
-      </c>
-      <c r="D43" s="13">
-        <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46042</v>
-      </c>
-      <c r="E43" s="35">
-        <f>'Nach Mannschaften sortiert'!E55</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <f>'Nach Mannschaften sortiert'!F55</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="2">
-        <f>'Nach Mannschaften sortiert'!G55</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <f>'Nach Mannschaften sortiert'!H55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="60">
-        <f>'Nach Mannschaften sortiert'!A58</f>
-        <v>56</v>
-      </c>
-      <c r="B44" s="60">
-        <f>'Nach Mannschaften sortiert'!B58</f>
-        <v>3</v>
-      </c>
-      <c r="C44" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C58</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D44" s="61">
-        <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46045</v>
-      </c>
-      <c r="E44" s="62">
-        <f>'Nach Mannschaften sortiert'!E58</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="60">
-        <f>'Nach Mannschaften sortiert'!F58</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="60">
-        <f>'Nach Mannschaften sortiert'!G58</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="60">
-        <f>'Nach Mannschaften sortiert'!H58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="60">
-        <f>'Nach Mannschaften sortiert'!A49</f>
-        <v>47</v>
-      </c>
-      <c r="B45" s="60">
-        <f>'Nach Mannschaften sortiert'!B49</f>
-        <v>4</v>
-      </c>
-      <c r="C45" s="60" t="str">
-        <f>'Nach Mannschaften sortiert'!C49</f>
-        <v>U14</v>
-      </c>
-      <c r="D45" s="61">
-        <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46036</v>
-      </c>
-      <c r="E45" s="62">
-        <f>'Nach Mannschaften sortiert'!E49</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="60">
-        <f>'Nach Mannschaften sortiert'!F49</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="60">
-        <f>'Nach Mannschaften sortiert'!G49</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="60">
-        <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
     </row>
@@ -11780,137 +11853,137 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <f>'Nach Mannschaften sortiert'!A57</f>
-        <v>55</v>
+        <f>'Nach Mannschaften sortiert'!A58</f>
+        <v>57</v>
       </c>
       <c r="B47" s="2">
-        <f>'Nach Mannschaften sortiert'!B57</f>
+        <f>'Nach Mannschaften sortiert'!B58</f>
         <v>2</v>
       </c>
       <c r="C47" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C57</f>
+        <f>'Nach Mannschaften sortiert'!C58</f>
         <v>U12_1</v>
       </c>
       <c r="D47" s="13">
-        <f>'Nach Mannschaften sortiert'!D57</f>
+        <f>'Nach Mannschaften sortiert'!D58</f>
         <v>46044</v>
       </c>
       <c r="E47" s="35">
-        <f>'Nach Mannschaften sortiert'!E57</f>
+        <f>'Nach Mannschaften sortiert'!E58</f>
         <v>0</v>
       </c>
       <c r="F47" s="2">
-        <f>'Nach Mannschaften sortiert'!F57</f>
+        <f>'Nach Mannschaften sortiert'!F58</f>
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <f>'Nach Mannschaften sortiert'!G57</f>
+        <f>'Nach Mannschaften sortiert'!G58</f>
         <v>0</v>
       </c>
       <c r="H47" s="2">
-        <f>'Nach Mannschaften sortiert'!H57</f>
+        <f>'Nach Mannschaften sortiert'!H58</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="57">
-        <f>'Nach Mannschaften sortiert'!A39</f>
-        <v>37</v>
+        <f>'Nach Mannschaften sortiert'!A40</f>
+        <v>39</v>
       </c>
       <c r="B48" s="57">
-        <f>'Nach Mannschaften sortiert'!B39</f>
+        <f>'Nach Mannschaften sortiert'!B40</f>
         <v>4</v>
       </c>
       <c r="C48" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C39</f>
+        <f>'Nach Mannschaften sortiert'!C40</f>
         <v>U16</v>
       </c>
       <c r="D48" s="58">
-        <f>'Nach Mannschaften sortiert'!D39</f>
+        <f>'Nach Mannschaften sortiert'!D40</f>
         <v>46026</v>
       </c>
       <c r="E48" s="59">
-        <f>'Nach Mannschaften sortiert'!E39</f>
+        <f>'Nach Mannschaften sortiert'!E40</f>
         <v>0</v>
       </c>
       <c r="F48" s="57">
-        <f>'Nach Mannschaften sortiert'!F39</f>
+        <f>'Nach Mannschaften sortiert'!F40</f>
         <v>0</v>
       </c>
       <c r="G48" s="57">
-        <f>'Nach Mannschaften sortiert'!G39</f>
+        <f>'Nach Mannschaften sortiert'!G40</f>
         <v>0</v>
       </c>
       <c r="H48" s="57">
-        <f>'Nach Mannschaften sortiert'!H39</f>
+        <f>'Nach Mannschaften sortiert'!H40</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <f>'Nach Mannschaften sortiert'!A59</f>
-        <v>57</v>
+        <f>'Nach Mannschaften sortiert'!A60</f>
+        <v>59</v>
       </c>
       <c r="B49" s="2">
-        <f>'Nach Mannschaften sortiert'!B59</f>
+        <f>'Nach Mannschaften sortiert'!B60</f>
         <v>4</v>
       </c>
       <c r="C49" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C59</f>
+        <f>'Nach Mannschaften sortiert'!C60</f>
         <v>U12_1</v>
       </c>
       <c r="D49" s="13">
-        <f>'Nach Mannschaften sortiert'!D59</f>
+        <f>'Nach Mannschaften sortiert'!D60</f>
         <v>46046</v>
       </c>
       <c r="E49" s="35">
-        <f>'Nach Mannschaften sortiert'!E59</f>
+        <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="F49" s="2">
-        <f>'Nach Mannschaften sortiert'!F59</f>
+        <f>'Nach Mannschaften sortiert'!F60</f>
         <v>0</v>
       </c>
       <c r="G49" s="2">
-        <f>'Nach Mannschaften sortiert'!G59</f>
+        <f>'Nach Mannschaften sortiert'!G60</f>
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <f>'Nach Mannschaften sortiert'!H59</f>
+        <f>'Nach Mannschaften sortiert'!H60</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <f>'Nach Mannschaften sortiert'!A60</f>
-        <v>58</v>
+        <f>'Nach Mannschaften sortiert'!A61</f>
+        <v>60</v>
       </c>
       <c r="B50" s="2">
-        <f>'Nach Mannschaften sortiert'!B60</f>
+        <f>'Nach Mannschaften sortiert'!B61</f>
         <v>5</v>
       </c>
       <c r="C50" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C60</f>
+        <f>'Nach Mannschaften sortiert'!C61</f>
         <v>U12_1</v>
       </c>
       <c r="D50" s="13">
-        <f>'Nach Mannschaften sortiert'!D60</f>
+        <f>'Nach Mannschaften sortiert'!D61</f>
         <v>46047</v>
       </c>
       <c r="E50" s="35">
-        <f>'Nach Mannschaften sortiert'!E60</f>
+        <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="F50" s="2">
-        <f>'Nach Mannschaften sortiert'!F60</f>
+        <f>'Nach Mannschaften sortiert'!F61</f>
         <v>0</v>
       </c>
       <c r="G50" s="2">
-        <f>'Nach Mannschaften sortiert'!G60</f>
+        <f>'Nach Mannschaften sortiert'!G61</f>
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <f>'Nach Mannschaften sortiert'!H60</f>
+        <f>'Nach Mannschaften sortiert'!H61</f>
         <v>0</v>
       </c>
     </row>
@@ -11950,69 +12023,69 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="57">
-        <f>'Nach Mannschaften sortiert'!A17</f>
-        <v>15</v>
+        <f>'Nach Mannschaften sortiert'!A18</f>
+        <v>17</v>
       </c>
       <c r="B52" s="57">
-        <f>'Nach Mannschaften sortiert'!B17</f>
+        <f>'Nach Mannschaften sortiert'!B18</f>
         <v>8</v>
       </c>
       <c r="C52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
+        <f>'Nach Mannschaften sortiert'!C18</f>
         <v>KM</v>
       </c>
       <c r="D52" s="58">
-        <f>'Nach Mannschaften sortiert'!D17</f>
+        <f>'Nach Mannschaften sortiert'!D18</f>
         <v>46297</v>
       </c>
       <c r="E52" s="59">
-        <f>'Nach Mannschaften sortiert'!E17</f>
+        <f>'Nach Mannschaften sortiert'!E18</f>
         <v>0.79166666666666663</v>
       </c>
       <c r="F52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F17</f>
+        <f>'Nach Mannschaften sortiert'!F18</f>
         <v>Siegendorf</v>
       </c>
       <c r="G52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G17</f>
+        <f>'Nach Mannschaften sortiert'!G18</f>
         <v>Siegendorf</v>
       </c>
       <c r="H52" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H17</f>
+        <f>'Nach Mannschaften sortiert'!H18</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <f>'Nach Mannschaften sortiert'!A62</f>
-        <v>60</v>
+        <f>'Nach Mannschaften sortiert'!A63</f>
+        <v>62</v>
       </c>
       <c r="B53" s="2">
-        <f>'Nach Mannschaften sortiert'!B62</f>
+        <f>'Nach Mannschaften sortiert'!B63</f>
         <v>7</v>
       </c>
       <c r="C53" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C62</f>
+        <f>'Nach Mannschaften sortiert'!C63</f>
         <v>U12_1</v>
       </c>
       <c r="D53" s="13">
-        <f>'Nach Mannschaften sortiert'!D62</f>
+        <f>'Nach Mannschaften sortiert'!D63</f>
         <v>46049</v>
       </c>
       <c r="E53" s="35">
-        <f>'Nach Mannschaften sortiert'!E62</f>
+        <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="F53" s="2">
-        <f>'Nach Mannschaften sortiert'!F62</f>
+        <f>'Nach Mannschaften sortiert'!F63</f>
         <v>0</v>
       </c>
       <c r="G53" s="2">
-        <f>'Nach Mannschaften sortiert'!G62</f>
+        <f>'Nach Mannschaften sortiert'!G63</f>
         <v>0</v>
       </c>
       <c r="H53" s="2">
-        <f>'Nach Mannschaften sortiert'!H62</f>
+        <f>'Nach Mannschaften sortiert'!H63</f>
         <v>0</v>
       </c>
     </row>
@@ -12052,137 +12125,137 @@
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <f>'Nach Mannschaften sortiert'!A76</f>
-        <v>74</v>
+        <f>'Nach Mannschaften sortiert'!A77</f>
+        <v>76</v>
       </c>
       <c r="B55" s="2">
-        <f>'Nach Mannschaften sortiert'!B76</f>
+        <f>'Nach Mannschaften sortiert'!B77</f>
         <v>1</v>
       </c>
       <c r="C55" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C76</f>
+        <f>'Nach Mannschaften sortiert'!C77</f>
         <v>U11</v>
       </c>
       <c r="D55" s="13">
-        <f>'Nach Mannschaften sortiert'!D76</f>
+        <f>'Nach Mannschaften sortiert'!D77</f>
         <v>46063</v>
       </c>
       <c r="E55" s="35">
-        <f>'Nach Mannschaften sortiert'!E76</f>
+        <f>'Nach Mannschaften sortiert'!E77</f>
         <v>0</v>
       </c>
       <c r="F55" s="2">
-        <f>'Nach Mannschaften sortiert'!F76</f>
+        <f>'Nach Mannschaften sortiert'!F77</f>
         <v>0</v>
       </c>
       <c r="G55" s="2">
-        <f>'Nach Mannschaften sortiert'!G76</f>
+        <f>'Nach Mannschaften sortiert'!G77</f>
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <f>'Nach Mannschaften sortiert'!H76</f>
+        <f>'Nach Mannschaften sortiert'!H77</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="57">
-        <f>'Nach Mannschaften sortiert'!A82</f>
-        <v>80</v>
+        <f>'Nach Mannschaften sortiert'!A83</f>
+        <v>82</v>
       </c>
       <c r="B56" s="57">
-        <f>'Nach Mannschaften sortiert'!B82</f>
+        <f>'Nach Mannschaften sortiert'!B83</f>
         <v>7</v>
       </c>
       <c r="C56" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C82</f>
+        <f>'Nach Mannschaften sortiert'!C83</f>
         <v>U11</v>
       </c>
       <c r="D56" s="58">
-        <f>'Nach Mannschaften sortiert'!D82</f>
+        <f>'Nach Mannschaften sortiert'!D83</f>
         <v>46069</v>
       </c>
       <c r="E56" s="59">
-        <f>'Nach Mannschaften sortiert'!E82</f>
+        <f>'Nach Mannschaften sortiert'!E83</f>
         <v>0</v>
       </c>
       <c r="F56" s="57">
-        <f>'Nach Mannschaften sortiert'!F82</f>
+        <f>'Nach Mannschaften sortiert'!F83</f>
         <v>0</v>
       </c>
       <c r="G56" s="57">
-        <f>'Nach Mannschaften sortiert'!G82</f>
+        <f>'Nach Mannschaften sortiert'!G83</f>
         <v>0</v>
       </c>
       <c r="H56" s="57">
-        <f>'Nach Mannschaften sortiert'!H82</f>
+        <f>'Nach Mannschaften sortiert'!H83</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <f>'Nach Mannschaften sortiert'!A79</f>
-        <v>77</v>
+        <f>'Nach Mannschaften sortiert'!A80</f>
+        <v>79</v>
       </c>
       <c r="B57" s="2">
-        <f>'Nach Mannschaften sortiert'!B79</f>
+        <f>'Nach Mannschaften sortiert'!B80</f>
         <v>4</v>
       </c>
       <c r="C57" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C79</f>
+        <f>'Nach Mannschaften sortiert'!C80</f>
         <v>U11</v>
       </c>
       <c r="D57" s="13">
-        <f>'Nach Mannschaften sortiert'!D79</f>
+        <f>'Nach Mannschaften sortiert'!D80</f>
         <v>46066</v>
       </c>
       <c r="E57" s="35">
-        <f>'Nach Mannschaften sortiert'!E79</f>
+        <f>'Nach Mannschaften sortiert'!E80</f>
         <v>0</v>
       </c>
       <c r="F57" s="2">
-        <f>'Nach Mannschaften sortiert'!F79</f>
+        <f>'Nach Mannschaften sortiert'!F80</f>
         <v>0</v>
       </c>
       <c r="G57" s="2">
-        <f>'Nach Mannschaften sortiert'!G79</f>
+        <f>'Nach Mannschaften sortiert'!G80</f>
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <f>'Nach Mannschaften sortiert'!H79</f>
+        <f>'Nach Mannschaften sortiert'!H80</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="57">
-        <f>'Nach Mannschaften sortiert'!A19</f>
-        <v>17</v>
+        <f>'Nach Mannschaften sortiert'!A20</f>
+        <v>19</v>
       </c>
       <c r="B58" s="57">
-        <f>'Nach Mannschaften sortiert'!B19</f>
+        <f>'Nach Mannschaften sortiert'!B20</f>
         <v>10</v>
       </c>
       <c r="C58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C19</f>
+        <f>'Nach Mannschaften sortiert'!C20</f>
         <v>KM</v>
       </c>
       <c r="D58" s="58">
-        <f>'Nach Mannschaften sortiert'!D19</f>
+        <f>'Nach Mannschaften sortiert'!D20</f>
         <v>46311</v>
       </c>
       <c r="E58" s="59">
-        <f>'Nach Mannschaften sortiert'!E19</f>
+        <f>'Nach Mannschaften sortiert'!E20</f>
         <v>0.8125</v>
       </c>
       <c r="F58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F19</f>
+        <f>'Nach Mannschaften sortiert'!F20</f>
         <v>Hornstein</v>
       </c>
       <c r="G58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G19</f>
+        <f>'Nach Mannschaften sortiert'!G20</f>
         <v>Hornstein</v>
       </c>
       <c r="H58" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H19</f>
+        <f>'Nach Mannschaften sortiert'!H20</f>
         <v>Auswärts</v>
       </c>
     </row>
@@ -12222,137 +12295,137 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="57">
-        <f>'Nach Mannschaften sortiert'!A53</f>
-        <v>51</v>
+        <f>'Nach Mannschaften sortiert'!A54</f>
+        <v>53</v>
       </c>
       <c r="B60" s="57">
-        <f>'Nach Mannschaften sortiert'!B53</f>
+        <f>'Nach Mannschaften sortiert'!B54</f>
         <v>8</v>
       </c>
       <c r="C60" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C53</f>
+        <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U14</v>
       </c>
       <c r="D60" s="58">
-        <f>'Nach Mannschaften sortiert'!D53</f>
+        <f>'Nach Mannschaften sortiert'!D54</f>
         <v>46040</v>
       </c>
       <c r="E60" s="59">
-        <f>'Nach Mannschaften sortiert'!E53</f>
+        <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="F60" s="57">
-        <f>'Nach Mannschaften sortiert'!F53</f>
+        <f>'Nach Mannschaften sortiert'!F54</f>
         <v>0</v>
       </c>
       <c r="G60" s="57">
-        <f>'Nach Mannschaften sortiert'!G53</f>
+        <f>'Nach Mannschaften sortiert'!G54</f>
         <v>0</v>
       </c>
       <c r="H60" s="57">
-        <f>'Nach Mannschaften sortiert'!H53</f>
+        <f>'Nach Mannschaften sortiert'!H54</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <f>'Nach Mannschaften sortiert'!A83</f>
-        <v>81</v>
+        <f>'Nach Mannschaften sortiert'!A84</f>
+        <v>83</v>
       </c>
       <c r="B61" s="2">
-        <f>'Nach Mannschaften sortiert'!B83</f>
+        <f>'Nach Mannschaften sortiert'!B84</f>
         <v>8</v>
       </c>
       <c r="C61" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C83</f>
+        <f>'Nach Mannschaften sortiert'!C84</f>
         <v>U11</v>
       </c>
       <c r="D61" s="13">
-        <f>'Nach Mannschaften sortiert'!D83</f>
+        <f>'Nach Mannschaften sortiert'!D84</f>
         <v>46070</v>
       </c>
       <c r="E61" s="35">
-        <f>'Nach Mannschaften sortiert'!E83</f>
+        <f>'Nach Mannschaften sortiert'!E84</f>
         <v>0</v>
       </c>
       <c r="F61" s="2">
-        <f>'Nach Mannschaften sortiert'!F83</f>
+        <f>'Nach Mannschaften sortiert'!F84</f>
         <v>0</v>
       </c>
       <c r="G61" s="2">
-        <f>'Nach Mannschaften sortiert'!G83</f>
+        <f>'Nach Mannschaften sortiert'!G84</f>
         <v>0</v>
       </c>
       <c r="H61" s="2">
-        <f>'Nach Mannschaften sortiert'!H83</f>
+        <f>'Nach Mannschaften sortiert'!H84</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="54">
-        <f>'Nach Mannschaften sortiert'!A54</f>
-        <v>52</v>
+        <f>'Nach Mannschaften sortiert'!A55</f>
+        <v>54</v>
       </c>
       <c r="B62" s="54">
-        <f>'Nach Mannschaften sortiert'!B54</f>
+        <f>'Nach Mannschaften sortiert'!B55</f>
         <v>9</v>
       </c>
       <c r="C62" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C54</f>
+        <f>'Nach Mannschaften sortiert'!C55</f>
         <v>U14</v>
       </c>
       <c r="D62" s="55">
-        <f>'Nach Mannschaften sortiert'!D54</f>
+        <f>'Nach Mannschaften sortiert'!D55</f>
         <v>46041</v>
       </c>
       <c r="E62" s="56">
-        <f>'Nach Mannschaften sortiert'!E54</f>
+        <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
       <c r="F62" s="54">
-        <f>'Nach Mannschaften sortiert'!F54</f>
+        <f>'Nach Mannschaften sortiert'!F55</f>
         <v>0</v>
       </c>
       <c r="G62" s="54">
-        <f>'Nach Mannschaften sortiert'!G54</f>
+        <f>'Nach Mannschaften sortiert'!G55</f>
         <v>0</v>
       </c>
       <c r="H62" s="54">
-        <f>'Nach Mannschaften sortiert'!H54</f>
+        <f>'Nach Mannschaften sortiert'!H55</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <f>'Nach Mannschaften sortiert'!A85</f>
-        <v>83</v>
+        <f>'Nach Mannschaften sortiert'!A86</f>
+        <v>85</v>
       </c>
       <c r="B63" s="2">
-        <f>'Nach Mannschaften sortiert'!B85</f>
+        <f>'Nach Mannschaften sortiert'!B86</f>
         <v>10</v>
       </c>
       <c r="C63" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C85</f>
+        <f>'Nach Mannschaften sortiert'!C86</f>
         <v>U11</v>
       </c>
       <c r="D63" s="13">
-        <f>'Nach Mannschaften sortiert'!D85</f>
+        <f>'Nach Mannschaften sortiert'!D86</f>
         <v>46072</v>
       </c>
       <c r="E63" s="35">
-        <f>'Nach Mannschaften sortiert'!E85</f>
+        <f>'Nach Mannschaften sortiert'!E86</f>
         <v>0</v>
       </c>
       <c r="F63" s="2">
-        <f>'Nach Mannschaften sortiert'!F85</f>
+        <f>'Nach Mannschaften sortiert'!F86</f>
         <v>0</v>
       </c>
       <c r="G63" s="2">
-        <f>'Nach Mannschaften sortiert'!G85</f>
+        <f>'Nach Mannschaften sortiert'!G86</f>
         <v>0</v>
       </c>
       <c r="H63" s="2">
-        <f>'Nach Mannschaften sortiert'!H85</f>
+        <f>'Nach Mannschaften sortiert'!H86</f>
         <v>0</v>
       </c>
     </row>
@@ -12392,15 +12465,15 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="57">
-        <f>'Nach Mannschaften sortiert'!A84</f>
-        <v>82</v>
+        <f>'Nach Mannschaften sortiert'!A85</f>
+        <v>84</v>
       </c>
       <c r="B65" s="57">
-        <f>'Nach Mannschaften sortiert'!B84</f>
+        <f>'Nach Mannschaften sortiert'!B85</f>
         <v>9</v>
       </c>
       <c r="C65" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C84</f>
+        <f>'Nach Mannschaften sortiert'!C85</f>
         <v>U11</v>
       </c>
       <c r="D65" s="58">
@@ -12410,525 +12483,525 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F65" s="57">
-        <f>'Nach Mannschaften sortiert'!F84</f>
+        <f>'Nach Mannschaften sortiert'!F85</f>
         <v>0</v>
       </c>
       <c r="G65" s="57">
-        <f>'Nach Mannschaften sortiert'!G84</f>
+        <f>'Nach Mannschaften sortiert'!G85</f>
         <v>0</v>
       </c>
       <c r="H65" s="57">
-        <f>'Nach Mannschaften sortiert'!H84</f>
+        <f>'Nach Mannschaften sortiert'!H85</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <f>'Nach Mannschaften sortiert'!A92</f>
-        <v>90</v>
+        <f>'Nach Mannschaften sortiert'!A93</f>
+        <v>92</v>
       </c>
       <c r="B66" s="2">
-        <f>'Nach Mannschaften sortiert'!B92</f>
+        <f>'Nach Mannschaften sortiert'!B93</f>
         <v>2</v>
       </c>
       <c r="C66" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C92</f>
+        <f>'Nach Mannschaften sortiert'!C93</f>
         <v>U9</v>
       </c>
       <c r="D66" s="13">
-        <f>'Nach Mannschaften sortiert'!D92</f>
+        <f>'Nach Mannschaften sortiert'!D93</f>
         <v>46079</v>
       </c>
       <c r="E66" s="35">
-        <f>'Nach Mannschaften sortiert'!E92</f>
+        <f>'Nach Mannschaften sortiert'!E93</f>
         <v>0</v>
       </c>
       <c r="F66" s="2">
-        <f>'Nach Mannschaften sortiert'!F92</f>
+        <f>'Nach Mannschaften sortiert'!F93</f>
         <v>0</v>
       </c>
       <c r="G66" s="2">
-        <f>'Nach Mannschaften sortiert'!G92</f>
+        <f>'Nach Mannschaften sortiert'!G93</f>
         <v>0</v>
       </c>
       <c r="H66" s="2">
-        <f>'Nach Mannschaften sortiert'!H92</f>
+        <f>'Nach Mannschaften sortiert'!H93</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <f>'Nach Mannschaften sortiert'!A93</f>
-        <v>91</v>
+        <f>'Nach Mannschaften sortiert'!A94</f>
+        <v>93</v>
       </c>
       <c r="B67" s="2">
-        <f>'Nach Mannschaften sortiert'!B93</f>
+        <f>'Nach Mannschaften sortiert'!B94</f>
         <v>3</v>
       </c>
       <c r="C67" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C93</f>
+        <f>'Nach Mannschaften sortiert'!C94</f>
         <v>U9</v>
       </c>
       <c r="D67" s="13">
-        <f>'Nach Mannschaften sortiert'!D93</f>
+        <f>'Nach Mannschaften sortiert'!D94</f>
         <v>46080</v>
       </c>
       <c r="E67" s="35">
-        <f>'Nach Mannschaften sortiert'!E93</f>
+        <f>'Nach Mannschaften sortiert'!E94</f>
         <v>0</v>
       </c>
       <c r="F67" s="2">
-        <f>'Nach Mannschaften sortiert'!F93</f>
+        <f>'Nach Mannschaften sortiert'!F94</f>
         <v>0</v>
       </c>
       <c r="G67" s="2">
-        <f>'Nach Mannschaften sortiert'!G93</f>
+        <f>'Nach Mannschaften sortiert'!G94</f>
         <v>0</v>
       </c>
       <c r="H67" s="2">
-        <f>'Nach Mannschaften sortiert'!H93</f>
+        <f>'Nach Mannschaften sortiert'!H94</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <f>'Nach Mannschaften sortiert'!A94</f>
-        <v>92</v>
+        <f>'Nach Mannschaften sortiert'!A95</f>
+        <v>94</v>
       </c>
       <c r="B68" s="2">
-        <f>'Nach Mannschaften sortiert'!B94</f>
+        <f>'Nach Mannschaften sortiert'!B95</f>
         <v>4</v>
       </c>
       <c r="C68" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C94</f>
+        <f>'Nach Mannschaften sortiert'!C95</f>
         <v>U9</v>
       </c>
       <c r="D68" s="13">
-        <f>'Nach Mannschaften sortiert'!D94</f>
+        <f>'Nach Mannschaften sortiert'!D95</f>
         <v>46081</v>
       </c>
       <c r="E68" s="35">
-        <f>'Nach Mannschaften sortiert'!E94</f>
+        <f>'Nach Mannschaften sortiert'!E95</f>
         <v>0</v>
       </c>
       <c r="F68" s="2">
-        <f>'Nach Mannschaften sortiert'!F94</f>
+        <f>'Nach Mannschaften sortiert'!F95</f>
         <v>0</v>
       </c>
       <c r="G68" s="2">
-        <f>'Nach Mannschaften sortiert'!G94</f>
+        <f>'Nach Mannschaften sortiert'!G95</f>
         <v>0</v>
       </c>
       <c r="H68" s="2">
-        <f>'Nach Mannschaften sortiert'!H94</f>
+        <f>'Nach Mannschaften sortiert'!H95</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <f>'Nach Mannschaften sortiert'!A100</f>
-        <v>98</v>
+        <f>'Nach Mannschaften sortiert'!A101</f>
+        <v>100</v>
       </c>
       <c r="B69" s="2">
-        <f>'Nach Mannschaften sortiert'!B100</f>
+        <f>'Nach Mannschaften sortiert'!B101</f>
         <v>10</v>
       </c>
       <c r="C69" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C100</f>
+        <f>'Nach Mannschaften sortiert'!C101</f>
         <v>U9</v>
       </c>
       <c r="D69" s="13">
-        <f>'Nach Mannschaften sortiert'!D100</f>
+        <f>'Nach Mannschaften sortiert'!D101</f>
         <v>46087</v>
       </c>
       <c r="E69" s="35">
-        <f>'Nach Mannschaften sortiert'!E100</f>
+        <f>'Nach Mannschaften sortiert'!E101</f>
         <v>0</v>
       </c>
       <c r="F69" s="2">
-        <f>'Nach Mannschaften sortiert'!F100</f>
+        <f>'Nach Mannschaften sortiert'!F101</f>
         <v>0</v>
       </c>
       <c r="G69" s="2">
-        <f>'Nach Mannschaften sortiert'!G100</f>
+        <f>'Nach Mannschaften sortiert'!G101</f>
         <v>0</v>
       </c>
       <c r="H69" s="2">
-        <f>'Nach Mannschaften sortiert'!H100</f>
+        <f>'Nach Mannschaften sortiert'!H101</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="57">
-        <f>'Nach Mannschaften sortiert'!A61</f>
-        <v>59</v>
+        <f>'Nach Mannschaften sortiert'!A62</f>
+        <v>61</v>
       </c>
       <c r="B70" s="57">
-        <f>'Nach Mannschaften sortiert'!B61</f>
+        <f>'Nach Mannschaften sortiert'!B62</f>
         <v>6</v>
       </c>
       <c r="C70" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C61</f>
+        <f>'Nach Mannschaften sortiert'!C62</f>
         <v>U12_1</v>
       </c>
       <c r="D70" s="58">
-        <f>'Nach Mannschaften sortiert'!D61</f>
+        <f>'Nach Mannschaften sortiert'!D62</f>
         <v>46048</v>
       </c>
       <c r="E70" s="59">
-        <f>'Nach Mannschaften sortiert'!E61</f>
+        <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="F70" s="57">
-        <f>'Nach Mannschaften sortiert'!F61</f>
+        <f>'Nach Mannschaften sortiert'!F62</f>
         <v>0</v>
       </c>
       <c r="G70" s="57">
-        <f>'Nach Mannschaften sortiert'!G61</f>
+        <f>'Nach Mannschaften sortiert'!G62</f>
         <v>0</v>
       </c>
       <c r="H70" s="57">
-        <f>'Nach Mannschaften sortiert'!H61</f>
+        <f>'Nach Mannschaften sortiert'!H62</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <f>'Nach Mannschaften sortiert'!A102</f>
-        <v>100</v>
+        <f>'Nach Mannschaften sortiert'!A103</f>
+        <v>102</v>
       </c>
       <c r="B71" s="2">
-        <f>'Nach Mannschaften sortiert'!B102</f>
+        <f>'Nach Mannschaften sortiert'!B103</f>
         <v>2</v>
       </c>
       <c r="C71" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C102</f>
+        <f>'Nach Mannschaften sortiert'!C103</f>
         <v>U8</v>
       </c>
       <c r="D71" s="13">
-        <f>'Nach Mannschaften sortiert'!D102</f>
+        <f>'Nach Mannschaften sortiert'!D103</f>
         <v>46089</v>
       </c>
       <c r="E71" s="35">
-        <f>'Nach Mannschaften sortiert'!E102</f>
+        <f>'Nach Mannschaften sortiert'!E103</f>
         <v>0</v>
       </c>
       <c r="F71" s="2">
-        <f>'Nach Mannschaften sortiert'!F102</f>
+        <f>'Nach Mannschaften sortiert'!F103</f>
         <v>0</v>
       </c>
       <c r="G71" s="2">
-        <f>'Nach Mannschaften sortiert'!G102</f>
+        <f>'Nach Mannschaften sortiert'!G103</f>
         <v>0</v>
       </c>
       <c r="H71" s="2">
-        <f>'Nach Mannschaften sortiert'!H102</f>
+        <f>'Nach Mannschaften sortiert'!H103</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <f>'Nach Mannschaften sortiert'!A103</f>
-        <v>101</v>
+        <f>'Nach Mannschaften sortiert'!A104</f>
+        <v>103</v>
       </c>
       <c r="B72" s="2">
-        <f>'Nach Mannschaften sortiert'!B103</f>
+        <f>'Nach Mannschaften sortiert'!B104</f>
         <v>3</v>
       </c>
       <c r="C72" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C103</f>
+        <f>'Nach Mannschaften sortiert'!C104</f>
         <v>U8</v>
       </c>
       <c r="D72" s="13">
-        <f>'Nach Mannschaften sortiert'!D103</f>
+        <f>'Nach Mannschaften sortiert'!D104</f>
         <v>46090</v>
       </c>
       <c r="E72" s="35">
-        <f>'Nach Mannschaften sortiert'!E103</f>
+        <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0</v>
       </c>
       <c r="F72" s="2">
-        <f>'Nach Mannschaften sortiert'!F103</f>
+        <f>'Nach Mannschaften sortiert'!F104</f>
         <v>0</v>
       </c>
       <c r="G72" s="2">
-        <f>'Nach Mannschaften sortiert'!G103</f>
+        <f>'Nach Mannschaften sortiert'!G104</f>
         <v>0</v>
       </c>
       <c r="H72" s="2">
-        <f>'Nach Mannschaften sortiert'!H103</f>
+        <f>'Nach Mannschaften sortiert'!H104</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <f>'Nach Mannschaften sortiert'!A104</f>
-        <v>102</v>
+        <f>'Nach Mannschaften sortiert'!A105</f>
+        <v>104</v>
       </c>
       <c r="B73" s="2">
-        <f>'Nach Mannschaften sortiert'!B104</f>
+        <f>'Nach Mannschaften sortiert'!B105</f>
         <v>4</v>
       </c>
       <c r="C73" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C104</f>
+        <f>'Nach Mannschaften sortiert'!C105</f>
         <v>U8</v>
       </c>
       <c r="D73" s="13">
-        <f>'Nach Mannschaften sortiert'!D104</f>
+        <f>'Nach Mannschaften sortiert'!D105</f>
         <v>46091</v>
       </c>
       <c r="E73" s="35">
-        <f>'Nach Mannschaften sortiert'!E104</f>
+        <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="F73" s="2">
-        <f>'Nach Mannschaften sortiert'!F104</f>
+        <f>'Nach Mannschaften sortiert'!F105</f>
         <v>0</v>
       </c>
       <c r="G73" s="2">
-        <f>'Nach Mannschaften sortiert'!G104</f>
+        <f>'Nach Mannschaften sortiert'!G105</f>
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <f>'Nach Mannschaften sortiert'!H104</f>
+        <f>'Nach Mannschaften sortiert'!H105</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <f>'Nach Mannschaften sortiert'!A105</f>
-        <v>103</v>
+        <f>'Nach Mannschaften sortiert'!A106</f>
+        <v>105</v>
       </c>
       <c r="B74" s="2">
-        <f>'Nach Mannschaften sortiert'!B105</f>
+        <f>'Nach Mannschaften sortiert'!B106</f>
         <v>5</v>
       </c>
       <c r="C74" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C105</f>
+        <f>'Nach Mannschaften sortiert'!C106</f>
         <v>U8</v>
       </c>
       <c r="D74" s="13">
-        <f>'Nach Mannschaften sortiert'!D105</f>
+        <f>'Nach Mannschaften sortiert'!D106</f>
         <v>46092</v>
       </c>
       <c r="E74" s="35">
-        <f>'Nach Mannschaften sortiert'!E105</f>
+        <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="F74" s="2">
-        <f>'Nach Mannschaften sortiert'!F105</f>
+        <f>'Nach Mannschaften sortiert'!F106</f>
         <v>0</v>
       </c>
       <c r="G74" s="2">
-        <f>'Nach Mannschaften sortiert'!G105</f>
+        <f>'Nach Mannschaften sortiert'!G106</f>
         <v>0</v>
       </c>
       <c r="H74" s="2">
-        <f>'Nach Mannschaften sortiert'!H105</f>
+        <f>'Nach Mannschaften sortiert'!H106</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="57">
-        <f>'Nach Mannschaften sortiert'!A22</f>
-        <v>20</v>
+        <f>'Nach Mannschaften sortiert'!A23</f>
+        <v>22</v>
       </c>
       <c r="B75" s="57">
-        <f>'Nach Mannschaften sortiert'!B22</f>
+        <f>'Nach Mannschaften sortiert'!B23</f>
         <v>13</v>
       </c>
       <c r="C75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C22</f>
+        <f>'Nach Mannschaften sortiert'!C23</f>
         <v>KM</v>
       </c>
       <c r="D75" s="58">
-        <f>'Nach Mannschaften sortiert'!D22</f>
+        <f>'Nach Mannschaften sortiert'!D23</f>
         <v>46333</v>
       </c>
       <c r="E75" s="59">
-        <f>'Nach Mannschaften sortiert'!E22</f>
+        <f>'Nach Mannschaften sortiert'!E23</f>
         <v>0.6875</v>
       </c>
       <c r="F75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!F22</f>
+        <f>'Nach Mannschaften sortiert'!F23</f>
         <v>Neufeld</v>
       </c>
       <c r="G75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!G22</f>
+        <f>'Nach Mannschaften sortiert'!G23</f>
         <v>Andau</v>
       </c>
       <c r="H75" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!H22</f>
+        <f>'Nach Mannschaften sortiert'!H23</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <f>'Nach Mannschaften sortiert'!A107</f>
-        <v>105</v>
+        <f>'Nach Mannschaften sortiert'!A108</f>
+        <v>107</v>
       </c>
       <c r="B76" s="2">
-        <f>'Nach Mannschaften sortiert'!B107</f>
+        <f>'Nach Mannschaften sortiert'!B108</f>
         <v>2</v>
       </c>
       <c r="C76" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C107</f>
+        <f>'Nach Mannschaften sortiert'!C108</f>
         <v>U7</v>
       </c>
       <c r="D76" s="13">
-        <f>'Nach Mannschaften sortiert'!D107</f>
+        <f>'Nach Mannschaften sortiert'!D108</f>
         <v>46094</v>
       </c>
       <c r="E76" s="35">
-        <f>'Nach Mannschaften sortiert'!E107</f>
+        <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="F76" s="2">
-        <f>'Nach Mannschaften sortiert'!F107</f>
+        <f>'Nach Mannschaften sortiert'!F108</f>
         <v>0</v>
       </c>
       <c r="G76" s="2">
-        <f>'Nach Mannschaften sortiert'!G107</f>
+        <f>'Nach Mannschaften sortiert'!G108</f>
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <f>'Nach Mannschaften sortiert'!H107</f>
+        <f>'Nach Mannschaften sortiert'!H108</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <f>'Nach Mannschaften sortiert'!A108</f>
-        <v>106</v>
+        <f>'Nach Mannschaften sortiert'!A109</f>
+        <v>108</v>
       </c>
       <c r="B77" s="2">
-        <f>'Nach Mannschaften sortiert'!B108</f>
+        <f>'Nach Mannschaften sortiert'!B109</f>
         <v>3</v>
       </c>
       <c r="C77" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C108</f>
+        <f>'Nach Mannschaften sortiert'!C109</f>
         <v>U7</v>
       </c>
       <c r="D77" s="13">
-        <f>'Nach Mannschaften sortiert'!D108</f>
+        <f>'Nach Mannschaften sortiert'!D109</f>
         <v>46095</v>
       </c>
       <c r="E77" s="35">
-        <f>'Nach Mannschaften sortiert'!E108</f>
+        <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="F77" s="2">
-        <f>'Nach Mannschaften sortiert'!F108</f>
+        <f>'Nach Mannschaften sortiert'!F109</f>
         <v>0</v>
       </c>
       <c r="G77" s="2">
-        <f>'Nach Mannschaften sortiert'!G108</f>
+        <f>'Nach Mannschaften sortiert'!G109</f>
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <f>'Nach Mannschaften sortiert'!H108</f>
+        <f>'Nach Mannschaften sortiert'!H109</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <f>'Nach Mannschaften sortiert'!A109</f>
-        <v>107</v>
+        <f>'Nach Mannschaften sortiert'!A110</f>
+        <v>109</v>
       </c>
       <c r="B78" s="2">
-        <f>'Nach Mannschaften sortiert'!B109</f>
+        <f>'Nach Mannschaften sortiert'!B110</f>
         <v>4</v>
       </c>
       <c r="C78" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C109</f>
+        <f>'Nach Mannschaften sortiert'!C110</f>
         <v>U7</v>
       </c>
       <c r="D78" s="13">
-        <f>'Nach Mannschaften sortiert'!D109</f>
+        <f>'Nach Mannschaften sortiert'!D110</f>
         <v>46096</v>
       </c>
       <c r="E78" s="35">
-        <f>'Nach Mannschaften sortiert'!E109</f>
+        <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="F78" s="2">
-        <f>'Nach Mannschaften sortiert'!F109</f>
+        <f>'Nach Mannschaften sortiert'!F110</f>
         <v>0</v>
       </c>
       <c r="G78" s="2">
-        <f>'Nach Mannschaften sortiert'!G109</f>
+        <f>'Nach Mannschaften sortiert'!G110</f>
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <f>'Nach Mannschaften sortiert'!H109</f>
+        <f>'Nach Mannschaften sortiert'!H110</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <f>'Nach Mannschaften sortiert'!A110</f>
-        <v>108</v>
+        <f>'Nach Mannschaften sortiert'!A111</f>
+        <v>110</v>
       </c>
       <c r="B79" s="2">
-        <f>'Nach Mannschaften sortiert'!B110</f>
+        <f>'Nach Mannschaften sortiert'!B111</f>
         <v>5</v>
       </c>
       <c r="C79" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C110</f>
+        <f>'Nach Mannschaften sortiert'!C111</f>
         <v>U7</v>
       </c>
       <c r="D79" s="13">
-        <f>'Nach Mannschaften sortiert'!D110</f>
+        <f>'Nach Mannschaften sortiert'!D111</f>
         <v>46097</v>
       </c>
       <c r="E79" s="35">
-        <f>'Nach Mannschaften sortiert'!E110</f>
+        <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="F79" s="2">
-        <f>'Nach Mannschaften sortiert'!F110</f>
+        <f>'Nach Mannschaften sortiert'!F111</f>
         <v>0</v>
       </c>
       <c r="G79" s="2">
-        <f>'Nach Mannschaften sortiert'!G110</f>
+        <f>'Nach Mannschaften sortiert'!G111</f>
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <f>'Nach Mannschaften sortiert'!H110</f>
+        <f>'Nach Mannschaften sortiert'!H111</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="57">
-        <f>'Nach Mannschaften sortiert'!A63</f>
-        <v>61</v>
+        <f>'Nach Mannschaften sortiert'!A64</f>
+        <v>63</v>
       </c>
       <c r="B80" s="57">
-        <f>'Nach Mannschaften sortiert'!B63</f>
+        <f>'Nach Mannschaften sortiert'!B64</f>
         <v>8</v>
       </c>
       <c r="C80" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C63</f>
+        <f>'Nach Mannschaften sortiert'!C64</f>
         <v>U12_1</v>
       </c>
       <c r="D80" s="58">
-        <f>'Nach Mannschaften sortiert'!D63</f>
+        <f>'Nach Mannschaften sortiert'!D64</f>
         <v>46050</v>
       </c>
       <c r="E80" s="59">
-        <f>'Nach Mannschaften sortiert'!E63</f>
+        <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="F80" s="57">
-        <f>'Nach Mannschaften sortiert'!F63</f>
+        <f>'Nach Mannschaften sortiert'!F64</f>
         <v>0</v>
       </c>
       <c r="G80" s="57">
-        <f>'Nach Mannschaften sortiert'!G63</f>
+        <f>'Nach Mannschaften sortiert'!G64</f>
         <v>0</v>
       </c>
       <c r="H80" s="57">
-        <f>'Nach Mannschaften sortiert'!H63</f>
+        <f>'Nach Mannschaften sortiert'!H64</f>
         <v>0</v>
       </c>
     </row>
@@ -12968,35 +13041,35 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="57">
-        <f>'Nach Mannschaften sortiert'!A45</f>
-        <v>43</v>
+        <f>'Nach Mannschaften sortiert'!A46</f>
+        <v>45</v>
       </c>
       <c r="B82" s="57">
-        <f>'Nach Mannschaften sortiert'!B45</f>
+        <f>'Nach Mannschaften sortiert'!B46</f>
         <v>10</v>
       </c>
       <c r="C82" s="57" t="str">
-        <f>'Nach Mannschaften sortiert'!C45</f>
+        <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U16</v>
       </c>
       <c r="D82" s="58">
-        <f>'Nach Mannschaften sortiert'!D45</f>
+        <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46032</v>
       </c>
       <c r="E82" s="59">
-        <f>'Nach Mannschaften sortiert'!E45</f>
+        <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="F82" s="57">
-        <f>'Nach Mannschaften sortiert'!F45</f>
+        <f>'Nach Mannschaften sortiert'!F46</f>
         <v>0</v>
       </c>
       <c r="G82" s="57">
-        <f>'Nach Mannschaften sortiert'!G45</f>
+        <f>'Nach Mannschaften sortiert'!G46</f>
         <v>0</v>
       </c>
       <c r="H82" s="57">
-        <f>'Nach Mannschaften sortiert'!H45</f>
+        <f>'Nach Mannschaften sortiert'!H46</f>
         <v>0</v>
       </c>
     </row>
@@ -13036,35 +13109,35 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <f>'Nach Mannschaften sortiert'!A122</f>
-        <v>120</v>
+        <f>'Nach Mannschaften sortiert'!A123</f>
+        <v>122</v>
       </c>
       <c r="B84" s="2">
-        <f>'Nach Mannschaften sortiert'!B122</f>
+        <f>'Nach Mannschaften sortiert'!B123</f>
         <v>2</v>
       </c>
       <c r="C84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!C122</f>
+        <f>'Nach Mannschaften sortiert'!C123</f>
         <v>GGG</v>
       </c>
       <c r="D84" s="13">
-        <f>'Nach Mannschaften sortiert'!D122</f>
+        <f>'Nach Mannschaften sortiert'!D123</f>
         <v>46256</v>
       </c>
       <c r="E84" s="35">
-        <f>'Nach Mannschaften sortiert'!E122</f>
+        <f>'Nach Mannschaften sortiert'!E123</f>
         <v>0.375</v>
       </c>
       <c r="F84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!F122</f>
+        <f>'Nach Mannschaften sortiert'!F123</f>
         <v>Neufeld</v>
       </c>
       <c r="G84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!G122</f>
+        <f>'Nach Mannschaften sortiert'!G123</f>
         <v>viele Gegner</v>
       </c>
       <c r="H84" s="2" t="str">
-        <f>'Nach Mannschaften sortiert'!H122</f>
+        <f>'Nach Mannschaften sortiert'!H123</f>
         <v>Heim</v>
       </c>
     </row>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540CC439-C732-4B4D-AA46-FA13030FD358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFF76D6-E378-41BE-849D-4E9B4F0D5AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="175">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -570,6 +570,9 @@
   </si>
   <si>
     <t>inaktiv</t>
+  </si>
+  <si>
+    <t>Bad Erlach</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1072,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1333,6 +1336,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -1572,7 +1576,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="54" bestFit="1" customWidth="1"/>
@@ -1639,7 +1643,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f t="shared" ref="A3:A35" si="0">A2+1</f>
+        <f t="shared" ref="A3:A36" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="5">
@@ -1880,30 +1884,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+    <row r="12" spans="1:8" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="54">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="10">
-        <v>46250</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="D12" s="9">
+        <v>46445</v>
+      </c>
+      <c r="E12" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1913,22 +1917,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E13" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>15</v>
@@ -1940,25 +1944,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E14" s="3">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1967,25 +1971,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E15" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1994,25 +1998,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E16" s="3">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -2021,25 +2025,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E17" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -2048,25 +2052,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E18" s="3">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -2075,25 +2079,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="10">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="E19" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -2102,25 +2106,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="10">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="E20" s="3">
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2129,25 +2133,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E21" s="3">
         <v>0.8125</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -2156,25 +2160,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E22" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -2183,25 +2187,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E23" s="3">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -2210,25 +2214,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E24" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -2237,25 +2241,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D25" s="10">
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="E25" s="3">
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -2264,22 +2268,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E26" s="3">
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>15</v>
@@ -2291,25 +2295,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D27" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E27" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -2318,25 +2322,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E28" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -2345,25 +2349,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D29" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E29" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -2372,25 +2376,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D30" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E30" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2399,25 +2403,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E31" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -2426,391 +2430,398 @@
         <v>31</v>
       </c>
       <c r="B32" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D32" s="10">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="E32" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="10">
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="E33" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D34" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E34" s="3">
         <v>0.72916666666666663</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E35" s="3">
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H35" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="4">
         <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
-        <f t="shared" ref="A36:A67" si="1">A35+1</f>
-        <v>35</v>
-      </c>
-      <c r="B36" s="4">
-        <v>12</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D36" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E36" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A37:A68" si="1">A36+1</f>
         <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D37" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E37" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B38" s="21">
-        <v>1</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="28">
-        <v>46023</v>
-      </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="4">
+        <v>13</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="10">
+        <v>46333</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="21">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="B39" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D39" s="28">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="21">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="B40" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D40" s="28">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="21">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B41" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D41" s="28">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="21">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B42" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="28">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="21"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="21">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="B43" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="28">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="21"/>
       <c r="G43" s="21"/>
       <c r="H43" s="21"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="21">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="B44" s="21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="28">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="21"/>
       <c r="G44" s="21"/>
       <c r="H44" s="21"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="21">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="B45" s="21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="28">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21"/>
       <c r="H45" s="21"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="21">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B46" s="21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="28">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="21"/>
       <c r="G46" s="21"/>
       <c r="H46" s="21"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="21">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="B47" s="21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D47" s="28">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="21"/>
       <c r="G47" s="21"/>
       <c r="H47" s="21"/>
     </row>
-    <row r="48" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="18">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="21">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B48" s="13">
-        <v>1</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" s="14">
-        <v>46033</v>
-      </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="17"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B48" s="21">
+        <v>10</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="28">
+        <v>46032</v>
+      </c>
+      <c r="E48" s="22"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="18">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="B49" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D49" s="14">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
-      <c r="I49" s="16"/>
+      <c r="I49" s="17"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="18">
@@ -2818,13 +2829,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D50" s="14">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="13"/>
@@ -2838,13 +2849,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D51" s="14">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="13"/>
@@ -2858,13 +2869,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D52" s="14">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="13"/>
@@ -2878,13 +2889,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D53" s="14">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="13"/>
@@ -2898,13 +2909,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D54" s="14">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="13"/>
@@ -2918,13 +2929,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D55" s="14">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="13"/>
@@ -2938,13 +2949,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="14">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="13"/>
@@ -2958,13 +2969,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D57" s="14">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="13"/>
@@ -2973,23 +2984,24 @@
       <c r="I57" s="16"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="6">
+      <c r="A58" s="18">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="B58" s="6">
-        <v>1</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D58" s="23">
-        <v>46043</v>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
+      <c r="B58" s="13">
+        <v>10</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" s="14">
+        <v>46042</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="16"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
@@ -2997,13 +3009,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D59" s="23">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="6"/>
@@ -3016,13 +3028,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D60" s="23">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="6"/>
@@ -3035,13 +3047,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D61" s="23">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="6"/>
@@ -3054,13 +3066,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D62" s="23">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="6"/>
@@ -3073,13 +3085,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D63" s="23">
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="6"/>
@@ -3092,13 +3104,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D64" s="23">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="6"/>
@@ -3111,13 +3123,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D65" s="23">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="6"/>
@@ -3130,13 +3142,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D66" s="23">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="6"/>
@@ -3149,13 +3161,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D67" s="23">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="6"/>
@@ -3163,37 +3175,37 @@
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="90">
-        <f t="shared" ref="A68:A99" si="2">A67+1</f>
+      <c r="A68" s="6">
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="B68" s="90">
-        <v>1</v>
-      </c>
-      <c r="C68" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="D68" s="91">
-        <v>46053</v>
-      </c>
-      <c r="E68" s="92"/>
-      <c r="F68" s="90"/>
-      <c r="G68" s="90"/>
-      <c r="H68" s="90"/>
+      <c r="B68" s="6">
+        <v>10</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="23">
+        <v>46052</v>
+      </c>
+      <c r="E68" s="7"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A69:A100" si="2">A68+1</f>
         <v>68</v>
       </c>
       <c r="B69" s="90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D69" s="91">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="E69" s="92"/>
       <c r="F69" s="90"/>
@@ -3206,13 +3218,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D70" s="91">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="E70" s="92"/>
       <c r="F70" s="90"/>
@@ -3225,13 +3237,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="91">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="E71" s="92"/>
       <c r="F71" s="90"/>
@@ -3244,13 +3256,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D72" s="91">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="E72" s="92"/>
       <c r="F72" s="90"/>
@@ -3263,13 +3275,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D73" s="91">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="E73" s="92"/>
       <c r="F73" s="90"/>
@@ -3282,13 +3294,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="91">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="E74" s="92"/>
       <c r="F74" s="90"/>
@@ -3301,13 +3313,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="91">
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="E75" s="92"/>
       <c r="F75" s="90"/>
@@ -3320,13 +3332,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="90">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C76" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="91">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="E76" s="92"/>
       <c r="F76" s="90"/>
@@ -3339,13 +3351,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="90">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C77" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D77" s="91">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="E77" s="92"/>
       <c r="F77" s="90"/>
@@ -3353,23 +3365,23 @@
       <c r="H77" s="90"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="19">
+      <c r="A78" s="90">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="B78" s="19">
-        <v>1</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D78" s="24">
-        <v>46063</v>
-      </c>
-      <c r="E78" s="20"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
+      <c r="B78" s="90">
+        <v>10</v>
+      </c>
+      <c r="C78" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" s="91">
+        <v>46062</v>
+      </c>
+      <c r="E78" s="92"/>
+      <c r="F78" s="90"/>
+      <c r="G78" s="90"/>
+      <c r="H78" s="90"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="19">
@@ -3377,13 +3389,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D79" s="24">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="E79" s="20"/>
       <c r="F79" s="19"/>
@@ -3396,13 +3408,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D80" s="24">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="E80" s="20"/>
       <c r="F80" s="19"/>
@@ -3415,13 +3427,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D81" s="24">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="E81" s="20"/>
       <c r="F81" s="19"/>
@@ -3434,13 +3446,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D82" s="24">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="E82" s="20"/>
       <c r="F82" s="19"/>
@@ -3453,13 +3465,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D83" s="24">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="E83" s="20"/>
       <c r="F83" s="19"/>
@@ -3472,13 +3484,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D84" s="24">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="E84" s="20"/>
       <c r="F84" s="19"/>
@@ -3491,13 +3503,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D85" s="24">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="E85" s="20"/>
       <c r="F85" s="19"/>
@@ -3510,13 +3522,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C86" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D86" s="24">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E86" s="20"/>
       <c r="F86" s="19"/>
@@ -3529,13 +3541,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C87" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="24">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E87" s="20"/>
       <c r="F87" s="19"/>
@@ -3543,31 +3555,23 @@
       <c r="H87" s="19"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="87">
+      <c r="A88" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="B88" s="87">
-        <v>1</v>
-      </c>
-      <c r="C88" s="87" t="s">
-        <v>40</v>
-      </c>
-      <c r="D88" s="88">
-        <v>46312</v>
-      </c>
-      <c r="E88" s="89">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F88" s="89" t="s">
-        <v>19</v>
-      </c>
-      <c r="G88" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="H88" s="87" t="s">
-        <v>11</v>
-      </c>
+      <c r="B88" s="19">
+        <v>10</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D88" s="24">
+        <v>46072</v>
+      </c>
+      <c r="E88" s="20"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="19"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="87">
@@ -3575,18 +3579,26 @@
         <v>88</v>
       </c>
       <c r="B89" s="87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D89" s="88">
-        <v>46074</v>
-      </c>
-      <c r="E89" s="89"/>
-      <c r="F89" s="87"/>
-      <c r="G89" s="87"/>
-      <c r="H89" s="87"/>
+        <v>46312</v>
+      </c>
+      <c r="E89" s="89">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F89" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="H89" s="87" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="87">
@@ -3594,13 +3606,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D90" s="88">
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="E90" s="89"/>
       <c r="F90" s="87"/>
@@ -3613,13 +3625,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C91" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D91" s="88">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="E91" s="89"/>
       <c r="F91" s="87"/>
@@ -3632,13 +3644,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D92" s="88">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="E92" s="89"/>
       <c r="F92" s="87"/>
@@ -3646,23 +3658,23 @@
       <c r="H92" s="87"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="8">
+      <c r="A93" s="87">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="B93" s="8">
-        <v>1</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D93" s="29">
-        <v>46078</v>
-      </c>
-      <c r="E93" s="12"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
+      <c r="B93" s="87">
+        <v>5</v>
+      </c>
+      <c r="C93" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="D93" s="88">
+        <v>46077</v>
+      </c>
+      <c r="E93" s="89"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="87"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
@@ -3670,13 +3682,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D94" s="29">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="8"/>
@@ -3689,13 +3701,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D95" s="29">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="8"/>
@@ -3708,13 +3720,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D96" s="29">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="8"/>
@@ -3727,13 +3739,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D97" s="29">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="8"/>
@@ -3746,13 +3758,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D98" s="29">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="8"/>
@@ -3765,13 +3777,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D99" s="29">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="8"/>
@@ -3780,17 +3792,17 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
-        <f t="shared" ref="A100:A131" si="3">A99+1</f>
+        <f t="shared" si="2"/>
         <v>99</v>
       </c>
       <c r="B100" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D100" s="29">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="8"/>
@@ -3799,17 +3811,17 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A101:A132" si="3">A100+1</f>
         <v>100</v>
       </c>
       <c r="B101" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D101" s="29">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="8"/>
@@ -3822,13 +3834,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D102" s="29">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="8"/>
@@ -3836,31 +3848,23 @@
       <c r="H102" s="8"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="25">
+      <c r="A103" s="8">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="B103" s="25">
-        <v>1</v>
-      </c>
-      <c r="C103" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D103" s="26">
-        <v>46312</v>
-      </c>
-      <c r="E103" s="27">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F103" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="G103" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H103" s="25" t="s">
-        <v>11</v>
-      </c>
+      <c r="B103" s="8">
+        <v>10</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D103" s="29">
+        <v>46087</v>
+      </c>
+      <c r="E103" s="12"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="25">
@@ -3868,18 +3872,26 @@
         <v>103</v>
       </c>
       <c r="B104" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D104" s="26">
-        <v>46089</v>
-      </c>
-      <c r="E104" s="27"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="25"/>
-      <c r="H104" s="25"/>
+        <v>46312</v>
+      </c>
+      <c r="E104" s="27">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F104" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H104" s="25" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="25">
@@ -3887,13 +3899,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C105" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D105" s="26">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E105" s="27"/>
       <c r="F105" s="25"/>
@@ -3906,13 +3918,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C106" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D106" s="26">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="E106" s="27"/>
       <c r="F106" s="25"/>
@@ -3925,13 +3937,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D107" s="26">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E107" s="27"/>
       <c r="F107" s="25"/>
@@ -3939,23 +3951,23 @@
       <c r="H107" s="25"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="42">
+      <c r="A108" s="25">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
-      <c r="B108" s="42">
-        <v>1</v>
-      </c>
-      <c r="C108" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D108" s="43">
-        <v>46312</v>
-      </c>
-      <c r="E108" s="44"/>
-      <c r="F108" s="42"/>
-      <c r="G108" s="42"/>
-      <c r="H108" s="42"/>
+      <c r="B108" s="25">
+        <v>5</v>
+      </c>
+      <c r="C108" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D108" s="26">
+        <v>46092</v>
+      </c>
+      <c r="E108" s="27"/>
+      <c r="F108" s="25"/>
+      <c r="G108" s="25"/>
+      <c r="H108" s="25"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="42">
@@ -3963,13 +3975,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D109" s="43">
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="E109" s="44"/>
       <c r="F109" s="42"/>
@@ -3982,13 +3994,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C110" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D110" s="43">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="E110" s="44"/>
       <c r="F110" s="42"/>
@@ -4001,13 +4013,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C111" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D111" s="43">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="E111" s="44"/>
       <c r="F111" s="42"/>
@@ -4020,13 +4032,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C112" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D112" s="43">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="E112" s="44"/>
       <c r="F112" s="42"/>
@@ -4034,31 +4046,23 @@
       <c r="H112" s="42"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="30">
+      <c r="A113" s="42">
         <f t="shared" si="3"/>
         <v>112</v>
       </c>
-      <c r="B113" s="30">
-        <v>1</v>
-      </c>
-      <c r="C113" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D113" s="59">
-        <v>46230</v>
-      </c>
-      <c r="E113" s="82">
-        <v>0.375</v>
-      </c>
-      <c r="F113" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G113" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H113" s="31" t="s">
-        <v>11</v>
-      </c>
+      <c r="B113" s="42">
+        <v>5</v>
+      </c>
+      <c r="C113" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D113" s="43">
+        <v>46097</v>
+      </c>
+      <c r="E113" s="44"/>
+      <c r="F113" s="42"/>
+      <c r="G113" s="42"/>
+      <c r="H113" s="42"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="30">
@@ -4066,13 +4070,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D114" s="59">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="E114" s="82">
         <v>0.375</v>
@@ -4093,13 +4097,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C115" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D115" s="59">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="E115" s="82">
         <v>0.375</v>
@@ -4120,13 +4124,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C116" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D116" s="59">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E116" s="82">
         <v>0.375</v>
@@ -4147,13 +4151,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D117" s="59">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="E117" s="82">
         <v>0.375</v>
@@ -4174,13 +4178,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D118" s="59">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="E118" s="82">
         <v>0.375</v>
@@ -4189,7 +4193,7 @@
         <v>19</v>
       </c>
       <c r="G118" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H118" s="31" t="s">
         <v>11</v>
@@ -4201,13 +4205,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C119" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D119" s="59">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E119" s="82">
         <v>0.375</v>
@@ -4228,13 +4232,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D120" s="59">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E120" s="82">
         <v>0.375</v>
@@ -4255,13 +4259,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C121" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D121" s="59">
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="E121" s="82">
         <v>0.375</v>
@@ -4270,7 +4274,7 @@
         <v>19</v>
       </c>
       <c r="G121" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H121" s="31" t="s">
         <v>11</v>
@@ -4282,13 +4286,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C122" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D122" s="59">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="E122" s="82">
         <v>0.375</v>
@@ -4309,13 +4313,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C123" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D123" s="59">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E123" s="82">
         <v>0.375</v>
@@ -4331,56 +4335,56 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="40">
+      <c r="A124" s="30">
         <f t="shared" si="3"/>
         <v>123</v>
       </c>
-      <c r="B124" s="40">
-        <v>2</v>
-      </c>
-      <c r="C124" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D124" s="60">
-        <v>46256</v>
-      </c>
-      <c r="E124" s="83">
+      <c r="B124" s="30">
+        <v>11</v>
+      </c>
+      <c r="C124" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D124" s="59">
+        <v>46323</v>
+      </c>
+      <c r="E124" s="82">
         <v>0.375</v>
       </c>
-      <c r="F124" s="41" t="s">
+      <c r="F124" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G124" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H124" s="41" t="s">
+      <c r="G124" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H124" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="54">
+      <c r="A125" s="40">
         <f t="shared" si="3"/>
         <v>124</v>
       </c>
-      <c r="B125" s="54">
-        <v>1</v>
-      </c>
-      <c r="C125" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D125" s="55">
-        <v>46367</v>
-      </c>
-      <c r="E125" s="95">
-        <v>0.6875</v>
-      </c>
-      <c r="F125" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G125" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="H125" s="54" t="s">
+      <c r="B125" s="40">
+        <v>2</v>
+      </c>
+      <c r="C125" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D125" s="60">
+        <v>46256</v>
+      </c>
+      <c r="E125" s="83">
+        <v>0.375</v>
+      </c>
+      <c r="F125" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H125" s="41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4390,16 +4394,16 @@
         <v>125</v>
       </c>
       <c r="B126" s="54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D126" s="55">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="E126" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F126" s="54" t="s">
         <v>52</v>
@@ -4417,16 +4421,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C127" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D127" s="55">
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="E127" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F127" s="54" t="s">
         <v>52</v>
@@ -4444,22 +4448,22 @@
         <v>127</v>
       </c>
       <c r="B128" s="54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C128" s="54" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D128" s="55">
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="E128" s="95">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="F128" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G128" s="54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H128" s="54" t="s">
         <v>11</v>
@@ -4471,22 +4475,22 @@
         <v>128</v>
       </c>
       <c r="B129" s="54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C129" s="54" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D129" s="55">
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="E129" s="95">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F129" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G129" s="54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H129" s="54" t="s">
         <v>11</v>
@@ -4498,16 +4502,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D130" s="55">
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="E130" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F130" s="54" t="s">
         <v>52</v>
@@ -4525,16 +4529,16 @@
         <v>130</v>
       </c>
       <c r="B131" s="54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D131" s="55">
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="E131" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F131" s="54" t="s">
         <v>52</v>
@@ -4546,24 +4550,51 @@
         <v>11</v>
       </c>
     </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="54">
+        <f t="shared" si="3"/>
+        <v>131</v>
+      </c>
+      <c r="B132" s="54">
+        <v>6</v>
+      </c>
+      <c r="C132" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D132" s="55">
+        <v>46404</v>
+      </c>
+      <c r="E132" s="95">
+        <v>0.375</v>
+      </c>
+      <c r="F132" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="G132" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="H132" s="54" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H107" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H107">
-      <sortCondition ref="A1:A107"/>
+  <autoFilter ref="A1:H108" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H108">
+      <sortCondition ref="A1:A108"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="47" max="16383" man="1"/>
-    <brk id="57" max="16383" man="1"/>
+    <brk id="48" max="16383" man="1"/>
+    <brk id="58" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="84" customWidth="1"/>
@@ -4625,7 +4656,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="96">
-        <f t="shared" ref="D2:D34" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
+        <f t="shared" ref="D2:D35" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="E2" s="96" t="str">
@@ -5010,61 +5041,63 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="84"/>
       <c r="B12" s="81">
         <f>'Nach Mannschaften sortiert'!D12</f>
-        <v>46250</v>
+        <v>46445</v>
       </c>
       <c r="C12" s="96">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0.72916666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="96">
-        <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <f t="shared" ref="D12" si="2">IF(I12 = "KM",C12+"1:45",IF(I12="U23",C12+"1:45",IF(I12 = "U16",C12+"1:45",IF(I12 = "U15",C12+"1:30",IF(I12 = "U14",C12+"1:30",IF(I12 = "U13",C12+"1:35",IF(I12 = "U12",C12+"1:10",IF(I12 = "U11",C12+"1:10",IF(I12 = "U10",C12+"1:03",C12+"3:00")))))))))</f>
+        <v>0.57291666666666663</v>
       </c>
       <c r="E12" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
-        <v>KITTSEE</v>
-      </c>
-      <c r="G12" t="str">
+        <v>BAD ERLACH</v>
+      </c>
+      <c r="F12" s="84"/>
+      <c r="G12" s="111" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Auswärts</v>
       </c>
-      <c r="H12" t="str">
+      <c r="H12" s="111" t="str">
         <f>'Nach Mannschaften sortiert'!G12</f>
-        <v>Kittsee</v>
-      </c>
-      <c r="I12" t="str">
+        <v>Bad Erlach</v>
+      </c>
+      <c r="I12" s="111" t="str">
         <f>'Nach Mannschaften sortiert'!C12</f>
         <v>KM</v>
       </c>
       <c r="J12" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K12" t="s">
-        <v>73</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="K12" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="L12" s="111" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" s="81">
         <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C13" s="96">
         <f>'Nach Mannschaften sortiert'!E13</f>
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D13" s="96">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E13" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G13" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
@@ -5072,7 +5105,7 @@
       </c>
       <c r="H13" t="str">
         <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I13" t="str">
         <f>'Nach Mannschaften sortiert'!C13</f>
@@ -5091,27 +5124,27 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="81">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C14" s="96">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D14" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.90625</v>
       </c>
       <c r="E14" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G14" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H14" t="str">
         <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I14" t="str">
         <f>'Nach Mannschaften sortiert'!C14</f>
@@ -5130,27 +5163,27 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" s="81">
         <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C15" s="96">
         <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D15" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E15" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G15" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H15" t="str">
         <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I15" t="str">
         <f>'Nach Mannschaften sortiert'!C15</f>
@@ -5169,27 +5202,27 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" s="81">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C16" s="96">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="D16" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E16" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G16" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H16" t="str">
         <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I16" t="str">
         <f>'Nach Mannschaften sortiert'!C16</f>
@@ -5208,27 +5241,27 @@
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="81">
         <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C17" s="96">
         <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D17" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E17" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G17" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H17" t="str">
         <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I17" t="str">
         <f>'Nach Mannschaften sortiert'!C17</f>
@@ -5247,27 +5280,27 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="81">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C18" s="96">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D18" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E18" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G18" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H18" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I18" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
@@ -5286,27 +5319,27 @@
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="81">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C19" s="96">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D19" s="96">
         <f t="shared" si="0"/>
-        <v>0.86458333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E19" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G19" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H19" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I19" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
@@ -5325,27 +5358,27 @@
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="81">
         <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="C20" s="96">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D20" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E20" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G20" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H20" t="str">
         <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I20" t="str">
         <f>'Nach Mannschaften sortiert'!C20</f>
@@ -5364,7 +5397,7 @@
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="81">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C21" s="96">
         <f>'Nach Mannschaften sortiert'!E21</f>
@@ -5376,15 +5409,15 @@
       </c>
       <c r="E21" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G21" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H21" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I21" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
@@ -5403,27 +5436,27 @@
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="81">
         <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C22" s="96">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D22" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E22" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G22" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H22" t="str">
         <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I22" t="str">
         <f>'Nach Mannschaften sortiert'!C22</f>
@@ -5442,27 +5475,27 @@
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="81">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C23" s="96">
         <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D23" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E23" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G23" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H23" t="str">
         <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I23" t="str">
         <f>'Nach Mannschaften sortiert'!C23</f>
@@ -5481,27 +5514,27 @@
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="81">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C24" s="96">
         <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D24" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E24" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G24" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H24" t="str">
         <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I24" t="str">
         <f>'Nach Mannschaften sortiert'!C24</f>
@@ -5520,31 +5553,31 @@
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="81">
         <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="C25" s="96">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D25" s="96">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E25" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
-        <v>KITTSEE</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G25" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H25" t="str">
         <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Kittsee</v>
+        <v>Andau</v>
       </c>
       <c r="I25" t="str">
         <f>'Nach Mannschaften sortiert'!C25</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J25" s="84" t="s">
         <v>68</v>
@@ -5559,19 +5592,19 @@
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="81">
         <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C26" s="96">
         <f>'Nach Mannschaften sortiert'!E26</f>
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D26" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="E26" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G26" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
@@ -5579,7 +5612,7 @@
       </c>
       <c r="H26" t="str">
         <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I26" t="str">
         <f>'Nach Mannschaften sortiert'!C26</f>
@@ -5598,27 +5631,27 @@
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="81">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C27" s="96">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D27" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E27" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G27" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H27" t="str">
         <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I27" t="str">
         <f>'Nach Mannschaften sortiert'!C27</f>
@@ -5637,27 +5670,27 @@
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="81">
         <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C28" s="96">
         <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D28" s="96">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E28" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G28" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H28" t="str">
         <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I28" t="str">
         <f>'Nach Mannschaften sortiert'!C28</f>
@@ -5676,27 +5709,27 @@
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="81">
         <f>'Nach Mannschaften sortiert'!D29</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C29" s="96">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D29" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E29" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G29" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H29" t="str">
         <f>'Nach Mannschaften sortiert'!G29</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I29" t="str">
         <f>'Nach Mannschaften sortiert'!C29</f>
@@ -5715,27 +5748,27 @@
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="81">
         <f>'Nach Mannschaften sortiert'!D30</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C30" s="96">
         <f>'Nach Mannschaften sortiert'!E30</f>
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D30" s="96">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E30" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G30" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H30" t="str">
         <f>'Nach Mannschaften sortiert'!G30</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I30" t="str">
         <f>'Nach Mannschaften sortiert'!C30</f>
@@ -5754,27 +5787,27 @@
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="81">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C31" s="96">
         <f>'Nach Mannschaften sortiert'!E31</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D31" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.65625</v>
       </c>
       <c r="E31" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G31" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H31" t="str">
         <f>'Nach Mannschaften sortiert'!G31</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I31" t="str">
         <f>'Nach Mannschaften sortiert'!C31</f>
@@ -5793,27 +5826,27 @@
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="81">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C32" s="96">
         <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D32" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E32" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G32" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H32" t="str">
         <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
@@ -5832,27 +5865,27 @@
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="81">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="C33" s="96">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D33" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.78125</v>
       </c>
       <c r="E33" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G33" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H33" t="str">
         <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I33" t="str">
         <f>'Nach Mannschaften sortiert'!C33</f>
@@ -5871,7 +5904,7 @@
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="81">
         <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C34" s="96">
         <f>'Nach Mannschaften sortiert'!E34</f>
@@ -5883,15 +5916,15 @@
       </c>
       <c r="E34" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G34" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H34" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I34" t="str">
         <f>'Nach Mannschaften sortiert'!C34</f>
@@ -5910,27 +5943,27 @@
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="81">
         <f>'Nach Mannschaften sortiert'!D35</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C35" s="96">
         <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D35" s="96">
-        <f t="shared" ref="D35:D66" si="2">IF(I35 = "KM",C35+"1:45",IF(I35="U23",C35+"1:45",IF(I35 = "U16",C35+"1:45",IF(I35 = "U15",C35+"1:30",IF(I35 = "U14",C35+"1:30",IF(I35 = "U13",C35+"1:35",IF(I35 = "U12",C35+"1:10",IF(I35 = "U11",C35+"1:10",IF(I35 = "U10",C35+"1:03",C35+"3:00")))))))))</f>
-        <v>0.69791666666666663</v>
+        <f t="shared" si="0"/>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E35" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G35" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H35" t="str">
         <f>'Nach Mannschaften sortiert'!G35</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I35" t="str">
         <f>'Nach Mannschaften sortiert'!C35</f>
@@ -5949,27 +5982,27 @@
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="81">
         <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C36" s="96">
         <f>'Nach Mannschaften sortiert'!E36</f>
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D36" s="96">
-        <f t="shared" si="2"/>
-        <v>0.73958333333333326</v>
+        <f t="shared" ref="D36:D67" si="3">IF(I36 = "KM",C36+"1:45",IF(I36="U23",C36+"1:45",IF(I36 = "U16",C36+"1:45",IF(I36 = "U15",C36+"1:30",IF(I36 = "U14",C36+"1:30",IF(I36 = "U13",C36+"1:35",IF(I36 = "U12",C36+"1:10",IF(I36 = "U11",C36+"1:10",IF(I36 = "U10",C36+"1:03",C36+"3:00")))))))))</f>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E36" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G36" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H36" t="str">
         <f>'Nach Mannschaften sortiert'!G36</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I36" t="str">
         <f>'Nach Mannschaften sortiert'!C36</f>
@@ -5988,27 +6021,27 @@
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="81">
         <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C37" s="96">
         <f>'Nach Mannschaften sortiert'!E37</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D37" s="96">
-        <f t="shared" si="2"/>
-        <v>0.67708333333333326</v>
+        <f t="shared" si="3"/>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E37" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G37" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H37" t="str">
         <f>'Nach Mannschaften sortiert'!G37</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I37" t="str">
         <f>'Nach Mannschaften sortiert'!C37</f>
@@ -6027,31 +6060,31 @@
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="81">
         <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46023</v>
+        <v>46333</v>
       </c>
       <c r="C38" s="96">
         <f>'Nach Mannschaften sortiert'!E38</f>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D38" s="96">
-        <f t="shared" si="2"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E38" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
-        <v/>
-      </c>
-      <c r="G38">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G38" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
-        <v>0</v>
-      </c>
-      <c r="H38">
+        <v>Heim</v>
+      </c>
+      <c r="H38" t="str">
         <f>'Nach Mannschaften sortiert'!G38</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I38" t="str">
         <f>'Nach Mannschaften sortiert'!C38</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J38" s="84" t="s">
         <v>68</v>
@@ -6066,14 +6099,14 @@
     <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="81">
         <f>'Nach Mannschaften sortiert'!D39</f>
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C39" s="96">
         <f>'Nach Mannschaften sortiert'!E39</f>
         <v>0</v>
       </c>
       <c r="D39" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E39" s="96" t="str">
@@ -6105,14 +6138,14 @@
     <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="81">
         <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C40" s="96">
         <f>'Nach Mannschaften sortiert'!E40</f>
         <v>0</v>
       </c>
       <c r="D40" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E40" s="96" t="str">
@@ -6144,14 +6177,14 @@
     <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="81">
         <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C41" s="96">
         <f>'Nach Mannschaften sortiert'!E41</f>
         <v>0</v>
       </c>
       <c r="D41" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E41" s="96" t="str">
@@ -6183,14 +6216,14 @@
     <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="81">
         <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C42" s="96">
         <f>'Nach Mannschaften sortiert'!E42</f>
         <v>0</v>
       </c>
       <c r="D42" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E42" s="96" t="str">
@@ -6222,14 +6255,14 @@
     <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="81">
         <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C43" s="96">
         <f>'Nach Mannschaften sortiert'!E43</f>
         <v>0</v>
       </c>
       <c r="D43" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E43" s="96" t="str">
@@ -6261,14 +6294,14 @@
     <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="81">
         <f>'Nach Mannschaften sortiert'!D44</f>
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C44" s="96">
         <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="D44" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E44" s="96" t="str">
@@ -6300,14 +6333,14 @@
     <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="81">
         <f>'Nach Mannschaften sortiert'!D45</f>
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C45" s="96">
         <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="D45" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E45" s="96" t="str">
@@ -6339,14 +6372,14 @@
     <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="81">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C46" s="96">
         <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="D46" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E46" s="96" t="str">
@@ -6378,14 +6411,14 @@
     <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="81">
         <f>'Nach Mannschaften sortiert'!D47</f>
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C47" s="96">
         <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="D47" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E47" s="96" t="str">
@@ -6417,15 +6450,15 @@
     <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="81">
         <f>'Nach Mannschaften sortiert'!D48</f>
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C48" s="96">
         <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="D48" s="96">
-        <f t="shared" si="2"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="3"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E48" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F48)</f>
@@ -6441,7 +6474,7 @@
       </c>
       <c r="I48" t="str">
         <f>'Nach Mannschaften sortiert'!C48</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J48" s="84" t="s">
         <v>68</v>
@@ -6456,14 +6489,14 @@
     <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="81">
         <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C49" s="96">
         <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="D49" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E49" s="96" t="str">
@@ -6495,14 +6528,14 @@
     <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="81">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C50" s="96">
         <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="D50" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E50" s="96" t="str">
@@ -6534,14 +6567,14 @@
     <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="81">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C51" s="96">
         <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="D51" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E51" s="96" t="str">
@@ -6573,14 +6606,14 @@
     <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="81">
         <f>'Nach Mannschaften sortiert'!D52</f>
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="C52" s="96">
         <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="D52" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E52" s="96" t="str">
@@ -6612,14 +6645,14 @@
     <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="81">
         <f>'Nach Mannschaften sortiert'!D53</f>
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="C53" s="96">
         <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="D53" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E53" s="96" t="str">
@@ -6651,14 +6684,14 @@
     <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="81">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C54" s="96">
         <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="D54" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E54" s="96" t="str">
@@ -6690,14 +6723,14 @@
     <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="81">
         <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C55" s="96">
         <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
       <c r="D55" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E55" s="96" t="str">
@@ -6729,14 +6762,14 @@
     <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
         <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C56" s="96">
         <f>'Nach Mannschaften sortiert'!E56</f>
         <v>0</v>
       </c>
       <c r="D56" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E56" s="96" t="str">
@@ -6768,14 +6801,14 @@
     <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="81">
         <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C57" s="96">
         <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
       <c r="D57" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E57" s="96" t="str">
@@ -6807,15 +6840,15 @@
     <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="81">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C58" s="96">
         <f>'Nach Mannschaften sortiert'!E58</f>
         <v>0</v>
       </c>
       <c r="D58" s="96">
-        <f t="shared" si="2"/>
-        <v>0.125</v>
+        <f t="shared" si="3"/>
+        <v>6.25E-2</v>
       </c>
       <c r="E58" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F58)</f>
@@ -6831,7 +6864,7 @@
       </c>
       <c r="I58" t="str">
         <f>'Nach Mannschaften sortiert'!C58</f>
-        <v>U12_1</v>
+        <v>U14</v>
       </c>
       <c r="J58" s="84" t="s">
         <v>68</v>
@@ -6846,14 +6879,14 @@
     <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="81">
         <f>'Nach Mannschaften sortiert'!D59</f>
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C59" s="96">
         <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="D59" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E59" s="96" t="str">
@@ -6885,14 +6918,14 @@
     <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="81">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C60" s="96">
         <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="D60" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E60" s="96" t="str">
@@ -6924,14 +6957,14 @@
     <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="81">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C61" s="96">
         <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="D61" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E61" s="96" t="str">
@@ -6963,14 +6996,14 @@
     <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="81">
         <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C62" s="96">
         <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="D62" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E62" s="96" t="str">
@@ -7002,14 +7035,14 @@
     <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="81">
         <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="C63" s="96">
         <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="D63" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E63" s="96" t="str">
@@ -7041,14 +7074,14 @@
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="81">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="C64" s="96">
         <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="D64" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E64" s="96" t="str">
@@ -7080,14 +7113,14 @@
     <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="81">
         <f>'Nach Mannschaften sortiert'!D65</f>
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C65" s="96">
         <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="D65" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E65" s="96" t="str">
@@ -7119,14 +7152,14 @@
     <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="81">
         <f>'Nach Mannschaften sortiert'!D66</f>
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C66" s="96">
         <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="D66" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E66" s="96" t="str">
@@ -7158,14 +7191,14 @@
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="81">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="C67" s="96">
         <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="D67" s="96">
-        <f t="shared" ref="D67:D87" si="3">IF(I67 = "KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67 = "U16",C67+"1:45",IF(I67 = "U15",C67+"1:30",IF(I67 = "U14",C67+"1:30",IF(I67 = "U13",C67+"1:35",IF(I67 = "U12",C67+"1:10",IF(I67 = "U11",C67+"1:10",IF(I67 = "U10",C67+"1:03",C67+"3:00")))))))))</f>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E67" s="96" t="str">
@@ -7197,14 +7230,14 @@
     <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="81">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C68" s="96">
         <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="D68" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D68:D88" si="4">IF(I68 = "KM",C68+"1:45",IF(I68="U23",C68+"1:45",IF(I68 = "U16",C68+"1:45",IF(I68 = "U15",C68+"1:30",IF(I68 = "U14",C68+"1:30",IF(I68 = "U13",C68+"1:35",IF(I68 = "U12",C68+"1:10",IF(I68 = "U11",C68+"1:10",IF(I68 = "U10",C68+"1:03",C68+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E68" s="96" t="str">
@@ -7221,7 +7254,7 @@
       </c>
       <c r="I68" t="str">
         <f>'Nach Mannschaften sortiert'!C68</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J68" s="84" t="s">
         <v>68</v>
@@ -7236,14 +7269,14 @@
     <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="81">
         <f>'Nach Mannschaften sortiert'!D69</f>
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="C69" s="96">
         <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="D69" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E69" s="96" t="str">
@@ -7275,14 +7308,14 @@
     <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="81">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C70" s="96">
         <f>'Nach Mannschaften sortiert'!E70</f>
         <v>0</v>
       </c>
       <c r="D70" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E70" s="96" t="str">
@@ -7314,14 +7347,14 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="81">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C71" s="96">
         <f>'Nach Mannschaften sortiert'!E71</f>
         <v>0</v>
       </c>
       <c r="D71" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E71" s="96" t="str">
@@ -7353,14 +7386,14 @@
     <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="81">
         <f>'Nach Mannschaften sortiert'!D72</f>
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="C72" s="96">
         <f>'Nach Mannschaften sortiert'!E72</f>
         <v>0</v>
       </c>
       <c r="D72" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E72" s="96" t="str">
@@ -7392,14 +7425,14 @@
     <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="81">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C73" s="96">
         <f>'Nach Mannschaften sortiert'!E73</f>
         <v>0</v>
       </c>
       <c r="D73" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E73" s="96" t="str">
@@ -7431,14 +7464,14 @@
     <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="81">
         <f>'Nach Mannschaften sortiert'!D74</f>
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="C74" s="96">
         <f>'Nach Mannschaften sortiert'!E74</f>
         <v>0</v>
       </c>
       <c r="D74" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E74" s="96" t="str">
@@ -7470,14 +7503,14 @@
     <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="81">
         <f>'Nach Mannschaften sortiert'!D75</f>
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="C75" s="96">
         <f>'Nach Mannschaften sortiert'!E75</f>
         <v>0</v>
       </c>
       <c r="D75" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E75" s="96" t="str">
@@ -7509,14 +7542,14 @@
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="81">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C76" s="96">
         <f>'Nach Mannschaften sortiert'!E76</f>
         <v>0</v>
       </c>
       <c r="D76" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E76" s="96" t="str">
@@ -7548,14 +7581,14 @@
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="81">
         <f>'Nach Mannschaften sortiert'!D77</f>
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C77" s="96">
         <f>'Nach Mannschaften sortiert'!E77</f>
         <v>0</v>
       </c>
       <c r="D77" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E77" s="96" t="str">
@@ -7587,15 +7620,15 @@
     <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="81">
         <f>'Nach Mannschaften sortiert'!D78</f>
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="C78" s="96">
         <f>'Nach Mannschaften sortiert'!E78</f>
         <v>0</v>
       </c>
       <c r="D78" s="96">
-        <f t="shared" si="3"/>
-        <v>4.8611111111111112E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.125</v>
       </c>
       <c r="E78" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F78)</f>
@@ -7611,7 +7644,7 @@
       </c>
       <c r="I78" t="str">
         <f>'Nach Mannschaften sortiert'!C78</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J78" s="84" t="s">
         <v>68</v>
@@ -7626,14 +7659,14 @@
     <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="81">
         <f>'Nach Mannschaften sortiert'!D79</f>
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C79" s="96">
         <f>'Nach Mannschaften sortiert'!E79</f>
         <v>0</v>
       </c>
       <c r="D79" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E79" s="96" t="str">
@@ -7665,14 +7698,14 @@
     <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="81">
         <f>'Nach Mannschaften sortiert'!D80</f>
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C80" s="96">
         <f>'Nach Mannschaften sortiert'!E80</f>
         <v>0</v>
       </c>
       <c r="D80" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E80" s="96" t="str">
@@ -7704,14 +7737,14 @@
     <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="81">
         <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C81" s="96">
         <f>'Nach Mannschaften sortiert'!E81</f>
         <v>0</v>
       </c>
       <c r="D81" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E81" s="96" t="str">
@@ -7743,14 +7776,14 @@
     <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="81">
         <f>'Nach Mannschaften sortiert'!D82</f>
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="C82" s="96">
         <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="D82" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E82" s="96" t="str">
@@ -7782,14 +7815,14 @@
     <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="81">
         <f>'Nach Mannschaften sortiert'!D83</f>
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="C83" s="96">
         <f>'Nach Mannschaften sortiert'!E83</f>
         <v>0</v>
       </c>
       <c r="D83" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E83" s="96" t="str">
@@ -7821,14 +7854,14 @@
     <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="81">
         <f>'Nach Mannschaften sortiert'!D84</f>
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="C84" s="96">
         <f>'Nach Mannschaften sortiert'!E84</f>
         <v>0</v>
       </c>
       <c r="D84" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E84" s="96" t="str">
@@ -7860,14 +7893,14 @@
     <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="81">
         <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="C85" s="96">
         <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="D85" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E85" s="96" t="str">
@@ -7899,14 +7932,14 @@
     <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="81">
         <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="C86" s="96">
         <f>'Nach Mannschaften sortiert'!E86</f>
         <v>0</v>
       </c>
       <c r="D86" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E86" s="96" t="str">
@@ -7938,14 +7971,14 @@
     <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="81">
         <f>'Nach Mannschaften sortiert'!D87</f>
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C87" s="96">
         <f>'Nach Mannschaften sortiert'!E87</f>
         <v>0</v>
       </c>
       <c r="D87" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E87" s="96" t="str">
@@ -7977,30 +8010,31 @@
     <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="81">
         <f>'Nach Mannschaften sortiert'!D88</f>
-        <v>46312</v>
+        <v>46072</v>
       </c>
       <c r="C88" s="96">
         <f>'Nach Mannschaften sortiert'!E88</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D88" s="96">
-        <v>0.5</v>
+        <f t="shared" si="4"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E88" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F88)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="G88">
         <f>'Nach Mannschaften sortiert'!H88</f>
-        <v>Heim</v>
-      </c>
-      <c r="H88" t="str">
+        <v>0</v>
+      </c>
+      <c r="H88">
         <f>'Nach Mannschaften sortiert'!G88</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
         <f>'Nach Mannschaften sortiert'!C88</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J88" s="84" t="s">
         <v>68</v>
@@ -8015,27 +8049,26 @@
     <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="81">
         <f>'Nach Mannschaften sortiert'!D89</f>
-        <v>46074</v>
+        <v>46312</v>
       </c>
       <c r="C89" s="96">
         <f>'Nach Mannschaften sortiert'!E89</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D89" s="96">
-        <f t="shared" ref="D89:D102" si="4">IF(I89 = "KM",C89+"1:45",IF(I89="U23",C89+"1:45",IF(I89 = "U16",C89+"1:45",IF(I89 = "U15",C89+"1:30",IF(I89 = "U14",C89+"1:30",IF(I89 = "U13",C89+"1:35",IF(I89 = "U12",C89+"1:10",IF(I89 = "U11",C89+"1:10",IF(I89 = "U10",C89+"1:03",C89+"3:00")))))))))</f>
-        <v>4.3750000000000004E-2</v>
+        <v>0.5</v>
       </c>
       <c r="E89" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F89)</f>
-        <v/>
-      </c>
-      <c r="G89">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G89" t="str">
         <f>'Nach Mannschaften sortiert'!H89</f>
-        <v>0</v>
-      </c>
-      <c r="H89">
+        <v>Heim</v>
+      </c>
+      <c r="H89" t="str">
         <f>'Nach Mannschaften sortiert'!G89</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I89" t="str">
         <f>'Nach Mannschaften sortiert'!C89</f>
@@ -8054,14 +8087,14 @@
     <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="81">
         <f>'Nach Mannschaften sortiert'!D90</f>
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="C90" s="96">
         <f>'Nach Mannschaften sortiert'!E90</f>
         <v>0</v>
       </c>
       <c r="D90" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D90:D103" si="5">IF(I90 = "KM",C90+"1:45",IF(I90="U23",C90+"1:45",IF(I90 = "U16",C90+"1:45",IF(I90 = "U15",C90+"1:30",IF(I90 = "U14",C90+"1:30",IF(I90 = "U13",C90+"1:35",IF(I90 = "U12",C90+"1:10",IF(I90 = "U11",C90+"1:10",IF(I90 = "U10",C90+"1:03",C90+"3:00")))))))))</f>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E90" s="96" t="str">
@@ -8093,14 +8126,14 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="81">
         <f>'Nach Mannschaften sortiert'!D91</f>
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="C91" s="96">
         <f>'Nach Mannschaften sortiert'!E91</f>
         <v>0</v>
       </c>
       <c r="D91" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E91" s="96" t="str">
@@ -8132,14 +8165,14 @@
     <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="81">
         <f>'Nach Mannschaften sortiert'!D92</f>
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C92" s="96">
         <f>'Nach Mannschaften sortiert'!E92</f>
         <v>0</v>
       </c>
       <c r="D92" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E92" s="96" t="str">
@@ -8171,15 +8204,15 @@
     <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="81">
         <f>'Nach Mannschaften sortiert'!D93</f>
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C93" s="96">
         <f>'Nach Mannschaften sortiert'!E93</f>
         <v>0</v>
       </c>
       <c r="D93" s="96">
-        <f t="shared" si="4"/>
-        <v>0.125</v>
+        <f t="shared" si="5"/>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E93" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F93)</f>
@@ -8195,7 +8228,7 @@
       </c>
       <c r="I93" t="str">
         <f>'Nach Mannschaften sortiert'!C93</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J93" s="84" t="s">
         <v>68</v>
@@ -8210,14 +8243,14 @@
     <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="81">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="C94" s="96">
         <f>'Nach Mannschaften sortiert'!E94</f>
         <v>0</v>
       </c>
       <c r="D94" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E94" s="96" t="str">
@@ -8249,14 +8282,14 @@
     <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95" s="81">
         <f>'Nach Mannschaften sortiert'!D95</f>
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C95" s="96">
         <f>'Nach Mannschaften sortiert'!E95</f>
         <v>0</v>
       </c>
       <c r="D95" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E95" s="96" t="str">
@@ -8288,14 +8321,14 @@
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="81">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C96" s="96">
         <f>'Nach Mannschaften sortiert'!E96</f>
         <v>0</v>
       </c>
       <c r="D96" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E96" s="96" t="str">
@@ -8327,14 +8360,14 @@
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="81">
         <f>'Nach Mannschaften sortiert'!D97</f>
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C97" s="96">
         <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="D97" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E97" s="96" t="str">
@@ -8366,14 +8399,14 @@
     <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B98" s="81">
         <f>'Nach Mannschaften sortiert'!D98</f>
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C98" s="96">
         <f>'Nach Mannschaften sortiert'!E98</f>
         <v>0</v>
       </c>
       <c r="D98" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E98" s="96" t="str">
@@ -8405,14 +8438,14 @@
     <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B99" s="81">
         <f>'Nach Mannschaften sortiert'!D99</f>
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C99" s="96">
         <f>'Nach Mannschaften sortiert'!E99</f>
         <v>0</v>
       </c>
       <c r="D99" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E99" s="96" t="str">
@@ -8444,14 +8477,14 @@
     <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100" s="81">
         <f>'Nach Mannschaften sortiert'!D100</f>
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C100" s="96">
         <f>'Nach Mannschaften sortiert'!E100</f>
         <v>0</v>
       </c>
       <c r="D100" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E100" s="96" t="str">
@@ -8483,14 +8516,14 @@
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101" s="81">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C101" s="96">
         <f>'Nach Mannschaften sortiert'!E101</f>
         <v>0</v>
       </c>
       <c r="D101" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E101" s="96" t="str">
@@ -8522,14 +8555,14 @@
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102" s="81">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="C102" s="96">
         <f>'Nach Mannschaften sortiert'!E102</f>
         <v>0</v>
       </c>
       <c r="D102" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E102" s="96" t="str">
@@ -8561,30 +8594,31 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="81">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46312</v>
+        <v>46087</v>
       </c>
       <c r="C103" s="96">
         <f>'Nach Mannschaften sortiert'!E103</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D103" s="96">
-        <v>0.5</v>
+        <f t="shared" si="5"/>
+        <v>0.125</v>
       </c>
       <c r="E103" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F103)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="G103">
         <f>'Nach Mannschaften sortiert'!H103</f>
-        <v>Heim</v>
-      </c>
-      <c r="H103" t="str">
+        <v>0</v>
+      </c>
+      <c r="H103">
         <f>'Nach Mannschaften sortiert'!G103</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I103" t="str">
         <f>'Nach Mannschaften sortiert'!C103</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J103" s="84" t="s">
         <v>68</v>
@@ -8599,27 +8633,26 @@
     <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B104" s="81">
         <f>'Nach Mannschaften sortiert'!D104</f>
-        <v>46089</v>
+        <v>46312</v>
       </c>
       <c r="C104" s="96">
         <f>'Nach Mannschaften sortiert'!E104</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D104" s="96">
-        <f t="shared" ref="D104:D124" si="5">IF(I104 = "KM",C104+"1:45",IF(I104="U23",C104+"1:45",IF(I104 = "U16",C104+"1:45",IF(I104 = "U15",C104+"1:30",IF(I104 = "U14",C104+"1:30",IF(I104 = "U13",C104+"1:35",IF(I104 = "U12",C104+"1:10",IF(I104 = "U11",C104+"1:10",IF(I104 = "U10",C104+"1:03",C104+"3:00")))))))))</f>
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E104" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F104)</f>
-        <v/>
-      </c>
-      <c r="G104">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G104" t="str">
         <f>'Nach Mannschaften sortiert'!H104</f>
-        <v>0</v>
-      </c>
-      <c r="H104">
+        <v>Heim</v>
+      </c>
+      <c r="H104" t="str">
         <f>'Nach Mannschaften sortiert'!G104</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I104" t="str">
         <f>'Nach Mannschaften sortiert'!C104</f>
@@ -8638,14 +8671,14 @@
     <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105" s="81">
         <f>'Nach Mannschaften sortiert'!D105</f>
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="C105" s="96">
         <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="D105" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="D105:D125" si="6">IF(I105 = "KM",C105+"1:45",IF(I105="U23",C105+"1:45",IF(I105 = "U16",C105+"1:45",IF(I105 = "U15",C105+"1:30",IF(I105 = "U14",C105+"1:30",IF(I105 = "U13",C105+"1:35",IF(I105 = "U12",C105+"1:10",IF(I105 = "U11",C105+"1:10",IF(I105 = "U10",C105+"1:03",C105+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E105" s="96" t="str">
@@ -8677,14 +8710,14 @@
     <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106" s="81">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C106" s="96">
         <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="D106" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E106" s="96" t="str">
@@ -8716,14 +8749,14 @@
     <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B107" s="81">
         <f>'Nach Mannschaften sortiert'!D107</f>
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C107" s="96">
         <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="D107" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E107" s="96" t="str">
@@ -8755,14 +8788,14 @@
     <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B108" s="81">
         <f>'Nach Mannschaften sortiert'!D108</f>
-        <v>46312</v>
+        <v>46092</v>
       </c>
       <c r="C108" s="96">
         <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="D108" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E108" s="96" t="str">
@@ -8779,7 +8812,7 @@
       </c>
       <c r="I108" t="str">
         <f>'Nach Mannschaften sortiert'!C108</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J108" s="84" t="s">
         <v>68</v>
@@ -8794,14 +8827,14 @@
     <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109" s="81">
         <f>'Nach Mannschaften sortiert'!D109</f>
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="C109" s="96">
         <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="D109" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E109" s="96" t="str">
@@ -8833,14 +8866,14 @@
     <row r="110" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B110" s="81">
         <f>'Nach Mannschaften sortiert'!D110</f>
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="C110" s="96">
         <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="D110" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E110" s="96" t="str">
@@ -8872,14 +8905,14 @@
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="81">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="C111" s="96">
         <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="D111" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E111" s="96" t="str">
@@ -8911,14 +8944,14 @@
     <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112" s="81">
         <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="C112" s="96">
         <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="D112" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E112" s="96" t="str">
@@ -8950,31 +8983,31 @@
     <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113" s="81">
         <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46230</v>
+        <v>46097</v>
       </c>
       <c r="C113" s="96">
         <f>'Nach Mannschaften sortiert'!E113</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D113" s="96">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>0.125</v>
       </c>
       <c r="E113" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F113)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="G113">
         <f>'Nach Mannschaften sortiert'!H113</f>
-        <v>Heim</v>
-      </c>
-      <c r="H113" t="str">
+        <v>0</v>
+      </c>
+      <c r="H113">
         <f>'Nach Mannschaften sortiert'!G113</f>
-        <v>REAL MADRID CAMP</v>
+        <v>0</v>
       </c>
       <c r="I113" t="str">
         <f>'Nach Mannschaften sortiert'!C113</f>
-        <v>Camp</v>
+        <v>U7</v>
       </c>
       <c r="J113" s="84" t="s">
         <v>68</v>
@@ -8989,14 +9022,14 @@
     <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114" s="81">
         <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C114" s="96">
         <f>'Nach Mannschaften sortiert'!E114</f>
         <v>0.375</v>
       </c>
       <c r="D114" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E114" s="96" t="str">
@@ -9028,14 +9061,14 @@
     <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115" s="81">
         <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C115" s="96">
         <f>'Nach Mannschaften sortiert'!E115</f>
         <v>0.375</v>
       </c>
       <c r="D115" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E115" s="96" t="str">
@@ -9067,14 +9100,14 @@
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116" s="81">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C116" s="96">
         <f>'Nach Mannschaften sortiert'!E116</f>
         <v>0.375</v>
       </c>
       <c r="D116" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E116" s="96" t="str">
@@ -9106,14 +9139,14 @@
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117" s="81">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="C117" s="96">
         <f>'Nach Mannschaften sortiert'!E117</f>
         <v>0.375</v>
       </c>
       <c r="D117" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E117" s="96" t="str">
@@ -9145,14 +9178,14 @@
     <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B118" s="81">
         <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="C118" s="96">
         <f>'Nach Mannschaften sortiert'!E118</f>
         <v>0.375</v>
       </c>
       <c r="D118" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E118" s="96" t="str">
@@ -9165,7 +9198,7 @@
       </c>
       <c r="H118" t="str">
         <f>'Nach Mannschaften sortiert'!G118</f>
-        <v>MÄDCHENCAMP</v>
+        <v>REAL MADRID CAMP</v>
       </c>
       <c r="I118" t="str">
         <f>'Nach Mannschaften sortiert'!C118</f>
@@ -9184,14 +9217,14 @@
     <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B119" s="81">
         <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C119" s="96">
         <f>'Nach Mannschaften sortiert'!E119</f>
         <v>0.375</v>
       </c>
       <c r="D119" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E119" s="96" t="str">
@@ -9223,14 +9256,14 @@
     <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B120" s="81">
         <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="C120" s="96">
         <f>'Nach Mannschaften sortiert'!E120</f>
         <v>0.375</v>
       </c>
       <c r="D120" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E120" s="96" t="str">
@@ -9262,14 +9295,14 @@
     <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B121" s="81">
         <f>'Nach Mannschaften sortiert'!D121</f>
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="C121" s="96">
         <f>'Nach Mannschaften sortiert'!E121</f>
         <v>0.375</v>
       </c>
       <c r="D121" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E121" s="96" t="str">
@@ -9282,7 +9315,7 @@
       </c>
       <c r="H121" t="str">
         <f>'Nach Mannschaften sortiert'!G121</f>
-        <v>Teco 7 Camp</v>
+        <v>MÄDCHENCAMP</v>
       </c>
       <c r="I121" t="str">
         <f>'Nach Mannschaften sortiert'!C121</f>
@@ -9301,14 +9334,14 @@
     <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B122" s="81">
         <f>'Nach Mannschaften sortiert'!D122</f>
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C122" s="96">
         <f>'Nach Mannschaften sortiert'!E122</f>
         <v>0.375</v>
       </c>
       <c r="D122" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E122" s="96" t="str">
@@ -9340,14 +9373,14 @@
     <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B123" s="81">
         <f>'Nach Mannschaften sortiert'!D123</f>
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C123" s="96">
         <f>'Nach Mannschaften sortiert'!E123</f>
         <v>0.375</v>
       </c>
       <c r="D123" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E123" s="96" t="str">
@@ -9379,14 +9412,14 @@
     <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B124" s="81">
         <f>'Nach Mannschaften sortiert'!D124</f>
-        <v>46256</v>
+        <v>46323</v>
       </c>
       <c r="C124" s="96">
         <f>'Nach Mannschaften sortiert'!E124</f>
         <v>0.375</v>
       </c>
       <c r="D124" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E124" s="96" t="str">
@@ -9399,11 +9432,11 @@
       </c>
       <c r="H124" t="str">
         <f>'Nach Mannschaften sortiert'!G124</f>
-        <v>viele Gegner</v>
+        <v>Teco 7 Camp</v>
       </c>
       <c r="I124" t="str">
         <f>'Nach Mannschaften sortiert'!C124</f>
-        <v>GGG</v>
+        <v>Camp</v>
       </c>
       <c r="J124" s="84" t="s">
         <v>68</v>
@@ -9418,18 +9451,19 @@
     <row r="125" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B125" s="81">
         <f>'Nach Mannschaften sortiert'!D125</f>
-        <v>46367</v>
+        <v>46256</v>
       </c>
       <c r="C125" s="96">
         <f>'Nach Mannschaften sortiert'!E125</f>
-        <v>0.6875</v>
+        <v>0.375</v>
       </c>
       <c r="D125" s="96">
-        <v>0.875</v>
+        <f t="shared" si="6"/>
+        <v>0.5</v>
       </c>
       <c r="E125" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F125)</f>
-        <v>STEINBRUNN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G125" t="str">
         <f>'Nach Mannschaften sortiert'!H125</f>
@@ -9437,11 +9471,11 @@
       </c>
       <c r="H125" t="str">
         <f>'Nach Mannschaften sortiert'!G125</f>
-        <v>Hallencup 2026_27</v>
+        <v>viele Gegner</v>
       </c>
       <c r="I125" t="str">
         <f>'Nach Mannschaften sortiert'!C125</f>
-        <v>Hallenturnie</v>
+        <v>GGG</v>
       </c>
       <c r="J125" s="84" t="s">
         <v>68</v>
@@ -9456,11 +9490,11 @@
     <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B126" s="81">
         <f>'Nach Mannschaften sortiert'!D126</f>
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="C126" s="96">
         <f>'Nach Mannschaften sortiert'!E126</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D126" s="96">
         <v>0.875</v>
@@ -9494,11 +9528,11 @@
     <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B127" s="81">
         <f>'Nach Mannschaften sortiert'!D127</f>
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="C127" s="96">
         <f>'Nach Mannschaften sortiert'!E127</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D127" s="96">
         <v>0.875</v>
@@ -9532,11 +9566,11 @@
     <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B128" s="81">
         <f>'Nach Mannschaften sortiert'!D128</f>
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="C128" s="96">
         <f>'Nach Mannschaften sortiert'!E128</f>
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D128" s="96">
         <v>0.875</v>
@@ -9545,20 +9579,17 @@
         <f>UPPER('Nach Mannschaften sortiert'!F128)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="F128" s="84" t="s">
-        <v>74</v>
-      </c>
       <c r="G128" t="str">
         <f>'Nach Mannschaften sortiert'!H128</f>
         <v>Heim</v>
       </c>
       <c r="H128" t="str">
         <f>'Nach Mannschaften sortiert'!G128</f>
-        <v>Weihnachtsfeier 2026</v>
+        <v>Hallencup 2026_27</v>
       </c>
       <c r="I128" t="str">
         <f>'Nach Mannschaften sortiert'!C128</f>
-        <v>Weihnachtsfeier</v>
+        <v>Hallenturnie</v>
       </c>
       <c r="J128" s="84" t="s">
         <v>68</v>
@@ -9567,17 +9598,17 @@
         <v>73</v>
       </c>
       <c r="L128" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B129" s="81">
         <f>'Nach Mannschaften sortiert'!D129</f>
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="C129" s="96">
         <f>'Nach Mannschaften sortiert'!E129</f>
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D129" s="96">
         <v>0.875</v>
@@ -9586,17 +9617,20 @@
         <f>UPPER('Nach Mannschaften sortiert'!F129)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F129" s="84" t="s">
+        <v>74</v>
+      </c>
       <c r="G129" t="str">
         <f>'Nach Mannschaften sortiert'!H129</f>
         <v>Heim</v>
       </c>
       <c r="H129" t="str">
         <f>'Nach Mannschaften sortiert'!G129</f>
-        <v>Hallencup 2026_27</v>
+        <v>Weihnachtsfeier 2026</v>
       </c>
       <c r="I129" t="str">
         <f>'Nach Mannschaften sortiert'!C129</f>
-        <v>Hallenturnie</v>
+        <v>Weihnachtsfeier</v>
       </c>
       <c r="J129" s="84" t="s">
         <v>68</v>
@@ -9605,17 +9639,17 @@
         <v>73</v>
       </c>
       <c r="L129" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B130" s="81">
         <f>'Nach Mannschaften sortiert'!D130</f>
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="C130" s="96">
         <f>'Nach Mannschaften sortiert'!E130</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D130" s="96">
         <v>0.875</v>
@@ -9649,11 +9683,11 @@
     <row r="131" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B131" s="81">
         <f>'Nach Mannschaften sortiert'!D131</f>
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="C131" s="96">
         <f>'Nach Mannschaften sortiert'!E131</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D131" s="96">
         <v>0.875</v>
@@ -9681,6 +9715,44 @@
         <v>73</v>
       </c>
       <c r="L131" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B132" s="81">
+        <f>'Nach Mannschaften sortiert'!D132</f>
+        <v>46404</v>
+      </c>
+      <c r="C132" s="96">
+        <f>'Nach Mannschaften sortiert'!E132</f>
+        <v>0.375</v>
+      </c>
+      <c r="D132" s="96">
+        <v>0.875</v>
+      </c>
+      <c r="E132" s="96" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F132)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G132" t="str">
+        <f>'Nach Mannschaften sortiert'!H132</f>
+        <v>Heim</v>
+      </c>
+      <c r="H132" t="str">
+        <f>'Nach Mannschaften sortiert'!G132</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I132" t="str">
+        <f>'Nach Mannschaften sortiert'!C132</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J132" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="K132" t="s">
+        <v>73</v>
+      </c>
+      <c r="L132" t="s">
         <v>70</v>
       </c>
     </row>
@@ -9930,16 +10002,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
@@ -9966,7 +10038,7 @@
       <c r="H2" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="I2" s="114" t="s">
+      <c r="I2" s="115" t="s">
         <v>119</v>
       </c>
       <c r="J2" s="39"/>
@@ -9986,7 +10058,7 @@
       <c r="F3" s="61"/>
       <c r="G3" s="61"/>
       <c r="H3" s="63"/>
-      <c r="I3" s="115"/>
+      <c r="I3" s="116"/>
       <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10006,7 +10078,7 @@
       </c>
       <c r="G4" s="61"/>
       <c r="H4" s="63"/>
-      <c r="I4" s="115"/>
+      <c r="I4" s="116"/>
       <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10026,7 +10098,7 @@
       </c>
       <c r="G5" s="61"/>
       <c r="H5" s="63"/>
-      <c r="I5" s="115"/>
+      <c r="I5" s="116"/>
       <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10046,7 +10118,7 @@
       </c>
       <c r="G6" s="65"/>
       <c r="H6" s="63"/>
-      <c r="I6" s="115"/>
+      <c r="I6" s="116"/>
       <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10068,7 +10140,7 @@
         <v>129</v>
       </c>
       <c r="H7" s="63"/>
-      <c r="I7" s="115"/>
+      <c r="I7" s="116"/>
       <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10090,7 +10162,7 @@
         <v>129</v>
       </c>
       <c r="H8" s="63"/>
-      <c r="I8" s="115"/>
+      <c r="I8" s="116"/>
       <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10114,7 +10186,7 @@
       <c r="H9" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="I9" s="115"/>
+      <c r="I9" s="116"/>
       <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10136,7 +10208,7 @@
         <v>136</v>
       </c>
       <c r="H10" s="63"/>
-      <c r="I10" s="115"/>
+      <c r="I10" s="116"/>
       <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10156,7 +10228,7 @@
         <v>140</v>
       </c>
       <c r="H11" s="72"/>
-      <c r="I11" s="116"/>
+      <c r="I11" s="117"/>
       <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
@@ -10214,52 +10286,52 @@
       <c r="H14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="117" t="s">
+      <c r="A15" s="118" t="s">
         <v>145</v>
       </c>
-      <c r="B15" s="112"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="112"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="112"/>
-      <c r="H15" s="113"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="114"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="119" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="112"/>
-      <c r="C16" s="112"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="113"/>
+      <c r="B16" s="113"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="114"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="122" t="s">
         <v>147</v>
       </c>
-      <c r="B17" s="112"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="113"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="114"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="112" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="112"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="112"/>
-      <c r="H18" s="113"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="114"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -10328,783 +10400,783 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="54">
-        <f>'Nach Mannschaften sortiert'!A12</f>
-        <v>11</v>
+        <f>'Nach Mannschaften sortiert'!A13</f>
+        <v>12</v>
       </c>
       <c r="B2" s="54">
-        <f>'Nach Mannschaften sortiert'!B12</f>
+        <f>'Nach Mannschaften sortiert'!B13</f>
         <v>1</v>
       </c>
       <c r="C2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C12</f>
+        <f>'Nach Mannschaften sortiert'!C13</f>
         <v>KM</v>
       </c>
       <c r="D2" s="55">
-        <f>'Nach Mannschaften sortiert'!D12</f>
+        <f>'Nach Mannschaften sortiert'!D13</f>
         <v>46250</v>
       </c>
       <c r="E2" s="97">
-        <f>'Nach Mannschaften sortiert'!E12</f>
+        <f>'Nach Mannschaften sortiert'!E13</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="F2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F12</f>
+        <f>'Nach Mannschaften sortiert'!F13</f>
         <v>Kittsee</v>
       </c>
       <c r="G2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G12</f>
+        <f>'Nach Mannschaften sortiert'!G13</f>
         <v>Kittsee</v>
       </c>
       <c r="H2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H12</f>
+        <f>'Nach Mannschaften sortiert'!H13</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f>'Nach Mannschaften sortiert'!A13</f>
-        <v>12</v>
+        <f>'Nach Mannschaften sortiert'!A14</f>
+        <v>13</v>
       </c>
       <c r="B3" s="54">
-        <f>'Nach Mannschaften sortiert'!B13</f>
+        <f>'Nach Mannschaften sortiert'!B14</f>
         <v>2</v>
       </c>
       <c r="C3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C13</f>
+        <f>'Nach Mannschaften sortiert'!C14</f>
         <v>KM</v>
       </c>
       <c r="D3" s="55">
-        <f>'Nach Mannschaften sortiert'!D13</f>
+        <f>'Nach Mannschaften sortiert'!D14</f>
         <v>46255</v>
       </c>
       <c r="E3" s="97">
-        <f>'Nach Mannschaften sortiert'!E13</f>
+        <f>'Nach Mannschaften sortiert'!E14</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="F3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F13</f>
+        <f>'Nach Mannschaften sortiert'!F14</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="G3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G13</f>
+        <f>'Nach Mannschaften sortiert'!G14</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="H3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H13</f>
+        <f>'Nach Mannschaften sortiert'!H14</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54">
-        <f>'Nach Mannschaften sortiert'!A14</f>
-        <v>13</v>
+        <f>'Nach Mannschaften sortiert'!A15</f>
+        <v>14</v>
       </c>
       <c r="B4" s="54">
-        <f>'Nach Mannschaften sortiert'!B14</f>
+        <f>'Nach Mannschaften sortiert'!B15</f>
         <v>3</v>
       </c>
       <c r="C4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C14</f>
+        <f>'Nach Mannschaften sortiert'!C15</f>
         <v>KM</v>
       </c>
       <c r="D4" s="55">
-        <f>'Nach Mannschaften sortiert'!D14</f>
+        <f>'Nach Mannschaften sortiert'!D15</f>
         <v>46263</v>
       </c>
       <c r="E4" s="97">
-        <f>'Nach Mannschaften sortiert'!E14</f>
+        <f>'Nach Mannschaften sortiert'!E15</f>
         <v>0.75</v>
       </c>
       <c r="F4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F14</f>
+        <f>'Nach Mannschaften sortiert'!F15</f>
         <v>Neufeld</v>
       </c>
       <c r="G4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G14</f>
+        <f>'Nach Mannschaften sortiert'!G15</f>
         <v>Tadten</v>
       </c>
       <c r="H4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H14</f>
+        <f>'Nach Mannschaften sortiert'!H15</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="54">
-        <f>'Nach Mannschaften sortiert'!A48</f>
-        <v>47</v>
+        <f>'Nach Mannschaften sortiert'!A49</f>
+        <v>48</v>
       </c>
       <c r="B5" s="54">
-        <f>'Nach Mannschaften sortiert'!B48</f>
+        <f>'Nach Mannschaften sortiert'!B49</f>
         <v>1</v>
       </c>
       <c r="C5" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C48</f>
+        <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U14</v>
       </c>
       <c r="D5" s="55">
-        <f>'Nach Mannschaften sortiert'!D48</f>
+        <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46033</v>
       </c>
       <c r="E5" s="97">
-        <f>'Nach Mannschaften sortiert'!E48</f>
+        <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="F5" s="54">
-        <f>'Nach Mannschaften sortiert'!F48</f>
+        <f>'Nach Mannschaften sortiert'!F49</f>
         <v>0</v>
       </c>
       <c r="G5" s="54">
-        <f>'Nach Mannschaften sortiert'!G48</f>
+        <f>'Nach Mannschaften sortiert'!G49</f>
         <v>0</v>
       </c>
       <c r="H5" s="54">
-        <f>'Nach Mannschaften sortiert'!H48</f>
+        <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54">
+        <f>'Nach Mannschaften sortiert'!A17</f>
+        <v>16</v>
+      </c>
+      <c r="B6" s="54">
+        <f>'Nach Mannschaften sortiert'!B17</f>
+        <v>5</v>
+      </c>
+      <c r="C6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C17</f>
+        <v>KM</v>
+      </c>
+      <c r="D6" s="55">
+        <f>'Nach Mannschaften sortiert'!D17</f>
+        <v>46276</v>
+      </c>
+      <c r="E6" s="97">
+        <f>'Nach Mannschaften sortiert'!E17</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F17</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G17</f>
+        <v>Winden</v>
+      </c>
+      <c r="H6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H17</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="54">
+        <f>'Nach Mannschaften sortiert'!A59</f>
+        <v>58</v>
+      </c>
+      <c r="B7" s="54">
+        <f>'Nach Mannschaften sortiert'!B59</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C59</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D7" s="55">
+        <f>'Nach Mannschaften sortiert'!D59</f>
+        <v>46043</v>
+      </c>
+      <c r="E7" s="97">
+        <f>'Nach Mannschaften sortiert'!E59</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="54">
+        <f>'Nach Mannschaften sortiert'!F59</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="54">
+        <f>'Nach Mannschaften sortiert'!G59</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="54">
+        <f>'Nach Mannschaften sortiert'!H59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54">
+        <f>'Nach Mannschaften sortiert'!A19</f>
+        <v>18</v>
+      </c>
+      <c r="B8" s="54">
+        <f>'Nach Mannschaften sortiert'!B19</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C19</f>
+        <v>KM</v>
+      </c>
+      <c r="D8" s="55">
+        <f>'Nach Mannschaften sortiert'!D19</f>
+        <v>46291</v>
+      </c>
+      <c r="E8" s="97">
+        <f>'Nach Mannschaften sortiert'!E19</f>
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F19</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G19</f>
+        <v>Wallern</v>
+      </c>
+      <c r="H8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H19</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="52">
+        <f>'Nach Mannschaften sortiert'!A114</f>
+        <v>113</v>
+      </c>
+      <c r="B9" s="52">
+        <f>'Nach Mannschaften sortiert'!B114</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C114</f>
+        <v>Camp</v>
+      </c>
+      <c r="D9" s="53">
+        <f>'Nach Mannschaften sortiert'!D114</f>
+        <v>46230</v>
+      </c>
+      <c r="E9" s="98">
+        <f>'Nach Mannschaften sortiert'!E114</f>
+        <v>0.375</v>
+      </c>
+      <c r="F9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F114</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G114</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H114</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="54">
+        <f>'Nach Mannschaften sortiert'!A21</f>
+        <v>20</v>
+      </c>
+      <c r="B10" s="54">
+        <f>'Nach Mannschaften sortiert'!B21</f>
+        <v>9</v>
+      </c>
+      <c r="C10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C21</f>
+        <v>KM</v>
+      </c>
+      <c r="D10" s="55">
+        <f>'Nach Mannschaften sortiert'!D21</f>
+        <v>46304</v>
+      </c>
+      <c r="E10" s="97">
+        <f>'Nach Mannschaften sortiert'!E21</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F21</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G21</f>
+        <v>Wimpassing</v>
+      </c>
+      <c r="H10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H21</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="52">
+        <f>'Nach Mannschaften sortiert'!A115</f>
+        <v>114</v>
+      </c>
+      <c r="B11" s="52">
+        <f>'Nach Mannschaften sortiert'!B115</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C115</f>
+        <v>Camp</v>
+      </c>
+      <c r="D11" s="53">
+        <f>'Nach Mannschaften sortiert'!D115</f>
+        <v>46231</v>
+      </c>
+      <c r="E11" s="98">
+        <f>'Nach Mannschaften sortiert'!E115</f>
+        <v>0.375</v>
+      </c>
+      <c r="F11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F115</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G115</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H115</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="54">
+        <f>'Nach Mannschaften sortiert'!A23</f>
+        <v>22</v>
+      </c>
+      <c r="B12" s="54">
+        <f>'Nach Mannschaften sortiert'!B23</f>
+        <v>11</v>
+      </c>
+      <c r="C12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C23</f>
+        <v>KM</v>
+      </c>
+      <c r="D12" s="55">
+        <f>'Nach Mannschaften sortiert'!D23</f>
+        <v>46319</v>
+      </c>
+      <c r="E12" s="97">
+        <f>'Nach Mannschaften sortiert'!E23</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F23</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G23</f>
+        <v>Gols</v>
+      </c>
+      <c r="H12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H23</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <f>'Nach Mannschaften sortiert'!A24</f>
+        <v>23</v>
+      </c>
+      <c r="B13" s="54">
+        <f>'Nach Mannschaften sortiert'!B24</f>
+        <v>12</v>
+      </c>
+      <c r="C13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C24</f>
+        <v>KM</v>
+      </c>
+      <c r="D13" s="55">
+        <f>'Nach Mannschaften sortiert'!D24</f>
+        <v>46326</v>
+      </c>
+      <c r="E13" s="97">
+        <f>'Nach Mannschaften sortiert'!E24</f>
+        <v>0.75</v>
+      </c>
+      <c r="F13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F24</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="G13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G24</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="H13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H24</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="52">
+        <f>'Nach Mannschaften sortiert'!A116</f>
+        <v>115</v>
+      </c>
+      <c r="B14" s="52">
+        <f>'Nach Mannschaften sortiert'!B116</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C116</f>
+        <v>Camp</v>
+      </c>
+      <c r="D14" s="53">
+        <f>'Nach Mannschaften sortiert'!D116</f>
+        <v>46232</v>
+      </c>
+      <c r="E14" s="98">
+        <f>'Nach Mannschaften sortiert'!E116</f>
+        <v>0.375</v>
+      </c>
+      <c r="F14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F116</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G116</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H116</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
+        <f>'Nach Mannschaften sortiert'!A39</f>
+        <v>38</v>
+      </c>
+      <c r="B15" s="54">
+        <f>'Nach Mannschaften sortiert'!B39</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C39</f>
+        <v>U16</v>
+      </c>
+      <c r="D15" s="55">
+        <f>'Nach Mannschaften sortiert'!D39</f>
+        <v>46023</v>
+      </c>
+      <c r="E15" s="97">
+        <f>'Nach Mannschaften sortiert'!E39</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="54">
+        <f>'Nach Mannschaften sortiert'!F39</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="54">
+        <f>'Nach Mannschaften sortiert'!G39</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="54">
+        <f>'Nach Mannschaften sortiert'!H39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="48">
+        <f>'Nach Mannschaften sortiert'!A40</f>
+        <v>39</v>
+      </c>
+      <c r="B16" s="48">
+        <f>'Nach Mannschaften sortiert'!B40</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C40</f>
+        <v>U16</v>
+      </c>
+      <c r="D16" s="49">
+        <f>'Nach Mannschaften sortiert'!D40</f>
+        <v>46024</v>
+      </c>
+      <c r="E16" s="99">
+        <f>'Nach Mannschaften sortiert'!E40</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="48">
+        <f>'Nach Mannschaften sortiert'!F40</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="48">
+        <f>'Nach Mannschaften sortiert'!G40</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="48">
+        <f>'Nach Mannschaften sortiert'!H40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <f>'Nach Mannschaften sortiert'!A41</f>
+        <v>40</v>
+      </c>
+      <c r="B17" s="54">
+        <f>'Nach Mannschaften sortiert'!B41</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C41</f>
+        <v>U16</v>
+      </c>
+      <c r="D17" s="55">
+        <f>'Nach Mannschaften sortiert'!D41</f>
+        <v>46025</v>
+      </c>
+      <c r="E17" s="97">
+        <f>'Nach Mannschaften sortiert'!E41</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="54">
+        <f>'Nach Mannschaften sortiert'!F41</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="54">
+        <f>'Nach Mannschaften sortiert'!G41</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="54">
+        <f>'Nach Mannschaften sortiert'!H41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="54">
         <f>'Nach Mannschaften sortiert'!A16</f>
         <v>15</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B18" s="54">
         <f>'Nach Mannschaften sortiert'!B16</f>
-        <v>5</v>
-      </c>
-      <c r="C6" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!C16</f>
         <v>KM</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D18" s="55">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46276</v>
-      </c>
-      <c r="E6" s="97">
+        <v>46270</v>
+      </c>
+      <c r="E18" s="97">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F6" s="54" t="str">
+        <v>0.6875</v>
+      </c>
+      <c r="F18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F16</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="G18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>Winden</v>
-      </c>
-      <c r="H6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="H18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="54">
-        <f>'Nach Mannschaften sortiert'!A58</f>
-        <v>57</v>
-      </c>
-      <c r="B7" s="54">
-        <f>'Nach Mannschaften sortiert'!B58</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C58</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D7" s="55">
-        <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46043</v>
-      </c>
-      <c r="E7" s="97">
-        <f>'Nach Mannschaften sortiert'!E58</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="54">
-        <f>'Nach Mannschaften sortiert'!F58</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="54">
-        <f>'Nach Mannschaften sortiert'!G58</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="54">
-        <f>'Nach Mannschaften sortiert'!H58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54">
-        <f>'Nach Mannschaften sortiert'!A18</f>
-        <v>17</v>
-      </c>
-      <c r="B8" s="54">
-        <f>'Nach Mannschaften sortiert'!B18</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C18</f>
-        <v>KM</v>
-      </c>
-      <c r="D8" s="55">
-        <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46291</v>
-      </c>
-      <c r="E8" s="97">
-        <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.75</v>
-      </c>
-      <c r="F8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F18</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Wallern</v>
-      </c>
-      <c r="H8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="52">
-        <f>'Nach Mannschaften sortiert'!A113</f>
-        <v>112</v>
-      </c>
-      <c r="B9" s="52">
-        <f>'Nach Mannschaften sortiert'!B113</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C113</f>
-        <v>Camp</v>
-      </c>
-      <c r="D9" s="53">
-        <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46230</v>
-      </c>
-      <c r="E9" s="98">
-        <f>'Nach Mannschaften sortiert'!E113</f>
-        <v>0.375</v>
-      </c>
-      <c r="F9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F113</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G113</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H113</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54">
-        <f>'Nach Mannschaften sortiert'!A20</f>
-        <v>19</v>
-      </c>
-      <c r="B10" s="54">
-        <f>'Nach Mannschaften sortiert'!B20</f>
-        <v>9</v>
-      </c>
-      <c r="C10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C20</f>
-        <v>KM</v>
-      </c>
-      <c r="D10" s="55">
-        <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46304</v>
-      </c>
-      <c r="E10" s="97">
-        <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F20</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Wimpassing</v>
-      </c>
-      <c r="H10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="52">
-        <f>'Nach Mannschaften sortiert'!A114</f>
-        <v>113</v>
-      </c>
-      <c r="B11" s="52">
-        <f>'Nach Mannschaften sortiert'!B114</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C114</f>
-        <v>Camp</v>
-      </c>
-      <c r="D11" s="53">
-        <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46231</v>
-      </c>
-      <c r="E11" s="98">
-        <f>'Nach Mannschaften sortiert'!E114</f>
-        <v>0.375</v>
-      </c>
-      <c r="F11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F114</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G114</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H114</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <f>'Nach Mannschaften sortiert'!A22</f>
-        <v>21</v>
-      </c>
-      <c r="B12" s="54">
-        <f>'Nach Mannschaften sortiert'!B22</f>
-        <v>11</v>
-      </c>
-      <c r="C12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C22</f>
-        <v>KM</v>
-      </c>
-      <c r="D12" s="55">
-        <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46319</v>
-      </c>
-      <c r="E12" s="97">
-        <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F22</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Gols</v>
-      </c>
-      <c r="H12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54">
-        <f>'Nach Mannschaften sortiert'!A23</f>
-        <v>22</v>
-      </c>
-      <c r="B13" s="54">
-        <f>'Nach Mannschaften sortiert'!B23</f>
-        <v>12</v>
-      </c>
-      <c r="C13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C23</f>
-        <v>KM</v>
-      </c>
-      <c r="D13" s="55">
-        <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46326</v>
-      </c>
-      <c r="E13" s="97">
-        <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.75</v>
-      </c>
-      <c r="F13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F23</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="G13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="H13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="52">
-        <f>'Nach Mannschaften sortiert'!A115</f>
-        <v>114</v>
-      </c>
-      <c r="B14" s="52">
-        <f>'Nach Mannschaften sortiert'!B115</f>
-        <v>3</v>
-      </c>
-      <c r="C14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C115</f>
-        <v>Camp</v>
-      </c>
-      <c r="D14" s="53">
-        <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46232</v>
-      </c>
-      <c r="E14" s="98">
-        <f>'Nach Mannschaften sortiert'!E115</f>
-        <v>0.375</v>
-      </c>
-      <c r="F14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F115</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G115</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H115</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54">
-        <f>'Nach Mannschaften sortiert'!A38</f>
-        <v>37</v>
-      </c>
-      <c r="B15" s="54">
-        <f>'Nach Mannschaften sortiert'!B38</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C38</f>
-        <v>U16</v>
-      </c>
-      <c r="D15" s="55">
-        <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46023</v>
-      </c>
-      <c r="E15" s="97">
-        <f>'Nach Mannschaften sortiert'!E38</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="54">
-        <f>'Nach Mannschaften sortiert'!F38</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="54">
-        <f>'Nach Mannschaften sortiert'!G38</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="54">
-        <f>'Nach Mannschaften sortiert'!H38</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48">
-        <f>'Nach Mannschaften sortiert'!A39</f>
-        <v>38</v>
-      </c>
-      <c r="B16" s="48">
-        <f>'Nach Mannschaften sortiert'!B39</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C39</f>
-        <v>U16</v>
-      </c>
-      <c r="D16" s="49">
-        <f>'Nach Mannschaften sortiert'!D39</f>
-        <v>46024</v>
-      </c>
-      <c r="E16" s="99">
-        <f>'Nach Mannschaften sortiert'!E39</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="48">
-        <f>'Nach Mannschaften sortiert'!F39</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="48">
-        <f>'Nach Mannschaften sortiert'!G39</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="48">
-        <f>'Nach Mannschaften sortiert'!H39</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54">
-        <f>'Nach Mannschaften sortiert'!A40</f>
-        <v>39</v>
-      </c>
-      <c r="B17" s="54">
-        <f>'Nach Mannschaften sortiert'!B40</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C40</f>
-        <v>U16</v>
-      </c>
-      <c r="D17" s="55">
-        <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46025</v>
-      </c>
-      <c r="E17" s="97">
-        <f>'Nach Mannschaften sortiert'!E40</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="54">
-        <f>'Nach Mannschaften sortiert'!F40</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="54">
-        <f>'Nach Mannschaften sortiert'!G40</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="54">
-        <f>'Nach Mannschaften sortiert'!H40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="54">
-        <f>'Nach Mannschaften sortiert'!A15</f>
-        <v>14</v>
-      </c>
-      <c r="B18" s="54">
-        <f>'Nach Mannschaften sortiert'!B15</f>
-        <v>4</v>
-      </c>
-      <c r="C18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C15</f>
-        <v>KM</v>
-      </c>
-      <c r="D18" s="55">
-        <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46270</v>
-      </c>
-      <c r="E18" s="97">
-        <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.6875</v>
-      </c>
-      <c r="F18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F15</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="G18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="H18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H15</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54">
-        <f>'Nach Mannschaften sortiert'!A42</f>
-        <v>41</v>
+        <f>'Nach Mannschaften sortiert'!A43</f>
+        <v>42</v>
       </c>
       <c r="B19" s="54">
-        <f>'Nach Mannschaften sortiert'!B42</f>
+        <f>'Nach Mannschaften sortiert'!B43</f>
         <v>5</v>
       </c>
       <c r="C19" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C42</f>
+        <f>'Nach Mannschaften sortiert'!C43</f>
         <v>U16</v>
       </c>
       <c r="D19" s="55">
-        <f>'Nach Mannschaften sortiert'!D42</f>
+        <f>'Nach Mannschaften sortiert'!D43</f>
         <v>46027</v>
       </c>
       <c r="E19" s="97">
-        <f>'Nach Mannschaften sortiert'!E42</f>
+        <f>'Nach Mannschaften sortiert'!E43</f>
         <v>0</v>
       </c>
       <c r="F19" s="54">
-        <f>'Nach Mannschaften sortiert'!F42</f>
+        <f>'Nach Mannschaften sortiert'!F43</f>
         <v>0</v>
       </c>
       <c r="G19" s="54">
-        <f>'Nach Mannschaften sortiert'!G42</f>
+        <f>'Nach Mannschaften sortiert'!G43</f>
         <v>0</v>
       </c>
       <c r="H19" s="54">
-        <f>'Nach Mannschaften sortiert'!H42</f>
+        <f>'Nach Mannschaften sortiert'!H43</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
-        <f>'Nach Mannschaften sortiert'!A43</f>
-        <v>42</v>
+        <f>'Nach Mannschaften sortiert'!A44</f>
+        <v>43</v>
       </c>
       <c r="B20" s="46">
-        <f>'Nach Mannschaften sortiert'!B43</f>
+        <f>'Nach Mannschaften sortiert'!B44</f>
         <v>6</v>
       </c>
       <c r="C20" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C43</f>
+        <f>'Nach Mannschaften sortiert'!C44</f>
         <v>U16</v>
       </c>
       <c r="D20" s="47">
-        <f>'Nach Mannschaften sortiert'!D43</f>
+        <f>'Nach Mannschaften sortiert'!D44</f>
         <v>46028</v>
       </c>
       <c r="E20" s="100">
-        <f>'Nach Mannschaften sortiert'!E43</f>
+        <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="F20" s="46">
-        <f>'Nach Mannschaften sortiert'!F43</f>
+        <f>'Nach Mannschaften sortiert'!F44</f>
         <v>0</v>
       </c>
       <c r="G20" s="46">
-        <f>'Nach Mannschaften sortiert'!G43</f>
+        <f>'Nach Mannschaften sortiert'!G44</f>
         <v>0</v>
       </c>
       <c r="H20" s="46">
-        <f>'Nach Mannschaften sortiert'!H43</f>
+        <f>'Nach Mannschaften sortiert'!H44</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54">
-        <f>'Nach Mannschaften sortiert'!A44</f>
-        <v>43</v>
+        <f>'Nach Mannschaften sortiert'!A45</f>
+        <v>44</v>
       </c>
       <c r="B21" s="54">
-        <f>'Nach Mannschaften sortiert'!B44</f>
+        <f>'Nach Mannschaften sortiert'!B45</f>
         <v>7</v>
       </c>
       <c r="C21" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C44</f>
+        <f>'Nach Mannschaften sortiert'!C45</f>
         <v>U16</v>
       </c>
       <c r="D21" s="55">
-        <f>'Nach Mannschaften sortiert'!D44</f>
+        <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46029</v>
       </c>
       <c r="E21" s="97">
-        <f>'Nach Mannschaften sortiert'!E44</f>
+        <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="F21" s="54">
-        <f>'Nach Mannschaften sortiert'!F44</f>
+        <f>'Nach Mannschaften sortiert'!F45</f>
         <v>0</v>
       </c>
       <c r="G21" s="54">
-        <f>'Nach Mannschaften sortiert'!G44</f>
+        <f>'Nach Mannschaften sortiert'!G45</f>
         <v>0</v>
       </c>
       <c r="H21" s="54">
-        <f>'Nach Mannschaften sortiert'!H44</f>
+        <f>'Nach Mannschaften sortiert'!H45</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
-        <f>'Nach Mannschaften sortiert'!A45</f>
-        <v>44</v>
+        <f>'Nach Mannschaften sortiert'!A46</f>
+        <v>45</v>
       </c>
       <c r="B22" s="48">
-        <f>'Nach Mannschaften sortiert'!B45</f>
+        <f>'Nach Mannschaften sortiert'!B46</f>
         <v>8</v>
       </c>
       <c r="C22" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C45</f>
+        <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U16</v>
       </c>
       <c r="D22" s="49">
-        <f>'Nach Mannschaften sortiert'!D45</f>
+        <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46030</v>
       </c>
       <c r="E22" s="99">
-        <f>'Nach Mannschaften sortiert'!E45</f>
+        <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="F22" s="48">
-        <f>'Nach Mannschaften sortiert'!F45</f>
+        <f>'Nach Mannschaften sortiert'!F46</f>
         <v>0</v>
       </c>
       <c r="G22" s="48">
-        <f>'Nach Mannschaften sortiert'!G45</f>
+        <f>'Nach Mannschaften sortiert'!G46</f>
         <v>0</v>
       </c>
       <c r="H22" s="48">
-        <f>'Nach Mannschaften sortiert'!H45</f>
+        <f>'Nach Mannschaften sortiert'!H46</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54">
-        <f>'Nach Mannschaften sortiert'!A46</f>
-        <v>45</v>
+        <f>'Nach Mannschaften sortiert'!A47</f>
+        <v>46</v>
       </c>
       <c r="B23" s="54">
-        <f>'Nach Mannschaften sortiert'!B46</f>
+        <f>'Nach Mannschaften sortiert'!B47</f>
         <v>9</v>
       </c>
       <c r="C23" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C46</f>
+        <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U16</v>
       </c>
       <c r="D23" s="55">
-        <f>'Nach Mannschaften sortiert'!D46</f>
+        <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46031</v>
       </c>
       <c r="E23" s="97">
-        <f>'Nach Mannschaften sortiert'!E46</f>
+        <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="F23" s="54">
-        <f>'Nach Mannschaften sortiert'!F46</f>
+        <f>'Nach Mannschaften sortiert'!F47</f>
         <v>0</v>
       </c>
       <c r="G23" s="54">
-        <f>'Nach Mannschaften sortiert'!G46</f>
+        <f>'Nach Mannschaften sortiert'!G47</f>
         <v>0</v>
       </c>
       <c r="H23" s="54">
-        <f>'Nach Mannschaften sortiert'!H46</f>
+        <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
-        <f>'Nach Mannschaften sortiert'!A93</f>
-        <v>92</v>
+        <f>'Nach Mannschaften sortiert'!A94</f>
+        <v>93</v>
       </c>
       <c r="B24" s="50">
-        <f>'Nach Mannschaften sortiert'!B93</f>
+        <f>'Nach Mannschaften sortiert'!B94</f>
         <v>1</v>
       </c>
       <c r="C24" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C93</f>
+        <f>'Nach Mannschaften sortiert'!C94</f>
         <v>U9</v>
       </c>
       <c r="D24" s="51">
-        <f>'Nach Mannschaften sortiert'!D93</f>
+        <f>'Nach Mannschaften sortiert'!D94</f>
         <v>46078</v>
       </c>
       <c r="E24" s="101">
-        <f>'Nach Mannschaften sortiert'!E93</f>
+        <f>'Nach Mannschaften sortiert'!E94</f>
         <v>0</v>
       </c>
       <c r="F24" s="50">
-        <f>'Nach Mannschaften sortiert'!F93</f>
+        <f>'Nach Mannschaften sortiert'!F94</f>
         <v>0</v>
       </c>
       <c r="G24" s="50">
-        <f>'Nach Mannschaften sortiert'!G93</f>
+        <f>'Nach Mannschaften sortiert'!G94</f>
         <v>0</v>
       </c>
       <c r="H24" s="50">
-        <f>'Nach Mannschaften sortiert'!H93</f>
+        <f>'Nach Mannschaften sortiert'!H94</f>
         <v>0</v>
       </c>
     </row>
@@ -11144,35 +11216,35 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
-        <f>'Nach Mannschaften sortiert'!A103</f>
-        <v>102</v>
+        <f>'Nach Mannschaften sortiert'!A104</f>
+        <v>103</v>
       </c>
       <c r="B26" s="50">
-        <f>'Nach Mannschaften sortiert'!B103</f>
+        <f>'Nach Mannschaften sortiert'!B104</f>
         <v>1</v>
       </c>
       <c r="C26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C103</f>
+        <f>'Nach Mannschaften sortiert'!C104</f>
         <v>U8</v>
       </c>
       <c r="D26" s="51">
-        <f>'Nach Mannschaften sortiert'!D103</f>
+        <f>'Nach Mannschaften sortiert'!D104</f>
         <v>46312</v>
       </c>
       <c r="E26" s="101">
-        <f>'Nach Mannschaften sortiert'!E103</f>
+        <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0.39583333333333331</v>
       </c>
       <c r="F26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!F103</f>
+        <f>'Nach Mannschaften sortiert'!F104</f>
         <v>Neufeld</v>
       </c>
       <c r="G26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!G103</f>
+        <f>'Nach Mannschaften sortiert'!G104</f>
         <v>Heimturnier</v>
       </c>
       <c r="H26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!H103</f>
+        <f>'Nach Mannschaften sortiert'!H104</f>
         <v>Heim</v>
       </c>
     </row>
@@ -11246,35 +11318,35 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="50">
-        <f>'Nach Mannschaften sortiert'!A108</f>
-        <v>107</v>
+        <f>'Nach Mannschaften sortiert'!A109</f>
+        <v>108</v>
       </c>
       <c r="B29" s="50">
-        <f>'Nach Mannschaften sortiert'!B108</f>
+        <f>'Nach Mannschaften sortiert'!B109</f>
         <v>1</v>
       </c>
       <c r="C29" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C108</f>
+        <f>'Nach Mannschaften sortiert'!C109</f>
         <v>U7</v>
       </c>
       <c r="D29" s="51">
-        <f>'Nach Mannschaften sortiert'!D108</f>
+        <f>'Nach Mannschaften sortiert'!D109</f>
         <v>46312</v>
       </c>
       <c r="E29" s="101">
-        <f>'Nach Mannschaften sortiert'!E108</f>
+        <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="F29" s="50">
-        <f>'Nach Mannschaften sortiert'!F108</f>
+        <f>'Nach Mannschaften sortiert'!F109</f>
         <v>0</v>
       </c>
       <c r="G29" s="50">
-        <f>'Nach Mannschaften sortiert'!G108</f>
+        <f>'Nach Mannschaften sortiert'!G109</f>
         <v>0</v>
       </c>
       <c r="H29" s="50">
-        <f>'Nach Mannschaften sortiert'!H108</f>
+        <f>'Nach Mannschaften sortiert'!H109</f>
         <v>0</v>
       </c>
     </row>
@@ -11450,103 +11522,103 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="50">
-        <f>'Nach Mannschaften sortiert'!A79</f>
-        <v>78</v>
+        <f>'Nach Mannschaften sortiert'!A80</f>
+        <v>79</v>
       </c>
       <c r="B35" s="50">
-        <f>'Nach Mannschaften sortiert'!B79</f>
+        <f>'Nach Mannschaften sortiert'!B80</f>
         <v>2</v>
       </c>
       <c r="C35" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C79</f>
+        <f>'Nach Mannschaften sortiert'!C80</f>
         <v>U11</v>
       </c>
       <c r="D35" s="51">
-        <f>'Nach Mannschaften sortiert'!D79</f>
+        <f>'Nach Mannschaften sortiert'!D80</f>
         <v>46064</v>
       </c>
       <c r="E35" s="101">
-        <f>'Nach Mannschaften sortiert'!E79</f>
+        <f>'Nach Mannschaften sortiert'!E80</f>
         <v>0</v>
       </c>
       <c r="F35" s="50">
-        <f>'Nach Mannschaften sortiert'!F79</f>
+        <f>'Nach Mannschaften sortiert'!F80</f>
         <v>0</v>
       </c>
       <c r="G35" s="50">
-        <f>'Nach Mannschaften sortiert'!G79</f>
+        <f>'Nach Mannschaften sortiert'!G80</f>
         <v>0</v>
       </c>
       <c r="H35" s="50">
-        <f>'Nach Mannschaften sortiert'!H79</f>
+        <f>'Nach Mannschaften sortiert'!H80</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="54">
-        <f>'Nach Mannschaften sortiert'!A49</f>
-        <v>48</v>
+        <f>'Nach Mannschaften sortiert'!A50</f>
+        <v>49</v>
       </c>
       <c r="B36" s="54">
-        <f>'Nach Mannschaften sortiert'!B49</f>
+        <f>'Nach Mannschaften sortiert'!B50</f>
         <v>2</v>
       </c>
       <c r="C36" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C49</f>
+        <f>'Nach Mannschaften sortiert'!C50</f>
         <v>U14</v>
       </c>
       <c r="D36" s="55">
-        <f>'Nach Mannschaften sortiert'!D49</f>
+        <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46034</v>
       </c>
       <c r="E36" s="97">
-        <f>'Nach Mannschaften sortiert'!E49</f>
+        <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="F36" s="54">
-        <f>'Nach Mannschaften sortiert'!F49</f>
+        <f>'Nach Mannschaften sortiert'!F50</f>
         <v>0</v>
       </c>
       <c r="G36" s="54">
-        <f>'Nach Mannschaften sortiert'!G49</f>
+        <f>'Nach Mannschaften sortiert'!G50</f>
         <v>0</v>
       </c>
       <c r="H36" s="54">
-        <f>'Nach Mannschaften sortiert'!H49</f>
+        <f>'Nach Mannschaften sortiert'!H50</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="54">
-        <f>'Nach Mannschaften sortiert'!A50</f>
-        <v>49</v>
+        <f>'Nach Mannschaften sortiert'!A51</f>
+        <v>50</v>
       </c>
       <c r="B37" s="54">
-        <f>'Nach Mannschaften sortiert'!B50</f>
+        <f>'Nach Mannschaften sortiert'!B51</f>
         <v>3</v>
       </c>
       <c r="C37" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C50</f>
+        <f>'Nach Mannschaften sortiert'!C51</f>
         <v>U14</v>
       </c>
       <c r="D37" s="55">
-        <f>'Nach Mannschaften sortiert'!D50</f>
+        <f>'Nach Mannschaften sortiert'!D51</f>
         <v>46035</v>
       </c>
       <c r="E37" s="97">
-        <f>'Nach Mannschaften sortiert'!E50</f>
+        <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="F37" s="54">
-        <f>'Nach Mannschaften sortiert'!F50</f>
+        <f>'Nach Mannschaften sortiert'!F51</f>
         <v>0</v>
       </c>
       <c r="G37" s="54">
-        <f>'Nach Mannschaften sortiert'!G50</f>
+        <f>'Nach Mannschaften sortiert'!G51</f>
         <v>0</v>
       </c>
       <c r="H37" s="54">
-        <f>'Nach Mannschaften sortiert'!H50</f>
+        <f>'Nach Mannschaften sortiert'!H51</f>
         <v>0</v>
       </c>
     </row>
@@ -11620,205 +11692,205 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54">
+        <f>'Nach Mannschaften sortiert'!A53</f>
+        <v>52</v>
+      </c>
+      <c r="B40" s="54">
+        <f>'Nach Mannschaften sortiert'!B53</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C53</f>
+        <v>U14</v>
+      </c>
+      <c r="D40" s="55">
+        <f>'Nach Mannschaften sortiert'!D53</f>
+        <v>46037</v>
+      </c>
+      <c r="E40" s="97">
+        <f>'Nach Mannschaften sortiert'!E53</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="54">
+        <f>'Nach Mannschaften sortiert'!F53</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="54">
+        <f>'Nach Mannschaften sortiert'!G53</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="54">
+        <f>'Nach Mannschaften sortiert'!H53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="48">
+        <f>'Nach Mannschaften sortiert'!A18</f>
+        <v>17</v>
+      </c>
+      <c r="B41" s="48">
+        <f>'Nach Mannschaften sortiert'!B18</f>
+        <v>6</v>
+      </c>
+      <c r="C41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C18</f>
+        <v>KM</v>
+      </c>
+      <c r="D41" s="49">
+        <f>'Nach Mannschaften sortiert'!D18</f>
+        <v>46284</v>
+      </c>
+      <c r="E41" s="99">
+        <f>'Nach Mannschaften sortiert'!E18</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!F18</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="G41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!G18</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="H41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!H18</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="54">
+        <f>'Nach Mannschaften sortiert'!A84</f>
+        <v>83</v>
+      </c>
+      <c r="B42" s="54">
+        <f>'Nach Mannschaften sortiert'!B84</f>
+        <v>6</v>
+      </c>
+      <c r="C42" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C84</f>
+        <v>U11</v>
+      </c>
+      <c r="D42" s="55">
+        <f>'Nach Mannschaften sortiert'!D84</f>
+        <v>46068</v>
+      </c>
+      <c r="E42" s="97">
+        <f>'Nach Mannschaften sortiert'!E84</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="54">
+        <f>'Nach Mannschaften sortiert'!F84</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="54">
+        <f>'Nach Mannschaften sortiert'!G84</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="54">
+        <f>'Nach Mannschaften sortiert'!H84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="54">
+        <f>'Nach Mannschaften sortiert'!A58</f>
+        <v>57</v>
+      </c>
+      <c r="B43" s="54">
+        <f>'Nach Mannschaften sortiert'!B58</f>
+        <v>10</v>
+      </c>
+      <c r="C43" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C58</f>
+        <v>U14</v>
+      </c>
+      <c r="D43" s="55">
+        <f>'Nach Mannschaften sortiert'!D58</f>
+        <v>46042</v>
+      </c>
+      <c r="E43" s="97">
+        <f>'Nach Mannschaften sortiert'!E58</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="54">
+        <f>'Nach Mannschaften sortiert'!F58</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="54">
+        <f>'Nach Mannschaften sortiert'!G58</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="54">
+        <f>'Nach Mannschaften sortiert'!H58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="50">
+        <f>'Nach Mannschaften sortiert'!A61</f>
+        <v>60</v>
+      </c>
+      <c r="B44" s="50">
+        <f>'Nach Mannschaften sortiert'!B61</f>
+        <v>3</v>
+      </c>
+      <c r="C44" s="50" t="str">
+        <f>'Nach Mannschaften sortiert'!C61</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D44" s="51">
+        <f>'Nach Mannschaften sortiert'!D61</f>
+        <v>46045</v>
+      </c>
+      <c r="E44" s="101">
+        <f>'Nach Mannschaften sortiert'!E61</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="50">
+        <f>'Nach Mannschaften sortiert'!F61</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="50">
+        <f>'Nach Mannschaften sortiert'!G61</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="50">
+        <f>'Nach Mannschaften sortiert'!H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="50">
         <f>'Nach Mannschaften sortiert'!A52</f>
         <v>51</v>
       </c>
-      <c r="B40" s="54">
+      <c r="B45" s="50">
         <f>'Nach Mannschaften sortiert'!B52</f>
-        <v>5</v>
-      </c>
-      <c r="C40" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C45" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!C52</f>
         <v>U14</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D45" s="51">
         <f>'Nach Mannschaften sortiert'!D52</f>
-        <v>46037</v>
-      </c>
-      <c r="E40" s="97">
+        <v>46036</v>
+      </c>
+      <c r="E45" s="101">
         <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
-      <c r="F40" s="54">
+      <c r="F45" s="50">
         <f>'Nach Mannschaften sortiert'!F52</f>
         <v>0</v>
       </c>
-      <c r="G40" s="54">
+      <c r="G45" s="50">
         <f>'Nach Mannschaften sortiert'!G52</f>
         <v>0</v>
       </c>
-      <c r="H40" s="54">
+      <c r="H45" s="50">
         <f>'Nach Mannschaften sortiert'!H52</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="48">
-        <f>'Nach Mannschaften sortiert'!A17</f>
-        <v>16</v>
-      </c>
-      <c r="B41" s="48">
-        <f>'Nach Mannschaften sortiert'!B17</f>
-        <v>6</v>
-      </c>
-      <c r="C41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
-        <v>KM</v>
-      </c>
-      <c r="D41" s="49">
-        <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46284</v>
-      </c>
-      <c r="E41" s="99">
-        <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F17</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="G41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="H41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="54">
-        <f>'Nach Mannschaften sortiert'!A83</f>
-        <v>82</v>
-      </c>
-      <c r="B42" s="54">
-        <f>'Nach Mannschaften sortiert'!B83</f>
-        <v>6</v>
-      </c>
-      <c r="C42" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C83</f>
-        <v>U11</v>
-      </c>
-      <c r="D42" s="55">
-        <f>'Nach Mannschaften sortiert'!D83</f>
-        <v>46068</v>
-      </c>
-      <c r="E42" s="97">
-        <f>'Nach Mannschaften sortiert'!E83</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="54">
-        <f>'Nach Mannschaften sortiert'!F83</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="54">
-        <f>'Nach Mannschaften sortiert'!G83</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="54">
-        <f>'Nach Mannschaften sortiert'!H83</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="54">
-        <f>'Nach Mannschaften sortiert'!A57</f>
-        <v>56</v>
-      </c>
-      <c r="B43" s="54">
-        <f>'Nach Mannschaften sortiert'!B57</f>
-        <v>10</v>
-      </c>
-      <c r="C43" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C57</f>
-        <v>U14</v>
-      </c>
-      <c r="D43" s="55">
-        <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46042</v>
-      </c>
-      <c r="E43" s="97">
-        <f>'Nach Mannschaften sortiert'!E57</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="54">
-        <f>'Nach Mannschaften sortiert'!F57</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="54">
-        <f>'Nach Mannschaften sortiert'!G57</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="54">
-        <f>'Nach Mannschaften sortiert'!H57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="50">
-        <f>'Nach Mannschaften sortiert'!A60</f>
-        <v>59</v>
-      </c>
-      <c r="B44" s="50">
-        <f>'Nach Mannschaften sortiert'!B60</f>
-        <v>3</v>
-      </c>
-      <c r="C44" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C60</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D44" s="51">
-        <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46045</v>
-      </c>
-      <c r="E44" s="101">
-        <f>'Nach Mannschaften sortiert'!E60</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="50">
-        <f>'Nach Mannschaften sortiert'!F60</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="50">
-        <f>'Nach Mannschaften sortiert'!G60</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="50">
-        <f>'Nach Mannschaften sortiert'!H60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="50">
-        <f>'Nach Mannschaften sortiert'!A51</f>
-        <v>50</v>
-      </c>
-      <c r="B45" s="50">
-        <f>'Nach Mannschaften sortiert'!B51</f>
-        <v>4</v>
-      </c>
-      <c r="C45" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C51</f>
-        <v>U14</v>
-      </c>
-      <c r="D45" s="51">
-        <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46036</v>
-      </c>
-      <c r="E45" s="101">
-        <f>'Nach Mannschaften sortiert'!E51</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="50">
-        <f>'Nach Mannschaften sortiert'!F51</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="50">
-        <f>'Nach Mannschaften sortiert'!G51</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="50">
-        <f>'Nach Mannschaften sortiert'!H51</f>
         <v>0</v>
       </c>
     </row>
@@ -11858,137 +11930,137 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54">
-        <f>'Nach Mannschaften sortiert'!A59</f>
-        <v>58</v>
+        <f>'Nach Mannschaften sortiert'!A60</f>
+        <v>59</v>
       </c>
       <c r="B47" s="54">
-        <f>'Nach Mannschaften sortiert'!B59</f>
+        <f>'Nach Mannschaften sortiert'!B60</f>
         <v>2</v>
       </c>
       <c r="C47" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C59</f>
+        <f>'Nach Mannschaften sortiert'!C60</f>
         <v>U12_1</v>
       </c>
       <c r="D47" s="55">
-        <f>'Nach Mannschaften sortiert'!D59</f>
+        <f>'Nach Mannschaften sortiert'!D60</f>
         <v>46044</v>
       </c>
       <c r="E47" s="97">
-        <f>'Nach Mannschaften sortiert'!E59</f>
+        <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="F47" s="54">
-        <f>'Nach Mannschaften sortiert'!F59</f>
+        <f>'Nach Mannschaften sortiert'!F60</f>
         <v>0</v>
       </c>
       <c r="G47" s="54">
-        <f>'Nach Mannschaften sortiert'!G59</f>
+        <f>'Nach Mannschaften sortiert'!G60</f>
         <v>0</v>
       </c>
       <c r="H47" s="54">
-        <f>'Nach Mannschaften sortiert'!H59</f>
+        <f>'Nach Mannschaften sortiert'!H60</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="48">
-        <f>'Nach Mannschaften sortiert'!A41</f>
-        <v>40</v>
+        <f>'Nach Mannschaften sortiert'!A42</f>
+        <v>41</v>
       </c>
       <c r="B48" s="48">
-        <f>'Nach Mannschaften sortiert'!B41</f>
+        <f>'Nach Mannschaften sortiert'!B42</f>
         <v>4</v>
       </c>
       <c r="C48" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C41</f>
+        <f>'Nach Mannschaften sortiert'!C42</f>
         <v>U16</v>
       </c>
       <c r="D48" s="49">
-        <f>'Nach Mannschaften sortiert'!D41</f>
+        <f>'Nach Mannschaften sortiert'!D42</f>
         <v>46026</v>
       </c>
       <c r="E48" s="99">
-        <f>'Nach Mannschaften sortiert'!E41</f>
+        <f>'Nach Mannschaften sortiert'!E42</f>
         <v>0</v>
       </c>
       <c r="F48" s="48">
-        <f>'Nach Mannschaften sortiert'!F41</f>
+        <f>'Nach Mannschaften sortiert'!F42</f>
         <v>0</v>
       </c>
       <c r="G48" s="48">
-        <f>'Nach Mannschaften sortiert'!G41</f>
+        <f>'Nach Mannschaften sortiert'!G42</f>
         <v>0</v>
       </c>
       <c r="H48" s="48">
-        <f>'Nach Mannschaften sortiert'!H41</f>
+        <f>'Nach Mannschaften sortiert'!H42</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="54">
-        <f>'Nach Mannschaften sortiert'!A61</f>
-        <v>60</v>
+        <f>'Nach Mannschaften sortiert'!A62</f>
+        <v>61</v>
       </c>
       <c r="B49" s="54">
-        <f>'Nach Mannschaften sortiert'!B61</f>
+        <f>'Nach Mannschaften sortiert'!B62</f>
         <v>4</v>
       </c>
       <c r="C49" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C61</f>
+        <f>'Nach Mannschaften sortiert'!C62</f>
         <v>U12_1</v>
       </c>
       <c r="D49" s="55">
-        <f>'Nach Mannschaften sortiert'!D61</f>
+        <f>'Nach Mannschaften sortiert'!D62</f>
         <v>46046</v>
       </c>
       <c r="E49" s="97">
-        <f>'Nach Mannschaften sortiert'!E61</f>
+        <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="F49" s="54">
-        <f>'Nach Mannschaften sortiert'!F61</f>
+        <f>'Nach Mannschaften sortiert'!F62</f>
         <v>0</v>
       </c>
       <c r="G49" s="54">
-        <f>'Nach Mannschaften sortiert'!G61</f>
+        <f>'Nach Mannschaften sortiert'!G62</f>
         <v>0</v>
       </c>
       <c r="H49" s="54">
-        <f>'Nach Mannschaften sortiert'!H61</f>
+        <f>'Nach Mannschaften sortiert'!H62</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="54">
-        <f>'Nach Mannschaften sortiert'!A62</f>
-        <v>61</v>
+        <f>'Nach Mannschaften sortiert'!A63</f>
+        <v>62</v>
       </c>
       <c r="B50" s="54">
-        <f>'Nach Mannschaften sortiert'!B62</f>
+        <f>'Nach Mannschaften sortiert'!B63</f>
         <v>5</v>
       </c>
       <c r="C50" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C62</f>
+        <f>'Nach Mannschaften sortiert'!C63</f>
         <v>U12_1</v>
       </c>
       <c r="D50" s="55">
-        <f>'Nach Mannschaften sortiert'!D62</f>
+        <f>'Nach Mannschaften sortiert'!D63</f>
         <v>46047</v>
       </c>
       <c r="E50" s="97">
-        <f>'Nach Mannschaften sortiert'!E62</f>
+        <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="F50" s="54">
-        <f>'Nach Mannschaften sortiert'!F62</f>
+        <f>'Nach Mannschaften sortiert'!F63</f>
         <v>0</v>
       </c>
       <c r="G50" s="54">
-        <f>'Nach Mannschaften sortiert'!G62</f>
+        <f>'Nach Mannschaften sortiert'!G63</f>
         <v>0</v>
       </c>
       <c r="H50" s="54">
-        <f>'Nach Mannschaften sortiert'!H62</f>
+        <f>'Nach Mannschaften sortiert'!H63</f>
         <v>0</v>
       </c>
     </row>
@@ -12028,69 +12100,69 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="48">
-        <f>'Nach Mannschaften sortiert'!A19</f>
-        <v>18</v>
+        <f>'Nach Mannschaften sortiert'!A20</f>
+        <v>19</v>
       </c>
       <c r="B52" s="48">
-        <f>'Nach Mannschaften sortiert'!B19</f>
+        <f>'Nach Mannschaften sortiert'!B20</f>
         <v>8</v>
       </c>
       <c r="C52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C19</f>
+        <f>'Nach Mannschaften sortiert'!C20</f>
         <v>KM</v>
       </c>
       <c r="D52" s="49">
-        <f>'Nach Mannschaften sortiert'!D19</f>
+        <f>'Nach Mannschaften sortiert'!D20</f>
         <v>46297</v>
       </c>
       <c r="E52" s="99">
-        <f>'Nach Mannschaften sortiert'!E19</f>
+        <f>'Nach Mannschaften sortiert'!E20</f>
         <v>0.79166666666666663</v>
       </c>
       <c r="F52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F19</f>
+        <f>'Nach Mannschaften sortiert'!F20</f>
         <v>Siegendorf</v>
       </c>
       <c r="G52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G19</f>
+        <f>'Nach Mannschaften sortiert'!G20</f>
         <v>Siegendorf</v>
       </c>
       <c r="H52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H19</f>
+        <f>'Nach Mannschaften sortiert'!H20</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="54">
-        <f>'Nach Mannschaften sortiert'!A64</f>
-        <v>63</v>
+        <f>'Nach Mannschaften sortiert'!A65</f>
+        <v>64</v>
       </c>
       <c r="B53" s="54">
-        <f>'Nach Mannschaften sortiert'!B64</f>
+        <f>'Nach Mannschaften sortiert'!B65</f>
         <v>7</v>
       </c>
       <c r="C53" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C64</f>
+        <f>'Nach Mannschaften sortiert'!C65</f>
         <v>U12_1</v>
       </c>
       <c r="D53" s="55">
-        <f>'Nach Mannschaften sortiert'!D64</f>
+        <f>'Nach Mannschaften sortiert'!D65</f>
         <v>46049</v>
       </c>
       <c r="E53" s="97">
-        <f>'Nach Mannschaften sortiert'!E64</f>
+        <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="F53" s="54">
-        <f>'Nach Mannschaften sortiert'!F64</f>
+        <f>'Nach Mannschaften sortiert'!F65</f>
         <v>0</v>
       </c>
       <c r="G53" s="54">
-        <f>'Nach Mannschaften sortiert'!G64</f>
+        <f>'Nach Mannschaften sortiert'!G65</f>
         <v>0</v>
       </c>
       <c r="H53" s="54">
-        <f>'Nach Mannschaften sortiert'!H64</f>
+        <f>'Nach Mannschaften sortiert'!H65</f>
         <v>0</v>
       </c>
     </row>
@@ -12130,137 +12202,137 @@
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="54">
-        <f>'Nach Mannschaften sortiert'!A78</f>
-        <v>77</v>
+        <f>'Nach Mannschaften sortiert'!A79</f>
+        <v>78</v>
       </c>
       <c r="B55" s="54">
-        <f>'Nach Mannschaften sortiert'!B78</f>
+        <f>'Nach Mannschaften sortiert'!B79</f>
         <v>1</v>
       </c>
       <c r="C55" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C78</f>
+        <f>'Nach Mannschaften sortiert'!C79</f>
         <v>U11</v>
       </c>
       <c r="D55" s="55">
-        <f>'Nach Mannschaften sortiert'!D78</f>
+        <f>'Nach Mannschaften sortiert'!D79</f>
         <v>46063</v>
       </c>
       <c r="E55" s="97">
-        <f>'Nach Mannschaften sortiert'!E78</f>
+        <f>'Nach Mannschaften sortiert'!E79</f>
         <v>0</v>
       </c>
       <c r="F55" s="54">
-        <f>'Nach Mannschaften sortiert'!F78</f>
+        <f>'Nach Mannschaften sortiert'!F79</f>
         <v>0</v>
       </c>
       <c r="G55" s="54">
-        <f>'Nach Mannschaften sortiert'!G78</f>
+        <f>'Nach Mannschaften sortiert'!G79</f>
         <v>0</v>
       </c>
       <c r="H55" s="54">
-        <f>'Nach Mannschaften sortiert'!H78</f>
+        <f>'Nach Mannschaften sortiert'!H79</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="48">
-        <f>'Nach Mannschaften sortiert'!A84</f>
-        <v>83</v>
+        <f>'Nach Mannschaften sortiert'!A85</f>
+        <v>84</v>
       </c>
       <c r="B56" s="48">
-        <f>'Nach Mannschaften sortiert'!B84</f>
+        <f>'Nach Mannschaften sortiert'!B85</f>
         <v>7</v>
       </c>
       <c r="C56" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C84</f>
+        <f>'Nach Mannschaften sortiert'!C85</f>
         <v>U11</v>
       </c>
       <c r="D56" s="49">
-        <f>'Nach Mannschaften sortiert'!D84</f>
+        <f>'Nach Mannschaften sortiert'!D85</f>
         <v>46069</v>
       </c>
       <c r="E56" s="99">
-        <f>'Nach Mannschaften sortiert'!E84</f>
+        <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="F56" s="48">
-        <f>'Nach Mannschaften sortiert'!F84</f>
+        <f>'Nach Mannschaften sortiert'!F85</f>
         <v>0</v>
       </c>
       <c r="G56" s="48">
-        <f>'Nach Mannschaften sortiert'!G84</f>
+        <f>'Nach Mannschaften sortiert'!G85</f>
         <v>0</v>
       </c>
       <c r="H56" s="48">
-        <f>'Nach Mannschaften sortiert'!H84</f>
+        <f>'Nach Mannschaften sortiert'!H85</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="54">
-        <f>'Nach Mannschaften sortiert'!A81</f>
-        <v>80</v>
+        <f>'Nach Mannschaften sortiert'!A82</f>
+        <v>81</v>
       </c>
       <c r="B57" s="54">
-        <f>'Nach Mannschaften sortiert'!B81</f>
+        <f>'Nach Mannschaften sortiert'!B82</f>
         <v>4</v>
       </c>
       <c r="C57" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C81</f>
+        <f>'Nach Mannschaften sortiert'!C82</f>
         <v>U11</v>
       </c>
       <c r="D57" s="55">
-        <f>'Nach Mannschaften sortiert'!D81</f>
+        <f>'Nach Mannschaften sortiert'!D82</f>
         <v>46066</v>
       </c>
       <c r="E57" s="97">
-        <f>'Nach Mannschaften sortiert'!E81</f>
+        <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="F57" s="54">
-        <f>'Nach Mannschaften sortiert'!F81</f>
+        <f>'Nach Mannschaften sortiert'!F82</f>
         <v>0</v>
       </c>
       <c r="G57" s="54">
-        <f>'Nach Mannschaften sortiert'!G81</f>
+        <f>'Nach Mannschaften sortiert'!G82</f>
         <v>0</v>
       </c>
       <c r="H57" s="54">
-        <f>'Nach Mannschaften sortiert'!H81</f>
+        <f>'Nach Mannschaften sortiert'!H82</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="48">
-        <f>'Nach Mannschaften sortiert'!A21</f>
-        <v>20</v>
+        <f>'Nach Mannschaften sortiert'!A22</f>
+        <v>21</v>
       </c>
       <c r="B58" s="48">
-        <f>'Nach Mannschaften sortiert'!B21</f>
+        <f>'Nach Mannschaften sortiert'!B22</f>
         <v>10</v>
       </c>
       <c r="C58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C21</f>
+        <f>'Nach Mannschaften sortiert'!C22</f>
         <v>KM</v>
       </c>
       <c r="D58" s="49">
-        <f>'Nach Mannschaften sortiert'!D21</f>
+        <f>'Nach Mannschaften sortiert'!D22</f>
         <v>46311</v>
       </c>
       <c r="E58" s="99">
-        <f>'Nach Mannschaften sortiert'!E21</f>
+        <f>'Nach Mannschaften sortiert'!E22</f>
         <v>0.8125</v>
       </c>
       <c r="F58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F21</f>
+        <f>'Nach Mannschaften sortiert'!F22</f>
         <v>Hornstein</v>
       </c>
       <c r="G58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G21</f>
+        <f>'Nach Mannschaften sortiert'!G22</f>
         <v>Hornstein</v>
       </c>
       <c r="H58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H21</f>
+        <f>'Nach Mannschaften sortiert'!H22</f>
         <v>Auswärts</v>
       </c>
     </row>
@@ -12300,137 +12372,137 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="48">
-        <f>'Nach Mannschaften sortiert'!A55</f>
-        <v>54</v>
+        <f>'Nach Mannschaften sortiert'!A56</f>
+        <v>55</v>
       </c>
       <c r="B60" s="48">
-        <f>'Nach Mannschaften sortiert'!B55</f>
+        <f>'Nach Mannschaften sortiert'!B56</f>
         <v>8</v>
       </c>
       <c r="C60" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C55</f>
+        <f>'Nach Mannschaften sortiert'!C56</f>
         <v>U14</v>
       </c>
       <c r="D60" s="49">
-        <f>'Nach Mannschaften sortiert'!D55</f>
+        <f>'Nach Mannschaften sortiert'!D56</f>
         <v>46040</v>
       </c>
       <c r="E60" s="99">
-        <f>'Nach Mannschaften sortiert'!E55</f>
+        <f>'Nach Mannschaften sortiert'!E56</f>
         <v>0</v>
       </c>
       <c r="F60" s="48">
-        <f>'Nach Mannschaften sortiert'!F55</f>
+        <f>'Nach Mannschaften sortiert'!F56</f>
         <v>0</v>
       </c>
       <c r="G60" s="48">
-        <f>'Nach Mannschaften sortiert'!G55</f>
+        <f>'Nach Mannschaften sortiert'!G56</f>
         <v>0</v>
       </c>
       <c r="H60" s="48">
-        <f>'Nach Mannschaften sortiert'!H55</f>
+        <f>'Nach Mannschaften sortiert'!H56</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="54">
-        <f>'Nach Mannschaften sortiert'!A85</f>
-        <v>84</v>
+        <f>'Nach Mannschaften sortiert'!A86</f>
+        <v>85</v>
       </c>
       <c r="B61" s="54">
-        <f>'Nach Mannschaften sortiert'!B85</f>
+        <f>'Nach Mannschaften sortiert'!B86</f>
         <v>8</v>
       </c>
       <c r="C61" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C85</f>
+        <f>'Nach Mannschaften sortiert'!C86</f>
         <v>U11</v>
       </c>
       <c r="D61" s="55">
-        <f>'Nach Mannschaften sortiert'!D85</f>
+        <f>'Nach Mannschaften sortiert'!D86</f>
         <v>46070</v>
       </c>
       <c r="E61" s="97">
-        <f>'Nach Mannschaften sortiert'!E85</f>
+        <f>'Nach Mannschaften sortiert'!E86</f>
         <v>0</v>
       </c>
       <c r="F61" s="54">
-        <f>'Nach Mannschaften sortiert'!F85</f>
+        <f>'Nach Mannschaften sortiert'!F86</f>
         <v>0</v>
       </c>
       <c r="G61" s="54">
-        <f>'Nach Mannschaften sortiert'!G85</f>
+        <f>'Nach Mannschaften sortiert'!G86</f>
         <v>0</v>
       </c>
       <c r="H61" s="54">
-        <f>'Nach Mannschaften sortiert'!H85</f>
+        <f>'Nach Mannschaften sortiert'!H86</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="46">
-        <f>'Nach Mannschaften sortiert'!A56</f>
-        <v>55</v>
+        <f>'Nach Mannschaften sortiert'!A57</f>
+        <v>56</v>
       </c>
       <c r="B62" s="46">
-        <f>'Nach Mannschaften sortiert'!B56</f>
+        <f>'Nach Mannschaften sortiert'!B57</f>
         <v>9</v>
       </c>
       <c r="C62" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C56</f>
+        <f>'Nach Mannschaften sortiert'!C57</f>
         <v>U14</v>
       </c>
       <c r="D62" s="47">
-        <f>'Nach Mannschaften sortiert'!D56</f>
+        <f>'Nach Mannschaften sortiert'!D57</f>
         <v>46041</v>
       </c>
       <c r="E62" s="100">
-        <f>'Nach Mannschaften sortiert'!E56</f>
+        <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
       <c r="F62" s="46">
-        <f>'Nach Mannschaften sortiert'!F56</f>
+        <f>'Nach Mannschaften sortiert'!F57</f>
         <v>0</v>
       </c>
       <c r="G62" s="46">
-        <f>'Nach Mannschaften sortiert'!G56</f>
+        <f>'Nach Mannschaften sortiert'!G57</f>
         <v>0</v>
       </c>
       <c r="H62" s="46">
-        <f>'Nach Mannschaften sortiert'!H56</f>
+        <f>'Nach Mannschaften sortiert'!H57</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="54">
-        <f>'Nach Mannschaften sortiert'!A87</f>
-        <v>86</v>
+        <f>'Nach Mannschaften sortiert'!A88</f>
+        <v>87</v>
       </c>
       <c r="B63" s="54">
-        <f>'Nach Mannschaften sortiert'!B87</f>
+        <f>'Nach Mannschaften sortiert'!B88</f>
         <v>10</v>
       </c>
       <c r="C63" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C87</f>
+        <f>'Nach Mannschaften sortiert'!C88</f>
         <v>U11</v>
       </c>
       <c r="D63" s="55">
-        <f>'Nach Mannschaften sortiert'!D87</f>
+        <f>'Nach Mannschaften sortiert'!D88</f>
         <v>46072</v>
       </c>
       <c r="E63" s="97">
-        <f>'Nach Mannschaften sortiert'!E87</f>
+        <f>'Nach Mannschaften sortiert'!E88</f>
         <v>0</v>
       </c>
       <c r="F63" s="54">
-        <f>'Nach Mannschaften sortiert'!F87</f>
+        <f>'Nach Mannschaften sortiert'!F88</f>
         <v>0</v>
       </c>
       <c r="G63" s="54">
-        <f>'Nach Mannschaften sortiert'!G87</f>
+        <f>'Nach Mannschaften sortiert'!G88</f>
         <v>0</v>
       </c>
       <c r="H63" s="54">
-        <f>'Nach Mannschaften sortiert'!H87</f>
+        <f>'Nach Mannschaften sortiert'!H88</f>
         <v>0</v>
       </c>
     </row>
@@ -12470,15 +12542,15 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="48">
-        <f>'Nach Mannschaften sortiert'!A86</f>
-        <v>85</v>
+        <f>'Nach Mannschaften sortiert'!A87</f>
+        <v>86</v>
       </c>
       <c r="B65" s="48">
-        <f>'Nach Mannschaften sortiert'!B86</f>
+        <f>'Nach Mannschaften sortiert'!B87</f>
         <v>9</v>
       </c>
       <c r="C65" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C86</f>
+        <f>'Nach Mannschaften sortiert'!C87</f>
         <v>U11</v>
       </c>
       <c r="D65" s="49">
@@ -12488,525 +12560,525 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F65" s="48">
-        <f>'Nach Mannschaften sortiert'!F86</f>
+        <f>'Nach Mannschaften sortiert'!F87</f>
         <v>0</v>
       </c>
       <c r="G65" s="48">
-        <f>'Nach Mannschaften sortiert'!G86</f>
+        <f>'Nach Mannschaften sortiert'!G87</f>
         <v>0</v>
       </c>
       <c r="H65" s="48">
-        <f>'Nach Mannschaften sortiert'!H86</f>
+        <f>'Nach Mannschaften sortiert'!H87</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="54">
-        <f>'Nach Mannschaften sortiert'!A94</f>
-        <v>93</v>
+        <f>'Nach Mannschaften sortiert'!A95</f>
+        <v>94</v>
       </c>
       <c r="B66" s="54">
-        <f>'Nach Mannschaften sortiert'!B94</f>
+        <f>'Nach Mannschaften sortiert'!B95</f>
         <v>2</v>
       </c>
       <c r="C66" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C94</f>
+        <f>'Nach Mannschaften sortiert'!C95</f>
         <v>U9</v>
       </c>
       <c r="D66" s="55">
-        <f>'Nach Mannschaften sortiert'!D94</f>
+        <f>'Nach Mannschaften sortiert'!D95</f>
         <v>46079</v>
       </c>
       <c r="E66" s="97">
-        <f>'Nach Mannschaften sortiert'!E94</f>
+        <f>'Nach Mannschaften sortiert'!E95</f>
         <v>0</v>
       </c>
       <c r="F66" s="54">
-        <f>'Nach Mannschaften sortiert'!F94</f>
+        <f>'Nach Mannschaften sortiert'!F95</f>
         <v>0</v>
       </c>
       <c r="G66" s="54">
-        <f>'Nach Mannschaften sortiert'!G94</f>
+        <f>'Nach Mannschaften sortiert'!G95</f>
         <v>0</v>
       </c>
       <c r="H66" s="54">
-        <f>'Nach Mannschaften sortiert'!H94</f>
+        <f>'Nach Mannschaften sortiert'!H95</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="54">
-        <f>'Nach Mannschaften sortiert'!A95</f>
-        <v>94</v>
+        <f>'Nach Mannschaften sortiert'!A96</f>
+        <v>95</v>
       </c>
       <c r="B67" s="54">
-        <f>'Nach Mannschaften sortiert'!B95</f>
+        <f>'Nach Mannschaften sortiert'!B96</f>
         <v>3</v>
       </c>
       <c r="C67" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C95</f>
+        <f>'Nach Mannschaften sortiert'!C96</f>
         <v>U9</v>
       </c>
       <c r="D67" s="55">
-        <f>'Nach Mannschaften sortiert'!D95</f>
+        <f>'Nach Mannschaften sortiert'!D96</f>
         <v>46080</v>
       </c>
       <c r="E67" s="97">
-        <f>'Nach Mannschaften sortiert'!E95</f>
+        <f>'Nach Mannschaften sortiert'!E96</f>
         <v>0</v>
       </c>
       <c r="F67" s="54">
-        <f>'Nach Mannschaften sortiert'!F95</f>
+        <f>'Nach Mannschaften sortiert'!F96</f>
         <v>0</v>
       </c>
       <c r="G67" s="54">
-        <f>'Nach Mannschaften sortiert'!G95</f>
+        <f>'Nach Mannschaften sortiert'!G96</f>
         <v>0</v>
       </c>
       <c r="H67" s="54">
-        <f>'Nach Mannschaften sortiert'!H95</f>
+        <f>'Nach Mannschaften sortiert'!H96</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="54">
-        <f>'Nach Mannschaften sortiert'!A96</f>
-        <v>95</v>
+        <f>'Nach Mannschaften sortiert'!A97</f>
+        <v>96</v>
       </c>
       <c r="B68" s="54">
-        <f>'Nach Mannschaften sortiert'!B96</f>
+        <f>'Nach Mannschaften sortiert'!B97</f>
         <v>4</v>
       </c>
       <c r="C68" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C96</f>
+        <f>'Nach Mannschaften sortiert'!C97</f>
         <v>U9</v>
       </c>
       <c r="D68" s="55">
-        <f>'Nach Mannschaften sortiert'!D96</f>
+        <f>'Nach Mannschaften sortiert'!D97</f>
         <v>46081</v>
       </c>
       <c r="E68" s="97">
-        <f>'Nach Mannschaften sortiert'!E96</f>
+        <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="F68" s="54">
-        <f>'Nach Mannschaften sortiert'!F96</f>
+        <f>'Nach Mannschaften sortiert'!F97</f>
         <v>0</v>
       </c>
       <c r="G68" s="54">
-        <f>'Nach Mannschaften sortiert'!G96</f>
+        <f>'Nach Mannschaften sortiert'!G97</f>
         <v>0</v>
       </c>
       <c r="H68" s="54">
-        <f>'Nach Mannschaften sortiert'!H96</f>
+        <f>'Nach Mannschaften sortiert'!H97</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="54">
-        <f>'Nach Mannschaften sortiert'!A102</f>
-        <v>101</v>
+        <f>'Nach Mannschaften sortiert'!A103</f>
+        <v>102</v>
       </c>
       <c r="B69" s="54">
-        <f>'Nach Mannschaften sortiert'!B102</f>
+        <f>'Nach Mannschaften sortiert'!B103</f>
         <v>10</v>
       </c>
       <c r="C69" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C102</f>
+        <f>'Nach Mannschaften sortiert'!C103</f>
         <v>U9</v>
       </c>
       <c r="D69" s="55">
-        <f>'Nach Mannschaften sortiert'!D102</f>
+        <f>'Nach Mannschaften sortiert'!D103</f>
         <v>46087</v>
       </c>
       <c r="E69" s="97">
-        <f>'Nach Mannschaften sortiert'!E102</f>
+        <f>'Nach Mannschaften sortiert'!E103</f>
         <v>0</v>
       </c>
       <c r="F69" s="54">
-        <f>'Nach Mannschaften sortiert'!F102</f>
+        <f>'Nach Mannschaften sortiert'!F103</f>
         <v>0</v>
       </c>
       <c r="G69" s="54">
-        <f>'Nach Mannschaften sortiert'!G102</f>
+        <f>'Nach Mannschaften sortiert'!G103</f>
         <v>0</v>
       </c>
       <c r="H69" s="54">
-        <f>'Nach Mannschaften sortiert'!H102</f>
+        <f>'Nach Mannschaften sortiert'!H103</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="48">
-        <f>'Nach Mannschaften sortiert'!A63</f>
-        <v>62</v>
+        <f>'Nach Mannschaften sortiert'!A64</f>
+        <v>63</v>
       </c>
       <c r="B70" s="48">
-        <f>'Nach Mannschaften sortiert'!B63</f>
+        <f>'Nach Mannschaften sortiert'!B64</f>
         <v>6</v>
       </c>
       <c r="C70" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C63</f>
+        <f>'Nach Mannschaften sortiert'!C64</f>
         <v>U12_1</v>
       </c>
       <c r="D70" s="49">
-        <f>'Nach Mannschaften sortiert'!D63</f>
+        <f>'Nach Mannschaften sortiert'!D64</f>
         <v>46048</v>
       </c>
       <c r="E70" s="99">
-        <f>'Nach Mannschaften sortiert'!E63</f>
+        <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="F70" s="48">
-        <f>'Nach Mannschaften sortiert'!F63</f>
+        <f>'Nach Mannschaften sortiert'!F64</f>
         <v>0</v>
       </c>
       <c r="G70" s="48">
-        <f>'Nach Mannschaften sortiert'!G63</f>
+        <f>'Nach Mannschaften sortiert'!G64</f>
         <v>0</v>
       </c>
       <c r="H70" s="48">
-        <f>'Nach Mannschaften sortiert'!H63</f>
+        <f>'Nach Mannschaften sortiert'!H64</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="54">
-        <f>'Nach Mannschaften sortiert'!A104</f>
-        <v>103</v>
+        <f>'Nach Mannschaften sortiert'!A105</f>
+        <v>104</v>
       </c>
       <c r="B71" s="54">
-        <f>'Nach Mannschaften sortiert'!B104</f>
+        <f>'Nach Mannschaften sortiert'!B105</f>
         <v>2</v>
       </c>
       <c r="C71" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C104</f>
+        <f>'Nach Mannschaften sortiert'!C105</f>
         <v>U8</v>
       </c>
       <c r="D71" s="55">
-        <f>'Nach Mannschaften sortiert'!D104</f>
+        <f>'Nach Mannschaften sortiert'!D105</f>
         <v>46089</v>
       </c>
       <c r="E71" s="97">
-        <f>'Nach Mannschaften sortiert'!E104</f>
+        <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="F71" s="54">
-        <f>'Nach Mannschaften sortiert'!F104</f>
+        <f>'Nach Mannschaften sortiert'!F105</f>
         <v>0</v>
       </c>
       <c r="G71" s="54">
-        <f>'Nach Mannschaften sortiert'!G104</f>
+        <f>'Nach Mannschaften sortiert'!G105</f>
         <v>0</v>
       </c>
       <c r="H71" s="54">
-        <f>'Nach Mannschaften sortiert'!H104</f>
+        <f>'Nach Mannschaften sortiert'!H105</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="54">
-        <f>'Nach Mannschaften sortiert'!A105</f>
-        <v>104</v>
+        <f>'Nach Mannschaften sortiert'!A106</f>
+        <v>105</v>
       </c>
       <c r="B72" s="54">
-        <f>'Nach Mannschaften sortiert'!B105</f>
+        <f>'Nach Mannschaften sortiert'!B106</f>
         <v>3</v>
       </c>
       <c r="C72" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C105</f>
+        <f>'Nach Mannschaften sortiert'!C106</f>
         <v>U8</v>
       </c>
       <c r="D72" s="55">
-        <f>'Nach Mannschaften sortiert'!D105</f>
+        <f>'Nach Mannschaften sortiert'!D106</f>
         <v>46090</v>
       </c>
       <c r="E72" s="97">
-        <f>'Nach Mannschaften sortiert'!E105</f>
+        <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="F72" s="54">
-        <f>'Nach Mannschaften sortiert'!F105</f>
+        <f>'Nach Mannschaften sortiert'!F106</f>
         <v>0</v>
       </c>
       <c r="G72" s="54">
-        <f>'Nach Mannschaften sortiert'!G105</f>
+        <f>'Nach Mannschaften sortiert'!G106</f>
         <v>0</v>
       </c>
       <c r="H72" s="54">
-        <f>'Nach Mannschaften sortiert'!H105</f>
+        <f>'Nach Mannschaften sortiert'!H106</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="54">
-        <f>'Nach Mannschaften sortiert'!A106</f>
-        <v>105</v>
+        <f>'Nach Mannschaften sortiert'!A107</f>
+        <v>106</v>
       </c>
       <c r="B73" s="54">
-        <f>'Nach Mannschaften sortiert'!B106</f>
+        <f>'Nach Mannschaften sortiert'!B107</f>
         <v>4</v>
       </c>
       <c r="C73" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C106</f>
+        <f>'Nach Mannschaften sortiert'!C107</f>
         <v>U8</v>
       </c>
       <c r="D73" s="55">
-        <f>'Nach Mannschaften sortiert'!D106</f>
+        <f>'Nach Mannschaften sortiert'!D107</f>
         <v>46091</v>
       </c>
       <c r="E73" s="97">
-        <f>'Nach Mannschaften sortiert'!E106</f>
+        <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="F73" s="54">
-        <f>'Nach Mannschaften sortiert'!F106</f>
+        <f>'Nach Mannschaften sortiert'!F107</f>
         <v>0</v>
       </c>
       <c r="G73" s="54">
-        <f>'Nach Mannschaften sortiert'!G106</f>
+        <f>'Nach Mannschaften sortiert'!G107</f>
         <v>0</v>
       </c>
       <c r="H73" s="54">
-        <f>'Nach Mannschaften sortiert'!H106</f>
+        <f>'Nach Mannschaften sortiert'!H107</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="54">
-        <f>'Nach Mannschaften sortiert'!A107</f>
-        <v>106</v>
+        <f>'Nach Mannschaften sortiert'!A108</f>
+        <v>107</v>
       </c>
       <c r="B74" s="54">
-        <f>'Nach Mannschaften sortiert'!B107</f>
+        <f>'Nach Mannschaften sortiert'!B108</f>
         <v>5</v>
       </c>
       <c r="C74" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C107</f>
+        <f>'Nach Mannschaften sortiert'!C108</f>
         <v>U8</v>
       </c>
       <c r="D74" s="55">
-        <f>'Nach Mannschaften sortiert'!D107</f>
+        <f>'Nach Mannschaften sortiert'!D108</f>
         <v>46092</v>
       </c>
       <c r="E74" s="97">
-        <f>'Nach Mannschaften sortiert'!E107</f>
+        <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="F74" s="54">
-        <f>'Nach Mannschaften sortiert'!F107</f>
+        <f>'Nach Mannschaften sortiert'!F108</f>
         <v>0</v>
       </c>
       <c r="G74" s="54">
-        <f>'Nach Mannschaften sortiert'!G107</f>
+        <f>'Nach Mannschaften sortiert'!G108</f>
         <v>0</v>
       </c>
       <c r="H74" s="54">
-        <f>'Nach Mannschaften sortiert'!H107</f>
+        <f>'Nach Mannschaften sortiert'!H108</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="48">
-        <f>'Nach Mannschaften sortiert'!A24</f>
-        <v>23</v>
+        <f>'Nach Mannschaften sortiert'!A25</f>
+        <v>24</v>
       </c>
       <c r="B75" s="48">
-        <f>'Nach Mannschaften sortiert'!B24</f>
+        <f>'Nach Mannschaften sortiert'!B25</f>
         <v>13</v>
       </c>
       <c r="C75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C24</f>
+        <f>'Nach Mannschaften sortiert'!C25</f>
         <v>KM</v>
       </c>
       <c r="D75" s="49">
-        <f>'Nach Mannschaften sortiert'!D24</f>
+        <f>'Nach Mannschaften sortiert'!D25</f>
         <v>46333</v>
       </c>
       <c r="E75" s="99">
-        <f>'Nach Mannschaften sortiert'!E24</f>
+        <f>'Nach Mannschaften sortiert'!E25</f>
         <v>0.6875</v>
       </c>
       <c r="F75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F24</f>
+        <f>'Nach Mannschaften sortiert'!F25</f>
         <v>Neufeld</v>
       </c>
       <c r="G75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G24</f>
+        <f>'Nach Mannschaften sortiert'!G25</f>
         <v>Andau</v>
       </c>
       <c r="H75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H24</f>
+        <f>'Nach Mannschaften sortiert'!H25</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="54">
-        <f>'Nach Mannschaften sortiert'!A109</f>
-        <v>108</v>
+        <f>'Nach Mannschaften sortiert'!A110</f>
+        <v>109</v>
       </c>
       <c r="B76" s="54">
-        <f>'Nach Mannschaften sortiert'!B109</f>
+        <f>'Nach Mannschaften sortiert'!B110</f>
         <v>2</v>
       </c>
       <c r="C76" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C109</f>
+        <f>'Nach Mannschaften sortiert'!C110</f>
         <v>U7</v>
       </c>
       <c r="D76" s="55">
-        <f>'Nach Mannschaften sortiert'!D109</f>
+        <f>'Nach Mannschaften sortiert'!D110</f>
         <v>46094</v>
       </c>
       <c r="E76" s="97">
-        <f>'Nach Mannschaften sortiert'!E109</f>
+        <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="F76" s="54">
-        <f>'Nach Mannschaften sortiert'!F109</f>
+        <f>'Nach Mannschaften sortiert'!F110</f>
         <v>0</v>
       </c>
       <c r="G76" s="54">
-        <f>'Nach Mannschaften sortiert'!G109</f>
+        <f>'Nach Mannschaften sortiert'!G110</f>
         <v>0</v>
       </c>
       <c r="H76" s="54">
-        <f>'Nach Mannschaften sortiert'!H109</f>
+        <f>'Nach Mannschaften sortiert'!H110</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="54">
-        <f>'Nach Mannschaften sortiert'!A110</f>
-        <v>109</v>
+        <f>'Nach Mannschaften sortiert'!A111</f>
+        <v>110</v>
       </c>
       <c r="B77" s="54">
-        <f>'Nach Mannschaften sortiert'!B110</f>
+        <f>'Nach Mannschaften sortiert'!B111</f>
         <v>3</v>
       </c>
       <c r="C77" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C110</f>
+        <f>'Nach Mannschaften sortiert'!C111</f>
         <v>U7</v>
       </c>
       <c r="D77" s="55">
-        <f>'Nach Mannschaften sortiert'!D110</f>
+        <f>'Nach Mannschaften sortiert'!D111</f>
         <v>46095</v>
       </c>
       <c r="E77" s="97">
-        <f>'Nach Mannschaften sortiert'!E110</f>
+        <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="F77" s="54">
-        <f>'Nach Mannschaften sortiert'!F110</f>
+        <f>'Nach Mannschaften sortiert'!F111</f>
         <v>0</v>
       </c>
       <c r="G77" s="54">
-        <f>'Nach Mannschaften sortiert'!G110</f>
+        <f>'Nach Mannschaften sortiert'!G111</f>
         <v>0</v>
       </c>
       <c r="H77" s="54">
-        <f>'Nach Mannschaften sortiert'!H110</f>
+        <f>'Nach Mannschaften sortiert'!H111</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="54">
-        <f>'Nach Mannschaften sortiert'!A111</f>
-        <v>110</v>
+        <f>'Nach Mannschaften sortiert'!A112</f>
+        <v>111</v>
       </c>
       <c r="B78" s="54">
-        <f>'Nach Mannschaften sortiert'!B111</f>
+        <f>'Nach Mannschaften sortiert'!B112</f>
         <v>4</v>
       </c>
       <c r="C78" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C111</f>
+        <f>'Nach Mannschaften sortiert'!C112</f>
         <v>U7</v>
       </c>
       <c r="D78" s="55">
-        <f>'Nach Mannschaften sortiert'!D111</f>
+        <f>'Nach Mannschaften sortiert'!D112</f>
         <v>46096</v>
       </c>
       <c r="E78" s="97">
-        <f>'Nach Mannschaften sortiert'!E111</f>
+        <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="F78" s="54">
-        <f>'Nach Mannschaften sortiert'!F111</f>
+        <f>'Nach Mannschaften sortiert'!F112</f>
         <v>0</v>
       </c>
       <c r="G78" s="54">
-        <f>'Nach Mannschaften sortiert'!G111</f>
+        <f>'Nach Mannschaften sortiert'!G112</f>
         <v>0</v>
       </c>
       <c r="H78" s="54">
-        <f>'Nach Mannschaften sortiert'!H111</f>
+        <f>'Nach Mannschaften sortiert'!H112</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="54">
-        <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>111</v>
+        <f>'Nach Mannschaften sortiert'!A113</f>
+        <v>112</v>
       </c>
       <c r="B79" s="54">
-        <f>'Nach Mannschaften sortiert'!B112</f>
+        <f>'Nach Mannschaften sortiert'!B113</f>
         <v>5</v>
       </c>
       <c r="C79" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C112</f>
+        <f>'Nach Mannschaften sortiert'!C113</f>
         <v>U7</v>
       </c>
       <c r="D79" s="55">
-        <f>'Nach Mannschaften sortiert'!D112</f>
+        <f>'Nach Mannschaften sortiert'!D113</f>
         <v>46097</v>
       </c>
       <c r="E79" s="97">
-        <f>'Nach Mannschaften sortiert'!E112</f>
+        <f>'Nach Mannschaften sortiert'!E113</f>
         <v>0</v>
       </c>
       <c r="F79" s="54">
-        <f>'Nach Mannschaften sortiert'!F112</f>
+        <f>'Nach Mannschaften sortiert'!F113</f>
         <v>0</v>
       </c>
       <c r="G79" s="54">
-        <f>'Nach Mannschaften sortiert'!G112</f>
+        <f>'Nach Mannschaften sortiert'!G113</f>
         <v>0</v>
       </c>
       <c r="H79" s="54">
-        <f>'Nach Mannschaften sortiert'!H112</f>
+        <f>'Nach Mannschaften sortiert'!H113</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="48">
-        <f>'Nach Mannschaften sortiert'!A65</f>
-        <v>64</v>
+        <f>'Nach Mannschaften sortiert'!A66</f>
+        <v>65</v>
       </c>
       <c r="B80" s="48">
-        <f>'Nach Mannschaften sortiert'!B65</f>
+        <f>'Nach Mannschaften sortiert'!B66</f>
         <v>8</v>
       </c>
       <c r="C80" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C65</f>
+        <f>'Nach Mannschaften sortiert'!C66</f>
         <v>U12_1</v>
       </c>
       <c r="D80" s="49">
-        <f>'Nach Mannschaften sortiert'!D65</f>
+        <f>'Nach Mannschaften sortiert'!D66</f>
         <v>46050</v>
       </c>
       <c r="E80" s="99">
-        <f>'Nach Mannschaften sortiert'!E65</f>
+        <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="F80" s="48">
-        <f>'Nach Mannschaften sortiert'!F65</f>
+        <f>'Nach Mannschaften sortiert'!F66</f>
         <v>0</v>
       </c>
       <c r="G80" s="48">
-        <f>'Nach Mannschaften sortiert'!G65</f>
+        <f>'Nach Mannschaften sortiert'!G66</f>
         <v>0</v>
       </c>
       <c r="H80" s="48">
-        <f>'Nach Mannschaften sortiert'!H65</f>
+        <f>'Nach Mannschaften sortiert'!H66</f>
         <v>0</v>
       </c>
     </row>
@@ -13046,35 +13118,35 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="48">
-        <f>'Nach Mannschaften sortiert'!A47</f>
-        <v>46</v>
+        <f>'Nach Mannschaften sortiert'!A48</f>
+        <v>47</v>
       </c>
       <c r="B82" s="48">
-        <f>'Nach Mannschaften sortiert'!B47</f>
+        <f>'Nach Mannschaften sortiert'!B48</f>
         <v>10</v>
       </c>
       <c r="C82" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C47</f>
+        <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U16</v>
       </c>
       <c r="D82" s="49">
-        <f>'Nach Mannschaften sortiert'!D47</f>
+        <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46032</v>
       </c>
       <c r="E82" s="99">
-        <f>'Nach Mannschaften sortiert'!E47</f>
+        <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="F82" s="48">
-        <f>'Nach Mannschaften sortiert'!F47</f>
+        <f>'Nach Mannschaften sortiert'!F48</f>
         <v>0</v>
       </c>
       <c r="G82" s="48">
-        <f>'Nach Mannschaften sortiert'!G47</f>
+        <f>'Nach Mannschaften sortiert'!G48</f>
         <v>0</v>
       </c>
       <c r="H82" s="48">
-        <f>'Nach Mannschaften sortiert'!H47</f>
+        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
@@ -13114,35 +13186,35 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="54">
-        <f>'Nach Mannschaften sortiert'!A124</f>
-        <v>123</v>
+        <f>'Nach Mannschaften sortiert'!A125</f>
+        <v>124</v>
       </c>
       <c r="B84" s="54">
-        <f>'Nach Mannschaften sortiert'!B124</f>
+        <f>'Nach Mannschaften sortiert'!B125</f>
         <v>2</v>
       </c>
       <c r="C84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C124</f>
+        <f>'Nach Mannschaften sortiert'!C125</f>
         <v>GGG</v>
       </c>
       <c r="D84" s="55">
-        <f>'Nach Mannschaften sortiert'!D124</f>
+        <f>'Nach Mannschaften sortiert'!D125</f>
         <v>46256</v>
       </c>
       <c r="E84" s="97">
-        <f>'Nach Mannschaften sortiert'!E124</f>
+        <f>'Nach Mannschaften sortiert'!E125</f>
         <v>0.375</v>
       </c>
       <c r="F84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F124</f>
+        <f>'Nach Mannschaften sortiert'!F125</f>
         <v>Neufeld</v>
       </c>
       <c r="G84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G124</f>
+        <f>'Nach Mannschaften sortiert'!G125</f>
         <v>viele Gegner</v>
       </c>
       <c r="H84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H124</f>
+        <f>'Nach Mannschaften sortiert'!H125</f>
         <v>Heim</v>
       </c>
     </row>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAF5A63-045D-422F-8A21-9C1B539AA491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEF4EBA-BC90-4BDA-AB93-94A2B872D05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="175">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -567,6 +567,12 @@
   </si>
   <si>
     <t>Sommerein</t>
+  </si>
+  <si>
+    <t>Wiener Neustadt</t>
+  </si>
+  <si>
+    <t>Admira Wiener Neustadt</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1072,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1332,6 +1338,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -1571,7 +1578,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="54" bestFit="1" customWidth="1"/>
@@ -1638,7 +1645,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f t="shared" ref="A3:A37" si="0">A2+1</f>
+        <f t="shared" ref="A3:A38" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="5">
@@ -1744,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" s="113" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1753,19 +1760,19 @@
         <v>0</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D7" s="9">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="E7" s="93">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>15</v>
@@ -1783,19 +1790,19 @@
         <v>13</v>
       </c>
       <c r="D8" s="9">
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="E8" s="93">
-        <v>0.79166666666666663</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1807,22 +1814,22 @@
         <v>0</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="9">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="E9" s="93">
-        <v>0.45833333333333331</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1834,25 +1841,25 @@
         <v>0</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="9">
-        <v>46217</v>
+        <v>46243</v>
       </c>
       <c r="E10" s="93">
-        <v>0.8125</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="110" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="54">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1861,25 +1868,25 @@
         <v>0</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="9">
-        <v>46236</v>
+        <v>46217</v>
       </c>
       <c r="E11" s="93">
-        <v>0.4375</v>
+        <v>0.8125</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="110" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1891,22 +1898,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="9">
-        <v>46260</v>
+        <v>46236</v>
       </c>
       <c r="E12" s="93">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>170</v>
+        <v>23</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="111" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="54">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1915,48 +1922,48 @@
         <v>0</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="9">
-        <v>46445</v>
+        <v>46260</v>
       </c>
       <c r="E13" s="93">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="54">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="4">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="10">
-        <v>46250</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="D14" s="9">
+        <v>46445</v>
+      </c>
+      <c r="E14" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1966,22 +1973,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E15" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>15</v>
@@ -1993,25 +2000,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E16" s="3">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -2020,25 +2027,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E17" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -2047,25 +2054,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E18" s="3">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -2074,25 +2081,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E19" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -2101,25 +2108,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E20" s="3">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2128,25 +2135,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="10">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="E21" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -2155,25 +2162,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="10">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="E22" s="3">
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -2182,25 +2189,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E23" s="3">
         <v>0.8125</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -2209,25 +2216,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E24" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -2236,25 +2243,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E25" s="3">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -2263,25 +2270,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E26" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2290,25 +2297,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D27" s="10">
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="E27" s="3">
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -2317,22 +2324,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E28" s="3">
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>15</v>
@@ -2344,25 +2351,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D29" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E29" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -2371,25 +2378,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D30" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E30" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2398,25 +2405,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E31" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -2425,25 +2432,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D32" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E32" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -2452,25 +2459,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E33" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -2479,25 +2486,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D34" s="10">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="E34" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -2506,25 +2513,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="10">
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="E35" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -2533,25 +2540,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D36" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E36" s="3">
         <v>0.72916666666666663</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -2560,99 +2567,107 @@
         <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D37" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E37" s="3">
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <f t="shared" ref="A38:A69" si="1">A37+1</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D38" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E38" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A39:A70" si="1">A38+1</f>
         <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D39" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E39" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="21">
+      <c r="A40" s="4">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B40" s="21">
-        <v>1</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="28">
-        <v>46023</v>
-      </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
+      <c r="B40" s="4">
+        <v>13</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="10">
+        <v>46333</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="21">
@@ -2660,13 +2675,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D41" s="28">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="21"/>
@@ -2679,13 +2694,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="28">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="21"/>
@@ -2698,13 +2713,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="28">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="21"/>
@@ -2717,13 +2732,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="28">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="21"/>
@@ -2736,13 +2751,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="28">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="21"/>
@@ -2755,13 +2770,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="28">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="21"/>
@@ -2774,13 +2789,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D47" s="28">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="21"/>
@@ -2793,13 +2808,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="28">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="21"/>
@@ -2812,58 +2827,57 @@
         <v>48</v>
       </c>
       <c r="B49" s="21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="28">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="21"/>
       <c r="G49" s="21"/>
       <c r="H49" s="21"/>
     </row>
-    <row r="50" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="18">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="21">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B50" s="13">
-        <v>1</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="14">
-        <v>46033</v>
-      </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="17"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B50" s="21">
+        <v>10</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="28">
+        <v>46032</v>
+      </c>
+      <c r="E50" s="22"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+    </row>
+    <row r="51" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="18">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="B51" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D51" s="14">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
-      <c r="I51" s="16"/>
+      <c r="I51" s="17"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="18">
@@ -2871,13 +2885,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D52" s="14">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="13"/>
@@ -2891,13 +2905,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D53" s="14">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="13"/>
@@ -2911,13 +2925,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D54" s="14">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="13"/>
@@ -2931,13 +2945,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D55" s="14">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="13"/>
@@ -2951,13 +2965,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="14">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="13"/>
@@ -2971,13 +2985,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D57" s="14">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="13"/>
@@ -2991,13 +3005,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D58" s="14">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="13"/>
@@ -3011,13 +3025,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D59" s="14">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="13"/>
@@ -3026,23 +3040,24 @@
       <c r="I59" s="16"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="6">
+      <c r="A60" s="18">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="B60" s="6">
-        <v>1</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D60" s="23">
-        <v>46043</v>
-      </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
+      <c r="B60" s="13">
+        <v>10</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="14">
+        <v>46042</v>
+      </c>
+      <c r="E60" s="15"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="16"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
@@ -3050,13 +3065,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D61" s="23">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="6"/>
@@ -3069,13 +3084,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D62" s="23">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="6"/>
@@ -3088,13 +3103,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D63" s="23">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="6"/>
@@ -3107,13 +3122,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D64" s="23">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="6"/>
@@ -3126,13 +3141,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D65" s="23">
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="6"/>
@@ -3145,13 +3160,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D66" s="23">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="6"/>
@@ -3164,13 +3179,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D67" s="23">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="6"/>
@@ -3183,13 +3198,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D68" s="23">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="6"/>
@@ -3202,13 +3217,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D69" s="23">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="6"/>
@@ -3216,37 +3231,37 @@
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="90">
-        <f t="shared" ref="A70:A101" si="2">A69+1</f>
+      <c r="A70" s="6">
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B70" s="90">
-        <v>1</v>
-      </c>
-      <c r="C70" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="D70" s="91">
-        <v>46053</v>
-      </c>
-      <c r="E70" s="92"/>
-      <c r="F70" s="90"/>
-      <c r="G70" s="90"/>
-      <c r="H70" s="90"/>
+      <c r="B70" s="6">
+        <v>10</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="23">
+        <v>46052</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A71:A102" si="2">A70+1</f>
         <v>70</v>
       </c>
       <c r="B71" s="90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="91">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="E71" s="92"/>
       <c r="F71" s="90"/>
@@ -3259,13 +3274,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D72" s="91">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="E72" s="92"/>
       <c r="F72" s="90"/>
@@ -3278,13 +3293,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D73" s="91">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="E73" s="92"/>
       <c r="F73" s="90"/>
@@ -3297,13 +3312,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="91">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="E74" s="92"/>
       <c r="F74" s="90"/>
@@ -3316,13 +3331,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C75" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="91">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="E75" s="92"/>
       <c r="F75" s="90"/>
@@ -3335,13 +3350,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C76" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="91">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="E76" s="92"/>
       <c r="F76" s="90"/>
@@ -3354,13 +3369,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C77" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D77" s="91">
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="E77" s="92"/>
       <c r="F77" s="90"/>
@@ -3373,13 +3388,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="90">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C78" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D78" s="91">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="E78" s="92"/>
       <c r="F78" s="90"/>
@@ -3392,13 +3407,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="90">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C79" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D79" s="91">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="E79" s="92"/>
       <c r="F79" s="90"/>
@@ -3406,23 +3421,23 @@
       <c r="H79" s="90"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="19">
+      <c r="A80" s="90">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="B80" s="19">
-        <v>1</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D80" s="24">
-        <v>46063</v>
-      </c>
-      <c r="E80" s="20"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
+      <c r="B80" s="90">
+        <v>10</v>
+      </c>
+      <c r="C80" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="91">
+        <v>46062</v>
+      </c>
+      <c r="E80" s="92"/>
+      <c r="F80" s="90"/>
+      <c r="G80" s="90"/>
+      <c r="H80" s="90"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
@@ -3430,13 +3445,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D81" s="24">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="E81" s="20"/>
       <c r="F81" s="19"/>
@@ -3449,13 +3464,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D82" s="24">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="E82" s="20"/>
       <c r="F82" s="19"/>
@@ -3468,13 +3483,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C83" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D83" s="24">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="E83" s="20"/>
       <c r="F83" s="19"/>
@@ -3487,13 +3502,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D84" s="24">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="E84" s="20"/>
       <c r="F84" s="19"/>
@@ -3506,13 +3521,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D85" s="24">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="E85" s="20"/>
       <c r="F85" s="19"/>
@@ -3525,13 +3540,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C86" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D86" s="24">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="E86" s="20"/>
       <c r="F86" s="19"/>
@@ -3544,13 +3559,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C87" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="24">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="E87" s="20"/>
       <c r="F87" s="19"/>
@@ -3563,13 +3578,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C88" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D88" s="24">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E88" s="20"/>
       <c r="F88" s="19"/>
@@ -3582,13 +3597,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C89" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D89" s="24">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E89" s="20"/>
       <c r="F89" s="19"/>
@@ -3596,31 +3611,23 @@
       <c r="H89" s="19"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="87">
+      <c r="A90" s="19">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="B90" s="87">
-        <v>1</v>
-      </c>
-      <c r="C90" s="87" t="s">
-        <v>40</v>
-      </c>
-      <c r="D90" s="88">
-        <v>46312</v>
-      </c>
-      <c r="E90" s="89">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F90" s="89" t="s">
-        <v>19</v>
-      </c>
-      <c r="G90" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="H90" s="87" t="s">
-        <v>11</v>
-      </c>
+      <c r="B90" s="19">
+        <v>10</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D90" s="24">
+        <v>46072</v>
+      </c>
+      <c r="E90" s="20"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="19"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="87">
@@ -3628,18 +3635,26 @@
         <v>90</v>
       </c>
       <c r="B91" s="87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D91" s="88">
-        <v>46074</v>
-      </c>
-      <c r="E91" s="89"/>
-      <c r="F91" s="87"/>
-      <c r="G91" s="87"/>
-      <c r="H91" s="87"/>
+        <v>46312</v>
+      </c>
+      <c r="E91" s="89">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F91" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="H91" s="87" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="87">
@@ -3647,13 +3662,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D92" s="88">
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="E92" s="89"/>
       <c r="F92" s="87"/>
@@ -3666,13 +3681,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D93" s="88">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="E93" s="89"/>
       <c r="F93" s="87"/>
@@ -3685,13 +3700,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D94" s="88">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="E94" s="89"/>
       <c r="F94" s="87"/>
@@ -3699,23 +3714,23 @@
       <c r="H94" s="87"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="8">
+      <c r="A95" s="87">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="B95" s="8">
-        <v>1</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D95" s="29">
-        <v>46078</v>
-      </c>
-      <c r="E95" s="12"/>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
+      <c r="B95" s="87">
+        <v>5</v>
+      </c>
+      <c r="C95" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="D95" s="88">
+        <v>46077</v>
+      </c>
+      <c r="E95" s="89"/>
+      <c r="F95" s="87"/>
+      <c r="G95" s="87"/>
+      <c r="H95" s="87"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
@@ -3723,13 +3738,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D96" s="29">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="8"/>
@@ -3742,13 +3757,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D97" s="29">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="8"/>
@@ -3761,13 +3776,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D98" s="29">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="8"/>
@@ -3780,13 +3795,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D99" s="29">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="8"/>
@@ -3799,13 +3814,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D100" s="29">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="8"/>
@@ -3818,13 +3833,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D101" s="29">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="8"/>
@@ -3833,17 +3848,17 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
-        <f t="shared" ref="A102:A133" si="3">A101+1</f>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="B102" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D102" s="29">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="8"/>
@@ -3852,17 +3867,17 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A103:A134" si="3">A102+1</f>
         <v>102</v>
       </c>
       <c r="B103" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D103" s="29">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="8"/>
@@ -3875,13 +3890,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D104" s="29">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="8"/>
@@ -3889,31 +3904,23 @@
       <c r="H104" s="8"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="25">
+      <c r="A105" s="8">
         <f t="shared" si="3"/>
         <v>104</v>
       </c>
-      <c r="B105" s="25">
-        <v>1</v>
-      </c>
-      <c r="C105" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D105" s="26">
-        <v>46312</v>
-      </c>
-      <c r="E105" s="27">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F105" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="G105" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H105" s="25" t="s">
-        <v>11</v>
-      </c>
+      <c r="B105" s="8">
+        <v>10</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D105" s="29">
+        <v>46087</v>
+      </c>
+      <c r="E105" s="12"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="25">
@@ -3921,18 +3928,26 @@
         <v>105</v>
       </c>
       <c r="B106" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D106" s="26">
-        <v>46089</v>
-      </c>
-      <c r="E106" s="27"/>
-      <c r="F106" s="25"/>
-      <c r="G106" s="25"/>
-      <c r="H106" s="25"/>
+        <v>46312</v>
+      </c>
+      <c r="E106" s="27">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F106" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G106" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H106" s="25" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -3940,13 +3955,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C107" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D107" s="26">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E107" s="27"/>
       <c r="F107" s="25"/>
@@ -3959,13 +3974,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D108" s="26">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="E108" s="27"/>
       <c r="F108" s="25"/>
@@ -3978,13 +3993,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D109" s="26">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E109" s="27"/>
       <c r="F109" s="25"/>
@@ -3992,23 +4007,23 @@
       <c r="H109" s="25"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="42">
+      <c r="A110" s="25">
         <f t="shared" si="3"/>
         <v>109</v>
       </c>
-      <c r="B110" s="42">
-        <v>1</v>
-      </c>
-      <c r="C110" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D110" s="43">
-        <v>46312</v>
-      </c>
-      <c r="E110" s="44"/>
-      <c r="F110" s="42"/>
-      <c r="G110" s="42"/>
-      <c r="H110" s="42"/>
+      <c r="B110" s="25">
+        <v>5</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D110" s="26">
+        <v>46092</v>
+      </c>
+      <c r="E110" s="27"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
+      <c r="H110" s="25"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="42">
@@ -4016,13 +4031,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D111" s="43">
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="E111" s="44"/>
       <c r="F111" s="42"/>
@@ -4035,13 +4050,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D112" s="43">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="E112" s="44"/>
       <c r="F112" s="42"/>
@@ -4054,13 +4069,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C113" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D113" s="43">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="E113" s="44"/>
       <c r="F113" s="42"/>
@@ -4073,13 +4088,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D114" s="43">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="E114" s="44"/>
       <c r="F114" s="42"/>
@@ -4087,31 +4102,23 @@
       <c r="H114" s="42"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="30">
+      <c r="A115" s="42">
         <f t="shared" si="3"/>
         <v>114</v>
       </c>
-      <c r="B115" s="30">
-        <v>1</v>
-      </c>
-      <c r="C115" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D115" s="59">
-        <v>46230</v>
-      </c>
-      <c r="E115" s="82">
-        <v>0.375</v>
-      </c>
-      <c r="F115" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G115" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H115" s="31" t="s">
-        <v>11</v>
-      </c>
+      <c r="B115" s="42">
+        <v>5</v>
+      </c>
+      <c r="C115" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D115" s="43">
+        <v>46097</v>
+      </c>
+      <c r="E115" s="44"/>
+      <c r="F115" s="42"/>
+      <c r="G115" s="42"/>
+      <c r="H115" s="42"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="30">
@@ -4119,13 +4126,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D116" s="59">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="E116" s="82">
         <v>0.375</v>
@@ -4146,13 +4153,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D117" s="59">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="E117" s="82">
         <v>0.375</v>
@@ -4173,13 +4180,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C118" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D118" s="59">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E118" s="82">
         <v>0.375</v>
@@ -4200,13 +4207,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D119" s="59">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="E119" s="82">
         <v>0.375</v>
@@ -4227,13 +4234,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D120" s="59">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="E120" s="82">
         <v>0.375</v>
@@ -4242,7 +4249,7 @@
         <v>19</v>
       </c>
       <c r="G120" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H120" s="31" t="s">
         <v>11</v>
@@ -4254,13 +4261,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C121" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D121" s="59">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E121" s="82">
         <v>0.375</v>
@@ -4281,13 +4288,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D122" s="59">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E122" s="82">
         <v>0.375</v>
@@ -4308,13 +4315,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C123" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D123" s="59">
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="E123" s="82">
         <v>0.375</v>
@@ -4323,7 +4330,7 @@
         <v>19</v>
       </c>
       <c r="G123" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H123" s="31" t="s">
         <v>11</v>
@@ -4335,13 +4342,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C124" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D124" s="59">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="E124" s="82">
         <v>0.375</v>
@@ -4362,13 +4369,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C125" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D125" s="59">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E125" s="82">
         <v>0.375</v>
@@ -4384,56 +4391,56 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="40">
+      <c r="A126" s="30">
         <f t="shared" si="3"/>
         <v>125</v>
       </c>
-      <c r="B126" s="40">
-        <v>2</v>
-      </c>
-      <c r="C126" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D126" s="60">
-        <v>46256</v>
-      </c>
-      <c r="E126" s="83">
+      <c r="B126" s="30">
+        <v>11</v>
+      </c>
+      <c r="C126" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D126" s="59">
+        <v>46323</v>
+      </c>
+      <c r="E126" s="82">
         <v>0.375</v>
       </c>
-      <c r="F126" s="41" t="s">
+      <c r="F126" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G126" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H126" s="41" t="s">
+      <c r="G126" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H126" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="54">
+      <c r="A127" s="40">
         <f t="shared" si="3"/>
         <v>126</v>
       </c>
-      <c r="B127" s="54">
-        <v>1</v>
-      </c>
-      <c r="C127" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D127" s="55">
-        <v>46367</v>
-      </c>
-      <c r="E127" s="95">
-        <v>0.6875</v>
-      </c>
-      <c r="F127" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G127" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="H127" s="54" t="s">
+      <c r="B127" s="40">
+        <v>2</v>
+      </c>
+      <c r="C127" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D127" s="60">
+        <v>46256</v>
+      </c>
+      <c r="E127" s="83">
+        <v>0.375</v>
+      </c>
+      <c r="F127" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H127" s="41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4443,16 +4450,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D128" s="55">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="E128" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F128" s="54" t="s">
         <v>52</v>
@@ -4470,16 +4477,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C129" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D129" s="55">
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="E129" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F129" s="54" t="s">
         <v>52</v>
@@ -4497,22 +4504,22 @@
         <v>129</v>
       </c>
       <c r="B130" s="54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C130" s="54" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D130" s="55">
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="E130" s="95">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="F130" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G130" s="54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H130" s="54" t="s">
         <v>11</v>
@@ -4524,22 +4531,22 @@
         <v>130</v>
       </c>
       <c r="B131" s="54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C131" s="54" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D131" s="55">
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="E131" s="95">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F131" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G131" s="54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H131" s="54" t="s">
         <v>11</v>
@@ -4551,16 +4558,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D132" s="55">
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="E132" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F132" s="54" t="s">
         <v>52</v>
@@ -4578,16 +4585,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C133" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D133" s="55">
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="E133" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F133" s="54" t="s">
         <v>52</v>
@@ -4599,24 +4606,51 @@
         <v>11</v>
       </c>
     </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="54">
+        <f t="shared" si="3"/>
+        <v>133</v>
+      </c>
+      <c r="B134" s="54">
+        <v>6</v>
+      </c>
+      <c r="C134" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D134" s="55">
+        <v>46404</v>
+      </c>
+      <c r="E134" s="95">
+        <v>0.375</v>
+      </c>
+      <c r="F134" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="G134" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="H134" s="54" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H109" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H109">
-      <sortCondition ref="A1:A109"/>
+  <autoFilter ref="A1:H110" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H110">
+      <sortCondition ref="A1:A110"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="49" max="16383" man="1"/>
-    <brk id="59" max="16383" man="1"/>
+    <brk id="50" max="16383" man="1"/>
+    <brk id="60" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L133"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="84" customWidth="1"/>
@@ -4678,7 +4712,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="96">
-        <f t="shared" ref="D2:D36" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
+        <f t="shared" ref="D2:D37" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="E2" s="96" t="str">
@@ -4834,7 +4868,7 @@
         <v>0.8125</v>
       </c>
       <c r="D6" s="96">
-        <f t="shared" ref="D6:D13" si="1">IF(I6 = "KM",C6+"1:45",IF(I6="U23",C6+"1:45",IF(I6 = "U16",C6+"1:45",IF(I6 = "U15",C6+"1:30",IF(I6 = "U14",C6+"1:30",IF(I6 = "U13",C6+"1:35",IF(I6 = "U12",C6+"1:10",IF(I6 = "U11",C6+"1:10",IF(I6 = "U10",C6+"1:03",C6+"3:00")))))))))</f>
+        <f t="shared" ref="D6:D14" si="1">IF(I6 = "KM",C6+"1:45",IF(I6="U23",C6+"1:45",IF(I6 = "U16",C6+"1:45",IF(I6 = "U15",C6+"1:30",IF(I6 = "U14",C6+"1:30",IF(I6 = "U13",C6+"1:35",IF(I6 = "U12",C6+"1:10",IF(I6 = "U11",C6+"1:10",IF(I6 = "U10",C6+"1:03",C6+"3:00")))))))))</f>
         <v>0.88541666666666663</v>
       </c>
       <c r="E6" s="96" t="str">
@@ -4863,112 +4897,114 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="113" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="84"/>
       <c r="B7" s="81">
         <f>'Nach Mannschaften sortiert'!D7</f>
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="C7" s="96">
         <f>'Nach Mannschaften sortiert'!E7</f>
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D7" s="96">
-        <f t="shared" si="1"/>
-        <v>0.80208333333333326</v>
+        <f t="shared" ref="D7:D8" si="2">IF(I7 = "KM",C7+"1:45",IF(I7="U23",C7+"1:45",IF(I7 = "U16",C7+"1:45",IF(I7 = "U15",C7+"1:30",IF(I7 = "U14",C7+"1:30",IF(I7 = "U13",C7+"1:35",IF(I7 = "U12",C7+"1:10",IF(I7 = "U11",C7+"1:10",IF(I7 = "U10",C7+"1:03",C7+"3:00")))))))))</f>
+        <v>0.78125</v>
       </c>
       <c r="E7" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F7)</f>
-        <v>KITTSEE</v>
-      </c>
-      <c r="G7" s="112" t="str">
+        <v>WIENER NEUSTADT</v>
+      </c>
+      <c r="F7" s="84"/>
+      <c r="G7" s="113" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
         <v>Auswärts</v>
       </c>
-      <c r="H7" s="112" t="str">
+      <c r="H7" s="113" t="str">
         <f>'Nach Mannschaften sortiert'!G7</f>
-        <v>Kittsee</v>
-      </c>
-      <c r="I7" s="112" t="str">
+        <v>Admira Wiener Neustadt</v>
+      </c>
+      <c r="I7" s="113" t="str">
         <f>'Nach Mannschaften sortiert'!C7</f>
-        <v>KM</v>
+        <v>U23</v>
       </c>
       <c r="J7" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="112" t="s">
+      <c r="K7" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="L7" s="112" t="s">
+      <c r="L7" s="113" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" s="81">
         <f>'Nach Mannschaften sortiert'!D8</f>
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="C8" s="96">
         <f>'Nach Mannschaften sortiert'!E8</f>
-        <v>0.79166666666666663</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D8" s="96">
-        <f t="shared" si="1"/>
-        <v>0.86458333333333326</v>
+        <f t="shared" si="2"/>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E8" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F8)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G8" s="112" t="str">
+        <v>KITTSEE</v>
+      </c>
+      <c r="G8" s="113" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
-        <v>Heim</v>
-      </c>
-      <c r="H8" s="112" t="str">
+        <v>Auswärts</v>
+      </c>
+      <c r="H8" s="113" t="str">
         <f>'Nach Mannschaften sortiert'!G8</f>
-        <v>Bad Fischau</v>
-      </c>
-      <c r="I8" s="112" t="str">
+        <v>Kittsee</v>
+      </c>
+      <c r="I8" s="113" t="str">
         <f>'Nach Mannschaften sortiert'!C8</f>
         <v>KM</v>
       </c>
       <c r="J8" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="112" t="s">
+      <c r="K8" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="112" t="s">
+      <c r="L8" s="113" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="81">
         <f>'Nach Mannschaften sortiert'!D9</f>
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="C9" s="96">
         <f>'Nach Mannschaften sortiert'!E9</f>
-        <v>0.45833333333333331</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D9" s="96">
         <f t="shared" si="1"/>
-        <v>0.53125</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E9" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
-        <v>WIENER NEUDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G9" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H9" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G9</f>
-        <v>Wiener Neudorf</v>
+        <v>Bad Fischau</v>
       </c>
       <c r="I9" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C9</f>
-        <v>U16</v>
+        <v>KM</v>
       </c>
       <c r="J9" s="84" t="s">
         <v>68</v>
@@ -4980,36 +5016,34 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="110" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="84"/>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="81">
         <f>'Nach Mannschaften sortiert'!D10</f>
-        <v>46217</v>
+        <v>46243</v>
       </c>
       <c r="C10" s="96">
         <f>'Nach Mannschaften sortiert'!E10</f>
-        <v>0.8125</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D10" s="96">
         <f t="shared" si="1"/>
-        <v>0.88541666666666663</v>
+        <v>0.53125</v>
       </c>
       <c r="E10" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F10)</f>
-        <v>PÖTTSCHING</v>
-      </c>
-      <c r="F10" s="84"/>
+        <v>WIENER NEUDORF</v>
+      </c>
       <c r="G10" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
         <v>Auswärts</v>
       </c>
       <c r="H10" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G10</f>
-        <v>Pöttsching</v>
+        <v>Wiener Neudorf</v>
       </c>
       <c r="I10" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C10</f>
-        <v>KM</v>
+        <v>U16</v>
       </c>
       <c r="J10" s="84" t="s">
         <v>68</v>
@@ -5021,34 +5055,36 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" s="110" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="84"/>
       <c r="B11" s="81">
         <f>'Nach Mannschaften sortiert'!D11</f>
-        <v>46236</v>
+        <v>46217</v>
       </c>
       <c r="C11" s="96">
         <f>'Nach Mannschaften sortiert'!E11</f>
-        <v>0.4375</v>
+        <v>0.8125</v>
       </c>
       <c r="D11" s="96">
         <f t="shared" si="1"/>
-        <v>0.51041666666666663</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E11" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
-        <v>NEUFELD</v>
-      </c>
+        <v>PÖTTSCHING</v>
+      </c>
+      <c r="F11" s="84"/>
       <c r="G11" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H11" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G11</f>
-        <v>Theresienfeld</v>
+        <v>Pöttsching</v>
       </c>
       <c r="I11" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C11</f>
-        <v>U16</v>
+        <v>KM</v>
       </c>
       <c r="J11" s="84" t="s">
         <v>68</v>
@@ -5060,32 +5096,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="112" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="81">
         <f>'Nach Mannschaften sortiert'!D12</f>
-        <v>46260</v>
+        <v>46236</v>
       </c>
       <c r="C12" s="96">
         <f>'Nach Mannschaften sortiert'!E12</f>
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D12" s="96">
         <f t="shared" si="1"/>
-        <v>0.48958333333333337</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="E12" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="F12" s="84"/>
       <c r="G12" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Heim</v>
       </c>
       <c r="H12" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G12</f>
-        <v>Traiskirchen</v>
+        <v>Theresienfeld</v>
       </c>
       <c r="I12" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C12</f>
@@ -5101,36 +5135,36 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="111" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" s="112" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="84"/>
       <c r="B13" s="81">
         <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>46445</v>
+        <v>46260</v>
       </c>
       <c r="C13" s="96">
         <f>'Nach Mannschaften sortiert'!E13</f>
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D13" s="96">
         <f t="shared" si="1"/>
-        <v>0.57291666666666663</v>
+        <v>0.48958333333333337</v>
       </c>
       <c r="E13" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
-        <v>BAD ERLACH</v>
+        <v>NEUFELD</v>
       </c>
       <c r="F13" s="84"/>
       <c r="G13" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H13" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>Bad Erlach</v>
+        <v>Traiskirchen</v>
       </c>
       <c r="I13" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C13</f>
-        <v>KM</v>
+        <v>U16</v>
       </c>
       <c r="J13" s="84" t="s">
         <v>68</v>
@@ -5142,61 +5176,63 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="84"/>
       <c r="B14" s="81">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46250</v>
+        <v>46445</v>
       </c>
       <c r="C14" s="96">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.72916666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D14" s="96">
-        <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <f t="shared" si="1"/>
+        <v>0.57291666666666663</v>
       </c>
       <c r="E14" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
-        <v>KITTSEE</v>
-      </c>
-      <c r="G14" t="str">
+        <v>BAD ERLACH</v>
+      </c>
+      <c r="F14" s="84"/>
+      <c r="G14" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
         <v>Auswärts</v>
       </c>
-      <c r="H14" t="str">
+      <c r="H14" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>Kittsee</v>
-      </c>
-      <c r="I14" t="str">
+        <v>Bad Erlach</v>
+      </c>
+      <c r="I14" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C14</f>
         <v>KM</v>
       </c>
       <c r="J14" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K14" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="K14" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="112" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" s="81">
         <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C15" s="96">
         <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D15" s="96">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E15" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G15" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
@@ -5204,7 +5240,7 @@
       </c>
       <c r="H15" t="str">
         <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I15" t="str">
         <f>'Nach Mannschaften sortiert'!C15</f>
@@ -5223,27 +5259,27 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" s="81">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C16" s="96">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D16" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.90625</v>
       </c>
       <c r="E16" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G16" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H16" t="str">
         <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I16" t="str">
         <f>'Nach Mannschaften sortiert'!C16</f>
@@ -5262,27 +5298,27 @@
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="81">
         <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C17" s="96">
         <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D17" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E17" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G17" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H17" t="str">
         <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I17" t="str">
         <f>'Nach Mannschaften sortiert'!C17</f>
@@ -5301,27 +5337,27 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="81">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C18" s="96">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="D18" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E18" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G18" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H18" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I18" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
@@ -5340,27 +5376,27 @@
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="81">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C19" s="96">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D19" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E19" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G19" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H19" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I19" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
@@ -5379,27 +5415,27 @@
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="81">
         <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C20" s="96">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D20" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E20" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G20" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H20" t="str">
         <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I20" t="str">
         <f>'Nach Mannschaften sortiert'!C20</f>
@@ -5418,27 +5454,27 @@
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="81">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C21" s="96">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D21" s="96">
         <f t="shared" si="0"/>
-        <v>0.86458333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E21" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G21" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H21" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I21" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
@@ -5457,27 +5493,27 @@
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="81">
         <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="C22" s="96">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D22" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E22" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G22" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H22" t="str">
         <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I22" t="str">
         <f>'Nach Mannschaften sortiert'!C22</f>
@@ -5496,7 +5532,7 @@
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="81">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C23" s="96">
         <f>'Nach Mannschaften sortiert'!E23</f>
@@ -5508,15 +5544,15 @@
       </c>
       <c r="E23" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G23" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H23" t="str">
         <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I23" t="str">
         <f>'Nach Mannschaften sortiert'!C23</f>
@@ -5535,27 +5571,27 @@
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="81">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C24" s="96">
         <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D24" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E24" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G24" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H24" t="str">
         <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I24" t="str">
         <f>'Nach Mannschaften sortiert'!C24</f>
@@ -5574,27 +5610,27 @@
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="81">
         <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C25" s="96">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D25" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E25" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G25" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H25" t="str">
         <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I25" t="str">
         <f>'Nach Mannschaften sortiert'!C25</f>
@@ -5613,27 +5649,27 @@
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="81">
         <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C26" s="96">
         <f>'Nach Mannschaften sortiert'!E26</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D26" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E26" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G26" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H26" t="str">
         <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I26" t="str">
         <f>'Nach Mannschaften sortiert'!C26</f>
@@ -5652,31 +5688,31 @@
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="81">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="C27" s="96">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D27" s="96">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E27" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
-        <v>KITTSEE</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G27" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H27" t="str">
         <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>Kittsee</v>
+        <v>Andau</v>
       </c>
       <c r="I27" t="str">
         <f>'Nach Mannschaften sortiert'!C27</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J27" s="84" t="s">
         <v>68</v>
@@ -5691,19 +5727,19 @@
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="81">
         <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C28" s="96">
         <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D28" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="E28" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G28" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
@@ -5711,7 +5747,7 @@
       </c>
       <c r="H28" t="str">
         <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I28" t="str">
         <f>'Nach Mannschaften sortiert'!C28</f>
@@ -5730,27 +5766,27 @@
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="81">
         <f>'Nach Mannschaften sortiert'!D29</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C29" s="96">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D29" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E29" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G29" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H29" t="str">
         <f>'Nach Mannschaften sortiert'!G29</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I29" t="str">
         <f>'Nach Mannschaften sortiert'!C29</f>
@@ -5769,27 +5805,27 @@
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="81">
         <f>'Nach Mannschaften sortiert'!D30</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C30" s="96">
         <f>'Nach Mannschaften sortiert'!E30</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D30" s="96">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E30" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G30" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H30" t="str">
         <f>'Nach Mannschaften sortiert'!G30</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I30" t="str">
         <f>'Nach Mannschaften sortiert'!C30</f>
@@ -5808,27 +5844,27 @@
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="81">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C31" s="96">
         <f>'Nach Mannschaften sortiert'!E31</f>
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D31" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E31" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G31" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H31" t="str">
         <f>'Nach Mannschaften sortiert'!G31</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I31" t="str">
         <f>'Nach Mannschaften sortiert'!C31</f>
@@ -5847,27 +5883,27 @@
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="81">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C32" s="96">
         <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D32" s="96">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E32" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G32" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H32" t="str">
         <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
@@ -5886,27 +5922,27 @@
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="81">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C33" s="96">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D33" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.65625</v>
       </c>
       <c r="E33" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G33" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H33" t="str">
         <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I33" t="str">
         <f>'Nach Mannschaften sortiert'!C33</f>
@@ -5925,27 +5961,27 @@
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="81">
         <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C34" s="96">
         <f>'Nach Mannschaften sortiert'!E34</f>
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D34" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E34" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G34" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H34" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I34" t="str">
         <f>'Nach Mannschaften sortiert'!C34</f>
@@ -5964,27 +6000,27 @@
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="81">
         <f>'Nach Mannschaften sortiert'!D35</f>
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="C35" s="96">
         <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D35" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.78125</v>
       </c>
       <c r="E35" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G35" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H35" t="str">
         <f>'Nach Mannschaften sortiert'!G35</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I35" t="str">
         <f>'Nach Mannschaften sortiert'!C35</f>
@@ -6003,7 +6039,7 @@
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="81">
         <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C36" s="96">
         <f>'Nach Mannschaften sortiert'!E36</f>
@@ -6015,15 +6051,15 @@
       </c>
       <c r="E36" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G36" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H36" t="str">
         <f>'Nach Mannschaften sortiert'!G36</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I36" t="str">
         <f>'Nach Mannschaften sortiert'!C36</f>
@@ -6042,27 +6078,27 @@
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="81">
         <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C37" s="96">
         <f>'Nach Mannschaften sortiert'!E37</f>
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D37" s="96">
-        <f t="shared" ref="D37:D68" si="2">IF(I37 = "KM",C37+"1:45",IF(I37="U23",C37+"1:45",IF(I37 = "U16",C37+"1:45",IF(I37 = "U15",C37+"1:30",IF(I37 = "U14",C37+"1:30",IF(I37 = "U13",C37+"1:35",IF(I37 = "U12",C37+"1:10",IF(I37 = "U11",C37+"1:10",IF(I37 = "U10",C37+"1:03",C37+"3:00")))))))))</f>
-        <v>0.69791666666666663</v>
+        <f t="shared" si="0"/>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E37" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G37" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H37" t="str">
         <f>'Nach Mannschaften sortiert'!G37</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I37" t="str">
         <f>'Nach Mannschaften sortiert'!C37</f>
@@ -6081,27 +6117,27 @@
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="81">
         <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C38" s="96">
         <f>'Nach Mannschaften sortiert'!E38</f>
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D38" s="96">
-        <f t="shared" si="2"/>
-        <v>0.73958333333333326</v>
+        <f t="shared" ref="D38:D69" si="3">IF(I38 = "KM",C38+"1:45",IF(I38="U23",C38+"1:45",IF(I38 = "U16",C38+"1:45",IF(I38 = "U15",C38+"1:30",IF(I38 = "U14",C38+"1:30",IF(I38 = "U13",C38+"1:35",IF(I38 = "U12",C38+"1:10",IF(I38 = "U11",C38+"1:10",IF(I38 = "U10",C38+"1:03",C38+"3:00")))))))))</f>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E38" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G38" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H38" t="str">
         <f>'Nach Mannschaften sortiert'!G38</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I38" t="str">
         <f>'Nach Mannschaften sortiert'!C38</f>
@@ -6120,27 +6156,27 @@
     <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="81">
         <f>'Nach Mannschaften sortiert'!D39</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C39" s="96">
         <f>'Nach Mannschaften sortiert'!E39</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D39" s="96">
-        <f t="shared" si="2"/>
-        <v>0.67708333333333326</v>
+        <f t="shared" si="3"/>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E39" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G39" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H39" t="str">
         <f>'Nach Mannschaften sortiert'!G39</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I39" t="str">
         <f>'Nach Mannschaften sortiert'!C39</f>
@@ -6159,31 +6195,31 @@
     <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="81">
         <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46023</v>
+        <v>46333</v>
       </c>
       <c r="C40" s="96">
         <f>'Nach Mannschaften sortiert'!E40</f>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D40" s="96">
-        <f t="shared" si="2"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E40" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
-        <v/>
-      </c>
-      <c r="G40">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G40" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
-        <v>0</v>
-      </c>
-      <c r="H40">
+        <v>Heim</v>
+      </c>
+      <c r="H40" t="str">
         <f>'Nach Mannschaften sortiert'!G40</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I40" t="str">
         <f>'Nach Mannschaften sortiert'!C40</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J40" s="84" t="s">
         <v>68</v>
@@ -6198,14 +6234,14 @@
     <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="81">
         <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C41" s="96">
         <f>'Nach Mannschaften sortiert'!E41</f>
         <v>0</v>
       </c>
       <c r="D41" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E41" s="96" t="str">
@@ -6237,14 +6273,14 @@
     <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="81">
         <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C42" s="96">
         <f>'Nach Mannschaften sortiert'!E42</f>
         <v>0</v>
       </c>
       <c r="D42" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E42" s="96" t="str">
@@ -6276,14 +6312,14 @@
     <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="81">
         <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C43" s="96">
         <f>'Nach Mannschaften sortiert'!E43</f>
         <v>0</v>
       </c>
       <c r="D43" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E43" s="96" t="str">
@@ -6315,14 +6351,14 @@
     <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="81">
         <f>'Nach Mannschaften sortiert'!D44</f>
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C44" s="96">
         <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="D44" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E44" s="96" t="str">
@@ -6354,14 +6390,14 @@
     <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="81">
         <f>'Nach Mannschaften sortiert'!D45</f>
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C45" s="96">
         <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="D45" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E45" s="96" t="str">
@@ -6393,14 +6429,14 @@
     <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="81">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C46" s="96">
         <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="D46" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E46" s="96" t="str">
@@ -6432,14 +6468,14 @@
     <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="81">
         <f>'Nach Mannschaften sortiert'!D47</f>
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C47" s="96">
         <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="D47" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E47" s="96" t="str">
@@ -6471,14 +6507,14 @@
     <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="81">
         <f>'Nach Mannschaften sortiert'!D48</f>
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C48" s="96">
         <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="D48" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E48" s="96" t="str">
@@ -6510,14 +6546,14 @@
     <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="81">
         <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C49" s="96">
         <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="D49" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E49" s="96" t="str">
@@ -6549,15 +6585,15 @@
     <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="81">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C50" s="96">
         <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="D50" s="96">
-        <f t="shared" si="2"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="3"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E50" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
@@ -6573,7 +6609,7 @@
       </c>
       <c r="I50" t="str">
         <f>'Nach Mannschaften sortiert'!C50</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J50" s="84" t="s">
         <v>68</v>
@@ -6588,14 +6624,14 @@
     <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="81">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C51" s="96">
         <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="D51" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E51" s="96" t="str">
@@ -6627,14 +6663,14 @@
     <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="81">
         <f>'Nach Mannschaften sortiert'!D52</f>
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C52" s="96">
         <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="D52" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E52" s="96" t="str">
@@ -6666,14 +6702,14 @@
     <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="81">
         <f>'Nach Mannschaften sortiert'!D53</f>
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C53" s="96">
         <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="D53" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E53" s="96" t="str">
@@ -6705,14 +6741,14 @@
     <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="81">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="C54" s="96">
         <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="D54" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E54" s="96" t="str">
@@ -6744,14 +6780,14 @@
     <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="81">
         <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="C55" s="96">
         <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
       <c r="D55" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E55" s="96" t="str">
@@ -6783,14 +6819,14 @@
     <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
         <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C56" s="96">
         <f>'Nach Mannschaften sortiert'!E56</f>
         <v>0</v>
       </c>
       <c r="D56" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E56" s="96" t="str">
@@ -6822,14 +6858,14 @@
     <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="81">
         <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C57" s="96">
         <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
       <c r="D57" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E57" s="96" t="str">
@@ -6861,14 +6897,14 @@
     <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="81">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C58" s="96">
         <f>'Nach Mannschaften sortiert'!E58</f>
         <v>0</v>
       </c>
       <c r="D58" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E58" s="96" t="str">
@@ -6900,14 +6936,14 @@
     <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="81">
         <f>'Nach Mannschaften sortiert'!D59</f>
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C59" s="96">
         <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="D59" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E59" s="96" t="str">
@@ -6939,15 +6975,15 @@
     <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="81">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C60" s="96">
         <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="D60" s="96">
-        <f t="shared" si="2"/>
-        <v>0.125</v>
+        <f t="shared" si="3"/>
+        <v>6.25E-2</v>
       </c>
       <c r="E60" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
@@ -6963,7 +6999,7 @@
       </c>
       <c r="I60" t="str">
         <f>'Nach Mannschaften sortiert'!C60</f>
-        <v>U12_1</v>
+        <v>U14</v>
       </c>
       <c r="J60" s="84" t="s">
         <v>68</v>
@@ -6978,14 +7014,14 @@
     <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="81">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C61" s="96">
         <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="D61" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E61" s="96" t="str">
@@ -7017,14 +7053,14 @@
     <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="81">
         <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C62" s="96">
         <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="D62" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E62" s="96" t="str">
@@ -7056,14 +7092,14 @@
     <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="81">
         <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C63" s="96">
         <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="D63" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E63" s="96" t="str">
@@ -7095,14 +7131,14 @@
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="81">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C64" s="96">
         <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="D64" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E64" s="96" t="str">
@@ -7134,14 +7170,14 @@
     <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="81">
         <f>'Nach Mannschaften sortiert'!D65</f>
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="C65" s="96">
         <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="D65" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E65" s="96" t="str">
@@ -7173,14 +7209,14 @@
     <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="81">
         <f>'Nach Mannschaften sortiert'!D66</f>
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="C66" s="96">
         <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="D66" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E66" s="96" t="str">
@@ -7212,14 +7248,14 @@
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="81">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C67" s="96">
         <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="D67" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E67" s="96" t="str">
@@ -7251,14 +7287,14 @@
     <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="81">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C68" s="96">
         <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="D68" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E68" s="96" t="str">
@@ -7290,14 +7326,14 @@
     <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="81">
         <f>'Nach Mannschaften sortiert'!D69</f>
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="C69" s="96">
         <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="D69" s="96">
-        <f t="shared" ref="D69:D89" si="3">IF(I69 = "KM",C69+"1:45",IF(I69="U23",C69+"1:45",IF(I69 = "U16",C69+"1:45",IF(I69 = "U15",C69+"1:30",IF(I69 = "U14",C69+"1:30",IF(I69 = "U13",C69+"1:35",IF(I69 = "U12",C69+"1:10",IF(I69 = "U11",C69+"1:10",IF(I69 = "U10",C69+"1:03",C69+"3:00")))))))))</f>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E69" s="96" t="str">
@@ -7329,14 +7365,14 @@
     <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="81">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C70" s="96">
         <f>'Nach Mannschaften sortiert'!E70</f>
         <v>0</v>
       </c>
       <c r="D70" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D70:D90" si="4">IF(I70 = "KM",C70+"1:45",IF(I70="U23",C70+"1:45",IF(I70 = "U16",C70+"1:45",IF(I70 = "U15",C70+"1:30",IF(I70 = "U14",C70+"1:30",IF(I70 = "U13",C70+"1:35",IF(I70 = "U12",C70+"1:10",IF(I70 = "U11",C70+"1:10",IF(I70 = "U10",C70+"1:03",C70+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E70" s="96" t="str">
@@ -7353,7 +7389,7 @@
       </c>
       <c r="I70" t="str">
         <f>'Nach Mannschaften sortiert'!C70</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J70" s="84" t="s">
         <v>68</v>
@@ -7368,14 +7404,14 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="81">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="C71" s="96">
         <f>'Nach Mannschaften sortiert'!E71</f>
         <v>0</v>
       </c>
       <c r="D71" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E71" s="96" t="str">
@@ -7407,14 +7443,14 @@
     <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="81">
         <f>'Nach Mannschaften sortiert'!D72</f>
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C72" s="96">
         <f>'Nach Mannschaften sortiert'!E72</f>
         <v>0</v>
       </c>
       <c r="D72" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E72" s="96" t="str">
@@ -7446,14 +7482,14 @@
     <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="81">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C73" s="96">
         <f>'Nach Mannschaften sortiert'!E73</f>
         <v>0</v>
       </c>
       <c r="D73" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E73" s="96" t="str">
@@ -7485,14 +7521,14 @@
     <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="81">
         <f>'Nach Mannschaften sortiert'!D74</f>
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="C74" s="96">
         <f>'Nach Mannschaften sortiert'!E74</f>
         <v>0</v>
       </c>
       <c r="D74" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E74" s="96" t="str">
@@ -7524,14 +7560,14 @@
     <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="81">
         <f>'Nach Mannschaften sortiert'!D75</f>
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C75" s="96">
         <f>'Nach Mannschaften sortiert'!E75</f>
         <v>0</v>
       </c>
       <c r="D75" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E75" s="96" t="str">
@@ -7563,14 +7599,14 @@
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="81">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="C76" s="96">
         <f>'Nach Mannschaften sortiert'!E76</f>
         <v>0</v>
       </c>
       <c r="D76" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E76" s="96" t="str">
@@ -7602,14 +7638,14 @@
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="81">
         <f>'Nach Mannschaften sortiert'!D77</f>
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="C77" s="96">
         <f>'Nach Mannschaften sortiert'!E77</f>
         <v>0</v>
       </c>
       <c r="D77" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E77" s="96" t="str">
@@ -7641,14 +7677,14 @@
     <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="81">
         <f>'Nach Mannschaften sortiert'!D78</f>
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C78" s="96">
         <f>'Nach Mannschaften sortiert'!E78</f>
         <v>0</v>
       </c>
       <c r="D78" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E78" s="96" t="str">
@@ -7680,14 +7716,14 @@
     <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="81">
         <f>'Nach Mannschaften sortiert'!D79</f>
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C79" s="96">
         <f>'Nach Mannschaften sortiert'!E79</f>
         <v>0</v>
       </c>
       <c r="D79" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E79" s="96" t="str">
@@ -7719,15 +7755,15 @@
     <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="81">
         <f>'Nach Mannschaften sortiert'!D80</f>
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="C80" s="96">
         <f>'Nach Mannschaften sortiert'!E80</f>
         <v>0</v>
       </c>
       <c r="D80" s="96">
-        <f t="shared" si="3"/>
-        <v>4.8611111111111112E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.125</v>
       </c>
       <c r="E80" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F80)</f>
@@ -7743,7 +7779,7 @@
       </c>
       <c r="I80" t="str">
         <f>'Nach Mannschaften sortiert'!C80</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J80" s="84" t="s">
         <v>68</v>
@@ -7758,14 +7794,14 @@
     <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="81">
         <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C81" s="96">
         <f>'Nach Mannschaften sortiert'!E81</f>
         <v>0</v>
       </c>
       <c r="D81" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E81" s="96" t="str">
@@ -7797,14 +7833,14 @@
     <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="81">
         <f>'Nach Mannschaften sortiert'!D82</f>
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C82" s="96">
         <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="D82" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E82" s="96" t="str">
@@ -7836,14 +7872,14 @@
     <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="81">
         <f>'Nach Mannschaften sortiert'!D83</f>
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C83" s="96">
         <f>'Nach Mannschaften sortiert'!E83</f>
         <v>0</v>
       </c>
       <c r="D83" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E83" s="96" t="str">
@@ -7875,14 +7911,14 @@
     <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="81">
         <f>'Nach Mannschaften sortiert'!D84</f>
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="C84" s="96">
         <f>'Nach Mannschaften sortiert'!E84</f>
         <v>0</v>
       </c>
       <c r="D84" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E84" s="96" t="str">
@@ -7914,14 +7950,14 @@
     <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="81">
         <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="C85" s="96">
         <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="D85" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E85" s="96" t="str">
@@ -7953,14 +7989,14 @@
     <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="81">
         <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="C86" s="96">
         <f>'Nach Mannschaften sortiert'!E86</f>
         <v>0</v>
       </c>
       <c r="D86" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E86" s="96" t="str">
@@ -7992,14 +8028,14 @@
     <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="81">
         <f>'Nach Mannschaften sortiert'!D87</f>
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="C87" s="96">
         <f>'Nach Mannschaften sortiert'!E87</f>
         <v>0</v>
       </c>
       <c r="D87" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E87" s="96" t="str">
@@ -8031,14 +8067,14 @@
     <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="81">
         <f>'Nach Mannschaften sortiert'!D88</f>
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="C88" s="96">
         <f>'Nach Mannschaften sortiert'!E88</f>
         <v>0</v>
       </c>
       <c r="D88" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E88" s="96" t="str">
@@ -8070,14 +8106,14 @@
     <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="81">
         <f>'Nach Mannschaften sortiert'!D89</f>
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C89" s="96">
         <f>'Nach Mannschaften sortiert'!E89</f>
         <v>0</v>
       </c>
       <c r="D89" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E89" s="96" t="str">
@@ -8109,30 +8145,31 @@
     <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="81">
         <f>'Nach Mannschaften sortiert'!D90</f>
-        <v>46312</v>
+        <v>46072</v>
       </c>
       <c r="C90" s="96">
         <f>'Nach Mannschaften sortiert'!E90</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D90" s="96">
-        <v>0.5</v>
+        <f t="shared" si="4"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E90" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F90)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="G90">
         <f>'Nach Mannschaften sortiert'!H90</f>
-        <v>Heim</v>
-      </c>
-      <c r="H90" t="str">
+        <v>0</v>
+      </c>
+      <c r="H90">
         <f>'Nach Mannschaften sortiert'!G90</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I90" t="str">
         <f>'Nach Mannschaften sortiert'!C90</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J90" s="84" t="s">
         <v>68</v>
@@ -8147,27 +8184,26 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="81">
         <f>'Nach Mannschaften sortiert'!D91</f>
-        <v>46074</v>
+        <v>46312</v>
       </c>
       <c r="C91" s="96">
         <f>'Nach Mannschaften sortiert'!E91</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D91" s="96">
-        <f t="shared" ref="D91:D104" si="4">IF(I91 = "KM",C91+"1:45",IF(I91="U23",C91+"1:45",IF(I91 = "U16",C91+"1:45",IF(I91 = "U15",C91+"1:30",IF(I91 = "U14",C91+"1:30",IF(I91 = "U13",C91+"1:35",IF(I91 = "U12",C91+"1:10",IF(I91 = "U11",C91+"1:10",IF(I91 = "U10",C91+"1:03",C91+"3:00")))))))))</f>
-        <v>4.3750000000000004E-2</v>
+        <v>0.5</v>
       </c>
       <c r="E91" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F91)</f>
-        <v/>
-      </c>
-      <c r="G91">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G91" t="str">
         <f>'Nach Mannschaften sortiert'!H91</f>
-        <v>0</v>
-      </c>
-      <c r="H91">
+        <v>Heim</v>
+      </c>
+      <c r="H91" t="str">
         <f>'Nach Mannschaften sortiert'!G91</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I91" t="str">
         <f>'Nach Mannschaften sortiert'!C91</f>
@@ -8186,14 +8222,14 @@
     <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="81">
         <f>'Nach Mannschaften sortiert'!D92</f>
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="C92" s="96">
         <f>'Nach Mannschaften sortiert'!E92</f>
         <v>0</v>
       </c>
       <c r="D92" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D92:D105" si="5">IF(I92 = "KM",C92+"1:45",IF(I92="U23",C92+"1:45",IF(I92 = "U16",C92+"1:45",IF(I92 = "U15",C92+"1:30",IF(I92 = "U14",C92+"1:30",IF(I92 = "U13",C92+"1:35",IF(I92 = "U12",C92+"1:10",IF(I92 = "U11",C92+"1:10",IF(I92 = "U10",C92+"1:03",C92+"3:00")))))))))</f>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E92" s="96" t="str">
@@ -8225,14 +8261,14 @@
     <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="81">
         <f>'Nach Mannschaften sortiert'!D93</f>
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="C93" s="96">
         <f>'Nach Mannschaften sortiert'!E93</f>
         <v>0</v>
       </c>
       <c r="D93" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E93" s="96" t="str">
@@ -8264,14 +8300,14 @@
     <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="81">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C94" s="96">
         <f>'Nach Mannschaften sortiert'!E94</f>
         <v>0</v>
       </c>
       <c r="D94" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E94" s="96" t="str">
@@ -8303,15 +8339,15 @@
     <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95" s="81">
         <f>'Nach Mannschaften sortiert'!D95</f>
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C95" s="96">
         <f>'Nach Mannschaften sortiert'!E95</f>
         <v>0</v>
       </c>
       <c r="D95" s="96">
-        <f t="shared" si="4"/>
-        <v>0.125</v>
+        <f t="shared" si="5"/>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E95" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F95)</f>
@@ -8327,7 +8363,7 @@
       </c>
       <c r="I95" t="str">
         <f>'Nach Mannschaften sortiert'!C95</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J95" s="84" t="s">
         <v>68</v>
@@ -8342,14 +8378,14 @@
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="81">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="C96" s="96">
         <f>'Nach Mannschaften sortiert'!E96</f>
         <v>0</v>
       </c>
       <c r="D96" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E96" s="96" t="str">
@@ -8381,14 +8417,14 @@
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="81">
         <f>'Nach Mannschaften sortiert'!D97</f>
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C97" s="96">
         <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="D97" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E97" s="96" t="str">
@@ -8420,14 +8456,14 @@
     <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B98" s="81">
         <f>'Nach Mannschaften sortiert'!D98</f>
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C98" s="96">
         <f>'Nach Mannschaften sortiert'!E98</f>
         <v>0</v>
       </c>
       <c r="D98" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E98" s="96" t="str">
@@ -8459,14 +8495,14 @@
     <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B99" s="81">
         <f>'Nach Mannschaften sortiert'!D99</f>
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C99" s="96">
         <f>'Nach Mannschaften sortiert'!E99</f>
         <v>0</v>
       </c>
       <c r="D99" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E99" s="96" t="str">
@@ -8498,14 +8534,14 @@
     <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100" s="81">
         <f>'Nach Mannschaften sortiert'!D100</f>
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C100" s="96">
         <f>'Nach Mannschaften sortiert'!E100</f>
         <v>0</v>
       </c>
       <c r="D100" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E100" s="96" t="str">
@@ -8537,14 +8573,14 @@
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101" s="81">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C101" s="96">
         <f>'Nach Mannschaften sortiert'!E101</f>
         <v>0</v>
       </c>
       <c r="D101" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E101" s="96" t="str">
@@ -8576,14 +8612,14 @@
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102" s="81">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C102" s="96">
         <f>'Nach Mannschaften sortiert'!E102</f>
         <v>0</v>
       </c>
       <c r="D102" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E102" s="96" t="str">
@@ -8615,14 +8651,14 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="81">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C103" s="96">
         <f>'Nach Mannschaften sortiert'!E103</f>
         <v>0</v>
       </c>
       <c r="D103" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E103" s="96" t="str">
@@ -8654,14 +8690,14 @@
     <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B104" s="81">
         <f>'Nach Mannschaften sortiert'!D104</f>
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="C104" s="96">
         <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0</v>
       </c>
       <c r="D104" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E104" s="96" t="str">
@@ -8693,30 +8729,31 @@
     <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105" s="81">
         <f>'Nach Mannschaften sortiert'!D105</f>
-        <v>46312</v>
+        <v>46087</v>
       </c>
       <c r="C105" s="96">
         <f>'Nach Mannschaften sortiert'!E105</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D105" s="96">
-        <v>0.5</v>
+        <f t="shared" si="5"/>
+        <v>0.125</v>
       </c>
       <c r="E105" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F105)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="G105">
         <f>'Nach Mannschaften sortiert'!H105</f>
-        <v>Heim</v>
-      </c>
-      <c r="H105" t="str">
+        <v>0</v>
+      </c>
+      <c r="H105">
         <f>'Nach Mannschaften sortiert'!G105</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>'Nach Mannschaften sortiert'!C105</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J105" s="84" t="s">
         <v>68</v>
@@ -8731,27 +8768,26 @@
     <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106" s="81">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46089</v>
+        <v>46312</v>
       </c>
       <c r="C106" s="96">
         <f>'Nach Mannschaften sortiert'!E106</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D106" s="96">
-        <f t="shared" ref="D106:D126" si="5">IF(I106 = "KM",C106+"1:45",IF(I106="U23",C106+"1:45",IF(I106 = "U16",C106+"1:45",IF(I106 = "U15",C106+"1:30",IF(I106 = "U14",C106+"1:30",IF(I106 = "U13",C106+"1:35",IF(I106 = "U12",C106+"1:10",IF(I106 = "U11",C106+"1:10",IF(I106 = "U10",C106+"1:03",C106+"3:00")))))))))</f>
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E106" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F106)</f>
-        <v/>
-      </c>
-      <c r="G106">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G106" t="str">
         <f>'Nach Mannschaften sortiert'!H106</f>
-        <v>0</v>
-      </c>
-      <c r="H106">
+        <v>Heim</v>
+      </c>
+      <c r="H106" t="str">
         <f>'Nach Mannschaften sortiert'!G106</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I106" t="str">
         <f>'Nach Mannschaften sortiert'!C106</f>
@@ -8770,14 +8806,14 @@
     <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B107" s="81">
         <f>'Nach Mannschaften sortiert'!D107</f>
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="C107" s="96">
         <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="D107" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="D107:D127" si="6">IF(I107 = "KM",C107+"1:45",IF(I107="U23",C107+"1:45",IF(I107 = "U16",C107+"1:45",IF(I107 = "U15",C107+"1:30",IF(I107 = "U14",C107+"1:30",IF(I107 = "U13",C107+"1:35",IF(I107 = "U12",C107+"1:10",IF(I107 = "U11",C107+"1:10",IF(I107 = "U10",C107+"1:03",C107+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E107" s="96" t="str">
@@ -8809,14 +8845,14 @@
     <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B108" s="81">
         <f>'Nach Mannschaften sortiert'!D108</f>
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C108" s="96">
         <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="D108" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E108" s="96" t="str">
@@ -8848,14 +8884,14 @@
     <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109" s="81">
         <f>'Nach Mannschaften sortiert'!D109</f>
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C109" s="96">
         <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="D109" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E109" s="96" t="str">
@@ -8887,14 +8923,14 @@
     <row r="110" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B110" s="81">
         <f>'Nach Mannschaften sortiert'!D110</f>
-        <v>46312</v>
+        <v>46092</v>
       </c>
       <c r="C110" s="96">
         <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="D110" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E110" s="96" t="str">
@@ -8911,7 +8947,7 @@
       </c>
       <c r="I110" t="str">
         <f>'Nach Mannschaften sortiert'!C110</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J110" s="84" t="s">
         <v>68</v>
@@ -8926,14 +8962,14 @@
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="81">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="C111" s="96">
         <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="D111" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E111" s="96" t="str">
@@ -8965,14 +9001,14 @@
     <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112" s="81">
         <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="C112" s="96">
         <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="D112" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E112" s="96" t="str">
@@ -9004,14 +9040,14 @@
     <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113" s="81">
         <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="C113" s="96">
         <f>'Nach Mannschaften sortiert'!E113</f>
         <v>0</v>
       </c>
       <c r="D113" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E113" s="96" t="str">
@@ -9043,14 +9079,14 @@
     <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114" s="81">
         <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="C114" s="96">
         <f>'Nach Mannschaften sortiert'!E114</f>
         <v>0</v>
       </c>
       <c r="D114" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E114" s="96" t="str">
@@ -9082,31 +9118,31 @@
     <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115" s="81">
         <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46230</v>
+        <v>46097</v>
       </c>
       <c r="C115" s="96">
         <f>'Nach Mannschaften sortiert'!E115</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D115" s="96">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>0.125</v>
       </c>
       <c r="E115" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F115)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="G115">
         <f>'Nach Mannschaften sortiert'!H115</f>
-        <v>Heim</v>
-      </c>
-      <c r="H115" t="str">
+        <v>0</v>
+      </c>
+      <c r="H115">
         <f>'Nach Mannschaften sortiert'!G115</f>
-        <v>REAL MADRID CAMP</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>'Nach Mannschaften sortiert'!C115</f>
-        <v>Camp</v>
+        <v>U7</v>
       </c>
       <c r="J115" s="84" t="s">
         <v>68</v>
@@ -9121,14 +9157,14 @@
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116" s="81">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C116" s="96">
         <f>'Nach Mannschaften sortiert'!E116</f>
         <v>0.375</v>
       </c>
       <c r="D116" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E116" s="96" t="str">
@@ -9160,14 +9196,14 @@
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117" s="81">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C117" s="96">
         <f>'Nach Mannschaften sortiert'!E117</f>
         <v>0.375</v>
       </c>
       <c r="D117" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E117" s="96" t="str">
@@ -9199,14 +9235,14 @@
     <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B118" s="81">
         <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C118" s="96">
         <f>'Nach Mannschaften sortiert'!E118</f>
         <v>0.375</v>
       </c>
       <c r="D118" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E118" s="96" t="str">
@@ -9238,14 +9274,14 @@
     <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B119" s="81">
         <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="C119" s="96">
         <f>'Nach Mannschaften sortiert'!E119</f>
         <v>0.375</v>
       </c>
       <c r="D119" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E119" s="96" t="str">
@@ -9277,14 +9313,14 @@
     <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B120" s="81">
         <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="C120" s="96">
         <f>'Nach Mannschaften sortiert'!E120</f>
         <v>0.375</v>
       </c>
       <c r="D120" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E120" s="96" t="str">
@@ -9297,7 +9333,7 @@
       </c>
       <c r="H120" t="str">
         <f>'Nach Mannschaften sortiert'!G120</f>
-        <v>MÄDCHENCAMP</v>
+        <v>REAL MADRID CAMP</v>
       </c>
       <c r="I120" t="str">
         <f>'Nach Mannschaften sortiert'!C120</f>
@@ -9316,14 +9352,14 @@
     <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B121" s="81">
         <f>'Nach Mannschaften sortiert'!D121</f>
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C121" s="96">
         <f>'Nach Mannschaften sortiert'!E121</f>
         <v>0.375</v>
       </c>
       <c r="D121" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E121" s="96" t="str">
@@ -9355,14 +9391,14 @@
     <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B122" s="81">
         <f>'Nach Mannschaften sortiert'!D122</f>
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="C122" s="96">
         <f>'Nach Mannschaften sortiert'!E122</f>
         <v>0.375</v>
       </c>
       <c r="D122" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E122" s="96" t="str">
@@ -9394,14 +9430,14 @@
     <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B123" s="81">
         <f>'Nach Mannschaften sortiert'!D123</f>
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="C123" s="96">
         <f>'Nach Mannschaften sortiert'!E123</f>
         <v>0.375</v>
       </c>
       <c r="D123" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E123" s="96" t="str">
@@ -9414,7 +9450,7 @@
       </c>
       <c r="H123" t="str">
         <f>'Nach Mannschaften sortiert'!G123</f>
-        <v>Teco 7 Camp</v>
+        <v>MÄDCHENCAMP</v>
       </c>
       <c r="I123" t="str">
         <f>'Nach Mannschaften sortiert'!C123</f>
@@ -9433,14 +9469,14 @@
     <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B124" s="81">
         <f>'Nach Mannschaften sortiert'!D124</f>
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C124" s="96">
         <f>'Nach Mannschaften sortiert'!E124</f>
         <v>0.375</v>
       </c>
       <c r="D124" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E124" s="96" t="str">
@@ -9472,14 +9508,14 @@
     <row r="125" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B125" s="81">
         <f>'Nach Mannschaften sortiert'!D125</f>
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C125" s="96">
         <f>'Nach Mannschaften sortiert'!E125</f>
         <v>0.375</v>
       </c>
       <c r="D125" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E125" s="96" t="str">
@@ -9511,14 +9547,14 @@
     <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B126" s="81">
         <f>'Nach Mannschaften sortiert'!D126</f>
-        <v>46256</v>
+        <v>46323</v>
       </c>
       <c r="C126" s="96">
         <f>'Nach Mannschaften sortiert'!E126</f>
         <v>0.375</v>
       </c>
       <c r="D126" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E126" s="96" t="str">
@@ -9531,11 +9567,11 @@
       </c>
       <c r="H126" t="str">
         <f>'Nach Mannschaften sortiert'!G126</f>
-        <v>viele Gegner</v>
+        <v>Teco 7 Camp</v>
       </c>
       <c r="I126" t="str">
         <f>'Nach Mannschaften sortiert'!C126</f>
-        <v>GGG</v>
+        <v>Camp</v>
       </c>
       <c r="J126" s="84" t="s">
         <v>68</v>
@@ -9550,18 +9586,19 @@
     <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B127" s="81">
         <f>'Nach Mannschaften sortiert'!D127</f>
-        <v>46367</v>
+        <v>46256</v>
       </c>
       <c r="C127" s="96">
         <f>'Nach Mannschaften sortiert'!E127</f>
-        <v>0.6875</v>
+        <v>0.375</v>
       </c>
       <c r="D127" s="96">
-        <v>0.875</v>
+        <f t="shared" si="6"/>
+        <v>0.5</v>
       </c>
       <c r="E127" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F127)</f>
-        <v>STEINBRUNN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G127" t="str">
         <f>'Nach Mannschaften sortiert'!H127</f>
@@ -9569,11 +9606,11 @@
       </c>
       <c r="H127" t="str">
         <f>'Nach Mannschaften sortiert'!G127</f>
-        <v>Hallencup 2026_27</v>
+        <v>viele Gegner</v>
       </c>
       <c r="I127" t="str">
         <f>'Nach Mannschaften sortiert'!C127</f>
-        <v>Hallenturnie</v>
+        <v>GGG</v>
       </c>
       <c r="J127" s="84" t="s">
         <v>68</v>
@@ -9588,11 +9625,11 @@
     <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B128" s="81">
         <f>'Nach Mannschaften sortiert'!D128</f>
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="C128" s="96">
         <f>'Nach Mannschaften sortiert'!E128</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D128" s="96">
         <v>0.875</v>
@@ -9626,11 +9663,11 @@
     <row r="129" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B129" s="81">
         <f>'Nach Mannschaften sortiert'!D129</f>
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="C129" s="96">
         <f>'Nach Mannschaften sortiert'!E129</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D129" s="96">
         <v>0.875</v>
@@ -9664,11 +9701,11 @@
     <row r="130" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B130" s="81">
         <f>'Nach Mannschaften sortiert'!D130</f>
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="C130" s="96">
         <f>'Nach Mannschaften sortiert'!E130</f>
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D130" s="96">
         <v>0.875</v>
@@ -9677,20 +9714,17 @@
         <f>UPPER('Nach Mannschaften sortiert'!F130)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="F130" s="84" t="s">
-        <v>72</v>
-      </c>
       <c r="G130" t="str">
         <f>'Nach Mannschaften sortiert'!H130</f>
         <v>Heim</v>
       </c>
       <c r="H130" t="str">
         <f>'Nach Mannschaften sortiert'!G130</f>
-        <v>Weihnachtsfeier 2026</v>
+        <v>Hallencup 2026_27</v>
       </c>
       <c r="I130" t="str">
         <f>'Nach Mannschaften sortiert'!C130</f>
-        <v>Weihnachtsfeier</v>
+        <v>Hallenturnie</v>
       </c>
       <c r="J130" s="84" t="s">
         <v>68</v>
@@ -9699,17 +9733,17 @@
         <v>71</v>
       </c>
       <c r="L130" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B131" s="81">
         <f>'Nach Mannschaften sortiert'!D131</f>
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="C131" s="96">
         <f>'Nach Mannschaften sortiert'!E131</f>
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D131" s="96">
         <v>0.875</v>
@@ -9718,17 +9752,20 @@
         <f>UPPER('Nach Mannschaften sortiert'!F131)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F131" s="84" t="s">
+        <v>72</v>
+      </c>
       <c r="G131" t="str">
         <f>'Nach Mannschaften sortiert'!H131</f>
         <v>Heim</v>
       </c>
       <c r="H131" t="str">
         <f>'Nach Mannschaften sortiert'!G131</f>
-        <v>Hallencup 2026_27</v>
+        <v>Weihnachtsfeier 2026</v>
       </c>
       <c r="I131" t="str">
         <f>'Nach Mannschaften sortiert'!C131</f>
-        <v>Hallenturnie</v>
+        <v>Weihnachtsfeier</v>
       </c>
       <c r="J131" s="84" t="s">
         <v>68</v>
@@ -9737,17 +9774,17 @@
         <v>71</v>
       </c>
       <c r="L131" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="132" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B132" s="81">
         <f>'Nach Mannschaften sortiert'!D132</f>
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="C132" s="96">
         <f>'Nach Mannschaften sortiert'!E132</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D132" s="96">
         <v>0.875</v>
@@ -9781,11 +9818,11 @@
     <row r="133" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B133" s="81">
         <f>'Nach Mannschaften sortiert'!D133</f>
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="C133" s="96">
         <f>'Nach Mannschaften sortiert'!E133</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D133" s="96">
         <v>0.875</v>
@@ -9813,6 +9850,44 @@
         <v>71</v>
       </c>
       <c r="L133" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="134" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B134" s="81">
+        <f>'Nach Mannschaften sortiert'!D134</f>
+        <v>46404</v>
+      </c>
+      <c r="C134" s="96">
+        <f>'Nach Mannschaften sortiert'!E134</f>
+        <v>0.375</v>
+      </c>
+      <c r="D134" s="96">
+        <v>0.875</v>
+      </c>
+      <c r="E134" s="96" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F134)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G134" t="str">
+        <f>'Nach Mannschaften sortiert'!H134</f>
+        <v>Heim</v>
+      </c>
+      <c r="H134" t="str">
+        <f>'Nach Mannschaften sortiert'!G134</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I134" t="str">
+        <f>'Nach Mannschaften sortiert'!C134</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J134" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="K134" t="s">
+        <v>71</v>
+      </c>
+      <c r="L134" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10062,16 +10137,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="122" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
@@ -10098,7 +10173,7 @@
       <c r="H2" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="I2" s="116" t="s">
+      <c r="I2" s="117" t="s">
         <v>117</v>
       </c>
       <c r="J2" s="39"/>
@@ -10118,7 +10193,7 @@
       <c r="F3" s="61"/>
       <c r="G3" s="61"/>
       <c r="H3" s="63"/>
-      <c r="I3" s="117"/>
+      <c r="I3" s="118"/>
       <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10138,7 +10213,7 @@
       </c>
       <c r="G4" s="61"/>
       <c r="H4" s="63"/>
-      <c r="I4" s="117"/>
+      <c r="I4" s="118"/>
       <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10158,7 +10233,7 @@
       </c>
       <c r="G5" s="61"/>
       <c r="H5" s="63"/>
-      <c r="I5" s="117"/>
+      <c r="I5" s="118"/>
       <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10178,7 +10253,7 @@
       </c>
       <c r="G6" s="65"/>
       <c r="H6" s="63"/>
-      <c r="I6" s="117"/>
+      <c r="I6" s="118"/>
       <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10200,7 +10275,7 @@
         <v>127</v>
       </c>
       <c r="H7" s="63"/>
-      <c r="I7" s="117"/>
+      <c r="I7" s="118"/>
       <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10222,7 +10297,7 @@
         <v>127</v>
       </c>
       <c r="H8" s="63"/>
-      <c r="I8" s="117"/>
+      <c r="I8" s="118"/>
       <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10246,7 +10321,7 @@
       <c r="H9" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="I9" s="117"/>
+      <c r="I9" s="118"/>
       <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10268,7 +10343,7 @@
         <v>134</v>
       </c>
       <c r="H10" s="63"/>
-      <c r="I10" s="117"/>
+      <c r="I10" s="118"/>
       <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10288,7 +10363,7 @@
         <v>138</v>
       </c>
       <c r="H11" s="72"/>
-      <c r="I11" s="118"/>
+      <c r="I11" s="119"/>
       <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
@@ -10346,52 +10421,52 @@
       <c r="H14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="119" t="s">
+      <c r="A15" s="120" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="115"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="116"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="121" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="114"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="115"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="116"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="123" t="s">
+      <c r="A17" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="115"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="116"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="113" t="s">
+      <c r="A18" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="114"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="115"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="116"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -10460,783 +10535,783 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="54">
-        <f>'Nach Mannschaften sortiert'!A14</f>
-        <v>13</v>
+        <f>'Nach Mannschaften sortiert'!A15</f>
+        <v>14</v>
       </c>
       <c r="B2" s="54">
-        <f>'Nach Mannschaften sortiert'!B14</f>
+        <f>'Nach Mannschaften sortiert'!B15</f>
         <v>1</v>
       </c>
       <c r="C2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C14</f>
+        <f>'Nach Mannschaften sortiert'!C15</f>
         <v>KM</v>
       </c>
       <c r="D2" s="55">
-        <f>'Nach Mannschaften sortiert'!D14</f>
+        <f>'Nach Mannschaften sortiert'!D15</f>
         <v>46250</v>
       </c>
       <c r="E2" s="97">
-        <f>'Nach Mannschaften sortiert'!E14</f>
+        <f>'Nach Mannschaften sortiert'!E15</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="F2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F14</f>
+        <f>'Nach Mannschaften sortiert'!F15</f>
         <v>Kittsee</v>
       </c>
       <c r="G2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G14</f>
+        <f>'Nach Mannschaften sortiert'!G15</f>
         <v>Kittsee</v>
       </c>
       <c r="H2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H14</f>
+        <f>'Nach Mannschaften sortiert'!H15</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f>'Nach Mannschaften sortiert'!A15</f>
-        <v>14</v>
+        <f>'Nach Mannschaften sortiert'!A16</f>
+        <v>15</v>
       </c>
       <c r="B3" s="54">
-        <f>'Nach Mannschaften sortiert'!B15</f>
+        <f>'Nach Mannschaften sortiert'!B16</f>
         <v>2</v>
       </c>
       <c r="C3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C15</f>
+        <f>'Nach Mannschaften sortiert'!C16</f>
         <v>KM</v>
       </c>
       <c r="D3" s="55">
-        <f>'Nach Mannschaften sortiert'!D15</f>
+        <f>'Nach Mannschaften sortiert'!D16</f>
         <v>46255</v>
       </c>
       <c r="E3" s="97">
-        <f>'Nach Mannschaften sortiert'!E15</f>
+        <f>'Nach Mannschaften sortiert'!E16</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="F3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F15</f>
+        <f>'Nach Mannschaften sortiert'!F16</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="G3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G15</f>
+        <f>'Nach Mannschaften sortiert'!G16</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="H3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H15</f>
+        <f>'Nach Mannschaften sortiert'!H16</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54">
-        <f>'Nach Mannschaften sortiert'!A16</f>
-        <v>15</v>
+        <f>'Nach Mannschaften sortiert'!A17</f>
+        <v>16</v>
       </c>
       <c r="B4" s="54">
-        <f>'Nach Mannschaften sortiert'!B16</f>
+        <f>'Nach Mannschaften sortiert'!B17</f>
         <v>3</v>
       </c>
       <c r="C4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C16</f>
+        <f>'Nach Mannschaften sortiert'!C17</f>
         <v>KM</v>
       </c>
       <c r="D4" s="55">
-        <f>'Nach Mannschaften sortiert'!D16</f>
+        <f>'Nach Mannschaften sortiert'!D17</f>
         <v>46263</v>
       </c>
       <c r="E4" s="97">
-        <f>'Nach Mannschaften sortiert'!E16</f>
+        <f>'Nach Mannschaften sortiert'!E17</f>
         <v>0.75</v>
       </c>
       <c r="F4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F16</f>
+        <f>'Nach Mannschaften sortiert'!F17</f>
         <v>Neufeld</v>
       </c>
       <c r="G4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G16</f>
+        <f>'Nach Mannschaften sortiert'!G17</f>
         <v>Tadten</v>
       </c>
       <c r="H4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H16</f>
+        <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="54">
-        <f>'Nach Mannschaften sortiert'!A50</f>
-        <v>49</v>
+        <f>'Nach Mannschaften sortiert'!A51</f>
+        <v>50</v>
       </c>
       <c r="B5" s="54">
-        <f>'Nach Mannschaften sortiert'!B50</f>
+        <f>'Nach Mannschaften sortiert'!B51</f>
         <v>1</v>
       </c>
       <c r="C5" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C50</f>
+        <f>'Nach Mannschaften sortiert'!C51</f>
         <v>U14</v>
       </c>
       <c r="D5" s="55">
-        <f>'Nach Mannschaften sortiert'!D50</f>
+        <f>'Nach Mannschaften sortiert'!D51</f>
         <v>46033</v>
       </c>
       <c r="E5" s="97">
-        <f>'Nach Mannschaften sortiert'!E50</f>
+        <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="F5" s="54">
-        <f>'Nach Mannschaften sortiert'!F50</f>
+        <f>'Nach Mannschaften sortiert'!F51</f>
         <v>0</v>
       </c>
       <c r="G5" s="54">
-        <f>'Nach Mannschaften sortiert'!G50</f>
+        <f>'Nach Mannschaften sortiert'!G51</f>
         <v>0</v>
       </c>
       <c r="H5" s="54">
-        <f>'Nach Mannschaften sortiert'!H50</f>
+        <f>'Nach Mannschaften sortiert'!H51</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54">
+        <f>'Nach Mannschaften sortiert'!A19</f>
+        <v>18</v>
+      </c>
+      <c r="B6" s="54">
+        <f>'Nach Mannschaften sortiert'!B19</f>
+        <v>5</v>
+      </c>
+      <c r="C6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C19</f>
+        <v>KM</v>
+      </c>
+      <c r="D6" s="55">
+        <f>'Nach Mannschaften sortiert'!D19</f>
+        <v>46276</v>
+      </c>
+      <c r="E6" s="97">
+        <f>'Nach Mannschaften sortiert'!E19</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F19</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G19</f>
+        <v>Winden</v>
+      </c>
+      <c r="H6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H19</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="54">
+        <f>'Nach Mannschaften sortiert'!A61</f>
+        <v>60</v>
+      </c>
+      <c r="B7" s="54">
+        <f>'Nach Mannschaften sortiert'!B61</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C61</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D7" s="55">
+        <f>'Nach Mannschaften sortiert'!D61</f>
+        <v>46043</v>
+      </c>
+      <c r="E7" s="97">
+        <f>'Nach Mannschaften sortiert'!E61</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="54">
+        <f>'Nach Mannschaften sortiert'!F61</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="54">
+        <f>'Nach Mannschaften sortiert'!G61</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="54">
+        <f>'Nach Mannschaften sortiert'!H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54">
+        <f>'Nach Mannschaften sortiert'!A21</f>
+        <v>20</v>
+      </c>
+      <c r="B8" s="54">
+        <f>'Nach Mannschaften sortiert'!B21</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C21</f>
+        <v>KM</v>
+      </c>
+      <c r="D8" s="55">
+        <f>'Nach Mannschaften sortiert'!D21</f>
+        <v>46291</v>
+      </c>
+      <c r="E8" s="97">
+        <f>'Nach Mannschaften sortiert'!E21</f>
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F21</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G21</f>
+        <v>Wallern</v>
+      </c>
+      <c r="H8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H21</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="52">
+        <f>'Nach Mannschaften sortiert'!A116</f>
+        <v>115</v>
+      </c>
+      <c r="B9" s="52">
+        <f>'Nach Mannschaften sortiert'!B116</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C116</f>
+        <v>Camp</v>
+      </c>
+      <c r="D9" s="53">
+        <f>'Nach Mannschaften sortiert'!D116</f>
+        <v>46230</v>
+      </c>
+      <c r="E9" s="98">
+        <f>'Nach Mannschaften sortiert'!E116</f>
+        <v>0.375</v>
+      </c>
+      <c r="F9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F116</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G116</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H116</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="54">
+        <f>'Nach Mannschaften sortiert'!A23</f>
+        <v>22</v>
+      </c>
+      <c r="B10" s="54">
+        <f>'Nach Mannschaften sortiert'!B23</f>
+        <v>9</v>
+      </c>
+      <c r="C10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C23</f>
+        <v>KM</v>
+      </c>
+      <c r="D10" s="55">
+        <f>'Nach Mannschaften sortiert'!D23</f>
+        <v>46304</v>
+      </c>
+      <c r="E10" s="97">
+        <f>'Nach Mannschaften sortiert'!E23</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F23</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G23</f>
+        <v>Wimpassing</v>
+      </c>
+      <c r="H10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H23</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="52">
+        <f>'Nach Mannschaften sortiert'!A117</f>
+        <v>116</v>
+      </c>
+      <c r="B11" s="52">
+        <f>'Nach Mannschaften sortiert'!B117</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C117</f>
+        <v>Camp</v>
+      </c>
+      <c r="D11" s="53">
+        <f>'Nach Mannschaften sortiert'!D117</f>
+        <v>46231</v>
+      </c>
+      <c r="E11" s="98">
+        <f>'Nach Mannschaften sortiert'!E117</f>
+        <v>0.375</v>
+      </c>
+      <c r="F11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F117</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G117</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H117</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="54">
+        <f>'Nach Mannschaften sortiert'!A25</f>
+        <v>24</v>
+      </c>
+      <c r="B12" s="54">
+        <f>'Nach Mannschaften sortiert'!B25</f>
+        <v>11</v>
+      </c>
+      <c r="C12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C25</f>
+        <v>KM</v>
+      </c>
+      <c r="D12" s="55">
+        <f>'Nach Mannschaften sortiert'!D25</f>
+        <v>46319</v>
+      </c>
+      <c r="E12" s="97">
+        <f>'Nach Mannschaften sortiert'!E25</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F25</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G25</f>
+        <v>Gols</v>
+      </c>
+      <c r="H12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H25</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <f>'Nach Mannschaften sortiert'!A26</f>
+        <v>25</v>
+      </c>
+      <c r="B13" s="54">
+        <f>'Nach Mannschaften sortiert'!B26</f>
+        <v>12</v>
+      </c>
+      <c r="C13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C26</f>
+        <v>KM</v>
+      </c>
+      <c r="D13" s="55">
+        <f>'Nach Mannschaften sortiert'!D26</f>
+        <v>46326</v>
+      </c>
+      <c r="E13" s="97">
+        <f>'Nach Mannschaften sortiert'!E26</f>
+        <v>0.75</v>
+      </c>
+      <c r="F13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F26</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="G13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G26</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="H13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H26</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="52">
+        <f>'Nach Mannschaften sortiert'!A118</f>
+        <v>117</v>
+      </c>
+      <c r="B14" s="52">
+        <f>'Nach Mannschaften sortiert'!B118</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C118</f>
+        <v>Camp</v>
+      </c>
+      <c r="D14" s="53">
+        <f>'Nach Mannschaften sortiert'!D118</f>
+        <v>46232</v>
+      </c>
+      <c r="E14" s="98">
+        <f>'Nach Mannschaften sortiert'!E118</f>
+        <v>0.375</v>
+      </c>
+      <c r="F14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F118</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G118</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H118</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
+        <f>'Nach Mannschaften sortiert'!A41</f>
+        <v>40</v>
+      </c>
+      <c r="B15" s="54">
+        <f>'Nach Mannschaften sortiert'!B41</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C41</f>
+        <v>U16</v>
+      </c>
+      <c r="D15" s="55">
+        <f>'Nach Mannschaften sortiert'!D41</f>
+        <v>46023</v>
+      </c>
+      <c r="E15" s="97">
+        <f>'Nach Mannschaften sortiert'!E41</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="54">
+        <f>'Nach Mannschaften sortiert'!F41</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="54">
+        <f>'Nach Mannschaften sortiert'!G41</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="54">
+        <f>'Nach Mannschaften sortiert'!H41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="48">
+        <f>'Nach Mannschaften sortiert'!A42</f>
+        <v>41</v>
+      </c>
+      <c r="B16" s="48">
+        <f>'Nach Mannschaften sortiert'!B42</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C42</f>
+        <v>U16</v>
+      </c>
+      <c r="D16" s="49">
+        <f>'Nach Mannschaften sortiert'!D42</f>
+        <v>46024</v>
+      </c>
+      <c r="E16" s="99">
+        <f>'Nach Mannschaften sortiert'!E42</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="48">
+        <f>'Nach Mannschaften sortiert'!F42</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="48">
+        <f>'Nach Mannschaften sortiert'!G42</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="48">
+        <f>'Nach Mannschaften sortiert'!H42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <f>'Nach Mannschaften sortiert'!A43</f>
+        <v>42</v>
+      </c>
+      <c r="B17" s="54">
+        <f>'Nach Mannschaften sortiert'!B43</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C43</f>
+        <v>U16</v>
+      </c>
+      <c r="D17" s="55">
+        <f>'Nach Mannschaften sortiert'!D43</f>
+        <v>46025</v>
+      </c>
+      <c r="E17" s="97">
+        <f>'Nach Mannschaften sortiert'!E43</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="54">
+        <f>'Nach Mannschaften sortiert'!F43</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="54">
+        <f>'Nach Mannschaften sortiert'!G43</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="54">
+        <f>'Nach Mannschaften sortiert'!H43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="54">
         <f>'Nach Mannschaften sortiert'!A18</f>
         <v>17</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B18" s="54">
         <f>'Nach Mannschaften sortiert'!B18</f>
-        <v>5</v>
-      </c>
-      <c r="C6" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
         <v>KM</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D18" s="55">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46276</v>
-      </c>
-      <c r="E6" s="97">
+        <v>46270</v>
+      </c>
+      <c r="E18" s="97">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F6" s="54" t="str">
+        <v>0.6875</v>
+      </c>
+      <c r="F18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F18</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="G18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Winden</v>
-      </c>
-      <c r="H6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="H18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="54">
-        <f>'Nach Mannschaften sortiert'!A60</f>
-        <v>59</v>
-      </c>
-      <c r="B7" s="54">
-        <f>'Nach Mannschaften sortiert'!B60</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C60</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D7" s="55">
-        <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46043</v>
-      </c>
-      <c r="E7" s="97">
-        <f>'Nach Mannschaften sortiert'!E60</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="54">
-        <f>'Nach Mannschaften sortiert'!F60</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="54">
-        <f>'Nach Mannschaften sortiert'!G60</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="54">
-        <f>'Nach Mannschaften sortiert'!H60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54">
-        <f>'Nach Mannschaften sortiert'!A20</f>
-        <v>19</v>
-      </c>
-      <c r="B8" s="54">
-        <f>'Nach Mannschaften sortiert'!B20</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C20</f>
-        <v>KM</v>
-      </c>
-      <c r="D8" s="55">
-        <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46291</v>
-      </c>
-      <c r="E8" s="97">
-        <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.75</v>
-      </c>
-      <c r="F8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F20</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Wallern</v>
-      </c>
-      <c r="H8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="52">
-        <f>'Nach Mannschaften sortiert'!A115</f>
-        <v>114</v>
-      </c>
-      <c r="B9" s="52">
-        <f>'Nach Mannschaften sortiert'!B115</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C115</f>
-        <v>Camp</v>
-      </c>
-      <c r="D9" s="53">
-        <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46230</v>
-      </c>
-      <c r="E9" s="98">
-        <f>'Nach Mannschaften sortiert'!E115</f>
-        <v>0.375</v>
-      </c>
-      <c r="F9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F115</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G115</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H115</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54">
-        <f>'Nach Mannschaften sortiert'!A22</f>
-        <v>21</v>
-      </c>
-      <c r="B10" s="54">
-        <f>'Nach Mannschaften sortiert'!B22</f>
-        <v>9</v>
-      </c>
-      <c r="C10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C22</f>
-        <v>KM</v>
-      </c>
-      <c r="D10" s="55">
-        <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46304</v>
-      </c>
-      <c r="E10" s="97">
-        <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F22</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Wimpassing</v>
-      </c>
-      <c r="H10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="52">
-        <f>'Nach Mannschaften sortiert'!A116</f>
-        <v>115</v>
-      </c>
-      <c r="B11" s="52">
-        <f>'Nach Mannschaften sortiert'!B116</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C116</f>
-        <v>Camp</v>
-      </c>
-      <c r="D11" s="53">
-        <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46231</v>
-      </c>
-      <c r="E11" s="98">
-        <f>'Nach Mannschaften sortiert'!E116</f>
-        <v>0.375</v>
-      </c>
-      <c r="F11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F116</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G116</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H116</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <f>'Nach Mannschaften sortiert'!A24</f>
-        <v>23</v>
-      </c>
-      <c r="B12" s="54">
-        <f>'Nach Mannschaften sortiert'!B24</f>
-        <v>11</v>
-      </c>
-      <c r="C12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C24</f>
-        <v>KM</v>
-      </c>
-      <c r="D12" s="55">
-        <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46319</v>
-      </c>
-      <c r="E12" s="97">
-        <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F24</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>Gols</v>
-      </c>
-      <c r="H12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H24</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54">
-        <f>'Nach Mannschaften sortiert'!A25</f>
-        <v>24</v>
-      </c>
-      <c r="B13" s="54">
-        <f>'Nach Mannschaften sortiert'!B25</f>
-        <v>12</v>
-      </c>
-      <c r="C13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C25</f>
-        <v>KM</v>
-      </c>
-      <c r="D13" s="55">
-        <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46326</v>
-      </c>
-      <c r="E13" s="97">
-        <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.75</v>
-      </c>
-      <c r="F13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F25</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="G13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="H13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="52">
-        <f>'Nach Mannschaften sortiert'!A117</f>
-        <v>116</v>
-      </c>
-      <c r="B14" s="52">
-        <f>'Nach Mannschaften sortiert'!B117</f>
-        <v>3</v>
-      </c>
-      <c r="C14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C117</f>
-        <v>Camp</v>
-      </c>
-      <c r="D14" s="53">
-        <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46232</v>
-      </c>
-      <c r="E14" s="98">
-        <f>'Nach Mannschaften sortiert'!E117</f>
-        <v>0.375</v>
-      </c>
-      <c r="F14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F117</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G117</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H117</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54">
-        <f>'Nach Mannschaften sortiert'!A40</f>
-        <v>39</v>
-      </c>
-      <c r="B15" s="54">
-        <f>'Nach Mannschaften sortiert'!B40</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C40</f>
-        <v>U16</v>
-      </c>
-      <c r="D15" s="55">
-        <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46023</v>
-      </c>
-      <c r="E15" s="97">
-        <f>'Nach Mannschaften sortiert'!E40</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="54">
-        <f>'Nach Mannschaften sortiert'!F40</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="54">
-        <f>'Nach Mannschaften sortiert'!G40</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="54">
-        <f>'Nach Mannschaften sortiert'!H40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48">
-        <f>'Nach Mannschaften sortiert'!A41</f>
-        <v>40</v>
-      </c>
-      <c r="B16" s="48">
-        <f>'Nach Mannschaften sortiert'!B41</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C41</f>
-        <v>U16</v>
-      </c>
-      <c r="D16" s="49">
-        <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46024</v>
-      </c>
-      <c r="E16" s="99">
-        <f>'Nach Mannschaften sortiert'!E41</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="48">
-        <f>'Nach Mannschaften sortiert'!F41</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="48">
-        <f>'Nach Mannschaften sortiert'!G41</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="48">
-        <f>'Nach Mannschaften sortiert'!H41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54">
-        <f>'Nach Mannschaften sortiert'!A42</f>
-        <v>41</v>
-      </c>
-      <c r="B17" s="54">
-        <f>'Nach Mannschaften sortiert'!B42</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C42</f>
-        <v>U16</v>
-      </c>
-      <c r="D17" s="55">
-        <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46025</v>
-      </c>
-      <c r="E17" s="97">
-        <f>'Nach Mannschaften sortiert'!E42</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="54">
-        <f>'Nach Mannschaften sortiert'!F42</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="54">
-        <f>'Nach Mannschaften sortiert'!G42</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="54">
-        <f>'Nach Mannschaften sortiert'!H42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="54">
-        <f>'Nach Mannschaften sortiert'!A17</f>
-        <v>16</v>
-      </c>
-      <c r="B18" s="54">
-        <f>'Nach Mannschaften sortiert'!B17</f>
-        <v>4</v>
-      </c>
-      <c r="C18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
-        <v>KM</v>
-      </c>
-      <c r="D18" s="55">
-        <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46270</v>
-      </c>
-      <c r="E18" s="97">
-        <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.6875</v>
-      </c>
-      <c r="F18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F17</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="G18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="H18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54">
-        <f>'Nach Mannschaften sortiert'!A44</f>
-        <v>43</v>
+        <f>'Nach Mannschaften sortiert'!A45</f>
+        <v>44</v>
       </c>
       <c r="B19" s="54">
-        <f>'Nach Mannschaften sortiert'!B44</f>
+        <f>'Nach Mannschaften sortiert'!B45</f>
         <v>5</v>
       </c>
       <c r="C19" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C44</f>
+        <f>'Nach Mannschaften sortiert'!C45</f>
         <v>U16</v>
       </c>
       <c r="D19" s="55">
-        <f>'Nach Mannschaften sortiert'!D44</f>
+        <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46027</v>
       </c>
       <c r="E19" s="97">
-        <f>'Nach Mannschaften sortiert'!E44</f>
+        <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="F19" s="54">
-        <f>'Nach Mannschaften sortiert'!F44</f>
+        <f>'Nach Mannschaften sortiert'!F45</f>
         <v>0</v>
       </c>
       <c r="G19" s="54">
-        <f>'Nach Mannschaften sortiert'!G44</f>
+        <f>'Nach Mannschaften sortiert'!G45</f>
         <v>0</v>
       </c>
       <c r="H19" s="54">
-        <f>'Nach Mannschaften sortiert'!H44</f>
+        <f>'Nach Mannschaften sortiert'!H45</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
-        <f>'Nach Mannschaften sortiert'!A45</f>
-        <v>44</v>
+        <f>'Nach Mannschaften sortiert'!A46</f>
+        <v>45</v>
       </c>
       <c r="B20" s="46">
-        <f>'Nach Mannschaften sortiert'!B45</f>
+        <f>'Nach Mannschaften sortiert'!B46</f>
         <v>6</v>
       </c>
       <c r="C20" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C45</f>
+        <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U16</v>
       </c>
       <c r="D20" s="47">
-        <f>'Nach Mannschaften sortiert'!D45</f>
+        <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46028</v>
       </c>
       <c r="E20" s="100">
-        <f>'Nach Mannschaften sortiert'!E45</f>
+        <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="F20" s="46">
-        <f>'Nach Mannschaften sortiert'!F45</f>
+        <f>'Nach Mannschaften sortiert'!F46</f>
         <v>0</v>
       </c>
       <c r="G20" s="46">
-        <f>'Nach Mannschaften sortiert'!G45</f>
+        <f>'Nach Mannschaften sortiert'!G46</f>
         <v>0</v>
       </c>
       <c r="H20" s="46">
-        <f>'Nach Mannschaften sortiert'!H45</f>
+        <f>'Nach Mannschaften sortiert'!H46</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54">
-        <f>'Nach Mannschaften sortiert'!A46</f>
-        <v>45</v>
+        <f>'Nach Mannschaften sortiert'!A47</f>
+        <v>46</v>
       </c>
       <c r="B21" s="54">
-        <f>'Nach Mannschaften sortiert'!B46</f>
+        <f>'Nach Mannschaften sortiert'!B47</f>
         <v>7</v>
       </c>
       <c r="C21" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C46</f>
+        <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U16</v>
       </c>
       <c r="D21" s="55">
-        <f>'Nach Mannschaften sortiert'!D46</f>
+        <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46029</v>
       </c>
       <c r="E21" s="97">
-        <f>'Nach Mannschaften sortiert'!E46</f>
+        <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="F21" s="54">
-        <f>'Nach Mannschaften sortiert'!F46</f>
+        <f>'Nach Mannschaften sortiert'!F47</f>
         <v>0</v>
       </c>
       <c r="G21" s="54">
-        <f>'Nach Mannschaften sortiert'!G46</f>
+        <f>'Nach Mannschaften sortiert'!G47</f>
         <v>0</v>
       </c>
       <c r="H21" s="54">
-        <f>'Nach Mannschaften sortiert'!H46</f>
+        <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
-        <f>'Nach Mannschaften sortiert'!A47</f>
-        <v>46</v>
+        <f>'Nach Mannschaften sortiert'!A48</f>
+        <v>47</v>
       </c>
       <c r="B22" s="48">
-        <f>'Nach Mannschaften sortiert'!B47</f>
+        <f>'Nach Mannschaften sortiert'!B48</f>
         <v>8</v>
       </c>
       <c r="C22" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C47</f>
+        <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U16</v>
       </c>
       <c r="D22" s="49">
-        <f>'Nach Mannschaften sortiert'!D47</f>
+        <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46030</v>
       </c>
       <c r="E22" s="99">
-        <f>'Nach Mannschaften sortiert'!E47</f>
+        <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="F22" s="48">
-        <f>'Nach Mannschaften sortiert'!F47</f>
+        <f>'Nach Mannschaften sortiert'!F48</f>
         <v>0</v>
       </c>
       <c r="G22" s="48">
-        <f>'Nach Mannschaften sortiert'!G47</f>
+        <f>'Nach Mannschaften sortiert'!G48</f>
         <v>0</v>
       </c>
       <c r="H22" s="48">
-        <f>'Nach Mannschaften sortiert'!H47</f>
+        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54">
-        <f>'Nach Mannschaften sortiert'!A48</f>
-        <v>47</v>
+        <f>'Nach Mannschaften sortiert'!A49</f>
+        <v>48</v>
       </c>
       <c r="B23" s="54">
-        <f>'Nach Mannschaften sortiert'!B48</f>
+        <f>'Nach Mannschaften sortiert'!B49</f>
         <v>9</v>
       </c>
       <c r="C23" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C48</f>
+        <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U16</v>
       </c>
       <c r="D23" s="55">
-        <f>'Nach Mannschaften sortiert'!D48</f>
+        <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46031</v>
       </c>
       <c r="E23" s="97">
-        <f>'Nach Mannschaften sortiert'!E48</f>
+        <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="F23" s="54">
-        <f>'Nach Mannschaften sortiert'!F48</f>
+        <f>'Nach Mannschaften sortiert'!F49</f>
         <v>0</v>
       </c>
       <c r="G23" s="54">
-        <f>'Nach Mannschaften sortiert'!G48</f>
+        <f>'Nach Mannschaften sortiert'!G49</f>
         <v>0</v>
       </c>
       <c r="H23" s="54">
-        <f>'Nach Mannschaften sortiert'!H48</f>
+        <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
-        <f>'Nach Mannschaften sortiert'!A95</f>
-        <v>94</v>
+        <f>'Nach Mannschaften sortiert'!A96</f>
+        <v>95</v>
       </c>
       <c r="B24" s="50">
-        <f>'Nach Mannschaften sortiert'!B95</f>
+        <f>'Nach Mannschaften sortiert'!B96</f>
         <v>1</v>
       </c>
       <c r="C24" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C95</f>
+        <f>'Nach Mannschaften sortiert'!C96</f>
         <v>U9</v>
       </c>
       <c r="D24" s="51">
-        <f>'Nach Mannschaften sortiert'!D95</f>
+        <f>'Nach Mannschaften sortiert'!D96</f>
         <v>46078</v>
       </c>
       <c r="E24" s="101">
-        <f>'Nach Mannschaften sortiert'!E95</f>
+        <f>'Nach Mannschaften sortiert'!E96</f>
         <v>0</v>
       </c>
       <c r="F24" s="50">
-        <f>'Nach Mannschaften sortiert'!F95</f>
+        <f>'Nach Mannschaften sortiert'!F96</f>
         <v>0</v>
       </c>
       <c r="G24" s="50">
-        <f>'Nach Mannschaften sortiert'!G95</f>
+        <f>'Nach Mannschaften sortiert'!G96</f>
         <v>0</v>
       </c>
       <c r="H24" s="50">
-        <f>'Nach Mannschaften sortiert'!H95</f>
+        <f>'Nach Mannschaften sortiert'!H96</f>
         <v>0</v>
       </c>
     </row>
@@ -11276,35 +11351,35 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
-        <f>'Nach Mannschaften sortiert'!A105</f>
-        <v>104</v>
+        <f>'Nach Mannschaften sortiert'!A106</f>
+        <v>105</v>
       </c>
       <c r="B26" s="50">
-        <f>'Nach Mannschaften sortiert'!B105</f>
+        <f>'Nach Mannschaften sortiert'!B106</f>
         <v>1</v>
       </c>
       <c r="C26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C105</f>
+        <f>'Nach Mannschaften sortiert'!C106</f>
         <v>U8</v>
       </c>
       <c r="D26" s="51">
-        <f>'Nach Mannschaften sortiert'!D105</f>
+        <f>'Nach Mannschaften sortiert'!D106</f>
         <v>46312</v>
       </c>
       <c r="E26" s="101">
-        <f>'Nach Mannschaften sortiert'!E105</f>
+        <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0.39583333333333331</v>
       </c>
       <c r="F26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!F105</f>
+        <f>'Nach Mannschaften sortiert'!F106</f>
         <v>Neufeld</v>
       </c>
       <c r="G26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!G105</f>
+        <f>'Nach Mannschaften sortiert'!G106</f>
         <v>Heimturnier</v>
       </c>
       <c r="H26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!H105</f>
+        <f>'Nach Mannschaften sortiert'!H106</f>
         <v>Heim</v>
       </c>
     </row>
@@ -11378,35 +11453,35 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="50">
-        <f>'Nach Mannschaften sortiert'!A110</f>
-        <v>109</v>
+        <f>'Nach Mannschaften sortiert'!A111</f>
+        <v>110</v>
       </c>
       <c r="B29" s="50">
-        <f>'Nach Mannschaften sortiert'!B110</f>
+        <f>'Nach Mannschaften sortiert'!B111</f>
         <v>1</v>
       </c>
       <c r="C29" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C110</f>
+        <f>'Nach Mannschaften sortiert'!C111</f>
         <v>U7</v>
       </c>
       <c r="D29" s="51">
-        <f>'Nach Mannschaften sortiert'!D110</f>
+        <f>'Nach Mannschaften sortiert'!D111</f>
         <v>46312</v>
       </c>
       <c r="E29" s="101">
-        <f>'Nach Mannschaften sortiert'!E110</f>
+        <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="F29" s="50">
-        <f>'Nach Mannschaften sortiert'!F110</f>
+        <f>'Nach Mannschaften sortiert'!F111</f>
         <v>0</v>
       </c>
       <c r="G29" s="50">
-        <f>'Nach Mannschaften sortiert'!G110</f>
+        <f>'Nach Mannschaften sortiert'!G111</f>
         <v>0</v>
       </c>
       <c r="H29" s="50">
-        <f>'Nach Mannschaften sortiert'!H110</f>
+        <f>'Nach Mannschaften sortiert'!H111</f>
         <v>0</v>
       </c>
     </row>
@@ -11582,103 +11657,103 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="50">
-        <f>'Nach Mannschaften sortiert'!A81</f>
-        <v>80</v>
+        <f>'Nach Mannschaften sortiert'!A82</f>
+        <v>81</v>
       </c>
       <c r="B35" s="50">
-        <f>'Nach Mannschaften sortiert'!B81</f>
+        <f>'Nach Mannschaften sortiert'!B82</f>
         <v>2</v>
       </c>
       <c r="C35" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C81</f>
+        <f>'Nach Mannschaften sortiert'!C82</f>
         <v>U11</v>
       </c>
       <c r="D35" s="51">
-        <f>'Nach Mannschaften sortiert'!D81</f>
+        <f>'Nach Mannschaften sortiert'!D82</f>
         <v>46064</v>
       </c>
       <c r="E35" s="101">
-        <f>'Nach Mannschaften sortiert'!E81</f>
+        <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="F35" s="50">
-        <f>'Nach Mannschaften sortiert'!F81</f>
+        <f>'Nach Mannschaften sortiert'!F82</f>
         <v>0</v>
       </c>
       <c r="G35" s="50">
-        <f>'Nach Mannschaften sortiert'!G81</f>
+        <f>'Nach Mannschaften sortiert'!G82</f>
         <v>0</v>
       </c>
       <c r="H35" s="50">
-        <f>'Nach Mannschaften sortiert'!H81</f>
+        <f>'Nach Mannschaften sortiert'!H82</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="54">
-        <f>'Nach Mannschaften sortiert'!A51</f>
-        <v>50</v>
+        <f>'Nach Mannschaften sortiert'!A52</f>
+        <v>51</v>
       </c>
       <c r="B36" s="54">
-        <f>'Nach Mannschaften sortiert'!B51</f>
+        <f>'Nach Mannschaften sortiert'!B52</f>
         <v>2</v>
       </c>
       <c r="C36" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C51</f>
+        <f>'Nach Mannschaften sortiert'!C52</f>
         <v>U14</v>
       </c>
       <c r="D36" s="55">
-        <f>'Nach Mannschaften sortiert'!D51</f>
+        <f>'Nach Mannschaften sortiert'!D52</f>
         <v>46034</v>
       </c>
       <c r="E36" s="97">
-        <f>'Nach Mannschaften sortiert'!E51</f>
+        <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="F36" s="54">
-        <f>'Nach Mannschaften sortiert'!F51</f>
+        <f>'Nach Mannschaften sortiert'!F52</f>
         <v>0</v>
       </c>
       <c r="G36" s="54">
-        <f>'Nach Mannschaften sortiert'!G51</f>
+        <f>'Nach Mannschaften sortiert'!G52</f>
         <v>0</v>
       </c>
       <c r="H36" s="54">
-        <f>'Nach Mannschaften sortiert'!H51</f>
+        <f>'Nach Mannschaften sortiert'!H52</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="54">
-        <f>'Nach Mannschaften sortiert'!A52</f>
-        <v>51</v>
+        <f>'Nach Mannschaften sortiert'!A53</f>
+        <v>52</v>
       </c>
       <c r="B37" s="54">
-        <f>'Nach Mannschaften sortiert'!B52</f>
+        <f>'Nach Mannschaften sortiert'!B53</f>
         <v>3</v>
       </c>
       <c r="C37" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C52</f>
+        <f>'Nach Mannschaften sortiert'!C53</f>
         <v>U14</v>
       </c>
       <c r="D37" s="55">
-        <f>'Nach Mannschaften sortiert'!D52</f>
+        <f>'Nach Mannschaften sortiert'!D53</f>
         <v>46035</v>
       </c>
       <c r="E37" s="97">
-        <f>'Nach Mannschaften sortiert'!E52</f>
+        <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="F37" s="54">
-        <f>'Nach Mannschaften sortiert'!F52</f>
+        <f>'Nach Mannschaften sortiert'!F53</f>
         <v>0</v>
       </c>
       <c r="G37" s="54">
-        <f>'Nach Mannschaften sortiert'!G52</f>
+        <f>'Nach Mannschaften sortiert'!G53</f>
         <v>0</v>
       </c>
       <c r="H37" s="54">
-        <f>'Nach Mannschaften sortiert'!H52</f>
+        <f>'Nach Mannschaften sortiert'!H53</f>
         <v>0</v>
       </c>
     </row>
@@ -11752,205 +11827,205 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54">
+        <f>'Nach Mannschaften sortiert'!A55</f>
+        <v>54</v>
+      </c>
+      <c r="B40" s="54">
+        <f>'Nach Mannschaften sortiert'!B55</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C55</f>
+        <v>U14</v>
+      </c>
+      <c r="D40" s="55">
+        <f>'Nach Mannschaften sortiert'!D55</f>
+        <v>46037</v>
+      </c>
+      <c r="E40" s="97">
+        <f>'Nach Mannschaften sortiert'!E55</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="54">
+        <f>'Nach Mannschaften sortiert'!F55</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="54">
+        <f>'Nach Mannschaften sortiert'!G55</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="54">
+        <f>'Nach Mannschaften sortiert'!H55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="48">
+        <f>'Nach Mannschaften sortiert'!A20</f>
+        <v>19</v>
+      </c>
+      <c r="B41" s="48">
+        <f>'Nach Mannschaften sortiert'!B20</f>
+        <v>6</v>
+      </c>
+      <c r="C41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C20</f>
+        <v>KM</v>
+      </c>
+      <c r="D41" s="49">
+        <f>'Nach Mannschaften sortiert'!D20</f>
+        <v>46284</v>
+      </c>
+      <c r="E41" s="99">
+        <f>'Nach Mannschaften sortiert'!E20</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!F20</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="G41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!G20</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="H41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!H20</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="54">
+        <f>'Nach Mannschaften sortiert'!A86</f>
+        <v>85</v>
+      </c>
+      <c r="B42" s="54">
+        <f>'Nach Mannschaften sortiert'!B86</f>
+        <v>6</v>
+      </c>
+      <c r="C42" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C86</f>
+        <v>U11</v>
+      </c>
+      <c r="D42" s="55">
+        <f>'Nach Mannschaften sortiert'!D86</f>
+        <v>46068</v>
+      </c>
+      <c r="E42" s="97">
+        <f>'Nach Mannschaften sortiert'!E86</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="54">
+        <f>'Nach Mannschaften sortiert'!F86</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="54">
+        <f>'Nach Mannschaften sortiert'!G86</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="54">
+        <f>'Nach Mannschaften sortiert'!H86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="54">
+        <f>'Nach Mannschaften sortiert'!A60</f>
+        <v>59</v>
+      </c>
+      <c r="B43" s="54">
+        <f>'Nach Mannschaften sortiert'!B60</f>
+        <v>10</v>
+      </c>
+      <c r="C43" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C60</f>
+        <v>U14</v>
+      </c>
+      <c r="D43" s="55">
+        <f>'Nach Mannschaften sortiert'!D60</f>
+        <v>46042</v>
+      </c>
+      <c r="E43" s="97">
+        <f>'Nach Mannschaften sortiert'!E60</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="54">
+        <f>'Nach Mannschaften sortiert'!F60</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="54">
+        <f>'Nach Mannschaften sortiert'!G60</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="54">
+        <f>'Nach Mannschaften sortiert'!H60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="50">
+        <f>'Nach Mannschaften sortiert'!A63</f>
+        <v>62</v>
+      </c>
+      <c r="B44" s="50">
+        <f>'Nach Mannschaften sortiert'!B63</f>
+        <v>3</v>
+      </c>
+      <c r="C44" s="50" t="str">
+        <f>'Nach Mannschaften sortiert'!C63</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D44" s="51">
+        <f>'Nach Mannschaften sortiert'!D63</f>
+        <v>46045</v>
+      </c>
+      <c r="E44" s="101">
+        <f>'Nach Mannschaften sortiert'!E63</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="50">
+        <f>'Nach Mannschaften sortiert'!F63</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="50">
+        <f>'Nach Mannschaften sortiert'!G63</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="50">
+        <f>'Nach Mannschaften sortiert'!H63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="50">
         <f>'Nach Mannschaften sortiert'!A54</f>
         <v>53</v>
       </c>
-      <c r="B40" s="54">
+      <c r="B45" s="50">
         <f>'Nach Mannschaften sortiert'!B54</f>
-        <v>5</v>
-      </c>
-      <c r="C40" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C45" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U14</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D45" s="51">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46037</v>
-      </c>
-      <c r="E40" s="97">
+        <v>46036</v>
+      </c>
+      <c r="E45" s="101">
         <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
-      <c r="F40" s="54">
+      <c r="F45" s="50">
         <f>'Nach Mannschaften sortiert'!F54</f>
         <v>0</v>
       </c>
-      <c r="G40" s="54">
+      <c r="G45" s="50">
         <f>'Nach Mannschaften sortiert'!G54</f>
         <v>0</v>
       </c>
-      <c r="H40" s="54">
+      <c r="H45" s="50">
         <f>'Nach Mannschaften sortiert'!H54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="48">
-        <f>'Nach Mannschaften sortiert'!A19</f>
-        <v>18</v>
-      </c>
-      <c r="B41" s="48">
-        <f>'Nach Mannschaften sortiert'!B19</f>
-        <v>6</v>
-      </c>
-      <c r="C41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C19</f>
-        <v>KM</v>
-      </c>
-      <c r="D41" s="49">
-        <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46284</v>
-      </c>
-      <c r="E41" s="99">
-        <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F19</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="G41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="H41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="54">
-        <f>'Nach Mannschaften sortiert'!A85</f>
-        <v>84</v>
-      </c>
-      <c r="B42" s="54">
-        <f>'Nach Mannschaften sortiert'!B85</f>
-        <v>6</v>
-      </c>
-      <c r="C42" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C85</f>
-        <v>U11</v>
-      </c>
-      <c r="D42" s="55">
-        <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46068</v>
-      </c>
-      <c r="E42" s="97">
-        <f>'Nach Mannschaften sortiert'!E85</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="54">
-        <f>'Nach Mannschaften sortiert'!F85</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="54">
-        <f>'Nach Mannschaften sortiert'!G85</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="54">
-        <f>'Nach Mannschaften sortiert'!H85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="54">
-        <f>'Nach Mannschaften sortiert'!A59</f>
-        <v>58</v>
-      </c>
-      <c r="B43" s="54">
-        <f>'Nach Mannschaften sortiert'!B59</f>
-        <v>10</v>
-      </c>
-      <c r="C43" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C59</f>
-        <v>U14</v>
-      </c>
-      <c r="D43" s="55">
-        <f>'Nach Mannschaften sortiert'!D59</f>
-        <v>46042</v>
-      </c>
-      <c r="E43" s="97">
-        <f>'Nach Mannschaften sortiert'!E59</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="54">
-        <f>'Nach Mannschaften sortiert'!F59</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="54">
-        <f>'Nach Mannschaften sortiert'!G59</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="54">
-        <f>'Nach Mannschaften sortiert'!H59</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="50">
-        <f>'Nach Mannschaften sortiert'!A62</f>
-        <v>61</v>
-      </c>
-      <c r="B44" s="50">
-        <f>'Nach Mannschaften sortiert'!B62</f>
-        <v>3</v>
-      </c>
-      <c r="C44" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C62</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D44" s="51">
-        <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46045</v>
-      </c>
-      <c r="E44" s="101">
-        <f>'Nach Mannschaften sortiert'!E62</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="50">
-        <f>'Nach Mannschaften sortiert'!F62</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="50">
-        <f>'Nach Mannschaften sortiert'!G62</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="50">
-        <f>'Nach Mannschaften sortiert'!H62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="50">
-        <f>'Nach Mannschaften sortiert'!A53</f>
-        <v>52</v>
-      </c>
-      <c r="B45" s="50">
-        <f>'Nach Mannschaften sortiert'!B53</f>
-        <v>4</v>
-      </c>
-      <c r="C45" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C53</f>
-        <v>U14</v>
-      </c>
-      <c r="D45" s="51">
-        <f>'Nach Mannschaften sortiert'!D53</f>
-        <v>46036</v>
-      </c>
-      <c r="E45" s="101">
-        <f>'Nach Mannschaften sortiert'!E53</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="50">
-        <f>'Nach Mannschaften sortiert'!F53</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="50">
-        <f>'Nach Mannschaften sortiert'!G53</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="50">
-        <f>'Nach Mannschaften sortiert'!H53</f>
         <v>0</v>
       </c>
     </row>
@@ -11990,137 +12065,137 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54">
-        <f>'Nach Mannschaften sortiert'!A61</f>
-        <v>60</v>
+        <f>'Nach Mannschaften sortiert'!A62</f>
+        <v>61</v>
       </c>
       <c r="B47" s="54">
-        <f>'Nach Mannschaften sortiert'!B61</f>
+        <f>'Nach Mannschaften sortiert'!B62</f>
         <v>2</v>
       </c>
       <c r="C47" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C61</f>
+        <f>'Nach Mannschaften sortiert'!C62</f>
         <v>U12_1</v>
       </c>
       <c r="D47" s="55">
-        <f>'Nach Mannschaften sortiert'!D61</f>
+        <f>'Nach Mannschaften sortiert'!D62</f>
         <v>46044</v>
       </c>
       <c r="E47" s="97">
-        <f>'Nach Mannschaften sortiert'!E61</f>
+        <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="F47" s="54">
-        <f>'Nach Mannschaften sortiert'!F61</f>
+        <f>'Nach Mannschaften sortiert'!F62</f>
         <v>0</v>
       </c>
       <c r="G47" s="54">
-        <f>'Nach Mannschaften sortiert'!G61</f>
+        <f>'Nach Mannschaften sortiert'!G62</f>
         <v>0</v>
       </c>
       <c r="H47" s="54">
-        <f>'Nach Mannschaften sortiert'!H61</f>
+        <f>'Nach Mannschaften sortiert'!H62</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="48">
-        <f>'Nach Mannschaften sortiert'!A43</f>
-        <v>42</v>
+        <f>'Nach Mannschaften sortiert'!A44</f>
+        <v>43</v>
       </c>
       <c r="B48" s="48">
-        <f>'Nach Mannschaften sortiert'!B43</f>
+        <f>'Nach Mannschaften sortiert'!B44</f>
         <v>4</v>
       </c>
       <c r="C48" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C43</f>
+        <f>'Nach Mannschaften sortiert'!C44</f>
         <v>U16</v>
       </c>
       <c r="D48" s="49">
-        <f>'Nach Mannschaften sortiert'!D43</f>
+        <f>'Nach Mannschaften sortiert'!D44</f>
         <v>46026</v>
       </c>
       <c r="E48" s="99">
-        <f>'Nach Mannschaften sortiert'!E43</f>
+        <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="F48" s="48">
-        <f>'Nach Mannschaften sortiert'!F43</f>
+        <f>'Nach Mannschaften sortiert'!F44</f>
         <v>0</v>
       </c>
       <c r="G48" s="48">
-        <f>'Nach Mannschaften sortiert'!G43</f>
+        <f>'Nach Mannschaften sortiert'!G44</f>
         <v>0</v>
       </c>
       <c r="H48" s="48">
-        <f>'Nach Mannschaften sortiert'!H43</f>
+        <f>'Nach Mannschaften sortiert'!H44</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="54">
-        <f>'Nach Mannschaften sortiert'!A63</f>
-        <v>62</v>
+        <f>'Nach Mannschaften sortiert'!A64</f>
+        <v>63</v>
       </c>
       <c r="B49" s="54">
-        <f>'Nach Mannschaften sortiert'!B63</f>
+        <f>'Nach Mannschaften sortiert'!B64</f>
         <v>4</v>
       </c>
       <c r="C49" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C63</f>
+        <f>'Nach Mannschaften sortiert'!C64</f>
         <v>U12_1</v>
       </c>
       <c r="D49" s="55">
-        <f>'Nach Mannschaften sortiert'!D63</f>
+        <f>'Nach Mannschaften sortiert'!D64</f>
         <v>46046</v>
       </c>
       <c r="E49" s="97">
-        <f>'Nach Mannschaften sortiert'!E63</f>
+        <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="F49" s="54">
-        <f>'Nach Mannschaften sortiert'!F63</f>
+        <f>'Nach Mannschaften sortiert'!F64</f>
         <v>0</v>
       </c>
       <c r="G49" s="54">
-        <f>'Nach Mannschaften sortiert'!G63</f>
+        <f>'Nach Mannschaften sortiert'!G64</f>
         <v>0</v>
       </c>
       <c r="H49" s="54">
-        <f>'Nach Mannschaften sortiert'!H63</f>
+        <f>'Nach Mannschaften sortiert'!H64</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="54">
-        <f>'Nach Mannschaften sortiert'!A64</f>
-        <v>63</v>
+        <f>'Nach Mannschaften sortiert'!A65</f>
+        <v>64</v>
       </c>
       <c r="B50" s="54">
-        <f>'Nach Mannschaften sortiert'!B64</f>
+        <f>'Nach Mannschaften sortiert'!B65</f>
         <v>5</v>
       </c>
       <c r="C50" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C64</f>
+        <f>'Nach Mannschaften sortiert'!C65</f>
         <v>U12_1</v>
       </c>
       <c r="D50" s="55">
-        <f>'Nach Mannschaften sortiert'!D64</f>
+        <f>'Nach Mannschaften sortiert'!D65</f>
         <v>46047</v>
       </c>
       <c r="E50" s="97">
-        <f>'Nach Mannschaften sortiert'!E64</f>
+        <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="F50" s="54">
-        <f>'Nach Mannschaften sortiert'!F64</f>
+        <f>'Nach Mannschaften sortiert'!F65</f>
         <v>0</v>
       </c>
       <c r="G50" s="54">
-        <f>'Nach Mannschaften sortiert'!G64</f>
+        <f>'Nach Mannschaften sortiert'!G65</f>
         <v>0</v>
       </c>
       <c r="H50" s="54">
-        <f>'Nach Mannschaften sortiert'!H64</f>
+        <f>'Nach Mannschaften sortiert'!H65</f>
         <v>0</v>
       </c>
     </row>
@@ -12160,69 +12235,69 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="48">
-        <f>'Nach Mannschaften sortiert'!A21</f>
-        <v>20</v>
+        <f>'Nach Mannschaften sortiert'!A22</f>
+        <v>21</v>
       </c>
       <c r="B52" s="48">
-        <f>'Nach Mannschaften sortiert'!B21</f>
+        <f>'Nach Mannschaften sortiert'!B22</f>
         <v>8</v>
       </c>
       <c r="C52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C21</f>
+        <f>'Nach Mannschaften sortiert'!C22</f>
         <v>KM</v>
       </c>
       <c r="D52" s="49">
-        <f>'Nach Mannschaften sortiert'!D21</f>
+        <f>'Nach Mannschaften sortiert'!D22</f>
         <v>46297</v>
       </c>
       <c r="E52" s="99">
-        <f>'Nach Mannschaften sortiert'!E21</f>
+        <f>'Nach Mannschaften sortiert'!E22</f>
         <v>0.79166666666666663</v>
       </c>
       <c r="F52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F21</f>
+        <f>'Nach Mannschaften sortiert'!F22</f>
         <v>Siegendorf</v>
       </c>
       <c r="G52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G21</f>
+        <f>'Nach Mannschaften sortiert'!G22</f>
         <v>Siegendorf</v>
       </c>
       <c r="H52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H21</f>
+        <f>'Nach Mannschaften sortiert'!H22</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="54">
-        <f>'Nach Mannschaften sortiert'!A66</f>
-        <v>65</v>
+        <f>'Nach Mannschaften sortiert'!A67</f>
+        <v>66</v>
       </c>
       <c r="B53" s="54">
-        <f>'Nach Mannschaften sortiert'!B66</f>
+        <f>'Nach Mannschaften sortiert'!B67</f>
         <v>7</v>
       </c>
       <c r="C53" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C66</f>
+        <f>'Nach Mannschaften sortiert'!C67</f>
         <v>U12_1</v>
       </c>
       <c r="D53" s="55">
-        <f>'Nach Mannschaften sortiert'!D66</f>
+        <f>'Nach Mannschaften sortiert'!D67</f>
         <v>46049</v>
       </c>
       <c r="E53" s="97">
-        <f>'Nach Mannschaften sortiert'!E66</f>
+        <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="F53" s="54">
-        <f>'Nach Mannschaften sortiert'!F66</f>
+        <f>'Nach Mannschaften sortiert'!F67</f>
         <v>0</v>
       </c>
       <c r="G53" s="54">
-        <f>'Nach Mannschaften sortiert'!G66</f>
+        <f>'Nach Mannschaften sortiert'!G67</f>
         <v>0</v>
       </c>
       <c r="H53" s="54">
-        <f>'Nach Mannschaften sortiert'!H66</f>
+        <f>'Nach Mannschaften sortiert'!H67</f>
         <v>0</v>
       </c>
     </row>
@@ -12262,137 +12337,137 @@
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="54">
-        <f>'Nach Mannschaften sortiert'!A80</f>
-        <v>79</v>
+        <f>'Nach Mannschaften sortiert'!A81</f>
+        <v>80</v>
       </c>
       <c r="B55" s="54">
-        <f>'Nach Mannschaften sortiert'!B80</f>
+        <f>'Nach Mannschaften sortiert'!B81</f>
         <v>1</v>
       </c>
       <c r="C55" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C80</f>
+        <f>'Nach Mannschaften sortiert'!C81</f>
         <v>U11</v>
       </c>
       <c r="D55" s="55">
-        <f>'Nach Mannschaften sortiert'!D80</f>
+        <f>'Nach Mannschaften sortiert'!D81</f>
         <v>46063</v>
       </c>
       <c r="E55" s="97">
-        <f>'Nach Mannschaften sortiert'!E80</f>
+        <f>'Nach Mannschaften sortiert'!E81</f>
         <v>0</v>
       </c>
       <c r="F55" s="54">
-        <f>'Nach Mannschaften sortiert'!F80</f>
+        <f>'Nach Mannschaften sortiert'!F81</f>
         <v>0</v>
       </c>
       <c r="G55" s="54">
-        <f>'Nach Mannschaften sortiert'!G80</f>
+        <f>'Nach Mannschaften sortiert'!G81</f>
         <v>0</v>
       </c>
       <c r="H55" s="54">
-        <f>'Nach Mannschaften sortiert'!H80</f>
+        <f>'Nach Mannschaften sortiert'!H81</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="48">
-        <f>'Nach Mannschaften sortiert'!A86</f>
-        <v>85</v>
+        <f>'Nach Mannschaften sortiert'!A87</f>
+        <v>86</v>
       </c>
       <c r="B56" s="48">
-        <f>'Nach Mannschaften sortiert'!B86</f>
+        <f>'Nach Mannschaften sortiert'!B87</f>
         <v>7</v>
       </c>
       <c r="C56" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C86</f>
+        <f>'Nach Mannschaften sortiert'!C87</f>
         <v>U11</v>
       </c>
       <c r="D56" s="49">
-        <f>'Nach Mannschaften sortiert'!D86</f>
+        <f>'Nach Mannschaften sortiert'!D87</f>
         <v>46069</v>
       </c>
       <c r="E56" s="99">
-        <f>'Nach Mannschaften sortiert'!E86</f>
+        <f>'Nach Mannschaften sortiert'!E87</f>
         <v>0</v>
       </c>
       <c r="F56" s="48">
-        <f>'Nach Mannschaften sortiert'!F86</f>
+        <f>'Nach Mannschaften sortiert'!F87</f>
         <v>0</v>
       </c>
       <c r="G56" s="48">
-        <f>'Nach Mannschaften sortiert'!G86</f>
+        <f>'Nach Mannschaften sortiert'!G87</f>
         <v>0</v>
       </c>
       <c r="H56" s="48">
-        <f>'Nach Mannschaften sortiert'!H86</f>
+        <f>'Nach Mannschaften sortiert'!H87</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="54">
-        <f>'Nach Mannschaften sortiert'!A83</f>
-        <v>82</v>
+        <f>'Nach Mannschaften sortiert'!A84</f>
+        <v>83</v>
       </c>
       <c r="B57" s="54">
-        <f>'Nach Mannschaften sortiert'!B83</f>
+        <f>'Nach Mannschaften sortiert'!B84</f>
         <v>4</v>
       </c>
       <c r="C57" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C83</f>
+        <f>'Nach Mannschaften sortiert'!C84</f>
         <v>U11</v>
       </c>
       <c r="D57" s="55">
-        <f>'Nach Mannschaften sortiert'!D83</f>
+        <f>'Nach Mannschaften sortiert'!D84</f>
         <v>46066</v>
       </c>
       <c r="E57" s="97">
-        <f>'Nach Mannschaften sortiert'!E83</f>
+        <f>'Nach Mannschaften sortiert'!E84</f>
         <v>0</v>
       </c>
       <c r="F57" s="54">
-        <f>'Nach Mannschaften sortiert'!F83</f>
+        <f>'Nach Mannschaften sortiert'!F84</f>
         <v>0</v>
       </c>
       <c r="G57" s="54">
-        <f>'Nach Mannschaften sortiert'!G83</f>
+        <f>'Nach Mannschaften sortiert'!G84</f>
         <v>0</v>
       </c>
       <c r="H57" s="54">
-        <f>'Nach Mannschaften sortiert'!H83</f>
+        <f>'Nach Mannschaften sortiert'!H84</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="48">
-        <f>'Nach Mannschaften sortiert'!A23</f>
-        <v>22</v>
+        <f>'Nach Mannschaften sortiert'!A24</f>
+        <v>23</v>
       </c>
       <c r="B58" s="48">
-        <f>'Nach Mannschaften sortiert'!B23</f>
+        <f>'Nach Mannschaften sortiert'!B24</f>
         <v>10</v>
       </c>
       <c r="C58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C23</f>
+        <f>'Nach Mannschaften sortiert'!C24</f>
         <v>KM</v>
       </c>
       <c r="D58" s="49">
-        <f>'Nach Mannschaften sortiert'!D23</f>
+        <f>'Nach Mannschaften sortiert'!D24</f>
         <v>46311</v>
       </c>
       <c r="E58" s="99">
-        <f>'Nach Mannschaften sortiert'!E23</f>
+        <f>'Nach Mannschaften sortiert'!E24</f>
         <v>0.8125</v>
       </c>
       <c r="F58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F23</f>
+        <f>'Nach Mannschaften sortiert'!F24</f>
         <v>Hornstein</v>
       </c>
       <c r="G58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G23</f>
+        <f>'Nach Mannschaften sortiert'!G24</f>
         <v>Hornstein</v>
       </c>
       <c r="H58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H23</f>
+        <f>'Nach Mannschaften sortiert'!H24</f>
         <v>Auswärts</v>
       </c>
     </row>
@@ -12432,137 +12507,137 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="48">
-        <f>'Nach Mannschaften sortiert'!A57</f>
-        <v>56</v>
+        <f>'Nach Mannschaften sortiert'!A58</f>
+        <v>57</v>
       </c>
       <c r="B60" s="48">
-        <f>'Nach Mannschaften sortiert'!B57</f>
+        <f>'Nach Mannschaften sortiert'!B58</f>
         <v>8</v>
       </c>
       <c r="C60" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C57</f>
+        <f>'Nach Mannschaften sortiert'!C58</f>
         <v>U14</v>
       </c>
       <c r="D60" s="49">
-        <f>'Nach Mannschaften sortiert'!D57</f>
+        <f>'Nach Mannschaften sortiert'!D58</f>
         <v>46040</v>
       </c>
       <c r="E60" s="99">
-        <f>'Nach Mannschaften sortiert'!E57</f>
+        <f>'Nach Mannschaften sortiert'!E58</f>
         <v>0</v>
       </c>
       <c r="F60" s="48">
-        <f>'Nach Mannschaften sortiert'!F57</f>
+        <f>'Nach Mannschaften sortiert'!F58</f>
         <v>0</v>
       </c>
       <c r="G60" s="48">
-        <f>'Nach Mannschaften sortiert'!G57</f>
+        <f>'Nach Mannschaften sortiert'!G58</f>
         <v>0</v>
       </c>
       <c r="H60" s="48">
-        <f>'Nach Mannschaften sortiert'!H57</f>
+        <f>'Nach Mannschaften sortiert'!H58</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="54">
-        <f>'Nach Mannschaften sortiert'!A87</f>
-        <v>86</v>
+        <f>'Nach Mannschaften sortiert'!A88</f>
+        <v>87</v>
       </c>
       <c r="B61" s="54">
-        <f>'Nach Mannschaften sortiert'!B87</f>
+        <f>'Nach Mannschaften sortiert'!B88</f>
         <v>8</v>
       </c>
       <c r="C61" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C87</f>
+        <f>'Nach Mannschaften sortiert'!C88</f>
         <v>U11</v>
       </c>
       <c r="D61" s="55">
-        <f>'Nach Mannschaften sortiert'!D87</f>
+        <f>'Nach Mannschaften sortiert'!D88</f>
         <v>46070</v>
       </c>
       <c r="E61" s="97">
-        <f>'Nach Mannschaften sortiert'!E87</f>
+        <f>'Nach Mannschaften sortiert'!E88</f>
         <v>0</v>
       </c>
       <c r="F61" s="54">
-        <f>'Nach Mannschaften sortiert'!F87</f>
+        <f>'Nach Mannschaften sortiert'!F88</f>
         <v>0</v>
       </c>
       <c r="G61" s="54">
-        <f>'Nach Mannschaften sortiert'!G87</f>
+        <f>'Nach Mannschaften sortiert'!G88</f>
         <v>0</v>
       </c>
       <c r="H61" s="54">
-        <f>'Nach Mannschaften sortiert'!H87</f>
+        <f>'Nach Mannschaften sortiert'!H88</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="46">
-        <f>'Nach Mannschaften sortiert'!A58</f>
-        <v>57</v>
+        <f>'Nach Mannschaften sortiert'!A59</f>
+        <v>58</v>
       </c>
       <c r="B62" s="46">
-        <f>'Nach Mannschaften sortiert'!B58</f>
+        <f>'Nach Mannschaften sortiert'!B59</f>
         <v>9</v>
       </c>
       <c r="C62" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C58</f>
+        <f>'Nach Mannschaften sortiert'!C59</f>
         <v>U14</v>
       </c>
       <c r="D62" s="47">
-        <f>'Nach Mannschaften sortiert'!D58</f>
+        <f>'Nach Mannschaften sortiert'!D59</f>
         <v>46041</v>
       </c>
       <c r="E62" s="100">
-        <f>'Nach Mannschaften sortiert'!E58</f>
+        <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="F62" s="46">
-        <f>'Nach Mannschaften sortiert'!F58</f>
+        <f>'Nach Mannschaften sortiert'!F59</f>
         <v>0</v>
       </c>
       <c r="G62" s="46">
-        <f>'Nach Mannschaften sortiert'!G58</f>
+        <f>'Nach Mannschaften sortiert'!G59</f>
         <v>0</v>
       </c>
       <c r="H62" s="46">
-        <f>'Nach Mannschaften sortiert'!H58</f>
+        <f>'Nach Mannschaften sortiert'!H59</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="54">
-        <f>'Nach Mannschaften sortiert'!A89</f>
-        <v>88</v>
+        <f>'Nach Mannschaften sortiert'!A90</f>
+        <v>89</v>
       </c>
       <c r="B63" s="54">
-        <f>'Nach Mannschaften sortiert'!B89</f>
+        <f>'Nach Mannschaften sortiert'!B90</f>
         <v>10</v>
       </c>
       <c r="C63" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C89</f>
+        <f>'Nach Mannschaften sortiert'!C90</f>
         <v>U11</v>
       </c>
       <c r="D63" s="55">
-        <f>'Nach Mannschaften sortiert'!D89</f>
+        <f>'Nach Mannschaften sortiert'!D90</f>
         <v>46072</v>
       </c>
       <c r="E63" s="97">
-        <f>'Nach Mannschaften sortiert'!E89</f>
+        <f>'Nach Mannschaften sortiert'!E90</f>
         <v>0</v>
       </c>
       <c r="F63" s="54">
-        <f>'Nach Mannschaften sortiert'!F89</f>
+        <f>'Nach Mannschaften sortiert'!F90</f>
         <v>0</v>
       </c>
       <c r="G63" s="54">
-        <f>'Nach Mannschaften sortiert'!G89</f>
+        <f>'Nach Mannschaften sortiert'!G90</f>
         <v>0</v>
       </c>
       <c r="H63" s="54">
-        <f>'Nach Mannschaften sortiert'!H89</f>
+        <f>'Nach Mannschaften sortiert'!H90</f>
         <v>0</v>
       </c>
     </row>
@@ -12602,15 +12677,15 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="48">
-        <f>'Nach Mannschaften sortiert'!A88</f>
-        <v>87</v>
+        <f>'Nach Mannschaften sortiert'!A89</f>
+        <v>88</v>
       </c>
       <c r="B65" s="48">
-        <f>'Nach Mannschaften sortiert'!B88</f>
+        <f>'Nach Mannschaften sortiert'!B89</f>
         <v>9</v>
       </c>
       <c r="C65" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C88</f>
+        <f>'Nach Mannschaften sortiert'!C89</f>
         <v>U11</v>
       </c>
       <c r="D65" s="49">
@@ -12620,525 +12695,525 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F65" s="48">
-        <f>'Nach Mannschaften sortiert'!F88</f>
+        <f>'Nach Mannschaften sortiert'!F89</f>
         <v>0</v>
       </c>
       <c r="G65" s="48">
-        <f>'Nach Mannschaften sortiert'!G88</f>
+        <f>'Nach Mannschaften sortiert'!G89</f>
         <v>0</v>
       </c>
       <c r="H65" s="48">
-        <f>'Nach Mannschaften sortiert'!H88</f>
+        <f>'Nach Mannschaften sortiert'!H89</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="54">
-        <f>'Nach Mannschaften sortiert'!A96</f>
-        <v>95</v>
+        <f>'Nach Mannschaften sortiert'!A97</f>
+        <v>96</v>
       </c>
       <c r="B66" s="54">
-        <f>'Nach Mannschaften sortiert'!B96</f>
+        <f>'Nach Mannschaften sortiert'!B97</f>
         <v>2</v>
       </c>
       <c r="C66" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C96</f>
+        <f>'Nach Mannschaften sortiert'!C97</f>
         <v>U9</v>
       </c>
       <c r="D66" s="55">
-        <f>'Nach Mannschaften sortiert'!D96</f>
+        <f>'Nach Mannschaften sortiert'!D97</f>
         <v>46079</v>
       </c>
       <c r="E66" s="97">
-        <f>'Nach Mannschaften sortiert'!E96</f>
+        <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="F66" s="54">
-        <f>'Nach Mannschaften sortiert'!F96</f>
+        <f>'Nach Mannschaften sortiert'!F97</f>
         <v>0</v>
       </c>
       <c r="G66" s="54">
-        <f>'Nach Mannschaften sortiert'!G96</f>
+        <f>'Nach Mannschaften sortiert'!G97</f>
         <v>0</v>
       </c>
       <c r="H66" s="54">
-        <f>'Nach Mannschaften sortiert'!H96</f>
+        <f>'Nach Mannschaften sortiert'!H97</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="54">
-        <f>'Nach Mannschaften sortiert'!A97</f>
-        <v>96</v>
+        <f>'Nach Mannschaften sortiert'!A98</f>
+        <v>97</v>
       </c>
       <c r="B67" s="54">
-        <f>'Nach Mannschaften sortiert'!B97</f>
+        <f>'Nach Mannschaften sortiert'!B98</f>
         <v>3</v>
       </c>
       <c r="C67" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C97</f>
+        <f>'Nach Mannschaften sortiert'!C98</f>
         <v>U9</v>
       </c>
       <c r="D67" s="55">
-        <f>'Nach Mannschaften sortiert'!D97</f>
+        <f>'Nach Mannschaften sortiert'!D98</f>
         <v>46080</v>
       </c>
       <c r="E67" s="97">
-        <f>'Nach Mannschaften sortiert'!E97</f>
+        <f>'Nach Mannschaften sortiert'!E98</f>
         <v>0</v>
       </c>
       <c r="F67" s="54">
-        <f>'Nach Mannschaften sortiert'!F97</f>
+        <f>'Nach Mannschaften sortiert'!F98</f>
         <v>0</v>
       </c>
       <c r="G67" s="54">
-        <f>'Nach Mannschaften sortiert'!G97</f>
+        <f>'Nach Mannschaften sortiert'!G98</f>
         <v>0</v>
       </c>
       <c r="H67" s="54">
-        <f>'Nach Mannschaften sortiert'!H97</f>
+        <f>'Nach Mannschaften sortiert'!H98</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="54">
-        <f>'Nach Mannschaften sortiert'!A98</f>
-        <v>97</v>
+        <f>'Nach Mannschaften sortiert'!A99</f>
+        <v>98</v>
       </c>
       <c r="B68" s="54">
-        <f>'Nach Mannschaften sortiert'!B98</f>
+        <f>'Nach Mannschaften sortiert'!B99</f>
         <v>4</v>
       </c>
       <c r="C68" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C98</f>
+        <f>'Nach Mannschaften sortiert'!C99</f>
         <v>U9</v>
       </c>
       <c r="D68" s="55">
-        <f>'Nach Mannschaften sortiert'!D98</f>
+        <f>'Nach Mannschaften sortiert'!D99</f>
         <v>46081</v>
       </c>
       <c r="E68" s="97">
-        <f>'Nach Mannschaften sortiert'!E98</f>
+        <f>'Nach Mannschaften sortiert'!E99</f>
         <v>0</v>
       </c>
       <c r="F68" s="54">
-        <f>'Nach Mannschaften sortiert'!F98</f>
+        <f>'Nach Mannschaften sortiert'!F99</f>
         <v>0</v>
       </c>
       <c r="G68" s="54">
-        <f>'Nach Mannschaften sortiert'!G98</f>
+        <f>'Nach Mannschaften sortiert'!G99</f>
         <v>0</v>
       </c>
       <c r="H68" s="54">
-        <f>'Nach Mannschaften sortiert'!H98</f>
+        <f>'Nach Mannschaften sortiert'!H99</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="54">
-        <f>'Nach Mannschaften sortiert'!A104</f>
-        <v>103</v>
+        <f>'Nach Mannschaften sortiert'!A105</f>
+        <v>104</v>
       </c>
       <c r="B69" s="54">
-        <f>'Nach Mannschaften sortiert'!B104</f>
+        <f>'Nach Mannschaften sortiert'!B105</f>
         <v>10</v>
       </c>
       <c r="C69" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C104</f>
+        <f>'Nach Mannschaften sortiert'!C105</f>
         <v>U9</v>
       </c>
       <c r="D69" s="55">
-        <f>'Nach Mannschaften sortiert'!D104</f>
+        <f>'Nach Mannschaften sortiert'!D105</f>
         <v>46087</v>
       </c>
       <c r="E69" s="97">
-        <f>'Nach Mannschaften sortiert'!E104</f>
+        <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="F69" s="54">
-        <f>'Nach Mannschaften sortiert'!F104</f>
+        <f>'Nach Mannschaften sortiert'!F105</f>
         <v>0</v>
       </c>
       <c r="G69" s="54">
-        <f>'Nach Mannschaften sortiert'!G104</f>
+        <f>'Nach Mannschaften sortiert'!G105</f>
         <v>0</v>
       </c>
       <c r="H69" s="54">
-        <f>'Nach Mannschaften sortiert'!H104</f>
+        <f>'Nach Mannschaften sortiert'!H105</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="48">
-        <f>'Nach Mannschaften sortiert'!A65</f>
-        <v>64</v>
+        <f>'Nach Mannschaften sortiert'!A66</f>
+        <v>65</v>
       </c>
       <c r="B70" s="48">
-        <f>'Nach Mannschaften sortiert'!B65</f>
+        <f>'Nach Mannschaften sortiert'!B66</f>
         <v>6</v>
       </c>
       <c r="C70" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C65</f>
+        <f>'Nach Mannschaften sortiert'!C66</f>
         <v>U12_1</v>
       </c>
       <c r="D70" s="49">
-        <f>'Nach Mannschaften sortiert'!D65</f>
+        <f>'Nach Mannschaften sortiert'!D66</f>
         <v>46048</v>
       </c>
       <c r="E70" s="99">
-        <f>'Nach Mannschaften sortiert'!E65</f>
+        <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="F70" s="48">
-        <f>'Nach Mannschaften sortiert'!F65</f>
+        <f>'Nach Mannschaften sortiert'!F66</f>
         <v>0</v>
       </c>
       <c r="G70" s="48">
-        <f>'Nach Mannschaften sortiert'!G65</f>
+        <f>'Nach Mannschaften sortiert'!G66</f>
         <v>0</v>
       </c>
       <c r="H70" s="48">
-        <f>'Nach Mannschaften sortiert'!H65</f>
+        <f>'Nach Mannschaften sortiert'!H66</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="54">
-        <f>'Nach Mannschaften sortiert'!A106</f>
-        <v>105</v>
+        <f>'Nach Mannschaften sortiert'!A107</f>
+        <v>106</v>
       </c>
       <c r="B71" s="54">
-        <f>'Nach Mannschaften sortiert'!B106</f>
+        <f>'Nach Mannschaften sortiert'!B107</f>
         <v>2</v>
       </c>
       <c r="C71" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C106</f>
+        <f>'Nach Mannschaften sortiert'!C107</f>
         <v>U8</v>
       </c>
       <c r="D71" s="55">
-        <f>'Nach Mannschaften sortiert'!D106</f>
+        <f>'Nach Mannschaften sortiert'!D107</f>
         <v>46089</v>
       </c>
       <c r="E71" s="97">
-        <f>'Nach Mannschaften sortiert'!E106</f>
+        <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="F71" s="54">
-        <f>'Nach Mannschaften sortiert'!F106</f>
+        <f>'Nach Mannschaften sortiert'!F107</f>
         <v>0</v>
       </c>
       <c r="G71" s="54">
-        <f>'Nach Mannschaften sortiert'!G106</f>
+        <f>'Nach Mannschaften sortiert'!G107</f>
         <v>0</v>
       </c>
       <c r="H71" s="54">
-        <f>'Nach Mannschaften sortiert'!H106</f>
+        <f>'Nach Mannschaften sortiert'!H107</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="54">
-        <f>'Nach Mannschaften sortiert'!A107</f>
-        <v>106</v>
+        <f>'Nach Mannschaften sortiert'!A108</f>
+        <v>107</v>
       </c>
       <c r="B72" s="54">
-        <f>'Nach Mannschaften sortiert'!B107</f>
+        <f>'Nach Mannschaften sortiert'!B108</f>
         <v>3</v>
       </c>
       <c r="C72" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C107</f>
+        <f>'Nach Mannschaften sortiert'!C108</f>
         <v>U8</v>
       </c>
       <c r="D72" s="55">
-        <f>'Nach Mannschaften sortiert'!D107</f>
+        <f>'Nach Mannschaften sortiert'!D108</f>
         <v>46090</v>
       </c>
       <c r="E72" s="97">
-        <f>'Nach Mannschaften sortiert'!E107</f>
+        <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="F72" s="54">
-        <f>'Nach Mannschaften sortiert'!F107</f>
+        <f>'Nach Mannschaften sortiert'!F108</f>
         <v>0</v>
       </c>
       <c r="G72" s="54">
-        <f>'Nach Mannschaften sortiert'!G107</f>
+        <f>'Nach Mannschaften sortiert'!G108</f>
         <v>0</v>
       </c>
       <c r="H72" s="54">
-        <f>'Nach Mannschaften sortiert'!H107</f>
+        <f>'Nach Mannschaften sortiert'!H108</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="54">
-        <f>'Nach Mannschaften sortiert'!A108</f>
-        <v>107</v>
+        <f>'Nach Mannschaften sortiert'!A109</f>
+        <v>108</v>
       </c>
       <c r="B73" s="54">
-        <f>'Nach Mannschaften sortiert'!B108</f>
+        <f>'Nach Mannschaften sortiert'!B109</f>
         <v>4</v>
       </c>
       <c r="C73" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C108</f>
+        <f>'Nach Mannschaften sortiert'!C109</f>
         <v>U8</v>
       </c>
       <c r="D73" s="55">
-        <f>'Nach Mannschaften sortiert'!D108</f>
+        <f>'Nach Mannschaften sortiert'!D109</f>
         <v>46091</v>
       </c>
       <c r="E73" s="97">
-        <f>'Nach Mannschaften sortiert'!E108</f>
+        <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="F73" s="54">
-        <f>'Nach Mannschaften sortiert'!F108</f>
+        <f>'Nach Mannschaften sortiert'!F109</f>
         <v>0</v>
       </c>
       <c r="G73" s="54">
-        <f>'Nach Mannschaften sortiert'!G108</f>
+        <f>'Nach Mannschaften sortiert'!G109</f>
         <v>0</v>
       </c>
       <c r="H73" s="54">
-        <f>'Nach Mannschaften sortiert'!H108</f>
+        <f>'Nach Mannschaften sortiert'!H109</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="54">
-        <f>'Nach Mannschaften sortiert'!A109</f>
-        <v>108</v>
+        <f>'Nach Mannschaften sortiert'!A110</f>
+        <v>109</v>
       </c>
       <c r="B74" s="54">
-        <f>'Nach Mannschaften sortiert'!B109</f>
+        <f>'Nach Mannschaften sortiert'!B110</f>
         <v>5</v>
       </c>
       <c r="C74" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C109</f>
+        <f>'Nach Mannschaften sortiert'!C110</f>
         <v>U8</v>
       </c>
       <c r="D74" s="55">
-        <f>'Nach Mannschaften sortiert'!D109</f>
+        <f>'Nach Mannschaften sortiert'!D110</f>
         <v>46092</v>
       </c>
       <c r="E74" s="97">
-        <f>'Nach Mannschaften sortiert'!E109</f>
+        <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="F74" s="54">
-        <f>'Nach Mannschaften sortiert'!F109</f>
+        <f>'Nach Mannschaften sortiert'!F110</f>
         <v>0</v>
       </c>
       <c r="G74" s="54">
-        <f>'Nach Mannschaften sortiert'!G109</f>
+        <f>'Nach Mannschaften sortiert'!G110</f>
         <v>0</v>
       </c>
       <c r="H74" s="54">
-        <f>'Nach Mannschaften sortiert'!H109</f>
+        <f>'Nach Mannschaften sortiert'!H110</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="48">
-        <f>'Nach Mannschaften sortiert'!A26</f>
-        <v>25</v>
+        <f>'Nach Mannschaften sortiert'!A27</f>
+        <v>26</v>
       </c>
       <c r="B75" s="48">
-        <f>'Nach Mannschaften sortiert'!B26</f>
+        <f>'Nach Mannschaften sortiert'!B27</f>
         <v>13</v>
       </c>
       <c r="C75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C26</f>
+        <f>'Nach Mannschaften sortiert'!C27</f>
         <v>KM</v>
       </c>
       <c r="D75" s="49">
-        <f>'Nach Mannschaften sortiert'!D26</f>
+        <f>'Nach Mannschaften sortiert'!D27</f>
         <v>46333</v>
       </c>
       <c r="E75" s="99">
-        <f>'Nach Mannschaften sortiert'!E26</f>
+        <f>'Nach Mannschaften sortiert'!E27</f>
         <v>0.6875</v>
       </c>
       <c r="F75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F26</f>
+        <f>'Nach Mannschaften sortiert'!F27</f>
         <v>Neufeld</v>
       </c>
       <c r="G75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G26</f>
+        <f>'Nach Mannschaften sortiert'!G27</f>
         <v>Andau</v>
       </c>
       <c r="H75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H26</f>
+        <f>'Nach Mannschaften sortiert'!H27</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="54">
-        <f>'Nach Mannschaften sortiert'!A111</f>
-        <v>110</v>
+        <f>'Nach Mannschaften sortiert'!A112</f>
+        <v>111</v>
       </c>
       <c r="B76" s="54">
-        <f>'Nach Mannschaften sortiert'!B111</f>
+        <f>'Nach Mannschaften sortiert'!B112</f>
         <v>2</v>
       </c>
       <c r="C76" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C111</f>
+        <f>'Nach Mannschaften sortiert'!C112</f>
         <v>U7</v>
       </c>
       <c r="D76" s="55">
-        <f>'Nach Mannschaften sortiert'!D111</f>
+        <f>'Nach Mannschaften sortiert'!D112</f>
         <v>46094</v>
       </c>
       <c r="E76" s="97">
-        <f>'Nach Mannschaften sortiert'!E111</f>
+        <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="F76" s="54">
-        <f>'Nach Mannschaften sortiert'!F111</f>
+        <f>'Nach Mannschaften sortiert'!F112</f>
         <v>0</v>
       </c>
       <c r="G76" s="54">
-        <f>'Nach Mannschaften sortiert'!G111</f>
+        <f>'Nach Mannschaften sortiert'!G112</f>
         <v>0</v>
       </c>
       <c r="H76" s="54">
-        <f>'Nach Mannschaften sortiert'!H111</f>
+        <f>'Nach Mannschaften sortiert'!H112</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="54">
-        <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>111</v>
+        <f>'Nach Mannschaften sortiert'!A113</f>
+        <v>112</v>
       </c>
       <c r="B77" s="54">
-        <f>'Nach Mannschaften sortiert'!B112</f>
+        <f>'Nach Mannschaften sortiert'!B113</f>
         <v>3</v>
       </c>
       <c r="C77" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C112</f>
+        <f>'Nach Mannschaften sortiert'!C113</f>
         <v>U7</v>
       </c>
       <c r="D77" s="55">
-        <f>'Nach Mannschaften sortiert'!D112</f>
+        <f>'Nach Mannschaften sortiert'!D113</f>
         <v>46095</v>
       </c>
       <c r="E77" s="97">
-        <f>'Nach Mannschaften sortiert'!E112</f>
+        <f>'Nach Mannschaften sortiert'!E113</f>
         <v>0</v>
       </c>
       <c r="F77" s="54">
-        <f>'Nach Mannschaften sortiert'!F112</f>
+        <f>'Nach Mannschaften sortiert'!F113</f>
         <v>0</v>
       </c>
       <c r="G77" s="54">
-        <f>'Nach Mannschaften sortiert'!G112</f>
+        <f>'Nach Mannschaften sortiert'!G113</f>
         <v>0</v>
       </c>
       <c r="H77" s="54">
-        <f>'Nach Mannschaften sortiert'!H112</f>
+        <f>'Nach Mannschaften sortiert'!H113</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="54">
-        <f>'Nach Mannschaften sortiert'!A113</f>
-        <v>112</v>
+        <f>'Nach Mannschaften sortiert'!A114</f>
+        <v>113</v>
       </c>
       <c r="B78" s="54">
-        <f>'Nach Mannschaften sortiert'!B113</f>
+        <f>'Nach Mannschaften sortiert'!B114</f>
         <v>4</v>
       </c>
       <c r="C78" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C113</f>
+        <f>'Nach Mannschaften sortiert'!C114</f>
         <v>U7</v>
       </c>
       <c r="D78" s="55">
-        <f>'Nach Mannschaften sortiert'!D113</f>
+        <f>'Nach Mannschaften sortiert'!D114</f>
         <v>46096</v>
       </c>
       <c r="E78" s="97">
-        <f>'Nach Mannschaften sortiert'!E113</f>
+        <f>'Nach Mannschaften sortiert'!E114</f>
         <v>0</v>
       </c>
       <c r="F78" s="54">
-        <f>'Nach Mannschaften sortiert'!F113</f>
+        <f>'Nach Mannschaften sortiert'!F114</f>
         <v>0</v>
       </c>
       <c r="G78" s="54">
-        <f>'Nach Mannschaften sortiert'!G113</f>
+        <f>'Nach Mannschaften sortiert'!G114</f>
         <v>0</v>
       </c>
       <c r="H78" s="54">
-        <f>'Nach Mannschaften sortiert'!H113</f>
+        <f>'Nach Mannschaften sortiert'!H114</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="54">
-        <f>'Nach Mannschaften sortiert'!A114</f>
-        <v>113</v>
+        <f>'Nach Mannschaften sortiert'!A115</f>
+        <v>114</v>
       </c>
       <c r="B79" s="54">
-        <f>'Nach Mannschaften sortiert'!B114</f>
+        <f>'Nach Mannschaften sortiert'!B115</f>
         <v>5</v>
       </c>
       <c r="C79" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C114</f>
+        <f>'Nach Mannschaften sortiert'!C115</f>
         <v>U7</v>
       </c>
       <c r="D79" s="55">
-        <f>'Nach Mannschaften sortiert'!D114</f>
+        <f>'Nach Mannschaften sortiert'!D115</f>
         <v>46097</v>
       </c>
       <c r="E79" s="97">
-        <f>'Nach Mannschaften sortiert'!E114</f>
+        <f>'Nach Mannschaften sortiert'!E115</f>
         <v>0</v>
       </c>
       <c r="F79" s="54">
-        <f>'Nach Mannschaften sortiert'!F114</f>
+        <f>'Nach Mannschaften sortiert'!F115</f>
         <v>0</v>
       </c>
       <c r="G79" s="54">
-        <f>'Nach Mannschaften sortiert'!G114</f>
+        <f>'Nach Mannschaften sortiert'!G115</f>
         <v>0</v>
       </c>
       <c r="H79" s="54">
-        <f>'Nach Mannschaften sortiert'!H114</f>
+        <f>'Nach Mannschaften sortiert'!H115</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="48">
-        <f>'Nach Mannschaften sortiert'!A67</f>
-        <v>66</v>
+        <f>'Nach Mannschaften sortiert'!A68</f>
+        <v>67</v>
       </c>
       <c r="B80" s="48">
-        <f>'Nach Mannschaften sortiert'!B67</f>
+        <f>'Nach Mannschaften sortiert'!B68</f>
         <v>8</v>
       </c>
       <c r="C80" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C67</f>
+        <f>'Nach Mannschaften sortiert'!C68</f>
         <v>U12_1</v>
       </c>
       <c r="D80" s="49">
-        <f>'Nach Mannschaften sortiert'!D67</f>
+        <f>'Nach Mannschaften sortiert'!D68</f>
         <v>46050</v>
       </c>
       <c r="E80" s="99">
-        <f>'Nach Mannschaften sortiert'!E67</f>
+        <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="F80" s="48">
-        <f>'Nach Mannschaften sortiert'!F67</f>
+        <f>'Nach Mannschaften sortiert'!F68</f>
         <v>0</v>
       </c>
       <c r="G80" s="48">
-        <f>'Nach Mannschaften sortiert'!G67</f>
+        <f>'Nach Mannschaften sortiert'!G68</f>
         <v>0</v>
       </c>
       <c r="H80" s="48">
-        <f>'Nach Mannschaften sortiert'!H67</f>
+        <f>'Nach Mannschaften sortiert'!H68</f>
         <v>0</v>
       </c>
     </row>
@@ -13178,35 +13253,35 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="48">
-        <f>'Nach Mannschaften sortiert'!A49</f>
-        <v>48</v>
+        <f>'Nach Mannschaften sortiert'!A50</f>
+        <v>49</v>
       </c>
       <c r="B82" s="48">
-        <f>'Nach Mannschaften sortiert'!B49</f>
+        <f>'Nach Mannschaften sortiert'!B50</f>
         <v>10</v>
       </c>
       <c r="C82" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C49</f>
+        <f>'Nach Mannschaften sortiert'!C50</f>
         <v>U16</v>
       </c>
       <c r="D82" s="49">
-        <f>'Nach Mannschaften sortiert'!D49</f>
+        <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46032</v>
       </c>
       <c r="E82" s="99">
-        <f>'Nach Mannschaften sortiert'!E49</f>
+        <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="F82" s="48">
-        <f>'Nach Mannschaften sortiert'!F49</f>
+        <f>'Nach Mannschaften sortiert'!F50</f>
         <v>0</v>
       </c>
       <c r="G82" s="48">
-        <f>'Nach Mannschaften sortiert'!G49</f>
+        <f>'Nach Mannschaften sortiert'!G50</f>
         <v>0</v>
       </c>
       <c r="H82" s="48">
-        <f>'Nach Mannschaften sortiert'!H49</f>
+        <f>'Nach Mannschaften sortiert'!H50</f>
         <v>0</v>
       </c>
     </row>
@@ -13246,35 +13321,35 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="54">
-        <f>'Nach Mannschaften sortiert'!A126</f>
-        <v>125</v>
+        <f>'Nach Mannschaften sortiert'!A127</f>
+        <v>126</v>
       </c>
       <c r="B84" s="54">
-        <f>'Nach Mannschaften sortiert'!B126</f>
+        <f>'Nach Mannschaften sortiert'!B127</f>
         <v>2</v>
       </c>
       <c r="C84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C126</f>
+        <f>'Nach Mannschaften sortiert'!C127</f>
         <v>GGG</v>
       </c>
       <c r="D84" s="55">
-        <f>'Nach Mannschaften sortiert'!D126</f>
+        <f>'Nach Mannschaften sortiert'!D127</f>
         <v>46256</v>
       </c>
       <c r="E84" s="97">
-        <f>'Nach Mannschaften sortiert'!E126</f>
+        <f>'Nach Mannschaften sortiert'!E127</f>
         <v>0.375</v>
       </c>
       <c r="F84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F126</f>
+        <f>'Nach Mannschaften sortiert'!F127</f>
         <v>Neufeld</v>
       </c>
       <c r="G84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G126</f>
+        <f>'Nach Mannschaften sortiert'!G127</f>
         <v>viele Gegner</v>
       </c>
       <c r="H84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H126</f>
+        <f>'Nach Mannschaften sortiert'!H127</f>
         <v>Heim</v>
       </c>
     </row>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEF4EBA-BC90-4BDA-AB93-94A2B872D05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D7A1AD-15F0-486A-8980-D1394C6E6BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="176">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -573,6 +573,9 @@
   </si>
   <si>
     <t>Admira Wiener Neustadt</t>
+  </si>
+  <si>
+    <t>Laxenburg</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1075,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1339,6 +1342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -1578,7 +1582,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="54" bestFit="1" customWidth="1"/>
@@ -1645,7 +1649,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f t="shared" ref="A3:A38" si="0">A2+1</f>
+        <f t="shared" ref="A3:A39" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="5">
@@ -1913,7 +1917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" s="114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="54">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1925,22 +1929,22 @@
         <v>12</v>
       </c>
       <c r="D13" s="9">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="E13" s="93">
         <v>0.41666666666666669</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="111" customFormat="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="54">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1949,48 +1953,48 @@
         <v>0</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="9">
-        <v>46445</v>
+        <v>46260</v>
       </c>
       <c r="E14" s="93">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="4">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="10">
-        <v>46250</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="D15" s="9">
+        <v>46445</v>
+      </c>
+      <c r="E15" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2000,22 +2004,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E16" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>15</v>
@@ -2027,25 +2031,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E17" s="3">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -2054,25 +2058,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E18" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -2081,25 +2085,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E19" s="3">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -2108,25 +2112,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E20" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2135,25 +2139,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E21" s="3">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -2162,25 +2166,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="10">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="E22" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -2189,25 +2193,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="10">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="E23" s="3">
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -2216,25 +2220,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E24" s="3">
         <v>0.8125</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -2243,25 +2247,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E25" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -2270,25 +2274,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E26" s="3">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2297,25 +2301,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E27" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -2324,25 +2328,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D28" s="10">
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="E28" s="3">
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -2351,22 +2355,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D29" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E29" s="3">
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>15</v>
@@ -2378,25 +2382,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D30" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E30" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2405,25 +2409,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E31" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -2432,25 +2436,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D32" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E32" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -2459,25 +2463,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E33" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -2486,25 +2490,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D34" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E34" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -2513,25 +2517,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="10">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="E35" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -2540,25 +2544,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D36" s="10">
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="E36" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -2567,25 +2571,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D37" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E37" s="3">
         <v>0.72916666666666663</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -2594,99 +2598,107 @@
         <v>37</v>
       </c>
       <c r="B38" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D38" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E38" s="3">
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <f t="shared" ref="A39:A70" si="1">A38+1</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D39" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E39" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A40:A71" si="1">A39+1</f>
         <v>39</v>
       </c>
       <c r="B40" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E40" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="21">
+      <c r="A41" s="4">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B41" s="21">
-        <v>1</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="28">
-        <v>46023</v>
-      </c>
-      <c r="E41" s="22"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="B41" s="4">
+        <v>13</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="10">
+        <v>46333</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="21">
@@ -2694,13 +2706,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="28">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="21"/>
@@ -2713,13 +2725,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="28">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="21"/>
@@ -2732,13 +2744,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="28">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="21"/>
@@ -2751,13 +2763,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="28">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="21"/>
@@ -2770,13 +2782,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="28">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="21"/>
@@ -2789,13 +2801,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D47" s="28">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="21"/>
@@ -2808,13 +2820,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="28">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="21"/>
@@ -2827,13 +2839,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="28">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="21"/>
@@ -2846,58 +2858,57 @@
         <v>49</v>
       </c>
       <c r="B50" s="21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C50" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D50" s="28">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="21"/>
       <c r="G50" s="21"/>
       <c r="H50" s="21"/>
     </row>
-    <row r="51" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="18">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="21">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B51" s="13">
-        <v>1</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="14">
-        <v>46033</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="17"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B51" s="21">
+        <v>10</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="28">
+        <v>46032</v>
+      </c>
+      <c r="E51" s="22"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+    </row>
+    <row r="52" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="18">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="B52" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D52" s="14">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
-      <c r="I52" s="16"/>
+      <c r="I52" s="17"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="18">
@@ -2905,13 +2916,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D53" s="14">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="13"/>
@@ -2925,13 +2936,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D54" s="14">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="13"/>
@@ -2945,13 +2956,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D55" s="14">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="13"/>
@@ -2965,13 +2976,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="14">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="13"/>
@@ -2985,13 +2996,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D57" s="14">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="13"/>
@@ -3005,13 +3016,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D58" s="14">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="13"/>
@@ -3025,13 +3036,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D59" s="14">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="13"/>
@@ -3045,13 +3056,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D60" s="14">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="13"/>
@@ -3060,23 +3071,24 @@
       <c r="I60" s="16"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="6">
+      <c r="A61" s="18">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="B61" s="6">
-        <v>1</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D61" s="23">
-        <v>46043</v>
-      </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+      <c r="B61" s="13">
+        <v>10</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" s="14">
+        <v>46042</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="16"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
@@ -3084,13 +3096,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D62" s="23">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="6"/>
@@ -3103,13 +3115,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D63" s="23">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="6"/>
@@ -3122,13 +3134,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D64" s="23">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="6"/>
@@ -3141,13 +3153,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D65" s="23">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="6"/>
@@ -3160,13 +3172,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D66" s="23">
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="6"/>
@@ -3179,13 +3191,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D67" s="23">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="6"/>
@@ -3198,13 +3210,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D68" s="23">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="6"/>
@@ -3217,13 +3229,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D69" s="23">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="6"/>
@@ -3236,13 +3248,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D70" s="23">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="6"/>
@@ -3250,37 +3262,37 @@
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="90">
-        <f t="shared" ref="A71:A102" si="2">A70+1</f>
+      <c r="A71" s="6">
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="B71" s="90">
-        <v>1</v>
-      </c>
-      <c r="C71" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="D71" s="91">
-        <v>46053</v>
-      </c>
-      <c r="E71" s="92"/>
-      <c r="F71" s="90"/>
-      <c r="G71" s="90"/>
-      <c r="H71" s="90"/>
+      <c r="B71" s="6">
+        <v>10</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="23">
+        <v>46052</v>
+      </c>
+      <c r="E71" s="7"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A72:A103" si="2">A71+1</f>
         <v>71</v>
       </c>
       <c r="B72" s="90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D72" s="91">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="E72" s="92"/>
       <c r="F72" s="90"/>
@@ -3293,13 +3305,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D73" s="91">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="E73" s="92"/>
       <c r="F73" s="90"/>
@@ -3312,13 +3324,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="91">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="E74" s="92"/>
       <c r="F74" s="90"/>
@@ -3331,13 +3343,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="91">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="E75" s="92"/>
       <c r="F75" s="90"/>
@@ -3350,13 +3362,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="91">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="E76" s="92"/>
       <c r="F76" s="90"/>
@@ -3369,13 +3381,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D77" s="91">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="E77" s="92"/>
       <c r="F77" s="90"/>
@@ -3388,13 +3400,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D78" s="91">
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="E78" s="92"/>
       <c r="F78" s="90"/>
@@ -3407,13 +3419,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="90">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C79" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D79" s="91">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="E79" s="92"/>
       <c r="F79" s="90"/>
@@ -3426,13 +3438,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="90">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C80" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D80" s="91">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="E80" s="92"/>
       <c r="F80" s="90"/>
@@ -3440,23 +3452,23 @@
       <c r="H80" s="90"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="19">
+      <c r="A81" s="90">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="B81" s="19">
-        <v>1</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D81" s="24">
-        <v>46063</v>
-      </c>
-      <c r="E81" s="20"/>
-      <c r="F81" s="19"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="19"/>
+      <c r="B81" s="90">
+        <v>10</v>
+      </c>
+      <c r="C81" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" s="91">
+        <v>46062</v>
+      </c>
+      <c r="E81" s="92"/>
+      <c r="F81" s="90"/>
+      <c r="G81" s="90"/>
+      <c r="H81" s="90"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
@@ -3464,13 +3476,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D82" s="24">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="E82" s="20"/>
       <c r="F82" s="19"/>
@@ -3483,13 +3495,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D83" s="24">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="E83" s="20"/>
       <c r="F83" s="19"/>
@@ -3502,13 +3514,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D84" s="24">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="E84" s="20"/>
       <c r="F84" s="19"/>
@@ -3521,13 +3533,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D85" s="24">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="E85" s="20"/>
       <c r="F85" s="19"/>
@@ -3540,13 +3552,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D86" s="24">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="E86" s="20"/>
       <c r="F86" s="19"/>
@@ -3559,13 +3571,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="24">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="E87" s="20"/>
       <c r="F87" s="19"/>
@@ -3578,13 +3590,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D88" s="24">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="E88" s="20"/>
       <c r="F88" s="19"/>
@@ -3597,13 +3609,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C89" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D89" s="24">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E89" s="20"/>
       <c r="F89" s="19"/>
@@ -3616,13 +3628,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C90" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D90" s="24">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E90" s="20"/>
       <c r="F90" s="19"/>
@@ -3630,31 +3642,23 @@
       <c r="H90" s="19"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="87">
+      <c r="A91" s="19">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="B91" s="87">
-        <v>1</v>
-      </c>
-      <c r="C91" s="87" t="s">
-        <v>40</v>
-      </c>
-      <c r="D91" s="88">
-        <v>46312</v>
-      </c>
-      <c r="E91" s="89">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F91" s="89" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="H91" s="87" t="s">
-        <v>11</v>
-      </c>
+      <c r="B91" s="19">
+        <v>10</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" s="24">
+        <v>46072</v>
+      </c>
+      <c r="E91" s="20"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="19"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="87">
@@ -3662,18 +3666,26 @@
         <v>91</v>
       </c>
       <c r="B92" s="87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D92" s="88">
-        <v>46074</v>
-      </c>
-      <c r="E92" s="89"/>
-      <c r="F92" s="87"/>
-      <c r="G92" s="87"/>
-      <c r="H92" s="87"/>
+        <v>46312</v>
+      </c>
+      <c r="E92" s="89">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F92" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="H92" s="87" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="87">
@@ -3681,13 +3693,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D93" s="88">
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="E93" s="89"/>
       <c r="F93" s="87"/>
@@ -3700,13 +3712,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C94" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D94" s="88">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="E94" s="89"/>
       <c r="F94" s="87"/>
@@ -3719,13 +3731,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D95" s="88">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="E95" s="89"/>
       <c r="F95" s="87"/>
@@ -3733,23 +3745,23 @@
       <c r="H95" s="87"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="8">
+      <c r="A96" s="87">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="B96" s="8">
-        <v>1</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D96" s="29">
-        <v>46078</v>
-      </c>
-      <c r="E96" s="12"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
+      <c r="B96" s="87">
+        <v>5</v>
+      </c>
+      <c r="C96" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="D96" s="88">
+        <v>46077</v>
+      </c>
+      <c r="E96" s="89"/>
+      <c r="F96" s="87"/>
+      <c r="G96" s="87"/>
+      <c r="H96" s="87"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
@@ -3757,13 +3769,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D97" s="29">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="8"/>
@@ -3776,13 +3788,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D98" s="29">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="8"/>
@@ -3795,13 +3807,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D99" s="29">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="8"/>
@@ -3814,13 +3826,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D100" s="29">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="8"/>
@@ -3833,13 +3845,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D101" s="29">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="8"/>
@@ -3852,13 +3864,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D102" s="29">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="8"/>
@@ -3867,17 +3879,17 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
-        <f t="shared" ref="A103:A134" si="3">A102+1</f>
+        <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="B103" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D103" s="29">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="8"/>
@@ -3886,17 +3898,17 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A104:A135" si="3">A103+1</f>
         <v>103</v>
       </c>
       <c r="B104" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D104" s="29">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="8"/>
@@ -3909,13 +3921,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D105" s="29">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="8"/>
@@ -3923,31 +3935,23 @@
       <c r="H105" s="8"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="25">
+      <c r="A106" s="8">
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="B106" s="25">
-        <v>1</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D106" s="26">
-        <v>46312</v>
-      </c>
-      <c r="E106" s="27">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F106" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="G106" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H106" s="25" t="s">
-        <v>11</v>
-      </c>
+      <c r="B106" s="8">
+        <v>10</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D106" s="29">
+        <v>46087</v>
+      </c>
+      <c r="E106" s="12"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -3955,18 +3959,26 @@
         <v>106</v>
       </c>
       <c r="B107" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D107" s="26">
-        <v>46089</v>
-      </c>
-      <c r="E107" s="27"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
-      <c r="H107" s="25"/>
+        <v>46312</v>
+      </c>
+      <c r="E107" s="27">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F107" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G107" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H107" s="25" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="25">
@@ -3974,13 +3986,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D108" s="26">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E108" s="27"/>
       <c r="F108" s="25"/>
@@ -3993,13 +4005,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D109" s="26">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="E109" s="27"/>
       <c r="F109" s="25"/>
@@ -4012,13 +4024,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D110" s="26">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E110" s="27"/>
       <c r="F110" s="25"/>
@@ -4026,23 +4038,23 @@
       <c r="H110" s="25"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="42">
+      <c r="A111" s="25">
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
-      <c r="B111" s="42">
-        <v>1</v>
-      </c>
-      <c r="C111" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D111" s="43">
-        <v>46312</v>
-      </c>
-      <c r="E111" s="44"/>
-      <c r="F111" s="42"/>
-      <c r="G111" s="42"/>
-      <c r="H111" s="42"/>
+      <c r="B111" s="25">
+        <v>5</v>
+      </c>
+      <c r="C111" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D111" s="26">
+        <v>46092</v>
+      </c>
+      <c r="E111" s="27"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
+      <c r="H111" s="25"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="42">
@@ -4050,13 +4062,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D112" s="43">
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="E112" s="44"/>
       <c r="F112" s="42"/>
@@ -4069,13 +4081,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D113" s="43">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="E113" s="44"/>
       <c r="F113" s="42"/>
@@ -4088,13 +4100,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C114" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D114" s="43">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="E114" s="44"/>
       <c r="F114" s="42"/>
@@ -4107,13 +4119,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D115" s="43">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="E115" s="44"/>
       <c r="F115" s="42"/>
@@ -4121,31 +4133,23 @@
       <c r="H115" s="42"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="30">
+      <c r="A116" s="42">
         <f t="shared" si="3"/>
         <v>115</v>
       </c>
-      <c r="B116" s="30">
-        <v>1</v>
-      </c>
-      <c r="C116" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D116" s="59">
-        <v>46230</v>
-      </c>
-      <c r="E116" s="82">
-        <v>0.375</v>
-      </c>
-      <c r="F116" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G116" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H116" s="31" t="s">
-        <v>11</v>
-      </c>
+      <c r="B116" s="42">
+        <v>5</v>
+      </c>
+      <c r="C116" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D116" s="43">
+        <v>46097</v>
+      </c>
+      <c r="E116" s="44"/>
+      <c r="F116" s="42"/>
+      <c r="G116" s="42"/>
+      <c r="H116" s="42"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="30">
@@ -4153,13 +4157,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D117" s="59">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="E117" s="82">
         <v>0.375</v>
@@ -4180,13 +4184,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D118" s="59">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="E118" s="82">
         <v>0.375</v>
@@ -4207,13 +4211,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C119" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D119" s="59">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E119" s="82">
         <v>0.375</v>
@@ -4234,13 +4238,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D120" s="59">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="E120" s="82">
         <v>0.375</v>
@@ -4261,13 +4265,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D121" s="59">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="E121" s="82">
         <v>0.375</v>
@@ -4276,7 +4280,7 @@
         <v>19</v>
       </c>
       <c r="G121" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H121" s="31" t="s">
         <v>11</v>
@@ -4288,13 +4292,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D122" s="59">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E122" s="82">
         <v>0.375</v>
@@ -4315,13 +4319,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D123" s="59">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E123" s="82">
         <v>0.375</v>
@@ -4342,13 +4346,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C124" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D124" s="59">
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="E124" s="82">
         <v>0.375</v>
@@ -4357,7 +4361,7 @@
         <v>19</v>
       </c>
       <c r="G124" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H124" s="31" t="s">
         <v>11</v>
@@ -4369,13 +4373,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D125" s="59">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="E125" s="82">
         <v>0.375</v>
@@ -4396,13 +4400,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C126" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D126" s="59">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E126" s="82">
         <v>0.375</v>
@@ -4418,56 +4422,56 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="40">
+      <c r="A127" s="30">
         <f t="shared" si="3"/>
         <v>126</v>
       </c>
-      <c r="B127" s="40">
-        <v>2</v>
-      </c>
-      <c r="C127" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D127" s="60">
-        <v>46256</v>
-      </c>
-      <c r="E127" s="83">
+      <c r="B127" s="30">
+        <v>11</v>
+      </c>
+      <c r="C127" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D127" s="59">
+        <v>46323</v>
+      </c>
+      <c r="E127" s="82">
         <v>0.375</v>
       </c>
-      <c r="F127" s="41" t="s">
+      <c r="F127" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G127" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H127" s="41" t="s">
+      <c r="G127" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H127" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="54">
+      <c r="A128" s="40">
         <f t="shared" si="3"/>
         <v>127</v>
       </c>
-      <c r="B128" s="54">
-        <v>1</v>
-      </c>
-      <c r="C128" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D128" s="55">
-        <v>46367</v>
-      </c>
-      <c r="E128" s="95">
-        <v>0.6875</v>
-      </c>
-      <c r="F128" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G128" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="H128" s="54" t="s">
+      <c r="B128" s="40">
+        <v>2</v>
+      </c>
+      <c r="C128" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" s="60">
+        <v>46256</v>
+      </c>
+      <c r="E128" s="83">
+        <v>0.375</v>
+      </c>
+      <c r="F128" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H128" s="41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4477,16 +4481,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D129" s="55">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="E129" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F129" s="54" t="s">
         <v>52</v>
@@ -4504,16 +4508,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D130" s="55">
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="E130" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F130" s="54" t="s">
         <v>52</v>
@@ -4531,22 +4535,22 @@
         <v>130</v>
       </c>
       <c r="B131" s="54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C131" s="54" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D131" s="55">
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="E131" s="95">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="F131" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G131" s="54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H131" s="54" t="s">
         <v>11</v>
@@ -4558,22 +4562,22 @@
         <v>131</v>
       </c>
       <c r="B132" s="54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C132" s="54" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D132" s="55">
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="E132" s="95">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F132" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G132" s="54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H132" s="54" t="s">
         <v>11</v>
@@ -4585,16 +4589,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D133" s="55">
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="E133" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F133" s="54" t="s">
         <v>52</v>
@@ -4612,16 +4616,16 @@
         <v>133</v>
       </c>
       <c r="B134" s="54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C134" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D134" s="55">
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="E134" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F134" s="54" t="s">
         <v>52</v>
@@ -4633,24 +4637,51 @@
         <v>11</v>
       </c>
     </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="54">
+        <f t="shared" si="3"/>
+        <v>134</v>
+      </c>
+      <c r="B135" s="54">
+        <v>6</v>
+      </c>
+      <c r="C135" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D135" s="55">
+        <v>46404</v>
+      </c>
+      <c r="E135" s="95">
+        <v>0.375</v>
+      </c>
+      <c r="F135" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="G135" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="H135" s="54" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H110" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H110">
-      <sortCondition ref="A1:A110"/>
+  <autoFilter ref="A1:H111" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H111">
+      <sortCondition ref="A1:A111"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="50" max="16383" man="1"/>
-    <brk id="60" max="16383" man="1"/>
+    <brk id="51" max="16383" man="1"/>
+    <brk id="61" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="84" customWidth="1"/>
@@ -4712,7 +4743,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="96">
-        <f t="shared" ref="D2:D37" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
+        <f t="shared" ref="D2:D38" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="E2" s="96" t="str">
@@ -4868,7 +4899,7 @@
         <v>0.8125</v>
       </c>
       <c r="D6" s="96">
-        <f t="shared" ref="D6:D14" si="1">IF(I6 = "KM",C6+"1:45",IF(I6="U23",C6+"1:45",IF(I6 = "U16",C6+"1:45",IF(I6 = "U15",C6+"1:30",IF(I6 = "U14",C6+"1:30",IF(I6 = "U13",C6+"1:35",IF(I6 = "U12",C6+"1:10",IF(I6 = "U11",C6+"1:10",IF(I6 = "U10",C6+"1:03",C6+"3:00")))))))))</f>
+        <f t="shared" ref="D6:D15" si="1">IF(I6 = "KM",C6+"1:45",IF(I6="U23",C6+"1:45",IF(I6 = "U16",C6+"1:45",IF(I6 = "U15",C6+"1:30",IF(I6 = "U14",C6+"1:30",IF(I6 = "U13",C6+"1:35",IF(I6 = "U12",C6+"1:10",IF(I6 = "U11",C6+"1:10",IF(I6 = "U10",C6+"1:03",C6+"3:00")))))))))</f>
         <v>0.88541666666666663</v>
       </c>
       <c r="E6" s="96" t="str">
@@ -5135,77 +5166,77 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="112" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" s="114" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="84"/>
       <c r="B13" s="81">
         <f>'Nach Mannschaften sortiert'!D13</f>
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="C13" s="96">
         <f>'Nach Mannschaften sortiert'!E13</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="D13" s="96">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D13" si="3">IF(I13 = "KM",C13+"1:45",IF(I13="U23",C13+"1:45",IF(I13 = "U16",C13+"1:45",IF(I13 = "U15",C13+"1:30",IF(I13 = "U14",C13+"1:30",IF(I13 = "U13",C13+"1:35",IF(I13 = "U12",C13+"1:10",IF(I13 = "U11",C13+"1:10",IF(I13 = "U10",C13+"1:03",C13+"3:00")))))))))</f>
         <v>0.48958333333333337</v>
       </c>
       <c r="E13" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
-        <v>NEUFELD</v>
+        <v>LAXENBURG</v>
       </c>
       <c r="F13" s="84"/>
-      <c r="G13" s="112" t="str">
+      <c r="G13" s="114" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
-        <v>Heim</v>
-      </c>
-      <c r="H13" s="112" t="str">
+        <v>Auswärts</v>
+      </c>
+      <c r="H13" s="114" t="str">
         <f>'Nach Mannschaften sortiert'!G13</f>
-        <v>Traiskirchen</v>
-      </c>
-      <c r="I13" s="112" t="str">
+        <v>Laxenburg</v>
+      </c>
+      <c r="I13" s="114" t="str">
         <f>'Nach Mannschaften sortiert'!C13</f>
         <v>U16</v>
       </c>
       <c r="J13" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="112" t="s">
+      <c r="K13" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="L13" s="112" t="s">
+      <c r="L13" s="114" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="111" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" s="112" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="84"/>
       <c r="B14" s="81">
         <f>'Nach Mannschaften sortiert'!D14</f>
-        <v>46445</v>
+        <v>46260</v>
       </c>
       <c r="C14" s="96">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D14" s="96">
         <f t="shared" si="1"/>
-        <v>0.57291666666666663</v>
+        <v>0.48958333333333337</v>
       </c>
       <c r="E14" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
-        <v>BAD ERLACH</v>
+        <v>NEUFELD</v>
       </c>
       <c r="F14" s="84"/>
       <c r="G14" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H14" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G14</f>
-        <v>Bad Erlach</v>
+        <v>Traiskirchen</v>
       </c>
       <c r="I14" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C14</f>
-        <v>KM</v>
+        <v>U16</v>
       </c>
       <c r="J14" s="84" t="s">
         <v>68</v>
@@ -5217,61 +5248,63 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="84"/>
       <c r="B15" s="81">
         <f>'Nach Mannschaften sortiert'!D15</f>
-        <v>46250</v>
+        <v>46445</v>
       </c>
       <c r="C15" s="96">
         <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.72916666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D15" s="96">
-        <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <f t="shared" si="1"/>
+        <v>0.57291666666666663</v>
       </c>
       <c r="E15" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
-        <v>KITTSEE</v>
-      </c>
-      <c r="G15" t="str">
+        <v>BAD ERLACH</v>
+      </c>
+      <c r="F15" s="84"/>
+      <c r="G15" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
         <v>Auswärts</v>
       </c>
-      <c r="H15" t="str">
+      <c r="H15" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!G15</f>
-        <v>Kittsee</v>
-      </c>
-      <c r="I15" t="str">
+        <v>Bad Erlach</v>
+      </c>
+      <c r="I15" s="112" t="str">
         <f>'Nach Mannschaften sortiert'!C15</f>
         <v>KM</v>
       </c>
       <c r="J15" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K15" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="K15" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15" s="112" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" s="81">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C16" s="96">
         <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D16" s="96">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E16" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G16" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
@@ -5279,7 +5312,7 @@
       </c>
       <c r="H16" t="str">
         <f>'Nach Mannschaften sortiert'!G16</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I16" t="str">
         <f>'Nach Mannschaften sortiert'!C16</f>
@@ -5298,27 +5331,27 @@
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="81">
         <f>'Nach Mannschaften sortiert'!D17</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C17" s="96">
         <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D17" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.90625</v>
       </c>
       <c r="E17" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G17" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H17" t="str">
         <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I17" t="str">
         <f>'Nach Mannschaften sortiert'!C17</f>
@@ -5337,27 +5370,27 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="81">
         <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C18" s="96">
         <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D18" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E18" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G18" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H18" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I18" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
@@ -5376,27 +5409,27 @@
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="81">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C19" s="96">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="D19" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E19" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G19" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H19" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I19" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
@@ -5415,27 +5448,27 @@
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="81">
         <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C20" s="96">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D20" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E20" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G20" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H20" t="str">
         <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I20" t="str">
         <f>'Nach Mannschaften sortiert'!C20</f>
@@ -5454,27 +5487,27 @@
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="81">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C21" s="96">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D21" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E21" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G21" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H21" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I21" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
@@ -5493,27 +5526,27 @@
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="81">
         <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C22" s="96">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D22" s="96">
         <f t="shared" si="0"/>
-        <v>0.86458333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E22" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G22" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H22" t="str">
         <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I22" t="str">
         <f>'Nach Mannschaften sortiert'!C22</f>
@@ -5532,27 +5565,27 @@
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="81">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="C23" s="96">
         <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D23" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E23" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G23" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H23" t="str">
         <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I23" t="str">
         <f>'Nach Mannschaften sortiert'!C23</f>
@@ -5571,7 +5604,7 @@
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="81">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C24" s="96">
         <f>'Nach Mannschaften sortiert'!E24</f>
@@ -5583,15 +5616,15 @@
       </c>
       <c r="E24" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G24" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H24" t="str">
         <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I24" t="str">
         <f>'Nach Mannschaften sortiert'!C24</f>
@@ -5610,27 +5643,27 @@
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="81">
         <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C25" s="96">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D25" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E25" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G25" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H25" t="str">
         <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I25" t="str">
         <f>'Nach Mannschaften sortiert'!C25</f>
@@ -5649,27 +5682,27 @@
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="81">
         <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C26" s="96">
         <f>'Nach Mannschaften sortiert'!E26</f>
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E26" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G26" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H26" t="str">
         <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I26" t="str">
         <f>'Nach Mannschaften sortiert'!C26</f>
@@ -5688,27 +5721,27 @@
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="81">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C27" s="96">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D27" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E27" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G27" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H27" t="str">
         <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I27" t="str">
         <f>'Nach Mannschaften sortiert'!C27</f>
@@ -5727,31 +5760,31 @@
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="81">
         <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="C28" s="96">
         <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D28" s="96">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E28" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
-        <v>KITTSEE</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G28" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H28" t="str">
         <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>Kittsee</v>
+        <v>Andau</v>
       </c>
       <c r="I28" t="str">
         <f>'Nach Mannschaften sortiert'!C28</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J28" s="84" t="s">
         <v>68</v>
@@ -5766,19 +5799,19 @@
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="81">
         <f>'Nach Mannschaften sortiert'!D29</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C29" s="96">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D29" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="E29" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G29" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
@@ -5786,7 +5819,7 @@
       </c>
       <c r="H29" t="str">
         <f>'Nach Mannschaften sortiert'!G29</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I29" t="str">
         <f>'Nach Mannschaften sortiert'!C29</f>
@@ -5805,27 +5838,27 @@
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="81">
         <f>'Nach Mannschaften sortiert'!D30</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C30" s="96">
         <f>'Nach Mannschaften sortiert'!E30</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D30" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E30" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G30" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H30" t="str">
         <f>'Nach Mannschaften sortiert'!G30</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I30" t="str">
         <f>'Nach Mannschaften sortiert'!C30</f>
@@ -5844,27 +5877,27 @@
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="81">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C31" s="96">
         <f>'Nach Mannschaften sortiert'!E31</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D31" s="96">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E31" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G31" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H31" t="str">
         <f>'Nach Mannschaften sortiert'!G31</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I31" t="str">
         <f>'Nach Mannschaften sortiert'!C31</f>
@@ -5883,27 +5916,27 @@
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="81">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C32" s="96">
         <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D32" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E32" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G32" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H32" t="str">
         <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
@@ -5922,27 +5955,27 @@
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="81">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C33" s="96">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D33" s="96">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E33" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G33" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H33" t="str">
         <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I33" t="str">
         <f>'Nach Mannschaften sortiert'!C33</f>
@@ -5961,27 +5994,27 @@
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="81">
         <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C34" s="96">
         <f>'Nach Mannschaften sortiert'!E34</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D34" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.65625</v>
       </c>
       <c r="E34" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G34" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H34" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I34" t="str">
         <f>'Nach Mannschaften sortiert'!C34</f>
@@ -6000,27 +6033,27 @@
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="81">
         <f>'Nach Mannschaften sortiert'!D35</f>
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C35" s="96">
         <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D35" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E35" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G35" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H35" t="str">
         <f>'Nach Mannschaften sortiert'!G35</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I35" t="str">
         <f>'Nach Mannschaften sortiert'!C35</f>
@@ -6039,27 +6072,27 @@
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="81">
         <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="C36" s="96">
         <f>'Nach Mannschaften sortiert'!E36</f>
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D36" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.78125</v>
       </c>
       <c r="E36" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G36" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H36" t="str">
         <f>'Nach Mannschaften sortiert'!G36</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I36" t="str">
         <f>'Nach Mannschaften sortiert'!C36</f>
@@ -6078,7 +6111,7 @@
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="81">
         <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C37" s="96">
         <f>'Nach Mannschaften sortiert'!E37</f>
@@ -6090,15 +6123,15 @@
       </c>
       <c r="E37" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G37" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H37" t="str">
         <f>'Nach Mannschaften sortiert'!G37</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I37" t="str">
         <f>'Nach Mannschaften sortiert'!C37</f>
@@ -6117,27 +6150,27 @@
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="81">
         <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C38" s="96">
         <f>'Nach Mannschaften sortiert'!E38</f>
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D38" s="96">
-        <f t="shared" ref="D38:D69" si="3">IF(I38 = "KM",C38+"1:45",IF(I38="U23",C38+"1:45",IF(I38 = "U16",C38+"1:45",IF(I38 = "U15",C38+"1:30",IF(I38 = "U14",C38+"1:30",IF(I38 = "U13",C38+"1:35",IF(I38 = "U12",C38+"1:10",IF(I38 = "U11",C38+"1:10",IF(I38 = "U10",C38+"1:03",C38+"3:00")))))))))</f>
-        <v>0.69791666666666663</v>
+        <f t="shared" si="0"/>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E38" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G38" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H38" t="str">
         <f>'Nach Mannschaften sortiert'!G38</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I38" t="str">
         <f>'Nach Mannschaften sortiert'!C38</f>
@@ -6156,27 +6189,27 @@
     <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="81">
         <f>'Nach Mannschaften sortiert'!D39</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C39" s="96">
         <f>'Nach Mannschaften sortiert'!E39</f>
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D39" s="96">
-        <f t="shared" si="3"/>
-        <v>0.73958333333333326</v>
+        <f t="shared" ref="D39:D70" si="4">IF(I39 = "KM",C39+"1:45",IF(I39="U23",C39+"1:45",IF(I39 = "U16",C39+"1:45",IF(I39 = "U15",C39+"1:30",IF(I39 = "U14",C39+"1:30",IF(I39 = "U13",C39+"1:35",IF(I39 = "U12",C39+"1:10",IF(I39 = "U11",C39+"1:10",IF(I39 = "U10",C39+"1:03",C39+"3:00")))))))))</f>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E39" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G39" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H39" t="str">
         <f>'Nach Mannschaften sortiert'!G39</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I39" t="str">
         <f>'Nach Mannschaften sortiert'!C39</f>
@@ -6195,27 +6228,27 @@
     <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="81">
         <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C40" s="96">
         <f>'Nach Mannschaften sortiert'!E40</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D40" s="96">
-        <f t="shared" si="3"/>
-        <v>0.67708333333333326</v>
+        <f t="shared" si="4"/>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E40" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G40" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H40" t="str">
         <f>'Nach Mannschaften sortiert'!G40</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I40" t="str">
         <f>'Nach Mannschaften sortiert'!C40</f>
@@ -6234,31 +6267,31 @@
     <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="81">
         <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46023</v>
+        <v>46333</v>
       </c>
       <c r="C41" s="96">
         <f>'Nach Mannschaften sortiert'!E41</f>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D41" s="96">
-        <f t="shared" si="3"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E41" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F41)</f>
-        <v/>
-      </c>
-      <c r="G41">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G41" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
-        <v>0</v>
-      </c>
-      <c r="H41">
+        <v>Heim</v>
+      </c>
+      <c r="H41" t="str">
         <f>'Nach Mannschaften sortiert'!G41</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I41" t="str">
         <f>'Nach Mannschaften sortiert'!C41</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J41" s="84" t="s">
         <v>68</v>
@@ -6273,14 +6306,14 @@
     <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="81">
         <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C42" s="96">
         <f>'Nach Mannschaften sortiert'!E42</f>
         <v>0</v>
       </c>
       <c r="D42" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E42" s="96" t="str">
@@ -6312,14 +6345,14 @@
     <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="81">
         <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C43" s="96">
         <f>'Nach Mannschaften sortiert'!E43</f>
         <v>0</v>
       </c>
       <c r="D43" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E43" s="96" t="str">
@@ -6351,14 +6384,14 @@
     <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="81">
         <f>'Nach Mannschaften sortiert'!D44</f>
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C44" s="96">
         <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="D44" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E44" s="96" t="str">
@@ -6390,14 +6423,14 @@
     <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="81">
         <f>'Nach Mannschaften sortiert'!D45</f>
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C45" s="96">
         <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="D45" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E45" s="96" t="str">
@@ -6429,14 +6462,14 @@
     <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="81">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C46" s="96">
         <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="D46" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E46" s="96" t="str">
@@ -6468,14 +6501,14 @@
     <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="81">
         <f>'Nach Mannschaften sortiert'!D47</f>
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C47" s="96">
         <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="D47" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E47" s="96" t="str">
@@ -6507,14 +6540,14 @@
     <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="81">
         <f>'Nach Mannschaften sortiert'!D48</f>
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C48" s="96">
         <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="D48" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E48" s="96" t="str">
@@ -6546,14 +6579,14 @@
     <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="81">
         <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C49" s="96">
         <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="D49" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E49" s="96" t="str">
@@ -6585,14 +6618,14 @@
     <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="81">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C50" s="96">
         <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="D50" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E50" s="96" t="str">
@@ -6624,15 +6657,15 @@
     <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="81">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C51" s="96">
         <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="D51" s="96">
-        <f t="shared" si="3"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="4"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E51" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
@@ -6648,7 +6681,7 @@
       </c>
       <c r="I51" t="str">
         <f>'Nach Mannschaften sortiert'!C51</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J51" s="84" t="s">
         <v>68</v>
@@ -6663,14 +6696,14 @@
     <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="81">
         <f>'Nach Mannschaften sortiert'!D52</f>
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C52" s="96">
         <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="D52" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E52" s="96" t="str">
@@ -6702,14 +6735,14 @@
     <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="81">
         <f>'Nach Mannschaften sortiert'!D53</f>
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C53" s="96">
         <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="D53" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E53" s="96" t="str">
@@ -6741,14 +6774,14 @@
     <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="81">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C54" s="96">
         <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="D54" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E54" s="96" t="str">
@@ -6780,14 +6813,14 @@
     <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="81">
         <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="C55" s="96">
         <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
       <c r="D55" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E55" s="96" t="str">
@@ -6819,14 +6852,14 @@
     <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
         <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="C56" s="96">
         <f>'Nach Mannschaften sortiert'!E56</f>
         <v>0</v>
       </c>
       <c r="D56" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E56" s="96" t="str">
@@ -6858,14 +6891,14 @@
     <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="81">
         <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C57" s="96">
         <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
       <c r="D57" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E57" s="96" t="str">
@@ -6897,14 +6930,14 @@
     <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="81">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C58" s="96">
         <f>'Nach Mannschaften sortiert'!E58</f>
         <v>0</v>
       </c>
       <c r="D58" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E58" s="96" t="str">
@@ -6936,14 +6969,14 @@
     <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="81">
         <f>'Nach Mannschaften sortiert'!D59</f>
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C59" s="96">
         <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="D59" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E59" s="96" t="str">
@@ -6975,14 +7008,14 @@
     <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="81">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C60" s="96">
         <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="D60" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.25E-2</v>
       </c>
       <c r="E60" s="96" t="str">
@@ -7014,15 +7047,15 @@
     <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="81">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C61" s="96">
         <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="D61" s="96">
-        <f t="shared" si="3"/>
-        <v>0.125</v>
+        <f t="shared" si="4"/>
+        <v>6.25E-2</v>
       </c>
       <c r="E61" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F61)</f>
@@ -7038,7 +7071,7 @@
       </c>
       <c r="I61" t="str">
         <f>'Nach Mannschaften sortiert'!C61</f>
-        <v>U12_1</v>
+        <v>U14</v>
       </c>
       <c r="J61" s="84" t="s">
         <v>68</v>
@@ -7053,14 +7086,14 @@
     <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="81">
         <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C62" s="96">
         <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="D62" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E62" s="96" t="str">
@@ -7092,14 +7125,14 @@
     <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="81">
         <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C63" s="96">
         <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="D63" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E63" s="96" t="str">
@@ -7131,14 +7164,14 @@
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="81">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C64" s="96">
         <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="D64" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E64" s="96" t="str">
@@ -7170,14 +7203,14 @@
     <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="81">
         <f>'Nach Mannschaften sortiert'!D65</f>
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C65" s="96">
         <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="D65" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E65" s="96" t="str">
@@ -7209,14 +7242,14 @@
     <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="81">
         <f>'Nach Mannschaften sortiert'!D66</f>
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="C66" s="96">
         <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="D66" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E66" s="96" t="str">
@@ -7248,14 +7281,14 @@
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="81">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="C67" s="96">
         <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="D67" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E67" s="96" t="str">
@@ -7287,14 +7320,14 @@
     <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="81">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C68" s="96">
         <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="D68" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E68" s="96" t="str">
@@ -7326,14 +7359,14 @@
     <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="81">
         <f>'Nach Mannschaften sortiert'!D69</f>
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C69" s="96">
         <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="D69" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E69" s="96" t="str">
@@ -7365,14 +7398,14 @@
     <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="81">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="C70" s="96">
         <f>'Nach Mannschaften sortiert'!E70</f>
         <v>0</v>
       </c>
       <c r="D70" s="96">
-        <f t="shared" ref="D70:D90" si="4">IF(I70 = "KM",C70+"1:45",IF(I70="U23",C70+"1:45",IF(I70 = "U16",C70+"1:45",IF(I70 = "U15",C70+"1:30",IF(I70 = "U14",C70+"1:30",IF(I70 = "U13",C70+"1:35",IF(I70 = "U12",C70+"1:10",IF(I70 = "U11",C70+"1:10",IF(I70 = "U10",C70+"1:03",C70+"3:00")))))))))</f>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E70" s="96" t="str">
@@ -7404,14 +7437,14 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="81">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C71" s="96">
         <f>'Nach Mannschaften sortiert'!E71</f>
         <v>0</v>
       </c>
       <c r="D71" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D71:D91" si="5">IF(I71 = "KM",C71+"1:45",IF(I71="U23",C71+"1:45",IF(I71 = "U16",C71+"1:45",IF(I71 = "U15",C71+"1:30",IF(I71 = "U14",C71+"1:30",IF(I71 = "U13",C71+"1:35",IF(I71 = "U12",C71+"1:10",IF(I71 = "U11",C71+"1:10",IF(I71 = "U10",C71+"1:03",C71+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E71" s="96" t="str">
@@ -7428,7 +7461,7 @@
       </c>
       <c r="I71" t="str">
         <f>'Nach Mannschaften sortiert'!C71</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J71" s="84" t="s">
         <v>68</v>
@@ -7443,14 +7476,14 @@
     <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="81">
         <f>'Nach Mannschaften sortiert'!D72</f>
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="C72" s="96">
         <f>'Nach Mannschaften sortiert'!E72</f>
         <v>0</v>
       </c>
       <c r="D72" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E72" s="96" t="str">
@@ -7482,14 +7515,14 @@
     <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="81">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C73" s="96">
         <f>'Nach Mannschaften sortiert'!E73</f>
         <v>0</v>
       </c>
       <c r="D73" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E73" s="96" t="str">
@@ -7521,14 +7554,14 @@
     <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="81">
         <f>'Nach Mannschaften sortiert'!D74</f>
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C74" s="96">
         <f>'Nach Mannschaften sortiert'!E74</f>
         <v>0</v>
       </c>
       <c r="D74" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E74" s="96" t="str">
@@ -7560,14 +7593,14 @@
     <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="81">
         <f>'Nach Mannschaften sortiert'!D75</f>
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="C75" s="96">
         <f>'Nach Mannschaften sortiert'!E75</f>
         <v>0</v>
       </c>
       <c r="D75" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E75" s="96" t="str">
@@ -7599,14 +7632,14 @@
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="81">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C76" s="96">
         <f>'Nach Mannschaften sortiert'!E76</f>
         <v>0</v>
       </c>
       <c r="D76" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E76" s="96" t="str">
@@ -7638,14 +7671,14 @@
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="81">
         <f>'Nach Mannschaften sortiert'!D77</f>
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="C77" s="96">
         <f>'Nach Mannschaften sortiert'!E77</f>
         <v>0</v>
       </c>
       <c r="D77" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E77" s="96" t="str">
@@ -7677,14 +7710,14 @@
     <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="81">
         <f>'Nach Mannschaften sortiert'!D78</f>
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="C78" s="96">
         <f>'Nach Mannschaften sortiert'!E78</f>
         <v>0</v>
       </c>
       <c r="D78" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E78" s="96" t="str">
@@ -7716,14 +7749,14 @@
     <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="81">
         <f>'Nach Mannschaften sortiert'!D79</f>
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C79" s="96">
         <f>'Nach Mannschaften sortiert'!E79</f>
         <v>0</v>
       </c>
       <c r="D79" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E79" s="96" t="str">
@@ -7755,14 +7788,14 @@
     <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="81">
         <f>'Nach Mannschaften sortiert'!D80</f>
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C80" s="96">
         <f>'Nach Mannschaften sortiert'!E80</f>
         <v>0</v>
       </c>
       <c r="D80" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E80" s="96" t="str">
@@ -7794,15 +7827,15 @@
     <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="81">
         <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="C81" s="96">
         <f>'Nach Mannschaften sortiert'!E81</f>
         <v>0</v>
       </c>
       <c r="D81" s="96">
-        <f t="shared" si="4"/>
-        <v>4.8611111111111112E-2</v>
+        <f t="shared" si="5"/>
+        <v>0.125</v>
       </c>
       <c r="E81" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F81)</f>
@@ -7818,7 +7851,7 @@
       </c>
       <c r="I81" t="str">
         <f>'Nach Mannschaften sortiert'!C81</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J81" s="84" t="s">
         <v>68</v>
@@ -7833,14 +7866,14 @@
     <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="81">
         <f>'Nach Mannschaften sortiert'!D82</f>
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C82" s="96">
         <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="D82" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E82" s="96" t="str">
@@ -7872,14 +7905,14 @@
     <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="81">
         <f>'Nach Mannschaften sortiert'!D83</f>
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C83" s="96">
         <f>'Nach Mannschaften sortiert'!E83</f>
         <v>0</v>
       </c>
       <c r="D83" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E83" s="96" t="str">
@@ -7911,14 +7944,14 @@
     <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="81">
         <f>'Nach Mannschaften sortiert'!D84</f>
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C84" s="96">
         <f>'Nach Mannschaften sortiert'!E84</f>
         <v>0</v>
       </c>
       <c r="D84" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E84" s="96" t="str">
@@ -7950,14 +7983,14 @@
     <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="81">
         <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="C85" s="96">
         <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="D85" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E85" s="96" t="str">
@@ -7989,14 +8022,14 @@
     <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="81">
         <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="C86" s="96">
         <f>'Nach Mannschaften sortiert'!E86</f>
         <v>0</v>
       </c>
       <c r="D86" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E86" s="96" t="str">
@@ -8028,14 +8061,14 @@
     <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="81">
         <f>'Nach Mannschaften sortiert'!D87</f>
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="C87" s="96">
         <f>'Nach Mannschaften sortiert'!E87</f>
         <v>0</v>
       </c>
       <c r="D87" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E87" s="96" t="str">
@@ -8067,14 +8100,14 @@
     <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="81">
         <f>'Nach Mannschaften sortiert'!D88</f>
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="C88" s="96">
         <f>'Nach Mannschaften sortiert'!E88</f>
         <v>0</v>
       </c>
       <c r="D88" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E88" s="96" t="str">
@@ -8106,14 +8139,14 @@
     <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="81">
         <f>'Nach Mannschaften sortiert'!D89</f>
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="C89" s="96">
         <f>'Nach Mannschaften sortiert'!E89</f>
         <v>0</v>
       </c>
       <c r="D89" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E89" s="96" t="str">
@@ -8145,14 +8178,14 @@
     <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="81">
         <f>'Nach Mannschaften sortiert'!D90</f>
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C90" s="96">
         <f>'Nach Mannschaften sortiert'!E90</f>
         <v>0</v>
       </c>
       <c r="D90" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E90" s="96" t="str">
@@ -8184,30 +8217,31 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="81">
         <f>'Nach Mannschaften sortiert'!D91</f>
-        <v>46312</v>
+        <v>46072</v>
       </c>
       <c r="C91" s="96">
         <f>'Nach Mannschaften sortiert'!E91</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D91" s="96">
-        <v>0.5</v>
+        <f t="shared" si="5"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E91" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F91)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="G91">
         <f>'Nach Mannschaften sortiert'!H91</f>
-        <v>Heim</v>
-      </c>
-      <c r="H91" t="str">
+        <v>0</v>
+      </c>
+      <c r="H91">
         <f>'Nach Mannschaften sortiert'!G91</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I91" t="str">
         <f>'Nach Mannschaften sortiert'!C91</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J91" s="84" t="s">
         <v>68</v>
@@ -8222,27 +8256,26 @@
     <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="81">
         <f>'Nach Mannschaften sortiert'!D92</f>
-        <v>46074</v>
+        <v>46312</v>
       </c>
       <c r="C92" s="96">
         <f>'Nach Mannschaften sortiert'!E92</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D92" s="96">
-        <f t="shared" ref="D92:D105" si="5">IF(I92 = "KM",C92+"1:45",IF(I92="U23",C92+"1:45",IF(I92 = "U16",C92+"1:45",IF(I92 = "U15",C92+"1:30",IF(I92 = "U14",C92+"1:30",IF(I92 = "U13",C92+"1:35",IF(I92 = "U12",C92+"1:10",IF(I92 = "U11",C92+"1:10",IF(I92 = "U10",C92+"1:03",C92+"3:00")))))))))</f>
-        <v>4.3750000000000004E-2</v>
+        <v>0.5</v>
       </c>
       <c r="E92" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F92)</f>
-        <v/>
-      </c>
-      <c r="G92">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G92" t="str">
         <f>'Nach Mannschaften sortiert'!H92</f>
-        <v>0</v>
-      </c>
-      <c r="H92">
+        <v>Heim</v>
+      </c>
+      <c r="H92" t="str">
         <f>'Nach Mannschaften sortiert'!G92</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I92" t="str">
         <f>'Nach Mannschaften sortiert'!C92</f>
@@ -8261,14 +8294,14 @@
     <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="81">
         <f>'Nach Mannschaften sortiert'!D93</f>
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="C93" s="96">
         <f>'Nach Mannschaften sortiert'!E93</f>
         <v>0</v>
       </c>
       <c r="D93" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="D93:D106" si="6">IF(I93 = "KM",C93+"1:45",IF(I93="U23",C93+"1:45",IF(I93 = "U16",C93+"1:45",IF(I93 = "U15",C93+"1:30",IF(I93 = "U14",C93+"1:30",IF(I93 = "U13",C93+"1:35",IF(I93 = "U12",C93+"1:10",IF(I93 = "U11",C93+"1:10",IF(I93 = "U10",C93+"1:03",C93+"3:00")))))))))</f>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E93" s="96" t="str">
@@ -8300,14 +8333,14 @@
     <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="81">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="C94" s="96">
         <f>'Nach Mannschaften sortiert'!E94</f>
         <v>0</v>
       </c>
       <c r="D94" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E94" s="96" t="str">
@@ -8339,14 +8372,14 @@
     <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95" s="81">
         <f>'Nach Mannschaften sortiert'!D95</f>
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C95" s="96">
         <f>'Nach Mannschaften sortiert'!E95</f>
         <v>0</v>
       </c>
       <c r="D95" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E95" s="96" t="str">
@@ -8378,15 +8411,15 @@
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="81">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C96" s="96">
         <f>'Nach Mannschaften sortiert'!E96</f>
         <v>0</v>
       </c>
       <c r="D96" s="96">
-        <f t="shared" si="5"/>
-        <v>0.125</v>
+        <f t="shared" si="6"/>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E96" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F96)</f>
@@ -8402,7 +8435,7 @@
       </c>
       <c r="I96" t="str">
         <f>'Nach Mannschaften sortiert'!C96</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J96" s="84" t="s">
         <v>68</v>
@@ -8417,14 +8450,14 @@
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="81">
         <f>'Nach Mannschaften sortiert'!D97</f>
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="C97" s="96">
         <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="D97" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E97" s="96" t="str">
@@ -8456,14 +8489,14 @@
     <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B98" s="81">
         <f>'Nach Mannschaften sortiert'!D98</f>
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C98" s="96">
         <f>'Nach Mannschaften sortiert'!E98</f>
         <v>0</v>
       </c>
       <c r="D98" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E98" s="96" t="str">
@@ -8495,14 +8528,14 @@
     <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B99" s="81">
         <f>'Nach Mannschaften sortiert'!D99</f>
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C99" s="96">
         <f>'Nach Mannschaften sortiert'!E99</f>
         <v>0</v>
       </c>
       <c r="D99" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E99" s="96" t="str">
@@ -8534,14 +8567,14 @@
     <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100" s="81">
         <f>'Nach Mannschaften sortiert'!D100</f>
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C100" s="96">
         <f>'Nach Mannschaften sortiert'!E100</f>
         <v>0</v>
       </c>
       <c r="D100" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E100" s="96" t="str">
@@ -8573,14 +8606,14 @@
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101" s="81">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C101" s="96">
         <f>'Nach Mannschaften sortiert'!E101</f>
         <v>0</v>
       </c>
       <c r="D101" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E101" s="96" t="str">
@@ -8612,14 +8645,14 @@
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102" s="81">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C102" s="96">
         <f>'Nach Mannschaften sortiert'!E102</f>
         <v>0</v>
       </c>
       <c r="D102" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E102" s="96" t="str">
@@ -8651,14 +8684,14 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="81">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C103" s="96">
         <f>'Nach Mannschaften sortiert'!E103</f>
         <v>0</v>
       </c>
       <c r="D103" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E103" s="96" t="str">
@@ -8690,14 +8723,14 @@
     <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B104" s="81">
         <f>'Nach Mannschaften sortiert'!D104</f>
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C104" s="96">
         <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0</v>
       </c>
       <c r="D104" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E104" s="96" t="str">
@@ -8729,14 +8762,14 @@
     <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105" s="81">
         <f>'Nach Mannschaften sortiert'!D105</f>
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="C105" s="96">
         <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="D105" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E105" s="96" t="str">
@@ -8768,30 +8801,31 @@
     <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106" s="81">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46312</v>
+        <v>46087</v>
       </c>
       <c r="C106" s="96">
         <f>'Nach Mannschaften sortiert'!E106</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D106" s="96">
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>0.125</v>
       </c>
       <c r="E106" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F106)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="G106">
         <f>'Nach Mannschaften sortiert'!H106</f>
-        <v>Heim</v>
-      </c>
-      <c r="H106" t="str">
+        <v>0</v>
+      </c>
+      <c r="H106">
         <f>'Nach Mannschaften sortiert'!G106</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I106" t="str">
         <f>'Nach Mannschaften sortiert'!C106</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J106" s="84" t="s">
         <v>68</v>
@@ -8806,27 +8840,26 @@
     <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B107" s="81">
         <f>'Nach Mannschaften sortiert'!D107</f>
-        <v>46089</v>
+        <v>46312</v>
       </c>
       <c r="C107" s="96">
         <f>'Nach Mannschaften sortiert'!E107</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D107" s="96">
-        <f t="shared" ref="D107:D127" si="6">IF(I107 = "KM",C107+"1:45",IF(I107="U23",C107+"1:45",IF(I107 = "U16",C107+"1:45",IF(I107 = "U15",C107+"1:30",IF(I107 = "U14",C107+"1:30",IF(I107 = "U13",C107+"1:35",IF(I107 = "U12",C107+"1:10",IF(I107 = "U11",C107+"1:10",IF(I107 = "U10",C107+"1:03",C107+"3:00")))))))))</f>
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E107" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F107)</f>
-        <v/>
-      </c>
-      <c r="G107">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G107" t="str">
         <f>'Nach Mannschaften sortiert'!H107</f>
-        <v>0</v>
-      </c>
-      <c r="H107">
+        <v>Heim</v>
+      </c>
+      <c r="H107" t="str">
         <f>'Nach Mannschaften sortiert'!G107</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I107" t="str">
         <f>'Nach Mannschaften sortiert'!C107</f>
@@ -8845,14 +8878,14 @@
     <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B108" s="81">
         <f>'Nach Mannschaften sortiert'!D108</f>
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="C108" s="96">
         <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="D108" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D108:D128" si="7">IF(I108 = "KM",C108+"1:45",IF(I108="U23",C108+"1:45",IF(I108 = "U16",C108+"1:45",IF(I108 = "U15",C108+"1:30",IF(I108 = "U14",C108+"1:30",IF(I108 = "U13",C108+"1:35",IF(I108 = "U12",C108+"1:10",IF(I108 = "U11",C108+"1:10",IF(I108 = "U10",C108+"1:03",C108+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E108" s="96" t="str">
@@ -8884,14 +8917,14 @@
     <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109" s="81">
         <f>'Nach Mannschaften sortiert'!D109</f>
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C109" s="96">
         <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="D109" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="E109" s="96" t="str">
@@ -8923,14 +8956,14 @@
     <row r="110" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B110" s="81">
         <f>'Nach Mannschaften sortiert'!D110</f>
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C110" s="96">
         <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="D110" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="E110" s="96" t="str">
@@ -8962,14 +8995,14 @@
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="81">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46312</v>
+        <v>46092</v>
       </c>
       <c r="C111" s="96">
         <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="D111" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="E111" s="96" t="str">
@@ -8986,7 +9019,7 @@
       </c>
       <c r="I111" t="str">
         <f>'Nach Mannschaften sortiert'!C111</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J111" s="84" t="s">
         <v>68</v>
@@ -9001,14 +9034,14 @@
     <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112" s="81">
         <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="C112" s="96">
         <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="D112" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="E112" s="96" t="str">
@@ -9040,14 +9073,14 @@
     <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113" s="81">
         <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="C113" s="96">
         <f>'Nach Mannschaften sortiert'!E113</f>
         <v>0</v>
       </c>
       <c r="D113" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="E113" s="96" t="str">
@@ -9079,14 +9112,14 @@
     <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114" s="81">
         <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="C114" s="96">
         <f>'Nach Mannschaften sortiert'!E114</f>
         <v>0</v>
       </c>
       <c r="D114" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="E114" s="96" t="str">
@@ -9118,14 +9151,14 @@
     <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115" s="81">
         <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="C115" s="96">
         <f>'Nach Mannschaften sortiert'!E115</f>
         <v>0</v>
       </c>
       <c r="D115" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="E115" s="96" t="str">
@@ -9157,31 +9190,31 @@
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116" s="81">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46230</v>
+        <v>46097</v>
       </c>
       <c r="C116" s="96">
         <f>'Nach Mannschaften sortiert'!E116</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D116" s="96">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
+        <f t="shared" si="7"/>
+        <v>0.125</v>
       </c>
       <c r="E116" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F116)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="G116">
         <f>'Nach Mannschaften sortiert'!H116</f>
-        <v>Heim</v>
-      </c>
-      <c r="H116" t="str">
+        <v>0</v>
+      </c>
+      <c r="H116">
         <f>'Nach Mannschaften sortiert'!G116</f>
-        <v>REAL MADRID CAMP</v>
+        <v>0</v>
       </c>
       <c r="I116" t="str">
         <f>'Nach Mannschaften sortiert'!C116</f>
-        <v>Camp</v>
+        <v>U7</v>
       </c>
       <c r="J116" s="84" t="s">
         <v>68</v>
@@ -9196,14 +9229,14 @@
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117" s="81">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C117" s="96">
         <f>'Nach Mannschaften sortiert'!E117</f>
         <v>0.375</v>
       </c>
       <c r="D117" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E117" s="96" t="str">
@@ -9235,14 +9268,14 @@
     <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B118" s="81">
         <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C118" s="96">
         <f>'Nach Mannschaften sortiert'!E118</f>
         <v>0.375</v>
       </c>
       <c r="D118" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E118" s="96" t="str">
@@ -9274,14 +9307,14 @@
     <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B119" s="81">
         <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C119" s="96">
         <f>'Nach Mannschaften sortiert'!E119</f>
         <v>0.375</v>
       </c>
       <c r="D119" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E119" s="96" t="str">
@@ -9313,14 +9346,14 @@
     <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B120" s="81">
         <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="C120" s="96">
         <f>'Nach Mannschaften sortiert'!E120</f>
         <v>0.375</v>
       </c>
       <c r="D120" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E120" s="96" t="str">
@@ -9352,14 +9385,14 @@
     <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B121" s="81">
         <f>'Nach Mannschaften sortiert'!D121</f>
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="C121" s="96">
         <f>'Nach Mannschaften sortiert'!E121</f>
         <v>0.375</v>
       </c>
       <c r="D121" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E121" s="96" t="str">
@@ -9372,7 +9405,7 @@
       </c>
       <c r="H121" t="str">
         <f>'Nach Mannschaften sortiert'!G121</f>
-        <v>MÄDCHENCAMP</v>
+        <v>REAL MADRID CAMP</v>
       </c>
       <c r="I121" t="str">
         <f>'Nach Mannschaften sortiert'!C121</f>
@@ -9391,14 +9424,14 @@
     <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B122" s="81">
         <f>'Nach Mannschaften sortiert'!D122</f>
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C122" s="96">
         <f>'Nach Mannschaften sortiert'!E122</f>
         <v>0.375</v>
       </c>
       <c r="D122" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E122" s="96" t="str">
@@ -9430,14 +9463,14 @@
     <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B123" s="81">
         <f>'Nach Mannschaften sortiert'!D123</f>
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="C123" s="96">
         <f>'Nach Mannschaften sortiert'!E123</f>
         <v>0.375</v>
       </c>
       <c r="D123" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E123" s="96" t="str">
@@ -9469,14 +9502,14 @@
     <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B124" s="81">
         <f>'Nach Mannschaften sortiert'!D124</f>
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="C124" s="96">
         <f>'Nach Mannschaften sortiert'!E124</f>
         <v>0.375</v>
       </c>
       <c r="D124" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E124" s="96" t="str">
@@ -9489,7 +9522,7 @@
       </c>
       <c r="H124" t="str">
         <f>'Nach Mannschaften sortiert'!G124</f>
-        <v>Teco 7 Camp</v>
+        <v>MÄDCHENCAMP</v>
       </c>
       <c r="I124" t="str">
         <f>'Nach Mannschaften sortiert'!C124</f>
@@ -9508,14 +9541,14 @@
     <row r="125" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B125" s="81">
         <f>'Nach Mannschaften sortiert'!D125</f>
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C125" s="96">
         <f>'Nach Mannschaften sortiert'!E125</f>
         <v>0.375</v>
       </c>
       <c r="D125" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E125" s="96" t="str">
@@ -9547,14 +9580,14 @@
     <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B126" s="81">
         <f>'Nach Mannschaften sortiert'!D126</f>
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C126" s="96">
         <f>'Nach Mannschaften sortiert'!E126</f>
         <v>0.375</v>
       </c>
       <c r="D126" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E126" s="96" t="str">
@@ -9586,14 +9619,14 @@
     <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B127" s="81">
         <f>'Nach Mannschaften sortiert'!D127</f>
-        <v>46256</v>
+        <v>46323</v>
       </c>
       <c r="C127" s="96">
         <f>'Nach Mannschaften sortiert'!E127</f>
         <v>0.375</v>
       </c>
       <c r="D127" s="96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E127" s="96" t="str">
@@ -9606,11 +9639,11 @@
       </c>
       <c r="H127" t="str">
         <f>'Nach Mannschaften sortiert'!G127</f>
-        <v>viele Gegner</v>
+        <v>Teco 7 Camp</v>
       </c>
       <c r="I127" t="str">
         <f>'Nach Mannschaften sortiert'!C127</f>
-        <v>GGG</v>
+        <v>Camp</v>
       </c>
       <c r="J127" s="84" t="s">
         <v>68</v>
@@ -9625,18 +9658,19 @@
     <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B128" s="81">
         <f>'Nach Mannschaften sortiert'!D128</f>
-        <v>46367</v>
+        <v>46256</v>
       </c>
       <c r="C128" s="96">
         <f>'Nach Mannschaften sortiert'!E128</f>
-        <v>0.6875</v>
+        <v>0.375</v>
       </c>
       <c r="D128" s="96">
-        <v>0.875</v>
+        <f t="shared" si="7"/>
+        <v>0.5</v>
       </c>
       <c r="E128" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F128)</f>
-        <v>STEINBRUNN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G128" t="str">
         <f>'Nach Mannschaften sortiert'!H128</f>
@@ -9644,11 +9678,11 @@
       </c>
       <c r="H128" t="str">
         <f>'Nach Mannschaften sortiert'!G128</f>
-        <v>Hallencup 2026_27</v>
+        <v>viele Gegner</v>
       </c>
       <c r="I128" t="str">
         <f>'Nach Mannschaften sortiert'!C128</f>
-        <v>Hallenturnie</v>
+        <v>GGG</v>
       </c>
       <c r="J128" s="84" t="s">
         <v>68</v>
@@ -9663,11 +9697,11 @@
     <row r="129" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B129" s="81">
         <f>'Nach Mannschaften sortiert'!D129</f>
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="C129" s="96">
         <f>'Nach Mannschaften sortiert'!E129</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D129" s="96">
         <v>0.875</v>
@@ -9701,11 +9735,11 @@
     <row r="130" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B130" s="81">
         <f>'Nach Mannschaften sortiert'!D130</f>
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="C130" s="96">
         <f>'Nach Mannschaften sortiert'!E130</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D130" s="96">
         <v>0.875</v>
@@ -9739,11 +9773,11 @@
     <row r="131" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B131" s="81">
         <f>'Nach Mannschaften sortiert'!D131</f>
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="C131" s="96">
         <f>'Nach Mannschaften sortiert'!E131</f>
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D131" s="96">
         <v>0.875</v>
@@ -9752,20 +9786,17 @@
         <f>UPPER('Nach Mannschaften sortiert'!F131)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="F131" s="84" t="s">
-        <v>72</v>
-      </c>
       <c r="G131" t="str">
         <f>'Nach Mannschaften sortiert'!H131</f>
         <v>Heim</v>
       </c>
       <c r="H131" t="str">
         <f>'Nach Mannschaften sortiert'!G131</f>
-        <v>Weihnachtsfeier 2026</v>
+        <v>Hallencup 2026_27</v>
       </c>
       <c r="I131" t="str">
         <f>'Nach Mannschaften sortiert'!C131</f>
-        <v>Weihnachtsfeier</v>
+        <v>Hallenturnie</v>
       </c>
       <c r="J131" s="84" t="s">
         <v>68</v>
@@ -9774,17 +9805,17 @@
         <v>71</v>
       </c>
       <c r="L131" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B132" s="81">
         <f>'Nach Mannschaften sortiert'!D132</f>
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="C132" s="96">
         <f>'Nach Mannschaften sortiert'!E132</f>
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D132" s="96">
         <v>0.875</v>
@@ -9793,17 +9824,20 @@
         <f>UPPER('Nach Mannschaften sortiert'!F132)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F132" s="84" t="s">
+        <v>72</v>
+      </c>
       <c r="G132" t="str">
         <f>'Nach Mannschaften sortiert'!H132</f>
         <v>Heim</v>
       </c>
       <c r="H132" t="str">
         <f>'Nach Mannschaften sortiert'!G132</f>
-        <v>Hallencup 2026_27</v>
+        <v>Weihnachtsfeier 2026</v>
       </c>
       <c r="I132" t="str">
         <f>'Nach Mannschaften sortiert'!C132</f>
-        <v>Hallenturnie</v>
+        <v>Weihnachtsfeier</v>
       </c>
       <c r="J132" s="84" t="s">
         <v>68</v>
@@ -9812,17 +9846,17 @@
         <v>71</v>
       </c>
       <c r="L132" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="133" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B133" s="81">
         <f>'Nach Mannschaften sortiert'!D133</f>
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="C133" s="96">
         <f>'Nach Mannschaften sortiert'!E133</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D133" s="96">
         <v>0.875</v>
@@ -9856,11 +9890,11 @@
     <row r="134" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B134" s="81">
         <f>'Nach Mannschaften sortiert'!D134</f>
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="C134" s="96">
         <f>'Nach Mannschaften sortiert'!E134</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D134" s="96">
         <v>0.875</v>
@@ -9888,6 +9922,44 @@
         <v>71</v>
       </c>
       <c r="L134" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="135" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B135" s="81">
+        <f>'Nach Mannschaften sortiert'!D135</f>
+        <v>46404</v>
+      </c>
+      <c r="C135" s="96">
+        <f>'Nach Mannschaften sortiert'!E135</f>
+        <v>0.375</v>
+      </c>
+      <c r="D135" s="96">
+        <v>0.875</v>
+      </c>
+      <c r="E135" s="96" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F135)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G135" t="str">
+        <f>'Nach Mannschaften sortiert'!H135</f>
+        <v>Heim</v>
+      </c>
+      <c r="H135" t="str">
+        <f>'Nach Mannschaften sortiert'!G135</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I135" t="str">
+        <f>'Nach Mannschaften sortiert'!C135</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J135" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="K135" t="s">
+        <v>71</v>
+      </c>
+      <c r="L135" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10137,16 +10209,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
@@ -10173,7 +10245,7 @@
       <c r="H2" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="118" t="s">
         <v>117</v>
       </c>
       <c r="J2" s="39"/>
@@ -10193,7 +10265,7 @@
       <c r="F3" s="61"/>
       <c r="G3" s="61"/>
       <c r="H3" s="63"/>
-      <c r="I3" s="118"/>
+      <c r="I3" s="119"/>
       <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10213,7 +10285,7 @@
       </c>
       <c r="G4" s="61"/>
       <c r="H4" s="63"/>
-      <c r="I4" s="118"/>
+      <c r="I4" s="119"/>
       <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10233,7 +10305,7 @@
       </c>
       <c r="G5" s="61"/>
       <c r="H5" s="63"/>
-      <c r="I5" s="118"/>
+      <c r="I5" s="119"/>
       <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10253,7 +10325,7 @@
       </c>
       <c r="G6" s="65"/>
       <c r="H6" s="63"/>
-      <c r="I6" s="118"/>
+      <c r="I6" s="119"/>
       <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10275,7 +10347,7 @@
         <v>127</v>
       </c>
       <c r="H7" s="63"/>
-      <c r="I7" s="118"/>
+      <c r="I7" s="119"/>
       <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10297,7 +10369,7 @@
         <v>127</v>
       </c>
       <c r="H8" s="63"/>
-      <c r="I8" s="118"/>
+      <c r="I8" s="119"/>
       <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10321,7 +10393,7 @@
       <c r="H9" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="I9" s="118"/>
+      <c r="I9" s="119"/>
       <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10343,7 +10415,7 @@
         <v>134</v>
       </c>
       <c r="H10" s="63"/>
-      <c r="I10" s="118"/>
+      <c r="I10" s="119"/>
       <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10363,7 +10435,7 @@
         <v>138</v>
       </c>
       <c r="H11" s="72"/>
-      <c r="I11" s="119"/>
+      <c r="I11" s="120"/>
       <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
@@ -10421,52 +10493,52 @@
       <c r="H14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="120" t="s">
+      <c r="A15" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="117"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="121" t="s">
+      <c r="A16" s="122" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="116"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="117"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="124" t="s">
+      <c r="A17" s="125" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="116"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="117"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="114" t="s">
+      <c r="A18" s="115" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="116"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="117"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -10535,783 +10607,783 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="54">
-        <f>'Nach Mannschaften sortiert'!A15</f>
-        <v>14</v>
+        <f>'Nach Mannschaften sortiert'!A16</f>
+        <v>15</v>
       </c>
       <c r="B2" s="54">
-        <f>'Nach Mannschaften sortiert'!B15</f>
+        <f>'Nach Mannschaften sortiert'!B16</f>
         <v>1</v>
       </c>
       <c r="C2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C15</f>
+        <f>'Nach Mannschaften sortiert'!C16</f>
         <v>KM</v>
       </c>
       <c r="D2" s="55">
-        <f>'Nach Mannschaften sortiert'!D15</f>
+        <f>'Nach Mannschaften sortiert'!D16</f>
         <v>46250</v>
       </c>
       <c r="E2" s="97">
-        <f>'Nach Mannschaften sortiert'!E15</f>
+        <f>'Nach Mannschaften sortiert'!E16</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="F2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F15</f>
+        <f>'Nach Mannschaften sortiert'!F16</f>
         <v>Kittsee</v>
       </c>
       <c r="G2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G15</f>
+        <f>'Nach Mannschaften sortiert'!G16</f>
         <v>Kittsee</v>
       </c>
       <c r="H2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H15</f>
+        <f>'Nach Mannschaften sortiert'!H16</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f>'Nach Mannschaften sortiert'!A16</f>
-        <v>15</v>
+        <f>'Nach Mannschaften sortiert'!A17</f>
+        <v>16</v>
       </c>
       <c r="B3" s="54">
-        <f>'Nach Mannschaften sortiert'!B16</f>
+        <f>'Nach Mannschaften sortiert'!B17</f>
         <v>2</v>
       </c>
       <c r="C3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C16</f>
+        <f>'Nach Mannschaften sortiert'!C17</f>
         <v>KM</v>
       </c>
       <c r="D3" s="55">
-        <f>'Nach Mannschaften sortiert'!D16</f>
+        <f>'Nach Mannschaften sortiert'!D17</f>
         <v>46255</v>
       </c>
       <c r="E3" s="97">
-        <f>'Nach Mannschaften sortiert'!E16</f>
+        <f>'Nach Mannschaften sortiert'!E17</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="F3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F16</f>
+        <f>'Nach Mannschaften sortiert'!F17</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="G3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G16</f>
+        <f>'Nach Mannschaften sortiert'!G17</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="H3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H16</f>
+        <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54">
-        <f>'Nach Mannschaften sortiert'!A17</f>
-        <v>16</v>
+        <f>'Nach Mannschaften sortiert'!A18</f>
+        <v>17</v>
       </c>
       <c r="B4" s="54">
-        <f>'Nach Mannschaften sortiert'!B17</f>
+        <f>'Nach Mannschaften sortiert'!B18</f>
         <v>3</v>
       </c>
       <c r="C4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
+        <f>'Nach Mannschaften sortiert'!C18</f>
         <v>KM</v>
       </c>
       <c r="D4" s="55">
-        <f>'Nach Mannschaften sortiert'!D17</f>
+        <f>'Nach Mannschaften sortiert'!D18</f>
         <v>46263</v>
       </c>
       <c r="E4" s="97">
-        <f>'Nach Mannschaften sortiert'!E17</f>
+        <f>'Nach Mannschaften sortiert'!E18</f>
         <v>0.75</v>
       </c>
       <c r="F4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F17</f>
+        <f>'Nach Mannschaften sortiert'!F18</f>
         <v>Neufeld</v>
       </c>
       <c r="G4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G17</f>
+        <f>'Nach Mannschaften sortiert'!G18</f>
         <v>Tadten</v>
       </c>
       <c r="H4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H17</f>
+        <f>'Nach Mannschaften sortiert'!H18</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="54">
-        <f>'Nach Mannschaften sortiert'!A51</f>
-        <v>50</v>
+        <f>'Nach Mannschaften sortiert'!A52</f>
+        <v>51</v>
       </c>
       <c r="B5" s="54">
-        <f>'Nach Mannschaften sortiert'!B51</f>
+        <f>'Nach Mannschaften sortiert'!B52</f>
         <v>1</v>
       </c>
       <c r="C5" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C51</f>
+        <f>'Nach Mannschaften sortiert'!C52</f>
         <v>U14</v>
       </c>
       <c r="D5" s="55">
-        <f>'Nach Mannschaften sortiert'!D51</f>
+        <f>'Nach Mannschaften sortiert'!D52</f>
         <v>46033</v>
       </c>
       <c r="E5" s="97">
-        <f>'Nach Mannschaften sortiert'!E51</f>
+        <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="F5" s="54">
-        <f>'Nach Mannschaften sortiert'!F51</f>
+        <f>'Nach Mannschaften sortiert'!F52</f>
         <v>0</v>
       </c>
       <c r="G5" s="54">
-        <f>'Nach Mannschaften sortiert'!G51</f>
+        <f>'Nach Mannschaften sortiert'!G52</f>
         <v>0</v>
       </c>
       <c r="H5" s="54">
-        <f>'Nach Mannschaften sortiert'!H51</f>
+        <f>'Nach Mannschaften sortiert'!H52</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54">
+        <f>'Nach Mannschaften sortiert'!A20</f>
+        <v>19</v>
+      </c>
+      <c r="B6" s="54">
+        <f>'Nach Mannschaften sortiert'!B20</f>
+        <v>5</v>
+      </c>
+      <c r="C6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C20</f>
+        <v>KM</v>
+      </c>
+      <c r="D6" s="55">
+        <f>'Nach Mannschaften sortiert'!D20</f>
+        <v>46276</v>
+      </c>
+      <c r="E6" s="97">
+        <f>'Nach Mannschaften sortiert'!E20</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F20</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G20</f>
+        <v>Winden</v>
+      </c>
+      <c r="H6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H20</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="54">
+        <f>'Nach Mannschaften sortiert'!A62</f>
+        <v>61</v>
+      </c>
+      <c r="B7" s="54">
+        <f>'Nach Mannschaften sortiert'!B62</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C62</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D7" s="55">
+        <f>'Nach Mannschaften sortiert'!D62</f>
+        <v>46043</v>
+      </c>
+      <c r="E7" s="97">
+        <f>'Nach Mannschaften sortiert'!E62</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="54">
+        <f>'Nach Mannschaften sortiert'!F62</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="54">
+        <f>'Nach Mannschaften sortiert'!G62</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="54">
+        <f>'Nach Mannschaften sortiert'!H62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54">
+        <f>'Nach Mannschaften sortiert'!A22</f>
+        <v>21</v>
+      </c>
+      <c r="B8" s="54">
+        <f>'Nach Mannschaften sortiert'!B22</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C22</f>
+        <v>KM</v>
+      </c>
+      <c r="D8" s="55">
+        <f>'Nach Mannschaften sortiert'!D22</f>
+        <v>46291</v>
+      </c>
+      <c r="E8" s="97">
+        <f>'Nach Mannschaften sortiert'!E22</f>
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F22</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G22</f>
+        <v>Wallern</v>
+      </c>
+      <c r="H8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H22</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="52">
+        <f>'Nach Mannschaften sortiert'!A117</f>
+        <v>116</v>
+      </c>
+      <c r="B9" s="52">
+        <f>'Nach Mannschaften sortiert'!B117</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C117</f>
+        <v>Camp</v>
+      </c>
+      <c r="D9" s="53">
+        <f>'Nach Mannschaften sortiert'!D117</f>
+        <v>46230</v>
+      </c>
+      <c r="E9" s="98">
+        <f>'Nach Mannschaften sortiert'!E117</f>
+        <v>0.375</v>
+      </c>
+      <c r="F9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F117</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G117</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H117</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="54">
+        <f>'Nach Mannschaften sortiert'!A24</f>
+        <v>23</v>
+      </c>
+      <c r="B10" s="54">
+        <f>'Nach Mannschaften sortiert'!B24</f>
+        <v>9</v>
+      </c>
+      <c r="C10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C24</f>
+        <v>KM</v>
+      </c>
+      <c r="D10" s="55">
+        <f>'Nach Mannschaften sortiert'!D24</f>
+        <v>46304</v>
+      </c>
+      <c r="E10" s="97">
+        <f>'Nach Mannschaften sortiert'!E24</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F24</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G24</f>
+        <v>Wimpassing</v>
+      </c>
+      <c r="H10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H24</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="52">
+        <f>'Nach Mannschaften sortiert'!A118</f>
+        <v>117</v>
+      </c>
+      <c r="B11" s="52">
+        <f>'Nach Mannschaften sortiert'!B118</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C118</f>
+        <v>Camp</v>
+      </c>
+      <c r="D11" s="53">
+        <f>'Nach Mannschaften sortiert'!D118</f>
+        <v>46231</v>
+      </c>
+      <c r="E11" s="98">
+        <f>'Nach Mannschaften sortiert'!E118</f>
+        <v>0.375</v>
+      </c>
+      <c r="F11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F118</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G118</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H118</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="54">
+        <f>'Nach Mannschaften sortiert'!A26</f>
+        <v>25</v>
+      </c>
+      <c r="B12" s="54">
+        <f>'Nach Mannschaften sortiert'!B26</f>
+        <v>11</v>
+      </c>
+      <c r="C12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C26</f>
+        <v>KM</v>
+      </c>
+      <c r="D12" s="55">
+        <f>'Nach Mannschaften sortiert'!D26</f>
+        <v>46319</v>
+      </c>
+      <c r="E12" s="97">
+        <f>'Nach Mannschaften sortiert'!E26</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F26</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G26</f>
+        <v>Gols</v>
+      </c>
+      <c r="H12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H26</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <f>'Nach Mannschaften sortiert'!A27</f>
+        <v>26</v>
+      </c>
+      <c r="B13" s="54">
+        <f>'Nach Mannschaften sortiert'!B27</f>
+        <v>12</v>
+      </c>
+      <c r="C13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C27</f>
+        <v>KM</v>
+      </c>
+      <c r="D13" s="55">
+        <f>'Nach Mannschaften sortiert'!D27</f>
+        <v>46326</v>
+      </c>
+      <c r="E13" s="97">
+        <f>'Nach Mannschaften sortiert'!E27</f>
+        <v>0.75</v>
+      </c>
+      <c r="F13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F27</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="G13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G27</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="H13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H27</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="52">
+        <f>'Nach Mannschaften sortiert'!A119</f>
+        <v>118</v>
+      </c>
+      <c r="B14" s="52">
+        <f>'Nach Mannschaften sortiert'!B119</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C119</f>
+        <v>Camp</v>
+      </c>
+      <c r="D14" s="53">
+        <f>'Nach Mannschaften sortiert'!D119</f>
+        <v>46232</v>
+      </c>
+      <c r="E14" s="98">
+        <f>'Nach Mannschaften sortiert'!E119</f>
+        <v>0.375</v>
+      </c>
+      <c r="F14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F119</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G119</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H119</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
+        <f>'Nach Mannschaften sortiert'!A42</f>
+        <v>41</v>
+      </c>
+      <c r="B15" s="54">
+        <f>'Nach Mannschaften sortiert'!B42</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C42</f>
+        <v>U16</v>
+      </c>
+      <c r="D15" s="55">
+        <f>'Nach Mannschaften sortiert'!D42</f>
+        <v>46023</v>
+      </c>
+      <c r="E15" s="97">
+        <f>'Nach Mannschaften sortiert'!E42</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="54">
+        <f>'Nach Mannschaften sortiert'!F42</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="54">
+        <f>'Nach Mannschaften sortiert'!G42</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="54">
+        <f>'Nach Mannschaften sortiert'!H42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="48">
+        <f>'Nach Mannschaften sortiert'!A43</f>
+        <v>42</v>
+      </c>
+      <c r="B16" s="48">
+        <f>'Nach Mannschaften sortiert'!B43</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C43</f>
+        <v>U16</v>
+      </c>
+      <c r="D16" s="49">
+        <f>'Nach Mannschaften sortiert'!D43</f>
+        <v>46024</v>
+      </c>
+      <c r="E16" s="99">
+        <f>'Nach Mannschaften sortiert'!E43</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="48">
+        <f>'Nach Mannschaften sortiert'!F43</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="48">
+        <f>'Nach Mannschaften sortiert'!G43</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="48">
+        <f>'Nach Mannschaften sortiert'!H43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <f>'Nach Mannschaften sortiert'!A44</f>
+        <v>43</v>
+      </c>
+      <c r="B17" s="54">
+        <f>'Nach Mannschaften sortiert'!B44</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C44</f>
+        <v>U16</v>
+      </c>
+      <c r="D17" s="55">
+        <f>'Nach Mannschaften sortiert'!D44</f>
+        <v>46025</v>
+      </c>
+      <c r="E17" s="97">
+        <f>'Nach Mannschaften sortiert'!E44</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="54">
+        <f>'Nach Mannschaften sortiert'!F44</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="54">
+        <f>'Nach Mannschaften sortiert'!G44</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="54">
+        <f>'Nach Mannschaften sortiert'!H44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="54">
         <f>'Nach Mannschaften sortiert'!A19</f>
         <v>18</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B18" s="54">
         <f>'Nach Mannschaften sortiert'!B19</f>
-        <v>5</v>
-      </c>
-      <c r="C6" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
         <v>KM</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D18" s="55">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46276</v>
-      </c>
-      <c r="E6" s="97">
+        <v>46270</v>
+      </c>
+      <c r="E18" s="97">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F6" s="54" t="str">
+        <v>0.6875</v>
+      </c>
+      <c r="F18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F19</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="G18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Winden</v>
-      </c>
-      <c r="H6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="H18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="54">
-        <f>'Nach Mannschaften sortiert'!A61</f>
-        <v>60</v>
-      </c>
-      <c r="B7" s="54">
-        <f>'Nach Mannschaften sortiert'!B61</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C61</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D7" s="55">
-        <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46043</v>
-      </c>
-      <c r="E7" s="97">
-        <f>'Nach Mannschaften sortiert'!E61</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="54">
-        <f>'Nach Mannschaften sortiert'!F61</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="54">
-        <f>'Nach Mannschaften sortiert'!G61</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="54">
-        <f>'Nach Mannschaften sortiert'!H61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54">
-        <f>'Nach Mannschaften sortiert'!A21</f>
-        <v>20</v>
-      </c>
-      <c r="B8" s="54">
-        <f>'Nach Mannschaften sortiert'!B21</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C21</f>
-        <v>KM</v>
-      </c>
-      <c r="D8" s="55">
-        <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46291</v>
-      </c>
-      <c r="E8" s="97">
-        <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.75</v>
-      </c>
-      <c r="F8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F21</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Wallern</v>
-      </c>
-      <c r="H8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="52">
-        <f>'Nach Mannschaften sortiert'!A116</f>
-        <v>115</v>
-      </c>
-      <c r="B9" s="52">
-        <f>'Nach Mannschaften sortiert'!B116</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C116</f>
-        <v>Camp</v>
-      </c>
-      <c r="D9" s="53">
-        <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46230</v>
-      </c>
-      <c r="E9" s="98">
-        <f>'Nach Mannschaften sortiert'!E116</f>
-        <v>0.375</v>
-      </c>
-      <c r="F9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F116</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G116</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H116</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54">
-        <f>'Nach Mannschaften sortiert'!A23</f>
-        <v>22</v>
-      </c>
-      <c r="B10" s="54">
-        <f>'Nach Mannschaften sortiert'!B23</f>
-        <v>9</v>
-      </c>
-      <c r="C10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C23</f>
-        <v>KM</v>
-      </c>
-      <c r="D10" s="55">
-        <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46304</v>
-      </c>
-      <c r="E10" s="97">
-        <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F23</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Wimpassing</v>
-      </c>
-      <c r="H10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="52">
-        <f>'Nach Mannschaften sortiert'!A117</f>
-        <v>116</v>
-      </c>
-      <c r="B11" s="52">
-        <f>'Nach Mannschaften sortiert'!B117</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C117</f>
-        <v>Camp</v>
-      </c>
-      <c r="D11" s="53">
-        <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46231</v>
-      </c>
-      <c r="E11" s="98">
-        <f>'Nach Mannschaften sortiert'!E117</f>
-        <v>0.375</v>
-      </c>
-      <c r="F11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F117</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G117</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H117</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <f>'Nach Mannschaften sortiert'!A25</f>
-        <v>24</v>
-      </c>
-      <c r="B12" s="54">
-        <f>'Nach Mannschaften sortiert'!B25</f>
-        <v>11</v>
-      </c>
-      <c r="C12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C25</f>
-        <v>KM</v>
-      </c>
-      <c r="D12" s="55">
-        <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46319</v>
-      </c>
-      <c r="E12" s="97">
-        <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F25</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Gols</v>
-      </c>
-      <c r="H12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54">
-        <f>'Nach Mannschaften sortiert'!A26</f>
-        <v>25</v>
-      </c>
-      <c r="B13" s="54">
-        <f>'Nach Mannschaften sortiert'!B26</f>
-        <v>12</v>
-      </c>
-      <c r="C13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C26</f>
-        <v>KM</v>
-      </c>
-      <c r="D13" s="55">
-        <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>46326</v>
-      </c>
-      <c r="E13" s="97">
-        <f>'Nach Mannschaften sortiert'!E26</f>
-        <v>0.75</v>
-      </c>
-      <c r="F13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F26</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="G13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="H13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H26</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="52">
-        <f>'Nach Mannschaften sortiert'!A118</f>
-        <v>117</v>
-      </c>
-      <c r="B14" s="52">
-        <f>'Nach Mannschaften sortiert'!B118</f>
-        <v>3</v>
-      </c>
-      <c r="C14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C118</f>
-        <v>Camp</v>
-      </c>
-      <c r="D14" s="53">
-        <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46232</v>
-      </c>
-      <c r="E14" s="98">
-        <f>'Nach Mannschaften sortiert'!E118</f>
-        <v>0.375</v>
-      </c>
-      <c r="F14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F118</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G118</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H118</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54">
-        <f>'Nach Mannschaften sortiert'!A41</f>
-        <v>40</v>
-      </c>
-      <c r="B15" s="54">
-        <f>'Nach Mannschaften sortiert'!B41</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C41</f>
-        <v>U16</v>
-      </c>
-      <c r="D15" s="55">
-        <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46023</v>
-      </c>
-      <c r="E15" s="97">
-        <f>'Nach Mannschaften sortiert'!E41</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="54">
-        <f>'Nach Mannschaften sortiert'!F41</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="54">
-        <f>'Nach Mannschaften sortiert'!G41</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="54">
-        <f>'Nach Mannschaften sortiert'!H41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48">
-        <f>'Nach Mannschaften sortiert'!A42</f>
-        <v>41</v>
-      </c>
-      <c r="B16" s="48">
-        <f>'Nach Mannschaften sortiert'!B42</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C42</f>
-        <v>U16</v>
-      </c>
-      <c r="D16" s="49">
-        <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46024</v>
-      </c>
-      <c r="E16" s="99">
-        <f>'Nach Mannschaften sortiert'!E42</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="48">
-        <f>'Nach Mannschaften sortiert'!F42</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="48">
-        <f>'Nach Mannschaften sortiert'!G42</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="48">
-        <f>'Nach Mannschaften sortiert'!H42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54">
-        <f>'Nach Mannschaften sortiert'!A43</f>
-        <v>42</v>
-      </c>
-      <c r="B17" s="54">
-        <f>'Nach Mannschaften sortiert'!B43</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C43</f>
-        <v>U16</v>
-      </c>
-      <c r="D17" s="55">
-        <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46025</v>
-      </c>
-      <c r="E17" s="97">
-        <f>'Nach Mannschaften sortiert'!E43</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="54">
-        <f>'Nach Mannschaften sortiert'!F43</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="54">
-        <f>'Nach Mannschaften sortiert'!G43</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="54">
-        <f>'Nach Mannschaften sortiert'!H43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="54">
-        <f>'Nach Mannschaften sortiert'!A18</f>
-        <v>17</v>
-      </c>
-      <c r="B18" s="54">
-        <f>'Nach Mannschaften sortiert'!B18</f>
-        <v>4</v>
-      </c>
-      <c r="C18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C18</f>
-        <v>KM</v>
-      </c>
-      <c r="D18" s="55">
-        <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46270</v>
-      </c>
-      <c r="E18" s="97">
-        <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.6875</v>
-      </c>
-      <c r="F18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F18</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="G18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="H18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H18</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54">
-        <f>'Nach Mannschaften sortiert'!A45</f>
-        <v>44</v>
+        <f>'Nach Mannschaften sortiert'!A46</f>
+        <v>45</v>
       </c>
       <c r="B19" s="54">
-        <f>'Nach Mannschaften sortiert'!B45</f>
+        <f>'Nach Mannschaften sortiert'!B46</f>
         <v>5</v>
       </c>
       <c r="C19" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C45</f>
+        <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U16</v>
       </c>
       <c r="D19" s="55">
-        <f>'Nach Mannschaften sortiert'!D45</f>
+        <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46027</v>
       </c>
       <c r="E19" s="97">
-        <f>'Nach Mannschaften sortiert'!E45</f>
+        <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="F19" s="54">
-        <f>'Nach Mannschaften sortiert'!F45</f>
+        <f>'Nach Mannschaften sortiert'!F46</f>
         <v>0</v>
       </c>
       <c r="G19" s="54">
-        <f>'Nach Mannschaften sortiert'!G45</f>
+        <f>'Nach Mannschaften sortiert'!G46</f>
         <v>0</v>
       </c>
       <c r="H19" s="54">
-        <f>'Nach Mannschaften sortiert'!H45</f>
+        <f>'Nach Mannschaften sortiert'!H46</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
-        <f>'Nach Mannschaften sortiert'!A46</f>
-        <v>45</v>
+        <f>'Nach Mannschaften sortiert'!A47</f>
+        <v>46</v>
       </c>
       <c r="B20" s="46">
-        <f>'Nach Mannschaften sortiert'!B46</f>
+        <f>'Nach Mannschaften sortiert'!B47</f>
         <v>6</v>
       </c>
       <c r="C20" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C46</f>
+        <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U16</v>
       </c>
       <c r="D20" s="47">
-        <f>'Nach Mannschaften sortiert'!D46</f>
+        <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46028</v>
       </c>
       <c r="E20" s="100">
-        <f>'Nach Mannschaften sortiert'!E46</f>
+        <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="F20" s="46">
-        <f>'Nach Mannschaften sortiert'!F46</f>
+        <f>'Nach Mannschaften sortiert'!F47</f>
         <v>0</v>
       </c>
       <c r="G20" s="46">
-        <f>'Nach Mannschaften sortiert'!G46</f>
+        <f>'Nach Mannschaften sortiert'!G47</f>
         <v>0</v>
       </c>
       <c r="H20" s="46">
-        <f>'Nach Mannschaften sortiert'!H46</f>
+        <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54">
-        <f>'Nach Mannschaften sortiert'!A47</f>
-        <v>46</v>
+        <f>'Nach Mannschaften sortiert'!A48</f>
+        <v>47</v>
       </c>
       <c r="B21" s="54">
-        <f>'Nach Mannschaften sortiert'!B47</f>
+        <f>'Nach Mannschaften sortiert'!B48</f>
         <v>7</v>
       </c>
       <c r="C21" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C47</f>
+        <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U16</v>
       </c>
       <c r="D21" s="55">
-        <f>'Nach Mannschaften sortiert'!D47</f>
+        <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46029</v>
       </c>
       <c r="E21" s="97">
-        <f>'Nach Mannschaften sortiert'!E47</f>
+        <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="F21" s="54">
-        <f>'Nach Mannschaften sortiert'!F47</f>
+        <f>'Nach Mannschaften sortiert'!F48</f>
         <v>0</v>
       </c>
       <c r="G21" s="54">
-        <f>'Nach Mannschaften sortiert'!G47</f>
+        <f>'Nach Mannschaften sortiert'!G48</f>
         <v>0</v>
       </c>
       <c r="H21" s="54">
-        <f>'Nach Mannschaften sortiert'!H47</f>
+        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
-        <f>'Nach Mannschaften sortiert'!A48</f>
-        <v>47</v>
+        <f>'Nach Mannschaften sortiert'!A49</f>
+        <v>48</v>
       </c>
       <c r="B22" s="48">
-        <f>'Nach Mannschaften sortiert'!B48</f>
+        <f>'Nach Mannschaften sortiert'!B49</f>
         <v>8</v>
       </c>
       <c r="C22" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C48</f>
+        <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U16</v>
       </c>
       <c r="D22" s="49">
-        <f>'Nach Mannschaften sortiert'!D48</f>
+        <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46030</v>
       </c>
       <c r="E22" s="99">
-        <f>'Nach Mannschaften sortiert'!E48</f>
+        <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="F22" s="48">
-        <f>'Nach Mannschaften sortiert'!F48</f>
+        <f>'Nach Mannschaften sortiert'!F49</f>
         <v>0</v>
       </c>
       <c r="G22" s="48">
-        <f>'Nach Mannschaften sortiert'!G48</f>
+        <f>'Nach Mannschaften sortiert'!G49</f>
         <v>0</v>
       </c>
       <c r="H22" s="48">
-        <f>'Nach Mannschaften sortiert'!H48</f>
+        <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54">
-        <f>'Nach Mannschaften sortiert'!A49</f>
-        <v>48</v>
+        <f>'Nach Mannschaften sortiert'!A50</f>
+        <v>49</v>
       </c>
       <c r="B23" s="54">
-        <f>'Nach Mannschaften sortiert'!B49</f>
+        <f>'Nach Mannschaften sortiert'!B50</f>
         <v>9</v>
       </c>
       <c r="C23" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C49</f>
+        <f>'Nach Mannschaften sortiert'!C50</f>
         <v>U16</v>
       </c>
       <c r="D23" s="55">
-        <f>'Nach Mannschaften sortiert'!D49</f>
+        <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46031</v>
       </c>
       <c r="E23" s="97">
-        <f>'Nach Mannschaften sortiert'!E49</f>
+        <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="F23" s="54">
-        <f>'Nach Mannschaften sortiert'!F49</f>
+        <f>'Nach Mannschaften sortiert'!F50</f>
         <v>0</v>
       </c>
       <c r="G23" s="54">
-        <f>'Nach Mannschaften sortiert'!G49</f>
+        <f>'Nach Mannschaften sortiert'!G50</f>
         <v>0</v>
       </c>
       <c r="H23" s="54">
-        <f>'Nach Mannschaften sortiert'!H49</f>
+        <f>'Nach Mannschaften sortiert'!H50</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
-        <f>'Nach Mannschaften sortiert'!A96</f>
-        <v>95</v>
+        <f>'Nach Mannschaften sortiert'!A97</f>
+        <v>96</v>
       </c>
       <c r="B24" s="50">
-        <f>'Nach Mannschaften sortiert'!B96</f>
+        <f>'Nach Mannschaften sortiert'!B97</f>
         <v>1</v>
       </c>
       <c r="C24" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C96</f>
+        <f>'Nach Mannschaften sortiert'!C97</f>
         <v>U9</v>
       </c>
       <c r="D24" s="51">
-        <f>'Nach Mannschaften sortiert'!D96</f>
+        <f>'Nach Mannschaften sortiert'!D97</f>
         <v>46078</v>
       </c>
       <c r="E24" s="101">
-        <f>'Nach Mannschaften sortiert'!E96</f>
+        <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="F24" s="50">
-        <f>'Nach Mannschaften sortiert'!F96</f>
+        <f>'Nach Mannschaften sortiert'!F97</f>
         <v>0</v>
       </c>
       <c r="G24" s="50">
-        <f>'Nach Mannschaften sortiert'!G96</f>
+        <f>'Nach Mannschaften sortiert'!G97</f>
         <v>0</v>
       </c>
       <c r="H24" s="50">
-        <f>'Nach Mannschaften sortiert'!H96</f>
+        <f>'Nach Mannschaften sortiert'!H97</f>
         <v>0</v>
       </c>
     </row>
@@ -11351,35 +11423,35 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
-        <f>'Nach Mannschaften sortiert'!A106</f>
-        <v>105</v>
+        <f>'Nach Mannschaften sortiert'!A107</f>
+        <v>106</v>
       </c>
       <c r="B26" s="50">
-        <f>'Nach Mannschaften sortiert'!B106</f>
+        <f>'Nach Mannschaften sortiert'!B107</f>
         <v>1</v>
       </c>
       <c r="C26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C106</f>
+        <f>'Nach Mannschaften sortiert'!C107</f>
         <v>U8</v>
       </c>
       <c r="D26" s="51">
-        <f>'Nach Mannschaften sortiert'!D106</f>
+        <f>'Nach Mannschaften sortiert'!D107</f>
         <v>46312</v>
       </c>
       <c r="E26" s="101">
-        <f>'Nach Mannschaften sortiert'!E106</f>
+        <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0.39583333333333331</v>
       </c>
       <c r="F26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!F106</f>
+        <f>'Nach Mannschaften sortiert'!F107</f>
         <v>Neufeld</v>
       </c>
       <c r="G26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!G106</f>
+        <f>'Nach Mannschaften sortiert'!G107</f>
         <v>Heimturnier</v>
       </c>
       <c r="H26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!H106</f>
+        <f>'Nach Mannschaften sortiert'!H107</f>
         <v>Heim</v>
       </c>
     </row>
@@ -11453,35 +11525,35 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="50">
-        <f>'Nach Mannschaften sortiert'!A111</f>
-        <v>110</v>
+        <f>'Nach Mannschaften sortiert'!A112</f>
+        <v>111</v>
       </c>
       <c r="B29" s="50">
-        <f>'Nach Mannschaften sortiert'!B111</f>
+        <f>'Nach Mannschaften sortiert'!B112</f>
         <v>1</v>
       </c>
       <c r="C29" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C111</f>
+        <f>'Nach Mannschaften sortiert'!C112</f>
         <v>U7</v>
       </c>
       <c r="D29" s="51">
-        <f>'Nach Mannschaften sortiert'!D111</f>
+        <f>'Nach Mannschaften sortiert'!D112</f>
         <v>46312</v>
       </c>
       <c r="E29" s="101">
-        <f>'Nach Mannschaften sortiert'!E111</f>
+        <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="F29" s="50">
-        <f>'Nach Mannschaften sortiert'!F111</f>
+        <f>'Nach Mannschaften sortiert'!F112</f>
         <v>0</v>
       </c>
       <c r="G29" s="50">
-        <f>'Nach Mannschaften sortiert'!G111</f>
+        <f>'Nach Mannschaften sortiert'!G112</f>
         <v>0</v>
       </c>
       <c r="H29" s="50">
-        <f>'Nach Mannschaften sortiert'!H111</f>
+        <f>'Nach Mannschaften sortiert'!H112</f>
         <v>0</v>
       </c>
     </row>
@@ -11657,103 +11729,103 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="50">
-        <f>'Nach Mannschaften sortiert'!A82</f>
-        <v>81</v>
+        <f>'Nach Mannschaften sortiert'!A83</f>
+        <v>82</v>
       </c>
       <c r="B35" s="50">
-        <f>'Nach Mannschaften sortiert'!B82</f>
+        <f>'Nach Mannschaften sortiert'!B83</f>
         <v>2</v>
       </c>
       <c r="C35" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C82</f>
+        <f>'Nach Mannschaften sortiert'!C83</f>
         <v>U11</v>
       </c>
       <c r="D35" s="51">
-        <f>'Nach Mannschaften sortiert'!D82</f>
+        <f>'Nach Mannschaften sortiert'!D83</f>
         <v>46064</v>
       </c>
       <c r="E35" s="101">
-        <f>'Nach Mannschaften sortiert'!E82</f>
+        <f>'Nach Mannschaften sortiert'!E83</f>
         <v>0</v>
       </c>
       <c r="F35" s="50">
-        <f>'Nach Mannschaften sortiert'!F82</f>
+        <f>'Nach Mannschaften sortiert'!F83</f>
         <v>0</v>
       </c>
       <c r="G35" s="50">
-        <f>'Nach Mannschaften sortiert'!G82</f>
+        <f>'Nach Mannschaften sortiert'!G83</f>
         <v>0</v>
       </c>
       <c r="H35" s="50">
-        <f>'Nach Mannschaften sortiert'!H82</f>
+        <f>'Nach Mannschaften sortiert'!H83</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="54">
-        <f>'Nach Mannschaften sortiert'!A52</f>
-        <v>51</v>
+        <f>'Nach Mannschaften sortiert'!A53</f>
+        <v>52</v>
       </c>
       <c r="B36" s="54">
-        <f>'Nach Mannschaften sortiert'!B52</f>
+        <f>'Nach Mannschaften sortiert'!B53</f>
         <v>2</v>
       </c>
       <c r="C36" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C52</f>
+        <f>'Nach Mannschaften sortiert'!C53</f>
         <v>U14</v>
       </c>
       <c r="D36" s="55">
-        <f>'Nach Mannschaften sortiert'!D52</f>
+        <f>'Nach Mannschaften sortiert'!D53</f>
         <v>46034</v>
       </c>
       <c r="E36" s="97">
-        <f>'Nach Mannschaften sortiert'!E52</f>
+        <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="F36" s="54">
-        <f>'Nach Mannschaften sortiert'!F52</f>
+        <f>'Nach Mannschaften sortiert'!F53</f>
         <v>0</v>
       </c>
       <c r="G36" s="54">
-        <f>'Nach Mannschaften sortiert'!G52</f>
+        <f>'Nach Mannschaften sortiert'!G53</f>
         <v>0</v>
       </c>
       <c r="H36" s="54">
-        <f>'Nach Mannschaften sortiert'!H52</f>
+        <f>'Nach Mannschaften sortiert'!H53</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="54">
-        <f>'Nach Mannschaften sortiert'!A53</f>
-        <v>52</v>
+        <f>'Nach Mannschaften sortiert'!A54</f>
+        <v>53</v>
       </c>
       <c r="B37" s="54">
-        <f>'Nach Mannschaften sortiert'!B53</f>
+        <f>'Nach Mannschaften sortiert'!B54</f>
         <v>3</v>
       </c>
       <c r="C37" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C53</f>
+        <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U14</v>
       </c>
       <c r="D37" s="55">
-        <f>'Nach Mannschaften sortiert'!D53</f>
+        <f>'Nach Mannschaften sortiert'!D54</f>
         <v>46035</v>
       </c>
       <c r="E37" s="97">
-        <f>'Nach Mannschaften sortiert'!E53</f>
+        <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="F37" s="54">
-        <f>'Nach Mannschaften sortiert'!F53</f>
+        <f>'Nach Mannschaften sortiert'!F54</f>
         <v>0</v>
       </c>
       <c r="G37" s="54">
-        <f>'Nach Mannschaften sortiert'!G53</f>
+        <f>'Nach Mannschaften sortiert'!G54</f>
         <v>0</v>
       </c>
       <c r="H37" s="54">
-        <f>'Nach Mannschaften sortiert'!H53</f>
+        <f>'Nach Mannschaften sortiert'!H54</f>
         <v>0</v>
       </c>
     </row>
@@ -11827,205 +11899,205 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54">
+        <f>'Nach Mannschaften sortiert'!A56</f>
+        <v>55</v>
+      </c>
+      <c r="B40" s="54">
+        <f>'Nach Mannschaften sortiert'!B56</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C56</f>
+        <v>U14</v>
+      </c>
+      <c r="D40" s="55">
+        <f>'Nach Mannschaften sortiert'!D56</f>
+        <v>46037</v>
+      </c>
+      <c r="E40" s="97">
+        <f>'Nach Mannschaften sortiert'!E56</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="54">
+        <f>'Nach Mannschaften sortiert'!F56</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="54">
+        <f>'Nach Mannschaften sortiert'!G56</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="54">
+        <f>'Nach Mannschaften sortiert'!H56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="48">
+        <f>'Nach Mannschaften sortiert'!A21</f>
+        <v>20</v>
+      </c>
+      <c r="B41" s="48">
+        <f>'Nach Mannschaften sortiert'!B21</f>
+        <v>6</v>
+      </c>
+      <c r="C41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C21</f>
+        <v>KM</v>
+      </c>
+      <c r="D41" s="49">
+        <f>'Nach Mannschaften sortiert'!D21</f>
+        <v>46284</v>
+      </c>
+      <c r="E41" s="99">
+        <f>'Nach Mannschaften sortiert'!E21</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!F21</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="G41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!G21</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="H41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!H21</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="54">
+        <f>'Nach Mannschaften sortiert'!A87</f>
+        <v>86</v>
+      </c>
+      <c r="B42" s="54">
+        <f>'Nach Mannschaften sortiert'!B87</f>
+        <v>6</v>
+      </c>
+      <c r="C42" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C87</f>
+        <v>U11</v>
+      </c>
+      <c r="D42" s="55">
+        <f>'Nach Mannschaften sortiert'!D87</f>
+        <v>46068</v>
+      </c>
+      <c r="E42" s="97">
+        <f>'Nach Mannschaften sortiert'!E87</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="54">
+        <f>'Nach Mannschaften sortiert'!F87</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="54">
+        <f>'Nach Mannschaften sortiert'!G87</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="54">
+        <f>'Nach Mannschaften sortiert'!H87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="54">
+        <f>'Nach Mannschaften sortiert'!A61</f>
+        <v>60</v>
+      </c>
+      <c r="B43" s="54">
+        <f>'Nach Mannschaften sortiert'!B61</f>
+        <v>10</v>
+      </c>
+      <c r="C43" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C61</f>
+        <v>U14</v>
+      </c>
+      <c r="D43" s="55">
+        <f>'Nach Mannschaften sortiert'!D61</f>
+        <v>46042</v>
+      </c>
+      <c r="E43" s="97">
+        <f>'Nach Mannschaften sortiert'!E61</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="54">
+        <f>'Nach Mannschaften sortiert'!F61</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="54">
+        <f>'Nach Mannschaften sortiert'!G61</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="54">
+        <f>'Nach Mannschaften sortiert'!H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="50">
+        <f>'Nach Mannschaften sortiert'!A64</f>
+        <v>63</v>
+      </c>
+      <c r="B44" s="50">
+        <f>'Nach Mannschaften sortiert'!B64</f>
+        <v>3</v>
+      </c>
+      <c r="C44" s="50" t="str">
+        <f>'Nach Mannschaften sortiert'!C64</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D44" s="51">
+        <f>'Nach Mannschaften sortiert'!D64</f>
+        <v>46045</v>
+      </c>
+      <c r="E44" s="101">
+        <f>'Nach Mannschaften sortiert'!E64</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="50">
+        <f>'Nach Mannschaften sortiert'!F64</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="50">
+        <f>'Nach Mannschaften sortiert'!G64</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="50">
+        <f>'Nach Mannschaften sortiert'!H64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="50">
         <f>'Nach Mannschaften sortiert'!A55</f>
         <v>54</v>
       </c>
-      <c r="B40" s="54">
+      <c r="B45" s="50">
         <f>'Nach Mannschaften sortiert'!B55</f>
-        <v>5</v>
-      </c>
-      <c r="C40" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C45" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!C55</f>
         <v>U14</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D45" s="51">
         <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46037</v>
-      </c>
-      <c r="E40" s="97">
+        <v>46036</v>
+      </c>
+      <c r="E45" s="101">
         <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
-      <c r="F40" s="54">
+      <c r="F45" s="50">
         <f>'Nach Mannschaften sortiert'!F55</f>
         <v>0</v>
       </c>
-      <c r="G40" s="54">
+      <c r="G45" s="50">
         <f>'Nach Mannschaften sortiert'!G55</f>
         <v>0</v>
       </c>
-      <c r="H40" s="54">
+      <c r="H45" s="50">
         <f>'Nach Mannschaften sortiert'!H55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="48">
-        <f>'Nach Mannschaften sortiert'!A20</f>
-        <v>19</v>
-      </c>
-      <c r="B41" s="48">
-        <f>'Nach Mannschaften sortiert'!B20</f>
-        <v>6</v>
-      </c>
-      <c r="C41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C20</f>
-        <v>KM</v>
-      </c>
-      <c r="D41" s="49">
-        <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46284</v>
-      </c>
-      <c r="E41" s="99">
-        <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F20</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="G41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="H41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="54">
-        <f>'Nach Mannschaften sortiert'!A86</f>
-        <v>85</v>
-      </c>
-      <c r="B42" s="54">
-        <f>'Nach Mannschaften sortiert'!B86</f>
-        <v>6</v>
-      </c>
-      <c r="C42" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C86</f>
-        <v>U11</v>
-      </c>
-      <c r="D42" s="55">
-        <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46068</v>
-      </c>
-      <c r="E42" s="97">
-        <f>'Nach Mannschaften sortiert'!E86</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="54">
-        <f>'Nach Mannschaften sortiert'!F86</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="54">
-        <f>'Nach Mannschaften sortiert'!G86</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="54">
-        <f>'Nach Mannschaften sortiert'!H86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="54">
-        <f>'Nach Mannschaften sortiert'!A60</f>
-        <v>59</v>
-      </c>
-      <c r="B43" s="54">
-        <f>'Nach Mannschaften sortiert'!B60</f>
-        <v>10</v>
-      </c>
-      <c r="C43" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C60</f>
-        <v>U14</v>
-      </c>
-      <c r="D43" s="55">
-        <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46042</v>
-      </c>
-      <c r="E43" s="97">
-        <f>'Nach Mannschaften sortiert'!E60</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="54">
-        <f>'Nach Mannschaften sortiert'!F60</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="54">
-        <f>'Nach Mannschaften sortiert'!G60</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="54">
-        <f>'Nach Mannschaften sortiert'!H60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="50">
-        <f>'Nach Mannschaften sortiert'!A63</f>
-        <v>62</v>
-      </c>
-      <c r="B44" s="50">
-        <f>'Nach Mannschaften sortiert'!B63</f>
-        <v>3</v>
-      </c>
-      <c r="C44" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C63</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D44" s="51">
-        <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46045</v>
-      </c>
-      <c r="E44" s="101">
-        <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="50">
-        <f>'Nach Mannschaften sortiert'!F63</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="50">
-        <f>'Nach Mannschaften sortiert'!G63</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="50">
-        <f>'Nach Mannschaften sortiert'!H63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="50">
-        <f>'Nach Mannschaften sortiert'!A54</f>
-        <v>53</v>
-      </c>
-      <c r="B45" s="50">
-        <f>'Nach Mannschaften sortiert'!B54</f>
-        <v>4</v>
-      </c>
-      <c r="C45" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C54</f>
-        <v>U14</v>
-      </c>
-      <c r="D45" s="51">
-        <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46036</v>
-      </c>
-      <c r="E45" s="101">
-        <f>'Nach Mannschaften sortiert'!E54</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="50">
-        <f>'Nach Mannschaften sortiert'!F54</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="50">
-        <f>'Nach Mannschaften sortiert'!G54</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="50">
-        <f>'Nach Mannschaften sortiert'!H54</f>
         <v>0</v>
       </c>
     </row>
@@ -12065,137 +12137,137 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54">
-        <f>'Nach Mannschaften sortiert'!A62</f>
-        <v>61</v>
+        <f>'Nach Mannschaften sortiert'!A63</f>
+        <v>62</v>
       </c>
       <c r="B47" s="54">
-        <f>'Nach Mannschaften sortiert'!B62</f>
+        <f>'Nach Mannschaften sortiert'!B63</f>
         <v>2</v>
       </c>
       <c r="C47" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C62</f>
+        <f>'Nach Mannschaften sortiert'!C63</f>
         <v>U12_1</v>
       </c>
       <c r="D47" s="55">
-        <f>'Nach Mannschaften sortiert'!D62</f>
+        <f>'Nach Mannschaften sortiert'!D63</f>
         <v>46044</v>
       </c>
       <c r="E47" s="97">
-        <f>'Nach Mannschaften sortiert'!E62</f>
+        <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="F47" s="54">
-        <f>'Nach Mannschaften sortiert'!F62</f>
+        <f>'Nach Mannschaften sortiert'!F63</f>
         <v>0</v>
       </c>
       <c r="G47" s="54">
-        <f>'Nach Mannschaften sortiert'!G62</f>
+        <f>'Nach Mannschaften sortiert'!G63</f>
         <v>0</v>
       </c>
       <c r="H47" s="54">
-        <f>'Nach Mannschaften sortiert'!H62</f>
+        <f>'Nach Mannschaften sortiert'!H63</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="48">
-        <f>'Nach Mannschaften sortiert'!A44</f>
-        <v>43</v>
+        <f>'Nach Mannschaften sortiert'!A45</f>
+        <v>44</v>
       </c>
       <c r="B48" s="48">
-        <f>'Nach Mannschaften sortiert'!B44</f>
+        <f>'Nach Mannschaften sortiert'!B45</f>
         <v>4</v>
       </c>
       <c r="C48" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C44</f>
+        <f>'Nach Mannschaften sortiert'!C45</f>
         <v>U16</v>
       </c>
       <c r="D48" s="49">
-        <f>'Nach Mannschaften sortiert'!D44</f>
+        <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46026</v>
       </c>
       <c r="E48" s="99">
-        <f>'Nach Mannschaften sortiert'!E44</f>
+        <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="F48" s="48">
-        <f>'Nach Mannschaften sortiert'!F44</f>
+        <f>'Nach Mannschaften sortiert'!F45</f>
         <v>0</v>
       </c>
       <c r="G48" s="48">
-        <f>'Nach Mannschaften sortiert'!G44</f>
+        <f>'Nach Mannschaften sortiert'!G45</f>
         <v>0</v>
       </c>
       <c r="H48" s="48">
-        <f>'Nach Mannschaften sortiert'!H44</f>
+        <f>'Nach Mannschaften sortiert'!H45</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="54">
-        <f>'Nach Mannschaften sortiert'!A64</f>
-        <v>63</v>
+        <f>'Nach Mannschaften sortiert'!A65</f>
+        <v>64</v>
       </c>
       <c r="B49" s="54">
-        <f>'Nach Mannschaften sortiert'!B64</f>
+        <f>'Nach Mannschaften sortiert'!B65</f>
         <v>4</v>
       </c>
       <c r="C49" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C64</f>
+        <f>'Nach Mannschaften sortiert'!C65</f>
         <v>U12_1</v>
       </c>
       <c r="D49" s="55">
-        <f>'Nach Mannschaften sortiert'!D64</f>
+        <f>'Nach Mannschaften sortiert'!D65</f>
         <v>46046</v>
       </c>
       <c r="E49" s="97">
-        <f>'Nach Mannschaften sortiert'!E64</f>
+        <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="F49" s="54">
-        <f>'Nach Mannschaften sortiert'!F64</f>
+        <f>'Nach Mannschaften sortiert'!F65</f>
         <v>0</v>
       </c>
       <c r="G49" s="54">
-        <f>'Nach Mannschaften sortiert'!G64</f>
+        <f>'Nach Mannschaften sortiert'!G65</f>
         <v>0</v>
       </c>
       <c r="H49" s="54">
-        <f>'Nach Mannschaften sortiert'!H64</f>
+        <f>'Nach Mannschaften sortiert'!H65</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="54">
-        <f>'Nach Mannschaften sortiert'!A65</f>
-        <v>64</v>
+        <f>'Nach Mannschaften sortiert'!A66</f>
+        <v>65</v>
       </c>
       <c r="B50" s="54">
-        <f>'Nach Mannschaften sortiert'!B65</f>
+        <f>'Nach Mannschaften sortiert'!B66</f>
         <v>5</v>
       </c>
       <c r="C50" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C65</f>
+        <f>'Nach Mannschaften sortiert'!C66</f>
         <v>U12_1</v>
       </c>
       <c r="D50" s="55">
-        <f>'Nach Mannschaften sortiert'!D65</f>
+        <f>'Nach Mannschaften sortiert'!D66</f>
         <v>46047</v>
       </c>
       <c r="E50" s="97">
-        <f>'Nach Mannschaften sortiert'!E65</f>
+        <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="F50" s="54">
-        <f>'Nach Mannschaften sortiert'!F65</f>
+        <f>'Nach Mannschaften sortiert'!F66</f>
         <v>0</v>
       </c>
       <c r="G50" s="54">
-        <f>'Nach Mannschaften sortiert'!G65</f>
+        <f>'Nach Mannschaften sortiert'!G66</f>
         <v>0</v>
       </c>
       <c r="H50" s="54">
-        <f>'Nach Mannschaften sortiert'!H65</f>
+        <f>'Nach Mannschaften sortiert'!H66</f>
         <v>0</v>
       </c>
     </row>
@@ -12235,69 +12307,69 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="48">
-        <f>'Nach Mannschaften sortiert'!A22</f>
-        <v>21</v>
+        <f>'Nach Mannschaften sortiert'!A23</f>
+        <v>22</v>
       </c>
       <c r="B52" s="48">
-        <f>'Nach Mannschaften sortiert'!B22</f>
+        <f>'Nach Mannschaften sortiert'!B23</f>
         <v>8</v>
       </c>
       <c r="C52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C22</f>
+        <f>'Nach Mannschaften sortiert'!C23</f>
         <v>KM</v>
       </c>
       <c r="D52" s="49">
-        <f>'Nach Mannschaften sortiert'!D22</f>
+        <f>'Nach Mannschaften sortiert'!D23</f>
         <v>46297</v>
       </c>
       <c r="E52" s="99">
-        <f>'Nach Mannschaften sortiert'!E22</f>
+        <f>'Nach Mannschaften sortiert'!E23</f>
         <v>0.79166666666666663</v>
       </c>
       <c r="F52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F22</f>
+        <f>'Nach Mannschaften sortiert'!F23</f>
         <v>Siegendorf</v>
       </c>
       <c r="G52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G22</f>
+        <f>'Nach Mannschaften sortiert'!G23</f>
         <v>Siegendorf</v>
       </c>
       <c r="H52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H22</f>
+        <f>'Nach Mannschaften sortiert'!H23</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="54">
-        <f>'Nach Mannschaften sortiert'!A67</f>
-        <v>66</v>
+        <f>'Nach Mannschaften sortiert'!A68</f>
+        <v>67</v>
       </c>
       <c r="B53" s="54">
-        <f>'Nach Mannschaften sortiert'!B67</f>
+        <f>'Nach Mannschaften sortiert'!B68</f>
         <v>7</v>
       </c>
       <c r="C53" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C67</f>
+        <f>'Nach Mannschaften sortiert'!C68</f>
         <v>U12_1</v>
       </c>
       <c r="D53" s="55">
-        <f>'Nach Mannschaften sortiert'!D67</f>
+        <f>'Nach Mannschaften sortiert'!D68</f>
         <v>46049</v>
       </c>
       <c r="E53" s="97">
-        <f>'Nach Mannschaften sortiert'!E67</f>
+        <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="F53" s="54">
-        <f>'Nach Mannschaften sortiert'!F67</f>
+        <f>'Nach Mannschaften sortiert'!F68</f>
         <v>0</v>
       </c>
       <c r="G53" s="54">
-        <f>'Nach Mannschaften sortiert'!G67</f>
+        <f>'Nach Mannschaften sortiert'!G68</f>
         <v>0</v>
       </c>
       <c r="H53" s="54">
-        <f>'Nach Mannschaften sortiert'!H67</f>
+        <f>'Nach Mannschaften sortiert'!H68</f>
         <v>0</v>
       </c>
     </row>
@@ -12337,137 +12409,137 @@
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="54">
-        <f>'Nach Mannschaften sortiert'!A81</f>
-        <v>80</v>
+        <f>'Nach Mannschaften sortiert'!A82</f>
+        <v>81</v>
       </c>
       <c r="B55" s="54">
-        <f>'Nach Mannschaften sortiert'!B81</f>
+        <f>'Nach Mannschaften sortiert'!B82</f>
         <v>1</v>
       </c>
       <c r="C55" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C81</f>
+        <f>'Nach Mannschaften sortiert'!C82</f>
         <v>U11</v>
       </c>
       <c r="D55" s="55">
-        <f>'Nach Mannschaften sortiert'!D81</f>
+        <f>'Nach Mannschaften sortiert'!D82</f>
         <v>46063</v>
       </c>
       <c r="E55" s="97">
-        <f>'Nach Mannschaften sortiert'!E81</f>
+        <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="F55" s="54">
-        <f>'Nach Mannschaften sortiert'!F81</f>
+        <f>'Nach Mannschaften sortiert'!F82</f>
         <v>0</v>
       </c>
       <c r="G55" s="54">
-        <f>'Nach Mannschaften sortiert'!G81</f>
+        <f>'Nach Mannschaften sortiert'!G82</f>
         <v>0</v>
       </c>
       <c r="H55" s="54">
-        <f>'Nach Mannschaften sortiert'!H81</f>
+        <f>'Nach Mannschaften sortiert'!H82</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="48">
-        <f>'Nach Mannschaften sortiert'!A87</f>
-        <v>86</v>
+        <f>'Nach Mannschaften sortiert'!A88</f>
+        <v>87</v>
       </c>
       <c r="B56" s="48">
-        <f>'Nach Mannschaften sortiert'!B87</f>
+        <f>'Nach Mannschaften sortiert'!B88</f>
         <v>7</v>
       </c>
       <c r="C56" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C87</f>
+        <f>'Nach Mannschaften sortiert'!C88</f>
         <v>U11</v>
       </c>
       <c r="D56" s="49">
-        <f>'Nach Mannschaften sortiert'!D87</f>
+        <f>'Nach Mannschaften sortiert'!D88</f>
         <v>46069</v>
       </c>
       <c r="E56" s="99">
-        <f>'Nach Mannschaften sortiert'!E87</f>
+        <f>'Nach Mannschaften sortiert'!E88</f>
         <v>0</v>
       </c>
       <c r="F56" s="48">
-        <f>'Nach Mannschaften sortiert'!F87</f>
+        <f>'Nach Mannschaften sortiert'!F88</f>
         <v>0</v>
       </c>
       <c r="G56" s="48">
-        <f>'Nach Mannschaften sortiert'!G87</f>
+        <f>'Nach Mannschaften sortiert'!G88</f>
         <v>0</v>
       </c>
       <c r="H56" s="48">
-        <f>'Nach Mannschaften sortiert'!H87</f>
+        <f>'Nach Mannschaften sortiert'!H88</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="54">
-        <f>'Nach Mannschaften sortiert'!A84</f>
-        <v>83</v>
+        <f>'Nach Mannschaften sortiert'!A85</f>
+        <v>84</v>
       </c>
       <c r="B57" s="54">
-        <f>'Nach Mannschaften sortiert'!B84</f>
+        <f>'Nach Mannschaften sortiert'!B85</f>
         <v>4</v>
       </c>
       <c r="C57" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C84</f>
+        <f>'Nach Mannschaften sortiert'!C85</f>
         <v>U11</v>
       </c>
       <c r="D57" s="55">
-        <f>'Nach Mannschaften sortiert'!D84</f>
+        <f>'Nach Mannschaften sortiert'!D85</f>
         <v>46066</v>
       </c>
       <c r="E57" s="97">
-        <f>'Nach Mannschaften sortiert'!E84</f>
+        <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="F57" s="54">
-        <f>'Nach Mannschaften sortiert'!F84</f>
+        <f>'Nach Mannschaften sortiert'!F85</f>
         <v>0</v>
       </c>
       <c r="G57" s="54">
-        <f>'Nach Mannschaften sortiert'!G84</f>
+        <f>'Nach Mannschaften sortiert'!G85</f>
         <v>0</v>
       </c>
       <c r="H57" s="54">
-        <f>'Nach Mannschaften sortiert'!H84</f>
+        <f>'Nach Mannschaften sortiert'!H85</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="48">
-        <f>'Nach Mannschaften sortiert'!A24</f>
-        <v>23</v>
+        <f>'Nach Mannschaften sortiert'!A25</f>
+        <v>24</v>
       </c>
       <c r="B58" s="48">
-        <f>'Nach Mannschaften sortiert'!B24</f>
+        <f>'Nach Mannschaften sortiert'!B25</f>
         <v>10</v>
       </c>
       <c r="C58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C24</f>
+        <f>'Nach Mannschaften sortiert'!C25</f>
         <v>KM</v>
       </c>
       <c r="D58" s="49">
-        <f>'Nach Mannschaften sortiert'!D24</f>
+        <f>'Nach Mannschaften sortiert'!D25</f>
         <v>46311</v>
       </c>
       <c r="E58" s="99">
-        <f>'Nach Mannschaften sortiert'!E24</f>
+        <f>'Nach Mannschaften sortiert'!E25</f>
         <v>0.8125</v>
       </c>
       <c r="F58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F24</f>
+        <f>'Nach Mannschaften sortiert'!F25</f>
         <v>Hornstein</v>
       </c>
       <c r="G58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G24</f>
+        <f>'Nach Mannschaften sortiert'!G25</f>
         <v>Hornstein</v>
       </c>
       <c r="H58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H24</f>
+        <f>'Nach Mannschaften sortiert'!H25</f>
         <v>Auswärts</v>
       </c>
     </row>
@@ -12507,137 +12579,137 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="48">
-        <f>'Nach Mannschaften sortiert'!A58</f>
-        <v>57</v>
+        <f>'Nach Mannschaften sortiert'!A59</f>
+        <v>58</v>
       </c>
       <c r="B60" s="48">
-        <f>'Nach Mannschaften sortiert'!B58</f>
+        <f>'Nach Mannschaften sortiert'!B59</f>
         <v>8</v>
       </c>
       <c r="C60" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C58</f>
+        <f>'Nach Mannschaften sortiert'!C59</f>
         <v>U14</v>
       </c>
       <c r="D60" s="49">
-        <f>'Nach Mannschaften sortiert'!D58</f>
+        <f>'Nach Mannschaften sortiert'!D59</f>
         <v>46040</v>
       </c>
       <c r="E60" s="99">
-        <f>'Nach Mannschaften sortiert'!E58</f>
+        <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="F60" s="48">
-        <f>'Nach Mannschaften sortiert'!F58</f>
+        <f>'Nach Mannschaften sortiert'!F59</f>
         <v>0</v>
       </c>
       <c r="G60" s="48">
-        <f>'Nach Mannschaften sortiert'!G58</f>
+        <f>'Nach Mannschaften sortiert'!G59</f>
         <v>0</v>
       </c>
       <c r="H60" s="48">
-        <f>'Nach Mannschaften sortiert'!H58</f>
+        <f>'Nach Mannschaften sortiert'!H59</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="54">
-        <f>'Nach Mannschaften sortiert'!A88</f>
-        <v>87</v>
+        <f>'Nach Mannschaften sortiert'!A89</f>
+        <v>88</v>
       </c>
       <c r="B61" s="54">
-        <f>'Nach Mannschaften sortiert'!B88</f>
+        <f>'Nach Mannschaften sortiert'!B89</f>
         <v>8</v>
       </c>
       <c r="C61" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C88</f>
+        <f>'Nach Mannschaften sortiert'!C89</f>
         <v>U11</v>
       </c>
       <c r="D61" s="55">
-        <f>'Nach Mannschaften sortiert'!D88</f>
+        <f>'Nach Mannschaften sortiert'!D89</f>
         <v>46070</v>
       </c>
       <c r="E61" s="97">
-        <f>'Nach Mannschaften sortiert'!E88</f>
+        <f>'Nach Mannschaften sortiert'!E89</f>
         <v>0</v>
       </c>
       <c r="F61" s="54">
-        <f>'Nach Mannschaften sortiert'!F88</f>
+        <f>'Nach Mannschaften sortiert'!F89</f>
         <v>0</v>
       </c>
       <c r="G61" s="54">
-        <f>'Nach Mannschaften sortiert'!G88</f>
+        <f>'Nach Mannschaften sortiert'!G89</f>
         <v>0</v>
       </c>
       <c r="H61" s="54">
-        <f>'Nach Mannschaften sortiert'!H88</f>
+        <f>'Nach Mannschaften sortiert'!H89</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="46">
-        <f>'Nach Mannschaften sortiert'!A59</f>
-        <v>58</v>
+        <f>'Nach Mannschaften sortiert'!A60</f>
+        <v>59</v>
       </c>
       <c r="B62" s="46">
-        <f>'Nach Mannschaften sortiert'!B59</f>
+        <f>'Nach Mannschaften sortiert'!B60</f>
         <v>9</v>
       </c>
       <c r="C62" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C59</f>
+        <f>'Nach Mannschaften sortiert'!C60</f>
         <v>U14</v>
       </c>
       <c r="D62" s="47">
-        <f>'Nach Mannschaften sortiert'!D59</f>
+        <f>'Nach Mannschaften sortiert'!D60</f>
         <v>46041</v>
       </c>
       <c r="E62" s="100">
-        <f>'Nach Mannschaften sortiert'!E59</f>
+        <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="F62" s="46">
-        <f>'Nach Mannschaften sortiert'!F59</f>
+        <f>'Nach Mannschaften sortiert'!F60</f>
         <v>0</v>
       </c>
       <c r="G62" s="46">
-        <f>'Nach Mannschaften sortiert'!G59</f>
+        <f>'Nach Mannschaften sortiert'!G60</f>
         <v>0</v>
       </c>
       <c r="H62" s="46">
-        <f>'Nach Mannschaften sortiert'!H59</f>
+        <f>'Nach Mannschaften sortiert'!H60</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="54">
-        <f>'Nach Mannschaften sortiert'!A90</f>
-        <v>89</v>
+        <f>'Nach Mannschaften sortiert'!A91</f>
+        <v>90</v>
       </c>
       <c r="B63" s="54">
-        <f>'Nach Mannschaften sortiert'!B90</f>
+        <f>'Nach Mannschaften sortiert'!B91</f>
         <v>10</v>
       </c>
       <c r="C63" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C90</f>
+        <f>'Nach Mannschaften sortiert'!C91</f>
         <v>U11</v>
       </c>
       <c r="D63" s="55">
-        <f>'Nach Mannschaften sortiert'!D90</f>
+        <f>'Nach Mannschaften sortiert'!D91</f>
         <v>46072</v>
       </c>
       <c r="E63" s="97">
-        <f>'Nach Mannschaften sortiert'!E90</f>
+        <f>'Nach Mannschaften sortiert'!E91</f>
         <v>0</v>
       </c>
       <c r="F63" s="54">
-        <f>'Nach Mannschaften sortiert'!F90</f>
+        <f>'Nach Mannschaften sortiert'!F91</f>
         <v>0</v>
       </c>
       <c r="G63" s="54">
-        <f>'Nach Mannschaften sortiert'!G90</f>
+        <f>'Nach Mannschaften sortiert'!G91</f>
         <v>0</v>
       </c>
       <c r="H63" s="54">
-        <f>'Nach Mannschaften sortiert'!H90</f>
+        <f>'Nach Mannschaften sortiert'!H91</f>
         <v>0</v>
       </c>
     </row>
@@ -12677,15 +12749,15 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="48">
-        <f>'Nach Mannschaften sortiert'!A89</f>
-        <v>88</v>
+        <f>'Nach Mannschaften sortiert'!A90</f>
+        <v>89</v>
       </c>
       <c r="B65" s="48">
-        <f>'Nach Mannschaften sortiert'!B89</f>
+        <f>'Nach Mannschaften sortiert'!B90</f>
         <v>9</v>
       </c>
       <c r="C65" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C89</f>
+        <f>'Nach Mannschaften sortiert'!C90</f>
         <v>U11</v>
       </c>
       <c r="D65" s="49">
@@ -12695,525 +12767,525 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F65" s="48">
-        <f>'Nach Mannschaften sortiert'!F89</f>
+        <f>'Nach Mannschaften sortiert'!F90</f>
         <v>0</v>
       </c>
       <c r="G65" s="48">
-        <f>'Nach Mannschaften sortiert'!G89</f>
+        <f>'Nach Mannschaften sortiert'!G90</f>
         <v>0</v>
       </c>
       <c r="H65" s="48">
-        <f>'Nach Mannschaften sortiert'!H89</f>
+        <f>'Nach Mannschaften sortiert'!H90</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="54">
-        <f>'Nach Mannschaften sortiert'!A97</f>
-        <v>96</v>
+        <f>'Nach Mannschaften sortiert'!A98</f>
+        <v>97</v>
       </c>
       <c r="B66" s="54">
-        <f>'Nach Mannschaften sortiert'!B97</f>
+        <f>'Nach Mannschaften sortiert'!B98</f>
         <v>2</v>
       </c>
       <c r="C66" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C97</f>
+        <f>'Nach Mannschaften sortiert'!C98</f>
         <v>U9</v>
       </c>
       <c r="D66" s="55">
-        <f>'Nach Mannschaften sortiert'!D97</f>
+        <f>'Nach Mannschaften sortiert'!D98</f>
         <v>46079</v>
       </c>
       <c r="E66" s="97">
-        <f>'Nach Mannschaften sortiert'!E97</f>
+        <f>'Nach Mannschaften sortiert'!E98</f>
         <v>0</v>
       </c>
       <c r="F66" s="54">
-        <f>'Nach Mannschaften sortiert'!F97</f>
+        <f>'Nach Mannschaften sortiert'!F98</f>
         <v>0</v>
       </c>
       <c r="G66" s="54">
-        <f>'Nach Mannschaften sortiert'!G97</f>
+        <f>'Nach Mannschaften sortiert'!G98</f>
         <v>0</v>
       </c>
       <c r="H66" s="54">
-        <f>'Nach Mannschaften sortiert'!H97</f>
+        <f>'Nach Mannschaften sortiert'!H98</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="54">
-        <f>'Nach Mannschaften sortiert'!A98</f>
-        <v>97</v>
+        <f>'Nach Mannschaften sortiert'!A99</f>
+        <v>98</v>
       </c>
       <c r="B67" s="54">
-        <f>'Nach Mannschaften sortiert'!B98</f>
+        <f>'Nach Mannschaften sortiert'!B99</f>
         <v>3</v>
       </c>
       <c r="C67" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C98</f>
+        <f>'Nach Mannschaften sortiert'!C99</f>
         <v>U9</v>
       </c>
       <c r="D67" s="55">
-        <f>'Nach Mannschaften sortiert'!D98</f>
+        <f>'Nach Mannschaften sortiert'!D99</f>
         <v>46080</v>
       </c>
       <c r="E67" s="97">
-        <f>'Nach Mannschaften sortiert'!E98</f>
+        <f>'Nach Mannschaften sortiert'!E99</f>
         <v>0</v>
       </c>
       <c r="F67" s="54">
-        <f>'Nach Mannschaften sortiert'!F98</f>
+        <f>'Nach Mannschaften sortiert'!F99</f>
         <v>0</v>
       </c>
       <c r="G67" s="54">
-        <f>'Nach Mannschaften sortiert'!G98</f>
+        <f>'Nach Mannschaften sortiert'!G99</f>
         <v>0</v>
       </c>
       <c r="H67" s="54">
-        <f>'Nach Mannschaften sortiert'!H98</f>
+        <f>'Nach Mannschaften sortiert'!H99</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="54">
-        <f>'Nach Mannschaften sortiert'!A99</f>
-        <v>98</v>
+        <f>'Nach Mannschaften sortiert'!A100</f>
+        <v>99</v>
       </c>
       <c r="B68" s="54">
-        <f>'Nach Mannschaften sortiert'!B99</f>
+        <f>'Nach Mannschaften sortiert'!B100</f>
         <v>4</v>
       </c>
       <c r="C68" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C99</f>
+        <f>'Nach Mannschaften sortiert'!C100</f>
         <v>U9</v>
       </c>
       <c r="D68" s="55">
-        <f>'Nach Mannschaften sortiert'!D99</f>
+        <f>'Nach Mannschaften sortiert'!D100</f>
         <v>46081</v>
       </c>
       <c r="E68" s="97">
-        <f>'Nach Mannschaften sortiert'!E99</f>
+        <f>'Nach Mannschaften sortiert'!E100</f>
         <v>0</v>
       </c>
       <c r="F68" s="54">
-        <f>'Nach Mannschaften sortiert'!F99</f>
+        <f>'Nach Mannschaften sortiert'!F100</f>
         <v>0</v>
       </c>
       <c r="G68" s="54">
-        <f>'Nach Mannschaften sortiert'!G99</f>
+        <f>'Nach Mannschaften sortiert'!G100</f>
         <v>0</v>
       </c>
       <c r="H68" s="54">
-        <f>'Nach Mannschaften sortiert'!H99</f>
+        <f>'Nach Mannschaften sortiert'!H100</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="54">
-        <f>'Nach Mannschaften sortiert'!A105</f>
-        <v>104</v>
+        <f>'Nach Mannschaften sortiert'!A106</f>
+        <v>105</v>
       </c>
       <c r="B69" s="54">
-        <f>'Nach Mannschaften sortiert'!B105</f>
+        <f>'Nach Mannschaften sortiert'!B106</f>
         <v>10</v>
       </c>
       <c r="C69" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C105</f>
+        <f>'Nach Mannschaften sortiert'!C106</f>
         <v>U9</v>
       </c>
       <c r="D69" s="55">
-        <f>'Nach Mannschaften sortiert'!D105</f>
+        <f>'Nach Mannschaften sortiert'!D106</f>
         <v>46087</v>
       </c>
       <c r="E69" s="97">
-        <f>'Nach Mannschaften sortiert'!E105</f>
+        <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="F69" s="54">
-        <f>'Nach Mannschaften sortiert'!F105</f>
+        <f>'Nach Mannschaften sortiert'!F106</f>
         <v>0</v>
       </c>
       <c r="G69" s="54">
-        <f>'Nach Mannschaften sortiert'!G105</f>
+        <f>'Nach Mannschaften sortiert'!G106</f>
         <v>0</v>
       </c>
       <c r="H69" s="54">
-        <f>'Nach Mannschaften sortiert'!H105</f>
+        <f>'Nach Mannschaften sortiert'!H106</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="48">
-        <f>'Nach Mannschaften sortiert'!A66</f>
-        <v>65</v>
+        <f>'Nach Mannschaften sortiert'!A67</f>
+        <v>66</v>
       </c>
       <c r="B70" s="48">
-        <f>'Nach Mannschaften sortiert'!B66</f>
+        <f>'Nach Mannschaften sortiert'!B67</f>
         <v>6</v>
       </c>
       <c r="C70" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C66</f>
+        <f>'Nach Mannschaften sortiert'!C67</f>
         <v>U12_1</v>
       </c>
       <c r="D70" s="49">
-        <f>'Nach Mannschaften sortiert'!D66</f>
+        <f>'Nach Mannschaften sortiert'!D67</f>
         <v>46048</v>
       </c>
       <c r="E70" s="99">
-        <f>'Nach Mannschaften sortiert'!E66</f>
+        <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="F70" s="48">
-        <f>'Nach Mannschaften sortiert'!F66</f>
+        <f>'Nach Mannschaften sortiert'!F67</f>
         <v>0</v>
       </c>
       <c r="G70" s="48">
-        <f>'Nach Mannschaften sortiert'!G66</f>
+        <f>'Nach Mannschaften sortiert'!G67</f>
         <v>0</v>
       </c>
       <c r="H70" s="48">
-        <f>'Nach Mannschaften sortiert'!H66</f>
+        <f>'Nach Mannschaften sortiert'!H67</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="54">
-        <f>'Nach Mannschaften sortiert'!A107</f>
-        <v>106</v>
+        <f>'Nach Mannschaften sortiert'!A108</f>
+        <v>107</v>
       </c>
       <c r="B71" s="54">
-        <f>'Nach Mannschaften sortiert'!B107</f>
+        <f>'Nach Mannschaften sortiert'!B108</f>
         <v>2</v>
       </c>
       <c r="C71" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C107</f>
+        <f>'Nach Mannschaften sortiert'!C108</f>
         <v>U8</v>
       </c>
       <c r="D71" s="55">
-        <f>'Nach Mannschaften sortiert'!D107</f>
+        <f>'Nach Mannschaften sortiert'!D108</f>
         <v>46089</v>
       </c>
       <c r="E71" s="97">
-        <f>'Nach Mannschaften sortiert'!E107</f>
+        <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="F71" s="54">
-        <f>'Nach Mannschaften sortiert'!F107</f>
+        <f>'Nach Mannschaften sortiert'!F108</f>
         <v>0</v>
       </c>
       <c r="G71" s="54">
-        <f>'Nach Mannschaften sortiert'!G107</f>
+        <f>'Nach Mannschaften sortiert'!G108</f>
         <v>0</v>
       </c>
       <c r="H71" s="54">
-        <f>'Nach Mannschaften sortiert'!H107</f>
+        <f>'Nach Mannschaften sortiert'!H108</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="54">
-        <f>'Nach Mannschaften sortiert'!A108</f>
-        <v>107</v>
+        <f>'Nach Mannschaften sortiert'!A109</f>
+        <v>108</v>
       </c>
       <c r="B72" s="54">
-        <f>'Nach Mannschaften sortiert'!B108</f>
+        <f>'Nach Mannschaften sortiert'!B109</f>
         <v>3</v>
       </c>
       <c r="C72" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C108</f>
+        <f>'Nach Mannschaften sortiert'!C109</f>
         <v>U8</v>
       </c>
       <c r="D72" s="55">
-        <f>'Nach Mannschaften sortiert'!D108</f>
+        <f>'Nach Mannschaften sortiert'!D109</f>
         <v>46090</v>
       </c>
       <c r="E72" s="97">
-        <f>'Nach Mannschaften sortiert'!E108</f>
+        <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0</v>
       </c>
       <c r="F72" s="54">
-        <f>'Nach Mannschaften sortiert'!F108</f>
+        <f>'Nach Mannschaften sortiert'!F109</f>
         <v>0</v>
       </c>
       <c r="G72" s="54">
-        <f>'Nach Mannschaften sortiert'!G108</f>
+        <f>'Nach Mannschaften sortiert'!G109</f>
         <v>0</v>
       </c>
       <c r="H72" s="54">
-        <f>'Nach Mannschaften sortiert'!H108</f>
+        <f>'Nach Mannschaften sortiert'!H109</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="54">
-        <f>'Nach Mannschaften sortiert'!A109</f>
-        <v>108</v>
+        <f>'Nach Mannschaften sortiert'!A110</f>
+        <v>109</v>
       </c>
       <c r="B73" s="54">
-        <f>'Nach Mannschaften sortiert'!B109</f>
+        <f>'Nach Mannschaften sortiert'!B110</f>
         <v>4</v>
       </c>
       <c r="C73" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C109</f>
+        <f>'Nach Mannschaften sortiert'!C110</f>
         <v>U8</v>
       </c>
       <c r="D73" s="55">
-        <f>'Nach Mannschaften sortiert'!D109</f>
+        <f>'Nach Mannschaften sortiert'!D110</f>
         <v>46091</v>
       </c>
       <c r="E73" s="97">
-        <f>'Nach Mannschaften sortiert'!E109</f>
+        <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="F73" s="54">
-        <f>'Nach Mannschaften sortiert'!F109</f>
+        <f>'Nach Mannschaften sortiert'!F110</f>
         <v>0</v>
       </c>
       <c r="G73" s="54">
-        <f>'Nach Mannschaften sortiert'!G109</f>
+        <f>'Nach Mannschaften sortiert'!G110</f>
         <v>0</v>
       </c>
       <c r="H73" s="54">
-        <f>'Nach Mannschaften sortiert'!H109</f>
+        <f>'Nach Mannschaften sortiert'!H110</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="54">
-        <f>'Nach Mannschaften sortiert'!A110</f>
-        <v>109</v>
+        <f>'Nach Mannschaften sortiert'!A111</f>
+        <v>110</v>
       </c>
       <c r="B74" s="54">
-        <f>'Nach Mannschaften sortiert'!B110</f>
+        <f>'Nach Mannschaften sortiert'!B111</f>
         <v>5</v>
       </c>
       <c r="C74" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C110</f>
+        <f>'Nach Mannschaften sortiert'!C111</f>
         <v>U8</v>
       </c>
       <c r="D74" s="55">
-        <f>'Nach Mannschaften sortiert'!D110</f>
+        <f>'Nach Mannschaften sortiert'!D111</f>
         <v>46092</v>
       </c>
       <c r="E74" s="97">
-        <f>'Nach Mannschaften sortiert'!E110</f>
+        <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="F74" s="54">
-        <f>'Nach Mannschaften sortiert'!F110</f>
+        <f>'Nach Mannschaften sortiert'!F111</f>
         <v>0</v>
       </c>
       <c r="G74" s="54">
-        <f>'Nach Mannschaften sortiert'!G110</f>
+        <f>'Nach Mannschaften sortiert'!G111</f>
         <v>0</v>
       </c>
       <c r="H74" s="54">
-        <f>'Nach Mannschaften sortiert'!H110</f>
+        <f>'Nach Mannschaften sortiert'!H111</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="48">
-        <f>'Nach Mannschaften sortiert'!A27</f>
-        <v>26</v>
+        <f>'Nach Mannschaften sortiert'!A28</f>
+        <v>27</v>
       </c>
       <c r="B75" s="48">
-        <f>'Nach Mannschaften sortiert'!B27</f>
+        <f>'Nach Mannschaften sortiert'!B28</f>
         <v>13</v>
       </c>
       <c r="C75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C27</f>
+        <f>'Nach Mannschaften sortiert'!C28</f>
         <v>KM</v>
       </c>
       <c r="D75" s="49">
-        <f>'Nach Mannschaften sortiert'!D27</f>
+        <f>'Nach Mannschaften sortiert'!D28</f>
         <v>46333</v>
       </c>
       <c r="E75" s="99">
-        <f>'Nach Mannschaften sortiert'!E27</f>
+        <f>'Nach Mannschaften sortiert'!E28</f>
         <v>0.6875</v>
       </c>
       <c r="F75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F27</f>
+        <f>'Nach Mannschaften sortiert'!F28</f>
         <v>Neufeld</v>
       </c>
       <c r="G75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G27</f>
+        <f>'Nach Mannschaften sortiert'!G28</f>
         <v>Andau</v>
       </c>
       <c r="H75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H27</f>
+        <f>'Nach Mannschaften sortiert'!H28</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="54">
-        <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>111</v>
+        <f>'Nach Mannschaften sortiert'!A113</f>
+        <v>112</v>
       </c>
       <c r="B76" s="54">
-        <f>'Nach Mannschaften sortiert'!B112</f>
+        <f>'Nach Mannschaften sortiert'!B113</f>
         <v>2</v>
       </c>
       <c r="C76" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C112</f>
+        <f>'Nach Mannschaften sortiert'!C113</f>
         <v>U7</v>
       </c>
       <c r="D76" s="55">
-        <f>'Nach Mannschaften sortiert'!D112</f>
+        <f>'Nach Mannschaften sortiert'!D113</f>
         <v>46094</v>
       </c>
       <c r="E76" s="97">
-        <f>'Nach Mannschaften sortiert'!E112</f>
+        <f>'Nach Mannschaften sortiert'!E113</f>
         <v>0</v>
       </c>
       <c r="F76" s="54">
-        <f>'Nach Mannschaften sortiert'!F112</f>
+        <f>'Nach Mannschaften sortiert'!F113</f>
         <v>0</v>
       </c>
       <c r="G76" s="54">
-        <f>'Nach Mannschaften sortiert'!G112</f>
+        <f>'Nach Mannschaften sortiert'!G113</f>
         <v>0</v>
       </c>
       <c r="H76" s="54">
-        <f>'Nach Mannschaften sortiert'!H112</f>
+        <f>'Nach Mannschaften sortiert'!H113</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="54">
-        <f>'Nach Mannschaften sortiert'!A113</f>
-        <v>112</v>
+        <f>'Nach Mannschaften sortiert'!A114</f>
+        <v>113</v>
       </c>
       <c r="B77" s="54">
-        <f>'Nach Mannschaften sortiert'!B113</f>
+        <f>'Nach Mannschaften sortiert'!B114</f>
         <v>3</v>
       </c>
       <c r="C77" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C113</f>
+        <f>'Nach Mannschaften sortiert'!C114</f>
         <v>U7</v>
       </c>
       <c r="D77" s="55">
-        <f>'Nach Mannschaften sortiert'!D113</f>
+        <f>'Nach Mannschaften sortiert'!D114</f>
         <v>46095</v>
       </c>
       <c r="E77" s="97">
-        <f>'Nach Mannschaften sortiert'!E113</f>
+        <f>'Nach Mannschaften sortiert'!E114</f>
         <v>0</v>
       </c>
       <c r="F77" s="54">
-        <f>'Nach Mannschaften sortiert'!F113</f>
+        <f>'Nach Mannschaften sortiert'!F114</f>
         <v>0</v>
       </c>
       <c r="G77" s="54">
-        <f>'Nach Mannschaften sortiert'!G113</f>
+        <f>'Nach Mannschaften sortiert'!G114</f>
         <v>0</v>
       </c>
       <c r="H77" s="54">
-        <f>'Nach Mannschaften sortiert'!H113</f>
+        <f>'Nach Mannschaften sortiert'!H114</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="54">
-        <f>'Nach Mannschaften sortiert'!A114</f>
-        <v>113</v>
+        <f>'Nach Mannschaften sortiert'!A115</f>
+        <v>114</v>
       </c>
       <c r="B78" s="54">
-        <f>'Nach Mannschaften sortiert'!B114</f>
+        <f>'Nach Mannschaften sortiert'!B115</f>
         <v>4</v>
       </c>
       <c r="C78" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C114</f>
+        <f>'Nach Mannschaften sortiert'!C115</f>
         <v>U7</v>
       </c>
       <c r="D78" s="55">
-        <f>'Nach Mannschaften sortiert'!D114</f>
+        <f>'Nach Mannschaften sortiert'!D115</f>
         <v>46096</v>
       </c>
       <c r="E78" s="97">
-        <f>'Nach Mannschaften sortiert'!E114</f>
+        <f>'Nach Mannschaften sortiert'!E115</f>
         <v>0</v>
       </c>
       <c r="F78" s="54">
-        <f>'Nach Mannschaften sortiert'!F114</f>
+        <f>'Nach Mannschaften sortiert'!F115</f>
         <v>0</v>
       </c>
       <c r="G78" s="54">
-        <f>'Nach Mannschaften sortiert'!G114</f>
+        <f>'Nach Mannschaften sortiert'!G115</f>
         <v>0</v>
       </c>
       <c r="H78" s="54">
-        <f>'Nach Mannschaften sortiert'!H114</f>
+        <f>'Nach Mannschaften sortiert'!H115</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="54">
-        <f>'Nach Mannschaften sortiert'!A115</f>
-        <v>114</v>
+        <f>'Nach Mannschaften sortiert'!A116</f>
+        <v>115</v>
       </c>
       <c r="B79" s="54">
-        <f>'Nach Mannschaften sortiert'!B115</f>
+        <f>'Nach Mannschaften sortiert'!B116</f>
         <v>5</v>
       </c>
       <c r="C79" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C115</f>
+        <f>'Nach Mannschaften sortiert'!C116</f>
         <v>U7</v>
       </c>
       <c r="D79" s="55">
-        <f>'Nach Mannschaften sortiert'!D115</f>
+        <f>'Nach Mannschaften sortiert'!D116</f>
         <v>46097</v>
       </c>
       <c r="E79" s="97">
-        <f>'Nach Mannschaften sortiert'!E115</f>
+        <f>'Nach Mannschaften sortiert'!E116</f>
         <v>0</v>
       </c>
       <c r="F79" s="54">
-        <f>'Nach Mannschaften sortiert'!F115</f>
+        <f>'Nach Mannschaften sortiert'!F116</f>
         <v>0</v>
       </c>
       <c r="G79" s="54">
-        <f>'Nach Mannschaften sortiert'!G115</f>
+        <f>'Nach Mannschaften sortiert'!G116</f>
         <v>0</v>
       </c>
       <c r="H79" s="54">
-        <f>'Nach Mannschaften sortiert'!H115</f>
+        <f>'Nach Mannschaften sortiert'!H116</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="48">
-        <f>'Nach Mannschaften sortiert'!A68</f>
-        <v>67</v>
+        <f>'Nach Mannschaften sortiert'!A69</f>
+        <v>68</v>
       </c>
       <c r="B80" s="48">
-        <f>'Nach Mannschaften sortiert'!B68</f>
+        <f>'Nach Mannschaften sortiert'!B69</f>
         <v>8</v>
       </c>
       <c r="C80" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C68</f>
+        <f>'Nach Mannschaften sortiert'!C69</f>
         <v>U12_1</v>
       </c>
       <c r="D80" s="49">
-        <f>'Nach Mannschaften sortiert'!D68</f>
+        <f>'Nach Mannschaften sortiert'!D69</f>
         <v>46050</v>
       </c>
       <c r="E80" s="99">
-        <f>'Nach Mannschaften sortiert'!E68</f>
+        <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="F80" s="48">
-        <f>'Nach Mannschaften sortiert'!F68</f>
+        <f>'Nach Mannschaften sortiert'!F69</f>
         <v>0</v>
       </c>
       <c r="G80" s="48">
-        <f>'Nach Mannschaften sortiert'!G68</f>
+        <f>'Nach Mannschaften sortiert'!G69</f>
         <v>0</v>
       </c>
       <c r="H80" s="48">
-        <f>'Nach Mannschaften sortiert'!H68</f>
+        <f>'Nach Mannschaften sortiert'!H69</f>
         <v>0</v>
       </c>
     </row>
@@ -13253,35 +13325,35 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="48">
-        <f>'Nach Mannschaften sortiert'!A50</f>
-        <v>49</v>
+        <f>'Nach Mannschaften sortiert'!A51</f>
+        <v>50</v>
       </c>
       <c r="B82" s="48">
-        <f>'Nach Mannschaften sortiert'!B50</f>
+        <f>'Nach Mannschaften sortiert'!B51</f>
         <v>10</v>
       </c>
       <c r="C82" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C50</f>
+        <f>'Nach Mannschaften sortiert'!C51</f>
         <v>U16</v>
       </c>
       <c r="D82" s="49">
-        <f>'Nach Mannschaften sortiert'!D50</f>
+        <f>'Nach Mannschaften sortiert'!D51</f>
         <v>46032</v>
       </c>
       <c r="E82" s="99">
-        <f>'Nach Mannschaften sortiert'!E50</f>
+        <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="F82" s="48">
-        <f>'Nach Mannschaften sortiert'!F50</f>
+        <f>'Nach Mannschaften sortiert'!F51</f>
         <v>0</v>
       </c>
       <c r="G82" s="48">
-        <f>'Nach Mannschaften sortiert'!G50</f>
+        <f>'Nach Mannschaften sortiert'!G51</f>
         <v>0</v>
       </c>
       <c r="H82" s="48">
-        <f>'Nach Mannschaften sortiert'!H50</f>
+        <f>'Nach Mannschaften sortiert'!H51</f>
         <v>0</v>
       </c>
     </row>
@@ -13321,35 +13393,35 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="54">
-        <f>'Nach Mannschaften sortiert'!A127</f>
-        <v>126</v>
+        <f>'Nach Mannschaften sortiert'!A128</f>
+        <v>127</v>
       </c>
       <c r="B84" s="54">
-        <f>'Nach Mannschaften sortiert'!B127</f>
+        <f>'Nach Mannschaften sortiert'!B128</f>
         <v>2</v>
       </c>
       <c r="C84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C127</f>
+        <f>'Nach Mannschaften sortiert'!C128</f>
         <v>GGG</v>
       </c>
       <c r="D84" s="55">
-        <f>'Nach Mannschaften sortiert'!D127</f>
+        <f>'Nach Mannschaften sortiert'!D128</f>
         <v>46256</v>
       </c>
       <c r="E84" s="97">
-        <f>'Nach Mannschaften sortiert'!E127</f>
+        <f>'Nach Mannschaften sortiert'!E128</f>
         <v>0.375</v>
       </c>
       <c r="F84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F127</f>
+        <f>'Nach Mannschaften sortiert'!F128</f>
         <v>Neufeld</v>
       </c>
       <c r="G84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G127</f>
+        <f>'Nach Mannschaften sortiert'!G128</f>
         <v>viele Gegner</v>
       </c>
       <c r="H84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H127</f>
+        <f>'Nach Mannschaften sortiert'!H128</f>
         <v>Heim</v>
       </c>
     </row>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078719A9-8E5D-4696-81DA-F247833A603B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDCCC93-2A47-4BDD-8109-A987BA81C35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="179">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -582,6 +582,9 @@
   </si>
   <si>
     <t>Vienna U13</t>
+  </si>
+  <si>
+    <t>SPG Theresienfeld</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1350,6 +1353,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -1589,7 +1593,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="54" bestFit="1" customWidth="1"/>
@@ -1656,7 +1660,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f t="shared" ref="A3:A40" si="0">A2+1</f>
+        <f t="shared" ref="A3:A41" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="5">
@@ -2005,7 +2009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="111" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" s="116" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="54">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2014,48 +2018,48 @@
         <v>0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="9">
-        <v>46445</v>
+        <v>46264</v>
       </c>
       <c r="E16" s="93">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>171</v>
+        <v>23</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+    <row r="17" spans="1:8" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="4">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="10">
-        <v>46250</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="4" t="s">
+      <c r="D17" s="9">
+        <v>46445</v>
+      </c>
+      <c r="E17" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2065,22 +2069,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E18" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>15</v>
@@ -2092,25 +2096,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E19" s="3">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -2119,25 +2123,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E20" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2146,25 +2150,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E21" s="3">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -2173,25 +2177,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -2200,25 +2204,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E23" s="3">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -2227,25 +2231,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="10">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="E24" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -2254,25 +2258,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="10">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="E25" s="3">
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -2281,25 +2285,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E26" s="3">
         <v>0.8125</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2308,25 +2312,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E27" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -2335,25 +2339,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E28" s="3">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -2362,25 +2366,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E29" s="3">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -2389,25 +2393,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D30" s="10">
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="E30" s="3">
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2416,22 +2420,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="10">
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="E31" s="3">
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>15</v>
@@ -2443,25 +2447,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D32" s="10">
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="E32" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -2470,25 +2474,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="10">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="E33" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -2497,25 +2501,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D34" s="10">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="E34" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -2524,25 +2528,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="10">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="E35" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -2551,25 +2555,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D36" s="10">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="E36" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -2578,25 +2582,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D37" s="10">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="E37" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -2605,25 +2609,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D38" s="10">
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="E38" s="3">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -2632,25 +2636,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D39" s="10">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="E39" s="3">
         <v>0.72916666666666663</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -2659,99 +2663,107 @@
         <v>39</v>
       </c>
       <c r="B40" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="10">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="E40" s="3">
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <f t="shared" ref="A41:A72" si="1">A40+1</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D41" s="10">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E41" s="3">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A42:A73" si="1">A41+1</f>
         <v>41</v>
       </c>
       <c r="B42" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="10">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E42" s="3">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="21">
+      <c r="A43" s="4">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="B43" s="21">
-        <v>1</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="28">
-        <v>46023</v>
-      </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
+      <c r="B43" s="4">
+        <v>13</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="10">
+        <v>46333</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="21">
@@ -2759,13 +2771,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="28">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="21"/>
@@ -2778,13 +2790,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="28">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="21"/>
@@ -2797,13 +2809,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="28">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="21"/>
@@ -2816,13 +2828,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D47" s="28">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="21"/>
@@ -2835,13 +2847,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="28">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="21"/>
@@ -2854,13 +2866,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="28">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="21"/>
@@ -2873,13 +2885,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D50" s="28">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="21"/>
@@ -2892,13 +2904,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C51" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D51" s="28">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="21"/>
@@ -2911,58 +2923,57 @@
         <v>51</v>
       </c>
       <c r="B52" s="21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C52" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D52" s="28">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="21"/>
       <c r="G52" s="21"/>
       <c r="H52" s="21"/>
     </row>
-    <row r="53" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="18">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="21">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B53" s="13">
-        <v>1</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D53" s="14">
-        <v>46033</v>
-      </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="17"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B53" s="21">
+        <v>10</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" s="28">
+        <v>46032</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+    </row>
+    <row r="54" spans="1:9" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="18">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B54" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D54" s="14">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
-      <c r="I54" s="16"/>
+      <c r="I54" s="17"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="18">
@@ -2970,13 +2981,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D55" s="14">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="13"/>
@@ -2990,13 +3001,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="14">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="13"/>
@@ -3010,13 +3021,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D57" s="14">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="13"/>
@@ -3030,13 +3041,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D58" s="14">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="13"/>
@@ -3050,13 +3061,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D59" s="14">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="13"/>
@@ -3070,13 +3081,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D60" s="14">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="13"/>
@@ -3090,13 +3101,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D61" s="14">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="E61" s="15"/>
       <c r="F61" s="13"/>
@@ -3110,13 +3121,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D62" s="14">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="13"/>
@@ -3125,23 +3136,24 @@
       <c r="I62" s="16"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="6">
+      <c r="A63" s="18">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="B63" s="6">
-        <v>1</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D63" s="23">
-        <v>46043</v>
-      </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
+      <c r="B63" s="13">
+        <v>10</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D63" s="14">
+        <v>46042</v>
+      </c>
+      <c r="E63" s="15"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="16"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
@@ -3149,13 +3161,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D64" s="23">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="6"/>
@@ -3168,13 +3180,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D65" s="23">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="6"/>
@@ -3187,13 +3199,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D66" s="23">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="6"/>
@@ -3206,13 +3218,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D67" s="23">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="6"/>
@@ -3225,13 +3237,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D68" s="23">
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="6"/>
@@ -3244,13 +3256,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D69" s="23">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="6"/>
@@ -3263,13 +3275,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D70" s="23">
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="6"/>
@@ -3282,13 +3294,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D71" s="23">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="6"/>
@@ -3301,13 +3313,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D72" s="23">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="6"/>
@@ -3315,37 +3327,37 @@
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="90">
-        <f t="shared" ref="A73:A104" si="2">A72+1</f>
+      <c r="A73" s="6">
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B73" s="90">
-        <v>1</v>
-      </c>
-      <c r="C73" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="D73" s="91">
-        <v>46053</v>
-      </c>
-      <c r="E73" s="92"/>
-      <c r="F73" s="90"/>
-      <c r="G73" s="90"/>
-      <c r="H73" s="90"/>
+      <c r="B73" s="6">
+        <v>10</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="23">
+        <v>46052</v>
+      </c>
+      <c r="E73" s="7"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A74:A105" si="2">A73+1</f>
         <v>73</v>
       </c>
       <c r="B74" s="90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="91">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="E74" s="92"/>
       <c r="F74" s="90"/>
@@ -3358,13 +3370,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="91">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="E75" s="92"/>
       <c r="F75" s="90"/>
@@ -3377,13 +3389,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="91">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="E76" s="92"/>
       <c r="F76" s="90"/>
@@ -3396,13 +3408,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D77" s="91">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="E77" s="92"/>
       <c r="F77" s="90"/>
@@ -3415,13 +3427,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D78" s="91">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="E78" s="92"/>
       <c r="F78" s="90"/>
@@ -3434,13 +3446,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D79" s="91">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="E79" s="92"/>
       <c r="F79" s="90"/>
@@ -3453,13 +3465,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D80" s="91">
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="E80" s="92"/>
       <c r="F80" s="90"/>
@@ -3472,13 +3484,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="90">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C81" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D81" s="91">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="E81" s="92"/>
       <c r="F81" s="90"/>
@@ -3491,13 +3503,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="90">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C82" s="90" t="s">
         <v>38</v>
       </c>
       <c r="D82" s="91">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="E82" s="92"/>
       <c r="F82" s="90"/>
@@ -3505,23 +3517,23 @@
       <c r="H82" s="90"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="19">
+      <c r="A83" s="90">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="B83" s="19">
-        <v>1</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D83" s="24">
-        <v>46063</v>
-      </c>
-      <c r="E83" s="20"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
+      <c r="B83" s="90">
+        <v>10</v>
+      </c>
+      <c r="C83" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" s="91">
+        <v>46062</v>
+      </c>
+      <c r="E83" s="92"/>
+      <c r="F83" s="90"/>
+      <c r="G83" s="90"/>
+      <c r="H83" s="90"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="19">
@@ -3529,13 +3541,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D84" s="24">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="E84" s="20"/>
       <c r="F84" s="19"/>
@@ -3548,13 +3560,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D85" s="24">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="E85" s="20"/>
       <c r="F85" s="19"/>
@@ -3567,13 +3579,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C86" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D86" s="24">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="E86" s="20"/>
       <c r="F86" s="19"/>
@@ -3586,13 +3598,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C87" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="24">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="E87" s="20"/>
       <c r="F87" s="19"/>
@@ -3605,13 +3617,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D88" s="24">
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="E88" s="20"/>
       <c r="F88" s="19"/>
@@ -3624,13 +3636,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D89" s="24">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="E89" s="20"/>
       <c r="F89" s="19"/>
@@ -3643,13 +3655,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C90" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D90" s="24">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="E90" s="20"/>
       <c r="F90" s="19"/>
@@ -3662,13 +3674,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C91" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D91" s="24">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="E91" s="20"/>
       <c r="F91" s="19"/>
@@ -3681,13 +3693,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C92" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D92" s="24">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="E92" s="20"/>
       <c r="F92" s="19"/>
@@ -3695,31 +3707,23 @@
       <c r="H92" s="19"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="87">
+      <c r="A93" s="19">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="B93" s="87">
-        <v>1</v>
-      </c>
-      <c r="C93" s="87" t="s">
-        <v>40</v>
-      </c>
-      <c r="D93" s="88">
-        <v>46312</v>
-      </c>
-      <c r="E93" s="89">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F93" s="89" t="s">
-        <v>19</v>
-      </c>
-      <c r="G93" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="H93" s="87" t="s">
-        <v>11</v>
-      </c>
+      <c r="B93" s="19">
+        <v>10</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D93" s="24">
+        <v>46072</v>
+      </c>
+      <c r="E93" s="20"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="19"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="87">
@@ -3727,18 +3731,26 @@
         <v>93</v>
       </c>
       <c r="B94" s="87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D94" s="88">
-        <v>46074</v>
-      </c>
-      <c r="E94" s="89"/>
-      <c r="F94" s="87"/>
-      <c r="G94" s="87"/>
-      <c r="H94" s="87"/>
+        <v>46312</v>
+      </c>
+      <c r="E94" s="89">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F94" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="G94" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="H94" s="87" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="87">
@@ -3746,13 +3758,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D95" s="88">
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="E95" s="89"/>
       <c r="F95" s="87"/>
@@ -3765,13 +3777,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C96" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D96" s="88">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="E96" s="89"/>
       <c r="F96" s="87"/>
@@ -3784,13 +3796,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97" s="87" t="s">
         <v>40</v>
       </c>
       <c r="D97" s="88">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="E97" s="89"/>
       <c r="F97" s="87"/>
@@ -3798,23 +3810,23 @@
       <c r="H97" s="87"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="8">
+      <c r="A98" s="87">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="B98" s="8">
-        <v>1</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D98" s="29">
-        <v>46078</v>
-      </c>
-      <c r="E98" s="12"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
+      <c r="B98" s="87">
+        <v>5</v>
+      </c>
+      <c r="C98" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="D98" s="88">
+        <v>46077</v>
+      </c>
+      <c r="E98" s="89"/>
+      <c r="F98" s="87"/>
+      <c r="G98" s="87"/>
+      <c r="H98" s="87"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
@@ -3822,13 +3834,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D99" s="29">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="8"/>
@@ -3841,13 +3853,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D100" s="29">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="8"/>
@@ -3860,13 +3872,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D101" s="29">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="8"/>
@@ -3879,13 +3891,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D102" s="29">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="8"/>
@@ -3898,13 +3910,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D103" s="29">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="8"/>
@@ -3917,13 +3929,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D104" s="29">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="8"/>
@@ -3932,17 +3944,17 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
-        <f t="shared" ref="A105:A136" si="3">A104+1</f>
+        <f t="shared" si="2"/>
         <v>104</v>
       </c>
       <c r="B105" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D105" s="29">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="8"/>
@@ -3951,17 +3963,17 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A106:A137" si="3">A105+1</f>
         <v>105</v>
       </c>
       <c r="B106" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D106" s="29">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="8"/>
@@ -3974,13 +3986,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D107" s="29">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="8"/>
@@ -3988,31 +4000,23 @@
       <c r="H107" s="8"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="25">
+      <c r="A108" s="8">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
-      <c r="B108" s="25">
-        <v>1</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D108" s="26">
-        <v>46312</v>
-      </c>
-      <c r="E108" s="27">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F108" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="G108" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H108" s="25" t="s">
-        <v>11</v>
-      </c>
+      <c r="B108" s="8">
+        <v>10</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D108" s="29">
+        <v>46087</v>
+      </c>
+      <c r="E108" s="12"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="25">
@@ -4020,18 +4024,26 @@
         <v>108</v>
       </c>
       <c r="B109" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D109" s="26">
-        <v>46089</v>
-      </c>
-      <c r="E109" s="27"/>
-      <c r="F109" s="25"/>
-      <c r="G109" s="25"/>
-      <c r="H109" s="25"/>
+        <v>46312</v>
+      </c>
+      <c r="E109" s="27">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G109" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H109" s="25" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="25">
@@ -4039,13 +4051,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C110" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D110" s="26">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="E110" s="27"/>
       <c r="F110" s="25"/>
@@ -4058,13 +4070,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C111" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D111" s="26">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="E111" s="27"/>
       <c r="F111" s="25"/>
@@ -4077,13 +4089,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C112" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D112" s="26">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E112" s="27"/>
       <c r="F112" s="25"/>
@@ -4091,23 +4103,23 @@
       <c r="H112" s="25"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="42">
+      <c r="A113" s="25">
         <f t="shared" si="3"/>
         <v>112</v>
       </c>
-      <c r="B113" s="42">
-        <v>1</v>
-      </c>
-      <c r="C113" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D113" s="43">
-        <v>46312</v>
-      </c>
-      <c r="E113" s="44"/>
-      <c r="F113" s="42"/>
-      <c r="G113" s="42"/>
-      <c r="H113" s="42"/>
+      <c r="B113" s="25">
+        <v>5</v>
+      </c>
+      <c r="C113" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D113" s="26">
+        <v>46092</v>
+      </c>
+      <c r="E113" s="27"/>
+      <c r="F113" s="25"/>
+      <c r="G113" s="25"/>
+      <c r="H113" s="25"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="42">
@@ -4115,13 +4127,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D114" s="43">
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="E114" s="44"/>
       <c r="F114" s="42"/>
@@ -4134,13 +4146,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C115" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D115" s="43">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="E115" s="44"/>
       <c r="F115" s="42"/>
@@ -4153,13 +4165,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C116" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D116" s="43">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="E116" s="44"/>
       <c r="F116" s="42"/>
@@ -4172,13 +4184,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D117" s="43">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="E117" s="44"/>
       <c r="F117" s="42"/>
@@ -4186,31 +4198,23 @@
       <c r="H117" s="42"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="30">
+      <c r="A118" s="42">
         <f t="shared" si="3"/>
         <v>117</v>
       </c>
-      <c r="B118" s="30">
-        <v>1</v>
-      </c>
-      <c r="C118" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D118" s="59">
-        <v>46230</v>
-      </c>
-      <c r="E118" s="82">
-        <v>0.375</v>
-      </c>
-      <c r="F118" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G118" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H118" s="31" t="s">
-        <v>11</v>
-      </c>
+      <c r="B118" s="42">
+        <v>5</v>
+      </c>
+      <c r="C118" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D118" s="43">
+        <v>46097</v>
+      </c>
+      <c r="E118" s="44"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="42"/>
+      <c r="H118" s="42"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="30">
@@ -4218,13 +4222,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D119" s="59">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="E119" s="82">
         <v>0.375</v>
@@ -4245,13 +4249,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C120" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D120" s="59">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="E120" s="82">
         <v>0.375</v>
@@ -4272,13 +4276,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C121" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D121" s="59">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E121" s="82">
         <v>0.375</v>
@@ -4299,13 +4303,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C122" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D122" s="59">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="E122" s="82">
         <v>0.375</v>
@@ -4326,13 +4330,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C123" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D123" s="59">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="E123" s="82">
         <v>0.375</v>
@@ -4341,7 +4345,7 @@
         <v>19</v>
       </c>
       <c r="G123" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H123" s="31" t="s">
         <v>11</v>
@@ -4353,13 +4357,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C124" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D124" s="59">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E124" s="82">
         <v>0.375</v>
@@ -4380,13 +4384,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C125" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D125" s="59">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E125" s="82">
         <v>0.375</v>
@@ -4407,13 +4411,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C126" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D126" s="59">
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="E126" s="82">
         <v>0.375</v>
@@ -4422,7 +4426,7 @@
         <v>19</v>
       </c>
       <c r="G126" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H126" s="31" t="s">
         <v>11</v>
@@ -4434,13 +4438,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C127" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D127" s="59">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="E127" s="82">
         <v>0.375</v>
@@ -4461,13 +4465,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C128" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D128" s="59">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E128" s="82">
         <v>0.375</v>
@@ -4483,56 +4487,56 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="40">
+      <c r="A129" s="30">
         <f t="shared" si="3"/>
         <v>128</v>
       </c>
-      <c r="B129" s="40">
-        <v>2</v>
-      </c>
-      <c r="C129" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D129" s="60">
-        <v>46256</v>
-      </c>
-      <c r="E129" s="83">
+      <c r="B129" s="30">
+        <v>11</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D129" s="59">
+        <v>46323</v>
+      </c>
+      <c r="E129" s="82">
         <v>0.375</v>
       </c>
-      <c r="F129" s="41" t="s">
+      <c r="F129" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G129" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H129" s="41" t="s">
+      <c r="G129" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H129" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="54">
+      <c r="A130" s="40">
         <f t="shared" si="3"/>
         <v>129</v>
       </c>
-      <c r="B130" s="54">
-        <v>1</v>
-      </c>
-      <c r="C130" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D130" s="55">
-        <v>46367</v>
-      </c>
-      <c r="E130" s="95">
-        <v>0.6875</v>
-      </c>
-      <c r="F130" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G130" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="H130" s="54" t="s">
+      <c r="B130" s="40">
+        <v>2</v>
+      </c>
+      <c r="C130" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D130" s="60">
+        <v>46256</v>
+      </c>
+      <c r="E130" s="83">
+        <v>0.375</v>
+      </c>
+      <c r="F130" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H130" s="41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4542,16 +4546,16 @@
         <v>130</v>
       </c>
       <c r="B131" s="54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C131" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D131" s="55">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="E131" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F131" s="54" t="s">
         <v>52</v>
@@ -4569,16 +4573,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D132" s="55">
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="E132" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F132" s="54" t="s">
         <v>52</v>
@@ -4596,22 +4600,22 @@
         <v>132</v>
       </c>
       <c r="B133" s="54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C133" s="54" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D133" s="55">
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="E133" s="95">
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="F133" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G133" s="54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H133" s="54" t="s">
         <v>11</v>
@@ -4623,22 +4627,22 @@
         <v>133</v>
       </c>
       <c r="B134" s="54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C134" s="54" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D134" s="55">
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="E134" s="95">
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F134" s="54" t="s">
         <v>52</v>
       </c>
       <c r="G134" s="54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H134" s="54" t="s">
         <v>11</v>
@@ -4650,16 +4654,16 @@
         <v>134</v>
       </c>
       <c r="B135" s="54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C135" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D135" s="55">
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="E135" s="95">
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="F135" s="54" t="s">
         <v>52</v>
@@ -4677,16 +4681,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C136" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D136" s="55">
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="E136" s="95">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F136" s="54" t="s">
         <v>52</v>
@@ -4698,24 +4702,51 @@
         <v>11</v>
       </c>
     </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="54">
+        <f t="shared" si="3"/>
+        <v>136</v>
+      </c>
+      <c r="B137" s="54">
+        <v>6</v>
+      </c>
+      <c r="C137" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D137" s="55">
+        <v>46404</v>
+      </c>
+      <c r="E137" s="95">
+        <v>0.375</v>
+      </c>
+      <c r="F137" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="G137" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="H137" s="54" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H112" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H112">
-      <sortCondition ref="A1:A112"/>
+  <autoFilter ref="A1:H113" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H113">
+      <sortCondition ref="A1:A113"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="52" max="16383" man="1"/>
-    <brk id="62" max="16383" man="1"/>
+    <brk id="53" max="16383" man="1"/>
+    <brk id="63" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="84" customWidth="1"/>
@@ -4777,7 +4808,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="96">
-        <f t="shared" ref="D2:D39" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
+        <f t="shared" ref="D2:D40" si="0">IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00")))))))))</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="E2" s="96" t="str">
@@ -4816,7 +4847,7 @@
         <v>0.75</v>
       </c>
       <c r="D3" s="96">
-        <f t="shared" ref="D3:D16" si="1">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
+        <f t="shared" ref="D3:D17" si="1">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00")))))))))</f>
         <v>0.82291666666666663</v>
       </c>
       <c r="E3" s="96" t="str">
@@ -5323,102 +5354,104 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="111" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" s="116" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="84"/>
       <c r="B16" s="81">
         <f>'Nach Mannschaften sortiert'!D16</f>
-        <v>46445</v>
+        <v>46264</v>
       </c>
       <c r="C16" s="96">
         <f>'Nach Mannschaften sortiert'!E16</f>
+        <v>0.4375</v>
+      </c>
+      <c r="D16" s="96">
+        <f t="shared" ref="D16" si="2">IF(I16 = "KM",C16+"1:45",IF(I16="U23",C16+"1:45",IF(I16 = "U16",C16+"1:45",IF(I16 = "U15",C16+"1:30",IF(I16 = "U14",C16+"1:30",IF(I16 = "U13",C16+"1:35",IF(I16 = "U12",C16+"1:10",IF(I16 = "U11",C16+"1:10",IF(I16 = "U10",C16+"1:03",C16+"3:00")))))))))</f>
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E16" s="96" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
+        <v>THERESIENFELD</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="116" t="str">
+        <f>'Nach Mannschaften sortiert'!H16</f>
+        <v>Auswärts</v>
+      </c>
+      <c r="H16" s="116" t="str">
+        <f>'Nach Mannschaften sortiert'!G16</f>
+        <v>SPG Theresienfeld</v>
+      </c>
+      <c r="I16" s="116" t="str">
+        <f>'Nach Mannschaften sortiert'!C16</f>
+        <v>U16</v>
+      </c>
+      <c r="J16" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16" s="116" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="116" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="111" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="84"/>
+      <c r="B17" s="81">
+        <f>'Nach Mannschaften sortiert'!D17</f>
+        <v>46445</v>
+      </c>
+      <c r="C17" s="96">
+        <f>'Nach Mannschaften sortiert'!E17</f>
         <v>0.5</v>
       </c>
-      <c r="D16" s="96">
+      <c r="D17" s="96">
         <f t="shared" si="1"/>
         <v>0.57291666666666663</v>
       </c>
-      <c r="E16" s="96" t="str">
-        <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
+      <c r="E17" s="96" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
         <v>BAD ERLACH</v>
       </c>
-      <c r="F16" s="84"/>
-      <c r="G16" s="115" t="str">
-        <f>'Nach Mannschaften sortiert'!H16</f>
+      <c r="F17" s="84"/>
+      <c r="G17" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Auswärts</v>
       </c>
-      <c r="H16" s="115" t="str">
-        <f>'Nach Mannschaften sortiert'!G16</f>
+      <c r="H17" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!G17</f>
         <v>Bad Erlach</v>
       </c>
-      <c r="I16" s="115" t="str">
-        <f>'Nach Mannschaften sortiert'!C16</f>
+      <c r="I17" s="115" t="str">
+        <f>'Nach Mannschaften sortiert'!C17</f>
         <v>KM</v>
       </c>
-      <c r="J16" s="84" t="s">
+      <c r="J17" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="115" t="s">
+      <c r="K17" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="L16" s="115" t="s">
+      <c r="L17" s="115" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="81">
-        <f>'Nach Mannschaften sortiert'!D17</f>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="81">
+        <f>'Nach Mannschaften sortiert'!D18</f>
         <v>46250</v>
       </c>
-      <c r="C17" s="96">
-        <f>'Nach Mannschaften sortiert'!E17</f>
+      <c r="C18" s="96">
+        <f>'Nach Mannschaften sortiert'!E18</f>
         <v>0.72916666666666663</v>
       </c>
-      <c r="D17" s="96">
+      <c r="D18" s="96">
         <f t="shared" si="0"/>
         <v>0.80208333333333326</v>
       </c>
-      <c r="E17" s="96" t="str">
-        <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
-        <v>KITTSEE</v>
-      </c>
-      <c r="G17" t="str">
-        <f>'Nach Mannschaften sortiert'!H17</f>
-        <v>Auswärts</v>
-      </c>
-      <c r="H17" t="str">
-        <f>'Nach Mannschaften sortiert'!G17</f>
-        <v>Kittsee</v>
-      </c>
-      <c r="I17" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
-        <v>KM</v>
-      </c>
-      <c r="J17" s="84" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="81">
-        <f>'Nach Mannschaften sortiert'!D18</f>
-        <v>46255</v>
-      </c>
-      <c r="C18" s="96">
-        <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D18" s="96">
-        <f t="shared" si="0"/>
-        <v>0.90625</v>
-      </c>
       <c r="E18" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G18" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
@@ -5426,7 +5459,7 @@
       </c>
       <c r="H18" t="str">
         <f>'Nach Mannschaften sortiert'!G18</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I18" t="str">
         <f>'Nach Mannschaften sortiert'!C18</f>
@@ -5442,30 +5475,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B19" s="81">
         <f>'Nach Mannschaften sortiert'!D19</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C19" s="96">
         <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D19" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.90625</v>
       </c>
       <c r="E19" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G19" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H19" t="str">
         <f>'Nach Mannschaften sortiert'!G19</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I19" t="str">
         <f>'Nach Mannschaften sortiert'!C19</f>
@@ -5481,30 +5514,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B20" s="81">
         <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C20" s="96">
         <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D20" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E20" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G20" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H20" t="str">
         <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I20" t="str">
         <f>'Nach Mannschaften sortiert'!C20</f>
@@ -5520,30 +5553,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B21" s="81">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C21" s="96">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="D21" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E21" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G21" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H21" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I21" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
@@ -5559,30 +5592,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B22" s="81">
         <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C22" s="96">
         <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D22" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E22" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G22" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H22" t="str">
         <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I22" t="str">
         <f>'Nach Mannschaften sortiert'!C22</f>
@@ -5598,30 +5631,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B23" s="81">
         <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C23" s="96">
         <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D23" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E23" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G23" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H23" t="str">
         <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I23" t="str">
         <f>'Nach Mannschaften sortiert'!C23</f>
@@ -5637,30 +5670,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B24" s="81">
         <f>'Nach Mannschaften sortiert'!D24</f>
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="C24" s="96">
         <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D24" s="96">
         <f t="shared" si="0"/>
-        <v>0.86458333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E24" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G24" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H24" t="str">
         <f>'Nach Mannschaften sortiert'!G24</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I24" t="str">
         <f>'Nach Mannschaften sortiert'!C24</f>
@@ -5676,30 +5709,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B25" s="81">
         <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="C25" s="96">
         <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D25" s="96">
         <f t="shared" si="0"/>
-        <v>0.88541666666666663</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E25" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G25" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H25" t="str">
         <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I25" t="str">
         <f>'Nach Mannschaften sortiert'!C25</f>
@@ -5715,10 +5748,10 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B26" s="81">
         <f>'Nach Mannschaften sortiert'!D26</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C26" s="96">
         <f>'Nach Mannschaften sortiert'!E26</f>
@@ -5730,15 +5763,15 @@
       </c>
       <c r="E26" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G26" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H26" t="str">
         <f>'Nach Mannschaften sortiert'!G26</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I26" t="str">
         <f>'Nach Mannschaften sortiert'!C26</f>
@@ -5754,30 +5787,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B27" s="81">
         <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C27" s="96">
         <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D27" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E27" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G27" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H27" t="str">
         <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I27" t="str">
         <f>'Nach Mannschaften sortiert'!C27</f>
@@ -5793,30 +5826,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B28" s="81">
         <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C28" s="96">
         <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D28" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.78125</v>
       </c>
       <c r="E28" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G28" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H28" t="str">
         <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I28" t="str">
         <f>'Nach Mannschaften sortiert'!C28</f>
@@ -5832,30 +5865,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B29" s="81">
         <f>'Nach Mannschaften sortiert'!D29</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C29" s="96">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="D29" s="96">
         <f t="shared" si="0"/>
-        <v>0.76041666666666663</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E29" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G29" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H29" t="str">
         <f>'Nach Mannschaften sortiert'!G29</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I29" t="str">
         <f>'Nach Mannschaften sortiert'!C29</f>
@@ -5871,34 +5904,34 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" s="81">
         <f>'Nach Mannschaften sortiert'!D30</f>
-        <v>46250</v>
+        <v>46333</v>
       </c>
       <c r="C30" s="96">
         <f>'Nach Mannschaften sortiert'!E30</f>
-        <v>0.64583333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D30" s="96">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E30" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
-        <v>KITTSEE</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G30" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H30" t="str">
         <f>'Nach Mannschaften sortiert'!G30</f>
-        <v>Kittsee</v>
+        <v>Andau</v>
       </c>
       <c r="I30" t="str">
         <f>'Nach Mannschaften sortiert'!C30</f>
-        <v>U23</v>
+        <v>KM</v>
       </c>
       <c r="J30" s="84" t="s">
         <v>68</v>
@@ -5910,22 +5943,22 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B31" s="81">
         <f>'Nach Mannschaften sortiert'!D31</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="C31" s="96">
         <f>'Nach Mannschaften sortiert'!E31</f>
-        <v>0.75</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D31" s="96">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.71875</v>
       </c>
       <c r="E31" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
-        <v>DEUTSCH JAHRNDORF</v>
+        <v>KITTSEE</v>
       </c>
       <c r="G31" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
@@ -5933,7 +5966,7 @@
       </c>
       <c r="H31" t="str">
         <f>'Nach Mannschaften sortiert'!G31</f>
-        <v>Deutsch Jahrndorf</v>
+        <v>Kittsee</v>
       </c>
       <c r="I31" t="str">
         <f>'Nach Mannschaften sortiert'!C31</f>
@@ -5949,30 +5982,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B32" s="81">
         <f>'Nach Mannschaften sortiert'!D32</f>
-        <v>46263</v>
+        <v>46255</v>
       </c>
       <c r="C32" s="96">
         <f>'Nach Mannschaften sortiert'!E32</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D32" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E32" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
-        <v>NEUFELD</v>
+        <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="G32" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H32" t="str">
         <f>'Nach Mannschaften sortiert'!G32</f>
-        <v>Tadten</v>
+        <v>Deutsch Jahrndorf</v>
       </c>
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
@@ -5991,27 +6024,27 @@
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="81">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="C33" s="96">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D33" s="96">
         <f t="shared" si="0"/>
-        <v>0.67708333333333326</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E33" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
-        <v>MÖNCHHOF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G33" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H33" t="str">
         <f>'Nach Mannschaften sortiert'!G33</f>
-        <v>Mönchhof</v>
+        <v>Tadten</v>
       </c>
       <c r="I33" t="str">
         <f>'Nach Mannschaften sortiert'!C33</f>
@@ -6030,27 +6063,27 @@
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="81">
         <f>'Nach Mannschaften sortiert'!D34</f>
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="C34" s="96">
         <f>'Nach Mannschaften sortiert'!E34</f>
-        <v>0.72916666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D34" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E34" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v>NEUFELD</v>
+        <v>MÖNCHHOF</v>
       </c>
       <c r="G34" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H34" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
-        <v>Winden</v>
+        <v>Mönchhof</v>
       </c>
       <c r="I34" t="str">
         <f>'Nach Mannschaften sortiert'!C34</f>
@@ -6069,27 +6102,27 @@
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="81">
         <f>'Nach Mannschaften sortiert'!D35</f>
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="C35" s="96">
         <f>'Nach Mannschaften sortiert'!E35</f>
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D35" s="96">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E35" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
-        <v>GATTENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G35" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H35" t="str">
         <f>'Nach Mannschaften sortiert'!G35</f>
-        <v>Gattendorf</v>
+        <v>Winden</v>
       </c>
       <c r="I35" t="str">
         <f>'Nach Mannschaften sortiert'!C35</f>
@@ -6108,27 +6141,27 @@
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="81">
         <f>'Nach Mannschaften sortiert'!D36</f>
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="C36" s="96">
         <f>'Nach Mannschaften sortiert'!E36</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D36" s="96">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.65625</v>
       </c>
       <c r="E36" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
-        <v>NEUFELD</v>
+        <v>GATTENDORF</v>
       </c>
       <c r="G36" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H36" t="str">
         <f>'Nach Mannschaften sortiert'!G36</f>
-        <v>Wallern</v>
+        <v>Gattendorf</v>
       </c>
       <c r="I36" t="str">
         <f>'Nach Mannschaften sortiert'!C36</f>
@@ -6147,27 +6180,27 @@
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="81">
         <f>'Nach Mannschaften sortiert'!D37</f>
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="C37" s="96">
         <f>'Nach Mannschaften sortiert'!E37</f>
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D37" s="96">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E37" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
-        <v>SIEGENDORF</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G37" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H37" t="str">
         <f>'Nach Mannschaften sortiert'!G37</f>
-        <v>Siegendorf</v>
+        <v>Wallern</v>
       </c>
       <c r="I37" t="str">
         <f>'Nach Mannschaften sortiert'!C37</f>
@@ -6186,27 +6219,27 @@
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="81">
         <f>'Nach Mannschaften sortiert'!D38</f>
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="C38" s="96">
         <f>'Nach Mannschaften sortiert'!E38</f>
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="96">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.78125</v>
       </c>
       <c r="E38" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
-        <v>NEUFELD</v>
+        <v>SIEGENDORF</v>
       </c>
       <c r="G38" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H38" t="str">
         <f>'Nach Mannschaften sortiert'!G38</f>
-        <v>Wimpassing</v>
+        <v>Siegendorf</v>
       </c>
       <c r="I38" t="str">
         <f>'Nach Mannschaften sortiert'!C38</f>
@@ -6225,7 +6258,7 @@
     <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="81">
         <f>'Nach Mannschaften sortiert'!D39</f>
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="C39" s="96">
         <f>'Nach Mannschaften sortiert'!E39</f>
@@ -6237,15 +6270,15 @@
       </c>
       <c r="E39" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
-        <v>HORNSTEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G39" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H39" t="str">
         <f>'Nach Mannschaften sortiert'!G39</f>
-        <v>Hornstein</v>
+        <v>Wimpassing</v>
       </c>
       <c r="I39" t="str">
         <f>'Nach Mannschaften sortiert'!C39</f>
@@ -6264,27 +6297,27 @@
     <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="81">
         <f>'Nach Mannschaften sortiert'!D40</f>
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="C40" s="96">
         <f>'Nach Mannschaften sortiert'!E40</f>
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D40" s="96">
-        <f t="shared" ref="D40:D71" si="2">IF(I40 = "KM",C40+"1:45",IF(I40="U23",C40+"1:45",IF(I40 = "U16",C40+"1:45",IF(I40 = "U15",C40+"1:30",IF(I40 = "U14",C40+"1:30",IF(I40 = "U13",C40+"1:35",IF(I40 = "U12",C40+"1:10",IF(I40 = "U11",C40+"1:10",IF(I40 = "U10",C40+"1:03",C40+"3:00")))))))))</f>
-        <v>0.69791666666666663</v>
+        <f t="shared" si="0"/>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E40" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
-        <v>NEUFELD</v>
+        <v>HORNSTEIN</v>
       </c>
       <c r="G40" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H40" t="str">
         <f>'Nach Mannschaften sortiert'!G40</f>
-        <v>Gols</v>
+        <v>Hornstein</v>
       </c>
       <c r="I40" t="str">
         <f>'Nach Mannschaften sortiert'!C40</f>
@@ -6303,27 +6336,27 @@
     <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="81">
         <f>'Nach Mannschaften sortiert'!D41</f>
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="C41" s="96">
         <f>'Nach Mannschaften sortiert'!E41</f>
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D41" s="96">
-        <f t="shared" si="2"/>
-        <v>0.73958333333333326</v>
+        <f t="shared" ref="D41:D72" si="3">IF(I41 = "KM",C41+"1:45",IF(I41="U23",C41+"1:45",IF(I41 = "U16",C41+"1:45",IF(I41 = "U15",C41+"1:30",IF(I41 = "U14",C41+"1:30",IF(I41 = "U13",C41+"1:35",IF(I41 = "U12",C41+"1:10",IF(I41 = "U11",C41+"1:10",IF(I41 = "U10",C41+"1:03",C41+"3:00")))))))))</f>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E41" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F41)</f>
-        <v>ILLMITZ</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G41" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H41" t="str">
         <f>'Nach Mannschaften sortiert'!G41</f>
-        <v>Illmitz</v>
+        <v>Gols</v>
       </c>
       <c r="I41" t="str">
         <f>'Nach Mannschaften sortiert'!C41</f>
@@ -6342,27 +6375,27 @@
     <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="81">
         <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="C42" s="96">
         <f>'Nach Mannschaften sortiert'!E42</f>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D42" s="96">
-        <f t="shared" si="2"/>
-        <v>0.67708333333333326</v>
+        <f t="shared" si="3"/>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E42" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
-        <v>NEUFELD</v>
+        <v>ILLMITZ</v>
       </c>
       <c r="G42" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>
-        <v>Heim</v>
+        <v>Auswärts</v>
       </c>
       <c r="H42" t="str">
         <f>'Nach Mannschaften sortiert'!G42</f>
-        <v>Andau</v>
+        <v>Illmitz</v>
       </c>
       <c r="I42" t="str">
         <f>'Nach Mannschaften sortiert'!C42</f>
@@ -6381,31 +6414,31 @@
     <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="81">
         <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46023</v>
+        <v>46333</v>
       </c>
       <c r="C43" s="96">
         <f>'Nach Mannschaften sortiert'!E43</f>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D43" s="96">
-        <f t="shared" si="2"/>
-        <v>7.2916666666666671E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.67708333333333326</v>
       </c>
       <c r="E43" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F43)</f>
-        <v/>
-      </c>
-      <c r="G43">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G43" t="str">
         <f>'Nach Mannschaften sortiert'!H43</f>
-        <v>0</v>
-      </c>
-      <c r="H43">
+        <v>Heim</v>
+      </c>
+      <c r="H43" t="str">
         <f>'Nach Mannschaften sortiert'!G43</f>
-        <v>0</v>
+        <v>Andau</v>
       </c>
       <c r="I43" t="str">
         <f>'Nach Mannschaften sortiert'!C43</f>
-        <v>U16</v>
+        <v>U23</v>
       </c>
       <c r="J43" s="84" t="s">
         <v>68</v>
@@ -6420,14 +6453,14 @@
     <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="81">
         <f>'Nach Mannschaften sortiert'!D44</f>
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C44" s="96">
         <f>'Nach Mannschaften sortiert'!E44</f>
         <v>0</v>
       </c>
       <c r="D44" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E44" s="96" t="str">
@@ -6459,14 +6492,14 @@
     <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="81">
         <f>'Nach Mannschaften sortiert'!D45</f>
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C45" s="96">
         <f>'Nach Mannschaften sortiert'!E45</f>
         <v>0</v>
       </c>
       <c r="D45" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E45" s="96" t="str">
@@ -6498,14 +6531,14 @@
     <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="81">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C46" s="96">
         <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0</v>
       </c>
       <c r="D46" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E46" s="96" t="str">
@@ -6537,14 +6570,14 @@
     <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="81">
         <f>'Nach Mannschaften sortiert'!D47</f>
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C47" s="96">
         <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="D47" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E47" s="96" t="str">
@@ -6576,14 +6609,14 @@
     <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="81">
         <f>'Nach Mannschaften sortiert'!D48</f>
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C48" s="96">
         <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="D48" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E48" s="96" t="str">
@@ -6615,14 +6648,14 @@
     <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="81">
         <f>'Nach Mannschaften sortiert'!D49</f>
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C49" s="96">
         <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="D49" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E49" s="96" t="str">
@@ -6654,14 +6687,14 @@
     <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="81">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C50" s="96">
         <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="D50" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E50" s="96" t="str">
@@ -6693,14 +6726,14 @@
     <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="81">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C51" s="96">
         <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="D51" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E51" s="96" t="str">
@@ -6732,14 +6765,14 @@
     <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="81">
         <f>'Nach Mannschaften sortiert'!D52</f>
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C52" s="96">
         <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="D52" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="E52" s="96" t="str">
@@ -6771,15 +6804,15 @@
     <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="81">
         <f>'Nach Mannschaften sortiert'!D53</f>
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C53" s="96">
         <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="D53" s="96">
-        <f t="shared" si="2"/>
-        <v>6.25E-2</v>
+        <f t="shared" si="3"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="E53" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F53)</f>
@@ -6795,7 +6828,7 @@
       </c>
       <c r="I53" t="str">
         <f>'Nach Mannschaften sortiert'!C53</f>
-        <v>U14</v>
+        <v>U16</v>
       </c>
       <c r="J53" s="84" t="s">
         <v>68</v>
@@ -6810,14 +6843,14 @@
     <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="81">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C54" s="96">
         <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="D54" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E54" s="96" t="str">
@@ -6849,14 +6882,14 @@
     <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="81">
         <f>'Nach Mannschaften sortiert'!D55</f>
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C55" s="96">
         <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
       <c r="D55" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E55" s="96" t="str">
@@ -6888,14 +6921,14 @@
     <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="81">
         <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C56" s="96">
         <f>'Nach Mannschaften sortiert'!E56</f>
         <v>0</v>
       </c>
       <c r="D56" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E56" s="96" t="str">
@@ -6927,14 +6960,14 @@
     <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="81">
         <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="C57" s="96">
         <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
       <c r="D57" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E57" s="96" t="str">
@@ -6966,14 +6999,14 @@
     <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="81">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="C58" s="96">
         <f>'Nach Mannschaften sortiert'!E58</f>
         <v>0</v>
       </c>
       <c r="D58" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E58" s="96" t="str">
@@ -7005,14 +7038,14 @@
     <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="81">
         <f>'Nach Mannschaften sortiert'!D59</f>
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C59" s="96">
         <f>'Nach Mannschaften sortiert'!E59</f>
         <v>0</v>
       </c>
       <c r="D59" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E59" s="96" t="str">
@@ -7044,14 +7077,14 @@
     <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="81">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C60" s="96">
         <f>'Nach Mannschaften sortiert'!E60</f>
         <v>0</v>
       </c>
       <c r="D60" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E60" s="96" t="str">
@@ -7083,14 +7116,14 @@
     <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="81">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C61" s="96">
         <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="D61" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E61" s="96" t="str">
@@ -7122,14 +7155,14 @@
     <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="81">
         <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C62" s="96">
         <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="D62" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.25E-2</v>
       </c>
       <c r="E62" s="96" t="str">
@@ -7161,15 +7194,15 @@
     <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="81">
         <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C63" s="96">
         <f>'Nach Mannschaften sortiert'!E63</f>
         <v>0</v>
       </c>
       <c r="D63" s="96">
-        <f t="shared" si="2"/>
-        <v>0.125</v>
+        <f t="shared" si="3"/>
+        <v>6.25E-2</v>
       </c>
       <c r="E63" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
@@ -7185,7 +7218,7 @@
       </c>
       <c r="I63" t="str">
         <f>'Nach Mannschaften sortiert'!C63</f>
-        <v>U12_1</v>
+        <v>U14</v>
       </c>
       <c r="J63" s="84" t="s">
         <v>68</v>
@@ -7200,14 +7233,14 @@
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="81">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C64" s="96">
         <f>'Nach Mannschaften sortiert'!E64</f>
         <v>0</v>
       </c>
       <c r="D64" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E64" s="96" t="str">
@@ -7239,14 +7272,14 @@
     <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="81">
         <f>'Nach Mannschaften sortiert'!D65</f>
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C65" s="96">
         <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="D65" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E65" s="96" t="str">
@@ -7278,14 +7311,14 @@
     <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="81">
         <f>'Nach Mannschaften sortiert'!D66</f>
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C66" s="96">
         <f>'Nach Mannschaften sortiert'!E66</f>
         <v>0</v>
       </c>
       <c r="D66" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E66" s="96" t="str">
@@ -7317,14 +7350,14 @@
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="81">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C67" s="96">
         <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="D67" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E67" s="96" t="str">
@@ -7356,14 +7389,14 @@
     <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="81">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46048</v>
+        <v>46047</v>
       </c>
       <c r="C68" s="96">
         <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="D68" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E68" s="96" t="str">
@@ -7395,14 +7428,14 @@
     <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="81">
         <f>'Nach Mannschaften sortiert'!D69</f>
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="C69" s="96">
         <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="D69" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E69" s="96" t="str">
@@ -7434,14 +7467,14 @@
     <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="81">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46050</v>
+        <v>46049</v>
       </c>
       <c r="C70" s="96">
         <f>'Nach Mannschaften sortiert'!E70</f>
         <v>0</v>
       </c>
       <c r="D70" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E70" s="96" t="str">
@@ -7473,14 +7506,14 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="81">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C71" s="96">
         <f>'Nach Mannschaften sortiert'!E71</f>
         <v>0</v>
       </c>
       <c r="D71" s="96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E71" s="96" t="str">
@@ -7512,14 +7545,14 @@
     <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="81">
         <f>'Nach Mannschaften sortiert'!D72</f>
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="C72" s="96">
         <f>'Nach Mannschaften sortiert'!E72</f>
         <v>0</v>
       </c>
       <c r="D72" s="96">
-        <f t="shared" ref="D72:D92" si="3">IF(I72 = "KM",C72+"1:45",IF(I72="U23",C72+"1:45",IF(I72 = "U16",C72+"1:45",IF(I72 = "U15",C72+"1:30",IF(I72 = "U14",C72+"1:30",IF(I72 = "U13",C72+"1:35",IF(I72 = "U12",C72+"1:10",IF(I72 = "U11",C72+"1:10",IF(I72 = "U10",C72+"1:03",C72+"3:00")))))))))</f>
+        <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
       <c r="E72" s="96" t="str">
@@ -7551,14 +7584,14 @@
     <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="81">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C73" s="96">
         <f>'Nach Mannschaften sortiert'!E73</f>
         <v>0</v>
       </c>
       <c r="D73" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D73:D93" si="4">IF(I73 = "KM",C73+"1:45",IF(I73="U23",C73+"1:45",IF(I73 = "U16",C73+"1:45",IF(I73 = "U15",C73+"1:30",IF(I73 = "U14",C73+"1:30",IF(I73 = "U13",C73+"1:35",IF(I73 = "U12",C73+"1:10",IF(I73 = "U11",C73+"1:10",IF(I73 = "U10",C73+"1:03",C73+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E73" s="96" t="str">
@@ -7575,7 +7608,7 @@
       </c>
       <c r="I73" t="str">
         <f>'Nach Mannschaften sortiert'!C73</f>
-        <v>U12_2</v>
+        <v>U12_1</v>
       </c>
       <c r="J73" s="84" t="s">
         <v>68</v>
@@ -7590,14 +7623,14 @@
     <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="81">
         <f>'Nach Mannschaften sortiert'!D74</f>
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="C74" s="96">
         <f>'Nach Mannschaften sortiert'!E74</f>
         <v>0</v>
       </c>
       <c r="D74" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E74" s="96" t="str">
@@ -7629,14 +7662,14 @@
     <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" s="81">
         <f>'Nach Mannschaften sortiert'!D75</f>
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C75" s="96">
         <f>'Nach Mannschaften sortiert'!E75</f>
         <v>0</v>
       </c>
       <c r="D75" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E75" s="96" t="str">
@@ -7668,14 +7701,14 @@
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="81">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C76" s="96">
         <f>'Nach Mannschaften sortiert'!E76</f>
         <v>0</v>
       </c>
       <c r="D76" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E76" s="96" t="str">
@@ -7707,14 +7740,14 @@
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="81">
         <f>'Nach Mannschaften sortiert'!D77</f>
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="C77" s="96">
         <f>'Nach Mannschaften sortiert'!E77</f>
         <v>0</v>
       </c>
       <c r="D77" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E77" s="96" t="str">
@@ -7746,14 +7779,14 @@
     <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="81">
         <f>'Nach Mannschaften sortiert'!D78</f>
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C78" s="96">
         <f>'Nach Mannschaften sortiert'!E78</f>
         <v>0</v>
       </c>
       <c r="D78" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E78" s="96" t="str">
@@ -7785,14 +7818,14 @@
     <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79" s="81">
         <f>'Nach Mannschaften sortiert'!D79</f>
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="C79" s="96">
         <f>'Nach Mannschaften sortiert'!E79</f>
         <v>0</v>
       </c>
       <c r="D79" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E79" s="96" t="str">
@@ -7824,14 +7857,14 @@
     <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80" s="81">
         <f>'Nach Mannschaften sortiert'!D80</f>
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="C80" s="96">
         <f>'Nach Mannschaften sortiert'!E80</f>
         <v>0</v>
       </c>
       <c r="D80" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E80" s="96" t="str">
@@ -7863,14 +7896,14 @@
     <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="81">
         <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C81" s="96">
         <f>'Nach Mannschaften sortiert'!E81</f>
         <v>0</v>
       </c>
       <c r="D81" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E81" s="96" t="str">
@@ -7902,14 +7935,14 @@
     <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="81">
         <f>'Nach Mannschaften sortiert'!D82</f>
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C82" s="96">
         <f>'Nach Mannschaften sortiert'!E82</f>
         <v>0</v>
       </c>
       <c r="D82" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.125</v>
       </c>
       <c r="E82" s="96" t="str">
@@ -7941,15 +7974,15 @@
     <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83" s="81">
         <f>'Nach Mannschaften sortiert'!D83</f>
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="C83" s="96">
         <f>'Nach Mannschaften sortiert'!E83</f>
         <v>0</v>
       </c>
       <c r="D83" s="96">
-        <f t="shared" si="3"/>
-        <v>4.8611111111111112E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.125</v>
       </c>
       <c r="E83" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F83)</f>
@@ -7965,7 +7998,7 @@
       </c>
       <c r="I83" t="str">
         <f>'Nach Mannschaften sortiert'!C83</f>
-        <v>U11</v>
+        <v>U12_2</v>
       </c>
       <c r="J83" s="84" t="s">
         <v>68</v>
@@ -7980,14 +8013,14 @@
     <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="81">
         <f>'Nach Mannschaften sortiert'!D84</f>
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C84" s="96">
         <f>'Nach Mannschaften sortiert'!E84</f>
         <v>0</v>
       </c>
       <c r="D84" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E84" s="96" t="str">
@@ -8019,14 +8052,14 @@
     <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="81">
         <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C85" s="96">
         <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="D85" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E85" s="96" t="str">
@@ -8058,14 +8091,14 @@
     <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86" s="81">
         <f>'Nach Mannschaften sortiert'!D86</f>
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C86" s="96">
         <f>'Nach Mannschaften sortiert'!E86</f>
         <v>0</v>
       </c>
       <c r="D86" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E86" s="96" t="str">
@@ -8097,14 +8130,14 @@
     <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="81">
         <f>'Nach Mannschaften sortiert'!D87</f>
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="C87" s="96">
         <f>'Nach Mannschaften sortiert'!E87</f>
         <v>0</v>
       </c>
       <c r="D87" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E87" s="96" t="str">
@@ -8136,14 +8169,14 @@
     <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="81">
         <f>'Nach Mannschaften sortiert'!D88</f>
-        <v>46068</v>
+        <v>46067</v>
       </c>
       <c r="C88" s="96">
         <f>'Nach Mannschaften sortiert'!E88</f>
         <v>0</v>
       </c>
       <c r="D88" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E88" s="96" t="str">
@@ -8175,14 +8208,14 @@
     <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89" s="81">
         <f>'Nach Mannschaften sortiert'!D89</f>
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="C89" s="96">
         <f>'Nach Mannschaften sortiert'!E89</f>
         <v>0</v>
       </c>
       <c r="D89" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E89" s="96" t="str">
@@ -8214,14 +8247,14 @@
     <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90" s="81">
         <f>'Nach Mannschaften sortiert'!D90</f>
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="C90" s="96">
         <f>'Nach Mannschaften sortiert'!E90</f>
         <v>0</v>
       </c>
       <c r="D90" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E90" s="96" t="str">
@@ -8253,14 +8286,14 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="81">
         <f>'Nach Mannschaften sortiert'!D91</f>
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="C91" s="96">
         <f>'Nach Mannschaften sortiert'!E91</f>
         <v>0</v>
       </c>
       <c r="D91" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E91" s="96" t="str">
@@ -8292,14 +8325,14 @@
     <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92" s="81">
         <f>'Nach Mannschaften sortiert'!D92</f>
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C92" s="96">
         <f>'Nach Mannschaften sortiert'!E92</f>
         <v>0</v>
       </c>
       <c r="D92" s="96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.8611111111111112E-2</v>
       </c>
       <c r="E92" s="96" t="str">
@@ -8331,30 +8364,31 @@
     <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="81">
         <f>'Nach Mannschaften sortiert'!D93</f>
-        <v>46312</v>
+        <v>46072</v>
       </c>
       <c r="C93" s="96">
         <f>'Nach Mannschaften sortiert'!E93</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D93" s="96">
-        <v>0.5</v>
+        <f t="shared" si="4"/>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="E93" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F93)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="G93">
         <f>'Nach Mannschaften sortiert'!H93</f>
-        <v>Heim</v>
-      </c>
-      <c r="H93" t="str">
+        <v>0</v>
+      </c>
+      <c r="H93">
         <f>'Nach Mannschaften sortiert'!G93</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>'Nach Mannschaften sortiert'!C93</f>
-        <v>U10</v>
+        <v>U11</v>
       </c>
       <c r="J93" s="84" t="s">
         <v>68</v>
@@ -8369,27 +8403,26 @@
     <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="81">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46074</v>
+        <v>46312</v>
       </c>
       <c r="C94" s="96">
         <f>'Nach Mannschaften sortiert'!E94</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D94" s="96">
-        <f t="shared" ref="D94:D107" si="4">IF(I94 = "KM",C94+"1:45",IF(I94="U23",C94+"1:45",IF(I94 = "U16",C94+"1:45",IF(I94 = "U15",C94+"1:30",IF(I94 = "U14",C94+"1:30",IF(I94 = "U13",C94+"1:35",IF(I94 = "U12",C94+"1:10",IF(I94 = "U11",C94+"1:10",IF(I94 = "U10",C94+"1:03",C94+"3:00")))))))))</f>
-        <v>4.3750000000000004E-2</v>
+        <v>0.5</v>
       </c>
       <c r="E94" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F94)</f>
-        <v/>
-      </c>
-      <c r="G94">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G94" t="str">
         <f>'Nach Mannschaften sortiert'!H94</f>
-        <v>0</v>
-      </c>
-      <c r="H94">
+        <v>Heim</v>
+      </c>
+      <c r="H94" t="str">
         <f>'Nach Mannschaften sortiert'!G94</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I94" t="str">
         <f>'Nach Mannschaften sortiert'!C94</f>
@@ -8408,14 +8441,14 @@
     <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95" s="81">
         <f>'Nach Mannschaften sortiert'!D95</f>
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="C95" s="96">
         <f>'Nach Mannschaften sortiert'!E95</f>
         <v>0</v>
       </c>
       <c r="D95" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D95:D108" si="5">IF(I95 = "KM",C95+"1:45",IF(I95="U23",C95+"1:45",IF(I95 = "U16",C95+"1:45",IF(I95 = "U15",C95+"1:30",IF(I95 = "U14",C95+"1:30",IF(I95 = "U13",C95+"1:35",IF(I95 = "U12",C95+"1:10",IF(I95 = "U11",C95+"1:10",IF(I95 = "U10",C95+"1:03",C95+"3:00")))))))))</f>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E95" s="96" t="str">
@@ -8447,14 +8480,14 @@
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="81">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="C96" s="96">
         <f>'Nach Mannschaften sortiert'!E96</f>
         <v>0</v>
       </c>
       <c r="D96" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E96" s="96" t="str">
@@ -8486,14 +8519,14 @@
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="81">
         <f>'Nach Mannschaften sortiert'!D97</f>
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C97" s="96">
         <f>'Nach Mannschaften sortiert'!E97</f>
         <v>0</v>
       </c>
       <c r="D97" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3750000000000004E-2</v>
       </c>
       <c r="E97" s="96" t="str">
@@ -8525,15 +8558,15 @@
     <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B98" s="81">
         <f>'Nach Mannschaften sortiert'!D98</f>
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C98" s="96">
         <f>'Nach Mannschaften sortiert'!E98</f>
         <v>0</v>
       </c>
       <c r="D98" s="96">
-        <f t="shared" si="4"/>
-        <v>0.125</v>
+        <f t="shared" si="5"/>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E98" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F98)</f>
@@ -8549,7 +8582,7 @@
       </c>
       <c r="I98" t="str">
         <f>'Nach Mannschaften sortiert'!C98</f>
-        <v>U9</v>
+        <v>U10</v>
       </c>
       <c r="J98" s="84" t="s">
         <v>68</v>
@@ -8564,14 +8597,14 @@
     <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B99" s="81">
         <f>'Nach Mannschaften sortiert'!D99</f>
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="C99" s="96">
         <f>'Nach Mannschaften sortiert'!E99</f>
         <v>0</v>
       </c>
       <c r="D99" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E99" s="96" t="str">
@@ -8603,14 +8636,14 @@
     <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100" s="81">
         <f>'Nach Mannschaften sortiert'!D100</f>
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C100" s="96">
         <f>'Nach Mannschaften sortiert'!E100</f>
         <v>0</v>
       </c>
       <c r="D100" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E100" s="96" t="str">
@@ -8642,14 +8675,14 @@
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101" s="81">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C101" s="96">
         <f>'Nach Mannschaften sortiert'!E101</f>
         <v>0</v>
       </c>
       <c r="D101" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E101" s="96" t="str">
@@ -8681,14 +8714,14 @@
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102" s="81">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C102" s="96">
         <f>'Nach Mannschaften sortiert'!E102</f>
         <v>0</v>
       </c>
       <c r="D102" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E102" s="96" t="str">
@@ -8720,14 +8753,14 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="81">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C103" s="96">
         <f>'Nach Mannschaften sortiert'!E103</f>
         <v>0</v>
       </c>
       <c r="D103" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E103" s="96" t="str">
@@ -8759,14 +8792,14 @@
     <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B104" s="81">
         <f>'Nach Mannschaften sortiert'!D104</f>
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C104" s="96">
         <f>'Nach Mannschaften sortiert'!E104</f>
         <v>0</v>
       </c>
       <c r="D104" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E104" s="96" t="str">
@@ -8798,14 +8831,14 @@
     <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105" s="81">
         <f>'Nach Mannschaften sortiert'!D105</f>
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C105" s="96">
         <f>'Nach Mannschaften sortiert'!E105</f>
         <v>0</v>
       </c>
       <c r="D105" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E105" s="96" t="str">
@@ -8837,14 +8870,14 @@
     <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106" s="81">
         <f>'Nach Mannschaften sortiert'!D106</f>
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C106" s="96">
         <f>'Nach Mannschaften sortiert'!E106</f>
         <v>0</v>
       </c>
       <c r="D106" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E106" s="96" t="str">
@@ -8876,14 +8909,14 @@
     <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B107" s="81">
         <f>'Nach Mannschaften sortiert'!D107</f>
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="C107" s="96">
         <f>'Nach Mannschaften sortiert'!E107</f>
         <v>0</v>
       </c>
       <c r="D107" s="96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
       <c r="E107" s="96" t="str">
@@ -8915,30 +8948,31 @@
     <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B108" s="81">
         <f>'Nach Mannschaften sortiert'!D108</f>
-        <v>46312</v>
+        <v>46087</v>
       </c>
       <c r="C108" s="96">
         <f>'Nach Mannschaften sortiert'!E108</f>
-        <v>0.39583333333333331</v>
+        <v>0</v>
       </c>
       <c r="D108" s="96">
-        <v>0.5</v>
+        <f t="shared" si="5"/>
+        <v>0.125</v>
       </c>
       <c r="E108" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F108)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="G108">
         <f>'Nach Mannschaften sortiert'!H108</f>
-        <v>Heim</v>
-      </c>
-      <c r="H108" t="str">
+        <v>0</v>
+      </c>
+      <c r="H108">
         <f>'Nach Mannschaften sortiert'!G108</f>
-        <v>Heimturnier</v>
+        <v>0</v>
       </c>
       <c r="I108" t="str">
         <f>'Nach Mannschaften sortiert'!C108</f>
-        <v>U8</v>
+        <v>U9</v>
       </c>
       <c r="J108" s="84" t="s">
         <v>68</v>
@@ -8953,27 +8987,26 @@
     <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109" s="81">
         <f>'Nach Mannschaften sortiert'!D109</f>
-        <v>46089</v>
+        <v>46312</v>
       </c>
       <c r="C109" s="96">
         <f>'Nach Mannschaften sortiert'!E109</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D109" s="96">
-        <f t="shared" ref="D109:D129" si="5">IF(I109 = "KM",C109+"1:45",IF(I109="U23",C109+"1:45",IF(I109 = "U16",C109+"1:45",IF(I109 = "U15",C109+"1:30",IF(I109 = "U14",C109+"1:30",IF(I109 = "U13",C109+"1:35",IF(I109 = "U12",C109+"1:10",IF(I109 = "U11",C109+"1:10",IF(I109 = "U10",C109+"1:03",C109+"3:00")))))))))</f>
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E109" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F109)</f>
-        <v/>
-      </c>
-      <c r="G109">
+        <v>NEUFELD</v>
+      </c>
+      <c r="G109" t="str">
         <f>'Nach Mannschaften sortiert'!H109</f>
-        <v>0</v>
-      </c>
-      <c r="H109">
+        <v>Heim</v>
+      </c>
+      <c r="H109" t="str">
         <f>'Nach Mannschaften sortiert'!G109</f>
-        <v>0</v>
+        <v>Heimturnier</v>
       </c>
       <c r="I109" t="str">
         <f>'Nach Mannschaften sortiert'!C109</f>
@@ -8992,14 +9025,14 @@
     <row r="110" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B110" s="81">
         <f>'Nach Mannschaften sortiert'!D110</f>
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="C110" s="96">
         <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="D110" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="D110:D130" si="6">IF(I110 = "KM",C110+"1:45",IF(I110="U23",C110+"1:45",IF(I110 = "U16",C110+"1:45",IF(I110 = "U15",C110+"1:30",IF(I110 = "U14",C110+"1:30",IF(I110 = "U13",C110+"1:35",IF(I110 = "U12",C110+"1:10",IF(I110 = "U11",C110+"1:10",IF(I110 = "U10",C110+"1:03",C110+"3:00")))))))))</f>
         <v>0.125</v>
       </c>
       <c r="E110" s="96" t="str">
@@ -9031,14 +9064,14 @@
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="81">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C111" s="96">
         <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="D111" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E111" s="96" t="str">
@@ -9070,14 +9103,14 @@
     <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112" s="81">
         <f>'Nach Mannschaften sortiert'!D112</f>
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C112" s="96">
         <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="D112" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E112" s="96" t="str">
@@ -9109,14 +9142,14 @@
     <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113" s="81">
         <f>'Nach Mannschaften sortiert'!D113</f>
-        <v>46312</v>
+        <v>46092</v>
       </c>
       <c r="C113" s="96">
         <f>'Nach Mannschaften sortiert'!E113</f>
         <v>0</v>
       </c>
       <c r="D113" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E113" s="96" t="str">
@@ -9133,7 +9166,7 @@
       </c>
       <c r="I113" t="str">
         <f>'Nach Mannschaften sortiert'!C113</f>
-        <v>U7</v>
+        <v>U8</v>
       </c>
       <c r="J113" s="84" t="s">
         <v>68</v>
@@ -9148,14 +9181,14 @@
     <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114" s="81">
         <f>'Nach Mannschaften sortiert'!D114</f>
-        <v>46094</v>
+        <v>46312</v>
       </c>
       <c r="C114" s="96">
         <f>'Nach Mannschaften sortiert'!E114</f>
         <v>0</v>
       </c>
       <c r="D114" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E114" s="96" t="str">
@@ -9187,14 +9220,14 @@
     <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115" s="81">
         <f>'Nach Mannschaften sortiert'!D115</f>
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="C115" s="96">
         <f>'Nach Mannschaften sortiert'!E115</f>
         <v>0</v>
       </c>
       <c r="D115" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E115" s="96" t="str">
@@ -9226,14 +9259,14 @@
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116" s="81">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="C116" s="96">
         <f>'Nach Mannschaften sortiert'!E116</f>
         <v>0</v>
       </c>
       <c r="D116" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E116" s="96" t="str">
@@ -9265,14 +9298,14 @@
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117" s="81">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="C117" s="96">
         <f>'Nach Mannschaften sortiert'!E117</f>
         <v>0</v>
       </c>
       <c r="D117" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.125</v>
       </c>
       <c r="E117" s="96" t="str">
@@ -9304,31 +9337,31 @@
     <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B118" s="81">
         <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46230</v>
+        <v>46097</v>
       </c>
       <c r="C118" s="96">
         <f>'Nach Mannschaften sortiert'!E118</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="D118" s="96">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>0.125</v>
       </c>
       <c r="E118" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F118)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="G118">
         <f>'Nach Mannschaften sortiert'!H118</f>
-        <v>Heim</v>
-      </c>
-      <c r="H118" t="str">
+        <v>0</v>
+      </c>
+      <c r="H118">
         <f>'Nach Mannschaften sortiert'!G118</f>
-        <v>REAL MADRID CAMP</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>'Nach Mannschaften sortiert'!C118</f>
-        <v>Camp</v>
+        <v>U7</v>
       </c>
       <c r="J118" s="84" t="s">
         <v>68</v>
@@ -9343,14 +9376,14 @@
     <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B119" s="81">
         <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="C119" s="96">
         <f>'Nach Mannschaften sortiert'!E119</f>
         <v>0.375</v>
       </c>
       <c r="D119" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E119" s="96" t="str">
@@ -9382,14 +9415,14 @@
     <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B120" s="81">
         <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="C120" s="96">
         <f>'Nach Mannschaften sortiert'!E120</f>
         <v>0.375</v>
       </c>
       <c r="D120" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E120" s="96" t="str">
@@ -9421,14 +9454,14 @@
     <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B121" s="81">
         <f>'Nach Mannschaften sortiert'!D121</f>
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="C121" s="96">
         <f>'Nach Mannschaften sortiert'!E121</f>
         <v>0.375</v>
       </c>
       <c r="D121" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E121" s="96" t="str">
@@ -9460,14 +9493,14 @@
     <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B122" s="81">
         <f>'Nach Mannschaften sortiert'!D122</f>
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="C122" s="96">
         <f>'Nach Mannschaften sortiert'!E122</f>
         <v>0.375</v>
       </c>
       <c r="D122" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E122" s="96" t="str">
@@ -9499,14 +9532,14 @@
     <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B123" s="81">
         <f>'Nach Mannschaften sortiert'!D123</f>
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="C123" s="96">
         <f>'Nach Mannschaften sortiert'!E123</f>
         <v>0.375</v>
       </c>
       <c r="D123" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E123" s="96" t="str">
@@ -9519,7 +9552,7 @@
       </c>
       <c r="H123" t="str">
         <f>'Nach Mannschaften sortiert'!G123</f>
-        <v>MÄDCHENCAMP</v>
+        <v>REAL MADRID CAMP</v>
       </c>
       <c r="I123" t="str">
         <f>'Nach Mannschaften sortiert'!C123</f>
@@ -9538,14 +9571,14 @@
     <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B124" s="81">
         <f>'Nach Mannschaften sortiert'!D124</f>
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C124" s="96">
         <f>'Nach Mannschaften sortiert'!E124</f>
         <v>0.375</v>
       </c>
       <c r="D124" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E124" s="96" t="str">
@@ -9577,14 +9610,14 @@
     <row r="125" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B125" s="81">
         <f>'Nach Mannschaften sortiert'!D125</f>
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="C125" s="96">
         <f>'Nach Mannschaften sortiert'!E125</f>
         <v>0.375</v>
       </c>
       <c r="D125" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E125" s="96" t="str">
@@ -9616,14 +9649,14 @@
     <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B126" s="81">
         <f>'Nach Mannschaften sortiert'!D126</f>
-        <v>46321</v>
+        <v>46239</v>
       </c>
       <c r="C126" s="96">
         <f>'Nach Mannschaften sortiert'!E126</f>
         <v>0.375</v>
       </c>
       <c r="D126" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E126" s="96" t="str">
@@ -9636,7 +9669,7 @@
       </c>
       <c r="H126" t="str">
         <f>'Nach Mannschaften sortiert'!G126</f>
-        <v>Teco 7 Camp</v>
+        <v>MÄDCHENCAMP</v>
       </c>
       <c r="I126" t="str">
         <f>'Nach Mannschaften sortiert'!C126</f>
@@ -9655,14 +9688,14 @@
     <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B127" s="81">
         <f>'Nach Mannschaften sortiert'!D127</f>
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C127" s="96">
         <f>'Nach Mannschaften sortiert'!E127</f>
         <v>0.375</v>
       </c>
       <c r="D127" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E127" s="96" t="str">
@@ -9694,14 +9727,14 @@
     <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B128" s="81">
         <f>'Nach Mannschaften sortiert'!D128</f>
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C128" s="96">
         <f>'Nach Mannschaften sortiert'!E128</f>
         <v>0.375</v>
       </c>
       <c r="D128" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E128" s="96" t="str">
@@ -9733,14 +9766,14 @@
     <row r="129" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B129" s="81">
         <f>'Nach Mannschaften sortiert'!D129</f>
-        <v>46256</v>
+        <v>46323</v>
       </c>
       <c r="C129" s="96">
         <f>'Nach Mannschaften sortiert'!E129</f>
         <v>0.375</v>
       </c>
       <c r="D129" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="E129" s="96" t="str">
@@ -9753,11 +9786,11 @@
       </c>
       <c r="H129" t="str">
         <f>'Nach Mannschaften sortiert'!G129</f>
-        <v>viele Gegner</v>
+        <v>Teco 7 Camp</v>
       </c>
       <c r="I129" t="str">
         <f>'Nach Mannschaften sortiert'!C129</f>
-        <v>GGG</v>
+        <v>Camp</v>
       </c>
       <c r="J129" s="84" t="s">
         <v>68</v>
@@ -9772,18 +9805,19 @@
     <row r="130" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B130" s="81">
         <f>'Nach Mannschaften sortiert'!D130</f>
-        <v>46367</v>
+        <v>46256</v>
       </c>
       <c r="C130" s="96">
         <f>'Nach Mannschaften sortiert'!E130</f>
-        <v>0.6875</v>
+        <v>0.375</v>
       </c>
       <c r="D130" s="96">
-        <v>0.875</v>
+        <f t="shared" si="6"/>
+        <v>0.5</v>
       </c>
       <c r="E130" s="96" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F130)</f>
-        <v>STEINBRUNN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G130" t="str">
         <f>'Nach Mannschaften sortiert'!H130</f>
@@ -9791,11 +9825,11 @@
       </c>
       <c r="H130" t="str">
         <f>'Nach Mannschaften sortiert'!G130</f>
-        <v>Hallencup 2026_27</v>
+        <v>viele Gegner</v>
       </c>
       <c r="I130" t="str">
         <f>'Nach Mannschaften sortiert'!C130</f>
-        <v>Hallenturnie</v>
+        <v>GGG</v>
       </c>
       <c r="J130" s="84" t="s">
         <v>68</v>
@@ -9810,11 +9844,11 @@
     <row r="131" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B131" s="81">
         <f>'Nach Mannschaften sortiert'!D131</f>
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="C131" s="96">
         <f>'Nach Mannschaften sortiert'!E131</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D131" s="96">
         <v>0.875</v>
@@ -9848,11 +9882,11 @@
     <row r="132" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B132" s="81">
         <f>'Nach Mannschaften sortiert'!D132</f>
-        <v>46369</v>
+        <v>46368</v>
       </c>
       <c r="C132" s="96">
         <f>'Nach Mannschaften sortiert'!E132</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D132" s="96">
         <v>0.875</v>
@@ -9886,11 +9920,11 @@
     <row r="133" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B133" s="81">
         <f>'Nach Mannschaften sortiert'!D133</f>
-        <v>46359</v>
+        <v>46369</v>
       </c>
       <c r="C133" s="96">
         <f>'Nach Mannschaften sortiert'!E133</f>
-        <v>0.70833333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="D133" s="96">
         <v>0.875</v>
@@ -9899,20 +9933,17 @@
         <f>UPPER('Nach Mannschaften sortiert'!F133)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="F133" s="84" t="s">
-        <v>72</v>
-      </c>
       <c r="G133" t="str">
         <f>'Nach Mannschaften sortiert'!H133</f>
         <v>Heim</v>
       </c>
       <c r="H133" t="str">
         <f>'Nach Mannschaften sortiert'!G133</f>
-        <v>Weihnachtsfeier 2026</v>
+        <v>Hallencup 2026_27</v>
       </c>
       <c r="I133" t="str">
         <f>'Nach Mannschaften sortiert'!C133</f>
-        <v>Weihnachtsfeier</v>
+        <v>Hallenturnie</v>
       </c>
       <c r="J133" s="84" t="s">
         <v>68</v>
@@ -9921,17 +9952,17 @@
         <v>71</v>
       </c>
       <c r="L133" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B134" s="81">
         <f>'Nach Mannschaften sortiert'!D134</f>
-        <v>46402</v>
+        <v>46359</v>
       </c>
       <c r="C134" s="96">
         <f>'Nach Mannschaften sortiert'!E134</f>
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D134" s="96">
         <v>0.875</v>
@@ -9940,17 +9971,20 @@
         <f>UPPER('Nach Mannschaften sortiert'!F134)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F134" s="84" t="s">
+        <v>72</v>
+      </c>
       <c r="G134" t="str">
         <f>'Nach Mannschaften sortiert'!H134</f>
         <v>Heim</v>
       </c>
       <c r="H134" t="str">
         <f>'Nach Mannschaften sortiert'!G134</f>
-        <v>Hallencup 2026_27</v>
+        <v>Weihnachtsfeier 2026</v>
       </c>
       <c r="I134" t="str">
         <f>'Nach Mannschaften sortiert'!C134</f>
-        <v>Hallenturnie</v>
+        <v>Weihnachtsfeier</v>
       </c>
       <c r="J134" s="84" t="s">
         <v>68</v>
@@ -9959,17 +9993,17 @@
         <v>71</v>
       </c>
       <c r="L134" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="135" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B135" s="81">
         <f>'Nach Mannschaften sortiert'!D135</f>
-        <v>46403</v>
+        <v>46402</v>
       </c>
       <c r="C135" s="96">
         <f>'Nach Mannschaften sortiert'!E135</f>
-        <v>0.35416666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="D135" s="96">
         <v>0.875</v>
@@ -10003,11 +10037,11 @@
     <row r="136" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B136" s="81">
         <f>'Nach Mannschaften sortiert'!D136</f>
-        <v>46404</v>
+        <v>46403</v>
       </c>
       <c r="C136" s="96">
         <f>'Nach Mannschaften sortiert'!E136</f>
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D136" s="96">
         <v>0.875</v>
@@ -10035,6 +10069,44 @@
         <v>71</v>
       </c>
       <c r="L136" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="137" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B137" s="81">
+        <f>'Nach Mannschaften sortiert'!D137</f>
+        <v>46404</v>
+      </c>
+      <c r="C137" s="96">
+        <f>'Nach Mannschaften sortiert'!E137</f>
+        <v>0.375</v>
+      </c>
+      <c r="D137" s="96">
+        <v>0.875</v>
+      </c>
+      <c r="E137" s="96" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F137)</f>
+        <v>STEINBRUNN</v>
+      </c>
+      <c r="G137" t="str">
+        <f>'Nach Mannschaften sortiert'!H137</f>
+        <v>Heim</v>
+      </c>
+      <c r="H137" t="str">
+        <f>'Nach Mannschaften sortiert'!G137</f>
+        <v>Hallencup 2026_27</v>
+      </c>
+      <c r="I137" t="str">
+        <f>'Nach Mannschaften sortiert'!C137</f>
+        <v>Hallenturnie</v>
+      </c>
+      <c r="J137" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="K137" t="s">
+        <v>71</v>
+      </c>
+      <c r="L137" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10284,16 +10356,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="125" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
@@ -10320,7 +10392,7 @@
       <c r="H2" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="I2" s="119" t="s">
+      <c r="I2" s="120" t="s">
         <v>117</v>
       </c>
       <c r="J2" s="39"/>
@@ -10340,7 +10412,7 @@
       <c r="F3" s="61"/>
       <c r="G3" s="61"/>
       <c r="H3" s="63"/>
-      <c r="I3" s="120"/>
+      <c r="I3" s="121"/>
       <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10360,7 +10432,7 @@
       </c>
       <c r="G4" s="61"/>
       <c r="H4" s="63"/>
-      <c r="I4" s="120"/>
+      <c r="I4" s="121"/>
       <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10380,7 +10452,7 @@
       </c>
       <c r="G5" s="61"/>
       <c r="H5" s="63"/>
-      <c r="I5" s="120"/>
+      <c r="I5" s="121"/>
       <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10400,7 +10472,7 @@
       </c>
       <c r="G6" s="65"/>
       <c r="H6" s="63"/>
-      <c r="I6" s="120"/>
+      <c r="I6" s="121"/>
       <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10422,7 +10494,7 @@
         <v>127</v>
       </c>
       <c r="H7" s="63"/>
-      <c r="I7" s="120"/>
+      <c r="I7" s="121"/>
       <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10444,7 +10516,7 @@
         <v>127</v>
       </c>
       <c r="H8" s="63"/>
-      <c r="I8" s="120"/>
+      <c r="I8" s="121"/>
       <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10468,7 +10540,7 @@
       <c r="H9" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="I9" s="120"/>
+      <c r="I9" s="121"/>
       <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10490,7 +10562,7 @@
         <v>134</v>
       </c>
       <c r="H10" s="63"/>
-      <c r="I10" s="120"/>
+      <c r="I10" s="121"/>
       <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10510,7 +10582,7 @@
         <v>138</v>
       </c>
       <c r="H11" s="72"/>
-      <c r="I11" s="121"/>
+      <c r="I11" s="122"/>
       <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
@@ -10568,52 +10640,52 @@
       <c r="H14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="123" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="119"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="123" t="s">
+      <c r="A16" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="118"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="119"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="127" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="118"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="119"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="116" t="s">
+      <c r="A18" s="117" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="118"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="119"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -10682,783 +10754,783 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="54">
-        <f>'Nach Mannschaften sortiert'!A17</f>
-        <v>16</v>
+        <f>'Nach Mannschaften sortiert'!A18</f>
+        <v>17</v>
       </c>
       <c r="B2" s="54">
-        <f>'Nach Mannschaften sortiert'!B17</f>
+        <f>'Nach Mannschaften sortiert'!B18</f>
         <v>1</v>
       </c>
       <c r="C2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C17</f>
+        <f>'Nach Mannschaften sortiert'!C18</f>
         <v>KM</v>
       </c>
       <c r="D2" s="55">
-        <f>'Nach Mannschaften sortiert'!D17</f>
+        <f>'Nach Mannschaften sortiert'!D18</f>
         <v>46250</v>
       </c>
       <c r="E2" s="97">
-        <f>'Nach Mannschaften sortiert'!E17</f>
+        <f>'Nach Mannschaften sortiert'!E18</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="F2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F17</f>
+        <f>'Nach Mannschaften sortiert'!F18</f>
         <v>Kittsee</v>
       </c>
       <c r="G2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G17</f>
+        <f>'Nach Mannschaften sortiert'!G18</f>
         <v>Kittsee</v>
       </c>
       <c r="H2" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H17</f>
+        <f>'Nach Mannschaften sortiert'!H18</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="54">
-        <f>'Nach Mannschaften sortiert'!A18</f>
-        <v>17</v>
+        <f>'Nach Mannschaften sortiert'!A19</f>
+        <v>18</v>
       </c>
       <c r="B3" s="54">
-        <f>'Nach Mannschaften sortiert'!B18</f>
+        <f>'Nach Mannschaften sortiert'!B19</f>
         <v>2</v>
       </c>
       <c r="C3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C18</f>
+        <f>'Nach Mannschaften sortiert'!C19</f>
         <v>KM</v>
       </c>
       <c r="D3" s="55">
-        <f>'Nach Mannschaften sortiert'!D18</f>
+        <f>'Nach Mannschaften sortiert'!D19</f>
         <v>46255</v>
       </c>
       <c r="E3" s="97">
-        <f>'Nach Mannschaften sortiert'!E18</f>
+        <f>'Nach Mannschaften sortiert'!E19</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="F3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F18</f>
+        <f>'Nach Mannschaften sortiert'!F19</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="G3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G18</f>
+        <f>'Nach Mannschaften sortiert'!G19</f>
         <v>Deutsch Jahrndorf</v>
       </c>
       <c r="H3" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H18</f>
+        <f>'Nach Mannschaften sortiert'!H19</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54">
-        <f>'Nach Mannschaften sortiert'!A19</f>
-        <v>18</v>
+        <f>'Nach Mannschaften sortiert'!A20</f>
+        <v>19</v>
       </c>
       <c r="B4" s="54">
-        <f>'Nach Mannschaften sortiert'!B19</f>
+        <f>'Nach Mannschaften sortiert'!B20</f>
         <v>3</v>
       </c>
       <c r="C4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C19</f>
+        <f>'Nach Mannschaften sortiert'!C20</f>
         <v>KM</v>
       </c>
       <c r="D4" s="55">
-        <f>'Nach Mannschaften sortiert'!D19</f>
+        <f>'Nach Mannschaften sortiert'!D20</f>
         <v>46263</v>
       </c>
       <c r="E4" s="97">
-        <f>'Nach Mannschaften sortiert'!E19</f>
+        <f>'Nach Mannschaften sortiert'!E20</f>
         <v>0.75</v>
       </c>
       <c r="F4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F19</f>
+        <f>'Nach Mannschaften sortiert'!F20</f>
         <v>Neufeld</v>
       </c>
       <c r="G4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G19</f>
+        <f>'Nach Mannschaften sortiert'!G20</f>
         <v>Tadten</v>
       </c>
       <c r="H4" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H19</f>
+        <f>'Nach Mannschaften sortiert'!H20</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="54">
-        <f>'Nach Mannschaften sortiert'!A53</f>
-        <v>52</v>
+        <f>'Nach Mannschaften sortiert'!A54</f>
+        <v>53</v>
       </c>
       <c r="B5" s="54">
-        <f>'Nach Mannschaften sortiert'!B53</f>
+        <f>'Nach Mannschaften sortiert'!B54</f>
         <v>1</v>
       </c>
       <c r="C5" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C53</f>
+        <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U14</v>
       </c>
       <c r="D5" s="55">
-        <f>'Nach Mannschaften sortiert'!D53</f>
+        <f>'Nach Mannschaften sortiert'!D54</f>
         <v>46033</v>
       </c>
       <c r="E5" s="97">
-        <f>'Nach Mannschaften sortiert'!E53</f>
+        <f>'Nach Mannschaften sortiert'!E54</f>
         <v>0</v>
       </c>
       <c r="F5" s="54">
-        <f>'Nach Mannschaften sortiert'!F53</f>
+        <f>'Nach Mannschaften sortiert'!F54</f>
         <v>0</v>
       </c>
       <c r="G5" s="54">
-        <f>'Nach Mannschaften sortiert'!G53</f>
+        <f>'Nach Mannschaften sortiert'!G54</f>
         <v>0</v>
       </c>
       <c r="H5" s="54">
-        <f>'Nach Mannschaften sortiert'!H53</f>
+        <f>'Nach Mannschaften sortiert'!H54</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54">
+        <f>'Nach Mannschaften sortiert'!A22</f>
+        <v>21</v>
+      </c>
+      <c r="B6" s="54">
+        <f>'Nach Mannschaften sortiert'!B22</f>
+        <v>5</v>
+      </c>
+      <c r="C6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C22</f>
+        <v>KM</v>
+      </c>
+      <c r="D6" s="55">
+        <f>'Nach Mannschaften sortiert'!D22</f>
+        <v>46276</v>
+      </c>
+      <c r="E6" s="97">
+        <f>'Nach Mannschaften sortiert'!E22</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F22</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G22</f>
+        <v>Winden</v>
+      </c>
+      <c r="H6" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H22</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="54">
+        <f>'Nach Mannschaften sortiert'!A64</f>
+        <v>63</v>
+      </c>
+      <c r="B7" s="54">
+        <f>'Nach Mannschaften sortiert'!B64</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C64</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D7" s="55">
+        <f>'Nach Mannschaften sortiert'!D64</f>
+        <v>46043</v>
+      </c>
+      <c r="E7" s="97">
+        <f>'Nach Mannschaften sortiert'!E64</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="54">
+        <f>'Nach Mannschaften sortiert'!F64</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="54">
+        <f>'Nach Mannschaften sortiert'!G64</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="54">
+        <f>'Nach Mannschaften sortiert'!H64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54">
+        <f>'Nach Mannschaften sortiert'!A24</f>
+        <v>23</v>
+      </c>
+      <c r="B8" s="54">
+        <f>'Nach Mannschaften sortiert'!B24</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C24</f>
+        <v>KM</v>
+      </c>
+      <c r="D8" s="55">
+        <f>'Nach Mannschaften sortiert'!D24</f>
+        <v>46291</v>
+      </c>
+      <c r="E8" s="97">
+        <f>'Nach Mannschaften sortiert'!E24</f>
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F24</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G24</f>
+        <v>Wallern</v>
+      </c>
+      <c r="H8" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H24</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="52">
+        <f>'Nach Mannschaften sortiert'!A119</f>
+        <v>118</v>
+      </c>
+      <c r="B9" s="52">
+        <f>'Nach Mannschaften sortiert'!B119</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C119</f>
+        <v>Camp</v>
+      </c>
+      <c r="D9" s="53">
+        <f>'Nach Mannschaften sortiert'!D119</f>
+        <v>46230</v>
+      </c>
+      <c r="E9" s="98">
+        <f>'Nach Mannschaften sortiert'!E119</f>
+        <v>0.375</v>
+      </c>
+      <c r="F9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F119</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G119</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H9" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H119</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="54">
+        <f>'Nach Mannschaften sortiert'!A26</f>
+        <v>25</v>
+      </c>
+      <c r="B10" s="54">
+        <f>'Nach Mannschaften sortiert'!B26</f>
+        <v>9</v>
+      </c>
+      <c r="C10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C26</f>
+        <v>KM</v>
+      </c>
+      <c r="D10" s="55">
+        <f>'Nach Mannschaften sortiert'!D26</f>
+        <v>46304</v>
+      </c>
+      <c r="E10" s="97">
+        <f>'Nach Mannschaften sortiert'!E26</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F26</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G26</f>
+        <v>Wimpassing</v>
+      </c>
+      <c r="H10" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H26</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="52">
+        <f>'Nach Mannschaften sortiert'!A120</f>
+        <v>119</v>
+      </c>
+      <c r="B11" s="52">
+        <f>'Nach Mannschaften sortiert'!B120</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C120</f>
+        <v>Camp</v>
+      </c>
+      <c r="D11" s="53">
+        <f>'Nach Mannschaften sortiert'!D120</f>
+        <v>46231</v>
+      </c>
+      <c r="E11" s="98">
+        <f>'Nach Mannschaften sortiert'!E120</f>
+        <v>0.375</v>
+      </c>
+      <c r="F11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F120</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G120</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H11" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H120</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="54">
+        <f>'Nach Mannschaften sortiert'!A28</f>
+        <v>27</v>
+      </c>
+      <c r="B12" s="54">
+        <f>'Nach Mannschaften sortiert'!B28</f>
+        <v>11</v>
+      </c>
+      <c r="C12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C28</f>
+        <v>KM</v>
+      </c>
+      <c r="D12" s="55">
+        <f>'Nach Mannschaften sortiert'!D28</f>
+        <v>46319</v>
+      </c>
+      <c r="E12" s="97">
+        <f>'Nach Mannschaften sortiert'!E28</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F28</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G28</f>
+        <v>Gols</v>
+      </c>
+      <c r="H12" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H28</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <f>'Nach Mannschaften sortiert'!A29</f>
+        <v>28</v>
+      </c>
+      <c r="B13" s="54">
+        <f>'Nach Mannschaften sortiert'!B29</f>
+        <v>12</v>
+      </c>
+      <c r="C13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C29</f>
+        <v>KM</v>
+      </c>
+      <c r="D13" s="55">
+        <f>'Nach Mannschaften sortiert'!D29</f>
+        <v>46326</v>
+      </c>
+      <c r="E13" s="97">
+        <f>'Nach Mannschaften sortiert'!E29</f>
+        <v>0.75</v>
+      </c>
+      <c r="F13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!F29</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="G13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!G29</f>
+        <v>Illmitz</v>
+      </c>
+      <c r="H13" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!H29</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="52">
+        <f>'Nach Mannschaften sortiert'!A121</f>
+        <v>120</v>
+      </c>
+      <c r="B14" s="52">
+        <f>'Nach Mannschaften sortiert'!B121</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!C121</f>
+        <v>Camp</v>
+      </c>
+      <c r="D14" s="53">
+        <f>'Nach Mannschaften sortiert'!D121</f>
+        <v>46232</v>
+      </c>
+      <c r="E14" s="98">
+        <f>'Nach Mannschaften sortiert'!E121</f>
+        <v>0.375</v>
+      </c>
+      <c r="F14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!F121</f>
+        <v>Neufeld</v>
+      </c>
+      <c r="G14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!G121</f>
+        <v>REAL MADRID CAMP</v>
+      </c>
+      <c r="H14" s="52" t="str">
+        <f>'Nach Mannschaften sortiert'!H121</f>
+        <v>Heim</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
+        <f>'Nach Mannschaften sortiert'!A44</f>
+        <v>43</v>
+      </c>
+      <c r="B15" s="54">
+        <f>'Nach Mannschaften sortiert'!B44</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C44</f>
+        <v>U16</v>
+      </c>
+      <c r="D15" s="55">
+        <f>'Nach Mannschaften sortiert'!D44</f>
+        <v>46023</v>
+      </c>
+      <c r="E15" s="97">
+        <f>'Nach Mannschaften sortiert'!E44</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="54">
+        <f>'Nach Mannschaften sortiert'!F44</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="54">
+        <f>'Nach Mannschaften sortiert'!G44</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="54">
+        <f>'Nach Mannschaften sortiert'!H44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="48">
+        <f>'Nach Mannschaften sortiert'!A45</f>
+        <v>44</v>
+      </c>
+      <c r="B16" s="48">
+        <f>'Nach Mannschaften sortiert'!B45</f>
+        <v>2</v>
+      </c>
+      <c r="C16" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C45</f>
+        <v>U16</v>
+      </c>
+      <c r="D16" s="49">
+        <f>'Nach Mannschaften sortiert'!D45</f>
+        <v>46024</v>
+      </c>
+      <c r="E16" s="99">
+        <f>'Nach Mannschaften sortiert'!E45</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="48">
+        <f>'Nach Mannschaften sortiert'!F45</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="48">
+        <f>'Nach Mannschaften sortiert'!G45</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="48">
+        <f>'Nach Mannschaften sortiert'!H45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <f>'Nach Mannschaften sortiert'!A46</f>
+        <v>45</v>
+      </c>
+      <c r="B17" s="54">
+        <f>'Nach Mannschaften sortiert'!B46</f>
+        <v>3</v>
+      </c>
+      <c r="C17" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C46</f>
+        <v>U16</v>
+      </c>
+      <c r="D17" s="55">
+        <f>'Nach Mannschaften sortiert'!D46</f>
+        <v>46025</v>
+      </c>
+      <c r="E17" s="97">
+        <f>'Nach Mannschaften sortiert'!E46</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="54">
+        <f>'Nach Mannschaften sortiert'!F46</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="54">
+        <f>'Nach Mannschaften sortiert'!G46</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="54">
+        <f>'Nach Mannschaften sortiert'!H46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="54">
         <f>'Nach Mannschaften sortiert'!A21</f>
         <v>20</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B18" s="54">
         <f>'Nach Mannschaften sortiert'!B21</f>
-        <v>5</v>
-      </c>
-      <c r="C6" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!C21</f>
         <v>KM</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D18" s="55">
         <f>'Nach Mannschaften sortiert'!D21</f>
-        <v>46276</v>
-      </c>
-      <c r="E6" s="97">
+        <v>46270</v>
+      </c>
+      <c r="E18" s="97">
         <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F6" s="54" t="str">
+        <v>0.6875</v>
+      </c>
+      <c r="F18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F21</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="G18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!G21</f>
-        <v>Winden</v>
-      </c>
-      <c r="H6" s="54" t="str">
+        <v>Mönchhof</v>
+      </c>
+      <c r="H18" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="54">
-        <f>'Nach Mannschaften sortiert'!A63</f>
-        <v>62</v>
-      </c>
-      <c r="B7" s="54">
-        <f>'Nach Mannschaften sortiert'!B63</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C63</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D7" s="55">
-        <f>'Nach Mannschaften sortiert'!D63</f>
-        <v>46043</v>
-      </c>
-      <c r="E7" s="97">
-        <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="54">
-        <f>'Nach Mannschaften sortiert'!F63</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="54">
-        <f>'Nach Mannschaften sortiert'!G63</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="54">
-        <f>'Nach Mannschaften sortiert'!H63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54">
-        <f>'Nach Mannschaften sortiert'!A23</f>
-        <v>22</v>
-      </c>
-      <c r="B8" s="54">
-        <f>'Nach Mannschaften sortiert'!B23</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C23</f>
-        <v>KM</v>
-      </c>
-      <c r="D8" s="55">
-        <f>'Nach Mannschaften sortiert'!D23</f>
-        <v>46291</v>
-      </c>
-      <c r="E8" s="97">
-        <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.75</v>
-      </c>
-      <c r="F8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F23</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G23</f>
-        <v>Wallern</v>
-      </c>
-      <c r="H8" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H23</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="52">
-        <f>'Nach Mannschaften sortiert'!A118</f>
-        <v>117</v>
-      </c>
-      <c r="B9" s="52">
-        <f>'Nach Mannschaften sortiert'!B118</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C118</f>
-        <v>Camp</v>
-      </c>
-      <c r="D9" s="53">
-        <f>'Nach Mannschaften sortiert'!D118</f>
-        <v>46230</v>
-      </c>
-      <c r="E9" s="98">
-        <f>'Nach Mannschaften sortiert'!E118</f>
-        <v>0.375</v>
-      </c>
-      <c r="F9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F118</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G118</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H118</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54">
-        <f>'Nach Mannschaften sortiert'!A25</f>
-        <v>24</v>
-      </c>
-      <c r="B10" s="54">
-        <f>'Nach Mannschaften sortiert'!B25</f>
-        <v>9</v>
-      </c>
-      <c r="C10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C25</f>
-        <v>KM</v>
-      </c>
-      <c r="D10" s="55">
-        <f>'Nach Mannschaften sortiert'!D25</f>
-        <v>46304</v>
-      </c>
-      <c r="E10" s="97">
-        <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F25</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G25</f>
-        <v>Wimpassing</v>
-      </c>
-      <c r="H10" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H25</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="52">
-        <f>'Nach Mannschaften sortiert'!A119</f>
-        <v>118</v>
-      </c>
-      <c r="B11" s="52">
-        <f>'Nach Mannschaften sortiert'!B119</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C119</f>
-        <v>Camp</v>
-      </c>
-      <c r="D11" s="53">
-        <f>'Nach Mannschaften sortiert'!D119</f>
-        <v>46231</v>
-      </c>
-      <c r="E11" s="98">
-        <f>'Nach Mannschaften sortiert'!E119</f>
-        <v>0.375</v>
-      </c>
-      <c r="F11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F119</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G119</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H119</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <f>'Nach Mannschaften sortiert'!A27</f>
-        <v>26</v>
-      </c>
-      <c r="B12" s="54">
-        <f>'Nach Mannschaften sortiert'!B27</f>
-        <v>11</v>
-      </c>
-      <c r="C12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C27</f>
-        <v>KM</v>
-      </c>
-      <c r="D12" s="55">
-        <f>'Nach Mannschaften sortiert'!D27</f>
-        <v>46319</v>
-      </c>
-      <c r="E12" s="97">
-        <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F27</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G27</f>
-        <v>Gols</v>
-      </c>
-      <c r="H12" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H27</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54">
-        <f>'Nach Mannschaften sortiert'!A28</f>
-        <v>27</v>
-      </c>
-      <c r="B13" s="54">
-        <f>'Nach Mannschaften sortiert'!B28</f>
-        <v>12</v>
-      </c>
-      <c r="C13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C28</f>
-        <v>KM</v>
-      </c>
-      <c r="D13" s="55">
-        <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46326</v>
-      </c>
-      <c r="E13" s="97">
-        <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0.75</v>
-      </c>
-      <c r="F13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F28</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="G13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G28</f>
-        <v>Illmitz</v>
-      </c>
-      <c r="H13" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H28</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="52">
-        <f>'Nach Mannschaften sortiert'!A120</f>
-        <v>119</v>
-      </c>
-      <c r="B14" s="52">
-        <f>'Nach Mannschaften sortiert'!B120</f>
-        <v>3</v>
-      </c>
-      <c r="C14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C120</f>
-        <v>Camp</v>
-      </c>
-      <c r="D14" s="53">
-        <f>'Nach Mannschaften sortiert'!D120</f>
-        <v>46232</v>
-      </c>
-      <c r="E14" s="98">
-        <f>'Nach Mannschaften sortiert'!E120</f>
-        <v>0.375</v>
-      </c>
-      <c r="F14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!F120</f>
-        <v>Neufeld</v>
-      </c>
-      <c r="G14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!G120</f>
-        <v>REAL MADRID CAMP</v>
-      </c>
-      <c r="H14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!H120</f>
-        <v>Heim</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54">
-        <f>'Nach Mannschaften sortiert'!A43</f>
-        <v>42</v>
-      </c>
-      <c r="B15" s="54">
-        <f>'Nach Mannschaften sortiert'!B43</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C43</f>
-        <v>U16</v>
-      </c>
-      <c r="D15" s="55">
-        <f>'Nach Mannschaften sortiert'!D43</f>
-        <v>46023</v>
-      </c>
-      <c r="E15" s="97">
-        <f>'Nach Mannschaften sortiert'!E43</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="54">
-        <f>'Nach Mannschaften sortiert'!F43</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="54">
-        <f>'Nach Mannschaften sortiert'!G43</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="54">
-        <f>'Nach Mannschaften sortiert'!H43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48">
-        <f>'Nach Mannschaften sortiert'!A44</f>
-        <v>43</v>
-      </c>
-      <c r="B16" s="48">
-        <f>'Nach Mannschaften sortiert'!B44</f>
-        <v>2</v>
-      </c>
-      <c r="C16" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C44</f>
-        <v>U16</v>
-      </c>
-      <c r="D16" s="49">
-        <f>'Nach Mannschaften sortiert'!D44</f>
-        <v>46024</v>
-      </c>
-      <c r="E16" s="99">
-        <f>'Nach Mannschaften sortiert'!E44</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="48">
-        <f>'Nach Mannschaften sortiert'!F44</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="48">
-        <f>'Nach Mannschaften sortiert'!G44</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="48">
-        <f>'Nach Mannschaften sortiert'!H44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54">
-        <f>'Nach Mannschaften sortiert'!A45</f>
-        <v>44</v>
-      </c>
-      <c r="B17" s="54">
-        <f>'Nach Mannschaften sortiert'!B45</f>
-        <v>3</v>
-      </c>
-      <c r="C17" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C45</f>
-        <v>U16</v>
-      </c>
-      <c r="D17" s="55">
-        <f>'Nach Mannschaften sortiert'!D45</f>
-        <v>46025</v>
-      </c>
-      <c r="E17" s="97">
-        <f>'Nach Mannschaften sortiert'!E45</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="54">
-        <f>'Nach Mannschaften sortiert'!F45</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="54">
-        <f>'Nach Mannschaften sortiert'!G45</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="54">
-        <f>'Nach Mannschaften sortiert'!H45</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="54">
-        <f>'Nach Mannschaften sortiert'!A20</f>
-        <v>19</v>
-      </c>
-      <c r="B18" s="54">
-        <f>'Nach Mannschaften sortiert'!B20</f>
-        <v>4</v>
-      </c>
-      <c r="C18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C20</f>
-        <v>KM</v>
-      </c>
-      <c r="D18" s="55">
-        <f>'Nach Mannschaften sortiert'!D20</f>
-        <v>46270</v>
-      </c>
-      <c r="E18" s="97">
-        <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.6875</v>
-      </c>
-      <c r="F18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F20</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="G18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G20</f>
-        <v>Mönchhof</v>
-      </c>
-      <c r="H18" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H20</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54">
-        <f>'Nach Mannschaften sortiert'!A47</f>
-        <v>46</v>
+        <f>'Nach Mannschaften sortiert'!A48</f>
+        <v>47</v>
       </c>
       <c r="B19" s="54">
-        <f>'Nach Mannschaften sortiert'!B47</f>
+        <f>'Nach Mannschaften sortiert'!B48</f>
         <v>5</v>
       </c>
       <c r="C19" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C47</f>
+        <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U16</v>
       </c>
       <c r="D19" s="55">
-        <f>'Nach Mannschaften sortiert'!D47</f>
+        <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46027</v>
       </c>
       <c r="E19" s="97">
-        <f>'Nach Mannschaften sortiert'!E47</f>
+        <f>'Nach Mannschaften sortiert'!E48</f>
         <v>0</v>
       </c>
       <c r="F19" s="54">
-        <f>'Nach Mannschaften sortiert'!F47</f>
+        <f>'Nach Mannschaften sortiert'!F48</f>
         <v>0</v>
       </c>
       <c r="G19" s="54">
-        <f>'Nach Mannschaften sortiert'!G47</f>
+        <f>'Nach Mannschaften sortiert'!G48</f>
         <v>0</v>
       </c>
       <c r="H19" s="54">
-        <f>'Nach Mannschaften sortiert'!H47</f>
+        <f>'Nach Mannschaften sortiert'!H48</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
-        <f>'Nach Mannschaften sortiert'!A48</f>
-        <v>47</v>
+        <f>'Nach Mannschaften sortiert'!A49</f>
+        <v>48</v>
       </c>
       <c r="B20" s="46">
-        <f>'Nach Mannschaften sortiert'!B48</f>
+        <f>'Nach Mannschaften sortiert'!B49</f>
         <v>6</v>
       </c>
       <c r="C20" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C48</f>
+        <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U16</v>
       </c>
       <c r="D20" s="47">
-        <f>'Nach Mannschaften sortiert'!D48</f>
+        <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46028</v>
       </c>
       <c r="E20" s="100">
-        <f>'Nach Mannschaften sortiert'!E48</f>
+        <f>'Nach Mannschaften sortiert'!E49</f>
         <v>0</v>
       </c>
       <c r="F20" s="46">
-        <f>'Nach Mannschaften sortiert'!F48</f>
+        <f>'Nach Mannschaften sortiert'!F49</f>
         <v>0</v>
       </c>
       <c r="G20" s="46">
-        <f>'Nach Mannschaften sortiert'!G48</f>
+        <f>'Nach Mannschaften sortiert'!G49</f>
         <v>0</v>
       </c>
       <c r="H20" s="46">
-        <f>'Nach Mannschaften sortiert'!H48</f>
+        <f>'Nach Mannschaften sortiert'!H49</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54">
-        <f>'Nach Mannschaften sortiert'!A49</f>
-        <v>48</v>
+        <f>'Nach Mannschaften sortiert'!A50</f>
+        <v>49</v>
       </c>
       <c r="B21" s="54">
-        <f>'Nach Mannschaften sortiert'!B49</f>
+        <f>'Nach Mannschaften sortiert'!B50</f>
         <v>7</v>
       </c>
       <c r="C21" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C49</f>
+        <f>'Nach Mannschaften sortiert'!C50</f>
         <v>U16</v>
       </c>
       <c r="D21" s="55">
-        <f>'Nach Mannschaften sortiert'!D49</f>
+        <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46029</v>
       </c>
       <c r="E21" s="97">
-        <f>'Nach Mannschaften sortiert'!E49</f>
+        <f>'Nach Mannschaften sortiert'!E50</f>
         <v>0</v>
       </c>
       <c r="F21" s="54">
-        <f>'Nach Mannschaften sortiert'!F49</f>
+        <f>'Nach Mannschaften sortiert'!F50</f>
         <v>0</v>
       </c>
       <c r="G21" s="54">
-        <f>'Nach Mannschaften sortiert'!G49</f>
+        <f>'Nach Mannschaften sortiert'!G50</f>
         <v>0</v>
       </c>
       <c r="H21" s="54">
-        <f>'Nach Mannschaften sortiert'!H49</f>
+        <f>'Nach Mannschaften sortiert'!H50</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
-        <f>'Nach Mannschaften sortiert'!A50</f>
-        <v>49</v>
+        <f>'Nach Mannschaften sortiert'!A51</f>
+        <v>50</v>
       </c>
       <c r="B22" s="48">
-        <f>'Nach Mannschaften sortiert'!B50</f>
+        <f>'Nach Mannschaften sortiert'!B51</f>
         <v>8</v>
       </c>
       <c r="C22" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C50</f>
+        <f>'Nach Mannschaften sortiert'!C51</f>
         <v>U16</v>
       </c>
       <c r="D22" s="49">
-        <f>'Nach Mannschaften sortiert'!D50</f>
+        <f>'Nach Mannschaften sortiert'!D51</f>
         <v>46030</v>
       </c>
       <c r="E22" s="99">
-        <f>'Nach Mannschaften sortiert'!E50</f>
+        <f>'Nach Mannschaften sortiert'!E51</f>
         <v>0</v>
       </c>
       <c r="F22" s="48">
-        <f>'Nach Mannschaften sortiert'!F50</f>
+        <f>'Nach Mannschaften sortiert'!F51</f>
         <v>0</v>
       </c>
       <c r="G22" s="48">
-        <f>'Nach Mannschaften sortiert'!G50</f>
+        <f>'Nach Mannschaften sortiert'!G51</f>
         <v>0</v>
       </c>
       <c r="H22" s="48">
-        <f>'Nach Mannschaften sortiert'!H50</f>
+        <f>'Nach Mannschaften sortiert'!H51</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54">
-        <f>'Nach Mannschaften sortiert'!A51</f>
-        <v>50</v>
+        <f>'Nach Mannschaften sortiert'!A52</f>
+        <v>51</v>
       </c>
       <c r="B23" s="54">
-        <f>'Nach Mannschaften sortiert'!B51</f>
+        <f>'Nach Mannschaften sortiert'!B52</f>
         <v>9</v>
       </c>
       <c r="C23" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C51</f>
+        <f>'Nach Mannschaften sortiert'!C52</f>
         <v>U16</v>
       </c>
       <c r="D23" s="55">
-        <f>'Nach Mannschaften sortiert'!D51</f>
+        <f>'Nach Mannschaften sortiert'!D52</f>
         <v>46031</v>
       </c>
       <c r="E23" s="97">
-        <f>'Nach Mannschaften sortiert'!E51</f>
+        <f>'Nach Mannschaften sortiert'!E52</f>
         <v>0</v>
       </c>
       <c r="F23" s="54">
-        <f>'Nach Mannschaften sortiert'!F51</f>
+        <f>'Nach Mannschaften sortiert'!F52</f>
         <v>0</v>
       </c>
       <c r="G23" s="54">
-        <f>'Nach Mannschaften sortiert'!G51</f>
+        <f>'Nach Mannschaften sortiert'!G52</f>
         <v>0</v>
       </c>
       <c r="H23" s="54">
-        <f>'Nach Mannschaften sortiert'!H51</f>
+        <f>'Nach Mannschaften sortiert'!H52</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
-        <f>'Nach Mannschaften sortiert'!A98</f>
-        <v>97</v>
+        <f>'Nach Mannschaften sortiert'!A99</f>
+        <v>98</v>
       </c>
       <c r="B24" s="50">
-        <f>'Nach Mannschaften sortiert'!B98</f>
+        <f>'Nach Mannschaften sortiert'!B99</f>
         <v>1</v>
       </c>
       <c r="C24" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C98</f>
+        <f>'Nach Mannschaften sortiert'!C99</f>
         <v>U9</v>
       </c>
       <c r="D24" s="51">
-        <f>'Nach Mannschaften sortiert'!D98</f>
+        <f>'Nach Mannschaften sortiert'!D99</f>
         <v>46078</v>
       </c>
       <c r="E24" s="101">
-        <f>'Nach Mannschaften sortiert'!E98</f>
+        <f>'Nach Mannschaften sortiert'!E99</f>
         <v>0</v>
       </c>
       <c r="F24" s="50">
-        <f>'Nach Mannschaften sortiert'!F98</f>
+        <f>'Nach Mannschaften sortiert'!F99</f>
         <v>0</v>
       </c>
       <c r="G24" s="50">
-        <f>'Nach Mannschaften sortiert'!G98</f>
+        <f>'Nach Mannschaften sortiert'!G99</f>
         <v>0</v>
       </c>
       <c r="H24" s="50">
-        <f>'Nach Mannschaften sortiert'!H98</f>
+        <f>'Nach Mannschaften sortiert'!H99</f>
         <v>0</v>
       </c>
     </row>
@@ -11498,35 +11570,35 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
-        <f>'Nach Mannschaften sortiert'!A108</f>
-        <v>107</v>
+        <f>'Nach Mannschaften sortiert'!A109</f>
+        <v>108</v>
       </c>
       <c r="B26" s="50">
-        <f>'Nach Mannschaften sortiert'!B108</f>
+        <f>'Nach Mannschaften sortiert'!B109</f>
         <v>1</v>
       </c>
       <c r="C26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C108</f>
+        <f>'Nach Mannschaften sortiert'!C109</f>
         <v>U8</v>
       </c>
       <c r="D26" s="51">
-        <f>'Nach Mannschaften sortiert'!D108</f>
+        <f>'Nach Mannschaften sortiert'!D109</f>
         <v>46312</v>
       </c>
       <c r="E26" s="101">
-        <f>'Nach Mannschaften sortiert'!E108</f>
+        <f>'Nach Mannschaften sortiert'!E109</f>
         <v>0.39583333333333331</v>
       </c>
       <c r="F26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!F108</f>
+        <f>'Nach Mannschaften sortiert'!F109</f>
         <v>Neufeld</v>
       </c>
       <c r="G26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!G108</f>
+        <f>'Nach Mannschaften sortiert'!G109</f>
         <v>Heimturnier</v>
       </c>
       <c r="H26" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!H108</f>
+        <f>'Nach Mannschaften sortiert'!H109</f>
         <v>Heim</v>
       </c>
     </row>
@@ -11600,35 +11672,35 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="50">
-        <f>'Nach Mannschaften sortiert'!A113</f>
-        <v>112</v>
+        <f>'Nach Mannschaften sortiert'!A114</f>
+        <v>113</v>
       </c>
       <c r="B29" s="50">
-        <f>'Nach Mannschaften sortiert'!B113</f>
+        <f>'Nach Mannschaften sortiert'!B114</f>
         <v>1</v>
       </c>
       <c r="C29" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C113</f>
+        <f>'Nach Mannschaften sortiert'!C114</f>
         <v>U7</v>
       </c>
       <c r="D29" s="51">
-        <f>'Nach Mannschaften sortiert'!D113</f>
+        <f>'Nach Mannschaften sortiert'!D114</f>
         <v>46312</v>
       </c>
       <c r="E29" s="101">
-        <f>'Nach Mannschaften sortiert'!E113</f>
+        <f>'Nach Mannschaften sortiert'!E114</f>
         <v>0</v>
       </c>
       <c r="F29" s="50">
-        <f>'Nach Mannschaften sortiert'!F113</f>
+        <f>'Nach Mannschaften sortiert'!F114</f>
         <v>0</v>
       </c>
       <c r="G29" s="50">
-        <f>'Nach Mannschaften sortiert'!G113</f>
+        <f>'Nach Mannschaften sortiert'!G114</f>
         <v>0</v>
       </c>
       <c r="H29" s="50">
-        <f>'Nach Mannschaften sortiert'!H113</f>
+        <f>'Nach Mannschaften sortiert'!H114</f>
         <v>0</v>
       </c>
     </row>
@@ -11804,103 +11876,103 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="50">
-        <f>'Nach Mannschaften sortiert'!A84</f>
-        <v>83</v>
+        <f>'Nach Mannschaften sortiert'!A85</f>
+        <v>84</v>
       </c>
       <c r="B35" s="50">
-        <f>'Nach Mannschaften sortiert'!B84</f>
+        <f>'Nach Mannschaften sortiert'!B85</f>
         <v>2</v>
       </c>
       <c r="C35" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C84</f>
+        <f>'Nach Mannschaften sortiert'!C85</f>
         <v>U11</v>
       </c>
       <c r="D35" s="51">
-        <f>'Nach Mannschaften sortiert'!D84</f>
+        <f>'Nach Mannschaften sortiert'!D85</f>
         <v>46064</v>
       </c>
       <c r="E35" s="101">
-        <f>'Nach Mannschaften sortiert'!E84</f>
+        <f>'Nach Mannschaften sortiert'!E85</f>
         <v>0</v>
       </c>
       <c r="F35" s="50">
-        <f>'Nach Mannschaften sortiert'!F84</f>
+        <f>'Nach Mannschaften sortiert'!F85</f>
         <v>0</v>
       </c>
       <c r="G35" s="50">
-        <f>'Nach Mannschaften sortiert'!G84</f>
+        <f>'Nach Mannschaften sortiert'!G85</f>
         <v>0</v>
       </c>
       <c r="H35" s="50">
-        <f>'Nach Mannschaften sortiert'!H84</f>
+        <f>'Nach Mannschaften sortiert'!H85</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="54">
-        <f>'Nach Mannschaften sortiert'!A54</f>
-        <v>53</v>
+        <f>'Nach Mannschaften sortiert'!A55</f>
+        <v>54</v>
       </c>
       <c r="B36" s="54">
-        <f>'Nach Mannschaften sortiert'!B54</f>
+        <f>'Nach Mannschaften sortiert'!B55</f>
         <v>2</v>
       </c>
       <c r="C36" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C54</f>
+        <f>'Nach Mannschaften sortiert'!C55</f>
         <v>U14</v>
       </c>
       <c r="D36" s="55">
-        <f>'Nach Mannschaften sortiert'!D54</f>
+        <f>'Nach Mannschaften sortiert'!D55</f>
         <v>46034</v>
       </c>
       <c r="E36" s="97">
-        <f>'Nach Mannschaften sortiert'!E54</f>
+        <f>'Nach Mannschaften sortiert'!E55</f>
         <v>0</v>
       </c>
       <c r="F36" s="54">
-        <f>'Nach Mannschaften sortiert'!F54</f>
+        <f>'Nach Mannschaften sortiert'!F55</f>
         <v>0</v>
       </c>
       <c r="G36" s="54">
-        <f>'Nach Mannschaften sortiert'!G54</f>
+        <f>'Nach Mannschaften sortiert'!G55</f>
         <v>0</v>
       </c>
       <c r="H36" s="54">
-        <f>'Nach Mannschaften sortiert'!H54</f>
+        <f>'Nach Mannschaften sortiert'!H55</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="54">
-        <f>'Nach Mannschaften sortiert'!A55</f>
-        <v>54</v>
+        <f>'Nach Mannschaften sortiert'!A56</f>
+        <v>55</v>
       </c>
       <c r="B37" s="54">
-        <f>'Nach Mannschaften sortiert'!B55</f>
+        <f>'Nach Mannschaften sortiert'!B56</f>
         <v>3</v>
       </c>
       <c r="C37" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C55</f>
+        <f>'Nach Mannschaften sortiert'!C56</f>
         <v>U14</v>
       </c>
       <c r="D37" s="55">
-        <f>'Nach Mannschaften sortiert'!D55</f>
+        <f>'Nach Mannschaften sortiert'!D56</f>
         <v>46035</v>
       </c>
       <c r="E37" s="97">
-        <f>'Nach Mannschaften sortiert'!E55</f>
+        <f>'Nach Mannschaften sortiert'!E56</f>
         <v>0</v>
       </c>
       <c r="F37" s="54">
-        <f>'Nach Mannschaften sortiert'!F55</f>
+        <f>'Nach Mannschaften sortiert'!F56</f>
         <v>0</v>
       </c>
       <c r="G37" s="54">
-        <f>'Nach Mannschaften sortiert'!G55</f>
+        <f>'Nach Mannschaften sortiert'!G56</f>
         <v>0</v>
       </c>
       <c r="H37" s="54">
-        <f>'Nach Mannschaften sortiert'!H55</f>
+        <f>'Nach Mannschaften sortiert'!H56</f>
         <v>0</v>
       </c>
     </row>
@@ -11974,205 +12046,205 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54">
+        <f>'Nach Mannschaften sortiert'!A58</f>
+        <v>57</v>
+      </c>
+      <c r="B40" s="54">
+        <f>'Nach Mannschaften sortiert'!B58</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C58</f>
+        <v>U14</v>
+      </c>
+      <c r="D40" s="55">
+        <f>'Nach Mannschaften sortiert'!D58</f>
+        <v>46037</v>
+      </c>
+      <c r="E40" s="97">
+        <f>'Nach Mannschaften sortiert'!E58</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="54">
+        <f>'Nach Mannschaften sortiert'!F58</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="54">
+        <f>'Nach Mannschaften sortiert'!G58</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="54">
+        <f>'Nach Mannschaften sortiert'!H58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="48">
+        <f>'Nach Mannschaften sortiert'!A23</f>
+        <v>22</v>
+      </c>
+      <c r="B41" s="48">
+        <f>'Nach Mannschaften sortiert'!B23</f>
+        <v>6</v>
+      </c>
+      <c r="C41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!C23</f>
+        <v>KM</v>
+      </c>
+      <c r="D41" s="49">
+        <f>'Nach Mannschaften sortiert'!D23</f>
+        <v>46284</v>
+      </c>
+      <c r="E41" s="99">
+        <f>'Nach Mannschaften sortiert'!E23</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!F23</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="G41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!G23</f>
+        <v>Gattendorf</v>
+      </c>
+      <c r="H41" s="48" t="str">
+        <f>'Nach Mannschaften sortiert'!H23</f>
+        <v>Auswärts</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="54">
+        <f>'Nach Mannschaften sortiert'!A89</f>
+        <v>88</v>
+      </c>
+      <c r="B42" s="54">
+        <f>'Nach Mannschaften sortiert'!B89</f>
+        <v>6</v>
+      </c>
+      <c r="C42" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C89</f>
+        <v>U11</v>
+      </c>
+      <c r="D42" s="55">
+        <f>'Nach Mannschaften sortiert'!D89</f>
+        <v>46068</v>
+      </c>
+      <c r="E42" s="97">
+        <f>'Nach Mannschaften sortiert'!E89</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="54">
+        <f>'Nach Mannschaften sortiert'!F89</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="54">
+        <f>'Nach Mannschaften sortiert'!G89</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="54">
+        <f>'Nach Mannschaften sortiert'!H89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="54">
+        <f>'Nach Mannschaften sortiert'!A63</f>
+        <v>62</v>
+      </c>
+      <c r="B43" s="54">
+        <f>'Nach Mannschaften sortiert'!B63</f>
+        <v>10</v>
+      </c>
+      <c r="C43" s="54" t="str">
+        <f>'Nach Mannschaften sortiert'!C63</f>
+        <v>U14</v>
+      </c>
+      <c r="D43" s="55">
+        <f>'Nach Mannschaften sortiert'!D63</f>
+        <v>46042</v>
+      </c>
+      <c r="E43" s="97">
+        <f>'Nach Mannschaften sortiert'!E63</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="54">
+        <f>'Nach Mannschaften sortiert'!F63</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="54">
+        <f>'Nach Mannschaften sortiert'!G63</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="54">
+        <f>'Nach Mannschaften sortiert'!H63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="50">
+        <f>'Nach Mannschaften sortiert'!A66</f>
+        <v>65</v>
+      </c>
+      <c r="B44" s="50">
+        <f>'Nach Mannschaften sortiert'!B66</f>
+        <v>3</v>
+      </c>
+      <c r="C44" s="50" t="str">
+        <f>'Nach Mannschaften sortiert'!C66</f>
+        <v>U12_1</v>
+      </c>
+      <c r="D44" s="51">
+        <f>'Nach Mannschaften sortiert'!D66</f>
+        <v>46045</v>
+      </c>
+      <c r="E44" s="101">
+        <f>'Nach Mannschaften sortiert'!E66</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="50">
+        <f>'Nach Mannschaften sortiert'!F66</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="50">
+        <f>'Nach Mannschaften sortiert'!G66</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="50">
+        <f>'Nach Mannschaften sortiert'!H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="50">
         <f>'Nach Mannschaften sortiert'!A57</f>
         <v>56</v>
       </c>
-      <c r="B40" s="54">
+      <c r="B45" s="50">
         <f>'Nach Mannschaften sortiert'!B57</f>
-        <v>5</v>
-      </c>
-      <c r="C40" s="54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C45" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!C57</f>
         <v>U14</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D45" s="51">
         <f>'Nach Mannschaften sortiert'!D57</f>
-        <v>46037</v>
-      </c>
-      <c r="E40" s="97">
+        <v>46036</v>
+      </c>
+      <c r="E45" s="101">
         <f>'Nach Mannschaften sortiert'!E57</f>
         <v>0</v>
       </c>
-      <c r="F40" s="54">
+      <c r="F45" s="50">
         <f>'Nach Mannschaften sortiert'!F57</f>
         <v>0</v>
       </c>
-      <c r="G40" s="54">
+      <c r="G45" s="50">
         <f>'Nach Mannschaften sortiert'!G57</f>
         <v>0</v>
       </c>
-      <c r="H40" s="54">
+      <c r="H45" s="50">
         <f>'Nach Mannschaften sortiert'!H57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="48">
-        <f>'Nach Mannschaften sortiert'!A22</f>
-        <v>21</v>
-      </c>
-      <c r="B41" s="48">
-        <f>'Nach Mannschaften sortiert'!B22</f>
-        <v>6</v>
-      </c>
-      <c r="C41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C22</f>
-        <v>KM</v>
-      </c>
-      <c r="D41" s="49">
-        <f>'Nach Mannschaften sortiert'!D22</f>
-        <v>46284</v>
-      </c>
-      <c r="E41" s="99">
-        <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F22</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="G41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G22</f>
-        <v>Gattendorf</v>
-      </c>
-      <c r="H41" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H22</f>
-        <v>Auswärts</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="54">
-        <f>'Nach Mannschaften sortiert'!A88</f>
-        <v>87</v>
-      </c>
-      <c r="B42" s="54">
-        <f>'Nach Mannschaften sortiert'!B88</f>
-        <v>6</v>
-      </c>
-      <c r="C42" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C88</f>
-        <v>U11</v>
-      </c>
-      <c r="D42" s="55">
-        <f>'Nach Mannschaften sortiert'!D88</f>
-        <v>46068</v>
-      </c>
-      <c r="E42" s="97">
-        <f>'Nach Mannschaften sortiert'!E88</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="54">
-        <f>'Nach Mannschaften sortiert'!F88</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="54">
-        <f>'Nach Mannschaften sortiert'!G88</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="54">
-        <f>'Nach Mannschaften sortiert'!H88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="54">
-        <f>'Nach Mannschaften sortiert'!A62</f>
-        <v>61</v>
-      </c>
-      <c r="B43" s="54">
-        <f>'Nach Mannschaften sortiert'!B62</f>
-        <v>10</v>
-      </c>
-      <c r="C43" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C62</f>
-        <v>U14</v>
-      </c>
-      <c r="D43" s="55">
-        <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46042</v>
-      </c>
-      <c r="E43" s="97">
-        <f>'Nach Mannschaften sortiert'!E62</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="54">
-        <f>'Nach Mannschaften sortiert'!F62</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="54">
-        <f>'Nach Mannschaften sortiert'!G62</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="54">
-        <f>'Nach Mannschaften sortiert'!H62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="50">
-        <f>'Nach Mannschaften sortiert'!A65</f>
-        <v>64</v>
-      </c>
-      <c r="B44" s="50">
-        <f>'Nach Mannschaften sortiert'!B65</f>
-        <v>3</v>
-      </c>
-      <c r="C44" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C65</f>
-        <v>U12_1</v>
-      </c>
-      <c r="D44" s="51">
-        <f>'Nach Mannschaften sortiert'!D65</f>
-        <v>46045</v>
-      </c>
-      <c r="E44" s="101">
-        <f>'Nach Mannschaften sortiert'!E65</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="50">
-        <f>'Nach Mannschaften sortiert'!F65</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="50">
-        <f>'Nach Mannschaften sortiert'!G65</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="50">
-        <f>'Nach Mannschaften sortiert'!H65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="50">
-        <f>'Nach Mannschaften sortiert'!A56</f>
-        <v>55</v>
-      </c>
-      <c r="B45" s="50">
-        <f>'Nach Mannschaften sortiert'!B56</f>
-        <v>4</v>
-      </c>
-      <c r="C45" s="50" t="str">
-        <f>'Nach Mannschaften sortiert'!C56</f>
-        <v>U14</v>
-      </c>
-      <c r="D45" s="51">
-        <f>'Nach Mannschaften sortiert'!D56</f>
-        <v>46036</v>
-      </c>
-      <c r="E45" s="101">
-        <f>'Nach Mannschaften sortiert'!E56</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="50">
-        <f>'Nach Mannschaften sortiert'!F56</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="50">
-        <f>'Nach Mannschaften sortiert'!G56</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="50">
-        <f>'Nach Mannschaften sortiert'!H56</f>
         <v>0</v>
       </c>
     </row>
@@ -12212,137 +12284,137 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54">
-        <f>'Nach Mannschaften sortiert'!A64</f>
-        <v>63</v>
+        <f>'Nach Mannschaften sortiert'!A65</f>
+        <v>64</v>
       </c>
       <c r="B47" s="54">
-        <f>'Nach Mannschaften sortiert'!B64</f>
+        <f>'Nach Mannschaften sortiert'!B65</f>
         <v>2</v>
       </c>
       <c r="C47" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C64</f>
+        <f>'Nach Mannschaften sortiert'!C65</f>
         <v>U12_1</v>
       </c>
       <c r="D47" s="55">
-        <f>'Nach Mannschaften sortiert'!D64</f>
+        <f>'Nach Mannschaften sortiert'!D65</f>
         <v>46044</v>
       </c>
       <c r="E47" s="97">
-        <f>'Nach Mannschaften sortiert'!E64</f>
+        <f>'Nach Mannschaften sortiert'!E65</f>
         <v>0</v>
       </c>
       <c r="F47" s="54">
-        <f>'Nach Mannschaften sortiert'!F64</f>
+        <f>'Nach Mannschaften sortiert'!F65</f>
         <v>0</v>
       </c>
       <c r="G47" s="54">
-        <f>'Nach Mannschaften sortiert'!G64</f>
+        <f>'Nach Mannschaften sortiert'!G65</f>
         <v>0</v>
       </c>
       <c r="H47" s="54">
-        <f>'Nach Mannschaften sortiert'!H64</f>
+        <f>'Nach Mannschaften sortiert'!H65</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="48">
-        <f>'Nach Mannschaften sortiert'!A46</f>
-        <v>45</v>
+        <f>'Nach Mannschaften sortiert'!A47</f>
+        <v>46</v>
       </c>
       <c r="B48" s="48">
-        <f>'Nach Mannschaften sortiert'!B46</f>
+        <f>'Nach Mannschaften sortiert'!B47</f>
         <v>4</v>
       </c>
       <c r="C48" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C46</f>
+        <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U16</v>
       </c>
       <c r="D48" s="49">
-        <f>'Nach Mannschaften sortiert'!D46</f>
+        <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46026</v>
       </c>
       <c r="E48" s="99">
-        <f>'Nach Mannschaften sortiert'!E46</f>
+        <f>'Nach Mannschaften sortiert'!E47</f>
         <v>0</v>
       </c>
       <c r="F48" s="48">
-        <f>'Nach Mannschaften sortiert'!F46</f>
+        <f>'Nach Mannschaften sortiert'!F47</f>
         <v>0</v>
       </c>
       <c r="G48" s="48">
-        <f>'Nach Mannschaften sortiert'!G46</f>
+        <f>'Nach Mannschaften sortiert'!G47</f>
         <v>0</v>
       </c>
       <c r="H48" s="48">
-        <f>'Nach Mannschaften sortiert'!H46</f>
+        <f>'Nach Mannschaften sortiert'!H47</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="54">
-        <f>'Nach Mannschaften sortiert'!A66</f>
-        <v>65</v>
+        <f>'Nach Mannschaften sortiert'!A67</f>
+        <v>66</v>
       </c>
       <c r="B49" s="54">
-        <f>'Nach Mannschaften sortiert'!B66</f>
+        <f>'Nach Mannschaften sortiert'!B67</f>
         <v>4</v>
       </c>
       <c r="C49" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C66</f>
+        <f>'Nach Mannschaften sortiert'!C67</f>
         <v>U12_1</v>
       </c>
       <c r="D49" s="55">
-        <f>'Nach Mannschaften sortiert'!D66</f>
+        <f>'Nach Mannschaften sortiert'!D67</f>
         <v>46046</v>
       </c>
       <c r="E49" s="97">
-        <f>'Nach Mannschaften sortiert'!E66</f>
+        <f>'Nach Mannschaften sortiert'!E67</f>
         <v>0</v>
       </c>
       <c r="F49" s="54">
-        <f>'Nach Mannschaften sortiert'!F66</f>
+        <f>'Nach Mannschaften sortiert'!F67</f>
         <v>0</v>
       </c>
       <c r="G49" s="54">
-        <f>'Nach Mannschaften sortiert'!G66</f>
+        <f>'Nach Mannschaften sortiert'!G67</f>
         <v>0</v>
       </c>
       <c r="H49" s="54">
-        <f>'Nach Mannschaften sortiert'!H66</f>
+        <f>'Nach Mannschaften sortiert'!H67</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="54">
-        <f>'Nach Mannschaften sortiert'!A67</f>
-        <v>66</v>
+        <f>'Nach Mannschaften sortiert'!A68</f>
+        <v>67</v>
       </c>
       <c r="B50" s="54">
-        <f>'Nach Mannschaften sortiert'!B67</f>
+        <f>'Nach Mannschaften sortiert'!B68</f>
         <v>5</v>
       </c>
       <c r="C50" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C67</f>
+        <f>'Nach Mannschaften sortiert'!C68</f>
         <v>U12_1</v>
       </c>
       <c r="D50" s="55">
-        <f>'Nach Mannschaften sortiert'!D67</f>
+        <f>'Nach Mannschaften sortiert'!D68</f>
         <v>46047</v>
       </c>
       <c r="E50" s="97">
-        <f>'Nach Mannschaften sortiert'!E67</f>
+        <f>'Nach Mannschaften sortiert'!E68</f>
         <v>0</v>
       </c>
       <c r="F50" s="54">
-        <f>'Nach Mannschaften sortiert'!F67</f>
+        <f>'Nach Mannschaften sortiert'!F68</f>
         <v>0</v>
       </c>
       <c r="G50" s="54">
-        <f>'Nach Mannschaften sortiert'!G67</f>
+        <f>'Nach Mannschaften sortiert'!G68</f>
         <v>0</v>
       </c>
       <c r="H50" s="54">
-        <f>'Nach Mannschaften sortiert'!H67</f>
+        <f>'Nach Mannschaften sortiert'!H68</f>
         <v>0</v>
       </c>
     </row>
@@ -12382,69 +12454,69 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="48">
-        <f>'Nach Mannschaften sortiert'!A24</f>
-        <v>23</v>
+        <f>'Nach Mannschaften sortiert'!A25</f>
+        <v>24</v>
       </c>
       <c r="B52" s="48">
-        <f>'Nach Mannschaften sortiert'!B24</f>
+        <f>'Nach Mannschaften sortiert'!B25</f>
         <v>8</v>
       </c>
       <c r="C52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C24</f>
+        <f>'Nach Mannschaften sortiert'!C25</f>
         <v>KM</v>
       </c>
       <c r="D52" s="49">
-        <f>'Nach Mannschaften sortiert'!D24</f>
+        <f>'Nach Mannschaften sortiert'!D25</f>
         <v>46297</v>
       </c>
       <c r="E52" s="99">
-        <f>'Nach Mannschaften sortiert'!E24</f>
+        <f>'Nach Mannschaften sortiert'!E25</f>
         <v>0.79166666666666663</v>
       </c>
       <c r="F52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F24</f>
+        <f>'Nach Mannschaften sortiert'!F25</f>
         <v>Siegendorf</v>
       </c>
       <c r="G52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G24</f>
+        <f>'Nach Mannschaften sortiert'!G25</f>
         <v>Siegendorf</v>
       </c>
       <c r="H52" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H24</f>
+        <f>'Nach Mannschaften sortiert'!H25</f>
         <v>Auswärts</v>
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="54">
-        <f>'Nach Mannschaften sortiert'!A69</f>
-        <v>68</v>
+        <f>'Nach Mannschaften sortiert'!A70</f>
+        <v>69</v>
       </c>
       <c r="B53" s="54">
-        <f>'Nach Mannschaften sortiert'!B69</f>
+        <f>'Nach Mannschaften sortiert'!B70</f>
         <v>7</v>
       </c>
       <c r="C53" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C69</f>
+        <f>'Nach Mannschaften sortiert'!C70</f>
         <v>U12_1</v>
       </c>
       <c r="D53" s="55">
-        <f>'Nach Mannschaften sortiert'!D69</f>
+        <f>'Nach Mannschaften sortiert'!D70</f>
         <v>46049</v>
       </c>
       <c r="E53" s="97">
-        <f>'Nach Mannschaften sortiert'!E69</f>
+        <f>'Nach Mannschaften sortiert'!E70</f>
         <v>0</v>
       </c>
       <c r="F53" s="54">
-        <f>'Nach Mannschaften sortiert'!F69</f>
+        <f>'Nach Mannschaften sortiert'!F70</f>
         <v>0</v>
       </c>
       <c r="G53" s="54">
-        <f>'Nach Mannschaften sortiert'!G69</f>
+        <f>'Nach Mannschaften sortiert'!G70</f>
         <v>0</v>
       </c>
       <c r="H53" s="54">
-        <f>'Nach Mannschaften sortiert'!H69</f>
+        <f>'Nach Mannschaften sortiert'!H70</f>
         <v>0</v>
       </c>
     </row>
@@ -12484,137 +12556,137 @@
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="54">
-        <f>'Nach Mannschaften sortiert'!A83</f>
-        <v>82</v>
+        <f>'Nach Mannschaften sortiert'!A84</f>
+        <v>83</v>
       </c>
       <c r="B55" s="54">
-        <f>'Nach Mannschaften sortiert'!B83</f>
+        <f>'Nach Mannschaften sortiert'!B84</f>
         <v>1</v>
       </c>
       <c r="C55" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C83</f>
+        <f>'Nach Mannschaften sortiert'!C84</f>
         <v>U11</v>
       </c>
       <c r="D55" s="55">
-        <f>'Nach Mannschaften sortiert'!D83</f>
+        <f>'Nach Mannschaften sortiert'!D84</f>
         <v>46063</v>
       </c>
       <c r="E55" s="97">
-        <f>'Nach Mannschaften sortiert'!E83</f>
+        <f>'Nach Mannschaften sortiert'!E84</f>
         <v>0</v>
       </c>
       <c r="F55" s="54">
-        <f>'Nach Mannschaften sortiert'!F83</f>
+        <f>'Nach Mannschaften sortiert'!F84</f>
         <v>0</v>
       </c>
       <c r="G55" s="54">
-        <f>'Nach Mannschaften sortiert'!G83</f>
+        <f>'Nach Mannschaften sortiert'!G84</f>
         <v>0</v>
       </c>
       <c r="H55" s="54">
-        <f>'Nach Mannschaften sortiert'!H83</f>
+        <f>'Nach Mannschaften sortiert'!H84</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="48">
-        <f>'Nach Mannschaften sortiert'!A89</f>
-        <v>88</v>
+        <f>'Nach Mannschaften sortiert'!A90</f>
+        <v>89</v>
       </c>
       <c r="B56" s="48">
-        <f>'Nach Mannschaften sortiert'!B89</f>
+        <f>'Nach Mannschaften sortiert'!B90</f>
         <v>7</v>
       </c>
       <c r="C56" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C89</f>
+        <f>'Nach Mannschaften sortiert'!C90</f>
         <v>U11</v>
       </c>
       <c r="D56" s="49">
-        <f>'Nach Mannschaften sortiert'!D89</f>
+        <f>'Nach Mannschaften sortiert'!D90</f>
         <v>46069</v>
       </c>
       <c r="E56" s="99">
-        <f>'Nach Mannschaften sortiert'!E89</f>
+        <f>'Nach Mannschaften sortiert'!E90</f>
         <v>0</v>
       </c>
       <c r="F56" s="48">
-        <f>'Nach Mannschaften sortiert'!F89</f>
+        <f>'Nach Mannschaften sortiert'!F90</f>
         <v>0</v>
       </c>
       <c r="G56" s="48">
-        <f>'Nach Mannschaften sortiert'!G89</f>
+        <f>'Nach Mannschaften sortiert'!G90</f>
         <v>0</v>
       </c>
       <c r="H56" s="48">
-        <f>'Nach Mannschaften sortiert'!H89</f>
+        <f>'Nach Mannschaften sortiert'!H90</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="54">
-        <f>'Nach Mannschaften sortiert'!A86</f>
-        <v>85</v>
+        <f>'Nach Mannschaften sortiert'!A87</f>
+        <v>86</v>
       </c>
       <c r="B57" s="54">
-        <f>'Nach Mannschaften sortiert'!B86</f>
+        <f>'Nach Mannschaften sortiert'!B87</f>
         <v>4</v>
       </c>
       <c r="C57" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C86</f>
+        <f>'Nach Mannschaften sortiert'!C87</f>
         <v>U11</v>
       </c>
       <c r="D57" s="55">
-        <f>'Nach Mannschaften sortiert'!D86</f>
+        <f>'Nach Mannschaften sortiert'!D87</f>
         <v>46066</v>
       </c>
       <c r="E57" s="97">
-        <f>'Nach Mannschaften sortiert'!E86</f>
+        <f>'Nach Mannschaften sortiert'!E87</f>
         <v>0</v>
       </c>
       <c r="F57" s="54">
-        <f>'Nach Mannschaften sortiert'!F86</f>
+        <f>'Nach Mannschaften sortiert'!F87</f>
         <v>0</v>
       </c>
       <c r="G57" s="54">
-        <f>'Nach Mannschaften sortiert'!G86</f>
+        <f>'Nach Mannschaften sortiert'!G87</f>
         <v>0</v>
       </c>
       <c r="H57" s="54">
-        <f>'Nach Mannschaften sortiert'!H86</f>
+        <f>'Nach Mannschaften sortiert'!H87</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="48">
-        <f>'Nach Mannschaften sortiert'!A26</f>
-        <v>25</v>
+        <f>'Nach Mannschaften sortiert'!A27</f>
+        <v>26</v>
       </c>
       <c r="B58" s="48">
-        <f>'Nach Mannschaften sortiert'!B26</f>
+        <f>'Nach Mannschaften sortiert'!B27</f>
         <v>10</v>
       </c>
       <c r="C58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C26</f>
+        <f>'Nach Mannschaften sortiert'!C27</f>
         <v>KM</v>
       </c>
       <c r="D58" s="49">
-        <f>'Nach Mannschaften sortiert'!D26</f>
+        <f>'Nach Mannschaften sortiert'!D27</f>
         <v>46311</v>
       </c>
       <c r="E58" s="99">
-        <f>'Nach Mannschaften sortiert'!E26</f>
+        <f>'Nach Mannschaften sortiert'!E27</f>
         <v>0.8125</v>
       </c>
       <c r="F58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F26</f>
+        <f>'Nach Mannschaften sortiert'!F27</f>
         <v>Hornstein</v>
       </c>
       <c r="G58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G26</f>
+        <f>'Nach Mannschaften sortiert'!G27</f>
         <v>Hornstein</v>
       </c>
       <c r="H58" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H26</f>
+        <f>'Nach Mannschaften sortiert'!H27</f>
         <v>Auswärts</v>
       </c>
     </row>
@@ -12654,137 +12726,137 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="48">
-        <f>'Nach Mannschaften sortiert'!A60</f>
-        <v>59</v>
+        <f>'Nach Mannschaften sortiert'!A61</f>
+        <v>60</v>
       </c>
       <c r="B60" s="48">
-        <f>'Nach Mannschaften sortiert'!B60</f>
+        <f>'Nach Mannschaften sortiert'!B61</f>
         <v>8</v>
       </c>
       <c r="C60" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C60</f>
+        <f>'Nach Mannschaften sortiert'!C61</f>
         <v>U14</v>
       </c>
       <c r="D60" s="49">
-        <f>'Nach Mannschaften sortiert'!D60</f>
+        <f>'Nach Mannschaften sortiert'!D61</f>
         <v>46040</v>
       </c>
       <c r="E60" s="99">
-        <f>'Nach Mannschaften sortiert'!E60</f>
+        <f>'Nach Mannschaften sortiert'!E61</f>
         <v>0</v>
       </c>
       <c r="F60" s="48">
-        <f>'Nach Mannschaften sortiert'!F60</f>
+        <f>'Nach Mannschaften sortiert'!F61</f>
         <v>0</v>
       </c>
       <c r="G60" s="48">
-        <f>'Nach Mannschaften sortiert'!G60</f>
+        <f>'Nach Mannschaften sortiert'!G61</f>
         <v>0</v>
       </c>
       <c r="H60" s="48">
-        <f>'Nach Mannschaften sortiert'!H60</f>
+        <f>'Nach Mannschaften sortiert'!H61</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="54">
-        <f>'Nach Mannschaften sortiert'!A90</f>
-        <v>89</v>
+        <f>'Nach Mannschaften sortiert'!A91</f>
+        <v>90</v>
       </c>
       <c r="B61" s="54">
-        <f>'Nach Mannschaften sortiert'!B90</f>
+        <f>'Nach Mannschaften sortiert'!B91</f>
         <v>8</v>
       </c>
       <c r="C61" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C90</f>
+        <f>'Nach Mannschaften sortiert'!C91</f>
         <v>U11</v>
       </c>
       <c r="D61" s="55">
-        <f>'Nach Mannschaften sortiert'!D90</f>
+        <f>'Nach Mannschaften sortiert'!D91</f>
         <v>46070</v>
       </c>
       <c r="E61" s="97">
-        <f>'Nach Mannschaften sortiert'!E90</f>
+        <f>'Nach Mannschaften sortiert'!E91</f>
         <v>0</v>
       </c>
       <c r="F61" s="54">
-        <f>'Nach Mannschaften sortiert'!F90</f>
+        <f>'Nach Mannschaften sortiert'!F91</f>
         <v>0</v>
       </c>
       <c r="G61" s="54">
-        <f>'Nach Mannschaften sortiert'!G90</f>
+        <f>'Nach Mannschaften sortiert'!G91</f>
         <v>0</v>
       </c>
       <c r="H61" s="54">
-        <f>'Nach Mannschaften sortiert'!H90</f>
+        <f>'Nach Mannschaften sortiert'!H91</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="46">
-        <f>'Nach Mannschaften sortiert'!A61</f>
-        <v>60</v>
+        <f>'Nach Mannschaften sortiert'!A62</f>
+        <v>61</v>
       </c>
       <c r="B62" s="46">
-        <f>'Nach Mannschaften sortiert'!B61</f>
+        <f>'Nach Mannschaften sortiert'!B62</f>
         <v>9</v>
       </c>
       <c r="C62" s="46" t="str">
-        <f>'Nach Mannschaften sortiert'!C61</f>
+        <f>'Nach Mannschaften sortiert'!C62</f>
         <v>U14</v>
       </c>
       <c r="D62" s="47">
-        <f>'Nach Mannschaften sortiert'!D61</f>
+        <f>'Nach Mannschaften sortiert'!D62</f>
         <v>46041</v>
       </c>
       <c r="E62" s="100">
-        <f>'Nach Mannschaften sortiert'!E61</f>
+        <f>'Nach Mannschaften sortiert'!E62</f>
         <v>0</v>
       </c>
       <c r="F62" s="46">
-        <f>'Nach Mannschaften sortiert'!F61</f>
+        <f>'Nach Mannschaften sortiert'!F62</f>
         <v>0</v>
       </c>
       <c r="G62" s="46">
-        <f>'Nach Mannschaften sortiert'!G61</f>
+        <f>'Nach Mannschaften sortiert'!G62</f>
         <v>0</v>
       </c>
       <c r="H62" s="46">
-        <f>'Nach Mannschaften sortiert'!H61</f>
+        <f>'Nach Mannschaften sortiert'!H62</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="54">
-        <f>'Nach Mannschaften sortiert'!A92</f>
-        <v>91</v>
+        <f>'Nach Mannschaften sortiert'!A93</f>
+        <v>92</v>
       </c>
       <c r="B63" s="54">
-        <f>'Nach Mannschaften sortiert'!B92</f>
+        <f>'Nach Mannschaften sortiert'!B93</f>
         <v>10</v>
       </c>
       <c r="C63" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C92</f>
+        <f>'Nach Mannschaften sortiert'!C93</f>
         <v>U11</v>
       </c>
       <c r="D63" s="55">
-        <f>'Nach Mannschaften sortiert'!D92</f>
+        <f>'Nach Mannschaften sortiert'!D93</f>
         <v>46072</v>
       </c>
       <c r="E63" s="97">
-        <f>'Nach Mannschaften sortiert'!E92</f>
+        <f>'Nach Mannschaften sortiert'!E93</f>
         <v>0</v>
       </c>
       <c r="F63" s="54">
-        <f>'Nach Mannschaften sortiert'!F92</f>
+        <f>'Nach Mannschaften sortiert'!F93</f>
         <v>0</v>
       </c>
       <c r="G63" s="54">
-        <f>'Nach Mannschaften sortiert'!G92</f>
+        <f>'Nach Mannschaften sortiert'!G93</f>
         <v>0</v>
       </c>
       <c r="H63" s="54">
-        <f>'Nach Mannschaften sortiert'!H92</f>
+        <f>'Nach Mannschaften sortiert'!H93</f>
         <v>0</v>
       </c>
     </row>
@@ -12824,15 +12896,15 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="48">
-        <f>'Nach Mannschaften sortiert'!A91</f>
-        <v>90</v>
+        <f>'Nach Mannschaften sortiert'!A92</f>
+        <v>91</v>
       </c>
       <c r="B65" s="48">
-        <f>'Nach Mannschaften sortiert'!B91</f>
+        <f>'Nach Mannschaften sortiert'!B92</f>
         <v>9</v>
       </c>
       <c r="C65" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C91</f>
+        <f>'Nach Mannschaften sortiert'!C92</f>
         <v>U11</v>
       </c>
       <c r="D65" s="49">
@@ -12842,525 +12914,525 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F65" s="48">
-        <f>'Nach Mannschaften sortiert'!F91</f>
+        <f>'Nach Mannschaften sortiert'!F92</f>
         <v>0</v>
       </c>
       <c r="G65" s="48">
-        <f>'Nach Mannschaften sortiert'!G91</f>
+        <f>'Nach Mannschaften sortiert'!G92</f>
         <v>0</v>
       </c>
       <c r="H65" s="48">
-        <f>'Nach Mannschaften sortiert'!H91</f>
+        <f>'Nach Mannschaften sortiert'!H92</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="54">
-        <f>'Nach Mannschaften sortiert'!A99</f>
-        <v>98</v>
+        <f>'Nach Mannschaften sortiert'!A100</f>
+        <v>99</v>
       </c>
       <c r="B66" s="54">
-        <f>'Nach Mannschaften sortiert'!B99</f>
+        <f>'Nach Mannschaften sortiert'!B100</f>
         <v>2</v>
       </c>
       <c r="C66" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C99</f>
+        <f>'Nach Mannschaften sortiert'!C100</f>
         <v>U9</v>
       </c>
       <c r="D66" s="55">
-        <f>'Nach Mannschaften sortiert'!D99</f>
+        <f>'Nach Mannschaften sortiert'!D100</f>
         <v>46079</v>
       </c>
       <c r="E66" s="97">
-        <f>'Nach Mannschaften sortiert'!E99</f>
+        <f>'Nach Mannschaften sortiert'!E100</f>
         <v>0</v>
       </c>
       <c r="F66" s="54">
-        <f>'Nach Mannschaften sortiert'!F99</f>
+        <f>'Nach Mannschaften sortiert'!F100</f>
         <v>0</v>
       </c>
       <c r="G66" s="54">
-        <f>'Nach Mannschaften sortiert'!G99</f>
+        <f>'Nach Mannschaften sortiert'!G100</f>
         <v>0</v>
       </c>
       <c r="H66" s="54">
-        <f>'Nach Mannschaften sortiert'!H99</f>
+        <f>'Nach Mannschaften sortiert'!H100</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="54">
-        <f>'Nach Mannschaften sortiert'!A100</f>
-        <v>99</v>
+        <f>'Nach Mannschaften sortiert'!A101</f>
+        <v>100</v>
       </c>
       <c r="B67" s="54">
-        <f>'Nach Mannschaften sortiert'!B100</f>
+        <f>'Nach Mannschaften sortiert'!B101</f>
         <v>3</v>
       </c>
       <c r="C67" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C100</f>
+        <f>'Nach Mannschaften sortiert'!C101</f>
         <v>U9</v>
       </c>
       <c r="D67" s="55">
-        <f>'Nach Mannschaften sortiert'!D100</f>
+        <f>'Nach Mannschaften sortiert'!D101</f>
         <v>46080</v>
       </c>
       <c r="E67" s="97">
-        <f>'Nach Mannschaften sortiert'!E100</f>
+        <f>'Nach Mannschaften sortiert'!E101</f>
         <v>0</v>
       </c>
       <c r="F67" s="54">
-        <f>'Nach Mannschaften sortiert'!F100</f>
+        <f>'Nach Mannschaften sortiert'!F101</f>
         <v>0</v>
       </c>
       <c r="G67" s="54">
-        <f>'Nach Mannschaften sortiert'!G100</f>
+        <f>'Nach Mannschaften sortiert'!G101</f>
         <v>0</v>
       </c>
       <c r="H67" s="54">
-        <f>'Nach Mannschaften sortiert'!H100</f>
+        <f>'Nach Mannschaften sortiert'!H101</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="54">
-        <f>'Nach Mannschaften sortiert'!A101</f>
-        <v>100</v>
+        <f>'Nach Mannschaften sortiert'!A102</f>
+        <v>101</v>
       </c>
       <c r="B68" s="54">
-        <f>'Nach Mannschaften sortiert'!B101</f>
+        <f>'Nach Mannschaften sortiert'!B102</f>
         <v>4</v>
       </c>
       <c r="C68" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C101</f>
+        <f>'Nach Mannschaften sortiert'!C102</f>
         <v>U9</v>
       </c>
       <c r="D68" s="55">
-        <f>'Nach Mannschaften sortiert'!D101</f>
+        <f>'Nach Mannschaften sortiert'!D102</f>
         <v>46081</v>
       </c>
       <c r="E68" s="97">
-        <f>'Nach Mannschaften sortiert'!E101</f>
+        <f>'Nach Mannschaften sortiert'!E102</f>
         <v>0</v>
       </c>
       <c r="F68" s="54">
-        <f>'Nach Mannschaften sortiert'!F101</f>
+        <f>'Nach Mannschaften sortiert'!F102</f>
         <v>0</v>
       </c>
       <c r="G68" s="54">
-        <f>'Nach Mannschaften sortiert'!G101</f>
+        <f>'Nach Mannschaften sortiert'!G102</f>
         <v>0</v>
       </c>
       <c r="H68" s="54">
-        <f>'Nach Mannschaften sortiert'!H101</f>
+        <f>'Nach Mannschaften sortiert'!H102</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="54">
-        <f>'Nach Mannschaften sortiert'!A107</f>
-        <v>106</v>
+        <f>'Nach Mannschaften sortiert'!A108</f>
+        <v>107</v>
       </c>
       <c r="B69" s="54">
-        <f>'Nach Mannschaften sortiert'!B107</f>
+        <f>'Nach Mannschaften sortiert'!B108</f>
         <v>10</v>
       </c>
       <c r="C69" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C107</f>
+        <f>'Nach Mannschaften sortiert'!C108</f>
         <v>U9</v>
       </c>
       <c r="D69" s="55">
-        <f>'Nach Mannschaften sortiert'!D107</f>
+        <f>'Nach Mannschaften sortiert'!D108</f>
         <v>46087</v>
       </c>
       <c r="E69" s="97">
-        <f>'Nach Mannschaften sortiert'!E107</f>
+        <f>'Nach Mannschaften sortiert'!E108</f>
         <v>0</v>
       </c>
       <c r="F69" s="54">
-        <f>'Nach Mannschaften sortiert'!F107</f>
+        <f>'Nach Mannschaften sortiert'!F108</f>
         <v>0</v>
       </c>
       <c r="G69" s="54">
-        <f>'Nach Mannschaften sortiert'!G107</f>
+        <f>'Nach Mannschaften sortiert'!G108</f>
         <v>0</v>
       </c>
       <c r="H69" s="54">
-        <f>'Nach Mannschaften sortiert'!H107</f>
+        <f>'Nach Mannschaften sortiert'!H108</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="48">
-        <f>'Nach Mannschaften sortiert'!A68</f>
-        <v>67</v>
+        <f>'Nach Mannschaften sortiert'!A69</f>
+        <v>68</v>
       </c>
       <c r="B70" s="48">
-        <f>'Nach Mannschaften sortiert'!B68</f>
+        <f>'Nach Mannschaften sortiert'!B69</f>
         <v>6</v>
       </c>
       <c r="C70" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C68</f>
+        <f>'Nach Mannschaften sortiert'!C69</f>
         <v>U12_1</v>
       </c>
       <c r="D70" s="49">
-        <f>'Nach Mannschaften sortiert'!D68</f>
+        <f>'Nach Mannschaften sortiert'!D69</f>
         <v>46048</v>
       </c>
       <c r="E70" s="99">
-        <f>'Nach Mannschaften sortiert'!E68</f>
+        <f>'Nach Mannschaften sortiert'!E69</f>
         <v>0</v>
       </c>
       <c r="F70" s="48">
-        <f>'Nach Mannschaften sortiert'!F68</f>
+        <f>'Nach Mannschaften sortiert'!F69</f>
         <v>0</v>
       </c>
       <c r="G70" s="48">
-        <f>'Nach Mannschaften sortiert'!G68</f>
+        <f>'Nach Mannschaften sortiert'!G69</f>
         <v>0</v>
       </c>
       <c r="H70" s="48">
-        <f>'Nach Mannschaften sortiert'!H68</f>
+        <f>'Nach Mannschaften sortiert'!H69</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="54">
-        <f>'Nach Mannschaften sortiert'!A109</f>
-        <v>108</v>
+        <f>'Nach Mannschaften sortiert'!A110</f>
+        <v>109</v>
       </c>
       <c r="B71" s="54">
-        <f>'Nach Mannschaften sortiert'!B109</f>
+        <f>'Nach Mannschaften sortiert'!B110</f>
         <v>2</v>
       </c>
       <c r="C71" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C109</f>
+        <f>'Nach Mannschaften sortiert'!C110</f>
         <v>U8</v>
       </c>
       <c r="D71" s="55">
-        <f>'Nach Mannschaften sortiert'!D109</f>
+        <f>'Nach Mannschaften sortiert'!D110</f>
         <v>46089</v>
       </c>
       <c r="E71" s="97">
-        <f>'Nach Mannschaften sortiert'!E109</f>
+        <f>'Nach Mannschaften sortiert'!E110</f>
         <v>0</v>
       </c>
       <c r="F71" s="54">
-        <f>'Nach Mannschaften sortiert'!F109</f>
+        <f>'Nach Mannschaften sortiert'!F110</f>
         <v>0</v>
       </c>
       <c r="G71" s="54">
-        <f>'Nach Mannschaften sortiert'!G109</f>
+        <f>'Nach Mannschaften sortiert'!G110</f>
         <v>0</v>
       </c>
       <c r="H71" s="54">
-        <f>'Nach Mannschaften sortiert'!H109</f>
+        <f>'Nach Mannschaften sortiert'!H110</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="54">
-        <f>'Nach Mannschaften sortiert'!A110</f>
-        <v>109</v>
+        <f>'Nach Mannschaften sortiert'!A111</f>
+        <v>110</v>
       </c>
       <c r="B72" s="54">
-        <f>'Nach Mannschaften sortiert'!B110</f>
+        <f>'Nach Mannschaften sortiert'!B111</f>
         <v>3</v>
       </c>
       <c r="C72" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C110</f>
+        <f>'Nach Mannschaften sortiert'!C111</f>
         <v>U8</v>
       </c>
       <c r="D72" s="55">
-        <f>'Nach Mannschaften sortiert'!D110</f>
+        <f>'Nach Mannschaften sortiert'!D111</f>
         <v>46090</v>
       </c>
       <c r="E72" s="97">
-        <f>'Nach Mannschaften sortiert'!E110</f>
+        <f>'Nach Mannschaften sortiert'!E111</f>
         <v>0</v>
       </c>
       <c r="F72" s="54">
-        <f>'Nach Mannschaften sortiert'!F110</f>
+        <f>'Nach Mannschaften sortiert'!F111</f>
         <v>0</v>
       </c>
       <c r="G72" s="54">
-        <f>'Nach Mannschaften sortiert'!G110</f>
+        <f>'Nach Mannschaften sortiert'!G111</f>
         <v>0</v>
       </c>
       <c r="H72" s="54">
-        <f>'Nach Mannschaften sortiert'!H110</f>
+        <f>'Nach Mannschaften sortiert'!H111</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="54">
-        <f>'Nach Mannschaften sortiert'!A111</f>
-        <v>110</v>
+        <f>'Nach Mannschaften sortiert'!A112</f>
+        <v>111</v>
       </c>
       <c r="B73" s="54">
-        <f>'Nach Mannschaften sortiert'!B111</f>
+        <f>'Nach Mannschaften sortiert'!B112</f>
         <v>4</v>
       </c>
       <c r="C73" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C111</f>
+        <f>'Nach Mannschaften sortiert'!C112</f>
         <v>U8</v>
       </c>
       <c r="D73" s="55">
-        <f>'Nach Mannschaften sortiert'!D111</f>
+        <f>'Nach Mannschaften sortiert'!D112</f>
         <v>46091</v>
       </c>
       <c r="E73" s="97">
-        <f>'Nach Mannschaften sortiert'!E111</f>
+        <f>'Nach Mannschaften sortiert'!E112</f>
         <v>0</v>
       </c>
       <c r="F73" s="54">
-        <f>'Nach Mannschaften sortiert'!F111</f>
+        <f>'Nach Mannschaften sortiert'!F112</f>
         <v>0</v>
       </c>
       <c r="G73" s="54">
-        <f>'Nach Mannschaften sortiert'!G111</f>
+        <f>'Nach Mannschaften sortiert'!G112</f>
         <v>0</v>
       </c>
       <c r="H73" s="54">
-        <f>'Nach Mannschaften sortiert'!H111</f>
+        <f>'Nach Mannschaften sortiert'!H112</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="54">
-        <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>111</v>
+        <f>'Nach Mannschaften sortiert'!A113</f>
+        <v>112</v>
       </c>
       <c r="B74" s="54">
-        <f>'Nach Mannschaften sortiert'!B112</f>
+        <f>'Nach Mannschaften sortiert'!B113</f>
         <v>5</v>
       </c>
       <c r="C74" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C112</f>
+        <f>'Nach Mannschaften sortiert'!C113</f>
         <v>U8</v>
       </c>
       <c r="D74" s="55">
-        <f>'Nach Mannschaften sortiert'!D112</f>
+        <f>'Nach Mannschaften sortiert'!D113</f>
         <v>46092</v>
       </c>
       <c r="E74" s="97">
-        <f>'Nach Mannschaften sortiert'!E112</f>
+        <f>'Nach Mannschaften sortiert'!E113</f>
         <v>0</v>
       </c>
       <c r="F74" s="54">
-        <f>'Nach Mannschaften sortiert'!F112</f>
+        <f>'Nach Mannschaften sortiert'!F113</f>
         <v>0</v>
       </c>
       <c r="G74" s="54">
-        <f>'Nach Mannschaften sortiert'!G112</f>
+        <f>'Nach Mannschaften sortiert'!G113</f>
         <v>0</v>
       </c>
       <c r="H74" s="54">
-        <f>'Nach Mannschaften sortiert'!H112</f>
+        <f>'Nach Mannschaften sortiert'!H113</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="48">
-        <f>'Nach Mannschaften sortiert'!A29</f>
-        <v>28</v>
+        <f>'Nach Mannschaften sortiert'!A30</f>
+        <v>29</v>
       </c>
       <c r="B75" s="48">
-        <f>'Nach Mannschaften sortiert'!B29</f>
+        <f>'Nach Mannschaften sortiert'!B30</f>
         <v>13</v>
       </c>
       <c r="C75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C29</f>
+        <f>'Nach Mannschaften sortiert'!C30</f>
         <v>KM</v>
       </c>
       <c r="D75" s="49">
-        <f>'Nach Mannschaften sortiert'!D29</f>
+        <f>'Nach Mannschaften sortiert'!D30</f>
         <v>46333</v>
       </c>
       <c r="E75" s="99">
-        <f>'Nach Mannschaften sortiert'!E29</f>
+        <f>'Nach Mannschaften sortiert'!E30</f>
         <v>0.6875</v>
       </c>
       <c r="F75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!F29</f>
+        <f>'Nach Mannschaften sortiert'!F30</f>
         <v>Neufeld</v>
       </c>
       <c r="G75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!G29</f>
+        <f>'Nach Mannschaften sortiert'!G30</f>
         <v>Andau</v>
       </c>
       <c r="H75" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!H29</f>
+        <f>'Nach Mannschaften sortiert'!H30</f>
         <v>Heim</v>
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="54">
-        <f>'Nach Mannschaften sortiert'!A114</f>
-        <v>113</v>
+        <f>'Nach Mannschaften sortiert'!A115</f>
+        <v>114</v>
       </c>
       <c r="B76" s="54">
-        <f>'Nach Mannschaften sortiert'!B114</f>
+        <f>'Nach Mannschaften sortiert'!B115</f>
         <v>2</v>
       </c>
       <c r="C76" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C114</f>
+        <f>'Nach Mannschaften sortiert'!C115</f>
         <v>U7</v>
       </c>
       <c r="D76" s="55">
-        <f>'Nach Mannschaften sortiert'!D114</f>
+        <f>'Nach Mannschaften sortiert'!D115</f>
         <v>46094</v>
       </c>
       <c r="E76" s="97">
-        <f>'Nach Mannschaften sortiert'!E114</f>
+        <f>'Nach Mannschaften sortiert'!E115</f>
         <v>0</v>
       </c>
       <c r="F76" s="54">
-        <f>'Nach Mannschaften sortiert'!F114</f>
+        <f>'Nach Mannschaften sortiert'!F115</f>
         <v>0</v>
       </c>
       <c r="G76" s="54">
-        <f>'Nach Mannschaften sortiert'!G114</f>
+        <f>'Nach Mannschaften sortiert'!G115</f>
         <v>0</v>
       </c>
       <c r="H76" s="54">
-        <f>'Nach Mannschaften sortiert'!H114</f>
+        <f>'Nach Mannschaften sortiert'!H115</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="54">
-        <f>'Nach Mannschaften sortiert'!A115</f>
-        <v>114</v>
+        <f>'Nach Mannschaften sortiert'!A116</f>
+        <v>115</v>
       </c>
       <c r="B77" s="54">
-        <f>'Nach Mannschaften sortiert'!B115</f>
+        <f>'Nach Mannschaften sortiert'!B116</f>
         <v>3</v>
       </c>
       <c r="C77" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C115</f>
+        <f>'Nach Mannschaften sortiert'!C116</f>
         <v>U7</v>
       </c>
       <c r="D77" s="55">
-        <f>'Nach Mannschaften sortiert'!D115</f>
+        <f>'Nach Mannschaften sortiert'!D116</f>
         <v>46095</v>
       </c>
       <c r="E77" s="97">
-        <f>'Nach Mannschaften sortiert'!E115</f>
+        <f>'Nach Mannschaften sortiert'!E116</f>
         <v>0</v>
       </c>
       <c r="F77" s="54">
-        <f>'Nach Mannschaften sortiert'!F115</f>
+        <f>'Nach Mannschaften sortiert'!F116</f>
         <v>0</v>
       </c>
       <c r="G77" s="54">
-        <f>'Nach Mannschaften sortiert'!G115</f>
+        <f>'Nach Mannschaften sortiert'!G116</f>
         <v>0</v>
       </c>
       <c r="H77" s="54">
-        <f>'Nach Mannschaften sortiert'!H115</f>
+        <f>'Nach Mannschaften sortiert'!H116</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="54">
-        <f>'Nach Mannschaften sortiert'!A116</f>
-        <v>115</v>
+        <f>'Nach Mannschaften sortiert'!A117</f>
+        <v>116</v>
       </c>
       <c r="B78" s="54">
-        <f>'Nach Mannschaften sortiert'!B116</f>
+        <f>'Nach Mannschaften sortiert'!B117</f>
         <v>4</v>
       </c>
       <c r="C78" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C116</f>
+        <f>'Nach Mannschaften sortiert'!C117</f>
         <v>U7</v>
       </c>
       <c r="D78" s="55">
-        <f>'Nach Mannschaften sortiert'!D116</f>
+        <f>'Nach Mannschaften sortiert'!D117</f>
         <v>46096</v>
       </c>
       <c r="E78" s="97">
-        <f>'Nach Mannschaften sortiert'!E116</f>
+        <f>'Nach Mannschaften sortiert'!E117</f>
         <v>0</v>
       </c>
       <c r="F78" s="54">
-        <f>'Nach Mannschaften sortiert'!F116</f>
+        <f>'Nach Mannschaften sortiert'!F117</f>
         <v>0</v>
       </c>
       <c r="G78" s="54">
-        <f>'Nach Mannschaften sortiert'!G116</f>
+        <f>'Nach Mannschaften sortiert'!G117</f>
         <v>0</v>
       </c>
       <c r="H78" s="54">
-        <f>'Nach Mannschaften sortiert'!H116</f>
+        <f>'Nach Mannschaften sortiert'!H117</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="54">
-        <f>'Nach Mannschaften sortiert'!A117</f>
-        <v>116</v>
+        <f>'Nach Mannschaften sortiert'!A118</f>
+        <v>117</v>
       </c>
       <c r="B79" s="54">
-        <f>'Nach Mannschaften sortiert'!B117</f>
+        <f>'Nach Mannschaften sortiert'!B118</f>
         <v>5</v>
       </c>
       <c r="C79" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C117</f>
+        <f>'Nach Mannschaften sortiert'!C118</f>
         <v>U7</v>
       </c>
       <c r="D79" s="55">
-        <f>'Nach Mannschaften sortiert'!D117</f>
+        <f>'Nach Mannschaften sortiert'!D118</f>
         <v>46097</v>
       </c>
       <c r="E79" s="97">
-        <f>'Nach Mannschaften sortiert'!E117</f>
+        <f>'Nach Mannschaften sortiert'!E118</f>
         <v>0</v>
       </c>
       <c r="F79" s="54">
-        <f>'Nach Mannschaften sortiert'!F117</f>
+        <f>'Nach Mannschaften sortiert'!F118</f>
         <v>0</v>
       </c>
       <c r="G79" s="54">
-        <f>'Nach Mannschaften sortiert'!G117</f>
+        <f>'Nach Mannschaften sortiert'!G118</f>
         <v>0</v>
       </c>
       <c r="H79" s="54">
-        <f>'Nach Mannschaften sortiert'!H117</f>
+        <f>'Nach Mannschaften sortiert'!H118</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="48">
-        <f>'Nach Mannschaften sortiert'!A70</f>
-        <v>69</v>
+        <f>'Nach Mannschaften sortiert'!A71</f>
+        <v>70</v>
       </c>
       <c r="B80" s="48">
-        <f>'Nach Mannschaften sortiert'!B70</f>
+        <f>'Nach Mannschaften sortiert'!B71</f>
         <v>8</v>
       </c>
       <c r="C80" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C70</f>
+        <f>'Nach Mannschaften sortiert'!C71</f>
         <v>U12_1</v>
       </c>
       <c r="D80" s="49">
-        <f>'Nach Mannschaften sortiert'!D70</f>
+        <f>'Nach Mannschaften sortiert'!D71</f>
         <v>46050</v>
       </c>
       <c r="E80" s="99">
-        <f>'Nach Mannschaften sortiert'!E70</f>
+        <f>'Nach Mannschaften sortiert'!E71</f>
         <v>0</v>
       </c>
       <c r="F80" s="48">
-        <f>'Nach Mannschaften sortiert'!F70</f>
+        <f>'Nach Mannschaften sortiert'!F71</f>
         <v>0</v>
       </c>
       <c r="G80" s="48">
-        <f>'Nach Mannschaften sortiert'!G70</f>
+        <f>'Nach Mannschaften sortiert'!G71</f>
         <v>0</v>
       </c>
       <c r="H80" s="48">
-        <f>'Nach Mannschaften sortiert'!H70</f>
+        <f>'Nach Mannschaften sortiert'!H71</f>
         <v>0</v>
       </c>
     </row>
@@ -13400,35 +13472,35 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="48">
-        <f>'Nach Mannschaften sortiert'!A52</f>
-        <v>51</v>
+        <f>'Nach Mannschaften sortiert'!A53</f>
+        <v>52</v>
       </c>
       <c r="B82" s="48">
-        <f>'Nach Mannschaften sortiert'!B52</f>
+        <f>'Nach Mannschaften sortiert'!B53</f>
         <v>10</v>
       </c>
       <c r="C82" s="48" t="str">
-        <f>'Nach Mannschaften sortiert'!C52</f>
+        <f>'Nach Mannschaften sortiert'!C53</f>
         <v>U16</v>
       </c>
       <c r="D82" s="49">
-        <f>'Nach Mannschaften sortiert'!D52</f>
+        <f>'Nach Mannschaften sortiert'!D53</f>
         <v>46032</v>
       </c>
       <c r="E82" s="99">
-        <f>'Nach Mannschaften sortiert'!E52</f>
+        <f>'Nach Mannschaften sortiert'!E53</f>
         <v>0</v>
       </c>
       <c r="F82" s="48">
-        <f>'Nach Mannschaften sortiert'!F52</f>
+        <f>'Nach Mannschaften sortiert'!F53</f>
         <v>0</v>
       </c>
       <c r="G82" s="48">
-        <f>'Nach Mannschaften sortiert'!G52</f>
+        <f>'Nach Mannschaften sortiert'!G53</f>
         <v>0</v>
       </c>
       <c r="H82" s="48">
-        <f>'Nach Mannschaften sortiert'!H52</f>
+        <f>'Nach Mannschaften sortiert'!H53</f>
         <v>0</v>
       </c>
     </row>
@@ -13468,35 +13540,35 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="54">
-        <f>'Nach Mannschaften sortiert'!A129</f>
-        <v>128</v>
+        <f>'Nach Mannschaften sortiert'!A130</f>
+        <v>129</v>
       </c>
       <c r="B84" s="54">
-        <f>'Nach Mannschaften sortiert'!B129</f>
+        <f>'Nach Mannschaften sortiert'!B130</f>
         <v>2</v>
       </c>
       <c r="C84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C129</f>
+        <f>'Nach Mannschaften sortiert'!C130</f>
         <v>GGG</v>
       </c>
       <c r="D84" s="55">
-        <f>'Nach Mannschaften sortiert'!D129</f>
+        <f>'Nach Mannschaften sortiert'!D130</f>
         <v>46256</v>
       </c>
       <c r="E84" s="97">
-        <f>'Nach Mannschaften sortiert'!E129</f>
+        <f>'Nach Mannschaften sortiert'!E130</f>
         <v>0.375</v>
       </c>
       <c r="F84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!F129</f>
+        <f>'Nach Mannschaften sortiert'!F130</f>
         <v>Neufeld</v>
       </c>
       <c r="G84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!G129</f>
+        <f>'Nach Mannschaften sortiert'!G130</f>
         <v>viele Gegner</v>
       </c>
       <c r="H84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!H129</f>
+        <f>'Nach Mannschaften sortiert'!H130</f>
         <v>Heim</v>
       </c>
     </row>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDCCC93-2A47-4BDD-8109-A987BA81C35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA803324-4EC7-44D0-97CE-1FC311279E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="181">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -585,6 +585,12 @@
   </si>
   <si>
     <t>SPG Theresienfeld</t>
+  </si>
+  <si>
+    <t>Fest ASV Neufeld</t>
+  </si>
+  <si>
+    <t>Oktoberfest 2026</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1090,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1354,6 +1360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -1593,7 +1600,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="54" bestFit="1" customWidth="1"/>
@@ -3963,7 +3970,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
-        <f t="shared" ref="A106:A137" si="3">A105+1</f>
+        <f t="shared" ref="A106:A138" si="3">A105+1</f>
         <v>105</v>
       </c>
       <c r="B106" s="8">
@@ -4726,6 +4733,33 @@
         <v>53</v>
       </c>
       <c r="H137" s="54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" s="117" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="54">
+        <f t="shared" si="3"/>
+        <v>137</v>
+      </c>
+      <c r="B138" s="54">
+        <v>0</v>
+      </c>
+      <c r="C138" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D138" s="55">
+        <v>46291</v>
+      </c>
+      <c r="E138" s="95">
+        <v>0.75</v>
+      </c>
+      <c r="F138" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="G138" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="H138" s="54" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4746,7 +4780,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="84" customWidth="1"/>
@@ -10107,6 +10141,44 @@
         <v>71</v>
       </c>
       <c r="L137" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="138" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B138" s="81">
+        <f>'Nach Mannschaften sortiert'!D138</f>
+        <v>46291</v>
+      </c>
+      <c r="C138" s="96">
+        <f>'Nach Mannschaften sortiert'!E138</f>
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="96">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="E138" s="96" t="str">
+        <f>UPPER('Nach Mannschaften sortiert'!F138)</f>
+        <v>NEUFELD</v>
+      </c>
+      <c r="G138" s="117" t="str">
+        <f>'Nach Mannschaften sortiert'!H138</f>
+        <v>Heim</v>
+      </c>
+      <c r="H138" s="117" t="str">
+        <f>'Nach Mannschaften sortiert'!G138</f>
+        <v>Oktoberfest 2026</v>
+      </c>
+      <c r="I138" s="117" t="str">
+        <f>'Nach Mannschaften sortiert'!C138</f>
+        <v>Fest ASV Neufeld</v>
+      </c>
+      <c r="J138" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="K138" s="117" t="s">
+        <v>71</v>
+      </c>
+      <c r="L138" s="117" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10356,16 +10428,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
@@ -10392,7 +10464,7 @@
       <c r="H2" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="I2" s="120" t="s">
+      <c r="I2" s="121" t="s">
         <v>117</v>
       </c>
       <c r="J2" s="39"/>
@@ -10412,7 +10484,7 @@
       <c r="F3" s="61"/>
       <c r="G3" s="61"/>
       <c r="H3" s="63"/>
-      <c r="I3" s="121"/>
+      <c r="I3" s="122"/>
       <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10432,7 +10504,7 @@
       </c>
       <c r="G4" s="61"/>
       <c r="H4" s="63"/>
-      <c r="I4" s="121"/>
+      <c r="I4" s="122"/>
       <c r="J4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10452,7 +10524,7 @@
       </c>
       <c r="G5" s="61"/>
       <c r="H5" s="63"/>
-      <c r="I5" s="121"/>
+      <c r="I5" s="122"/>
       <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10472,7 +10544,7 @@
       </c>
       <c r="G6" s="65"/>
       <c r="H6" s="63"/>
-      <c r="I6" s="121"/>
+      <c r="I6" s="122"/>
       <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10494,7 +10566,7 @@
         <v>127</v>
       </c>
       <c r="H7" s="63"/>
-      <c r="I7" s="121"/>
+      <c r="I7" s="122"/>
       <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10516,7 +10588,7 @@
         <v>127</v>
       </c>
       <c r="H8" s="63"/>
-      <c r="I8" s="121"/>
+      <c r="I8" s="122"/>
       <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10540,7 +10612,7 @@
       <c r="H9" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="I9" s="121"/>
+      <c r="I9" s="122"/>
       <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -10562,7 +10634,7 @@
         <v>134</v>
       </c>
       <c r="H10" s="63"/>
-      <c r="I10" s="121"/>
+      <c r="I10" s="122"/>
       <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10582,7 +10654,7 @@
         <v>138</v>
       </c>
       <c r="H11" s="72"/>
-      <c r="I11" s="122"/>
+      <c r="I11" s="123"/>
       <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
@@ -10640,52 +10712,52 @@
       <c r="H14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="124" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="119"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="125" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="119"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="120"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="127" t="s">
+      <c r="A17" s="128" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="119"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="120"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="117" t="s">
+      <c r="A18" s="118" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="119"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="120"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
